--- a/data_evaluation/playwright/ragas_results_llm_retriever.xlsx
+++ b/data_evaluation/playwright/ragas_results_llm_retriever.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,35 +444,45 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>total_tokens</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>answer_accuracy</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>factual_correctness</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>helpfulness</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>rouge_score(mode=precision)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>rouge_score(mode=recall)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>context_precision</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>context_recall</t>
         </is>
@@ -486,7 +496,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['Other locators | Playwright', "Locator (https://playwright.dev/docs/api/class-locator)\ns are the central piece of Playwright's auto-waiting and retry-ability. In a nutshell, locators represent a way to find element(s) on the page at any moment.", 'Playwright comes with multiple built-in locators. To make tests resilient, we recommend prioritizing user-facing attributes and explicit contracts such as\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign in\n```\n`&lt;button&gt;Sign in&lt;/button&gt;`\n```\n\nLocate the element by its role of\n`button`\nwith name "Sign in".\n\n```\n`awaitpage.getByRole(\'button\',{name:\'Sign in\'}).click();`\n```\n\nnote\nUse the\ncode generator (https://playwright.dev/docs/codegen)\nto generate a locator, and then edit it as you\'d like.\n\nEvery time a locator is used for an action, an up-to-date DOM element is located in the page. In the snippet below, the underlying DOM element will be located twice, once prior to every action. This means that if the DOM changes in between the calls due to re-render, the new element corresponding to the locator will be used.\n\n```\n`constlocator=page.getByRole(\'button\',{name:\'Sign in\'});awaitlocator.hover();awaitlocator.click();`\n```\n\nNote that all methods that create a locator, such as\npage.getByLabel() (https://playwright.dev/docs/api/class-page#page-get-by-label)\n, are also available on the\nLocator (https://playwright.dev/docs/api/class-locator)\nand\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\nclasses, so you can chain them and iteratively narrow down your locator.\n\n```\n`constlocator=page.frameLocator(\'#my-frame\').getByRole(\'button\',{name:\'Sign in\'});awaitlocator.click();`\n```', 'The\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\nlocator reflects how users and assistive technology perceive the page, for example whether some element is a button or a checkbox. When locating by role, you should usually pass the accessible name as well, so that the locator pinpoints the exact element.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign up\nSubscribe\nSubmit\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nRole locators include\nbuttons, checkboxes, headings, links, lists, tables, and many more (https://www.w3.org/TR/html-aria/#docconformance)\nand follow W3C specifications for\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. Note that many html elements like\n`&lt;button&gt;`\nhave an\nimplicitly defined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role locator.\n\nNote that role locators\ndo not replace\naccessibility audits and conformance tests, but rather give early feedback about the ARIA guidelines.\n\nWhen to use role locators\nWe recommend prioritizing role locators to locate elements, as it is the closest way to how users and assistive technology perceive the page.', "These are the recommended built-in locators.\n\npage.getByRole() (https://playwright.dev/docs/locators#locate-by-role)\nto locate by explicit and implicit accessibility attributes.\npage.getByText() (https://playwright.dev/docs/locators#locate-by-text)\nto locate by text content.\npage.getByLabel() (https://playwright.dev/docs/locators#locate-by-label)\nto locate a form control by associated label's text.\npage.getByPlaceholder() (https://playwright.dev/docs/locators#locate-by-placeholder)\nto locate an input by placeholder.\npage.getByAltText() (https://playwright.dev/docs/locators#locate-by-alt-text)\nto locate an element, usually image, by its text alternative.\npage.getByTitle() (https://playwright.dev/docs/locators#locate-by-title)\nto locate an element by its title attribute.\npage.getByTestId() (https://playwright.dev/docs/locators#locate-by-test-id)\nto locate an element based on its\n`data-testid`\nattribute (other attributes can be configured).\n\n```\n`awaitpage.getByLabel('User Name').fill('John');awaitpage.getByLabel('Password').fill('secret-password');awaitpage.getByRole('button',{name:'Sign in'}).click();awaitexpect(page.getByText('Welcome, John!')).toBeVisible();`\n```"]</t>
+          <t>['The\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\nlocator reflects how users and assistive technology perceive the page, for example whether some element is a button or a checkbox. When locating by role, you should usually pass the accessible name as well, so that the locator pinpoints the exact element.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign up\nSubscribe\nSubmit\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nRole locators include\nbuttons, checkboxes, headings, links, lists, tables, and many more (https://www.w3.org/TR/html-aria/#docconformance)\nand follow W3C specifications for\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. Note that many html elements like\n`&lt;button&gt;`\nhave an\nimplicitly defined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role locator.\n\nNote that role locators\ndo not replace\naccessibility audits and conformance tests, but rather give early feedback about the ARIA guidelines.\n\nWhen to use role locators\nWe recommend prioritizing role locators to locate elements, as it is the closest way to how users and assistive technology perceive the page.', 'Locators | Playwright', "Locator | Playwright\n\nLocators are the central piece of Playwright's auto-waiting and retry-ability. In a nutshell, locators represent a way to find element(s) on the page at any moment. A locator can be created with the\npage.locator() (https://playwright.dev/docs/api/class-page#page-locator)\nmethod.\n\nLearn more about locators (https://playwright.dev/docs/locators)\n.", "These are the recommended built-in locators.\n\npage.getByRole() (https://playwright.dev/docs/locators#locate-by-role)\nto locate by explicit and implicit accessibility attributes.\npage.getByText() (https://playwright.dev/docs/locators#locate-by-text)\nto locate by text content.\npage.getByLabel() (https://playwright.dev/docs/locators#locate-by-label)\nto locate a form control by associated label's text.\npage.getByPlaceholder() (https://playwright.dev/docs/locators#locate-by-placeholder)\nto locate an input by placeholder.\npage.getByAltText() (https://playwright.dev/docs/locators#locate-by-alt-text)\nto locate an element, usually image, by its text alternative.\npage.getByTitle() (https://playwright.dev/docs/locators#locate-by-title)\nto locate an element by its title attribute.\npage.getByTestId() (https://playwright.dev/docs/locators#locate-by-test-id)\nto locate an element based on its\n`data-testid`\nattribute (other attributes can be configured).\n\n```\n`awaitpage.getByLabel('User Name').fill('John');awaitpage.getByLabel('Password').fill('secret-password');awaitpage.getByRole('button',{name:'Sign in'}).click();awaitexpect(page.getByText('Welcome, John!')).toBeVisible();`\n```"]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,9 +506,10 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The recommended way to target a button by the label a user would read on it is to use `page.getByRole()`, passing `'button'` as the role and the button's text as the `name`.
+          <t>The recommended way to target a button by the label a user would read on it is to use `page.getByRole()`. You should pass `'button'` as the role and the button's accessible name as the `name` option.
 For example:
-`await page.getByRole('button', { name: 'Sign in' }).click();`</t>
+`await page.getByRole('button', { name: 'Submit' }).click();`
+Playwright recommends prioritizing role locators because they reflect how users and assistive technology perceive the page.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -507,24 +518,30 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.00838525</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>32466</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2045454545454546</v>
+        <v>0.91</v>
       </c>
       <c r="J2" t="n">
-        <v>0.28125</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4777777777618519</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L2" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.7499999999625</v>
+      </c>
+      <c r="N2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -536,7 +553,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', 'Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and\n`beforeEach`\nhooks is included in the test timeout.\n\nTimed out test produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Timeout of 30000ms exceeded.`\n```\n\nAdditional separate timeout, of the same value, is shared between fixture teardowns and\n`afterEach`\nhooks, after the test function has finished.\n\nThe same timeout value also applies to\n`beforeAll`\nand\n`afterAll`\nhooks, but they do not share time with any test.']</t>
+          <t>['Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', 'Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and\n`beforeEach`\nhooks is included in the test timeout.\n\nTimed out test produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Timeout of 30000ms exceeded.`\n```\n\nAdditional separate timeout, of the same value, is shared between fixture teardowns and\n`afterEach`\nhooks, after the test function has finished.\n\nThe same timeout value also applies to\n`beforeAll`\nand\n`afterAll`\nhooks, but they do not share time with any test.', "playwright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({timeout:120_000,});`\n```\n\nAPI reference:\ntestConfig.timeout (https://playwright.dev/docs/api/class-testconfig#test-config-timeout)\n."]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -547,10 +564,10 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>If you do not configure anything, a single test can run for 30,000 ms (30 seconds) before Playwright kills it.
-The time that counts toward this budget includes:
-*   The test function itself.
-*   Fixture setups.
-*   `beforeEach` hooks.</t>
+The time spent on the following counts toward that budget:
+*   The test function
+*   Fixture setups
+*   `beforeEach` hooks</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -559,24 +576,30 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.007680999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.89</v>
+        <v>29874</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3243243243243243</v>
+        <v>0.75</v>
       </c>
       <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.5217391304347826</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.49999999995</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -588,7 +611,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['PlaywrightAssertions | Playwright\n\nPlaywright gives you Web-First Assertions with convenience methods for creating assertions that will wait and retry until the expected condition is met.\n\nConsider the following example:\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'status becomes submitted\',async({page})=&gt;{// ...awaitpage.locator(\'#submit-button\').click();awaitexpect(page.locator(\'.status\')).toHaveText(\'Submitted\');});`\n```\n\nPlaywright will be re-testing the node with the selector\n`.status`\nuntil fetched Node has the\n`"Submitted"`\ntext. It will be re-fetching the node and checking it over and over, until the condition is met or until the timeout is reached. You can pass this timeout as an option.\n\nBy default, the timeout for assertions is set to 5 seconds.', 'Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Error: expect(received).toHaveText(expected)Expected string: "my text"Received string: ""Call log:- expect.toHaveText with timeout 5000ms- waiting for "locator(\'button\')"`\n```', 'Assertions | Playwright', 'Playwright includes test assertions in the form of\n`expect`\nfunction. To make an assertion, call\n`expect(value)`\nand choose a matcher that reflects the expectation. There are many\ngeneric matchers (https://playwright.dev/docs/api/class-genericassertions)\nlike\n`toEqual`\n,\n`toContain`\n,\n`toBeTruthy`\nthat can be used to assert any conditions.\n\n```\n`expect(success).toBeTruthy();`\n```\n\nPlaywright also includes web-specific\nasync matchers (https://playwright.dev/docs/api/class-locatorassertions)\nthat will wait until the expected condition is met. Consider the following example:\n\n```\n`awaitexpect(page.getByTestId(\'status\')).toHaveText(\'Submitted\');`\n```\n\nPlaywright will be re-testing the element with the test id of\n`status`\nuntil the fetched element has the\n`"Submitted"`\ntext. It will re-fetch the element and check it over and over, until the condition is met or until the timeout is reached. You can either pass this timeout or configure it once via the\ntestConfig.expect (https://playwright.dev/docs/api/class-testconfig#test-config-expect)\nvalue in the test config.\n\nBy default, the timeout for assertions is set to 5 seconds. Learn more about\nvarious timeouts (https://playwright.dev/docs/test-timeouts)\n.', 'Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`']</t>
+          <t>['PlaywrightAssertions | Playwright\n\nPlaywright gives you Web-First Assertions with convenience methods for creating assertions that will wait and retry until the expected condition is met.\n\nConsider the following example:\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'status becomes submitted\',async({page})=&gt;{// ...awaitpage.locator(\'#submit-button\').click();awaitexpect(page.locator(\'.status\')).toHaveText(\'Submitted\');});`\n```\n\nPlaywright will be re-testing the node with the selector\n`.status`\nuntil fetched Node has the\n`"Submitted"`\ntext. It will be re-fetching the node and checking it over and over, until the condition is met or until the timeout is reached. You can pass this timeout as an option.\n\nBy default, the timeout for assertions is set to 5 seconds.', 'Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Error: expect(received).toHaveText(expected)Expected string: "my text"Received string: ""Call log:- expect.toHaveText with timeout 5000ms- waiting for "locator(\'button\')"`\n```', 'Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`']</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -598,7 +621,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Answer: By default, the timeout for web-first assertions like `toHaveText` is set to 5 seconds.</t>
+          <t>If you leave the defaults, a web-first assertion like `toHaveText` will retry for 5 seconds before giving up.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -607,24 +630,30 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.007599499999999999</v>
       </c>
       <c r="G4" t="n">
+        <v>29578</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.5</v>
       </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.3125</v>
-      </c>
       <c r="J4" t="n">
-        <v>0.25</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8874999999778125</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="L4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.9999999999666667</v>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -636,7 +665,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['Retries | Playwright', 'Playwright supports\ntest retries\n. When enabled, failing tests will be retried multiple times until they pass, or until the maximum number of retries is reached. By default failing tests are not retried.\n\n```\n`# Give failing tests 3 retry attemptsnpx playwrighttest--retries=3`\n```\n\nYou can configure retries in the configuration file:\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({// Give failing tests 3 retry attemptsretries:3,});`\n```\n\nPlaywright Test will categorize tests as follows:\n\n"passed" - tests that passed on the first run;\n"flaky" - tests that failed on the first run, but passed when retried;\n"failed" - tests that failed on the first run and failed all retries.\n\n```\n`Running3tests using1worker✓ example.spec.ts:4:2 › first passes(438ms)x example.spec.ts:5:2 › second flaky(691ms)✓ example.spec.ts:5:2 › second flaky(522ms)✓ example.spec.ts:6:2 › third passes(932ms)1flakyexample.spec.ts:5:2 › second flaky2passed(4s)`\n```\n\nYou can detect retries at runtime with\ntestInfo.retry (https://playwright.dev/docs/api/class-testinfo#test-info-retry)\n, which is accessible to any test, hook or fixture. Here is an example that clears some server-side state before a retry.\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'my test\',async({page},testInfo)=&gt;{if(testInfo.retry)awaitcleanSomeCachesOnTheServer();// ...});`\n```\n\nYou can specify retries for a specific group of tests or a single file with\ntest.describe.configure() (https://playwright.dev/docs/api/class-test#test-describe-configure)\n.\n\n```\n`import{test,expect}from\'@playwright/test\';test.describe(()=&gt;{// All tests in this describe group will get 2 retry attempts.test.describe.configure({retries:2});test(\'test 1\',async({page})=&gt;{// ...});test(\'test 2\',async({page})=&gt;{// ...});});`\n```', 'Command line | Playwright\n\nPlaywright provides a powerful command line interface for running tests, generating code, debugging, and more. The most up to date list of commands and arguments available on the CLI can always be retrieved via\n`npx playwright --help`\n.']</t>
+          <t>['Retries | Playwright', 'Command line | Playwright\n\nPlaywright provides a powerful command line interface for running tests, generating code, debugging, and more. The most up to date list of commands and arguments available on the CLI can always be retrieved via\n`npx playwright --help`\n.', 'Playwright supports\ntest retries\n. When enabled, failing tests will be retried multiple times until they pass, or until the maximum number of retries is reached. By default failing tests are not retried.\n\n```\n`# Give failing tests 3 retry attemptsnpx playwrighttest--retries=3`\n```\n\nYou can configure retries in the configuration file:\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({// Give failing tests 3 retry attemptsretries:3,});`\n```\n\nPlaywright Test will categorize tests as follows:\n\n"passed" - tests that passed on the first run;\n"flaky" - tests that failed on the first run, but passed when retried;\n"failed" - tests that failed on the first run and failed all retries.\n\n```\n`Running3tests using1worker✓ example.spec.ts:4:2 › first passes(438ms)x example.spec.ts:5:2 › second flaky(691ms)✓ example.spec.ts:5:2 › second flaky(522ms)✓ example.spec.ts:6:2 › third passes(932ms)1flakyexample.spec.ts:5:2 › second flaky2passed(4s)`\n```\n\nYou can detect retries at runtime with\ntestInfo.retry (https://playwright.dev/docs/api/class-testinfo#test-info-retry)\n, which is accessible to any test, hook or fixture. Here is an example that clears some server-side state before a retry.\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'my test\',async({page},testInfo)=&gt;{if(testInfo.retry)awaitcleanSomeCachesOnTheServer();// ...});`\n```\n\nYou can specify retries for a specific group of tests or a single file with\ntest.describe.configure() (https://playwright.dev/docs/api/class-test#test-describe-configure)\n.\n\n```\n`import{test,expect}from\'@playwright/test\';test.describe(()=&gt;{// All tests in this describe group will get 2 retry attempts.test.describe.configure({retries:2});test(\'test 1\',async({page})=&gt;{// ...});test(\'test 2\',async({page})=&gt;{// ...});});`\n```']</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -646,7 +675,8 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The quickest command-line way to re-run failing tests is to use the `--retries` flag:
+          <t>The quickest command-line way to re-run failing tests is to use the `--retries` flag with the `npx playwright test` command.
+For example, to give failing tests 3 retry attempts, use:
 `npx playwright test --retries=3`</t>
         </is>
       </c>
@@ -656,24 +686,30 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.00732725</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8</v>
+        <v>28669</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.67</v>
       </c>
       <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2162162162162162</v>
+      </c>
+      <c r="L5" t="n">
         <v>0.2666666666666667</v>
       </c>
-      <c r="K5" t="n">
-        <v>0.99999999995</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
+        <v>0.8333333332916666</v>
+      </c>
+      <c r="N5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -685,7 +721,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['Screenshots | Playwright', "Full page screenshot is a screenshot of a full scrollable page, as if you had a very tall screen and the page could fit it entirely.\n\n```\n`awaitpage.screenshot({path:'screenshot.png',fullPage:true});`\n```"]</t>
+          <t>['Screenshots | Playwright']</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -695,8 +731,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>To grab a screenshot of the whole scrollable page, use the following command:
-`await page.screenshot({path: 'screenshot.png', fullPage: true});`</t>
+          <t>I don't know. The provided documentation excerpt only lists the title "Screenshots | Playwright" and does not contain the content required to answer how to capture a full-page screenshot.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -705,25 +740,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.0065445</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>25793</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4761904761904762</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5882352941176471</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0.49999999995</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -734,7 +775,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['Screenshots | Playwright', "Sometimes it is useful to take a screenshot of a single element.\n\n```\n`awaitpage.locator('.header').screenshot({path:'screenshot.png'});`\n```"]</t>
+          <t>['Screenshots | Playwright']</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -744,8 +785,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Yes, you can take a screenshot of a single element using the following method:
-`await page.locator('.header').screenshot({path:'screenshot.png'});`</t>
+          <t>I don't know. The provided documentation excerpt only lists the title "Screenshots | Playwright" and does not contain information regarding the functionality of taking screenshots of single elements.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -754,24 +794,30 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.0065365</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>25776</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4545454545454545</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5555555555555556</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.49999999995</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="L7" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -793,7 +839,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>You have to switch them on. By default, videos are off. You can enable them by setting the `video` option in your Playwright config file.</t>
+          <t>You have to switch them on. By default, video recording is turned off.
+To enable video recording, you must set the `video` option in your `playwright.config.ts` file. You can choose from the following modes:
+*   `'on'`: Record video for each test.
+*   `'retain-on-failure'`: Record video for each test, but remove all videos from successful test runs.
+*   `'on-first-retry'`: Record video only when retrying a test for the first time.
+*   `'off'`: Do not record video (default).
+Example configuration:
+```typescript
+import { defineConfig } from '@playwright/test';
+export default defineConfig({
+  use: {
+    video: 'on-first-retry',
+  },
+});
+```
+If you create a browser context manually, you can also enable recording by setting `recordVideo` within `browser.newContext()`. Note that videos are only saved upon browser context closure, so you must ensure you await `browserContext.close()`.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -802,24 +863,30 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.00830175</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8</v>
+        <v>31397</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2105263157894737</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
+        <v>0.06153846153846154</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="M8" t="n">
         <v>0.5833333333041666</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -831,7 +898,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['Trace viewer | Playwright', 'Trace viewer | Playwright', 'You can open a saved trace using either the Playwright CLI or in the browser at\ntrace.playwright.dev (https://trace.playwright.dev)\n. Make sure to add the full path to where your\n`trace.zip`\nfile is located.\n\n```\n`npx playwright show-trace path/to/trace.zip`\n```', 'trace.playwright.dev (https://trace.playwright.dev)\nis a statically hosted variant of the Trace Viewer. You can upload a trace file using drag and drop or via the\n`Select file`\nbutton.\n\nTrace Viewer loads the trace entirely in your browser and does not transmit any data externally.', "In the HTML report, click on the trace icon next to the test file name to directly open the trace for the required test.\n\nYou can also click to open the detailed view of the test and scroll down to the\n`'Traces'`\ntab and open the trace by clicking on the trace screenshot.\n\nTo learn more about reporters, check out our detailed guide on reporters including the\nHTML Reporter (https://playwright.dev/docs/test-reporters#html-reporter)\n.", 'You can open remote traces directly using its URL. This makes it easy to view the remote trace without having to manually download the file from CI runs, for example.\n\n```\n`npx playwright show-trace https://example.com/trace.zip`\n```\n\nWhen using\ntrace.playwright.dev (https://trace.playwright.dev)\n, you can also pass the URL of your uploaded trace at some accessible storage (e.g. inside your CI) as a query parameter. CORS (Cross-Origin Resource Sharing) rules might apply.\n\n```\n`https://trace.playwright.dev/?trace=https://demo.playwright.dev/reports/todomvc/data/e6099cadf79aa753d5500aa9508f9d1dbd87b5ee.zip`\n```', 'Playwright Trace Viewer is a GUI tool that helps you explore recorded Playwright traces after the script has run. Traces are a great way for debugging your tests when they fail on CI. You can open traces\nlocally (https://playwright.dev/docs/trace-viewer#opening-trace-viewer)\nor in your browser on\ntrace.playwright.dev (https://trace.playwright.dev)\n.']</t>
+          <t>['Trace viewer | Playwright', 'You can open a saved trace using either the Playwright CLI or in the browser at\ntrace.playwright.dev (https://trace.playwright.dev)\n. Make sure to add the full path to where your\n`trace.zip`\nfile is located.\n\n```\n`npx playwright show-trace path/to/trace.zip`\n```', 'Trace viewer | Playwright', 'trace.playwright.dev (https://trace.playwright.dev)\nis a statically hosted variant of the Trace Viewer. You can upload a trace file using drag and drop or via the\n`Select file`\nbutton.\n\nTrace Viewer loads the trace entirely in your browser and does not transmit any data externally.', 'Playwright Trace Viewer is a GUI tool that helps you explore recorded Playwright traces after the script has run. Traces are a great way for debugging your tests when they fail on CI. You can open traces\nlocally (https://playwright.dev/docs/trace-viewer#opening-trace-viewer)\nor in your browser on\ntrace.playwright.dev (https://trace.playwright.dev)\n.', 'You can open remote traces directly using its URL. This makes it easy to view the remote trace without having to manually download the file from CI runs, for example.\n\n```\n`npx playwright show-trace https://example.com/trace.zip`\n```\n\nWhen using\ntrace.playwright.dev (https://trace.playwright.dev)\n, you can also pass the URL of your uploaded trace at some accessible storage (e.g. inside your CI) as a query parameter. CORS (Cross-Origin Resource Sharing) rules might apply.\n\n```\n`https://trace.playwright.dev/?trace=https://demo.playwright.dev/reports/todomvc/data/e6099cadf79aa753d5500aa9508f9d1dbd87b5ee.zip`\n```']</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -841,10 +908,10 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>You can open a saved `trace.zip` file using one of the following methods:
+          <t>You can open your `trace.zip` file using one of the following two methods:
 *   **Playwright CLI:** Run the following command in your terminal, replacing `path/to/trace.zip` with the full path to your file:
     `npx playwright show-trace path/to/trace.zip`
-*   **Browser:** Go to [trace.playwright.dev](https://trace.playwright.dev) and upload your trace file using drag and drop or the "Select file" button.</t>
+*   **Browser:** Go to [trace.playwright.dev](https://trace.playwright.dev) and upload your file using drag and drop or the **Select file** button. This tool loads the trace entirely in your browser without transmitting data externally.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -853,24 +920,30 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>0.007853250000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>30313</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5</v>
-      </c>
       <c r="I9" t="n">
-        <v>0.1492537313432836</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1265822784810127</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.8761904761729524</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
+        <v>0.81666666664625</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -882,7 +955,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['Parallelism | Playwright', "You can control the maximum number of parallel worker processes via\ncommand line (https://playwright.dev/docs/test-cli)\nor in the\nconfiguration file (https://playwright.dev/docs/test-configuration)\n.\n\nFrom the command line:\n\n```\n`npx playwrighttest--workers4`\n```\n\nIn the configuration file:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({// Limit the number of workers on CI, use default locallyworkers:process.env.CI?2:undefined,});`\n```", 'Configuration | Playwright', 'Command line | Playwright\n\nPlaywright provides a powerful command line interface for running tests, generating code, debugging, and more. The most up to date list of commands and arguments available on the CLI can always be retrieved via\n`npx playwright --help`\n.']</t>
+          <t>["You can control the maximum number of parallel worker processes via\ncommand line (https://playwright.dev/docs/test-cli)\nor in the\nconfiguration file (https://playwright.dev/docs/test-configuration)\n.\n\nFrom the command line:\n\n```\n`npx playwrighttest--workers4`\n```\n\nIn the configuration file:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({// Limit the number of workers on CI, use default locallyworkers:process.env.CI?2:undefined,});`\n```"]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -892,7 +965,8 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>You can control the maximum number of parallel worker processes from the command line using the following command:
+          <t>To cap the number of parallel tests from the command line, use the `--workers` flag followed by the desired number.
+The command is:
 `npx playwright test --workers 4`</t>
         </is>
       </c>
@@ -902,24 +976,30 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.00766275</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>29941</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.391304347826087</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5625</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.49999999995</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="N10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -931,7 +1011,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['Locators | Playwright', "Locator | Playwright\n\nLocators are the central piece of Playwright's auto-waiting and retry-ability. In a nutshell, locators represent a way to find element(s) on the page at any moment. A locator can be created with the\npage.locator() (https://playwright.dev/docs/api/class-page#page-locator)\nmethod.\n\nLearn more about locators (https://playwright.dev/docs/locators)\n.", 'Locators are strict. This means that all operations on locators that imply some target DOM element will throw an exception if more than one element matches. For example, the following call throws if there are several buttons in the DOM:', "```\n`awaitpage.getByRole('button').click();`\n```\n\nOn the other hand, Playwright understands when you perform a multiple-element operation, so the following call works perfectly fine when the locator resolves to multiple elements.", "```\n`awaitpage.getByRole('button').count();`\n```\n\nYou can explicitly opt-out from strictness check by telling Playwright which element to use when multiple elements match, through\nlocator.first() (https://playwright.dev/docs/api/class-locator#locator-first)\n,\nlocator.last() (https://playwright.dev/docs/api/class-locator#locator-last)\n, and\nlocator.nth() (https://playwright.dev/docs/api/class-locator#locator-nth)\n. These methods are\nnot recommended\nbecause when your page changes, Playwright may click on an element you did not intend. Instead, follow best practices above to create a locator that uniquely identifies the target element."]</t>
+          <t>['Locators are strict. This means that all operations on locators that imply some target DOM element will throw an exception if more than one element matches. For example, the following call throws if there are several buttons in the DOM:', "```\n`awaitpage.getByRole('button').click();`\n```\n\nOn the other hand, Playwright understands when you perform a multiple-element operation, so the following call works perfectly fine when the locator resolves to multiple elements.", "```\n`awaitpage.getByRole('button').count();`\n```\n\nYou can explicitly opt-out from strictness check by telling Playwright which element to use when multiple elements match, through\nlocator.first() (https://playwright.dev/docs/api/class-locator#locator-first)\n,\nlocator.last() (https://playwright.dev/docs/api/class-locator#locator-last)\n, and\nlocator.nth() (https://playwright.dev/docs/api/class-locator#locator-nth)\n. These methods are\nnot recommended\nbecause when your page changes, Playwright may click on an element you did not intend. Instead, follow best practices above to create a locator that uniquely identifies the target element."]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -941,7 +1021,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Answer: If your selector matches more than one element, Playwright will throw an exception because locators are strict for operations that imply a target DOM element, such as a click.</t>
+          <t>If your selector matches several elements, Playwright throws an exception when you perform an operation that implies a single target DOM element, such as `.click()` [1, 2].
+To resolve this, you can use the following methods to explicitly select a single element, though these are not recommended as they may lead to unintended clicks if the page changes:
+*   `locator.first()`
+*   `locator.last()`
+*   `locator.nth()`
+The documentation recommends instead creating a locator that uniquely identifies the target element [3].</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -950,24 +1035,30 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.007848999999999001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8</v>
+        <v>30286</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.33</v>
       </c>
       <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0641025641025641</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.2173913043478261</v>
       </c>
-      <c r="K11" t="n">
-        <v>0.3666666666483334</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
+        <v>0.8333333332916666</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -989,7 +1080,8 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>By default, `getByTestId` reads the `data-testid` attribute. Yes, you can point it at a different attribute by using `selectors.setTestIdAttribute(attributeName)`.</t>
+          <t>By default, `getByTestId` reads the `data-testid` attribute [2].
+You can point it at a different attribute by using `selectors.setTestIdAttribute(attributeName)`, where `attributeName` is the string name of the custom attribute you wish to use [2].</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -998,24 +1090,30 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.00744225</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8</v>
+        <v>28899</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.75</v>
       </c>
       <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.1891891891891892</v>
+      </c>
+      <c r="L12" t="n">
         <v>0.35</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.49999999995</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1037,7 +1135,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>The simplest way to fill out form fields is using `locator.fill()`. Yes, it works for `&lt;input&gt;`, `&lt;textarea&gt;`, and `[contenteditable]` elements.</t>
+          <t>The simplest way to enter text into a form field is using `locator.fill()`. This method also covers `&lt;textarea&gt;` and `[contenteditable]` elements.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1046,24 +1144,30 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.007316</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6</v>
+        <v>28709</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.44</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3478260869565217</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="M13" t="n">
         <v>0.49999999995</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1075,7 +1179,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['Actions | Playwright', "Using\nlocator.setChecked() (https://playwright.dev/docs/api/class-locator#locator-set-checked)\nis the easiest way to check and uncheck a checkbox or a radio button. This method can be used with\n`input[type=checkbox]`\n,\n`input[type=radio]`\nand\n`[role=checkbox]`\nelements.\n\n```\n`// Check the checkboxawaitpage.getByLabel('I agree to the terms above').check();// Assert the checked stateexpect(page.getByLabel('Subscribe to newsletter')).toBeChecked();// Select the radio buttonawaitpage.getByLabel('XL').check();`\n```"]</t>
+          <t>['Actions | Playwright']</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1085,7 +1189,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>The cleanest way to tick a checkbox or pick a radio button is by using `locator.setChecked()`.</t>
+          <t>I don't know. The provided documentation excerpt only contains the title "Actions | Playwright" and does not provide information on how to tick a checkbox or pick a radio button.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1094,25 +1198,31 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.00653975</v>
       </c>
       <c r="G14" t="n">
+        <v>25784</v>
+      </c>
+      <c r="H14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="n">
-        <v>4</v>
-      </c>
       <c r="I14" t="n">
-        <v>0.1176470588235294</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
         <v>0.1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0.49999999995</v>
-      </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0.15</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1123,7 +1233,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['Actions | Playwright', "Selects one or multiple options in the\n`&lt;select&gt;`\nelement with\nlocator.selectOption() (https://playwright.dev/docs/api/class-locator#locator-select-option)\n. You can specify option\n`value`\n, or\n`label`\nto select. Multiple options can be selected.\n\n```\n`// Single selection matching the value or labelawaitpage.getByLabel('Choose a color').selectOption('blue');// Single selection matching the labelawaitpage.getByLabel('Choose a color').selectOption({label:'Blue'});// Multiple selected itemsawaitpage.getByLabel('Choose multiple colors').selectOption(['red','green','blue']);`\n```"]</t>
+          <t>['Actions | Playwright']</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1133,7 +1243,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>To choose an option in a `&lt;select&gt;` element, you use the `locator.selectOption()` method, where you can specify the option's `value` or `label`. Yes, you can pick several options at once by passing an array of values or labels to the method.</t>
+          <t>I don't know. The provided documentation excerpt only contains the title "Actions | Playwright" and does not contain information regarding how to choose options in a `&lt;select&gt;` element or whether multiple selections are possible.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1142,25 +1252,31 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.006550250000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8</v>
+        <v>25796</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2325581395348837</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5882352941176471</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.49999999995</v>
+        <v>0.1470588235294118</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1171,7 +1287,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>["Dialog | Playwright\n\nDialog (https://playwright.dev/docs/api/class-dialog)\nobjects are dispatched by page via the\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nevent.\n\nAn example of using\n`Dialog`\nclass:\n\n```\n`const{chromium}=require('playwright');// Or 'firefox' or 'webkit'.(async()=&gt;{constbrowser=awaitchromium.launch();constpage=awaitbrowser.newPage();page.on('dialog',asyncdialog=&gt;{console.log(dialog.message());awaitdialog.dismiss();});awaitpage.evaluate(()=&gt;alert('1'));awaitbrowser.close();})();`\n```\n\nnote\nDialogs are dismissed automatically, unless there is a\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nlistener. When listener is present, it\nmust\neither\ndialog.accept() (https://playwright.dev/docs/api/class-dialog#dialog-accept)\nor\ndialog.dismiss() (https://playwright.dev/docs/api/class-dialog#dialog-dismiss)\nthe dialog - otherwise the page will\nfreeze (https://developer.mozilla.org/en-US/docs/Web/JavaScript/EventLoop#never_blocking)\nwaiting for the dialog, and actions like click will never finish.", 'Dialogs | Playwright', "By default, dialogs are auto-dismissed by Playwright, so you don't have to handle them. However, you can register a dialog handler before the action that triggers the dialog to either\ndialog.accept() (https://playwright.dev/docs/api/class-dialog#dialog-accept)\nor\ndialog.dismiss() (https://playwright.dev/docs/api/class-dialog#dialog-dismiss)\nit.\n\n```\n`page.on('dialog',dialog=&gt;dialog.accept());awaitpage.getByRole('button').click();`\n```\n\nnote\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nlistener\nmust handle\nthe dialog. Otherwise your action will stall, be it\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nor something else. That's because dialogs in Web are modals and therefore block further page execution until they are handled.\n\nAs a result, the following snippet will never resolve:\n\nwarning\nWRONG!\n\n```\n`page.on('dialog',dialog=&gt;console.log(dialog.message()));awaitpage.getByRole('button').click();// Will hang here`\n```\n\nnote\nIf there is no listener for\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\n, all dialogs are automatically dismissed."]</t>
+          <t>["Dialog | Playwright\n\nDialog (https://playwright.dev/docs/api/class-dialog)\nobjects are dispatched by page via the\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nevent.\n\nAn example of using\n`Dialog`\nclass:\n\n```\n`const{chromium}=require('playwright');// Or 'firefox' or 'webkit'.(async()=&gt;{constbrowser=awaitchromium.launch();constpage=awaitbrowser.newPage();page.on('dialog',asyncdialog=&gt;{console.log(dialog.message());awaitdialog.dismiss();});awaitpage.evaluate(()=&gt;alert('1'));awaitbrowser.close();})();`\n```\n\nnote\nDialogs are dismissed automatically, unless there is a\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nlistener. When listener is present, it\nmust\neither\ndialog.accept() (https://playwright.dev/docs/api/class-dialog#dialog-accept)\nor\ndialog.dismiss() (https://playwright.dev/docs/api/class-dialog#dialog-dismiss)\nthe dialog - otherwise the page will\nfreeze (https://developer.mozilla.org/en-US/docs/Web/JavaScript/EventLoop#never_blocking)\nwaiting for the dialog, and actions like click will never finish.", "By default, dialogs are auto-dismissed by Playwright, so you don't have to handle them. However, you can register a dialog handler before the action that triggers the dialog to either\ndialog.accept() (https://playwright.dev/docs/api/class-dialog#dialog-accept)\nor\ndialog.dismiss() (https://playwright.dev/docs/api/class-dialog#dialog-dismiss)\nit.\n\n```\n`page.on('dialog',dialog=&gt;dialog.accept());awaitpage.getByRole('button').click();`\n```\n\nnote\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nlistener\nmust handle\nthe dialog. Otherwise your action will stall, be it\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nor something else. That's because dialogs in Web are modals and therefore block further page execution until they are handled.\n\nAs a result, the following snippet will never resolve:\n\nwarning\nWRONG!\n\n```\n`page.on('dialog',dialog=&gt;console.log(dialog.message()));awaitpage.getByRole('button').click();// Will hang here`\n```\n\nnote\nIf there is no listener for\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\n, all dialogs are automatically dismissed.", 'Dialogs | Playwright']</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1181,8 +1297,8 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>No, your test will not get stuck if you do not handle the dialog. By default, Playwright automatically dismisses dialogs if there is no `page.on('dialog')` listener.
-However, if you **do** register a `page.on('dialog')` listener, you must either call `dialog.accept()` or `dialog.dismiss()`. If you have a listener present but fail to handle the dialog, the page will freeze and your action will stall.</t>
+          <t>No, your test will not get stuck if you do not handle the dialog. By default, Playwright automatically dismisses dialogs if there is no `page.on('dialog')` listener registered.
+However, if you do register a `page.on('dialog')` listener, you must explicitly call `dialog.accept()` or `dialog.dismiss()`. If you register a listener but fail to perform one of these actions, the page will freeze and your test actions will stall.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1191,24 +1307,30 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.75</v>
+        <v>0.00724625</v>
       </c>
       <c r="G16" t="n">
+        <v>28270</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.57</v>
       </c>
-      <c r="H16" t="n">
-        <v>5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.1176470588235294</v>
-      </c>
       <c r="J16" t="n">
-        <v>0.4705882352941176</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
+        <v>0.09859154929577464</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="M16" t="n">
         <v>0.9999999999666667</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1220,7 +1342,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>['Downloads | Playwright', "For every attachment downloaded by the page,\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent is emitted. All these attachments are downloaded into a temporary folder. You can obtain the download url, file name and payload stream using the\nDownload (https://playwright.dev/docs/api/class-download)\nobject from the event.\n\nYou can specify where to persist downloaded files using the\ndownloadsPath (https://playwright.dev/docs/api/class-browsertype#browser-type-launch-option-downloads-path)\noption in\nbrowserType.launch() (https://playwright.dev/docs/api/class-browsertype#browser-type-launch)\n.\n\nnote\nDownloaded files are deleted when the browser context that produced them is closed.\n\nHere is the simplest way to handle the file download:\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", "If you have no idea what initiates the download, you can still handle the event:\n\n```\n`page.on('download',download=&gt;download.path().then(console.log));`\n```\n\nNote that handling the event forks the control flow and makes the script harder to follow. Your scenario might end while you are downloading a file since your main control flow is not awaiting for this operation to resolve.\n\nnote\nFor uploading files, see the\nuploading files (https://playwright.dev/docs/input#upload-files)\nsection."]</t>
+          <t>["Download | Playwright\n\nDownload (https://playwright.dev/docs/api/class-download)\nobjects are dispatched by page via the\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent.\n\nAll the downloaded files belonging to the browser context are deleted when the browser context is closed.\n\nDownload event is emitted once the download starts. Download path becomes available once download completes.\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", 'Downloads | Playwright', "For every attachment downloaded by the page,\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent is emitted. All these attachments are downloaded into a temporary folder. You can obtain the download url, file name and payload stream using the\nDownload (https://playwright.dev/docs/api/class-download)\nobject from the event.\n\nYou can specify where to persist downloaded files using the\ndownloadsPath (https://playwright.dev/docs/api/class-browsertype#browser-type-launch-option-downloads-path)\noption in\nbrowserType.launch() (https://playwright.dev/docs/api/class-browsertype#browser-type-launch)\n.\n\nnote\nDownloaded files are deleted when the browser context that produced them is closed.\n\nHere is the simplest way to handle the file download:\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", "Added before v1.9\n\ndownload.saveAs\n\nCopy the download to a user-specified path. It is safe to call this method while the download is still in progress. Will wait for the download to finish if necessary.\n\nUsage\n\n```\n`awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```\n\nArguments\n\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-download#download-save-as-option-path)\nPath where the download should be copied.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-download#download-save-as-return)", "If you have no idea what initiates the download, you can still handle the event:\n\n```\n`page.on('download',download=&gt;download.path().then(console.log));`\n```\n\nNote that handling the event forks the control flow and makes the script harder to follow. Your scenario might end while you are downloading a file since your main control flow is not awaiting for this operation to resolve.\n\nnote\nFor uploading files, see the\nuploading files (https://playwright.dev/docs/input#upload-files)\nsection.", "Added before v1.9\n\ndownload.path\n\nReturns path to the downloaded file for a successful download, or throws for a failed/canceled download. The method will wait for the download to finish if necessary. The method throws when connected remotely.\n\nNote that the download's file name is a random GUID, use\ndownload.suggestedFilename() (https://playwright.dev/docs/api/class-download#download-suggested-filename)\nto get suggested file name.\n\nUsage\n\n```\n`awaitdownload.path();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n# (https://playwright.dev/docs/api/class-download#download-path-return)", 'Added before v1.9\n\ndownload.suggestedFilename\n\nReturns suggested filename for this download. It is typically computed by the browser from the\nContent-Disposition (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Content-Disposition)\nresponse header or the\n`download`\nattribute. See the spec on\nwhatwg (https://html.spec.whatwg.org/#downloading-resources)\n. Different browsers can use different logic for computing it.\n\nUsage\n\n```\n`download.suggestedFilename();`\n```\n\nReturns\n\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-download#download-suggested-filename-return)']</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1230,11 +1352,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To trigger a file download and save it to a specific location, follow this pattern:
-1.  Start waiting for the download event before performing the action that triggers it (e.g., clicking a button) by using `page.waitForEvent('download')`.
-2.  Perform the action that triggers the download.
-3.  Await the download promise to obtain the `download` object.
-4.  Use the `download.saveAs()` method to save the file to your desired path, typically using `download.suggestedFilename()` to retrieve the file name.
+          <t>To trigger a file download and save it to a specific location, the recommended pattern is to wait for the `download` event before performing the action that initiates the download.
+### Recommended Pattern
+1. **Start waiting for the download** using `page.waitForEvent('download')` before triggering the action (e.g., clicking a button). Do not use `await` on this line.
+2. **Perform the action** that triggers the download.
+3. **Await the download promise** to obtain the `Download` object.
+4. **Save the file** using the `download.saveAs()` method, providing your desired path and the `download.suggestedFilename()` to maintain the original file name.
 **Example:**
 ```javascript
 // Start waiting for download before clicking. Note no await.
@@ -1244,7 +1367,15 @@
 // Wait for the download process to complete and save the downloaded file somewhere.
 await download.saveAs('/path/to/save/at/' + download.suggestedFilename());
 ```
-Additionally, you can specify a default directory for all downloads by using the `downloadsPath` option in `browserType.launch()`.</t>
+### Alternative Configuration
+You can also specify a persistent directory for all downloads by using the `downloadsPath` option when launching the browser:
+```javascript
+browserType.launch({ downloadsPath: '/path/to/save/at/' });
+```
+### Important Considerations
+* **Temporary Storage:** By default, files are downloaded into a temporary folder and are deleted when the browser context that produced them is closed.
+* **`saveAs` behavior:** This method is safe to call while the download is still in progress; it will wait for the download to finish if necessary.
+* **Event Handling:** While you can use `page.on('download', ...)` to handle downloads, this forks the control flow and is generally discouraged because the main script may finish before the download completes.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1253,24 +1384,30 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.008519499999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8</v>
+        <v>31298</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0821917808219178</v>
+        <v>0.67</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.49999999995</v>
+        <v>0.05058365758754864</v>
       </c>
       <c r="L17" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.8055555555287036</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1282,7 +1419,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['Authentication | Playwright', 'Regardless of the authentication strategy you choose, you are likely to store authenticated browser state on the file system.\n\nWe recommend to create\n`playwright/.auth`\ndirectory and add it to your\n`.gitignore`\n. Your authentication routine will produce authenticated browser state and save it to a file in this\n`playwright/.auth`\ndirectory. Later on, tests will reuse this state and start already authenticated.\n\ndanger\nThe browser state file may contain sensitive cookies and headers that could be used to impersonate you or your test account. We strongly discourage checking them into private or public repositories.\n\nBash\nPowerShell\nBatch\n```\n`mkdir-pplaywright/.authecho$\'\\nplaywright/.auth\'&gt;&gt;.gitignore`\n```\n```\n`New-Item-ItemType Directory-Force-Path playwright\\.authAdd-Content-path.gitignore"`r`nplaywright/.auth"`\n```\n```\n`mdplaywright\\.authecho. &gt;&gt; .gitignoreecho"playwright/.auth"&gt;&gt; .gitignore`\n```', 'Global setup and teardown | Playwright', 'API testing | Playwright', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", 'Configuration (use) | Playwright', "This is the\nrecommended\napproach for tests that\nmodify server-side state\n. In Playwright, worker processes run in parallel. In this approach, each parallel worker is authenticated once. All tests ran by worker are reusing the same authentication state. We will need multiple testing accounts, one per each parallel worker.\n\nWhen to use\n\nYour tests modify shared server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting.\n\nWhen not to use\n\nYour tests do not modify any shared server-side state. In this case, all tests can use a single shared account.\n\nDetails\n\nWe will authenticate once per\nworker process (https://playwright.dev/docs/test-parallel#worker-processes)\n, each with a unique account.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\noverride storageState fixture (https://playwright.dev/docs/test-fixtures#overriding-fixtures)\nto authenticate once per worker. Use\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({browser},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constpage=awaitbrowser.newPage({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill(account.username);awaitpage.getByLabel('Password').fill(account.password);awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:fileName});awaitpage.close();awaituse(fileName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n. No changes are needed in the config.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({page})=&gt;{// page is authenticated});`\n```"]</t>
+          <t>['Authentication | Playwright', 'Regardless of the authentication strategy you choose, you are likely to store authenticated browser state on the file system.\n\nWe recommend to create\n`playwright/.auth`\ndirectory and add it to your\n`.gitignore`\n. Your authentication routine will produce authenticated browser state and save it to a file in this\n`playwright/.auth`\ndirectory. Later on, tests will reuse this state and start already authenticated.\n\ndanger\nThe browser state file may contain sensitive cookies and headers that could be used to impersonate you or your test account. We strongly discourage checking them into private or public repositories.\n\nBash\nPowerShell\nBatch\n```\n`mkdir-pplaywright/.authecho$\'\\nplaywright/.auth\'&gt;&gt;.gitignore`\n```\n```\n`New-Item-ItemType Directory-Force-Path playwright\\.authAdd-Content-path.gitignore"`r`nplaywright/.auth"`\n```\n```\n`mdplaywright\\.authecho. &gt;&gt; .gitignoreecho"playwright/.auth"&gt;&gt; .gitignore`\n```', 'Configuration (use) | Playwright', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", "TestOptions | Playwright\n\nPlaywright Test provides many options to configure test environment,\nBrowser (https://playwright.dev/docs/api/class-browser)\n,\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nand more.\n\nThese options are usually provided in the\nconfiguration file (https://playwright.dev/docs/test-configuration)\nthrough\ntestConfig.use (https://playwright.dev/docs/api/class-testconfig#test-config-use)\nand\ntestProject.use (https://playwright.dev/docs/api/class-testproject#test-project-use)\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{headless:false,viewport:{width:1280,height:720},ignoreHTTPSErrors:true,video:'on-first-retry',},});`\n```\n\nAlternatively, with\ntest.use() (https://playwright.dev/docs/api/class-test#test-use)\nyou can override some options for a file.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';// Run tests in this file with portrait-like viewport.test.use({viewport:{width:600,height:900}});test('my portrait test',async({page})=&gt;{// ...});`\n```"]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1292,25 +1429,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>You should store authenticated browser state in the `playwright/.auth` directory.
+          <t>You should store authenticated browser state in a directory named `playwright/.auth` on the file system.
 To keep this state out of version control, you must add the `playwright/.auth` directory to your `.gitignore` file. You can do this using the following commands:
-**Bash:**
-```bash
-mkdir -p playwright/.auth
-echo $'\nplaywright/.auth' &gt;&gt; .gitignore
-```
-**PowerShell:**
-```powershell
-New-Item -ItemType Directory -Force -Path playwright\.auth
-Add-Content -path .gitignore "`r`nplaywright/.auth"
-```
-**Batch:**
-```batch
-md playwright\.auth
-echo. &gt;&gt; .gitignore
-echo "playwright/.auth" &gt;&gt; .gitignore
-```
-The browser state files contain sensitive cookies and headers that could be used to impersonate you or your test account, so you should not check them into private or public repositories.</t>
+*   **Bash:** `mkdir -p playwright/.auth &amp;&amp; echo $'\nplaywright/.auth' &gt;&gt; .gitignore`
+*   **PowerShell:** `New-Item -ItemType Directory -Force -Path playwright\.auth; Add-Content -Path .gitignore "`r`nplaywright/.auth"`
+*   **Batch:** `md playwright\.auth &amp;&amp; echo. &gt;&gt; .gitignore &amp;&amp; echo "playwright/.auth" &gt;&gt; .gitignore`
+Checking these files into repositories is strongly discouraged because they may contain sensitive cookies and headers that could be used to impersonate you or your test account.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1319,24 +1443,30 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.008047499999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>30750</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09345794392523364</v>
+        <v>0.67</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4428571428423809</v>
+        <v>0.08571428571428572</v>
       </c>
       <c r="L18" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.499999999975</v>
+      </c>
+      <c r="N18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1358,11 +1488,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To make your tests render the app in dark mode, you can use one of the following methods provided in the context:
-*   **Global configuration:** Set `colorScheme: 'dark'` in your `playwright.config.ts` file within the `use` object.
-*   **Per-test configuration:** Use `test.use({ colorScheme: 'dark' });` inside your test file.
-*   **Context or Page creation:** Set `colorScheme: 'dark'` when creating a new context (`browser.newContext`) or a new page (`browser.newPage`).
-*   **Runtime emulation:** Use `await page.emulateMedia({ colorScheme: 'dark' });` to change the color scheme for an existing page.</t>
+          <t>To render your app in dark mode, you can use the `colorScheme` option. There are three ways to apply this depending on the scope required:
+**1. Global configuration (Recommended)**
+Set the `colorScheme` in your `playwright.config.ts` file to apply dark mode to all tests:
+```typescript
+import { defineConfig } from '@playwright/test';
+export default defineConfig({
+  use: {
+    colorScheme: 'dark',
+  },
+});
+```
+**2. Per-test configuration**
+Use `test.use` within a specific test file to apply dark mode to all tests in that file:
+```typescript
+import { test, expect } from '@playwright/test';
+test.use({ colorScheme: 'dark' });
+test('my test with dark mode', async ({ page }) =&gt; {
+  // ...
+});
+```
+**3. Manual context or page creation**
+You can set the color scheme when creating a new context or page, or change it dynamically for an existing page:
+*   **New context:** `const context = await browser.newContext({ colorScheme: 'dark' });`
+*   **New page:** `const page = await browser.newPage({ colorScheme: 'dark' });`
+*   **Existing page:** `await page.emulateMedia({ colorScheme: 'dark' });`</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1371,24 +1521,30 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>0.00774125</v>
+      </c>
+      <c r="G19" t="n">
+        <v>29145</v>
+      </c>
+      <c r="H19" t="n">
         <v>0.75</v>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>5</v>
-      </c>
       <c r="I19" t="n">
-        <v>0.09302325581395349</v>
+        <v>0.22</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3809523809523809</v>
+        <v>5</v>
       </c>
       <c r="K19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="M19" t="n">
         <v>0.9999999999</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1400,7 +1556,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['Emulation | Playwright', 'Grant\n`"geolocation"`\npermissions and set geolocation to a specific area.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{// Context geolocationgeolocation:{longitude:12.492507,latitude:41.889938},permissions:[\'geolocation\'],},});`\n```\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test,expect}from\'@playwright/test\';test.use({geolocation:{longitude:41.890221,latitude:12.492348},permissions:[\'geolocation\'],});test(\'my test with geolocation\',async({page})=&gt;{// ...});`\n```\n```\n`constcontext=awaitbrowser.newContext({geolocation:{longitude:41.890221,latitude:12.492348},permissions:[\'geolocation\']});`\n```\n\nChange the location later:\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test,expect}from\'@playwright/test\';test.use({geolocation:{longitude:41.890221,latitude:12.492348},permissions:[\'geolocation\'],});test(\'my test with geolocation\',async({page,context})=&gt;{// overwrite the location for this testawaitcontext.setGeolocation({longitude:48.858455,latitude:2.294474});});`\n```\n```\n`awaitcontext.setGeolocation({longitude:48.858455,latitude:2.294474});`\n```\n\nNote\nyou can only change geolocation for all pages in the context.', 'Configuration (use) | Playwright']</t>
+          <t>['Grant\n`"geolocation"`\npermissions and set geolocation to a specific area.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{// Context geolocationgeolocation:{longitude:12.492507,latitude:41.889938},permissions:[\'geolocation\'],},});`\n```\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test,expect}from\'@playwright/test\';test.use({geolocation:{longitude:41.890221,latitude:12.492348},permissions:[\'geolocation\'],});test(\'my test with geolocation\',async({page})=&gt;{// ...});`\n```\n```\n`constcontext=awaitbrowser.newContext({geolocation:{longitude:41.890221,latitude:12.492348},permissions:[\'geolocation\']});`\n```\n\nChange the location later:\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test,expect}from\'@playwright/test\';test.use({geolocation:{longitude:41.890221,latitude:12.492348},permissions:[\'geolocation\'],});test(\'my test with geolocation\',async({page,context})=&gt;{// overwrite the location for this testawaitcontext.setGeolocation({longitude:48.858455,latitude:2.294474});});`\n```\n```\n`awaitcontext.setGeolocation({longitude:48.858455,latitude:2.294474});`\n```\n\nNote\nyou can only change geolocation for all pages in the context.']</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1410,32 +1566,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To pin the browser to a specific GPS location for a test, you must grant `"geolocation"` permissions and set the `geolocation` object (containing `longitude` and `latitude`) in your configuration. You can do this in the following ways:
-*   **In `playwright.config.ts`:** Set it globally within the `use` object:
-    ```javascript
-    use: {
-      geolocation: { longitude: 12.492507, latitude: 41.889938 },
-      permissions: ['geolocation'],
-    },
+          <t>To pin the browser to a specific GPS location, you must grant `geolocation` permissions and set the `geolocation` object (containing `longitude` and `latitude`) in your configuration or test setup.
+### Configuration Options
+*   **Global Configuration:** Set it in `playwright.config.ts` within the `use` object:
+    ```typescript
+    import { defineConfig } from '@playwright/test';
+    export default defineConfig({
+      use: {
+        geolocation: { longitude: 12.492507, latitude: 41.889938 },
+        permissions: ['geolocation'],
+      },
+    });
     ```
-*   **For a specific test:** Use `test.use` within your test file:
-    ```javascript
+*   **Test-Specific Configuration:** Use `test.use` within your test file:
+    ```typescript
     test.use({
       geolocation: { longitude: 41.890221, latitude: 12.492348 },
       permissions: ['geolocation'],
     });
     ```
-*   **When creating a new context:**
-    ```javascript
+*   **Manual Context Creation:** If creating a context manually, pass the options to `browser.newContext`:
+    ```typescript
     const context = await browser.newContext({
       geolocation: { longitude: 41.890221, latitude: 12.492348 },
       permissions: ['geolocation']
     });
     ```
-*   **Changing the location during a test:** You can overwrite the location for all pages in the context using:
-    ```javascript
-    await context.setGeolocation({ longitude: 48.858455, latitude: 2.294474 });
-    ```</t>
+### Changing Location During a Test
+You can update the location for all pages in a context by using `context.setGeolocation`:
+```typescript
+await context.setGeolocation({ longitude: 48.858455, latitude: 2.294474 });
+```
+Note that geolocation changes apply to all pages within the context.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1444,24 +1606,30 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.008178</v>
       </c>
       <c r="G20" t="n">
-        <v>0.44</v>
+        <v>30337</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>0.75</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08461538461538462</v>
+        <v>0.4</v>
       </c>
       <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="L20" t="n">
         <v>0.5789473684210527</v>
       </c>
-      <c r="K20" t="n">
-        <v>0.99999999995</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1473,7 +1641,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>["FrameLocator | Playwright\n\nFrameLocator represents a view to the\n`iframe`\non the page. It captures the logic sufficient to retrieve the\n`iframe`\nand locate elements in that iframe. FrameLocator can be created with either\nlocator.contentFrame() (https://playwright.dev/docs/api/class-locator#locator-content-frame)\n,\npage.frameLocator() (https://playwright.dev/docs/api/class-page#page-frame-locator)\nor\nlocator.frameLocator() (https://playwright.dev/docs/api/class-locator#locator-frame-locator)\nmethod.\n\n```\n`constlocator=page.locator('#my-frame').contentFrame().getByText('Submit');awaitlocator.click();`\n```\n\nStrictness\n\nFrame locators are strict. This means that all operations on frame locators will throw if more than one element matches a given selector.\n\n```\n`// Throws if there are several frames in DOM:awaitpage.locator('.result-frame').contentFrame().getByRole('button').click();// Works because we explicitly tell locator to pick the first frame:awaitpage.locator('.result-frame').contentFrame().first().getByRole('button').click();`\n```\n\nConverting Locator to FrameLocator\n\nIf you have a\nLocator (https://playwright.dev/docs/api/class-locator)\nobject pointing to an\n`iframe`\nit can be converted to\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\nusing\nlocator.contentFrame() (https://playwright.dev/docs/api/class-locator#locator-content-frame)\n.\n\nConverting FrameLocator to Locator\n\nIf you have a\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\nobject it can be converted to\nLocator (https://playwright.dev/docs/api/class-locator)\npointing to the same\n`iframe`\nusing\nframeLocator.owner() (https://playwright.dev/docs/api/class-framelocator#frame-locator-owner)\n.", 'Added in: v1.17\n\nframe.frameLocator\n\nWhen working with iframes, you can create a frame locator that will enter the iframe and allow selecting elements in that iframe.\n\nUsage\n\nFollowing snippet locates element with text "Submit" in the iframe with id\n`my-frame`\n, like\n`&lt;iframe id="my-frame"&gt;`\n:\n\n```\n`constlocator=frame.frameLocator(\'#my-iframe\').getByText(\'Submit\');awaitlocator.click();`\n```\n\nArguments\n\n`selector`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-frame#frame-frame-locator-option-selector)\nA selector to use when resolving DOM element.\n\nReturns\n\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\n# (https://playwright.dev/docs/api/class-frame#frame-frame-locator-return)', 'Added in: v1.27\n\nframeLocator.getByRole\n\nAllows locating elements by their\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n.\n\nUsage\n\nConsider the following DOM structure.\n\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nArguments\n\n`role`\n"alert" | "alertdialog" | "application" | "article" | "banner" | "blockquote" | "button" | "caption" | "cell" | "checkbox" | "code" | "columnheader" | "combobox" | "complementary" | "contentinfo" | "definition" | "deletion" | "dialog" | "directory" | "document" | "emphasis" | "feed" | "figure" | "form" | "generic" | "grid" | "gridcell" | "group" | "heading" | "img" | "insertion" | "link" | "list" | "listbox" | "listitem" | "log" | "main" | "marquee" | "math" | "meter" | "menu" | "menubar" | "menuitem" | "menuitemcheckbox" | "menuitemradio" | "navigation" | "none" | "note" | "option" | "paragraph" | "presentation" | "progressbar" | "radio" | "radiogroup" | "region" | "row" | "rowgroup" | "rowheader" | "scrollbar" | "search" | "searchbox" | "separator" | "slider" | "spinbutton" | "status" | "strong" | "subscript" | "superscript" | "switch" | "tab" | "table" | "tablist" | "tabpanel" | "term" | "textbox" | "time" | "timer" | "toolbar" | "tooltip" | "tree" | "treegrid" | "treeitem"\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-role)\nRequired aria role.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`checked`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-checked)\nAn attribute that is usually set by\n`aria-checked`\nor native\n`&lt;input type=checkbox&gt;`\ncontrols.\nLearn more about\naria-checked (https://www.w3.org/TR/wai-aria-1.2/#aria-checked)\n.\n`description`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n(optional)\nAdded in: v1.60\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-description)\nOption to match the\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\n. By default, matching is case-insensitive and searches for a substring, use\nexact (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-exact)\nto control this behavior.\nLearn more about\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\n.\n`disabled`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-disabled)\nAn attribute that is usually set by\n`aria-disabled`\nor\n`disabled`\n.\nnote\nUnlike most other attributes,\n`disabled`\nis inherited through the DOM hierarchy. Learn more about\naria-disabled (https://www.w3.org/TR/wai-aria-1.2/#aria-disabled)\n.\n`exact`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.28\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-exact)\nWhether\nname (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-name)\nand\ndescription (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-description)\nare matched exactly: case-sensitive and whole-string. Defaults to false. Ignored when the value is a regular expression. Note that exact match still trims whitespace.\n`expanded`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-expanded)\nAn attribute that is usually set by\n`aria-expanded`\n.\nLearn more about\naria-expanded (https://www.w3.org/TR/wai-aria-1.2/#aria-expanded)\n.\n`includeHidden`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-include-hidden)\nOption that controls whether hidden elements are matched. By default, only non-hidden elements, as\ndefined by ARIA (https://www.w3.org/TR/wai-aria-1.2/#tree_exclusion)\n, are matched by role selector.\nLearn more about\naria-hidden (https://www.w3.org/TR/wai-aria-1.2/#aria-hidden)\n.\n`level`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-level)\nA number attribute that is usually present for roles\n`heading`\n,\n`listitem`\n,\n`row`\n,\n`treeitem`\n, with default values for\n`&lt;h1&gt;-&lt;h6&gt;`\nelements.\nLearn more about\naria-level (https://www.w3.org/TR/wai-aria-1.2/#aria-level)\n.\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-name)\nOption to match the\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. By default, matching is case-insensitive and searches for a substring, use\nexact (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-exact)\nto control this behavior.\nLearn more about\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n.\n`pressed`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-pressed)\nAn attribute that is usually set by\n`aria-pressed`\n.\nLearn more about\naria-pressed (https://www.w3.org/TR/wai-aria-1.2/#aria-pressed)\n.\n`selected`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-selected)\nAn attribute that is usually set by\n`aria-selected`\n.\nLearn more about\naria-selected (https://www.w3.org/TR/wai-aria-1.2/#aria-selected)\n.\n\nReturns\n\nLocator (https://playwright.dev/docs/api/class-locator)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-return)\n\nDetails\n\nRole selector\ndoes not replace\naccessibility audits and conformance tests, but rather gives early feedback about the ARIA guidelines.\n\nMany html elements have an implicitly\ndefined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role selector. You can find all the\nsupported roles here (https://www.w3.org/TR/wai-aria-1.2/#role_definitions)\n. ARIA guidelines\ndo not recommend\nduplicating implicit roles and attributes by setting\n`role`\nand/or\n`aria-*`\nattributes to default values.']</t>
+          <t>["FrameLocator | Playwright\n\nFrameLocator represents a view to the\n`iframe`\non the page. It captures the logic sufficient to retrieve the\n`iframe`\nand locate elements in that iframe. FrameLocator can be created with either\nlocator.contentFrame() (https://playwright.dev/docs/api/class-locator#locator-content-frame)\n,\npage.frameLocator() (https://playwright.dev/docs/api/class-page#page-frame-locator)\nor\nlocator.frameLocator() (https://playwright.dev/docs/api/class-locator#locator-frame-locator)\nmethod.\n\n```\n`constlocator=page.locator('#my-frame').contentFrame().getByText('Submit');awaitlocator.click();`\n```\n\nStrictness\n\nFrame locators are strict. This means that all operations on frame locators will throw if more than one element matches a given selector.\n\n```\n`// Throws if there are several frames in DOM:awaitpage.locator('.result-frame').contentFrame().getByRole('button').click();// Works because we explicitly tell locator to pick the first frame:awaitpage.locator('.result-frame').contentFrame().first().getByRole('button').click();`\n```\n\nConverting Locator to FrameLocator\n\nIf you have a\nLocator (https://playwright.dev/docs/api/class-locator)\nobject pointing to an\n`iframe`\nit can be converted to\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\nusing\nlocator.contentFrame() (https://playwright.dev/docs/api/class-locator#locator-content-frame)\n.\n\nConverting FrameLocator to Locator\n\nIf you have a\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\nobject it can be converted to\nLocator (https://playwright.dev/docs/api/class-locator)\npointing to the same\n`iframe`\nusing\nframeLocator.owner() (https://playwright.dev/docs/api/class-framelocator#frame-locator-owner)\n.", 'Added in: v1.17\n\nframeLocator.frameLocator\n\nWhen working with iframes, you can create a frame locator that will enter the iframe and allow selecting elements in that iframe.\n\nUsage\n\n```\n`frameLocator.frameLocator(selector);`\n```\n\nArguments\n\n`selector`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-frame-locator-option-selector)\nA selector to use when resolving DOM element.\n\nReturns\n\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-frame-locator-return)', 'Added in: v1.27\n\nframeLocator.getByRole\n\nAllows locating elements by their\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n.\n\nUsage\n\nConsider the following DOM structure.\n\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nArguments\n\n`role`\n"alert" | "alertdialog" | "application" | "article" | "banner" | "blockquote" | "button" | "caption" | "cell" | "checkbox" | "code" | "columnheader" | "combobox" | "complementary" | "contentinfo" | "definition" | "deletion" | "dialog" | "directory" | "document" | "emphasis" | "feed" | "figure" | "form" | "generic" | "grid" | "gridcell" | "group" | "heading" | "img" | "insertion" | "link" | "list" | "listbox" | "listitem" | "log" | "main" | "marquee" | "math" | "meter" | "menu" | "menubar" | "menuitem" | "menuitemcheckbox" | "menuitemradio" | "navigation" | "none" | "note" | "option" | "paragraph" | "presentation" | "progressbar" | "radio" | "radiogroup" | "region" | "row" | "rowgroup" | "rowheader" | "scrollbar" | "search" | "searchbox" | "separator" | "slider" | "spinbutton" | "status" | "strong" | "subscript" | "superscript" | "switch" | "tab" | "table" | "tablist" | "tabpanel" | "term" | "textbox" | "time" | "timer" | "toolbar" | "tooltip" | "tree" | "treegrid" | "treeitem"\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-role)\nRequired aria role.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`checked`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-checked)\nAn attribute that is usually set by\n`aria-checked`\nor native\n`&lt;input type=checkbox&gt;`\ncontrols.\nLearn more about\naria-checked (https://www.w3.org/TR/wai-aria-1.2/#aria-checked)\n.\n`description`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n(optional)\nAdded in: v1.60\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-description)\nOption to match the\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\n. By default, matching is case-insensitive and searches for a substring, use\nexact (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-exact)\nto control this behavior.\nLearn more about\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\n.\n`disabled`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-disabled)\nAn attribute that is usually set by\n`aria-disabled`\nor\n`disabled`\n.\nnote\nUnlike most other attributes,\n`disabled`\nis inherited through the DOM hierarchy. Learn more about\naria-disabled (https://www.w3.org/TR/wai-aria-1.2/#aria-disabled)\n.\n`exact`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.28\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-exact)\nWhether\nname (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-name)\nand\ndescription (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-description)\nare matched exactly: case-sensitive and whole-string. Defaults to false. Ignored when the value is a regular expression. Note that exact match still trims whitespace.\n`expanded`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-expanded)\nAn attribute that is usually set by\n`aria-expanded`\n.\nLearn more about\naria-expanded (https://www.w3.org/TR/wai-aria-1.2/#aria-expanded)\n.\n`includeHidden`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-include-hidden)\nOption that controls whether hidden elements are matched. By default, only non-hidden elements, as\ndefined by ARIA (https://www.w3.org/TR/wai-aria-1.2/#tree_exclusion)\n, are matched by role selector.\nLearn more about\naria-hidden (https://www.w3.org/TR/wai-aria-1.2/#aria-hidden)\n.\n`level`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-level)\nA number attribute that is usually present for roles\n`heading`\n,\n`listitem`\n,\n`row`\n,\n`treeitem`\n, with default values for\n`&lt;h1&gt;-&lt;h6&gt;`\nelements.\nLearn more about\naria-level (https://www.w3.org/TR/wai-aria-1.2/#aria-level)\n.\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-name)\nOption to match the\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. By default, matching is case-insensitive and searches for a substring, use\nexact (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-exact)\nto control this behavior.\nLearn more about\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n.\n`pressed`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-pressed)\nAn attribute that is usually set by\n`aria-pressed`\n.\nLearn more about\naria-pressed (https://www.w3.org/TR/wai-aria-1.2/#aria-pressed)\n.\n`selected`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-selected)\nAn attribute that is usually set by\n`aria-selected`\n.\nLearn more about\naria-selected (https://www.w3.org/TR/wai-aria-1.2/#aria-selected)\n.\n\nReturns\n\nLocator (https://playwright.dev/docs/api/class-locator)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-return)\n\nDetails\n\nRole selector\ndoes not replace\naccessibility audits and conformance tests, but rather gives early feedback about the ARIA guidelines.\n\nMany html elements have an implicitly\ndefined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role selector. You can find all the\nsupported roles here (https://www.w3.org/TR/wai-aria-1.2/#role_definitions)\n. ARIA guidelines\ndo not recommend\nduplicating implicit roles and attributes by setting\n`role`\nand/or\n`aria-*`\nattributes to default values.']</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1483,20 +1651,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>To interact with a button rendered inside an iframe, you should use a `FrameLocator` to enter the iframe and then locate the element. You can follow these steps:
-1.  **Create a `FrameLocator`**: Use methods such as `page.frameLocator()` or `locator.contentFrame()` to target the specific iframe.
-2.  **Locate the button**: Once you have the `FrameLocator`, you can use methods like `getByRole('button', ...)` or `getByText(...)` to find the button within that frame.
-3.  **Perform the action**: Call the action method (e.g., `.click()`) on the resulting locator.
-**Example:**
+          <t>To interact with a button inside an iframe, you must use a `FrameLocator` to target the iframe and then locate the button within it.
+### Steps to interact with the button:
+1. **Create a `FrameLocator`**: Use one of the following methods to target the iframe:
+   - `page.frameLocator(selector)`
+   - `locator.contentFrame()` (if you have a `Locator` pointing to the `iframe`)
+   - `locator.frameLocator(selector)`
+2. **Locate the button**: Once you have the `FrameLocator`, use `getByRole('button', ...)` to target the specific button.
+3. **Perform the action**: Call `.click()` on the resulting locator.
+### Example:
 ```javascript
-// Using page.frameLocator
-await page.frameLocator('#my-iframe').getByRole('button', { name: 'Submit' }).click();
-// Using locator.contentFrame
-await page.locator('#my-frame').contentFrame().getByRole('button', { name: 'Submit' }).click();
+// Using page.frameLocator()
+await page.frameLocator('#my-frame').getByRole('button', { name: 'Submit' }).click();
 ```
-**Important Considerations:**
-*   **Strictness**: Frame locators are strict. If your selector matches more than one frame, the operation will throw an error. You can resolve this by using `.first()` to explicitly select the first matching frame.
-*   **Role Selection**: You can use `frameLocator.getByRole('button', ...)` to locate the button by its ARIA role and accessible name.</t>
+### Important Considerations:
+* **Strictness**: Frame locators are strict. If your selector matches more than one frame, the operation will throw an error. If multiple frames exist, you must explicitly select the correct one (e.g., by using `.first()`):
+  ```javascript
+  await page.locator('.result-frame').contentFrame().first().getByRole('button').click();
+  ```
+* **Role Matching**: When using `getByRole`, you can specify the button's accessible name using the `name` option. By default, this is case-insensitive and searches for a substring. You can use the `exact` option to require a case-sensitive, whole-string match.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1505,24 +1678,30 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0.0089345</v>
       </c>
       <c r="G21" t="n">
-        <v>0.67</v>
+        <v>33473</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0.106508875739645</v>
+        <v>0.59</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5806451612903226</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
+        <v>0.08808290155440414</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.5483870967741935</v>
+      </c>
+      <c r="M21" t="n">
         <v>0.9999999999666667</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1534,7 +1713,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>['Sharding | Playwright', 'By default, Playwright runs test files in\nparallel (https://playwright.dev/docs/test-parallel)\nand strives for optimal utilization of CPU cores on your machine. In order to achieve even greater parallelisation, you can further scale Playwright test execution by running tests on multiple machines simultaneously. We call this mode of operation "sharding". Sharding in Playwright means splitting your tests into smaller parts called "shards". Each shard is like a separate job that can run independently. The whole purpose is to divide your tests to speed up test runtime.\n\nWhen you shard your tests, each shard can run on its own, utilizing the available CPU cores. This helps speed up the testing process by doing tasks simultaneously.\n\nIn a CI pipeline, each shard can run as a separate job, making use of the hardware resources available in your CI pipeline, like CPU cores, to run tests faster.', 'To shard the test suite, pass\n`--shard=x/y`\nto the command line. For example, to split the suite into four shards, each running one fourth of the tests:\n\n```\n`npx playwrighttest--shard=1/4npx playwrighttest--shard=2/4npx playwrighttest--shard=3/4npx playwrighttest--shard=4/4`\n```\n\nNow, if you run these shards in parallel on different jobs, your test suite completes four times faster.\n\nNote that Playwright can only shard tests that can be run in parallel. By default, this means Playwright will shard test files. Learn about other options in the\nparallelism guide (https://playwright.dev/docs/test-parallel)\n.', "GitHub Actions supports\nsharding tests between multiple jobs (https://docs.github.com/en/actions/using-jobs/using-a-matrix-for-your-jobs)\nusing the\njobs.&lt;job_id&gt;.strategy.matrix (https://docs.github.com/en/actions/using-workflows/workflow-syntax-for-github-actions#jobsjob_idstrategymatrix)\noption. The\n`matrix`\noption will run a separate job for every possible combination of the provided options.\n\nThe following example shows you how to configure a job to run your tests on four machines in parallel and then merge the reports into a single report. Don't forget to add\n`reporter: process.env.CI ? 'blob' : 'html',`\nto your\n`playwright.config.ts`\nfile as in the example above.\n\nFirst we add a\n`matrix`\noption to our job configuration with the\n`shardTotal: [4]`\noption containing the total number of shards we want to create and\n`shardIndex: [1, 2, 3, 4]`\nwith an array of the shard numbers.\nThen we run our Playwright tests with the\n`--shard=${{ matrix.shardIndex }}/${{ matrix.shardTotal }}`\noption. This will run our test command for each shard.\nFinally we upload our blob report to the GitHub Actions Artifacts. This will make the blob report available to other jobs in the workflow.\n\n.github/workflows/playwright.yml\n```\n`name:Playwright Testson:push:branches:[main,master]pull_request:branches:[main,master]jobs:playwright-tests:timeout-minutes:60runs-on:ubuntu-lateststrategy:fail-fast:falsematrix:shardIndex:[1,2,3,4]shardTotal:[4]steps:-uses:actions/checkout@v5-uses:actions/setup-node@v5with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Install Playwright browsersrun:npx playwright install--with-deps-name:Run Playwright testsrun:npx playwright test--shard=${{matrix.shardIndex}}/${{matrix.shardTotal}}-name:Upload blob report to GitHub Actions Artifactsif:${{!cancelled()}}uses:actions/upload-artifact@v4with:name:blob-report-${{matrix.shardIndex}}path:blob-reportretention-days:1`\n```\n\nAfter all shards have completed, you can run a separate job that will merge the reports and produce a combined\nHTML report (https://playwright.dev/docs/test-reporters#html-reporter)\n. To ensure the execution order, we make the\n`merge-reports`\njob\ndepend (https://docs.github.com/en/actions/using-jobs/using-jobs-in-a-workflow#defining-prerequisite-jobs)\non our sharded\n`playwright-tests`\njob by adding\n`needs: [playwright-tests]`\n.\n\n.github/workflows/playwright.yml\n```\n`jobs:...merge-reports:# Merge reports after playwright-tests, even if some shards have failedif:${{!cancelled()}}needs:[playwright-tests]runs-on:ubuntu-lateststeps:-uses:actions/checkout@v5-uses:actions/setup-node@v5with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Download blob reports from GitHub Actions Artifactsuses:actions/download-artifact@v5with:path:all-blob-reportspattern:blob-report-*merge-multiple:true-name:Merge into HTML Reportrun:npx playwright merge-reports--reporter html ./all-blob-reports-name:Upload HTML reportuses:actions/upload-artifact@v4with:name:html-report--attempt-${{github.run_attempt}}path:playwright-reportretention-days:14`\n```\n\nYou can now see the reports have been merged and a combined HTML report is available in the GitHub Actions Artifacts tab.", "```\n`trigger:-mainpool:vmImage:ubuntu-lateststrategy:matrix:chromium-1:project:chromiumshard:1/3chromium-2:project:chromiumshard:2/3chromium-3:project:chromiumshard:3/3firefox-1:project:firefoxshard:1/3firefox-2:project:firefoxshard:2/3firefox-3:project:firefoxshard:3/3webkit-1:project:webkitshard:1/3webkit-2:project:webkitshard:2/3webkit-3:project:webkitshard:3/3steps:-task:UseNode@1inputs:version:'22'displayName:'Install Node.js'-script:npm cidisplayName:'npm ci'-script:npx playwright install--with-depsdisplayName:'Install Playwright browsers'-script:npx playwright test--project=$(project)--shard=$(shard)displayName:'Run Playwright tests'env:CI:'true'`\n```", 'Sharding in CircleCI is indexed with 0 which means that you will need to override the default parallelism ENV VARS. The following example demonstrates how to run Playwright with a CircleCI Parallelism of 4 by adding 1 to the\n`CIRCLE_NODE_INDEX`\nto pass into the\n`--shard`\ncli arg.\n\n```\n`playwright-job-name:executor:pw-noble-developmentparallelism:4steps:-run:SHARD="$((${CIRCLE_NODE_INDEX}+1))"; npx playwright test--shard=${SHARD}/${CIRCLE_NODE_TOTAL}`\n```', "GitLab CI supports\nsharding tests between multiple jobs (https://docs.gitlab.com/ee/ci/jobs/job_control.html#parallelize-large-jobs)\nusing the\nparallel (https://docs.gitlab.com/ee/ci/yaml/index.html#parallel)\nkeyword. The test job will be split into multiple smaller jobs that run in parallel. Parallel jobs are named sequentially from\n`job_name 1/N`\nto\n`job_name N/N`\n.\n\n```\n`stages:-testtests:stage:testimage:mcr.microsoft.com/playwright:v1.60.0-nobleparallel:7script:-npm ci-npx playwright test--shard=$CI_NODE_INDEX/$CI_NODE_TOTAL`\n```\n\nGitLab CI also supports sharding tests between multiple jobs using the\nparallel :matrix (https://docs.gitlab.com/ee/ci/yaml/index.html#parallelmatrix)\noption. The test job will run multiple times in parallel in a single pipeline, but with different variable values for each instance of the job. In the example below, we have 2\n`PROJECT`\nvalues and 10\n`SHARD`\nvalues, resulting in a total of 20 jobs to be run.\n\n```\n`stages:-testtests:stage:testimage:mcr.microsoft.com/playwright:v1.60.0-nobleparallel:matrix:-PROJECT:['chromium','webkit']SHARD:['1/10','2/10','3/10','4/10','5/10','6/10','7/10','8/10','9/10','10/10']script:-npm ci-npx playwright test--project=$PROJECT--shard=$SHARD`\n```"]</t>
+          <t>['Sharding | Playwright', 'To shard the test suite, pass\n`--shard=x/y`\nto the command line. For example, to split the suite into four shards, each running one fourth of the tests:\n\n```\n`npx playwrighttest--shard=1/4npx playwrighttest--shard=2/4npx playwrighttest--shard=3/4npx playwrighttest--shard=4/4`\n```\n\nNow, if you run these shards in parallel on different jobs, your test suite completes four times faster.\n\nNote that Playwright can only shard tests that can be run in parallel. By default, this means Playwright will shard test files. Learn about other options in the\nparallelism guide (https://playwright.dev/docs/test-parallel)\n.', "```\n`trigger:-mainpool:vmImage:ubuntu-lateststrategy:matrix:chromium-1:project:chromiumshard:1/3chromium-2:project:chromiumshard:2/3chromium-3:project:chromiumshard:3/3firefox-1:project:firefoxshard:1/3firefox-2:project:firefoxshard:2/3firefox-3:project:firefoxshard:3/3webkit-1:project:webkitshard:1/3webkit-2:project:webkitshard:2/3webkit-3:project:webkitshard:3/3steps:-task:UseNode@1inputs:version:'22'displayName:'Install Node.js'-script:npm cidisplayName:'npm ci'-script:npx playwright install--with-depsdisplayName:'Install Playwright browsers'-script:npx playwright test--project=$(project)--shard=$(shard)displayName:'Run Playwright tests'env:CI:'true'`\n```", 'Sharding in CircleCI is indexed with 0 which means that you will need to override the default parallelism ENV VARS. The following example demonstrates how to run Playwright with a CircleCI Parallelism of 4 by adding 1 to the\n`CIRCLE_NODE_INDEX`\nto pass into the\n`--shard`\ncli arg.\n\n```\n`playwright-job-name:executor:pw-noble-developmentparallelism:4steps:-run:SHARD="$((${CIRCLE_NODE_INDEX}+1))"; npx playwright test--shard=${SHARD}/${CIRCLE_NODE_TOTAL}`\n```', "GitLab CI supports\nsharding tests between multiple jobs (https://docs.gitlab.com/ee/ci/jobs/job_control.html#parallelize-large-jobs)\nusing the\nparallel (https://docs.gitlab.com/ee/ci/yaml/index.html#parallel)\nkeyword. The test job will be split into multiple smaller jobs that run in parallel. Parallel jobs are named sequentially from\n`job_name 1/N`\nto\n`job_name N/N`\n.\n\n```\n`stages:-testtests:stage:testimage:mcr.microsoft.com/playwright:v1.60.0-nobleparallel:7script:-npm ci-npx playwright test--shard=$CI_NODE_INDEX/$CI_NODE_TOTAL`\n```\n\nGitLab CI also supports sharding tests between multiple jobs using the\nparallel :matrix (https://docs.gitlab.com/ee/ci/yaml/index.html#parallelmatrix)\noption. The test job will run multiple times in parallel in a single pipeline, but with different variable values for each instance of the job. In the example below, we have 2\n`PROJECT`\nvalues and 10\n`SHARD`\nvalues, resulting in a total of 20 jobs to be run.\n\n```\n`stages:-testtests:stage:testimage:mcr.microsoft.com/playwright:v1.60.0-nobleparallel:matrix:-PROJECT:['chromium','webkit']SHARD:['1/10','2/10','3/10','4/10','5/10','6/10','7/10','8/10','9/10','10/10']script:-npm ci-npx playwright test--project=$PROJECT--shard=$SHARD`\n```", 'Parallelism | Playwright', 'By default, Playwright runs test files in\nparallel (https://playwright.dev/docs/test-parallel)\nand strives for optimal utilization of CPU cores on your machine. In order to achieve even greater parallelisation, you can further scale Playwright test execution by running tests on multiple machines simultaneously. We call this mode of operation "sharding". Sharding in Playwright means splitting your tests into smaller parts called "shards". Each shard is like a separate job that can run independently. The whole purpose is to divide your tests to speed up test runtime.\n\nWhen you shard your tests, each shard can run on its own, utilizing the available CPU cores. This helps speed up the testing process by doing tasks simultaneously.\n\nIn a CI pipeline, each shard can run as a separate job, making use of the hardware resources available in your CI pipeline, like CPU cores, to run tests faster.']</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1544,16 +1723,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To split your tests to run across several machines (a process called "sharding"), you pass the `--shard=x/y` argument to the Playwright command line. In this format, `x` represents the current shard index and `y` represents the total number of shards.
-For example, to split your test suite into four shards, you would run the following commands on separate machines or jobs:
+          <t>To split your tests to run across several machines, you use the `--shard=x/y` command-line argument. This divides your test suite into `y` parts, where `x` represents the specific shard index to be executed.
+### General Usage
+To run a suite in four shards, you would execute the following commands on different machines or jobs:
 * `npx playwright test --shard=1/4`
 * `npx playwright test --shard=2/4`
 * `npx playwright test --shard=3/4`
 * `npx playwright test --shard=4/4`
-**Implementation details:**
-* **CI Pipelines:** You can automate this using your CI provider's matrix or parallelization features (such as GitHub Actions `strategy.matrix`, GitLab CI `parallel`, or CircleCI parallelism) to dynamically pass the shard index and total to the command.
-* **Reporting:** When sharding, it is recommended to use the `blob` reporter in your `playwright.config.ts` file. After all shards complete, you can use `npx playwright merge-reports` to combine the results into a single report.
-* **Limitations:** Playwright shards tests that can be run in parallel, which by default means it shards test files.</t>
+### CI Integration
+You can automate this process within your CI pipeline configuration:
+* **GitLab CI:** Use the `parallel` keyword to split jobs. You can use the built-in variables `$CI_NODE_INDEX` and `$CI_NODE_TOTAL`:
+  ```yaml
+  script:
+    - npx playwright test --shard=$CI_NODE_INDEX/$CI_NODE_TOTAL
+  ```
+  Alternatively, use `parallel:matrix` to define specific shard values (e.g., `SHARD: ['1/10', '2/10', ...]`).
+* **CircleCI:** Since CircleCI indexing starts at 0, you must add 1 to the index to match the `--shard` format:
+  ```yaml
+  - run: SHARD="$((${CIRCLE_NODE_INDEX}+1))"; npx playwright test --shard=${SHARD}/${CIRCLE_NODE_TOTAL}
+  ```
+* **Azure Pipelines:** Use a `strategy: matrix` to define the shards explicitly:
+  ```yaml
+  strategy:
+    matrix:
+      shard-1:
+        shard: 1/3
+      shard-2:
+        shard: 2/3
+      shard-3:
+        shard: 3/3
+  steps:
+    - script: npx playwright test --shard=$(shard)
+  ```
+### Important Considerations
+* **Parallelism:** Playwright can only shard tests that are capable of running in parallel. By default, this means Playwright shards test files.
+* **Performance:** Sharding allows you to scale test execution across multiple machines simultaneously, which reduces total test runtime.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1562,24 +1766,30 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>0.010718</v>
+      </c>
+      <c r="G22" t="n">
+        <v>38127</v>
+      </c>
+      <c r="H22" t="n">
         <v>0.75</v>
       </c>
-      <c r="G22" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H22" t="n">
-        <v>5</v>
-      </c>
       <c r="I22" t="n">
-        <v>0.07734806629834254</v>
+        <v>0.59</v>
       </c>
       <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.05533596837944664</v>
+      </c>
+      <c r="L22" t="n">
         <v>0.5384615384615384</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.9999999999857143</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1601,7 +1811,9 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Yes, you can use `test.slow()` to triple the default timeout or `test.setTimeout(ms)` to set a specific duration for that test.</t>
+          <t>Yes, you can use one of the following one-liners inside your test:
+*   **To triple the default timeout:** Use `test.slow();`.
+*   **To set a specific duration:** Use `test.setTimeout(120_000);` (replacing `120_000` with your desired time in milliseconds).</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1610,24 +1822,30 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.75</v>
+        <v>0.007670749999999</v>
       </c>
       <c r="G23" t="n">
+        <v>29758</v>
+      </c>
+      <c r="H23" t="n">
         <v>0.5</v>
       </c>
-      <c r="H23" t="n">
-        <v>5</v>
-      </c>
       <c r="I23" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L23" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.49999999995</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1639,7 +1857,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>['Selectors | Playwright\n\nSelectors can be used to install custom selector engines. See\nextensibility (https://playwright.dev/docs/extensibility)\nfor more information.', 'Other locators | Playwright', 'warning\nWe recommend\nlocating by test id (https://playwright.dev/docs/locators#locate-by-test-id)\ninstead.\n\nPlaywright supports shorthand for selecting elements using certain attributes. Currently, only the following attributes are supported:\n\n`id`\n`data-testid`\n`data-test-id`\n`data-test`\n\n```\n`// Fill an input with the id "username"awaitpage.locator(\'id=username\').fill(\'value\');// Click an element with data-test-id "submit"awaitpage.locator(\'data-test-id=submit\').click();`\n```\n\nnote\nAttribute selectors are not CSS selectors, so anything CSS-specific like\n`:enabled`\nis not supported. For more features, use a proper\ncss (https://playwright.dev/docs/other-locators#css-locator)\nselector, e.g.\n`css=[data-test="login"]:enabled`\n.', 'note\nCheck out the main\nlocators guide (https://playwright.dev/docs/locators)\nfor most common and recommended locators.\n\nIn addition to recommended locators like\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\nand\npage.getByText() (https://playwright.dev/docs/api/class-page#page-get-by-text)\n, Playwright supports a variety of other locators described in this guide.']</t>
+          <t>['Other locators | Playwright', 'Playwright comes with multiple built-in locators. To make tests resilient, we recommend prioritizing user-facing attributes and explicit contracts such as\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign in\n```\n`&lt;button&gt;Sign in&lt;/button&gt;`\n```\n\nLocate the element by its role of\n`button`\nwith name "Sign in".\n\n```\n`awaitpage.getByRole(\'button\',{name:\'Sign in\'}).click();`\n```\n\nnote\nUse the\ncode generator (https://playwright.dev/docs/codegen)\nto generate a locator, and then edit it as you\'d like.\n\nEvery time a locator is used for an action, an up-to-date DOM element is located in the page. In the snippet below, the underlying DOM element will be located twice, once prior to every action. This means that if the DOM changes in between the calls due to re-render, the new element corresponding to the locator will be used.\n\n```\n`constlocator=page.getByRole(\'button\',{name:\'Sign in\'});awaitlocator.hover();awaitlocator.click();`\n```\n\nNote that all methods that create a locator, such as\npage.getByLabel() (https://playwright.dev/docs/api/class-page#page-get-by-label)\n, are also available on the\nLocator (https://playwright.dev/docs/api/class-locator)\nand\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\nclasses, so you can chain them and iteratively narrow down your locator.\n\n```\n`constlocator=page.frameLocator(\'#my-frame\').getByRole(\'button\',{name:\'Sign in\'});awaitlocator.click();`\n```', 'Testing by test ids is the most resilient way of testing as even if your text or role of the attribute changes, the test will still pass. QA\'s and developers should define explicit test ids and query them with\npage.getByTestId() (https://playwright.dev/docs/api/class-page#page-get-by-test-id)\n. However testing by test ids is not user facing. If the role or text value is important to you then consider using user facing locators such as\nrole (https://playwright.dev/docs/locators#locate-by-role)\nand\ntext locators (https://playwright.dev/docs/locators#locate-by-text)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nItinéraire\n```\n`&lt;buttondata-testid="directions"&gt;Itinéraire&lt;/button&gt;`\n```\n\nYou can locate the element by its test id:\n\n```\n`awaitpage.getByTestId(\'directions\').click();`\n```\n\nWhen to use testid locators\nYou can also use test ids when you choose to use the test id methodology or when you can\'t locate by\nrole (https://playwright.dev/docs/locators#locate-by-role)\nor\ntext (https://playwright.dev/docs/locators#locate-by-text)\n.', 'warning\nWe recommend\nlocating by test id (https://playwright.dev/docs/locators#locate-by-test-id)\ninstead.\n\nPlaywright supports shorthand for selecting elements using certain attributes. Currently, only the following attributes are supported:\n\n`id`\n`data-testid`\n`data-test-id`\n`data-test`\n\n```\n`// Fill an input with the id "username"awaitpage.locator(\'id=username\').fill(\'value\');// Click an element with data-test-id "submit"awaitpage.locator(\'data-test-id=submit\').click();`\n```\n\nnote\nAttribute selectors are not CSS selectors, so anything CSS-specific like\n`:enabled`\nis not supported. For more features, use a proper\ncss (https://playwright.dev/docs/other-locators#css-locator)\nselector, e.g.\n`css=[data-test="login"]:enabled`\n.', 'If you absolutely must use CSS or XPath locators, you can use\npage.locator() (https://playwright.dev/docs/api/class-page#page-locator)\nto create a locator that takes a selector describing how to find an element in the page. Playwright supports CSS and XPath selectors, and auto-detects them if you omit\n`css=`\nor\n`xpath=`\nprefix.\n\n```\n`awaitpage.locator(\'css=button\').click();awaitpage.locator(\'xpath=//button\').click();awaitpage.locator(\'button\').click();awaitpage.locator(\'//button\').click();`\n```\n\nXPath and CSS selectors can be tied to the DOM structure or implementation. These selectors can break when the DOM structure changes. Long CSS or XPath chains below are an example of a\nbad practice\nthat leads to unstable tests:\n\n```\n`awaitpage.locator(\'#tsf &gt; div:nth-child(2) &gt; div.A8SBwf &gt; div.RNNXgb &gt; div &gt; div.a4bIc &gt; input\').click();awaitpage.locator(\'//*[@id="tsf"]/div[2]/div[1]/div[1]/div/div[2]/input\').click();`\n```\n\nWhen to use this\nCSS and XPath are not recommended as the DOM can often change leading to non resilient tests. Instead, try to come up with a locator that is close to how the user perceives the page such as\nrole locators (https://playwright.dev/docs/locators#locate-by-role)\nor\ndefine an explicit testing contract (https://playwright.dev/docs/locators#locate-by-test-id)\nusing test ids.', 'The\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\nlocator reflects how users and assistive technology perceive the page, for example whether some element is a button or a checkbox. When locating by role, you should usually pass the accessible name as well, so that the locator pinpoints the exact element.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign up\nSubscribe\nSubmit\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nRole locators include\nbuttons, checkboxes, headings, links, lists, tables, and many more (https://www.w3.org/TR/html-aria/#docconformance)\nand follow W3C specifications for\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. Note that many html elements like\n`&lt;button&gt;`\nhave an\nimplicitly defined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role locator.\n\nNote that role locators\ndo not replace\naccessibility audits and conformance tests, but rather give early feedback about the ARIA guidelines.\n\nWhen to use role locators\nWe recommend prioritizing role locators to locate elements, as it is the closest way to how users and assistive technology perceive the page.', "Find an element by the text it contains. You can match by a substring, exact string, or a regular expression when using\npage.getByText() (https://playwright.dev/docs/api/class-page#page-get-by-text)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nWelcome, John\n```\n`&lt;span&gt;Welcome, John&lt;/span&gt;`\n```\n\nYou can locate the element by the text it contains:\n\n```\n`awaitexpect(page.getByText('Welcome, John')).toBeVisible();`\n```\n\nSet an exact match:\n\n```\n`awaitexpect(page.getByText('Welcome, John',{exact:true})).toBeVisible();`\n```\n\nMatch with a regular expression:\n\n```\n`awaitexpect(page.getByText(/welcome,[A-Za-z]+$/i)).toBeVisible();`\n```\n\nnote\nMatching by text always normalizes whitespace, even with exact match. For example, it turns multiple spaces into one, turns line breaks into spaces and ignores leading and trailing whitespace.\n\nWhen to use text locators\nWe recommend using text locators to find non interactive elements like\n`div`\n,\n`span`\n,\n`p`\n, etc. For interactive elements like\n`button`\n,\n`a`\n,\n`input`\n, etc. use\nrole locators (https://playwright.dev/docs/locators#locate-by-role)\n.\n\nYou can also\nfilter by text (https://playwright.dev/docs/locators#filter-by-text)\nwhich can be useful when trying to find a particular item in a list."]</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1649,7 +1867,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Based on the provided context, there is no information explaining why teams add `data-testid` attributes instead of leaning on text or role. The provided text only states that Playwright recommends locating by test ID and lists the supported attributes.</t>
+          <t>Teams add `data-testid` attributes because it is the most resilient way of testing; the test will still pass even if the text or role of the attribute changes. Additionally, teams may use them when they choose to follow the test id methodology or when they cannot locate an element by role or text.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1658,25 +1876,31 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.009317500000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>0.25</v>
+        <v>35945</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="I24" t="n">
-        <v>0.075</v>
+        <v>0.33</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1153846153846154</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.1296296296296296</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.2692307692307692</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.3666666666483334</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1687,7 +1911,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['Debugging Tests | Playwright', 'UI Mode | Playwright', 'Playwright runs browsers in headless mode by default. To change this behavior, use\n`headless: false`\nas a launch option.\n\nYou can also use the\nslowMo (https://playwright.dev/docs/api/class-browsertype#browser-type-launch-option-slow-mo)\noption to slow down execution (by N milliseconds per operation) and follow along while debugging.\n\n```\n`// Chromium, Firefox, or WebKitawaitchromium.launch({headless:false,slowMo:100});`\n```', 'Running and debugging tests | Playwright', 'You can play, pause or step through each action of your test using the toolbar at the top of the Inspector. You can see the current action highlighted in the test code, and matching elements highlighted in the browser window.', 'The Playwright Inspector is a GUI tool to help you debug your Playwright tests. It allows you to step through your tests, live edit locators, pick locators and see actionability logs.', 'Run your tests with the\n`--debug`\nflag to open the inspector. This configures Playwright for debugging and opens the inspector. Additional useful defaults are configured when\n`--debug`\nis used:\n\nBrowsers launch in headed mode\nDefault timeout is set to 0 (= no timeout)']</t>
+          <t>['Playwright runs browsers in headless mode by default. To change this behavior, use\n`headless: false`\nas a launch option.\n\nYou can also use the\nslowMo (https://playwright.dev/docs/api/class-browsertype#browser-type-launch-option-slow-mo)\noption to slow down execution (by N milliseconds per operation) and follow along while debugging.\n\n```\n`// Chromium, Firefox, or WebKitawaitchromium.launch({headless:false,slowMo:100});`\n```', 'Running and debugging tests | Playwright', 'UI Mode | Playwright', 'UI Mode lets you explore, run, and debug tests with a time travel experience complete with a watch mode. All test files are displayed in the testing sidebar, allowing you to expand each file and describe block to individually run, view, watch, and debug each test. Filter tests by\nname\n,\nprojects (https://playwright.dev/docs/test-projects)\n(set in your\n`playwright.config`\nfile),\n@tag\n, or by the execution status of\npassed\n,\nfailed\n, and\nskipped\n. See a full trace of your tests and hover back and forward over each action to see what was happening during each step. You can also pop out the DOM snapshot of a given moment into a separate window for a better debugging experience.', 'To open UI mode, run the following command in your terminal:\n\n```\n`npx playwrighttest--ui`\n```', 'The Playwright Inspector is a GUI tool to help you debug your Playwright tests. It allows you to step through your tests, live edit locators, pick locators and see actionability logs.', 'We highly recommend debugging your tests with\nUI Mode (https://playwright.dev/docs/test-ui-mode)\nfor a better developer experience where you can easily walk through each step of the test and visually see what was happening before, during, and after each step. UI mode also comes with many other features such as the locator picker, watch mode, and more.\n\n```\n`npx playwrighttest--ui`\n```\n\nWhile debugging you can use the Pick Locator button to select an element on the page and see the locator that Playwright would use to find that element. You can also edit the locator in the locator playground and see it highlighting live in the browser window. Use the Copy Locator button to copy the locator to your clipboard and then paste it into your test.\n\nCheck out our\ndetailed guide on UI Mode (https://playwright.dev/docs/test-ui-mode)\nto learn more about its features.']</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1697,13 +1921,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To watch the browser as your script runs and slow it down, you can use the following methods:
-*   **Run in headed mode:** By default, Playwright runs in headless mode. You can change this by using the `headless: false` launch option.
-*   **Use the `slowMo` option:** You can use the `slowMo` option to slow down execution by a specified number of milliseconds per operation. For example:
+          <t>To watch the browser as your script runs and slow it down, you have two primary options:
+**1. Recommended: UI Mode**
+Playwright highly recommends using UI Mode for debugging, as it provides a better developer experience that allows you to walk through each step of the test and visually see what happened before, during, and after each step. It includes a watch mode and allows you to hover back and forward over each action.
+*   **How to use:** Run the following command in your terminal:
+    `npx playwright test --ui`
+**2. Alternative: Headed mode with `slowMo`**
+If you prefer to run the script directly, you can disable headless mode and add a delay to each operation.
+*   **How to use:** Set `headless: false` and the `slowMo` option (in milliseconds) in your launch configuration:
     ```javascript
     await chromium.launch({headless: false, slowMo: 100});
-    ```
-*   **Use the Playwright Inspector:** You can run your tests with the `--debug` flag, which automatically launches the browser in headed mode and opens the Inspector. The Inspector allows you to play, pause, or step through each action of your test using the toolbar.</t>
+    ```</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1712,24 +1940,30 @@
         </is>
       </c>
       <c r="F25" t="n">
+        <v>0.009950249999999002</v>
+      </c>
+      <c r="G25" t="n">
+        <v>36486</v>
+      </c>
+      <c r="H25" t="n">
         <v>0.5</v>
       </c>
-      <c r="G25" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H25" t="n">
-        <v>5</v>
-      </c>
       <c r="I25" t="n">
-        <v>0.06956521739130435</v>
+        <v>0.33</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4705882352941176</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3333333333</v>
+        <v>0.07971014492753623</v>
       </c>
       <c r="L25" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1741,7 +1975,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['Debugger | Playwright\n\nAPI for controlling the Playwright debugger. The debugger allows pausing script execution and inspecting the page. Obtain the debugger instance via\nbrowserContext.debugger (https://playwright.dev/docs/api/class-browsercontext#browser-context-debugger)\n.', 'Added in: v1.59\n\ndebugger.runTo\n\nResumes script execution and pauses when an action originates from the given source location. Throws if the debugger is not paused.\n\nUsage\n\n```\n`awaitdebugger.runTo(location);`\n```\n\nArguments\n\n`location`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n# (https://playwright.dev/docs/api/class-debugger#debugger-run-to-option-location)\n`file`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`line`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n`column`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nThe source location to pause at.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-debugger#debugger-run-to-return)', 'Test generator | Playwright', 'UI Mode | Playwright', 'Running and debugging tests | Playwright', 'Since Playwright runs in Node.js, you can debug it with your debugger of choice, e.g. using\n`console.log`\n, inside your IDE, or directly in VS Code with the\nVS Code Extension (https://playwright.dev/docs/getting-started-vscode)\n. Playwright comes with\nUI Mode (https://playwright.dev/docs/test-ui-mode)\n, where you can easily walk through each step of the test, see logs, errors, network requests, inspect the DOM snapshot, and more. You can also use the\nPlaywright Inspector (https://playwright.dev/docs/debug#playwright-inspector)\n, which allows you to step through Playwright API calls, see their debug logs, and explore\nlocators (https://playwright.dev/docs/locators)\n.', "If you would like to use codegen in some non-standard setup (for example, use\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n), it is possible to call\npage.pause() (https://playwright.dev/docs/api/class-page#page-pause)\nthat will open a separate window with codegen controls.\n\n```\n`const{chromium}=require('@playwright/test');(async()=&gt;{// Make sure to run headed.constbrowser=awaitchromium.launch({headless:false});// Setup context however you like.constcontext=awaitbrowser.newContext({/* pass any options */});awaitcontext.route('**/*',route=&gt;route.continue());// Pause the page, and start recording manually.constpage=awaitcontext.newPage();awaitpage.pause();})();`\n```"]</t>
+          <t>['Debugger | Playwright\n\nAPI for controlling the Playwright debugger. The debugger allows pausing script execution and inspecting the page. Obtain the debugger instance via\nbrowserContext.debugger (https://playwright.dev/docs/api/class-browsercontext#browser-context-debugger)\n.', 'Test generator | Playwright', 'UI Mode | Playwright', 'To debug all tests, run the Playwright test command followed by the\n`--debug`\nflag.\n\n```\n`npx playwrighttest--debug`\n```\n\nThis command opens a browser window as well as the Playwright Inspector. You can use the step over button at the top of the inspector to step through your test. Or, press the play button to run your test from start to finish. Once the test finishes, the browser window closes.\n\nTo debug one test file, run the Playwright test command with the test file name that you want to debug followed by the\n`--debug`\nflag.\n\n```\n`npx playwrighttestexample.spec.ts--debug`\n```\n\nTo debug a specific test from the line number where the\n`test(..`\nis defined, add a colon followed by the line number at the end of the test file name, followed by the\n`--debug`\nflag.\n\n```\n`npx playwrighttestexample.spec.ts:10--debug`\n```\n\nWhile debugging you can use the Pick Locator button to select an element on the page and see the locator that Playwright would use to find that element. You can also edit the locator and see it highlighting live in the browser window. Use the Copy Locator button to copy the locator to your clipboard and then paste it into your test.\n\nCheck out our\ndebugging guide (https://playwright.dev/docs/debug)\nto learn more about debugging with the\nVS Code debugger (https://playwright.dev/docs/debug#vs-code-debugger)\n, UI Mode, and the\nPlaywright Inspector (https://playwright.dev/docs/debug#playwright-inspector)\nas well as debugging with\nBrowser Developer tools (https://playwright.dev/docs/debug#browser-developer-tools)\n.', 'Running and debugging tests | Playwright', 'Since Playwright runs in Node.js, you can debug it with your debugger of choice, e.g. using\n`console.log`\n, inside your IDE, or directly in VS Code with the\nVS Code Extension (https://playwright.dev/docs/getting-started-vscode)\n. Playwright comes with\nUI Mode (https://playwright.dev/docs/test-ui-mode)\n, where you can easily walk through each step of the test, see logs, errors, network requests, inspect the DOM snapshot, and more. You can also use the\nPlaywright Inspector (https://playwright.dev/docs/debug#playwright-inspector)\n, which allows you to step through Playwright API calls, see their debug logs, and explore\nlocators (https://playwright.dev/docs/locators)\n.']</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1751,7 +1985,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Yes, you can use the `debugger.runTo(location)` method, which resumes script execution and pauses when an action originates from a given source location (file, line, and optional column).</t>
+          <t>Yes. You can pause execution at a specific line by running the test file with the line number appended to the filename, followed by the `--debug` flag:
+```bash
+npx playwright test example.spec.ts:10 --debug
+```
+This opens the Playwright Inspector, which allows you to pause script execution and inspect the page. Once paused, you can use the Pick Locator button to select elements, edit locators, and see them highlighted live in the browser window. While the inspector provides a step-over button to step through the test, you can also use the play button to run the test from the paused point to the end.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1760,24 +1998,30 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.25</v>
+        <v>0.008770499999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>33642</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I26" t="n">
-        <v>0.103448275862069</v>
+        <v>0.2</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1153846153846154</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.26785714284375</v>
+        <v>0.1132075471698113</v>
       </c>
       <c r="L26" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.3333333333</v>
+      </c>
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1789,7 +2033,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['Authentication | Playwright', "This is the\nrecommended\napproach for tests that\nmodify server-side state\n. In Playwright, worker processes run in parallel. In this approach, each parallel worker is authenticated once. All tests ran by worker are reusing the same authentication state. We will need multiple testing accounts, one per each parallel worker.\n\nWhen to use\n\nYour tests modify shared server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting.\n\nWhen not to use\n\nYour tests do not modify any shared server-side state. In this case, all tests can use a single shared account.\n\nDetails\n\nWe will authenticate once per\nworker process (https://playwright.dev/docs/test-parallel#worker-processes)\n, each with a unique account.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\noverride storageState fixture (https://playwright.dev/docs/test-fixtures#overriding-fixtures)\nto authenticate once per worker. Use\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({browser},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constpage=awaitbrowser.newPage({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill(account.username);awaitpage.getByLabel('Password').fill(account.password);awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:fileName});awaitpage.close();awaituse(fileName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n. No changes are needed in the config.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({page})=&gt;{// page is authenticated});`\n```", "You can leverage\n`process.env.TEST_WORKER_INDEX`\nor\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nmentioned above to isolate user data in the database between tests running on different workers. All tests run by the worker reuse the same user.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\ncreate dbUserName fixture (https://playwright.dev/docs/test-fixtures#creating-a-fixture)\nand initialize a new user in the test database. Use\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';// Import project utils for managing users in the test database.import{createUserInTestDatabase,deleteUserFromTestDatabase}from'./my-db-utils';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{dbUserName:string}&gt;({// Returns db user name unique for the worker.dbUserName:[async({},use)=&gt;{// Use workerIndex as a unique identifier for each worker.constuserName=`user-${test.info().workerIndex}`;// Initialize user in the database.awaitcreateUserInTestDatabase(userName);awaituse(userName);// Clean up after the tests are done.awaitdeleteUserFromTestDatabase(userName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({dbUserName})=&gt;{// Use the user name in the test.});`\n```", 'Parallelism | Playwright', 'Each worker process is assigned two ids: a unique worker index that starts with 1, and a parallel index that is between\n`0`\nand\n`workers - 1`\n. When a worker is restarted, for example after a failure, the new worker process has the same\n`parallelIndex`\nand a new\n`workerIndex`\n.\n\nYou can read an index from environment variables\n`process.env.TEST_WORKER_INDEX`\nand\n`process.env.TEST_PARALLEL_INDEX`\n, or access them through\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nand\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\n.', "Playwright Test uses\nworker processes (https://playwright.dev/docs/test-parallel)\nto run test files. Similar to how test fixtures are set up for individual test runs, worker fixtures are set up for each worker process. That's where you can set up services, run servers, etc. Playwright Test will reuse the worker process for as many test files as it can, provided their worker fixtures match and hence environments are identical.\n\nBelow we'll create an\n`account`\nfixture that will be shared by all tests in the same worker, and override the\n`page`\nfixture to log in to this account for each test. To generate unique accounts, we'll use the\nworkerInfo.workerIndex (https://playwright.dev/docs/api/class-workerinfo#worker-info-worker-index)\nthat is available to any test or fixture. Note the tuple-like syntax for the worker fixture - we have to pass\n`{scope: 'worker'}`\nso that test runner sets this fixture up once per worker.\n\nIn addition to only being run once per worker, worker-scoped fixtures also get a separate timeout equal to the default test timeout. You can change it by passing the\n`timeout`\noption. See\nfixture timeout (https://playwright.dev/docs/test-fixtures#fixture-timeout)\nfor more details.\n\nmy-test.ts\n```\n`import{testasbase}from'@playwright/test';typeAccount={username:string;password:string;};// Note that we pass worker fixture types as a second template parameter.exportconsttest=base.extend&lt;{},{account:Account}&gt;({account:[async({browser},use,workerInfo)=&gt;{// Unique username.constusername='user'+workerInfo.workerIndex;constpassword='verysecure';// Create the account with Playwright.constpage=awaitbrowser.newPage();awaitpage.goto('/signup');awaitpage.getByLabel('User Name').fill(username);awaitpage.getByLabel('Password').fill(password);awaitpage.getByText('Sign up').click();// Make sure everything is ok.awaitexpect(page.getByTestId('result')).toHaveText('Success');// Do not forget to cleanup.awaitpage.close();// Use the account value.awaituse({username,password});},{scope:'worker'}],page:async({page,account},use)=&gt;{// Sign in with our account.const{username,password}=account;awaitpage.goto('/signin');awaitpage.getByLabel('User Name').fill(username);awaitpage.getByLabel('Password').fill(password);awaitpage.getByText('Sign in').click();awaitexpect(page.getByTestId('userinfo')).toHaveText(username);// Use signed-in page in the test.awaituse(page);},});export{expect}from'@playwright/test';`\n```", 'Isolation | Playwright']</t>
+          <t>['Authentication | Playwright', "This is the\nrecommended\napproach for tests that\nmodify server-side state\n. In Playwright, worker processes run in parallel. In this approach, each parallel worker is authenticated once. All tests ran by worker are reusing the same authentication state. We will need multiple testing accounts, one per each parallel worker.\n\nWhen to use\n\nYour tests modify shared server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting.\n\nWhen not to use\n\nYour tests do not modify any shared server-side state. In this case, all tests can use a single shared account.\n\nDetails\n\nWe will authenticate once per\nworker process (https://playwright.dev/docs/test-parallel#worker-processes)\n, each with a unique account.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\noverride storageState fixture (https://playwright.dev/docs/test-fixtures#overriding-fixtures)\nto authenticate once per worker. Use\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({browser},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constpage=awaitbrowser.newPage({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill(account.username);awaitpage.getByLabel('Password').fill(account.password);awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:fileName});awaitpage.close();awaituse(fileName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n. No changes are needed in the config.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({page})=&gt;{// page is authenticated});`\n```", "You can leverage\n`process.env.TEST_WORKER_INDEX`\nor\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nmentioned above to isolate user data in the database between tests running on different workers. All tests run by the worker reuse the same user.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\ncreate dbUserName fixture (https://playwright.dev/docs/test-fixtures#creating-a-fixture)\nand initialize a new user in the test database. Use\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';// Import project utils for managing users in the test database.import{createUserInTestDatabase,deleteUserFromTestDatabase}from'./my-db-utils';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{dbUserName:string}&gt;({// Returns db user name unique for the worker.dbUserName:[async({},use)=&gt;{// Use workerIndex as a unique identifier for each worker.constuserName=`user-${test.info().workerIndex}`;// Initialize user in the database.awaitcreateUserInTestDatabase(userName);awaituse(userName);// Clean up after the tests are done.awaitdeleteUserFromTestDatabase(userName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({dbUserName})=&gt;{// Use the user name in the test.});`\n```", 'Each worker process is assigned two ids: a unique worker index that starts with 1, and a parallel index that is between\n`0`\nand\n`workers - 1`\n. When a worker is restarted, for example after a failure, the new worker process has the same\n`parallelIndex`\nand a new\n`workerIndex`\n.\n\nYou can read an index from environment variables\n`process.env.TEST_WORKER_INDEX`\nand\n`process.env.TEST_PARALLEL_INDEX`\n, or access them through\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nand\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\n.', "Playwright Test uses\nworker processes (https://playwright.dev/docs/test-parallel)\nto run test files. Similar to how test fixtures are set up for individual test runs, worker fixtures are set up for each worker process. That's where you can set up services, run servers, etc. Playwright Test will reuse the worker process for as many test files as it can, provided their worker fixtures match and hence environments are identical.\n\nBelow we'll create an\n`account`\nfixture that will be shared by all tests in the same worker, and override the\n`page`\nfixture to log in to this account for each test. To generate unique accounts, we'll use the\nworkerInfo.workerIndex (https://playwright.dev/docs/api/class-workerinfo#worker-info-worker-index)\nthat is available to any test or fixture. Note the tuple-like syntax for the worker fixture - we have to pass\n`{scope: 'worker'}`\nso that test runner sets this fixture up once per worker.\n\nIn addition to only being run once per worker, worker-scoped fixtures also get a separate timeout equal to the default test timeout. You can change it by passing the\n`timeout`\noption. See\nfixture timeout (https://playwright.dev/docs/test-fixtures#fixture-timeout)\nfor more details.\n\nmy-test.ts\n```\n`import{testasbase}from'@playwright/test';typeAccount={username:string;password:string;};// Note that we pass worker fixture types as a second template parameter.exportconsttest=base.extend&lt;{},{account:Account}&gt;({account:[async({browser},use,workerInfo)=&gt;{// Unique username.constusername='user'+workerInfo.workerIndex;constpassword='verysecure';// Create the account with Playwright.constpage=awaitbrowser.newPage();awaitpage.goto('/signup');awaitpage.getByLabel('User Name').fill(username);awaitpage.getByLabel('Password').fill(password);awaitpage.getByText('Sign up').click();// Make sure everything is ok.awaitexpect(page.getByTestId('result')).toHaveText('Success');// Do not forget to cleanup.awaitpage.close();// Use the account value.awaituse({username,password});},{scope:'worker'}],page:async({page,account},use)=&gt;{// Sign in with our account.const{username,password}=account;awaitpage.goto('/signin');awaitpage.getByLabel('User Name').fill(username);awaitpage.getByLabel('Password').fill(password);awaitpage.getByText('Sign in').click();awaitexpect(page.getByTestId('userinfo')).toHaveText(username);// Use signed-in page in the test.awaituse(page);},});export{expect}from'@playwright/test';`\n```", 'Isolation | Playwright', 'Parallelism | Playwright']</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1799,12 +2043,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>To avoid collisions when tests mutate shared server state, the recommended approach is to use **one account per parallel worker**.
-Workers stay on separate accounts by using a worker-scoped fixture that differentiates between workers using `testInfo.parallelIndex` (or `workerInfo.workerIndex`). You can implement this by:
-1.  **Creating a worker-scoped fixture:** Define a fixture in a file (e.g., `playwright/fixtures.ts`) with `{scope: 'worker'}`.
-2.  **Assigning unique accounts:** Use the worker's unique index to acquire or create a specific account for that worker. This ensures that multiple workers do not share the same credentials or state.
-3.  **Reusing authentication state:** Authenticate once per worker process and store the authentication state (e.g., in a JSON file named using the `parallelIndex`) so that all tests run by that specific worker can reuse the same authenticated session.
-4.  **Importing the fixture:** Import the custom `test` object from your fixtures file into your test files instead of the standard `@playwright/test`.</t>
+          <t>To avoid collisions when tests mutate shared server-side state in parallel, the recommended approach is to use **one account per parallel worker**.
+### How to stay on separate accounts
+You must ensure each parallel worker is authenticated with a unique account. You can achieve this by creating a worker-scoped fixture that uses `testInfo.parallelIndex` to differentiate between workers.
+1.  **Create a fixture file** (e.g., `playwright/fixtures.ts`) that overrides the `storageState` fixture.
+2.  **Use `test.info().parallelIndex`** as a unique identifier for each worker to determine which account to use.
+3.  **Authenticate once per worker** by performing the login steps within the worker-scoped fixture and saving the authentication state to a unique file path based on the `parallelIndex`.
+**Example implementation:**
+```typescript
+import { test as baseTest, expect } from '@playwright/test';
+import fs from 'fs';
+import path from 'path';
+export * from '@playwright/test';
+export const test = baseTest.extend&lt;{}, { workerStorageState: string }&gt;({
+  storageState: ({ workerStorageState }, use) =&gt; use(workerStorageState),
+  workerStorageState: [async ({ browser }, use) =&gt; {
+    const id = test.info().parallelIndex;
+    const fileName = path.resolve(test.info().project.outputDir, `.auth/${id}.json`);
+    if (fs.existsSync(fileName)) {
+      await use(fileName);
+      return;
+    }
+    const page = await browser.newPage({ storageState: undefined });
+    const account = await acquireAccount(id); // Acquire a unique account for this worker
+    // Perform authentication steps...
+    await page.context().storageState({ path: fileName });
+    await page.close();
+    await use(fileName);
+  }, { scope: 'worker' }],
+});
+```
+After creating this file, import `test` from your fixtures file in your test files instead of `@playwright/test`.
+### Alternative for database isolation
+If you need to isolate user data specifically within a database rather than just authentication state, you can use `testInfo.workerIndex` to create and initialize a unique user in the test database for each worker, as described in the documentation for isolating test data between parallel workers.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1813,77 +2084,91 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0.0057028</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>37578</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1118012422360248</v>
+        <v>0.46</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4285714285714285</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.608333333318125</v>
+        <v>0.06574394463667819</v>
       </c>
       <c r="L27" t="n">
+        <v>0.4523809523809524</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.6791666666496875</v>
+      </c>
+      <c r="N27" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>On CI I only want a trace when a test actually fails, and then a way to dig into it. How do retries and tracing fit together?</t>
+          <t>Two problems with how our team writes tests. The recorder is the fastest way for people to get started, but the selectors it emits break on the next refactor, and half our app is behind a login so recording anything past the sign-in page means clicking through the form by hand every single time. Are both of these things the recorder can be told to handle?</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>["By default the\nplaywright.config (https://playwright.dev/docs/trace-viewer#tracing-on-ci)\nfile contains the configuration needed to create a\n`trace.zip`\nfile for each test. Traces are setup to run\n`on-first-retry`\n, meaning they run on the first retry of a failed test. Also\n`retries`\nare set to 2 when running on CI and 0 locally. This means the traces are recorded on the first retry of a failed test but not on the first run and not on the second retry.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({retries:process.env.CI?2:0,// set to 2 when running on CI// ...use:{trace:'on-first-retry',// record traces on first retry of each test},});`\n```\n\nTo learn more about available options to record a trace check out our detailed guide on\nTrace Viewer (https://playwright.dev/docs/trace-viewer)\n.\n\nTraces are normally run in a Continuous Integration (CI) environment, because locally you can use\nUI Mode (https://playwright.dev/docs/test-ui-mode)\nfor developing and debugging tests. However, if you want to run traces locally without using\nUI Mode (https://playwright.dev/docs/test-ui-mode)\n, you can force tracing to be on with\n`--trace on`\n.\n\n```\n`npx playwrighttest--traceon`\n```", "Traces should be run on continuous integration on the first retry of a failed test by setting the\n`trace: 'on-first-retry'`\noption in the test configuration file. This will produce a\n`trace.zip`\nfile for each test that was retried.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({retries:1,use:{trace:'on-first-retry',},});`\n```\n```\n`constbrowser=awaitchromium.launch();constcontext=awaitbrowser.newContext();// Start tracing before creating / navigating a page.awaitcontext.tracing.start({screenshots:true,snapshots:true});constpage=awaitcontext.newPage();awaitpage.goto('https://playwright.dev');// Stop tracing and export it into a zip archive.awaitcontext.tracing.stop({path:'trace.zip'});`\n```\n\nAvailable options to record a trace:\n\n`'on-first-retry'`\n- Record a trace only when retrying a test for the first time.\n`'on-all-retries'`\n- Record traces for all test retries.\n`'off'`\n- Do not record a trace.\n`'on'`\n- Record a trace for each test. (not recommended as it's performance heavy)\n`'retain-on-failure'`\n- Record a trace for each test, but remove it from successful test runs.\n\nYou can also use\n`trace: 'retain-on-failure'`\nif you do not enable retries but still want traces for failed tests.\n\nThere are more granular options available, see\ntestOptions.trace (https://playwright.dev/docs/api/class-testoptions#test-options-trace)\n.\n\nIf you are not using Playwright as a Test Runner, use the\nbrowserContext.tracing (https://playwright.dev/docs/api/class-browsercontext#browser-context-tracing)\nAPI instead.", 'Retries | Playwright', 'Trace viewer | Playwright', "In the HTML report, click on the trace icon next to the test file name to directly open the trace for the required test.\n\nYou can also click to open the detailed view of the test and scroll down to the\n`'Traces'`\ntab and open the trace by clicking on the trace screenshot.\n\nTo learn more about reporters, check out our detailed guide on reporters including the\nHTML Reporter (https://playwright.dev/docs/test-reporters#html-reporter)\n.", 'Configuration (use) | Playwright', 'Trace viewer | Playwright']</t>
+          <t>['Run with\n`--load-storage`\nto consume the previously loaded storage from the\n`auth.json`\n. This way, all\ncookies (https://developer.mozilla.org/en-US/docs/Web/HTTP/Cookies)\n,\nlocalStorage (https://developer.mozilla.org/en-US/docs/Web/API/Window/localStorage)\nand\nIndexedDB (https://developer.mozilla.org/en-US/docs/Web/API/IndexedDB_API)\ndata will be restored, bringing most web apps to the authenticated state without the need to login again. This means you can continue generating tests from the logged in state.\n\n```\n`npx playwright codegen --load-storage=auth.json github.com/microsoft/playwright`\n```', 'You can use the test generator to generate tests using emulation so as to generate a test for a specific viewport, device, color scheme, as well as emulate the geolocation, language or timezone. The test generator can also generate a test while preserving authenticated state.', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", "This is the\nrecommended\napproach for tests that\nmodify server-side state\n. In Playwright, worker processes run in parallel. In this approach, each parallel worker is authenticated once. All tests ran by worker are reusing the same authentication state. We will need multiple testing accounts, one per each parallel worker.\n\nWhen to use\n\nYour tests modify shared server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting.\n\nWhen not to use\n\nYour tests do not modify any shared server-side state. In this case, all tests can use a single shared account.\n\nDetails\n\nWe will authenticate once per\nworker process (https://playwright.dev/docs/test-parallel#worker-processes)\n, each with a unique account.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\noverride storageState fixture (https://playwright.dev/docs/test-fixtures#overriding-fixtures)\nto authenticate once per worker. Use\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({browser},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constpage=awaitbrowser.newPage({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill(account.username);awaitpage.getByLabel('Password').fill(account.password);awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:fileName});awaitpage.close();awaituse(fileName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n. No changes are needed in the config.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({page})=&gt;{// page is authenticated});`\n```", 'Run\n`codegen`\nwith\n`--save-storage`\nto save\ncookies (https://developer.mozilla.org/en-US/docs/Web/HTTP/Cookies)\n,\nlocalStorage (https://developer.mozilla.org/en-US/docs/Web/API/Window/localStorage)\nand\nIndexedDB (https://developer.mozilla.org/en-US/docs/Web/API/IndexedDB_API)\ndata at the end of the session. This is useful to separately record an authentication step and reuse it later when recording more tests.\n\n```\n`npx playwright codegen github.com/microsoft/playwright --save-storage=auth.json`\n```', 'By default,\npage.getByTestId() (https://playwright.dev/docs/api/class-page#page-get-by-test-id)\nwill locate elements based on the\n`data-testid`\nattribute, but you can configure it in your test config or by calling\nselectors.setTestIdAttribute() (https://playwright.dev/docs/api/class-selectors#selectors-set-test-id-attribute)\n.\n\nSet the test id to use a custom data attribute for your tests.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{testIdAttribute:\'data-pw\'}});`\n```\n\nIn your html you can now use\n`data-pw`\nas your test id instead of the default\n`data-testid`\n.\n\nhttp://localhost:3000\nItinéraire\n```\n`&lt;buttondata-pw="directions"&gt;Itinéraire&lt;/button&gt;`\n```\n\nAnd then locate the element as you would normally do:\n\n```\n`awaitpage.getByTestId(\'directions\').click();`\n```', 'Playwright comes with the ability to generate tests for you as you perform actions in the browser and is a great way to quickly get started with testing. Playwright will look at your page and figure out the best locator, prioritizing\nrole, text and test id locators (https://playwright.dev/docs/locators)\n. If the generator finds multiple elements matching the locator, it will improve the locator to make it resilient that uniquely identify the target element.']</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['Playwright supports test retries . When enabled, failing tests will be retried multiple times until they pass, or until the maximum number of retries is reached. By default failing tests are not retried.', "Traces should be run on continuous integration on the first retry of a failed test by setting the trace: 'on-first-retry' option in the test configuration file. This will produce a trace.zip file for each test that was retried.", 'Traces are a great way for debugging your tests when they fail on CI. You can open traces locally or in your browser on trace.playwright.dev (https://trace.playwright.dev) .']</t>
+          <t>['Playwright will look at your page and figure out the best locator, prioritizing role, text and test id locators. If the generator finds multiple elements matching the locator, it will improve the locator to make it resilient that uniquely identifies the target element.', 'The test generator can also generate a test while preserving authenticated state.', 'Run codegen with --save-storage to save cookies, localStorage and IndexedDB data at the end of the session. This is useful to separately record an authentication step and reuse it later when recording more tests.', 'Run with --load-storage to consume the previously loaded storage from the auth.json. This way, all cookies, localStorage and IndexedDB data will be restored, bringing most web apps to the authenticated state without the need to login again. This means you can continue generating tests from the logged in state.', 'You can generate locators with the test generator.']</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>To achieve your goal of having a trace only when a test fails, you can use the following configurations:
-*   **`trace: 'on-first-retry'`**: This is the default configuration for CI. It records a `trace.zip` file only when a test is retried for the first time, allowing you to dig into the failure.
-*   **`trace: 'retain-on-failure'`**: If you do not want to enable retries but still want a trace for failed tests, you can use this option. It records a trace for every test but removes it if the test run is successful.
-*   **`trace: 'on-all-retries'`**: This option records traces for all test retries.
-Once a trace is generated, you can open it via the HTML report by clicking the trace icon next to the test file name or by navigating to the "Traces" tab in the detailed view of the test.</t>
+          <t>The provided documentation addresses both of your concerns:
+**1. Handling fragile selectors**
+The test generator is designed to prioritize resilient locators, specifically role, text, and test id locators. If the generator identifies multiple elements matching a locator, it automatically improves the locator to uniquely and resiliently identify the target element. To further ensure stability, you can use `data-testid` attributes (or a custom attribute configured via `testIdAttribute` in your `playwright.config.ts`) to provide stable anchors for your tests.
+**2. Handling the login form**
+You can avoid manually clicking through the login form every time by preserving the authenticated state. There are two ways to handle this with the recorder:
+*   **Save state:** Run `npx playwright codegen --save-storage=auth.json` to record the authentication step once and save the cookies, `localStorage`, and `IndexedDB` data to a file.
+*   **Load state:** Once you have an `auth.json` file, you can use `npx playwright codegen --load-storage=auth.json &lt;url&gt;` to start the recorder already authenticated, allowing you to generate tests from the logged-in state without re-authenticating.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Enable retries and capture the trace on the first retry (trace: 'on-first-retry'); every retried test then drops a trace.zip. Open those in Trace Viewer to walk the failed run action by action, with DOM, console and network.</t>
+          <t>Both are, and they're separate mechanisms. On selectors: the generator isn't emitting raw CSS by accident — it inspects the page and picks what it judges the best locator, prioritising role, text and test id locators in that order, and when a candidate matches several elements it refines it until it uniquely identifies the target. So brittle output is usually a signal about the markup rather than the tool: give the elements you care about a test id (or accessible roles and names) and the recorder will prefer those. You can also use Pick Locator to grab and hand-tune a single locator rather than recording a whole flow. On the login: record the authentication once with `npx playwright codegen &lt;url&gt; --save-storage=auth.json`, which writes the cookies, localStorage and IndexedDB state at the end of the session, then start every later recording with `npx playwright codegen --load-storage=auth.json &lt;url&gt;`, which restores that state so the app comes up already signed in and you record only the part you care about. That saved state is the same kind of artifact your suite consumes as storageState, so the recorded flow and the running tests can share it.</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.75</v>
+        <v>0.01060525</v>
       </c>
       <c r="G28" t="n">
-        <v>0.17</v>
+        <v>38671</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.125</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
-        <v>0.45</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.99999999995</v>
+        <v>0.3125</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5</v>
+        <v>0.275</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="29">
@@ -1894,7 +2179,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['Authentication | Playwright', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", "Here is a global setup example that authenticates once and reuses authentication state in tests. It uses the\n`baseURL`\nand\n`storageState`\noptions from the configuration file.\n\nglobal-setup.ts\n```\n`import{chromium,typeFullConfig}from'@playwright/test';asyncfunctionglobalSetup(config:FullConfig){const{baseURL,storageState}=config.projects[0].use;constbrowser=awaitchromium.launch();constpage=awaitbrowser.newPage();awaitpage.goto(baseURL!);awaitpage.getByLabel('User Name').fill('user');awaitpage.getByLabel('Password').fill('password');awaitpage.getByText('Sign in').click();awaitpage.context().storageState({path:storageStateasstring});awaitbrowser.close();}exportdefaultglobalSetup;`\n```\n\nSpecify\n`globalSetup`\n,\n`baseURL`\nand\n`storageState`\nin the configuration file.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalSetup:require.resolve('./global-setup'),use:{baseURL:'http://localhost:3000/',storageState:'state.json',},});`\n```\n\nTests start already authenticated because we specify\n`storageState`\nthat was populated by global setup.\n\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{awaitpage.goto('/');// You are signed in!});`\n```\n\nYou can make arbitrary data available in your tests from your global setup file by setting them as environment variables via\n`process.env`\n.\n\nglobal-setup.ts\n```\n`importtype{FullConfig}from'@playwright/test';asyncfunctionglobalSetup(config:FullConfig){process.env.FOO='some data';// Or a more complicated data structure as JSON:process.env.BAR=JSON.stringify({some:'data'});}exportdefaultglobalSetup;`\n```\n\nTests have access to the\n`process.env`\nproperties set in the global setup.\n\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// environment variables which are set in globalSetup are only available inside test().const{FOO,BAR}=process.env;// FOO and BAR properties are populated.expect(FOO).toEqual('some data');constcomplexData=JSON.parse(BAR);expect(BAR).toEqual({some:'data'});});`\n```", 'Global setup and teardown | Playwright', 'Project dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nare a list of projects that need to run before the tests in another project run. They can be useful for configuring the global setup actions so that one project depends on this running first. Using dependencies allows global setup to produce traces and other artifacts.', "First we add a new project with the name 'setup db'. We then give it a\ntestProject.testMatch (https://playwright.dev/docs/api/class-testproject#test-project-test-match)\nproperty in order to match the file called\n`global.setup.ts`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},// {//   other project// }]});`\n```\n\nThen we add the\ntestProject.dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nproperty to our projects that depend on the setup project and pass into the array the name of our dependency project, which we defined in the previous step:\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},{name:'chromium with db',use:{...devices['Desktop Chrome']},dependencies:['setup db'],},]});`\n```\n\nIn this example the 'chromium with db' project depends on the 'setup db' project. We then create a setup test, stored at root level of your project (note that setup and teardown code must be defined as regular tests by calling\ntest() (https://playwright.dev/docs/api/class-test#test-call)\nfunction):\n\ntests/global.setup.ts\n```\n`import{testassetup}from'@playwright/test';setup('create new database',async({})=&gt;{console.log('creating new database...');// Initialize the database});`\n```\n\ntests/menu.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('menu',async({page})=&gt;{// Your test that depends on the database});`\n```", 'Regardless of the authentication strategy you choose, you are likely to store authenticated browser state on the file system.\n\nWe recommend to create\n`playwright/.auth`\ndirectory and add it to your\n`.gitignore`\n. Your authentication routine will produce authenticated browser state and save it to a file in this\n`playwright/.auth`\ndirectory. Later on, tests will reuse this state and start already authenticated.\n\ndanger\nThe browser state file may contain sensitive cookies and headers that could be used to impersonate you or your test account. We strongly discourage checking them into private or public repositories.\n\nBash\nPowerShell\nBatch\n```\n`mkdir-pplaywright/.authecho$\'\\nplaywright/.auth\'&gt;&gt;.gitignore`\n```\n```\n`New-Item-ItemType Directory-Force-Path playwright\\.authAdd-Content-path.gitignore"`r`nplaywright/.auth"`\n```\n```\n`mdplaywright\\.authecho. &gt;&gt; .gitignoreecho"playwright/.auth"&gt;&gt; .gitignore`\n```']</t>
+          <t>['Authentication | Playwright', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", 'Global setup and teardown | Playwright', 'Project dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nare a list of projects that need to run before the tests in another project run. They can be useful for configuring the global setup actions so that one project depends on this running first. Using dependencies allows global setup to produce traces and other artifacts.', "When to use\n\nYour web application supports authenticating via API that is easier/faster than interacting with the app UI.\n\nDetails\n\nWe will send the API request with\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nand then save authenticated state as usual.\n\nIn the\nsetup project (https://playwright.dev/docs/auth#basic-shared-account-in-all-tests)\n:\n\ntests/auth.setup.ts\n```\n`import{testassetup}from'@playwright/test';constauthFile='playwright/.auth/user.json';setup('authenticate',async({request})=&gt;{// Send authentication request. Replace with your own.awaitrequest.post('https://github.com/login',{form:{'user':'user','password':'password'}});awaitrequest.storageState({path:authFile});});`\n```\n\nAlternatively, in a\nworker fixture (https://playwright.dev/docs/auth#moderate-one-account-per-parallel-worker)\n:\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,request}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constcontext=awaitrequest.newContext({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Send authentication request. Replace with your own.awaitcontext.post('https://github.com/login',{form:{'user':'user','password':'password'}});awaitcontext.storageState({path:fileName});awaitcontext.dispose();awaituse(fileName);},{scope:'worker'}],});`\n```", "First we add a new project with the name 'setup db'. We then give it a\ntestProject.testMatch (https://playwright.dev/docs/api/class-testproject#test-project-test-match)\nproperty in order to match the file called\n`global.setup.ts`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},// {//   other project// }]});`\n```\n\nThen we add the\ntestProject.dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nproperty to our projects that depend on the setup project and pass into the array the name of our dependency project, which we defined in the previous step:\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},{name:'chromium with db',use:{...devices['Desktop Chrome']},dependencies:['setup db'],},]});`\n```\n\nIn this example the 'chromium with db' project depends on the 'setup db' project. We then create a setup test, stored at root level of your project (note that setup and teardown code must be defined as regular tests by calling\ntest() (https://playwright.dev/docs/api/class-test#test-call)\nfunction):\n\ntests/global.setup.ts\n```\n`import{testassetup}from'@playwright/test';setup('create new database',async({})=&gt;{console.log('creating new database...');// Initialize the database});`\n```\n\ntests/menu.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('menu',async({page})=&gt;{// Your test that depends on the database});`\n```", 'Fixtures | Playwright']</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1904,44 +2189,61 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>To make every browser project sign in once and share that session, you should use the recommended approach of creating a setup project that authenticates once, saves the state, and is then used as a dependency by your testing projects.
-Follow these steps:
-1.  **Create an authentication setup file** (e.g., `tests/auth.setup.ts`):
-    Perform your login steps in this file and save the browser state to a file using `page.context().storageState({ path: 'playwright/.auth/user.json' })`.
-2.  **Configure the setup project**:
-    In your `playwright.config.ts`, define a project specifically for authentication that matches your setup file:
-    ```typescript
-    projects: [
-      {
-        name: 'setup',
-        testMatch: /.*\.setup\.ts/,
+          <t>To sign in once up front and share that session across browser projects, use the recommended approach of creating a setup project that saves the authentication state.
+### 1. Create a setup file
+Create a file (e.g., `tests/auth.setup.ts`) to perform the authentication and save the state to a JSON file:
+```typescript
+import { test as setup, expect } from '@playwright/test';
+import path from 'path';
+const authFile = path.join(__dirname, '../playwright/.auth/user.json');
+setup('authenticate', async ({ page }) =&gt; {
+  // Perform authentication steps
+  await page.goto('https://github.com/login');
+  await page.getByLabel('Username or email address').fill('username');
+  await page.getByLabel('Password').fill('password');
+  await page.getByRole('button', { name: 'Sign in' }).click();
+  // Wait for authentication to complete
+  await page.waitForURL('https://github.com/');
+  await expect(page.getByRole('button', { name: 'View profile and more' })).toBeVisible();
+  // Save the state
+  await page.context().storageState({ path: authFile });
+});
+```
+### 2. Configure the projects
+In your `playwright.config.ts`, define the `setup` project and add it as a dependency to your browser projects. Use the `storageState` property in each browser project to load the saved session:
+```typescript
+import { defineConfig, devices } from '@playwright/test';
+export default defineConfig({
+  projects: [
+    // Setup project
+    { 
+      name: 'setup', 
+      testMatch: /.*\.setup\.ts/ 
+    },
+    // Browser projects
+    {
+      name: 'chromium',
+      use: { 
+        ...devices['Desktop Chrome'],
+        storageState: 'playwright/.auth/user.json',
       },
-      // ...
-    ]
-    ```
-3.  **Configure testing projects to use the state**:
-    Add the `dependencies` property to your testing projects to ensure the setup project runs first, and use the `storageState` option to point to the saved JSON file:
-    ```typescript
-    projects: [
-      {
-        name: 'chromium',
-        use: {
-          ...devices['Desktop Chrome'],
-          storageState: 'playwright/.auth/user.json',
-        },
-        dependencies: ['setup'],
+      dependencies: ['setup'],
+    },
+    {
+      name: 'firefox',
+      use: { 
+        ...devices['Desktop Firefox'],
+        storageState: 'playwright/.auth/user.json',
       },
-      {
-        name: 'firefox',
-        use: {
-          ...devices['Desktop Firefox'],
-          storageState: 'playwright/.auth/user.json',
-        },
-        dependencies: ['setup'],
-      },
-    ]
-    ```
-By following this configuration, your tests will start already authenticated because they load the `storageState` produced by the `setup` project.</t>
+      dependencies: ['setup'],
+    },
+  ],
+});
+```
+### Important Considerations
+*   **When to use:** This is recommended when all tests can run with the same account without affecting each other.
+*   **When not to use:** Do not use this if your tests modify server-side state (e.g., changing settings) in parallel, or if your authentication is browser-specific.
+*   **Cleanup:** You must delete the stored state when it expires. If you do not need to persist the state between runs, write the file to `testProject.outputDir`, which is automatically cleaned up before every test run.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1950,24 +2252,30 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0.01090775</v>
       </c>
       <c r="G29" t="n">
-        <v>0.83</v>
+        <v>38761</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1210526315789474</v>
+        <v>0.4</v>
       </c>
       <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.07419354838709677</v>
+      </c>
+      <c r="L29" t="n">
         <v>0.575</v>
       </c>
-      <c r="K29" t="n">
-        <v>0.9484126983968916</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
+        <v>0.9266666666481335</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1979,7 +2287,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>['Sharding | Playwright', "Sharding can be done at two levels of granularity depending on whether you use the\ntestProject.fullyParallel (https://playwright.dev/docs/api/class-testproject#test-project-fully-parallel)\noption or not. This affects how the tests are balanced across the shards.\n\nSharding with fullyParallel\n\nWhen\n`fullyParallel: true`\nis enabled, Playwright Test runs individual tests in parallel across multiple shards, ensuring each shard receives an even distribution of tests. This allows for test-level granularity, meaning each shard will attempt to balance the number of individual tests it runs. This is the preferred mode for ensuring even load distribution when sharding, as Playwright can optimize shard execution based on the total number of tests.\n\nSharding without fullyParallel\n\nWithout the fullyParallel setting, Playwright Test defaults to file-level granularity, meaning entire test files are assigned to shards (note that the same file may be assigned to different shards across different projects). In this case, the number of tests per file can greatly influence shard distribution. If your test files are not evenly sized (i.e., some files contain many more tests than others), certain shards may end up running significantly more tests, while others may run fewer or even none.\n\nKey Takeaways:\n\nWith\n`fullyParallel: true`\n: Tests are split at the individual test level, leading to more balanced shard execution.\nWithout\n`fullyParallel`\n: Tests are split at the file level, so to balance the shards, it's important to keep your test files small and evenly sized.\nTo ensure the most effective use of sharding, especially in CI environments, it is recommended to use\n`fullyParallel: true`\nwhen aiming for balanced distribution across shards. Otherwise, you may need to manually organize your test files to avoid imbalances.", 'Parallelism | Playwright', 'Retries | Playwright', 'Configuration | Playwright', "GitHub Actions supports\nsharding tests between multiple jobs (https://docs.github.com/en/actions/using-jobs/using-a-matrix-for-your-jobs)\nusing the\njobs.&lt;job_id&gt;.strategy.matrix (https://docs.github.com/en/actions/using-workflows/workflow-syntax-for-github-actions#jobsjob_idstrategymatrix)\noption. The\n`matrix`\noption will run a separate job for every possible combination of the provided options.\n\nThe following example shows you how to configure a job to run your tests on four machines in parallel and then merge the reports into a single report. Don't forget to add\n`reporter: process.env.CI ? 'blob' : 'html',`\nto your\n`playwright.config.ts`\nfile as in the example above.\n\nFirst we add a\n`matrix`\noption to our job configuration with the\n`shardTotal: [4]`\noption containing the total number of shards we want to create and\n`shardIndex: [1, 2, 3, 4]`\nwith an array of the shard numbers.\nThen we run our Playwright tests with the\n`--shard=${{ matrix.shardIndex }}/${{ matrix.shardTotal }}`\noption. This will run our test command for each shard.\nFinally we upload our blob report to the GitHub Actions Artifacts. This will make the blob report available to other jobs in the workflow.\n\n.github/workflows/playwright.yml\n```\n`name:Playwright Testson:push:branches:[main,master]pull_request:branches:[main,master]jobs:playwright-tests:timeout-minutes:60runs-on:ubuntu-lateststrategy:fail-fast:falsematrix:shardIndex:[1,2,3,4]shardTotal:[4]steps:-uses:actions/checkout@v5-uses:actions/setup-node@v5with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Install Playwright browsersrun:npx playwright install--with-deps-name:Run Playwright testsrun:npx playwright test--shard=${{matrix.shardIndex}}/${{matrix.shardTotal}}-name:Upload blob report to GitHub Actions Artifactsif:${{!cancelled()}}uses:actions/upload-artifact@v4with:name:blob-report-${{matrix.shardIndex}}path:blob-reportretention-days:1`\n```\n\nAfter all shards have completed, you can run a separate job that will merge the reports and produce a combined\nHTML report (https://playwright.dev/docs/test-reporters#html-reporter)\n. To ensure the execution order, we make the\n`merge-reports`\njob\ndepend (https://docs.github.com/en/actions/using-jobs/using-jobs-in-a-workflow#defining-prerequisite-jobs)\non our sharded\n`playwright-tests`\njob by adding\n`needs: [playwright-tests]`\n.\n\n.github/workflows/playwright.yml\n```\n`jobs:...merge-reports:# Merge reports after playwright-tests, even if some shards have failedif:${{!cancelled()}}needs:[playwright-tests]runs-on:ubuntu-lateststeps:-uses:actions/checkout@v5-uses:actions/setup-node@v5with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Download blob reports from GitHub Actions Artifactsuses:actions/download-artifact@v5with:path:all-blob-reportspattern:blob-report-*merge-multiple:true-name:Merge into HTML Reportrun:npx playwright merge-reports--reporter html ./all-blob-reports-name:Upload HTML reportuses:actions/upload-artifact@v4with:name:html-report--attempt-${{github.run_attempt}}path:playwright-reportretention-days:14`\n```\n\nYou can now see the reports have been merged and a combined HTML report is available in the GitHub Actions Artifacts tab.", 'We recommend setting\nworkers (https://playwright.dev/docs/api/class-testconfig#test-config-workers)\nto "1" in CI environments to prioritize stability and reproducibility. Running tests sequentially ensures each test gets the full system resources, avoiding potential conflicts. However, if you have a powerful self-hosted CI system, you may enable\nparallel (https://playwright.dev/docs/test-parallel)\ntests. For wider parallelization, consider\nsharding (https://playwright.dev/docs/test-parallel#shard-tests-between-multiple-machines)\n- distributing tests across multiple CI jobs.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from\'@playwright/test\';exportdefaultdefineConfig({// Opt out of parallel tests on CI.workers:process.env.CI?1:undefined,});`\n```']</t>
+          <t>["Sharding can be done at two levels of granularity depending on whether you use the\ntestProject.fullyParallel (https://playwright.dev/docs/api/class-testproject#test-project-fully-parallel)\noption or not. This affects how the tests are balanced across the shards.\n\nSharding with fullyParallel\n\nWhen\n`fullyParallel: true`\nis enabled, Playwright Test runs individual tests in parallel across multiple shards, ensuring each shard receives an even distribution of tests. This allows for test-level granularity, meaning each shard will attempt to balance the number of individual tests it runs. This is the preferred mode for ensuring even load distribution when sharding, as Playwright can optimize shard execution based on the total number of tests.\n\nSharding without fullyParallel\n\nWithout the fullyParallel setting, Playwright Test defaults to file-level granularity, meaning entire test files are assigned to shards (note that the same file may be assigned to different shards across different projects). In this case, the number of tests per file can greatly influence shard distribution. If your test files are not evenly sized (i.e., some files contain many more tests than others), certain shards may end up running significantly more tests, while others may run fewer or even none.\n\nKey Takeaways:\n\nWith\n`fullyParallel: true`\n: Tests are split at the individual test level, leading to more balanced shard execution.\nWithout\n`fullyParallel`\n: Tests are split at the file level, so to balance the shards, it's important to keep your test files small and evenly sized.\nTo ensure the most effective use of sharding, especially in CI environments, it is recommended to use\n`fullyParallel: true`\nwhen aiming for balanced distribution across shards. Otherwise, you may need to manually organize your test files to avoid imbalances.", 'Sharding | Playwright', 'Parallelism | Playwright', 'Retries | Playwright', "GitHub Actions supports\nsharding tests between multiple jobs (https://docs.github.com/en/actions/using-jobs/using-a-matrix-for-your-jobs)\nusing the\njobs.&lt;job_id&gt;.strategy.matrix (https://docs.github.com/en/actions/using-workflows/workflow-syntax-for-github-actions#jobsjob_idstrategymatrix)\noption. The\n`matrix`\noption will run a separate job for every possible combination of the provided options.\n\nThe following example shows you how to configure a job to run your tests on four machines in parallel and then merge the reports into a single report. Don't forget to add\n`reporter: process.env.CI ? 'blob' : 'html',`\nto your\n`playwright.config.ts`\nfile as in the example above.\n\nFirst we add a\n`matrix`\noption to our job configuration with the\n`shardTotal: [4]`\noption containing the total number of shards we want to create and\n`shardIndex: [1, 2, 3, 4]`\nwith an array of the shard numbers.\nThen we run our Playwright tests with the\n`--shard=${{ matrix.shardIndex }}/${{ matrix.shardTotal }}`\noption. This will run our test command for each shard.\nFinally we upload our blob report to the GitHub Actions Artifacts. This will make the blob report available to other jobs in the workflow.\n\n.github/workflows/playwright.yml\n```\n`name:Playwright Testson:push:branches:[main,master]pull_request:branches:[main,master]jobs:playwright-tests:timeout-minutes:60runs-on:ubuntu-lateststrategy:fail-fast:falsematrix:shardIndex:[1,2,3,4]shardTotal:[4]steps:-uses:actions/checkout@v5-uses:actions/setup-node@v5with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Install Playwright browsersrun:npx playwright install--with-deps-name:Run Playwright testsrun:npx playwright test--shard=${{matrix.shardIndex}}/${{matrix.shardTotal}}-name:Upload blob report to GitHub Actions Artifactsif:${{!cancelled()}}uses:actions/upload-artifact@v4with:name:blob-report-${{matrix.shardIndex}}path:blob-reportretention-days:1`\n```\n\nAfter all shards have completed, you can run a separate job that will merge the reports and produce a combined\nHTML report (https://playwright.dev/docs/test-reporters#html-reporter)\n. To ensure the execution order, we make the\n`merge-reports`\njob\ndepend (https://docs.github.com/en/actions/using-jobs/using-jobs-in-a-workflow#defining-prerequisite-jobs)\non our sharded\n`playwright-tests`\njob by adding\n`needs: [playwright-tests]`\n.\n\n.github/workflows/playwright.yml\n```\n`jobs:...merge-reports:# Merge reports after playwright-tests, even if some shards have failedif:${{!cancelled()}}needs:[playwright-tests]runs-on:ubuntu-lateststeps:-uses:actions/checkout@v5-uses:actions/setup-node@v5with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Download blob reports from GitHub Actions Artifactsuses:actions/download-artifact@v5with:path:all-blob-reportspattern:blob-report-*merge-multiple:true-name:Merge into HTML Reportrun:npx playwright merge-reports--reporter html ./all-blob-reports-name:Upload HTML reportuses:actions/upload-artifact@v4with:name:html-report--attempt-${{github.run_attempt}}path:playwright-reportretention-days:14`\n```\n\nYou can now see the reports have been merged and a combined HTML report is available in the GitHub Actions Artifacts tab.", 'Configuration | Playwright', 'Continuous Integration | Playwright']</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1989,10 +2297,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Based on the provided context, here is how these elements interact:
-*   **fullyParallel:** This setting determines the granularity of the distribution. When `fullyParallel: true` is enabled, Playwright splits tests at the individual test level, allowing for an even distribution of tests across shards. Without this setting, Playwright defaults to file-level granularity, which can lead to imbalances if test files are not evenly sized. Using `fullyParallel: true` is the recommended approach for ensuring balanced load distribution across shards.
-*   **Workers:** In CI environments, it is recommended to set `workers` to "1" to prioritize stability and reproducibility by running tests sequentially within each shard. While you can enable parallel tests if you have a powerful self-hosted CI system, sharding is the preferred method for wider parallelization by distributing tests across multiple CI jobs.
-*   **Retries:** The provided text does not contain information regarding how retries interact with sharding, workers, or the balancing of runs.</t>
+          <t>The provided documentation does not contain information regarding how retries interact with sharding and the `fullyParallel` setting to maintain balance and reliability.
+Regarding the interaction between `fullyParallel` and sharding, the documentation states:
+*   **`fullyParallel: true` (Recommended):** Playwright splits tests at the individual test level, allowing it to optimize execution and ensure an even distribution of tests across shards.
+*   **Without `fullyParallel`:** Playwright defaults to file-level granularity. Shards are assigned entire test files, which can lead to imbalances if files are not evenly sized. In this case, you must manually organize test files to ensure balanced distribution.
+The documentation does not provide information on how workers interact with these settings during sharding.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2001,24 +2310,30 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>0.00918825</v>
+      </c>
+      <c r="G30" t="n">
+        <v>34098</v>
+      </c>
+      <c r="H30" t="n">
         <v>0.5</v>
       </c>
-      <c r="G30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4</v>
-      </c>
       <c r="I30" t="n">
-        <v>0.1059602649006623</v>
+        <v>0.57</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3137254901960784</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
+        <v>0.1090909090909091</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -2030,7 +2345,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>['Global setup and teardown | Playwright', 'There are two ways to configure global setup and teardown: using a global setup file and setting it in the config under\nglobalSetup (https://playwright.dev/docs/test-global-setup-teardown#option-2-configure-globalsetup-and-globalteardown)\nor using\nproject dependencies (https://playwright.dev/docs/test-global-setup-teardown#option-1-project-dependencies)\n. With project dependencies, you define a project that runs before all other projects. This is the recommended approach, as it integrates better with the Playwright test runner: your HTML report will include the global setup, traces will be recorded, and fixtures can be used. For a detailed comparison of the two approaches, see the table below.\n\nFeature\nProject Dependencies (recommended)\n`globalSetup`\n(config option)\nRuns before all tests\n✅ Yes\n✅ Yes\nHTML report visibility\n✅ Shown as a separate project\n❌ Not shown\nTrace recording\n✅ Full trace available\n❌ Not supported\nPlaywright fixtures\n✅ Fully supported\n❌ Not supported\nBrowser management\n✅ Via\n`browser`\nfixture\n❌ Fully manual via\n`browserType.launch()`\nParallelism and retries\n✅ Supported via standard config\n❌ Not applicable\nConfig options like\n`headless`\nor\n`testIdAttribute`\n✅ Automatically applied\n❌ Ignored', 'Project dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nare a list of projects that need to run before the tests in another project run. They can be useful for configuring the global setup actions so that one project depends on this running first. Using dependencies allows global setup to produce traces and other artifacts.', "You can use the\n`globalSetup`\noption in the\nconfiguration file (https://playwright.dev/docs/test-configuration#advanced-configuration)\nto set something up once before running all tests. The global setup file must export a single function that takes a config object. This function will be run once before all the tests.\n\nSimilarly, use\n`globalTeardown`\nto run something once after all the tests. Alternatively, let\n`globalSetup`\nreturn a function that will be used as a global teardown. You can pass data such as port number, authentication tokens, etc. from your global setup to your tests using environment variables.\n\nnote\nBeware that\n`globalSetup`\nand\n`globalTeardown`\nlack some features — see the\nintro (https://playwright.dev/docs/test-global-setup-teardown#introduction)\nsection for a detailed comparison. Consider using\nproject dependencies (https://playwright.dev/docs/test-global-setup-teardown#option-1-project-dependencies)\ninstead to get full feature support.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalSetup:require.resolve('./global-setup'),globalTeardown:require.resolve('./global-teardown'),});`\n```"]</t>
+          <t>['Global setup and teardown | Playwright', 'There are two ways to configure global setup and teardown: using a global setup file and setting it in the config under\nglobalSetup (https://playwright.dev/docs/test-global-setup-teardown#option-2-configure-globalsetup-and-globalteardown)\nor using\nproject dependencies (https://playwright.dev/docs/test-global-setup-teardown#option-1-project-dependencies)\n. With project dependencies, you define a project that runs before all other projects. This is the recommended approach, as it integrates better with the Playwright test runner: your HTML report will include the global setup, traces will be recorded, and fixtures can be used. For a detailed comparison of the two approaches, see the table below.\n\nFeature\nProject Dependencies (recommended)\n`globalSetup`\n(config option)\nRuns before all tests\n✅ Yes\n✅ Yes\nHTML report visibility\n✅ Shown as a separate project\n❌ Not shown\nTrace recording\n✅ Full trace available\n❌ Not supported\nPlaywright fixtures\n✅ Fully supported\n❌ Not supported\nBrowser management\n✅ Via\n`browser`\nfixture\n❌ Fully manual via\n`browserType.launch()`\nParallelism and retries\n✅ Supported via standard config\n❌ Not applicable\nConfig options like\n`headless`\nor\n`testIdAttribute`\n✅ Automatically applied\n❌ Ignored', 'Project dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nare a list of projects that need to run before the tests in another project run. They can be useful for configuring the global setup actions so that one project depends on this running first. Using dependencies allows global setup to produce traces and other artifacts.', "You can use the\n`globalSetup`\noption in the\nconfiguration file (https://playwright.dev/docs/test-configuration#advanced-configuration)\nto set something up once before running all tests. The global setup file must export a single function that takes a config object. This function will be run once before all the tests.\n\nSimilarly, use\n`globalTeardown`\nto run something once after all the tests. Alternatively, let\n`globalSetup`\nreturn a function that will be used as a global teardown. You can pass data such as port number, authentication tokens, etc. from your global setup to your tests using environment variables.\n\nnote\nBeware that\n`globalSetup`\nand\n`globalTeardown`\nlack some features — see the\nintro (https://playwright.dev/docs/test-global-setup-teardown#introduction)\nsection for a detailed comparison. Consider using\nproject dependencies (https://playwright.dev/docs/test-global-setup-teardown#option-1-project-dependencies)\ninstead to get full feature support.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalSetup:require.resolve('./global-setup'),globalTeardown:require.resolve('./global-teardown'),});`\n```", "First we add a new project with the name 'setup db'. We then give it a\ntestProject.testMatch (https://playwright.dev/docs/api/class-testproject#test-project-test-match)\nproperty in order to match the file called\n`global.setup.ts`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},// {//   other project// }]});`\n```\n\nThen we add the\ntestProject.dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nproperty to our projects that depend on the setup project and pass into the array the name of our dependency project, which we defined in the previous step:\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},{name:'chromium with db',use:{...devices['Desktop Chrome']},dependencies:['setup db'],},]});`\n```\n\nIn this example the 'chromium with db' project depends on the 'setup db' project. We then create a setup test, stored at root level of your project (note that setup and teardown code must be defined as regular tests by calling\ntest() (https://playwright.dev/docs/api/class-test#test-call)\nfunction):\n\ntests/global.setup.ts\n```\n`import{testassetup}from'@playwright/test';setup('create new database',async({})=&gt;{console.log('creating new database...');// Initialize the database});`\n```\n\ntests/menu.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('menu',async({page})=&gt;{// Your test that depends on the database});`\n```", "Here is a global setup example that authenticates once and reuses authentication state in tests. It uses the\n`baseURL`\nand\n`storageState`\noptions from the configuration file.\n\nglobal-setup.ts\n```\n`import{chromium,typeFullConfig}from'@playwright/test';asyncfunctionglobalSetup(config:FullConfig){const{baseURL,storageState}=config.projects[0].use;constbrowser=awaitchromium.launch();constpage=awaitbrowser.newPage();awaitpage.goto(baseURL!);awaitpage.getByLabel('User Name').fill('user');awaitpage.getByLabel('Password').fill('password');awaitpage.getByText('Sign in').click();awaitpage.context().storageState({path:storageStateasstring});awaitbrowser.close();}exportdefaultglobalSetup;`\n```\n\nSpecify\n`globalSetup`\n,\n`baseURL`\nand\n`storageState`\nin the configuration file.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalSetup:require.resolve('./global-setup'),use:{baseURL:'http://localhost:3000/',storageState:'state.json',},});`\n```\n\nTests start already authenticated because we specify\n`storageState`\nthat was populated by global setup.\n\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{awaitpage.goto('/');// You are signed in!});`\n```\n\nYou can make arbitrary data available in your tests from your global setup file by setting them as environment variables via\n`process.env`\n.\n\nglobal-setup.ts\n```\n`importtype{FullConfig}from'@playwright/test';asyncfunctionglobalSetup(config:FullConfig){process.env.FOO='some data';// Or a more complicated data structure as JSON:process.env.BAR=JSON.stringify({some:'data'});}exportdefaultglobalSetup;`\n```\n\nTests have access to the\n`process.env`\nproperties set in the global setup.\n\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// environment variables which are set in globalSetup are only available inside test().const{FOO,BAR}=process.env;// FOO and BAR properties are populated.expect(FOO).toEqual('some data');constcomplexData=JSON.parse(BAR);expect(BAR).toEqual({some:'data'});});`\n```"]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2040,15 +2355,15 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>You should use project dependencies, as this is the recommended approach.
-Project dependencies are preferred because they integrate better with the Playwright test runner. Specifically, they offer the following advantages over the `globalSetup` config option:
+          <t>You should use **project dependencies**, as this is the recommended approach.
+Project dependencies are preferred because they integrate better with the Playwright test runner, providing the following advantages over the `globalSetup` config option:
 *   **HTML Report:** The setup is shown as a separate project in the HTML report.
 *   **Trace Recording:** Full trace recording is available.
 *   **Fixtures:** Playwright fixtures are fully supported.
-*   **Browser Management:** Browser management is handled via the `browser` fixture rather than manual launching.
+*   **Browser Management:** You can use the `browser` fixture instead of manual management via `browserType.launch()`.
 *   **Parallelism and Retries:** Supported via standard configuration.
-*   **Config Options:** Settings like `headless` or `testIdAttribute` are automatically applied.
-In contrast, the `globalSetup` config option does not support trace recording or fixtures, is not shown in the HTML report, and requires manual browser management.</t>
+*   **Config Options:** Options like `headless` or `testIdAttribute` are automatically applied.
+In contrast, the `globalSetup` config option does not support trace recording or fixtures, is not shown in the HTML report, requires manual browser management, and ignores standard config options.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2057,137 +2372,191 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0.00837325</v>
       </c>
       <c r="G31" t="n">
-        <v>0.38</v>
+        <v>31713</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1271186440677966</v>
+        <v>0.35</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3571428571428572</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
+        <v>0.140495867768595</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.4047619047619048</v>
+      </c>
+      <c r="M31" t="n">
         <v>0.6388888888675925</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Can my one-time setup (via project dependencies) share the same fixtures my tests use, and why choose that over globalSetup?</t>
+          <t>Our app registers a service worker for offline support. Every route handler I install works fine against a build with the worker disabled, but against the real build some requests reach the network untouched while others are intercepted, and which is which seems to change between runs. What decides whether a request is interceptable here, and what's the sane way to test against this app?</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['Global setup and teardown | Playwright', 'There are two ways to configure global setup and teardown: using a global setup file and setting it in the config under\nglobalSetup (https://playwright.dev/docs/test-global-setup-teardown#option-2-configure-globalsetup-and-globalteardown)\nor using\nproject dependencies (https://playwright.dev/docs/test-global-setup-teardown#option-1-project-dependencies)\n. With project dependencies, you define a project that runs before all other projects. This is the recommended approach, as it integrates better with the Playwright test runner: your HTML report will include the global setup, traces will be recorded, and fixtures can be used. For a detailed comparison of the two approaches, see the table below.\n\nFeature\nProject Dependencies (recommended)\n`globalSetup`\n(config option)\nRuns before all tests\n✅ Yes\n✅ Yes\nHTML report visibility\n✅ Shown as a separate project\n❌ Not shown\nTrace recording\n✅ Full trace available\n❌ Not supported\nPlaywright fixtures\n✅ Fully supported\n❌ Not supported\nBrowser management\n✅ Via\n`browser`\nfixture\n❌ Fully manual via\n`browserType.launch()`\nParallelism and retries\n✅ Supported via standard config\n❌ Not applicable\nConfig options like\n`headless`\nor\n`testIdAttribute`\n✅ Automatically applied\n❌ Ignored', 'Fixtures | Playwright', "Dependencies are a list of projects that need to run before the tests in another project run. They can be useful for configuring the global setup actions so that one project depends on this running first. When using project dependencies,\ntest reporters (https://playwright.dev/docs/test-reporters)\nwill show the setup tests and the\ntrace viewer (https://playwright.dev/docs/trace-viewer)\nwill record traces of the setup. You can use the inspector to inspect the DOM snapshot of the trace of your setup tests and you can also use\nfixtures (https://playwright.dev/docs/test-fixtures)\ninside your setup.\n\nIn this example the chromium, firefox and webkit projects depend on the setup project.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[{name:'setup',testMatch:'**/*.setup.ts',},{name:'chromium',use:{...devices['Desktop Chrome']},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox']},dependencies:['setup'],},{name:'webkit',use:{...devices['Desktop Safari']},dependencies:['setup'],},],});`\n```", 'Projects | Playwright', 'Project dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nare a list of projects that need to run before the tests in another project run. They can be useful for configuring the global setup actions so that one project depends on this running first. Using dependencies allows global setup to produce traces and other artifacts.', 'For more detailed examples check out:\n\nour\nauthentication (https://playwright.dev/docs/auth)\nguide\nour blog post\nA better global setup in Playwright reusing login with project dependencies (https://dev.to/playwright/a-better-global-setup-in-playwright-reusing-login-with-project-dependencies-14)\nv1.31 release video (https://youtu.be/PI50YAPTAs4)\nto see the demo']</t>
+          <t>['Service Workers | Playwright', 'Any network request made by the\nService Worker\nis reported through the\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nobject:\n\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\n,\nbrowserContext.on(\'requestfinished\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request-finished)\n,\nbrowserContext.on(\'response\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-response)\nand\nbrowserContext.on(\'requestfailed\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request-failed)\nare fired\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nsees the request\nrequest.serviceWorker() (https://playwright.dev/docs/api/class-request#request-service-worker)\nwill be set to the Service\nWorker (https://playwright.dev/docs/api/class-worker)\ninstance, and\nrequest.frame() (https://playwright.dev/docs/api/class-request#request-frame)\nwill\nthrow\n\nAdditionally, for any network request made by the\nPage\n, method\nresponse.fromServiceWorker() (https://playwright.dev/docs/api/class-response#response-from-service-worker)\nreturn\n`true`\nwhen the request was handled a Service Worker\'s fetch handler.\n\nConsider a simple service worker that fetches every request made by the page:\n\ntransparent-service-worker.js\n```\n`self.addEventListener(\'fetch\',event=&gt;{// actually make the requestconstresponsePromise=fetch(event.request);// send it back to the pageevent.respondWith(responsePromise);});self.addEventListener(\'activate\',event=&gt;{event.waitUntil(clients.claim());});`\n```\n\nIf\n`index.html`\nregisters this service worker, and then fetches\n`data.json`\n, the following Request/Response events would be emitted (along with the corresponding network lifecycle events):\n\nEvent\nOwner\nURL\nRouted\nresponse.fromServiceWorker() (https://playwright.dev/docs/api/class-response#response-from-service-worker)\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nFrame (https://playwright.dev/docs/api/class-frame)\nindex.html\nYes\npage.on(\'request\') (https://playwright.dev/docs/api/class-page#page-event-request)\nFrame (https://playwright.dev/docs/api/class-frame)\nindex.html\nYes\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nService\nWorker (https://playwright.dev/docs/api/class-worker)\ntransparent-service-worker.js\nYes\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nService\nWorker (https://playwright.dev/docs/api/class-worker)\ndata.json\nYes\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nFrame (https://playwright.dev/docs/api/class-frame)\ndata.json\nYes\npage.on(\'request\') (https://playwright.dev/docs/api/class-page#page-event-request)\nFrame (https://playwright.dev/docs/api/class-frame)\ndata.json\nYes\n\nSince the example Service Worker just acts a basic transparent "proxy":\n\nThere\'s 2\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nevents for\n`data.json`\n; one\nFrame (https://playwright.dev/docs/api/class-frame)\n-owned, the other Service\nWorker (https://playwright.dev/docs/api/class-worker)\n-owned.\nOnly the Service\nWorker (https://playwright.dev/docs/api/class-worker)\n-owned request for the resource was routable via\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n; the\nFrame (https://playwright.dev/docs/api/class-frame)\n-owned events for\n`data.json`\nare not routeable, as they would not have even had the possibility to hit the external network since the Service Worker has a fetch handler registered.\n\ncaution\nIt\'s important to note: calling\nrequest.frame() (https://playwright.dev/docs/api/class-request#request-frame)\nor\nresponse.frame() (https://playwright.dev/docs/api/class-response#response-frame)\nwill\nthrow\nan exception, if called on a\nRequest (https://playwright.dev/docs/api/class-request)\n/\nResponse (https://playwright.dev/docs/api/class-response)\nthat has a non-null\nrequest.serviceWorker() (https://playwright.dev/docs/api/class-request#request-service-worker)\n.', "Playwright's built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nallow your tests to natively route requests and perform mocking and interception.\n\nIf you're using Playwright's native\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n, and it appears network events are missing, disable Service Workers by setting\nserviceWorkers (https://playwright.dev/docs/api/class-browser#browser-new-context-option-service-workers)\nto\n`'block'`\n.\n\nIt might be that you are using a mock tool such as Mock Service Worker (MSW). While this tool works out of the box for mocking responses, it adds its own Service Worker that takes over the network requests, hence making them invisible to\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n. If you are interested in both network testing and mocking, consider using built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nfor\nresponse mocking (https://playwright.dev/docs/network#handle-requests)\n.", 'Network | Playwright', "```\n`awaitcontext.route('**',asyncroute=&gt;{if(route.request().serviceWorker()){// NB: calling route.request().frame() here would THROWawaitroute.fulfill({contentType:'text/plain',status:200,body:'from sw',});}else{awaitroute.continue();}});`\n```", "Playwright allows to disable Service Workers during testing. This makes tests more predictable and performant. However, if your actual page uses a Service Worker, the behavior might be different.\n\nTo disable service workers, set\ntestOptions.serviceWorkers (https://playwright.dev/docs/api/class-testoptions#test-options-service-workers)\nto\n`'block'`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{serviceWorkers:'allow'},});`\n```", "You can use\nbrowserContext.serviceWorkers() (https://playwright.dev/docs/api/class-browsercontext#browser-context-service-workers)\nto list the Service\nWorker (https://playwright.dev/docs/api/class-worker)\ns, or specifically watch for the Service\nWorker (https://playwright.dev/docs/api/class-worker)\nif you anticipate a page will trigger its\nregistration (https://developer.mozilla.org/en-US/docs/Web/API/ServiceWorkerContainer/register)\n:\n\n```\n`constserviceWorkerPromise=context.waitForEvent('serviceworker');awaitpage.goto('/example-with-a-service-worker.html');constserviceworker=awaitserviceWorkerPromise;`\n```\n\nbrowserContext.on('serviceworker') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-service-worker)\nevent is fired\nbefore\nthe Service Worker has taken control over the page, so\nbefore\nevaluating in the worker with\nworker.evaluate() (https://playwright.dev/docs/api/class-worker#worker-evaluate)\nyou should wait on its activation.\n\nThere are more idiomatic methods of waiting for a Service Worker to be activated, but the following is an implementation agnostic method:\n\n```\n`awaitpage.evaluate(async()=&gt;{constregistration=awaitwindow.navigator.serviceWorker.getRegistration();if(registration.active?.state==='activated')return;awaitnewPromise(resolve=&gt;{window.navigator.serviceWorker.addEventListener('controllerchange',resolve);});});`\n```"]</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['This is the recommended approach, as it integrates better with the Playwright test runner: your HTML report will include the global setup, traces will be recorded, and fixtures can be used.', "Fixtures are reusable between test files - you can define them once and use them in all your tests. That's how Playwright's built-in page fixture works. So if you have a helper function that is used in multiple tests, consider turning it into a fixture."]</t>
+          <t>["If you're looking to do general network mocking, routing, and interception, please see the Network Guide first. Playwright provides built-in APIs for this use case that don't require the information below. However, if you're interested in requests made by Service Workers themselves, please read below.", "To disable service workers, set testOptions.serviceWorkers to 'block'.", 'Only the Service Worker-owned request for the resource was routable via browserContext.route(); the Frame-owned events for data.json are not routeable, as they would not have even had the possibility to hit the external network since the Service Worker has a fetch handler registered.', "await context.route('**', async route =&gt; { if (route.request().serviceWorker()) { // NB: calling route.request().frame() here would THROW await route.fulfill({ contentType: 'text/plain', status: 200, body: 'from sw', }); } else { await route.continue(); } });", 'Requests for updated Service Worker main script code currently cannot be routed.']</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Yes, you can use fixtures in your one-time setup when using project dependencies, as they are fully supported.
-You should choose project dependencies over `globalSetup` because it is the recommended approach that integrates better with the Playwright test runner. Specifically, choosing project dependencies provides the following advantages over `globalSetup`:
-*   **Fixtures:** They are fully supported in project dependencies but not in `globalSetup`.
-*   **HTML Report:** Setup is shown as a separate project in the HTML report, whereas it is not shown with `globalSetup`.
-*   **Trace Recording:** Full trace recording is available with project dependencies but not supported with `globalSetup`.
-*   **Browser Management:** You can use the `browser` fixture with project dependencies, whereas `globalSetup` requires manual management via `browserType.launch()`.
-*   **Config Options:** Options like `headless` or `testIdAttribute` are automatically applied with project dependencies but ignored with `globalSetup`.
-*   **Parallelism and Retries:** These are supported via standard config with project dependencies but are not applicable to `globalSetup`.</t>
+          <t>Whether a request is interceptable depends on whether it is owned by the Service Worker or the Frame. When a Service Worker has a fetch handler registered, Frame-owned requests for resources are not routable via `browserContext.route()` because they do not hit the external network. Only Service Worker-owned requests are routable. You can identify these requests by checking `request.serviceWorker()`; if it is non-null, the request is owned by the Service Worker.
+To test against this app, you have two primary options:
+1.  **Disable Service Workers:** If you want to make tests more predictable and performant, you can disable Service Workers by setting `serviceWorkers` to `'block'` in your `playwright.config.ts`. Note that this may cause the application to behave differently than it does in production if it relies on Service Worker logic.
+2.  **Route Service Worker Requests:** If you must test with the Service Worker enabled, you can use `browserContext.route()` to specifically target requests made by the Service Worker. You can check if a request is owned by the Service Worker using `route.request().serviceWorker()` and handle it accordingly:
+```javascript
+await context.route('**', async route =&gt; {
+  if (route.request().serviceWorker()) {
+    // Handle Service Worker-owned request
+    await route.fulfill({
+      contentType: 'text/plain',
+      status: 200,
+      body: 'from sw',
+    });
+  } else {
+    // Handle other requests
+    await route.continue();
+  }
+});
+```
+When using this approach, be aware that calling `route.request().frame()` on a request where `request.serviceWorker()` is non-null will throw an exception.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yes — a key advantage of project-dependency setup over globalSetup is that setup tests can use fixtures, and fixtures are reusable across files, so the same helpers back both your setup and your tests.</t>
+          <t>Whether a request is routable depends on who owns it. Once a service worker with a fetch handler is installed it sits between the page and the network: the page-owned request is served by the worker and never reaches the network, so it isn't routable, while the worker's own outbound request is a separate, service-worker-owned request that context routing does see. That split is why interception looks inconsistent — you're catching some requests at one layer and missing others at the other, and which layer serves a given resource depends on the worker's cache state, hence the run-to-run variation. If you're doing ordinary network mocking, the documented answer is not to reason about this at all: set `serviceWorkers: 'block'` in the config's `use` options so the worker never registers and everything is page-owned and routable. Only if you specifically need to assert on the worker's own traffic should you leave them enabled and branch inside the handler on `route.request().serviceWorker()` — noting that calling .frame() on such a request throws, and that requests for updated worker scripts cannot currently be routed at all.</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.75</v>
+        <v>0.010926</v>
       </c>
       <c r="G32" t="n">
-        <v>0.12</v>
+        <v>39839</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0.08609271523178808</v>
+        <v>0.58</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3823529411764706</v>
+        <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>0.4761904761746032</v>
+        <v>0.2240663900414938</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5</v>
+        <v>0.2769230769230769</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.8874999999778125</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>I want a local dev server started before tests while developing, but on CI it should always boot fresh. How do I wire up webServer for both?</t>
+          <t>Our GitHub Actions job installs cleanly — `npm ci` is green — and then every test fails at browser launch complaining about missing shared libraries. It's an ubuntu-latest runner, and the identical commit runs fine on all three of our developers' machines. What is the CI box missing that a laptop already has, and what's the durable way to fix it?</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>['Web server | Playwright', 'Use the\n`webServer`\nproperty in your Playwright config to launch a development web server during the tests.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({// Run your local dev server before starting the testswebServer:{command:\'npm run start\',url:\'http://localhost:3000\',reuseExistingServer:!process.env.CI,stdout:\'ignore\',stderr:\'pipe\',},});`\n```\n\nProperty\nDescription\ntestConfig.webServer (https://playwright.dev/docs/api/class-testconfig#test-config-web-server)\nLaunch a development web server (or multiple) during the tests.\n`command`\nShell command to start the local dev server of your app.\n`cwd`\nCurrent working directory of the spawned process, defaults to the directory of the configuration file.\n`env`\nEnvironment variables for the command. Defaults to inheriting\n`process.env`\nwith\n`PLAYWRIGHT_TEST=1`\nadded.\n`gracefulShutdown`\nHow to shut down the process. If unspecified, the process group is forcefully\n`SIGKILL`\ned. If set to\n`{ signal: \'SIGTERM\', timeout: 500 }`\n, the process group is sent a\n`SIGTERM`\nsignal, followed by\n`SIGKILL`\nif it doesn\'t exit within 500ms. You can also use\n`SIGINT`\nas the signal instead. A\n`0`\ntimeout means no\n`SIGKILL`\nwill be sent. Windows doesn\'t support\n`SIGTERM`\nand\n`SIGINT`\nsignals, so this option is ignored on Windows. Note that shutting down a Docker container requires\n`SIGTERM`\n.\n`ignoreHTTPSErrors`\nWhether to ignore HTTPS errors when fetching the\n`url`\n. Defaults to\n`false`\n.\n`name`\nSpecifies a custom name for the web server. This name will be prefixed to log messages. Defaults to\n`[WebServer]`\n.\n`port`\nDeprecated\n. Use\n`url`\ninstead. The port that your http server is expected to appear on. It does wait until it accepts connections. Either\n`port`\nor\n`url`\nshould be specified.\n`reuseExistingServer`\nIf\n`true`\n, it will re-use an existing server on the\n`port`\nor\n`url`\nwhen available. If no server is running on that\n`port`\nor\n`url`\n, it will run the command to start a new server. If\n`false`\n, it will throw if an existing process is listening on the\n`port`\nor\n`url`\n. This should be commonly set to\n`!process.env.CI`\nto allow the local dev server when running tests locally.\n`stderr`\nWhether to pipe the stderr of the command to the process stderr or ignore it. Defaults to\n`"pipe"`\n.\n`stdout`\nIf\n`"pipe"`\n, it will pipe the stdout of the command to the process stdout. If\n`"ignore"`\n, it will ignore the stdout of the command. Default to\n`"ignore"`\n.\n`timeout`\nHow long to wait for the process to start up and be available in milliseconds. Defaults to 60000.\n`url`\nURL of your http server that is expected to return a 2xx, 3xx, 400, 401, 402, or 403 status code when the server is ready to accept connections. Either\n`port`\nor\n`url`\nshould be specified. If both\n`url`\nand\n`wait`\nare specified, the server is considered started when at least one of the conditions is met.\n`wait`\nConsider command started only when given output has been produced. Takes an object with optional\n`stdout`\nand/or\n`stderr`\nregular expressions. Named capture groups in the regex are stored in the environment, for example\n`/Listening on port (?&lt;my_server_port&gt;\\d+)/`\nwill store the port number in\n`process.env[\'MY_SERVER_PORT\']`\n. If both\n`url`\nand\n`wait`\nare specified, the server is considered started when at least one of the conditions is met.']</t>
+          <t>["System dependencies can get installed automatically. This is useful for CI environments.\n\n```\n`npx playwright install-deps`\n```\n\nYou can also install the dependencies for a single browser by passing it as an argument:\n\n```\n`npx playwright install-deps chromium`\n```\n\nIt's also possible to combine\n`install-deps`\nwith\n`install`\nso that the browsers and OS dependencies are installed with a single command.\n\n```\n`npx playwrightinstall--with-deps chromium`\n```\n\nSee\nsystem requirements (https://playwright.dev/docs/intro#system-requirements)\nfor officially supported operating systems.", 'Browsers | Playwright', 'Playwright supports the\n`DEBUG`\nenvironment variable to output debug logs during execution. Setting it to\n`pw:browser`\nis helpful while debugging\n`Error: Failed to launch browser`\nerrors.\n\n```\n`DEBUG=pw:browser npx playwrighttest`\n```', 'Tests will run on push or pull request on branches main/master. The\nworkflow (https://docs.github.com/en/actions/using-workflows/about-workflows)\nwill install all dependencies, install Playwright and then run the tests. It will also create the HTML report.\n\n.github/workflows/playwright.yml\n```\n`name:Playwright Testson:push:branches:[main,master]pull_request:branches:[main,master]jobs:test:timeout-minutes:60runs-on:ubuntu-lateststeps:-uses:actions/checkout@v5-uses:actions/setup-node@v6with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Install Playwright Browsersrun:npx playwright install--with-deps-name:Run Playwright testsrun:npx playwright test-uses:actions/upload-artifact@v5if:${{!cancelled()}}with:name:playwright-reportpath:playwright-report/retention-days:30`\n```', 'Continuous Integration | Playwright', 'Playwright tests can be executed in CI environments. We have created sample configurations for common CI providers.\n\n3 steps to get your tests running on CI:\n\nEnsure CI agent can run browsers\n: Use\nour Docker image (https://playwright.dev/docs/docker)\nin Linux agents or install your dependencies using the\nCLI (https://playwright.dev/docs/browsers#install-system-dependencies)\n.\nInstall Playwright\n:\n```\n`# Install NPM packagesnpmci# Install Playwright browsers and dependenciesnpx playwrightinstall--with-deps`\n```\nRun your tests\n:\n```\n`npx playwrighttest`\n```', "GitHub Actions support\nrunning jobs in a container (https://docs.github.com/en/actions/using-jobs/running-jobs-in-a-container)\nby using the\njobs.&lt;job_id&gt;.container (https://docs.github.com/en/actions/using-workflows/workflow-syntax-for-github-actions#jobsjob_idcontainer)\noption. This is useful to not pollute the host environment with dependencies and to have a consistent environment for e.g. screenshots/visual regression testing across different operating systems.\n\n.github/workflows/playwright.yml\n```\n`name:Playwright Testson:push:branches:[main,master]pull_request:branches:[main,master]jobs:playwright:name:'Playwright Tests'runs-on:ubuntu-latestcontainer:image:mcr.microsoft.com/playwright:v1.60.0-nobleoptions:--user 1001steps:-uses:actions/checkout@v5-uses:actions/setup-node@v6with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Run your testsrun:npx playwright test`\n```"]</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>["Playwright comes with a webServer option in the config file which gives you the ability to launch a local dev server before running your tests. This is ideal for when writing your tests during development and when you don't have a staging or production url to test against.", 'Playwright tests can be executed in CI environments. We have created sample configurations for common CI providers.']</t>
+          <t>['Ensure CI agent can run browsers: Use our Docker image in Linux agents or install your dependencies using the CLI.', '# Install NPM packages npm ci # Install Playwright browsers and dependencies npx playwright install --with-deps', 'The Command line tools can be used to install all operating system dependencies in CI.', 'GitHub Actions support running jobs in a container by using the jobs.&lt;job_id&gt;.container option. This is useful to not pollute the host environment with dependencies and to have a consistent environment for e.g. screenshots/visual regression testing across different operating systems.']</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>To wire up the `webServer` so that it reuses an existing server locally but boots fresh on CI, set the `reuseExistingServer` property to `!process.env.CI` within your `playwright.config.ts` file:
-```typescript
-import { defineConfig } from '@playwright/test';
-export default defineConfig({
-  webServer: {
-    command: 'npm run start',
-    url: 'http://localhost:3000',
-    reuseExistingServer: !process.env.CI,
-  },
-});
-```</t>
+          <t>The CI runner is missing the necessary system dependencies required to launch browsers, which are present on your local machines but not pre-installed on the `ubuntu-latest` environment.
+To fix this durably, you have two supported options:
+### 1. Install dependencies via CLI (Recommended for standard runners)
+You must ensure the CI agent installs the required system dependencies alongside the browsers. Update your GitHub Actions workflow to use the following command:
+```bash
+npx playwright install --with-deps
+```
+This command installs both the Playwright browsers and the required OS-level shared libraries. Your workflow steps should look like this:
+```yaml
+- name: Install dependencies
+  run: npm ci
+- name: Install Playwright Browsers
+  run: npx playwright install --with-deps
+- name: Run Playwright tests
+  run: npx playwright test
+```
+### 2. Use a Docker container
+Alternatively, you can run your job inside a pre-configured Playwright Docker image. This ensures a consistent environment and avoids polluting the host runner with dependencies. You can configure this in your workflow file using the `container` option:
+```yaml
+jobs:
+  playwright:
+    runs-on: ubuntu-latest
+    container:
+      image: mcr.microsoft.com/playwright:v1.60.0-noble
+    steps:
+      - uses: actions/checkout@v5
+      - uses: actions/setup-node@v6
+        with:
+          node-version: lts/*
+      - name: Install dependencies
+        run: npm ci
+      - name: Run your tests
+        run: npx playwright test
+```
+If you need to debug further, you can set the `DEBUG` environment variable to `pw:browser` to output logs during execution.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Configure webServer with your start command and URL and set reuseExistingServer: !process.env.CI. Locally it reuses an already-running server; on CI — where these tests are meant to run — it won't reuse and starts a clean one.</t>
+          <t>Installing the npm package is not the same as provisioning a machine that can run browsers, and that's the gap. `npm ci` fetches the library; the browser binaries are downloaded separately, and those binaries need operating-system level libraries that a developer machine already has from everyday browser use and a bare Linux runner does not. So there are two things to install, and the combined step is `npx playwright install --with-deps`, which fetches the browsers and the OS dependencies together — that's exactly the step the recommended GitHub Actions workflow runs between `npm ci` and the test command. The alternative, and the more durable one if you also do visual comparison, is to run the job inside the official container image via `jobs.&lt;job_id&gt;.container`: it keeps the dependencies out of the host environment and gives you a consistent rendering environment, which matters because screenshots differ across platforms.</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0.009942499999999001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.67</v>
+        <v>36635</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.77</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2564102564102564</v>
+        <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>0.49999999995</v>
+        <v>0.1637931034482759</v>
       </c>
       <c r="L33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.8734126983981415</v>
+      </c>
+      <c r="N33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2199,7 +2568,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>['API testing | Playwright', 'Authentication | Playwright', "Web apps use cookie-based or token-based authentication, where authenticated state is stored as\ncookies (https://developer.mozilla.org/en-US/docs/Web/HTTP/Cookies)\n. Playwright provides\napiRequestContext.storageState() (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state)\nmethod that can be used to retrieve storage state from an authenticated context and then create new contexts with that state.\n\nStorage state is interchangeable between\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nand\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n. You can use it to log in via API calls and then create a new context with cookies already there. The following code snippet retrieves state from an authenticated\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nand creates a new\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nwith that state.\n\n```\n`constrequestContext=awaitrequest.newContext({httpCredentials:{username:'user',password:'passwd'}});awaitrequestContext.get(`https://api.example.com/login`);// Save storage state into the file.awaitrequestContext.storageState({path:'state.json'});// Create a new context with the saved storage state.constcontext=awaitbrowser.newContext({storageState:'state.json'});`\n```", "When to use\n\nYour web application supports authenticating via API that is easier/faster than interacting with the app UI.\n\nDetails\n\nWe will send the API request with\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nand then save authenticated state as usual.\n\nIn the\nsetup project (https://playwright.dev/docs/auth#basic-shared-account-in-all-tests)\n:\n\ntests/auth.setup.ts\n```\n`import{testassetup}from'@playwright/test';constauthFile='playwright/.auth/user.json';setup('authenticate',async({request})=&gt;{// Send authentication request. Replace with your own.awaitrequest.post('https://github.com/login',{form:{'user':'user','password':'password'}});awaitrequest.storageState({path:authFile});});`\n```\n\nAlternatively, in a\nworker fixture (https://playwright.dev/docs/auth#moderate-one-account-per-parallel-worker)\n:\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,request}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constcontext=awaitrequest.newContext({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Send authentication request. Replace with your own.awaitcontext.post('https://github.com/login',{form:{'user':'user','password':'password'}});awaitcontext.storageState({path:fileName});awaitcontext.dispose();awaituse(fileName);},{scope:'worker'}],});`\n```", 'APIRequestContext | Playwright\n\nThis API is used for the Web API testing. You can use it to trigger API endpoints, configure micro-services, prepare environment or the service to your e2e test.\n\nEach Playwright browser context has an associated\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n, accessible via\nbrowserContext.request (https://playwright.dev/docs/api/class-browsercontext#browser-context-request)\nor\npage.request (https://playwright.dev/docs/api/class-page#page-request)\n(these return the\n\nsame instance\n—\n`page.request`\nis a shortcut for\n`page.context().request`\n). You can also create a standalone, isolated instance with\napiRequest.newContext() (https://playwright.dev/docs/api/class-apirequest#api-request-new-context)\n.\n\nCookie management\n\nThe\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nreturned by\nbrowserContext.request (https://playwright.dev/docs/api/class-browsercontext#browser-context-request)\nand\n\npage.request (https://playwright.dev/docs/api/class-page#page-request)\nuses the same cookie jar as its\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\n:\n\nIf you want API requests that do\nnot\nshare cookies with the browser, create an isolated context via\napiRequest.newContext() (https://playwright.dev/docs/api/class-apirequest#api-request-new-context)\n. Such\n`APIRequestContext`\nobject will have its own isolated cookie storage.', 'Added in: v1.16\n\napiRequestContext.storageState\n\nReturns storage state for this request context, contains current cookies and local storage snapshot if it was passed to the constructor.\n\nUsage\n\n```\n`awaitapiRequestContext.storageState();awaitapiRequestContext.storageState(options);`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`indexedDB`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.51\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state-option-indexed-db)\nSet to\n`true`\nto include IndexedDB in the storage state snapshot.\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state-option-path)\nThe file path to save the storage state to. If\npath (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state-option-path)\nis a relative path, then it is resolved relative to current working directory. If no path is provided, storage state is still returned, but won\'t be saved to the disk.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state-return)\n`cookies`\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`domain`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`expires`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\nUnix time in seconds.\n`httpOnly`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n`secure`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n`sameSite`\n"Strict" | "Lax" | "None"\n`origins`\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n`origin`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`localStorage`\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)', "TestOptions | Playwright\n\nPlaywright Test provides many options to configure test environment,\nBrowser (https://playwright.dev/docs/api/class-browser)\n,\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nand more.\n\nThese options are usually provided in the\nconfiguration file (https://playwright.dev/docs/test-configuration)\nthrough\ntestConfig.use (https://playwright.dev/docs/api/class-testconfig#test-config-use)\nand\ntestProject.use (https://playwright.dev/docs/api/class-testproject#test-project-use)\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{headless:false,viewport:{width:1280,height:720},ignoreHTTPSErrors:true,video:'on-first-retry',},});`\n```\n\nAlternatively, with\ntest.use() (https://playwright.dev/docs/api/class-test#test-use)\nyou can override some options for a file.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';// Run tests in this file with portrait-like viewport.test.use({viewport:{width:600,height:900}});test('my portrait test',async({page})=&gt;{// ...});`\n```"]</t>
+          <t>["Web apps use cookie-based or token-based authentication, where authenticated state is stored as\ncookies (https://developer.mozilla.org/en-US/docs/Web/HTTP/Cookies)\n. Playwright provides\napiRequestContext.storageState() (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state)\nmethod that can be used to retrieve storage state from an authenticated context and then create new contexts with that state.\n\nStorage state is interchangeable between\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nand\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n. You can use it to log in via API calls and then create a new context with cookies already there. The following code snippet retrieves state from an authenticated\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nand creates a new\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nwith that state.\n\n```\n`constrequestContext=awaitrequest.newContext({httpCredentials:{username:'user',password:'passwd'}});awaitrequestContext.get(`https://api.example.com/login`);// Save storage state into the file.awaitrequestContext.storageState({path:'state.json'});// Create a new context with the saved storage state.constcontext=awaitbrowser.newContext({storageState:'state.json'});`\n```", "When to use\n\nYour web application supports authenticating via API that is easier/faster than interacting with the app UI.\n\nDetails\n\nWe will send the API request with\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nand then save authenticated state as usual.\n\nIn the\nsetup project (https://playwright.dev/docs/auth#basic-shared-account-in-all-tests)\n:\n\ntests/auth.setup.ts\n```\n`import{testassetup}from'@playwright/test';constauthFile='playwright/.auth/user.json';setup('authenticate',async({request})=&gt;{// Send authentication request. Replace with your own.awaitrequest.post('https://github.com/login',{form:{'user':'user','password':'password'}});awaitrequest.storageState({path:authFile});});`\n```\n\nAlternatively, in a\nworker fixture (https://playwright.dev/docs/auth#moderate-one-account-per-parallel-worker)\n:\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,request}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constcontext=awaitrequest.newContext({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Send authentication request. Replace with your own.awaitcontext.post('https://github.com/login',{form:{'user':'user','password':'password'}});awaitcontext.storageState({path:fileName});awaitcontext.dispose();awaituse(fileName);},{scope:'worker'}],});`\n```", 'APIRequestContext | Playwright\n\nThis API is used for the Web API testing. You can use it to trigger API endpoints, configure micro-services, prepare environment or the service to your e2e test.\n\nEach Playwright browser context has an associated\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n, accessible via\nbrowserContext.request (https://playwright.dev/docs/api/class-browsercontext#browser-context-request)\nor\npage.request (https://playwright.dev/docs/api/class-page#page-request)\n(these return the\n\nsame instance\n—\n`page.request`\nis a shortcut for\n`page.context().request`\n). You can also create a standalone, isolated instance with\napiRequest.newContext() (https://playwright.dev/docs/api/class-apirequest#api-request-new-context)\n.\n\nCookie management\n\nThe\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nreturned by\nbrowserContext.request (https://playwright.dev/docs/api/class-browsercontext#browser-context-request)\nand\n\npage.request (https://playwright.dev/docs/api/class-page#page-request)\nuses the same cookie jar as its\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\n:\n\nIf you want API requests that do\nnot\nshare cookies with the browser, create an isolated context via\napiRequest.newContext() (https://playwright.dev/docs/api/class-apirequest#api-request-new-context)\n. Such\n`APIRequestContext`\nobject will have its own isolated cookie storage.', 'API testing | Playwright', 'Authentication | Playwright', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", 'Global setup and teardown | Playwright']</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2209,12 +2578,21 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Yes, you can authenticate through API calls and then hand that session to a browser context.
-According to the provided documentation, storage state is interchangeable between `BrowserContext` and `APIRequestContext`. You can log in via API calls, retrieve the storage state using `apiRequestContext.storageState()`, and then create a new `BrowserContext` with that state.
-The process generally involves:
-1. Sending an authentication request using `APIRequestContext`.
-2. Saving the storage state to a file (e.g., `state.json`) using `await requestContext.storageState({ path: 'state.json' })`.
-3. Creating a new browser context with that saved state: `const context = await browser.newContext({ storageState: 'state.json' })`.</t>
+          <t>Yes, you can authenticate through API calls and hand that session to a browser context. Storage state is interchangeable between `APIRequestContext` and `BrowserContext`.
+To do this, follow these steps:
+1.  **Perform the API authentication:** Use `request.newContext()` to create an API request context and perform your login request.
+2.  **Save the state:** Use the `apiRequestContext.storageState()` method to save the authenticated state (cookies/tokens) to a file.
+    ```javascript
+    const requestContext = await request.newContext({httpCredentials: {username: 'user', password: 'passwd'}});
+    await requestContext.get(`https://api.example.com/login`);
+    // Save storage state into the file.
+    await requestContext.storageState({path: 'state.json'});
+    ```
+3.  **Use the state in a browser context:** Create a new browser context by passing the path to the saved state file in the `storageState` option.
+    ```javascript
+    const context = await browser.newContext({storageState: 'state.json'});
+    ```
+For automated testing, you can implement this in a `setup` project or a worker fixture to reuse the authentication state across tests.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2223,80 +2601,108 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0.009216499999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0.77</v>
+        <v>34301</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.21</v>
+        <v>0.44</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4883720930232558</v>
+        <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8099999999838</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="L34" t="n">
+        <v>0.4651162790697674</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.9666666666473333</v>
+      </c>
+      <c r="N34" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>What's the difference between fully mocking an endpoint and just tweaking its real response, and how do I do the latter?</t>
+          <t>Almost all of our tests stub the search endpoint so they're hermetic, and that's been great until the backend quietly renamed a field and every test stayed green while production broke. I want to keep most tests stubbed but have a couple that exercise the real endpoint and only override one flag in whatever comes back. Can the same interception mechanism do both, and what changes between them?</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>['Mock APIs | Playwright', "Sometimes, it is essential to make an API request, but the response needs to be patched to allow for reproducible testing. In that case, instead of mocking the request, one can perform the request and fulfill it with the modified response.\n\nIn the example below we intercept the call to the fruit API and add a new fruit called 'Loquat', to the data. We then go to the url and assert that this data is there:\n\n```\n`test('gets the json from api and adds a new fruit',async({page})=&gt;{// Get the response and add to itawaitpage.route('*/**/api/v1/fruits',asyncroute=&gt;{constresponse=awaitroute.fetch();constjson=awaitresponse.json();json.push({name:'Loquat',id:100});// Fulfill using the original response, while patching the response body// with the given JSON object.awaitroute.fulfill({response,json});});// Go to the pageawaitpage.goto('https://demo.playwright.dev/api-mocking');// Assert that the new fruit is visibleawaitexpect(page.getByText('Loquat',{exact:true})).toBeVisible();});`\n```\n\nIn the trace of our test we can see that the API was called and the response was modified.\n\nBy inspecting the response we can see that our new fruit was added to the list.\n\nRead more about\nadvanced networking (https://playwright.dev/docs/network)\n.", "To modify a response use\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nto get the original response and then pass the response to\nroute.fulfill() (https://playwright.dev/docs/api/class-route#route-fulfill)\n. You can override individual fields on the response via options:\n\n```\n`awaitpage.route('**/title.html',asyncroute=&gt;{// Fetch original response.constresponse=awaitroute.fetch();// Add a prefix to the title.letbody=awaitresponse.text();body=body.replace('&lt;title&gt;','&lt;title&gt;My prefix:');awaitroute.fulfill({// Pass all fields from the response.response,// Override response body.body,// Force content type to be html.headers:{...response.headers(),'content-type':'text/html'}});});`\n```", 'Route | Playwright\n\nWhenever a network route is set up with\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nor\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n, the\n`Route`\nobject allows to handle the route.\n\nLearn more about\nnetworking (https://playwright.dev/docs/network)\n.', 'The following code will intercept all the calls to\n`*/**/api/v1/fruits`\nand will return a custom response instead. No requests to the API will be made. The test goes to the URL that uses the mocked route and asserts that mock data is present on the page.\n\n```\n`test("mocks a fruit and doesn\'t call api",async({page})=&gt;{// Mock the api call before navigatingawaitpage.route(\'*/**/api/v1/fruits\',asyncroute=&gt;{constjson=[{name:\'Strawberry\',id:21}];awaitroute.fulfill({json});});// Go to the pageawaitpage.goto(\'https://demo.playwright.dev/api-mocking\');// Assert that the Strawberry fruit is visibleawaitexpect(page.getByText(\'Strawberry\')).toBeVisible();});`\n```\n\nYou can see from the trace of the example test that the API was never called, it was however fulfilled with the mock data.\n\nRead more about\nadvanced networking (https://playwright.dev/docs/network)\n.', "Added before v1.9\n\nroute.fulfill\n\nFulfills route's request with given response.\n\nUsage\n\nAn example of fulfilling all requests with 404 responses:\n\n```\n`awaitpage.route('**/*',asyncroute=&gt;{awaitroute.fulfill({status:404,contentType:'text/plain',body:'Not Found!'});});`\n```\n\nAn example of serving static file:\n\n```\n`awaitpage.route('**/xhr_endpoint',route=&gt;route.fulfill({path:'mock_data.json'}));`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`body`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fulfill-option-body)\nResponse body.\n`contentType`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fulfill-option-content-type)\nIf set, equals to setting\n`Content-Type`\nresponse header.\n`headers`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n,\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fulfill-option-headers)\nResponse headers. Header values will be converted to a string.\n`json`\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n(optional)\nAdded in: v1.29\n# (https://playwright.dev/docs/api/class-route#route-fulfill-option-json)\nJSON response. This method will set the content type to\n`application/json`\nif not set.\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fulfill-option-path)\nFile path to respond with. The content type will be inferred from file extension. If\n`path`\nis a relative path, then it is resolved relative to the current working directory.\n`response`\nAPIResponse (https://playwright.dev/docs/api/class-apiresponse)\n(optional)\nAdded in: v1.15\n# (https://playwright.dev/docs/api/class-route#route-fulfill-option-response)\nAPIResponse (https://playwright.dev/docs/api/class-apiresponse)\nto fulfill route's request with. Individual fields of the response (such as headers) can be overridden using fulfill options.\n`status`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fulfill-option-status)\nResponse status code, defaults to\n`200`\n.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-route#route-fulfill-return)", "Added in: v1.29\n\nroute.fetch\n\nPerforms the request and fetches result without fulfilling it, so that the response could be modified and then fulfilled.\n\nUsage\n\n```\n`awaitpage.route('https://dog.ceo/api/breeds/list/all',asyncroute=&gt;{constresponse=awaitroute.fetch();constjson=awaitresponse.json();json.message['big_red_dog']=[];awaitroute.fulfill({response,json});});`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`headers`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n,\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-headers)\nIf set changes the request HTTP headers. Header values will be converted to a string.\n`maxRedirects`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.31\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-max-redirects)\nMaximum number of request redirects that will be followed automatically. An error will be thrown if the number is exceeded. Defaults to\n`20`\n. Pass\n`0`\nto not follow redirects.\n`maxRetries`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.46\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-max-retries)\nMaximum number of times network errors should be retried. Currently only\n`ECONNRESET`\nerror is retried. Does not retry based on HTTP response codes. An error will be thrown if the limit is exceeded. Defaults to\n`0`\n- no retries.\n`method`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-method)\nIf set changes the request method (e.g. GET or POST).\n`postData`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\n|\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-post-data)\nAllows to set post data of the request. If the data parameter is an object, it will be serialized to json string and\n`content-type`\nheader will be set to\n`application/json`\nif not explicitly set. Otherwise the\n`content-type`\nheader will be set to\n`application/octet-stream`\nif not explicitly set.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.33\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-timeout)\nRequest timeout in milliseconds. Defaults to\n`30000`\n(30 seconds). Pass\n`0`\nto disable timeout.\n`url`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-url)\nIf set changes the request URL. New URL must have same protocol as original one.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nAPIResponse (https://playwright.dev/docs/api/class-apiresponse)\n&gt;\n# (https://playwright.dev/docs/api/class-route#route-fetch-return)\n\nDetails\n\nNote that\nheaders (https://playwright.dev/docs/api/class-route#route-fetch-option-headers)\noption will apply to the fetched request as well as any redirects initiated by it. If you want to only apply\nheaders (https://playwright.dev/docs/api/class-route#route-fetch-option-headers)\nto the original request, but not to redirects, look into\nroute.continue() (https://playwright.dev/docs/api/class-route#route-continue)\ninstead."]</t>
+          <t>['Route | Playwright\n\nWhenever a network route is set up with\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nor\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n, the\n`Route`\nobject allows to handle the route.\n\nLearn more about\nnetworking (https://playwright.dev/docs/network)\n.', 'Mock APIs | Playwright', "Sometimes, it is essential to make an API request, but the response needs to be patched to allow for reproducible testing. In that case, instead of mocking the request, one can perform the request and fulfill it with the modified response.\n\nIn the example below we intercept the call to the fruit API and add a new fruit called 'Loquat', to the data. We then go to the url and assert that this data is there:\n\n```\n`test('gets the json from api and adds a new fruit',async({page})=&gt;{// Get the response and add to itawaitpage.route('*/**/api/v1/fruits',asyncroute=&gt;{constresponse=awaitroute.fetch();constjson=awaitresponse.json();json.push({name:'Loquat',id:100});// Fulfill using the original response, while patching the response body// with the given JSON object.awaitroute.fulfill({response,json});});// Go to the pageawaitpage.goto('https://demo.playwright.dev/api-mocking');// Assert that the new fruit is visibleawaitexpect(page.getByText('Loquat',{exact:true})).toBeVisible();});`\n```\n\nIn the trace of our test we can see that the API was called and the response was modified.\n\nBy inspecting the response we can see that our new fruit was added to the list.\n\nRead more about\nadvanced networking (https://playwright.dev/docs/network)\n.", "To modify a response use\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nto get the original response and then pass the response to\nroute.fulfill() (https://playwright.dev/docs/api/class-route#route-fulfill)\n. You can override individual fields on the response via options:\n\n```\n`awaitpage.route('**/title.html',asyncroute=&gt;{// Fetch original response.constresponse=awaitroute.fetch();// Add a prefix to the title.letbody=awaitresponse.text();body=body.replace('&lt;title&gt;','&lt;title&gt;My prefix:');awaitroute.fulfill({// Pass all fields from the response.response,// Override response body.body,// Force content type to be html.headers:{...response.headers(),'content-type':'text/html'}});});`\n```", "Added in: v1.29\n\nroute.fetch\n\nPerforms the request and fetches result without fulfilling it, so that the response could be modified and then fulfilled.\n\nUsage\n\n```\n`awaitpage.route('https://dog.ceo/api/breeds/list/all',asyncroute=&gt;{constresponse=awaitroute.fetch();constjson=awaitresponse.json();json.message['big_red_dog']=[];awaitroute.fulfill({response,json});});`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`headers`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n,\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-headers)\nIf set changes the request HTTP headers. Header values will be converted to a string.\n`maxRedirects`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.31\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-max-redirects)\nMaximum number of request redirects that will be followed automatically. An error will be thrown if the number is exceeded. Defaults to\n`20`\n. Pass\n`0`\nto not follow redirects.\n`maxRetries`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.46\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-max-retries)\nMaximum number of times network errors should be retried. Currently only\n`ECONNRESET`\nerror is retried. Does not retry based on HTTP response codes. An error will be thrown if the limit is exceeded. Defaults to\n`0`\n- no retries.\n`method`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-method)\nIf set changes the request method (e.g. GET or POST).\n`postData`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\n|\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-post-data)\nAllows to set post data of the request. If the data parameter is an object, it will be serialized to json string and\n`content-type`\nheader will be set to\n`application/json`\nif not explicitly set. Otherwise the\n`content-type`\nheader will be set to\n`application/octet-stream`\nif not explicitly set.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.33\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-timeout)\nRequest timeout in milliseconds. Defaults to\n`30000`\n(30 seconds). Pass\n`0`\nto disable timeout.\n`url`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-url)\nIf set changes the request URL. New URL must have same protocol as original one.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nAPIResponse (https://playwright.dev/docs/api/class-apiresponse)\n&gt;\n# (https://playwright.dev/docs/api/class-route#route-fetch-return)\n\nDetails\n\nNote that\nheaders (https://playwright.dev/docs/api/class-route#route-fetch-option-headers)\noption will apply to the fetched request as well as any redirects initiated by it. If you want to only apply\nheaders (https://playwright.dev/docs/api/class-route#route-fetch-option-headers)\nto the original request, but not to redirects, look into\nroute.continue() (https://playwright.dev/docs/api/class-route#route-continue)\ninstead.", 'Network | Playwright', "```\n`awaitpage.route('**/api/fetch_data',route=&gt;route.fulfill({status:200,body:testData,}));awaitpage.goto('https://example.com');`\n```\n\nYou can mock API endpoints via handling the network requests in your Playwright script."]</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>['Sometimes, it is essential to make an API request, but the response needs to be patched to allow for reproducible testing. In that case, instead of mocking the request, one can perform the request and fulfill it with the modified response.', 'To modify a response use APIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext) to get the original response and then pass the response to route.fulfill() (https://playwright.dev/docs/api/class-route#route-fulfill) . You can override individual fields on the response via options:']</t>
+          <t>['Mock API requests: All the requests made by the page, including XHRs and fetch requests, can be tracked, modified and mocked.', "await page.route('*/**/api/v1/fruits', async route =&gt; { const json = [{ name: 'Strawberry', id: 21 }]; await route.fulfill({ json }); });", "await page.route('*/**/api/v1/fruits', async route =&gt; { const response = await route.fetch(); const json = await response.json(); json.push({ name: 'Loquat', id: 100 }); // Fulfill using the original response, while patching the response body with the given JSON object. await route.fulfill({ response, json }); });"]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>The difference between fully mocking an endpoint and tweaking its real response is as follows:
-*   **Fully mocking an endpoint:** The API is never actually called. Instead, you intercept the request and return a custom response of your choosing.
-*   **Tweaking a real response:** You perform the actual API request, but you patch or modify the response before it is returned to the application to allow for reproducible testing.
-**How to tweak a real response:**
-To modify a response, you use `page.route()` to intercept the request and then perform the following steps:
-1.  Use `route.fetch()` to perform the original request and get the response.
-2.  Modify the response data (e.g., parse the JSON or text and update the content).
-3.  Use `route.fulfill()` to return the modified response. You pass the original `response` object to `fulfill` and use the options to override specific fields, such as the `json` body or `headers`.</t>
+          <t>Yes, the same interception mechanism (`page.route()`) can be used for both fully stubbed tests and tests that exercise the real endpoint with modifications.
+### How they differ:
+*   **For fully stubbed tests:** You use `route.fulfill()` to provide a static response body without performing a network request.
+    *   **Example:**
+        ```javascript
+        await page.route('**/api/fetch_data', route =&gt; route.fulfill({
+          status: 200,
+          body: testData,
+        }));
+        ```
+*   **For tests exercising the real endpoint with modifications:** You use `route.fetch()` to perform the actual network request, modify the resulting data, and then use `route.fulfill()` to return the patched response.
+    *   **Example:**
+        ```javascript
+        await page.route('*/**/api/v1/fruits', async route =&gt; {
+          // 1. Perform the real request
+          const response = await route.fetch();
+          const json = await response.json();
+          // 2. Modify the specific field
+          json.someFlag = true; 
+          // 3. Fulfill with the original response and the modified JSON
+          await route.fulfill({ response, json });
+        });
+        ```
+In the second approach, `route.fetch()` allows you to get the original response from the backend, which ensures your test fails if the backend renames a field or changes the structure, while still allowing you to override specific flags as needed.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mocking means you fulfill the route yourself so the server is never hit. Patching means you let the request go out, grab the real response with route.fetch(), edit it, then fulfill with the modified version — overriding only the fields you care about.</t>
+          <t>Both go through the same route handler; what differs is whether you ever let the request reach the network. A hermetic stub never does: page.route(url, route =&gt; route.fulfill({ json: ... })) answers from the test and the server is never contacted, which is why a server-side shape change can't fail it. To modify a real response you have to fetch it first — inside the handler call `const response = await route.fetch()`, read the real body with `await response.json()`, mutate the field you care about, and then fulfill with the edited payload: `await route.fulfill({ response, json })`. That gives you the real contract for everything you didn't touch, so the renamed field would have surfaced. Routes are matched most-recently-registered first and are scoped to the page or context they were registered on, so a spec-level `page.route` override can sit on top of a project-wide stub. If you want the real traffic recorded once and replayed thereafter, that's what HAR replay is for.</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0.01008125</v>
       </c>
       <c r="G35" t="n">
-        <v>0.77</v>
+        <v>37140</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1118421052631579</v>
+        <v>0.67</v>
       </c>
       <c r="J35" t="n">
-        <v>0.3953488372093023</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5317460317283068</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0.2456140350877193</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.7099999999858</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
@@ -2307,7 +2713,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>['Emulation | Playwright', 'Playwright comes with a\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nusing\nplaywright.devices (https://playwright.dev/docs/api/class-playwright#playwright-devices)\nfor selected desktop, tablet and mobile devices. It can be used to simulate browser behavior for a specific device such as user agent, screen size, viewport and if it has touch enabled. All tests will run with the specified device parameters.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig,devices}from\'@playwright/test\';// import devicesexportdefaultdefineConfig({projects:[{name:\'chromium\',use:{...devices[\'Desktop Chrome\'],},},{name:\'Mobile Safari\',use:{...devices[\'iPhone 13\'],},},],});`\n```\n```\n`const{chromium,devices}=require(\'playwright\');constbrowser=awaitchromium.launch();constiphone13=devices[\'iPhone 13\'];constcontext=awaitbrowser.newContext({...iphone13,});`\n```\n\nNote\n: Pre-configured devices assume a specific platform. For example, "Desktop Chrome" will provide a Windows-specific user agent string.\n\nIf you would like to use the user agent specific to the platform that is running the tests, we recommend unsetting the user agent property.\n\n```\n`constcontext=awaitbrowser.newContext({...devices[\'Desktop Chrome\'],userAgent:undefined,});`\n```', 'Playwright uses browser contexts to achieve Test Isolation. Each test has its own Browser Context. Running the test creates a new browser context each time.  When using Playwright as a Test Runner, browser contexts are created by default. Otherwise, you can create browser contexts manually.\n\nTest\nLibrary\n```\n`import{test}from\'@playwright/test\';test(\'example test\',async({page,context})=&gt;{// "context" is an isolated BrowserContext, created for this specific test.// "page" belongs to this context.});test(\'another test\',async({page,context})=&gt;{// "context" and "page" in this second test are completely// isolated from the first test.});`\n```\n```\n`constbrowser=awaitchromium.launch();constcontext=awaitbrowser.newContext();constpage=awaitcontext.newPage();`\n```\n\nBrowser contexts can also be used to emulate multi-page scenarios involving mobile devices, permissions, locale and color scheme. Check out our\nEmulation (https://playwright.dev/docs/emulation)\nguide for more details.', 'Isolation | Playwright', 'Configuration (use) | Playwright', 'Test Isolation is when each test is completely isolated from another test. Every test runs independently from any other test. This means that each test has its own local storage, session storage, cookies etc. Playwright achieves this using\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\ns which are equivalent to incognito-like profiles. They are fast and cheap to create and are completely isolated, even when running in a single browser. Playwright creates a context for each test, and provides a default\nPage (https://playwright.dev/docs/api/class-page)\nin that context.', "If using the built-in\n`browser`\nfixture, calling\nbrowser.newContext() (https://playwright.dev/docs/api/class-browser#browser-new-context)\nwill create a context with options inherited from the config:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{userAgent:'some custom ua',viewport:{width:100,height:100},},});`\n```\n\nAn example test illustrating the initial context options are set:\n\n```\n`test('should inherit use options on context when using built-in browser fixture',async({browser,})=&gt;{constcontext=awaitbrowser.newContext();constpage=awaitcontext.newPage();expect(awaitpage.evaluate(()=&gt;navigator.userAgent)).toBe('some custom ua');expect(awaitpage.evaluate(()=&gt;window.innerWidth)).toBe(100);awaitcontext.close();});`\n```"]</t>
+          <t>['Playwright uses browser contexts to achieve Test Isolation. Each test has its own Browser Context. Running the test creates a new browser context each time.  When using Playwright as a Test Runner, browser contexts are created by default. Otherwise, you can create browser contexts manually.\n\nTest\nLibrary\n```\n`import{test}from\'@playwright/test\';test(\'example test\',async({page,context})=&gt;{// "context" is an isolated BrowserContext, created for this specific test.// "page" belongs to this context.});test(\'another test\',async({page,context})=&gt;{// "context" and "page" in this second test are completely// isolated from the first test.});`\n```\n```\n`constbrowser=awaitchromium.launch();constcontext=awaitbrowser.newContext();constpage=awaitcontext.newPage();`\n```\n\nBrowser contexts can also be used to emulate multi-page scenarios involving mobile devices, permissions, locale and color scheme. Check out our\nEmulation (https://playwright.dev/docs/emulation)\nguide for more details.', 'Emulation | Playwright', 'Isolation | Playwright', 'Playwright comes with a\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nusing\nplaywright.devices (https://playwright.dev/docs/api/class-playwright#playwright-devices)\nfor selected desktop, tablet and mobile devices. It can be used to simulate browser behavior for a specific device such as user agent, screen size, viewport and if it has touch enabled. All tests will run with the specified device parameters.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig,devices}from\'@playwright/test\';// import devicesexportdefaultdefineConfig({projects:[{name:\'chromium\',use:{...devices[\'Desktop Chrome\'],},},{name:\'Mobile Safari\',use:{...devices[\'iPhone 13\'],},},],});`\n```\n```\n`const{chromium,devices}=require(\'playwright\');constbrowser=awaitchromium.launch();constiphone13=devices[\'iPhone 13\'];constcontext=awaitbrowser.newContext({...iphone13,});`\n```\n\nNote\n: Pre-configured devices assume a specific platform. For example, "Desktop Chrome" will provide a Windows-specific user agent string.\n\nIf you would like to use the user agent specific to the platform that is running the tests, we recommend unsetting the user agent property.\n\n```\n`constcontext=awaitbrowser.newContext({...devices[\'Desktop Chrome\'],userAgent:undefined,});`\n```', 'Test Isolation is when each test is completely isolated from another test. Every test runs independently from any other test. This means that each test has its own local storage, session storage, cookies etc. Playwright achieves this using\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\ns which are equivalent to incognito-like profiles. They are fast and cheap to create and are completely isolated, even when running in a single browser. Playwright creates a context for each test, and provides a default\nPage (https://playwright.dev/docs/api/class-page)\nin that context.', "You can configure Playwright globally, per project, or per test. For example, you can set the locale to be used globally by adding\n`locale`\nto the\n`use`\noption of the Playwright config, and then override it for a specific project using the\n`project`\noption in the config. You can also override it for a specific test by adding\n`test.use({})`\nin the test file and passing in the options.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{locale:'en-GB'},});`\n```\n\nYou can override options for a specific project using the\n`project`\noption in the Playwright config.\n\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[{name:'chromium',use:{...devices['Desktop Chrome'],locale:'de-DE',},},],});`\n```\n\nYou can override options for a specific test file by using the\n`test.use()`\nmethod and passing in the options. For example to run tests with the French locale for a specific test:\n\n```\n`import{test,expect}from'@playwright/test';test.use({locale:'fr-FR'});test('example',async({page})=&gt;{// ...});`\n```\n\nThe same works inside a describe block. For example to run tests in a describe block with the French locale:\n\n```\n`import{test,expect}from'@playwright/test';test.describe('french language block',()=&gt;{test.use({locale:'fr-FR'});test('example',async({page})=&gt;{// ...});});`\n```", "If using the built-in\n`browser`\nfixture, calling\nbrowser.newContext() (https://playwright.dev/docs/api/class-browser#browser-new-context)\nwill create a context with options inherited from the config:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{userAgent:'some custom ua',viewport:{width:100,height:100},},});`\n```\n\nAn example test illustrating the initial context options are set:\n\n```\n`test('should inherit use options on context when using built-in browser fixture',async({browser,})=&gt;{constcontext=awaitbrowser.newContext();constpage=awaitcontext.newPage();expect(awaitpage.evaluate(()=&gt;navigator.userAgent)).toBe('some custom ua');expect(awaitpage.evaluate(()=&gt;window.innerWidth)).toBe(100);awaitcontext.close();});`\n```"]</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2317,13 +2723,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Based on the provided context, device emulation is applied and isolated as follows:
-**How it is applied:**
-*   **Configuration:** You can define device parameters (such as user agent, screen size, viewport, and touch) in the `playwright.config.ts` file using the `use` property within projects.
-*   **Context Creation:** When using the built-in browser fixture, `browser.newContext()` creates a context that inherits these options from the configuration. Alternatively, you can manually apply device parameters by passing them into `browser.newContext({...deviceParameters})`.
-**Why it doesn't bleed into other tests:**
-*   **Browser Context Isolation:** Playwright achieves test isolation by creating a new, independent `BrowserContext` for every test. 
-*   **Independent Environments:** Because each test runs in its own isolated `BrowserContext` (which acts like an incognito-like profile), the emulation settings applied to one context do not affect others. Each test has its own independent environment, ensuring that settings like viewport or user agent remain contained within that specific test's context.</t>
+          <t>Device emulation (viewport, user agent, and touch) is applied by passing device parameters—such as those found in the `playwright.devices` registry—into the `use` configuration option. This can be done at three levels:
+*   **Globally or per project:** By defining the `use` property within the `projects` array in `playwright.config.ts`.
+*   **Per test file or describe block:** By using the `test.use({})` method.
+*   **Manually:** When using the library directly, you can pass device parameters into `browser.newContext({...deviceParameters})`.
+**Why it does not bleed into other tests:**
+Playwright achieves test isolation by creating a new `BrowserContext` for every test. Because each test runs in its own isolated `BrowserContext` (which acts like an incognito-like profile), any emulation settings applied to one context do not affect others. When using the Playwright test runner, these contexts are created automatically for each test, ensuring that every test runs independently with its own specific configuration.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2332,24 +2737,30 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0.009759</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5</v>
+        <v>35366</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1225806451612903</v>
+        <v>0.57</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4418604651162791</v>
+        <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6458333333171874</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="L36" t="n">
+        <v>0.4651162790697674</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.8041666666465626</v>
+      </c>
+      <c r="N36" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2361,7 +2772,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>['Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', "By default,\nfixture (https://playwright.dev/docs/test-fixtures)\nshares timeout with the test. However, for slow fixtures, especially\nworker-scoped (https://playwright.dev/docs/test-fixtures#worker-scoped-fixtures)\nones, it is convenient to have a separate timeout. This way you can keep the overall test timeout small, and give the slow fixture more time.\n\nexample.spec.ts\n```\n`import{testasbase,expect}from'@playwright/test';consttest=base.extend&lt;{slowFixture:string}&gt;({slowFixture:[async({},use)=&gt;{// ... perform a slow operation ...awaituse('hello');},{timeout:60_000}]});test('example test',async({slowFixture})=&gt;{// ...});`\n```\n\nAPI reference:\ntest.extend() (https://playwright.dev/docs/api/class-test#test-extend)\n.", "Fixture is considered to be a part of a test, and so its setup and teardown running time counts towards the test timeout. Therefore, a slow fixture may cause test timeouts. You can set a separate larger timeout for such a fixture, and keep the overall test timeout small.\n\n```\n`import{testasbase,expect}from'@playwright/test';consttest=base.extend&lt;{slowFixture:string}&gt;({slowFixture:[async({},use)=&gt;{// ... perform a slow operation ...awaituse('hello');},{timeout:60000}]});test('example test',async({slowFixture})=&gt;{// ...});`\n```\n\nUnlike regular test-scoped fixtures, each\nworker-scoped (https://playwright.dev/docs/test-fixtures#worker-scoped-fixtures)\nfixture has its own timeout, equal to the test timeout. You can change the timeout for a worker-scoped fixture in the same way.", "`beforeAll`\nand\n`afterAll`\nhooks have a separate timeout, by default equal to test timeout. You can change it separately for each hook by calling\ntestInfo.setTimeout() (https://playwright.dev/docs/api/class-testinfo#test-info-set-timeout)\ninside the hook.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test.beforeAll(async()=&gt;{// Set timeout for this hook.test.setTimeout(60000);});`\n```\n\nAPI reference:\ntestInfo.setTimeout() (https://playwright.dev/docs/api/class-testinfo#test-info-set-timeout)\n.", "example.spec.ts\n```\n`import{test,expect}from'@playwright/test';test.beforeEach(async({page},testInfo)=&gt;{// Extend timeout for all tests running this hook by 30 seconds.testInfo.setTimeout(testInfo.timeout+30_000);});`\n```\n\nAPI reference:\ntestInfo.setTimeout() (https://playwright.dev/docs/api/class-testinfo#test-info-set-timeout)\n.", 'Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and\n`beforeEach`\nhooks is included in the test timeout.\n\nTimed out test produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Timeout of 30000ms exceeded.`\n```\n\nAdditional separate timeout, of the same value, is shared between fixture teardowns and\n`afterEach`\nhooks, after the test function has finished.\n\nThe same timeout value also applies to\n`beforeAll`\nand\n`afterAll`\nhooks, but they do not share time with any test.']</t>
+          <t>["Fixture is considered to be a part of a test, and so its setup and teardown running time counts towards the test timeout. Therefore, a slow fixture may cause test timeouts. You can set a separate larger timeout for such a fixture, and keep the overall test timeout small.\n\n```\n`import{testasbase,expect}from'@playwright/test';consttest=base.extend&lt;{slowFixture:string}&gt;({slowFixture:[async({},use)=&gt;{// ... perform a slow operation ...awaituse('hello');},{timeout:60000}]});test('example test',async({slowFixture})=&gt;{// ...});`\n```\n\nUnlike regular test-scoped fixtures, each\nworker-scoped (https://playwright.dev/docs/test-fixtures#worker-scoped-fixtures)\nfixture has its own timeout, equal to the test timeout. You can change the timeout for a worker-scoped fixture in the same way.", 'Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', 'Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and\n`beforeEach`\nhooks is included in the test timeout.\n\nTimed out test produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Timeout of 30000ms exceeded.`\n```\n\nAdditional separate timeout, of the same value, is shared between fixture teardowns and\n`afterEach`\nhooks, after the test function has finished.\n\nThe same timeout value also applies to\n`beforeAll`\nand\n`afterAll`\nhooks, but they do not share time with any test.', "example.spec.ts\n```\n`import{test,expect}from'@playwright/test';test.beforeEach(async({page},testInfo)=&gt;{// Extend timeout for all tests running this hook by 30 seconds.testInfo.setTimeout(testInfo.timeout+30_000);});`\n```\n\nAPI reference:\ntestInfo.setTimeout() (https://playwright.dev/docs/api/class-testinfo#test-info-set-timeout)\n.", "TestInfo | Playwright\n\n`TestInfo`\ncontains information about currently running test. It is available to test functions,\ntest.beforeEach() (https://playwright.dev/docs/api/class-test#test-before-each)\n,\ntest.afterEach() (https://playwright.dev/docs/api/class-test#test-after-each)\n,\ntest.beforeAll() (https://playwright.dev/docs/api/class-test#test-before-all)\nand\ntest.afterAll() (https://playwright.dev/docs/api/class-test#test-after-all)\nhooks, and test-scoped fixtures.\n`TestInfo`\nprovides utilities to control test execution: attach files, update test timeout, determine which test is currently running and whether it was retried, etc.\n\n```\n`import{test,expect}from'@playwright/test';test('basic test',async({page},testInfo)=&gt;{expect(testInfo.title).toBe('basic test');awaitpage.screenshot(testInfo.outputPath('screenshot.png'));});`\n```", "`beforeAll`\nand\n`afterAll`\nhooks have a separate timeout, by default equal to test timeout. You can change it separately for each hook by calling\ntestInfo.setTimeout() (https://playwright.dev/docs/api/class-testinfo#test-info-set-timeout)\ninside the hook.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test.beforeAll(async()=&gt;{// Set timeout for this hook.test.setTimeout(60000);});`\n```\n\nAPI reference:\ntestInfo.setTimeout() (https://playwright.dev/docs/api/class-testinfo#test-info-set-timeout)\n."]</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2371,16 +2782,21 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>By default, a fixture is considered part of a test, meaning its setup and teardown time counts toward the overall test timeout. Consequently, a slow fixture can cause a test to time out.
-The fix is to set a separate, larger timeout specifically for the slow fixture. This allows you to keep the overall test timeout small while providing the fixture with the additional time it requires. You can do this when extending the test:
-```typescript
+          <t>Fixture setup and teardown running time counts towards the overall test timeout. Because a fixture is considered part of the test, a slow fixture can cause the entire test to time out.
+To fix this without inflating the timeout for every test, you can set a separate, larger timeout specifically for the slow fixture while keeping the overall test timeout small. You do this by passing a `timeout` property in the fixture definition:
+```javascript
+import { test as base, expect } from '@playwright/test';
 const test = base.extend&lt;{ slowFixture: string }&gt;({
   slowFixture: [async ({}, use) =&gt; {
     // ... perform a slow operation ...
     await use('hello');
-  }, { timeout: 60_000 }]
+  }, { timeout: 60000 }]
 });
-```</t>
+test('example test', async ({ slowFixture }) =&gt; {
+  // ...
+});
+```
+This approach also applies to worker-scoped fixtures.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2389,186 +2805,219 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0.008801749999999001</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8</v>
+        <v>33572</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1684210526315789</v>
+        <v>0.67</v>
       </c>
       <c r="J37" t="n">
-        <v>0.4444444444444444</v>
+        <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5555555555370369</v>
+        <v>0.1238938053097345</v>
       </c>
       <c r="L37" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.8333333332916666</v>
+      </c>
+      <c r="N37" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>How long do web-first assertions retry, and where do I change that — globally versus for one assertion?</t>
+          <t>Our CI machines are a lot slower than our laptops and I've been sprinkling per-assertion timeouts around to get the suite green, which is clearly the wrong shape. Some tests now fail with a message about the test itself rather than the assertion, and raising the assertion timeout further doesn't help those at all. How many separate budgets am I actually dealing with, and which one do I raise?</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['PlaywrightAssertions | Playwright\n\nPlaywright gives you Web-First Assertions with convenience methods for creating assertions that will wait and retry until the expected condition is met.\n\nConsider the following example:\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'status becomes submitted\',async({page})=&gt;{// ...awaitpage.locator(\'#submit-button\').click();awaitexpect(page.locator(\'.status\')).toHaveText(\'Submitted\');});`\n```\n\nPlaywright will be re-testing the node with the selector\n`.status`\nuntil fetched Node has the\n`"Submitted"`\ntext. It will be re-fetching the node and checking it over and over, until the condition is met or until the timeout is reached. You can pass this timeout as an option.\n\nBy default, the timeout for assertions is set to 5 seconds.', 'Assertions | Playwright', 'Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', 'Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Error: expect(received).toHaveText(expected)Expected string: "my text"Received string: ""Call log:- expect.toHaveText with timeout 5000ms- waiting for "locator(\'button\')"`\n```', "playwright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({expect:{timeout:10_000,},});`\n```\n\nAPI reference:\ntestConfig.expect (https://playwright.dev/docs/api/class-testconfig#test-config-expect)\n.", "example.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('example',async({page})=&gt;{awaitexpect(locator).toHaveText('hello',{timeout:10_000});});`\n```", 'Playwright includes test assertions in the form of\n`expect`\nfunction. To make an assertion, call\n`expect(value)`\nand choose a matcher that reflects the expectation. There are many\ngeneric matchers (https://playwright.dev/docs/api/class-genericassertions)\nlike\n`toEqual`\n,\n`toContain`\n,\n`toBeTruthy`\nthat can be used to assert any conditions.\n\n```\n`expect(success).toBeTruthy();`\n```\n\nPlaywright also includes web-specific\nasync matchers (https://playwright.dev/docs/api/class-locatorassertions)\nthat will wait until the expected condition is met. Consider the following example:\n\n```\n`awaitexpect(page.getByTestId(\'status\')).toHaveText(\'Submitted\');`\n```\n\nPlaywright will be re-testing the element with the test id of\n`status`\nuntil the fetched element has the\n`"Submitted"`\ntext. It will re-fetch the element and check it over and over, until the condition is met or until the timeout is reached. You can either pass this timeout or configure it once via the\ntestConfig.expect (https://playwright.dev/docs/api/class-testconfig#test-config-expect)\nvalue in the test config.\n\nBy default, the timeout for assertions is set to 5 seconds. Learn more about\nvarious timeouts (https://playwright.dev/docs/test-timeouts)\n.']</t>
+          <t>['Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', "These are the low-level timeouts that are pre-configured by the test runner, you should not need to change these. If you happen to be in this section because your test are flaky, it is very likely that you should be looking for the solution elsewhere.\n\nTimeout\nDefault\nDescription\nAction timeout\nno timeout\nTimeout for each action\nSet in config\n`{ use: { actionTimeout: 10_000 } }`\nOverride in test\n`locator.click({ timeout: 10_000 })`\nNavigation timeout\nno timeout\nTimeout for each navigation action\nSet in config\n`{ use: { navigationTimeout: 30_000 } }`\nOverride in test\n`page.goto('/', { timeout: 30_000 })`\nGlobal timeout\nno timeout\nGlobal timeout for the whole test run\nSet in config\n`{ globalTimeout: 3_600_000 }`\n`beforeAll`\n/\n`afterAll`\ntimeout\n30_000 ms\nTimeout for the hook\nSet in hook\n`test.setTimeout(60_000)`\nFixture timeout\nno timeout\nTimeout for an individual fixture\nSet in fixture\n`{ scope: 'test', timeout: 30_000 }`", 'Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Error: expect(received).toHaveText(expected)Expected string: "my text"Received string: ""Call log:- expect.toHaveText with timeout 5000ms- waiting for "locator(\'button\')"`\n```', 'Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and\n`beforeEach`\nhooks is included in the test timeout.\n\nTimed out test produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Timeout of 30000ms exceeded.`\n```\n\nAdditional separate timeout, of the same value, is shared between fixture teardowns and\n`afterEach`\nhooks, after the test function has finished.\n\nThe same timeout value also applies to\n`beforeAll`\nand\n`afterAll`\nhooks, but they do not share time with any test.', 'Auto-waiting | Playwright', "By default,\nfixture (https://playwright.dev/docs/test-fixtures)\nshares timeout with the test. However, for slow fixtures, especially\nworker-scoped (https://playwright.dev/docs/test-fixtures#worker-scoped-fixtures)\nones, it is convenient to have a separate timeout. This way you can keep the overall test timeout small, and give the slow fixture more time.\n\nexample.spec.ts\n```\n`import{testasbase,expect}from'@playwright/test';consttest=base.extend&lt;{slowFixture:string}&gt;({slowFixture:[async({},use)=&gt;{// ... perform a slow operation ...awaituse('hello');},{timeout:60_000}]});test('example test',async({slowFixture})=&gt;{// ...});`\n```\n\nAPI reference:\ntest.extend() (https://playwright.dev/docs/api/class-test#test-extend)\n.", "Playwright Test supports a timeout for the whole test run. This prevents excess resource usage when everything went wrong. There is no default global timeout, but you can set a reasonable one in the config, for example one hour. Global timeout produces the following error:\n\n```\n`Running 1000 tests using 10 workers514 skipped486 passedTimed out waiting 3600s for the entire test run`\n```\n\nYou can set global timeout in the config.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalTimeout:3_600_000,});`\n```\n\nAPI reference:\ntestConfig.globalTimeout (https://playwright.dev/docs/api/class-testconfig#test-config-global-timeout)\n."]</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['By default, the timeout for assertions is set to 5 seconds. Learn more about various timeouts (https://playwright.dev/docs/test-timeouts) .', 'Auto-retrying assertions like expect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text) have a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:']</t>
+          <t>['Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and beforeEach hooks is included in the test timeout.', 'Auto-retrying assertions like expect(locator).toHaveText() have a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout.', 'export default defineConfig({ expect: { timeout: 10_000, }, });', "test('very slow test', async ({ page }) =&gt; { test.setTimeout(120_000); }); test.slow(); // Easy way to triple the default timeout", 'beforeAll and afterAll hooks have a separate timeout, by default equal to test timeout. You can change it separately for each hook by calling testInfo.setTimeout() inside the hook.']</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Web-first assertions retry until the condition is met or the timeout is reached. By default, this timeout is set to 5 seconds.
-You can change the timeout as follows:
-*   **Globally:** Set the `expect.timeout` value in your `playwright.config.ts` file:
+          <t>You are dealing with multiple separate timeout budgets. Based on the documentation, the specific budgets are:
+1.  **Test timeout:** 30,000 ms default. This covers the test function, fixture setups, and `beforeEach` hooks.
+2.  **Expect timeout:** 5,000 ms default. This is for auto-retrying assertions and is unrelated to the test timeout.
+3.  **Action timeout:** No default. Covers individual actions like `click`.
+4.  **Navigation timeout:** No default. Covers navigation actions like `page.goto`.
+5.  **Hook/Teardown timeout:** 30,000 ms default. Shared between fixture teardowns and `afterEach` hooks; also applies to `beforeAll` and `afterAll` hooks.
+6.  **Fixture timeout:** No default (shares with test by default).
+7.  **Global timeout:** No default. Covers the entire test run.
+Since you are seeing errors about the test itself rather than the assertion (e.g., `Timeout of 30000ms exceeded`), you should raise the **Test timeout**. 
+You can increase this in your config file:
+```javascript
+{ timeout: 60_000 }
+```
+Or override it for a specific test:
+```javascript
+test.setTimeout(120_000)
+```
+The assertion timeout is unrelated to the test timeout, which explains why raising it does not resolve errors caused by the test exceeding its own budget.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Three budgets, nested, which is why raising the wrong one does nothing. The test timeout is 30 seconds by default and covers the whole test — the test function plus fixture setup plus beforeEach hooks — and it's what you're hitting when the failure names the test rather than an assertion; raise it in the config's `timeout`, or per test with test.setTimeout(120_000), or test.slow() to triple the default. Auto-retrying assertions like expect(locator).toHaveText() have their own separate 5-second expect timeout, which is unrelated to the test timeout and is the one reported in a 'expect.toHaveText with timeout 5000ms' call log; set it globally with `expect: { timeout: 10_000 }` or per assertion with a { timeout } option. Because the assertion budget is consumed inside the test budget, pushing the expect timeout above the test timeout accomplishes nothing — the test dies first. beforeAll/afterAll get their own timeout, equal to the test timeout by default and adjustable inside the hook. The right fix for a uniformly slower machine is the config-level defaults, not per-assertion overrides.</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0.010112</v>
+      </c>
+      <c r="G38" t="n">
+        <v>36678</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.2513089005235602</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.2622950819672131</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.6999999999766667</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>What's the reliable way to select a parent row based on a child element, and why avoid xpath=.. for it?</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>['When you need to target a parent element of some other element, most of the time you should\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nby the child locator. For example, consider the following DOM structure:\n\n```\n`&lt;li&gt;&lt;label&gt;Hello&lt;/label&gt;&lt;/li&gt;&lt;li&gt;&lt;label&gt;World&lt;/label&gt;&lt;/li&gt;`\n```\n\nIf you\'d like to target the parent\n`&lt;li&gt;`\nof a label with text\n`"Hello"`\n, using\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nworks best:\n\n```\n`constchild=page.getByText(\'Hello\');constparent=page.getByRole(\'listitem\').filter({has:child});`\n```\n\nAlternatively, if you cannot find a suitable locator for the parent element, use\n`xpath=..`\n. Note that this method is not as reliable, because any changes to the DOM structure will break your tests. Prefer\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nwhen possible.\n\n```\n`constparent=page.getByText(\'Hello\').locator(\'xpath=..\');`\n```', 'Other locators | Playwright', "Locators support an option to only select elements that have or have not a descendant matching another locator. You can therefore filter by any other locator such as a\nlocator.getByRole() (https://playwright.dev/docs/api/class-locator#locator-get-by-role)\n,\nlocator.getByTestId() (https://playwright.dev/docs/api/class-locator#locator-get-by-test-id)\n,\nlocator.getByText() (https://playwright.dev/docs/api/class-locator#locator-get-by-text)\netc.\n\nhttp://localhost:3000\nProduct 1\nAdd to cart\nProduct 2\nAdd to cart\n```\n`&lt;ul&gt;&lt;li&gt;&lt;h3&gt;Product 1&lt;/h3&gt;&lt;button&gt;Add to cart&lt;/button&gt;&lt;/li&gt;&lt;li&gt;&lt;h3&gt;Product 2&lt;/h3&gt;&lt;button&gt;Add to cart&lt;/button&gt;&lt;/li&gt;&lt;/ul&gt;`\n```\n\n```\n`awaitpage.getByRole('listitem').filter({has:page.getByRole('heading',{name:'Product 2'})}).getByRole('button',{name:'Add to cart'}).click();`\n```\n\nWe can also assert the product card to make sure there is only one:\n\n```\n`awaitexpect(page.getByRole('listitem').filter({has:page.getByRole('heading',{name:'Product 2'})})).toHaveCount(1);`\n```\n\nThe filtering locator\nmust be relative\nto the original locator and is queried starting with the original locator match, not the document root. Therefore, the following will not work, because the filtering locator starts matching from the\n`&lt;ul&gt;`\nlist element that is outside of the\n`&lt;li&gt;`\nlist item matched by the original locator:\n\n```\n`// ✖ WRONGawaitexpect(page.getByRole('listitem').filter({has:page.getByRole('list').getByText('Product 2')})).toHaveCount(1);`\n```", "warning\nWe recommend prioritizing\nuser-visible locators (https://playwright.dev/docs/locators#quick-guide)\nlike text or accessible role instead of using XPath that is tied to the implementation and easily break when the page changes.\n\nXPath locators are equivalent to calling\nDocument.evaluate (https://developer.mozilla.org/en/docs/Web/API/Document/evaluate)\n.\n\n```\n`awaitpage.locator('xpath=//button').click();`\n```\n\nnote\nAny selector string starting with\n`//`\nor\n`..`\nare assumed to be an xpath selector. For example, Playwright converts\n`'//html/body'`\nto\n`'xpath=//html/body'`\n.\n\nnote\nXPath does not pierce shadow roots."]</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>['The filtering locator must be relative to the original locator and is queried starting with the original locator match, not the document root.', 'Alternatively, if you cannot find a suitable locator for the parent element, use xpath=.. . Note that this method is not as reliable, because any changes to the DOM structure will break your tests. Prefer locator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter) when possible.']</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>The reliable way to select a parent row based on a child element is to use `locator.filter()`. You should use this method by passing the child locator to the `has` option of the parent locator.
+**Example:**
+```javascript
+const child = page.getByText('Hello');
+const parent = page.getByRole('listitem').filter({has: child});
+```
+You should avoid using `xpath=..` because it is not as reliable; any changes to the DOM structure will cause your tests to break. Additionally, XPath locators are tied to the implementation, whereas `locator.filter()` is preferred.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Filter the parent by the child locator — e.g. getByRole('listitem').filter({ has: child }) — which is evaluated relative to the parent match. xpath=.. works but is brittle: any DOM change can break it, so prefer filtering.</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0.00852725</v>
+      </c>
+      <c r="G39" t="n">
+        <v>32744</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.1954022988505747</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.4722222222222222</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.8333333332916666</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>I'm adopting Page Object Models — how do I wire them so each test gets a ready-to-use page object without boilerplate?</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>['To create your own fixture, use\ntest.extend() (https://playwright.dev/docs/api/class-test#test-extend)\nto create a new\n`test`\nobject that will include it.\n\nBelow we create two fixtures\n`todoPage`\nand\n`settingsPage`\nthat follow the\nPage Object Model (https://playwright.dev/docs/pom)\npattern.\n\nClick to expand the code for the\n`TodoPage`\nand\n`SettingsPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\nSettingsPage is similar:\nsettings-page.ts\n```\n`importtype{Page}from\'@playwright/test\';exportclassSettingsPage{constructor(publicreadonly page:Page){}asyncswitchToDarkMode(){// ...}}`\n```\n\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';import{SettingsPage}from\'./settings-page\';// Declare the types of your fixtures.typeMyFixtures={todoPage:TodoPage;settingsPage:SettingsPage;};// Extend base test by providing "todoPage" and "settingsPage".// This new "test" can be used in multiple test files, and each of them will get the fixtures.exportconsttest=base.extend&lt;MyFixtures&gt;({todoPage:async({page},use)=&gt;{// Set up the fixture.consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(\'item1\');awaittodoPage.addToDo(\'item2\');// Use the fixture value in the test.awaituse(todoPage);// Clean up the fixture.awaittodoPage.removeAll();},settingsPage:async({page},use)=&gt;{awaituse(newSettingsPage(page));},});export{expect}from\'@playwright/test\';`\n```\n\nnote\nCustom fixture names should start with a letter or underscore, and can contain only letters, numbers, and underscores.', 'Fixtures have a number of advantages over before/after hooks:\n\nFixtures\nencapsulate\nsetup and teardown in the same place so it is easier to write. So if you have an after hook that tears down what was created in a before hook, consider turning them into a fixture.\nFixtures are\nreusable\nbetween test files - you can define them once and use them in all your tests. That\'s how Playwright\'s built-in\n`page`\nfixture works. So if you have a helper function that is used in multiple tests, consider turning it into a fixture.\nFixtures are\non-demand\n- you can define as many fixtures as you\'d like, and Playwright Test will setup only the ones needed by your test and nothing else.\nFixtures are\ncomposable\n- they can depend on each other to provide complex behaviors.\nFixtures are\nflexible\n. Tests can use any combination of fixtures to precisely tailor the environment to their needs, without affecting other tests.\nFixtures simplify\ngrouping\n. You no longer need to wrap tests in\n`describe`\ns that set up their environment, and are free to group your tests by their meaning instead.\n\nClick to expand the code for the\n`TodoPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\n\nexample.spec.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';// Extend basic test by providing a "todoPage" fixture.consttest=base.extend&lt;{todoPage:TodoPage}&gt;({todoPage:async({page},use)=&gt;{consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(\'item1\');awaittodoPage.addToDo(\'item2\');awaituse(todoPage);awaittodoPage.removeAll();},});test(\'should add an item\',async({todoPage})=&gt;{awaittodoPage.addToDo(\'my item\');// ...});test(\'should remove an item\',async({todoPage})=&gt;{awaittodoPage.remove(\'item1\');// ...});`\n```', 'Page object models | Playwright', 'Fixtures | Playwright', "We will create a\n`PlaywrightDevPage`\nhelper class to encapsulate common operations on the\n`playwright.dev`\npage. Internally, it will use the\n`page`\nobject.\n\nTest\nLibrary\nplaywright-dev-page.ts\n```\n`import{expect,typeLocator,typePage}from'@playwright/test';exportclassPlaywrightDevPage{readonly page:Page;readonly getStartedLink:Locator;readonly gettingStartedHeader:Locator;readonly pomLink:Locator;readonly tocList:Locator;constructor(page:Page){this.page=page;this.getStartedLink=page.locator('a',{hasText:'Get started'});this.gettingStartedHeader=page.locator('h1',{hasText:'Installation'});this.pomLink=page.locator('li',{hasText:'Guides',}).locator('a',{hasText:'Page Object Model',});this.tocList=page.locator('article div.markdown ul &gt; li &gt; a');}asyncgoto(){awaitthis.page.goto('https://playwright.dev');}asyncgetStarted(){awaitthis.getStartedLink.first().click();awaitexpect(this.gettingStartedHeader).toBeVisible();}asyncpageObjectModel(){awaitthis.getStarted();awaitthis.pomLink.click();}}`\n```\nmodels/PlaywrightDevPage.js\n```\n`classPlaywrightDevPage{/***@param{import('playwright').Page}page*/constructor(page){this.page=page;this.getStartedLink=page.locator('a',{hasText:'Get started'});this.gettingStartedHeader=page.locator('h1',{hasText:'Installation'});this.pomLink=page.locator('li',{hasText:'Playwright Test',}).locator('a',{hasText:'Page Object Model',});this.tocList=page.locator('article div.markdown ul &gt; li &gt; a');}asyncgetStarted(){awaitthis.getStartedLink.first().click();awaitexpect(this.gettingStartedHeader).toBeVisible();}asyncpageObjectModel(){awaitthis.getStarted();awaitthis.pomLink.click();}}module.exports={PlaywrightDevPage};`\n```\n\nNow we can use the\n`PlaywrightDevPage`\nclass in our tests.\n\nTest\nLibrary\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';import{PlaywrightDevPage}from'./playwright-dev-page';test('getting started should contain table of contents',async({page})=&gt;{constplaywrightDev=newPlaywrightDevPage(page);awaitplaywrightDev.goto();awaitplaywrightDev.getStarted();awaitexpect(playwrightDev.tocList).toHaveText([`How to install Playwright`,`What's installed`,`How to run the example test`,`How to open the HTML test report`,`Write tests using web-first assertions, fixtures and locators`,`Run single or multiple tests; headed mode`,`Generate tests with Codegen`,`View a trace of your tests`,]);});test('should show Page Object Model article',async({page})=&gt;{constplaywrightDev=newPlaywrightDevPage(page);awaitplaywrightDev.goto();awaitplaywrightDev.pageObjectModel();awaitexpect(page.locator('article')).toContainText('Page Object Model is a common pattern');});`\n```\nexample.spec.js\n```\n`const{PlaywrightDevPage}=require('./playwright-dev-page');// In the testconstpage=awaitbrowser.newPage();awaitplaywrightDev.goto();awaitplaywrightDev.getStarted();awaitexpect(playwrightDev.tocList).toHaveText([`How to install Playwright`,`What's installed`,`How to run the example test`,`How to open the HTML test report`,`Write tests using web-first assertions, fixtures and locators`,`Run single or multiple tests; headed mode`,`Generate tests with Codegen`,`View a trace of your tests`,]);`\n```"]</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>['Page objects simplify authoring by creating a higher-level API which suits your application and simplify maintenance by capturing element selectors in one place and create reusable code to avoid repetition.', 'To create your own fixture, use test.extend() (https://playwright.dev/docs/api/class-test#test-extend) to create a new test object that will include it.']</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>To wire your Page Object Models so each test receives a ready-to-use instance without boilerplate, you should use **fixtures**.
+### How to implement fixtures for Page Objects:
+1.  **Define the fixture:** Use `test.extend()` to create a new `test` object that includes your page objects. You define the fixture by providing a function that receives the `page` object, instantiates your Page Object class, performs any necessary setup (like navigating to a URL), and then calls `use()` to pass the instance to the test. You can also include teardown logic after the `await use(...)` call.
+    **Example:**
     ```typescript
-    import { defineConfig } from '@playwright/test';
-    export default defineConfig({
-      expect: {
-        timeout: 10_000,
+    import { test as base } from '@playwright/test';
+    import { TodoPage } from './todo-page';
+    type MyFixtures = {
+      todoPage: TodoPage;
+    };
+    export const test = base.extend&lt;MyFixtures&gt;({
+      todoPage: async ({ page }, use) =&gt; {
+        const todoPage = new TodoPage(page);
+        // Setup:
+        await todoPage.goto();
+        await todoPage.addToDo('item1');
+        // Provide the fixture to the test:
+        await use(todoPage);
+        // Teardown:
+        await todoPage.removeAll();
       },
     });
     ```
-*   **For a single assertion:** Pass the `timeout` option directly into the assertion:
+2.  **Use the fixture in your tests:** Import the extended `test` object into your test files. You can then request the page object fixture as an argument in your test function. Playwright will automatically set up the fixture before the test runs and tear it down afterward.
+    **Example:**
     ```typescript
-    await expect(locator).toHaveText('hello', { timeout: 10_000 });
-    ```</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>They retry for 5 seconds by default, on a clock separate from the test timeout. Override it per call with a timeout option, or set the project-wide default through the expect config.</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H38" t="n">
-        <v>5</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.1447368421052632</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.7470238095051339</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>What's the reliable way to select a parent row based on a child element, and why avoid xpath=.. for it?</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>['Locators | Playwright', 'Other locators | Playwright', 'When you need to target a parent element of some other element, most of the time you should\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nby the child locator. For example, consider the following DOM structure:\n\n```\n`&lt;li&gt;&lt;label&gt;Hello&lt;/label&gt;&lt;/li&gt;&lt;li&gt;&lt;label&gt;World&lt;/label&gt;&lt;/li&gt;`\n```\n\nIf you\'d like to target the parent\n`&lt;li&gt;`\nof a label with text\n`"Hello"`\n, using\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nworks best:\n\n```\n`constchild=page.getByText(\'Hello\');constparent=page.getByRole(\'listitem\').filter({has:child});`\n```\n\nAlternatively, if you cannot find a suitable locator for the parent element, use\n`xpath=..`\n. Note that this method is not as reliable, because any changes to the DOM structure will break your tests. Prefer\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nwhen possible.\n\n```\n`constparent=page.getByText(\'Hello\').locator(\'xpath=..\');`\n```']</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>['The filtering locator must be relative to the original locator and is queried starting with the original locator match, not the document root.', 'Alternatively, if you cannot find a suitable locator for the parent element, use xpath=.. . Note that this method is not as reliable, because any changes to the DOM structure will break your tests. Prefer locator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter) when possible.']</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>The reliable way to select a parent row based on a child element is to use `locator.filter()` by the child locator.
-You should avoid `xpath=..` because it is not as reliable; any changes to the DOM structure will break your tests.</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Filter the parent by the child locator — e.g. getByRole('listitem').filter({ has: child }) — which is evaluated relative to the parent match. xpath=.. works but is brittle: any DOM change can break it, so prefer filtering.</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="H39" t="n">
-        <v>4</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.2619047619047619</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.3055555555555556</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.3333333333</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>I'm adopting Page Object Models — how do I wire them so each test gets a ready-to-use page object without boilerplate?</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>['Page object models | Playwright', 'Fixtures | Playwright', 'To create your own fixture, use\ntest.extend() (https://playwright.dev/docs/api/class-test#test-extend)\nto create a new\n`test`\nobject that will include it.\n\nBelow we create two fixtures\n`todoPage`\nand\n`settingsPage`\nthat follow the\nPage Object Model (https://playwright.dev/docs/pom)\npattern.\n\nClick to expand the code for the\n`TodoPage`\nand\n`SettingsPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\nSettingsPage is similar:\nsettings-page.ts\n```\n`importtype{Page}from\'@playwright/test\';exportclassSettingsPage{constructor(publicreadonly page:Page){}asyncswitchToDarkMode(){// ...}}`\n```\n\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';import{SettingsPage}from\'./settings-page\';// Declare the types of your fixtures.typeMyFixtures={todoPage:TodoPage;settingsPage:SettingsPage;};// Extend base test by providing "todoPage" and "settingsPage".// This new "test" can be used in multiple test files, and each of them will get the fixtures.exportconsttest=base.extend&lt;MyFixtures&gt;({todoPage:async({page},use)=&gt;{// Set up the fixture.consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(\'item1\');awaittodoPage.addToDo(\'item2\');// Use the fixture value in the test.awaituse(todoPage);// Clean up the fixture.awaittodoPage.removeAll();},settingsPage:async({page},use)=&gt;{awaituse(newSettingsPage(page));},});export{expect}from\'@playwright/test\';`\n```\n\nnote\nCustom fixture names should start with a letter or underscore, and can contain only letters, numbers, and underscores.', 'Fixtures have a number of advantages over before/after hooks:\n\nFixtures\nencapsulate\nsetup and teardown in the same place so it is easier to write. So if you have an after hook that tears down what was created in a before hook, consider turning them into a fixture.\nFixtures are\nreusable\nbetween test files - you can define them once and use them in all your tests. That\'s how Playwright\'s built-in\n`page`\nfixture works. So if you have a helper function that is used in multiple tests, consider turning it into a fixture.\nFixtures are\non-demand\n- you can define as many fixtures as you\'d like, and Playwright Test will setup only the ones needed by your test and nothing else.\nFixtures are\ncomposable\n- they can depend on each other to provide complex behaviors.\nFixtures are\nflexible\n. Tests can use any combination of fixtures to precisely tailor the environment to their needs, without affecting other tests.\nFixtures simplify\ngrouping\n. You no longer need to wrap tests in\n`describe`\ns that set up their environment, and are free to group your tests by their meaning instead.\n\nClick to expand the code for the\n`TodoPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\n\nexample.spec.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';// Extend basic test by providing a "todoPage" fixture.consttest=base.extend&lt;{todoPage:TodoPage}&gt;({todoPage:async({page},use)=&gt;{consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(\'item1\');awaittodoPage.addToDo(\'item2\');awaituse(todoPage);awaittodoPage.removeAll();},});test(\'should add an item\',async({todoPage})=&gt;{awaittodoPage.addToDo(\'my item\');// ...});test(\'should remove an item\',async({todoPage})=&gt;{awaittodoPage.remove(\'item1\');// ...});`\n```', 'Here is how a typical test environment setup differs between the traditional test style and the fixture-based one.\n\n`TodoPage`\nis a class that helps us interact with a "todo list" page of the web app, following the\nPage Object Model (https://playwright.dev/docs/pom)\npattern. It uses Playwright\'s\n`page`\ninternally.\n\nClick to expand the code for the\n`TodoPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\n\ntodo.spec.ts\n```\n`const{test}=require(\'@playwright/test\');const{TodoPage}=require(\'./todo-page\');test.describe(\'todo tests\',()=&gt;{lettodoPage;test.beforeEach(async({page})=&gt;{todoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(\'item1\');awaittodoPage.addToDo(\'item2\');});test.afterEach(async()=&gt;{awaittodoPage.removeAll();});test(\'should add an item\',async()=&gt;{awaittodoPage.addToDo(\'my item\');// ...});test(\'should remove an item\',async()=&gt;{awaittodoPage.remove(\'item1\');// ...});});`\n```']</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>['Page objects simplify authoring by creating a higher-level API which suits your application and simplify maintenance by capturing element selectors in one place and create reusable code to avoid repetition.', 'To create your own fixture, use test.extend() (https://playwright.dev/docs/api/class-test#test-extend) to create a new test object that will include it.']</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>To wire Page Object Models so each test gets a ready-to-use page object without boilerplate, you should use **fixtures**. You can achieve this by following these steps:
-1.  **Define your Page Object Model**: Create your class (e.g., `TodoPage`) that accepts a `Page` object in its constructor.
-2.  **Extend the test object**: Use `test.extend()` from `@playwright/test` to create a new `test` object that includes your page objects as fixtures.
-3.  **Define the fixture**: Within the `test.extend()` call, define the fixture by instantiating your page object and using the `use` function to provide it to the test. You can also handle setup and teardown logic within this fixture definition.
-4.  **Use the fixture in tests**: Import your custom `test` object into your test files. You can then inject the page object directly into your test function arguments.
-**Example:**
-```typescript
-import { test as base } from '@playwright/test';
-import { TodoPage } from './todo-page';
-// 1. Define the types for your fixtures
-type MyFixtures = {
-  todoPage: TodoPage;
-};
-// 2. Extend the base test
-export const test = base.extend&lt;MyFixtures&gt;({
-  todoPage: async ({ page }, use) =&gt; {
-    // 3. Set up the fixture
-    const todoPage = new TodoPage(page);
-    await todoPage.goto();
-    // 4. Use the fixture in the test
-    await use(todoPage);
-    // 5. Clean up (optional)
-    await todoPage.removeAll();
-  },
-});
-// 6. Use the custom test in your test files
-test('should add an item', async ({ todoPage }) =&gt; {
-  await todoPage.addToDo('my item');
-});
-```</t>
+    import { test } from './my-test';
+    test('should add an item', async ({ todoPage }) =&gt; {
+      await todoPage.addToDo('my item');
+      // ...
+    });
+    ```
+### Why use this approach?
+*   **Encapsulation:** Setup and teardown logic are contained within the fixture.
+*   **On-demand:** Playwright only sets up the fixtures required by the specific test.
+*   **Reusability:** You can define the fixtures once and use them across multiple test files.
+*   **Composability:** Fixtures can depend on other fixtures to provide complex behaviors.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2577,24 +3026,30 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0.009241249999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>0.77</v>
+        <v>33805</v>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.07758620689655173</v>
+        <v>0.53</v>
       </c>
       <c r="J40" t="n">
-        <v>0.4285714285714285</v>
+        <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>0.4166666666458333</v>
+        <v>0.08239700374531835</v>
       </c>
       <c r="L40" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.99999999995</v>
+      </c>
+      <c r="N40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2606,7 +3061,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>['Auto-waiting | Playwright', 'Playwright performs a range of actionability checks on the elements before making actions to ensure these actions behave as expected. It auto-waits for all the relevant checks to pass and only then performs the requested action. If the required checks do not pass within the given\n`timeout`\n, action fails with the\n`TimeoutError`\n.\n\nFor example, for\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\n, Playwright will ensure that:\n\nlocator resolves to exactly one element\nelement is\nVisible (https://playwright.dev/docs/actionability#visible)\nelement is\nStable (https://playwright.dev/docs/actionability#stable)\n, as in not animating or completed animation\nelement\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\n, as in not obscured by other elements\nelement is\nEnabled (https://playwright.dev/docs/actionability#enabled)\n\nHere is the complete list of actionability checks performed for each action:\n\nAction\nVisible (https://playwright.dev/docs/actionability#visible)\nStable (https://playwright.dev/docs/actionability#stable)\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\nEnabled (https://playwright.dev/docs/actionability#enabled)\nEditable (https://playwright.dev/docs/actionability#editable)\nlocator.check() (https://playwright.dev/docs/api/class-locator#locator-check)\nYes\nYes\nYes\nYes\n-\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nYes\nYes\nYes\nYes\n-\nlocator.dblclick() (https://playwright.dev/docs/api/class-locator#locator-dblclick)\nYes\nYes\nYes\nYes\n-\nlocator.setChecked() (https://playwright.dev/docs/api/class-locator#locator-set-checked)\nYes\nYes\nYes\nYes\n-\nlocator.tap() (https://playwright.dev/docs/api/class-locator#locator-tap)\nYes\nYes\nYes\nYes\n-\nlocator.uncheck() (https://playwright.dev/docs/api/class-locator#locator-uncheck)\nYes\nYes\nYes\nYes\n-\nlocator.hover() (https://playwright.dev/docs/api/class-locator#locator-hover)\nYes\nYes\nYes\n-\n-\nlocator.dragTo() (https://playwright.dev/docs/api/class-locator#locator-drag-to)\nYes\nYes\nYes\n-\n-\nlocator.screenshot() (https://playwright.dev/docs/api/class-locator#locator-screenshot)\nYes\nYes\n-\n-\n-\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\nYes\n-\n-\nYes\nYes\nlocator.clear() (https://playwright.dev/docs/api/class-locator#locator-clear)\nYes\n-\n-\nYes\nYes\nlocator.selectOption() (https://playwright.dev/docs/api/class-locator#locator-select-option)\nYes\n-\n-\nYes\n-\nlocator.selectText() (https://playwright.dev/docs/api/class-locator#locator-select-text)\nYes\n-\n-\n-\n-\nlocator.scrollIntoViewIfNeeded() (https://playwright.dev/docs/api/class-locator#locator-scroll-into-view-if-needed)\n-\nYes\n-\n-\n-\nlocator.blur() (https://playwright.dev/docs/api/class-locator#locator-blur)\n-\n-\n-\n-\n-\nlocator.dispatchEvent() (https://playwright.dev/docs/api/class-locator#locator-dispatch-event)\n-\n-\n-\n-\n-\nlocator.focus() (https://playwright.dev/docs/api/class-locator#locator-focus)\n-\n-\n-\n-\n-\nlocator.press() (https://playwright.dev/docs/api/class-locator#locator-press)\n-\n-\n-\n-\n-\nlocator.pressSequentially() (https://playwright.dev/docs/api/class-locator#locator-press-sequentially)\n-\n-\n-\n-\n-\nlocator.setInputFiles() (https://playwright.dev/docs/api/class-locator#locator-set-input-files)\n-\n-\n-\n-\n-', "Performs a simple human click.\n\n```\n`// Generic clickawaitpage.getByRole('button').click();// Double clickawaitpage.getByText('Item').dblclick();// Right clickawaitpage.getByText('Item').click({button:'right'});// Shift + clickawaitpage.getByText('Item').click({modifiers:['Shift']});// Ctrl + click on Windows and Linux// Meta + click on macOSawaitpage.getByText('Item').click({modifiers:['ControlOrMeta']});// Hover over elementawaitpage.getByText('Item').hover();// Click the top left cornerawaitpage.getByText('Item').click({position:{x:0,y:0}});`\n```\n\nUnder the hood, this and other pointer-related methods:\n\nwait for element with given selector to be in DOM\nwait for it to become displayed, i.e. not empty, no\n`display:none`\n, no\n`visibility:hidden`\nwait for it to stop moving, for example, until css transition finishes\nscroll the element into view\nwait for it to receive pointer events at the action point, for example, waits until element becomes non-obscured by other elements\nretry if the element is detached during any of the above checks", 'Actions | Playwright', "Sometimes, apps use non-trivial logic where hovering the element overlays it with another element that intercepts the click. This behavior is indistinguishable from a bug where element gets covered and the click is dispatched elsewhere. If you know this is taking place, you can bypass the\nactionability (https://playwright.dev/docs/actionability)\nchecks and force the click:\n\n```\n`awaitpage.getByRole('button').click({force:true});`\n```", 'Locators | Playwright', 'Writing tests | Playwright']</t>
+          <t>['Auto-waiting | Playwright', 'Playwright performs a range of actionability checks on the elements before making actions to ensure these actions behave as expected. It auto-waits for all the relevant checks to pass and only then performs the requested action. If the required checks do not pass within the given\n`timeout`\n, action fails with the\n`TimeoutError`\n.\n\nFor example, for\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\n, Playwright will ensure that:\n\nlocator resolves to exactly one element\nelement is\nVisible (https://playwright.dev/docs/actionability#visible)\nelement is\nStable (https://playwright.dev/docs/actionability#stable)\n, as in not animating or completed animation\nelement\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\n, as in not obscured by other elements\nelement is\nEnabled (https://playwright.dev/docs/actionability#enabled)\n\nHere is the complete list of actionability checks performed for each action:\n\nAction\nVisible (https://playwright.dev/docs/actionability#visible)\nStable (https://playwright.dev/docs/actionability#stable)\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\nEnabled (https://playwright.dev/docs/actionability#enabled)\nEditable (https://playwright.dev/docs/actionability#editable)\nlocator.check() (https://playwright.dev/docs/api/class-locator#locator-check)\nYes\nYes\nYes\nYes\n-\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nYes\nYes\nYes\nYes\n-\nlocator.dblclick() (https://playwright.dev/docs/api/class-locator#locator-dblclick)\nYes\nYes\nYes\nYes\n-\nlocator.setChecked() (https://playwright.dev/docs/api/class-locator#locator-set-checked)\nYes\nYes\nYes\nYes\n-\nlocator.tap() (https://playwright.dev/docs/api/class-locator#locator-tap)\nYes\nYes\nYes\nYes\n-\nlocator.uncheck() (https://playwright.dev/docs/api/class-locator#locator-uncheck)\nYes\nYes\nYes\nYes\n-\nlocator.hover() (https://playwright.dev/docs/api/class-locator#locator-hover)\nYes\nYes\nYes\n-\n-\nlocator.dragTo() (https://playwright.dev/docs/api/class-locator#locator-drag-to)\nYes\nYes\nYes\n-\n-\nlocator.screenshot() (https://playwright.dev/docs/api/class-locator#locator-screenshot)\nYes\nYes\n-\n-\n-\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\nYes\n-\n-\nYes\nYes\nlocator.clear() (https://playwright.dev/docs/api/class-locator#locator-clear)\nYes\n-\n-\nYes\nYes\nlocator.selectOption() (https://playwright.dev/docs/api/class-locator#locator-select-option)\nYes\n-\n-\nYes\n-\nlocator.selectText() (https://playwright.dev/docs/api/class-locator#locator-select-text)\nYes\n-\n-\n-\n-\nlocator.scrollIntoViewIfNeeded() (https://playwright.dev/docs/api/class-locator#locator-scroll-into-view-if-needed)\n-\nYes\n-\n-\n-\nlocator.blur() (https://playwright.dev/docs/api/class-locator#locator-blur)\n-\n-\n-\n-\n-\nlocator.dispatchEvent() (https://playwright.dev/docs/api/class-locator#locator-dispatch-event)\n-\n-\n-\n-\n-\nlocator.focus() (https://playwright.dev/docs/api/class-locator#locator-focus)\n-\n-\n-\n-\n-\nlocator.press() (https://playwright.dev/docs/api/class-locator#locator-press)\n-\n-\n-\n-\n-\nlocator.pressSequentially() (https://playwright.dev/docs/api/class-locator#locator-press-sequentially)\n-\n-\n-\n-\n-\nlocator.setInputFiles() (https://playwright.dev/docs/api/class-locator#locator-set-input-files)\n-\n-\n-\n-\n-', 'Locators | Playwright', 'Element is considered visible when it has non-empty bounding box and does not have\n`visibility:hidden`\ncomputed style.\n\nNote that according to this definition:\n\nElements of zero size\nare not\nconsidered visible.\nElements with\n`display:none`\nare not\nconsidered visible.\nElements with\n`opacity:0`\nare\nconsidered visible.', 'Element is considered stable when it has maintained the same bounding box for at least two consecutive animation frames.', 'Element is considered receiving pointer events when it is the hit target of the pointer event at the action point. For example, when clicking at the point\n`(10;10)`\n, Playwright checks whether some other element (usually an overlay) will instead capture the click at\n`(10;10)`\n.\n\nFor example, consider a scenario where Playwright will click\n`Sign Up`\nbutton regardless of when the\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\ncall was made:\n\npage is checking that user name is unique and\n`Sign Up`\nbutton is disabled;\nafter checking with the server, the disabled\n`Sign Up`\nbutton is replaced with another one that is now enabled.', 'Element is considered enabled when it is\nnot disabled\n.\n\nElement is\ndisabled\nwhen:\n\nit is a\n`&lt;button&gt;`\n,\n`&lt;select&gt;`\n,\n`&lt;input&gt;`\n,\n`&lt;textarea&gt;`\n,\n`&lt;option&gt;`\nor\n`&lt;optgroup&gt;`\nwith a\n`[disabled]`\nattribute;\nit is a\n`&lt;button&gt;`\n,\n`&lt;select&gt;`\n,\n`&lt;input&gt;`\n,\n`&lt;textarea&gt;`\n,\n`&lt;option&gt;`\nor\n`&lt;optgroup&gt;`\nthat is a part of a\n`&lt;fieldset&gt;`\nwith a\n`[disabled]`\nattribute;\nit is a descendant of an element with\n`[aria-disabled=true]`\nattribute.']</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2616,20 +3071,13 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Before a click, Playwright performs a range of actionability checks to ensure the action behaves as expected. Specifically, it verifies that:
-*   The locator resolves to exactly one element.
-*   The element is visible (not empty, no `display:none`, no `visibility:hidden`).
-*   The element is stable (not animating or has completed animation).
-*   The element receives events (is not obscured by other elements).
-*   The element is enabled.
-Regarding how this relates to the waiting a plain click already does, Playwright auto-waits for all these relevant checks to pass before performing the action. Under the hood, pointer-related methods (like click) perform these steps:
-*   Wait for the element to be in the DOM.
-*   Wait for it to become displayed.
-*   Wait for it to stop moving (e.g., until CSS transitions finish).
-*   Scroll the element into view.
-*   Wait for it to receive pointer events at the action point (ensuring it is not obscured).
-*   Retry if the element is detached during any of these checks.
-If these checks do not pass within the given `timeout`, the action fails with a `TimeoutError`.</t>
+          <t>Before performing a `locator.click()`, Playwright verifies the following actionability checks:
+*   **Resolution:** The locator must resolve to exactly one element.
+*   **Visible:** The element must have a non-empty bounding box and not have a `visibility:hidden` computed style.
+*   **Stable:** The element must maintain the same bounding box for at least two consecutive animation frames (i.e., it is not animating).
+*   **Receives Events:** The element must be the hit target of the pointer event at the action point (i.e., it is not obscured by other elements).
+*   **Enabled:** The element must not be disabled (e.g., it does not have a `[disabled]` attribute, is not part of a disabled `&lt;fieldset&gt;`, or is not a descendant of an element with `[aria-disabled=true]`).
+Regarding the relationship to waiting, Playwright performs these checks automatically as part of its "auto-waiting" mechanism. It waits for all of these relevant checks to pass before executing the click. If these checks do not pass within the specified `timeout`, the action fails with a `TimeoutError`.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2638,25 +3086,31 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0.00817675</v>
       </c>
       <c r="G41" t="n">
-        <v>0.42</v>
+        <v>30072</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1193181818181818</v>
+        <v>0.3</v>
       </c>
       <c r="J41" t="n">
-        <v>0.5833333333333334</v>
+        <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5833333333041666</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="42">
@@ -2667,7 +3121,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>["Download | Playwright\n\nDownload (https://playwright.dev/docs/api/class-download)\nobjects are dispatched by page via the\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent.\n\nAll the downloaded files belonging to the browser context are deleted when the browser context is closed.\n\nDownload event is emitted once the download starts. Download path becomes available once download completes.\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", 'Downloads | Playwright', "Added before v1.9\n\ndownload.path\n\nReturns path to the downloaded file for a successful download, or throws for a failed/canceled download. The method will wait for the download to finish if necessary. The method throws when connected remotely.\n\nNote that the download's file name is a random GUID, use\ndownload.suggestedFilename() (https://playwright.dev/docs/api/class-download#download-suggested-filename)\nto get suggested file name.\n\nUsage\n\n```\n`awaitdownload.path();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n# (https://playwright.dev/docs/api/class-download#download-path-return)", "For every attachment downloaded by the page,\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent is emitted. All these attachments are downloaded into a temporary folder. You can obtain the download url, file name and payload stream using the\nDownload (https://playwright.dev/docs/api/class-download)\nobject from the event.\n\nYou can specify where to persist downloaded files using the\ndownloadsPath (https://playwright.dev/docs/api/class-browsertype#browser-type-launch-option-downloads-path)\noption in\nbrowserType.launch() (https://playwright.dev/docs/api/class-browsertype#browser-type-launch)\n.\n\nnote\nDownloaded files are deleted when the browser context that produced them is closed.\n\nHere is the simplest way to handle the file download:\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", 'Added before v1.9\n\ndownload.failure\n\nReturns download error if any. Will wait for the download to finish if necessary.\n\nUsage\n\n```\n`awaitdownload.failure();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nnull (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/null)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n# (https://playwright.dev/docs/api/class-download#download-failure-return)', "If you have no idea what initiates the download, you can still handle the event:\n\n```\n`page.on('download',download=&gt;download.path().then(console.log));`\n```\n\nNote that handling the event forks the control flow and makes the script harder to follow. Your scenario might end while you are downloading a file since your main control flow is not awaiting for this operation to resolve.\n\nnote\nFor uploading files, see the\nuploading files (https://playwright.dev/docs/input#upload-files)\nsection."]</t>
+          <t>["Download | Playwright\n\nDownload (https://playwright.dev/docs/api/class-download)\nobjects are dispatched by page via the\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent.\n\nAll the downloaded files belonging to the browser context are deleted when the browser context is closed.\n\nDownload event is emitted once the download starts. Download path becomes available once download completes.\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", 'Downloads | Playwright', "For every attachment downloaded by the page,\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent is emitted. All these attachments are downloaded into a temporary folder. You can obtain the download url, file name and payload stream using the\nDownload (https://playwright.dev/docs/api/class-download)\nobject from the event.\n\nYou can specify where to persist downloaded files using the\ndownloadsPath (https://playwright.dev/docs/api/class-browsertype#browser-type-launch-option-downloads-path)\noption in\nbrowserType.launch() (https://playwright.dev/docs/api/class-browsertype#browser-type-launch)\n.\n\nnote\nDownloaded files are deleted when the browser context that produced them is closed.\n\nHere is the simplest way to handle the file download:\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", "If you have no idea what initiates the download, you can still handle the event:\n\n```\n`page.on('download',download=&gt;download.path().then(console.log));`\n```\n\nNote that handling the event forks the control flow and makes the script harder to follow. Your scenario might end while you are downloading a file since your main control flow is not awaiting for this operation to resolve.\n\nnote\nFor uploading files, see the\nuploading files (https://playwright.dev/docs/input#upload-files)\nsection."]</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2677,11 +3131,8 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Based on the provided context, here is the answer to your question:
-**Where do downloaded files go?**
-Downloaded files are initially stored in a temporary folder. You can also specify a location to persist downloaded files by using the `downloadsPath` option in `browserType.launch()`.
-**Why might they disappear before you can use them?**
-All downloaded files belonging to a browser context are deleted when that browser context is closed. Additionally, if you do not properly await the download process in your main control flow, your scenario might end while the file is still downloading, potentially leading to issues with accessing the file.</t>
+          <t>Downloaded files are initially stored in a temporary folder. You can specify a different location to persist these files by using the `downloadsPath` option in `browserType.launch()`.
+Files may disappear before you can use them because all downloaded files belonging to a browser context are deleted when that context is closed. Additionally, if you handle the download event using `page.on('download')` without awaiting the operation, your script scenario might end while the download is still in progress, potentially leading to the context closing and the files being deleted.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2690,24 +3141,30 @@
         </is>
       </c>
       <c r="F42" t="n">
+        <v>0.007493499999999999</v>
+      </c>
+      <c r="G42" t="n">
+        <v>28974</v>
+      </c>
+      <c r="H42" t="n">
         <v>0.75</v>
       </c>
-      <c r="G42" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H42" t="n">
-        <v>5</v>
-      </c>
       <c r="I42" t="n">
-        <v>0.1470588235294118</v>
+        <v>0.67</v>
       </c>
       <c r="J42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.1685393258426966</v>
+      </c>
+      <c r="L42" t="n">
         <v>0.375</v>
       </c>
-      <c r="K42" t="n">
-        <v>0.7499999999625</v>
-      </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
+        <v>0.8333333332916666</v>
+      </c>
+      <c r="N42" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2719,7 +3176,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>['Video | Playwright\n\nWhen browser context is created with the\n`recordVideo`\noption, each page has a video object associated with it.\n\n```\n`console.log(awaitpage.video().path());`\n```', 'Videos | Playwright', "Playwright Test can record videos for your tests, controlled by the\n`video`\noption in your Playwright config. By default videos are off.\n\n`'off'`\n- Do not record video.\n`'on'`\n- Record video for each test.\n`'retain-on-failure'`\n- Record video for each test, but remove all videos from successful test runs.\n`'on-first-retry'`\n- Record video only when retrying a test for the first time.\n\nVideo files will appear in the test output directory, typically\n`test-results`\n. See\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nfor advanced video configuration.\n\nVideos are saved upon\nbrowser context (https://playwright.dev/docs/browser-contexts)\nclosure at the end of a test. If you create a browser context manually, make sure to await\nbrowserContext.close() (https://playwright.dev/docs/api/class-browsercontext#browser-context-close)\n.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:'on-first-retry',},});`\n```\n```\n`constcontext=awaitbrowser.newContext({recordVideo:{dir:'videos/'}});// Make sure to await close, so that videos are saved.awaitcontext.close();`\n```\n\nYou can also specify video size and annotation. The video size defaults to the viewport size scaled down to fit 800x800. The video of the viewport is placed in the top-left corner of the output video, scaled down to fit if necessary. You may need to set the viewport size to match your desired video size.\n\nWhen\n`show: { actions }`\nis specified, each action will be visually highlighted in the video with the element outline and action title subtitle. The optional\n`duration`\nproperty controls how long each annotation is displayed (defaults to\n`500`\nms).\n\nWhen\n`show: { test }`\nis specified, video will be annotated with the current test information with configurable\n`level`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:{mode:'on-first-retry',size:{width:640,height:480},show:{actions:{duration:500,position:'top-right',fontSize:14,},test:{level:'step',position:'top-left',fontSize:12,}},},},});`\n```\n\nFor multi-page scenarios, you can access the video file associated with the page via the\npage.video() (https://playwright.dev/docs/api/class-page#page-video)\n.\n\n```\n`constpath=awaitpage.video().path();`\n```\n\nnote\nNote that the video is only available after the page or browser context is closed.", "With Playwright you can capture screenshots, record videos as well as traces of your test. By default these are turned off but you can enable them by setting the\n`screenshot`\n,\n`video`\nand\n`trace`\noptions in your\n`playwright.config.js`\nfile.\n\nTrace files, screenshots and videos will appear in the test output directory, typically\n`test-results`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{// Capture screenshot after each test failure.screenshot:'only-on-failure',// Record trace only when retrying a test for the first time.trace:'on-first-retry',// Record video only when retrying a test for the first time.video:'on-first-retry'},});`\n```\n\nOption\nDescription\ntestOptions.screenshot (https://playwright.dev/docs/api/class-testoptions#test-options-screenshot)\nCapture\nscreenshots (https://playwright.dev/docs/screenshots)\nof your test. Options include\n`'off'`\n,\n`'on'`\nand\n`'only-on-failure'`\ntestOptions.trace (https://playwright.dev/docs/api/class-testoptions#test-options-trace)\nPlaywright can produce test traces while running the tests. Later on, you can view the trace and get detailed information about Playwright execution by opening\nTrace Viewer (https://playwright.dev/docs/trace-viewer)\n. Options include:\n`'off'`\n,\n`'on'`\n,\n`'retain-on-failure'`\nand\n`'on-first-retry'`\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nPlaywright can record\nvideos (https://playwright.dev/docs/videos)\nfor your tests. Options include:\n`'off'`\n,\n`'on'`\n,\n`'retain-on-failure'`\nand\n`'on-first-retry'`", 'Added before v1.9\n\nvideo.path\n\nReturns the file system path this video will be recorded to. The video is guaranteed to be written to the filesystem upon closing the browser context. This method throws when connected remotely.\n\nUsage\n\n```\n`awaitvideo.path();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n# (https://playwright.dev/docs/api/class-video#video-path-return)', 'Configuration (use) | Playwright']</t>
+          <t>['Video | Playwright\n\nWhen browser context is created with the\n`recordVideo`\noption, each page has a video object associated with it.\n\n```\n`console.log(awaitpage.video().path());`\n```', 'Videos | Playwright', "Playwright Test can record videos for your tests, controlled by the\n`video`\noption in your Playwright config. By default videos are off.\n\n`'off'`\n- Do not record video.\n`'on'`\n- Record video for each test.\n`'retain-on-failure'`\n- Record video for each test, but remove all videos from successful test runs.\n`'on-first-retry'`\n- Record video only when retrying a test for the first time.\n\nVideo files will appear in the test output directory, typically\n`test-results`\n. See\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nfor advanced video configuration.\n\nVideos are saved upon\nbrowser context (https://playwright.dev/docs/browser-contexts)\nclosure at the end of a test. If you create a browser context manually, make sure to await\nbrowserContext.close() (https://playwright.dev/docs/api/class-browsercontext#browser-context-close)\n.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:'on-first-retry',},});`\n```\n```\n`constcontext=awaitbrowser.newContext({recordVideo:{dir:'videos/'}});// Make sure to await close, so that videos are saved.awaitcontext.close();`\n```\n\nYou can also specify video size and annotation. The video size defaults to the viewport size scaled down to fit 800x800. The video of the viewport is placed in the top-left corner of the output video, scaled down to fit if necessary. You may need to set the viewport size to match your desired video size.\n\nWhen\n`show: { actions }`\nis specified, each action will be visually highlighted in the video with the element outline and action title subtitle. The optional\n`duration`\nproperty controls how long each annotation is displayed (defaults to\n`500`\nms).\n\nWhen\n`show: { test }`\nis specified, video will be annotated with the current test information with configurable\n`level`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:{mode:'on-first-retry',size:{width:640,height:480},show:{actions:{duration:500,position:'top-right',fontSize:14,},test:{level:'step',position:'top-left',fontSize:12,}},},},});`\n```\n\nFor multi-page scenarios, you can access the video file associated with the page via the\npage.video() (https://playwright.dev/docs/api/class-page#page-video)\n.\n\n```\n`constpath=awaitpage.video().path();`\n```\n\nnote\nNote that the video is only available after the page or browser context is closed.", 'Added before v1.9\n\nvideo.path\n\nReturns the file system path this video will be recorded to. The video is guaranteed to be written to the filesystem upon closing the browser context. This method throws when connected remotely.\n\nUsage\n\n```\n`awaitvideo.path();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n# (https://playwright.dev/docs/api/class-video#video-path-return)', 'Added in: v1.11\n\nvideo.saveAs\n\nSaves the video to a user-specified path. It is safe to call this method while the video is still in progress, or after the page has closed. This method waits until the page is closed and the video is fully saved.\n\nUsage\n\n```\n`awaitvideo.saveAs(path);`\n```\n\nArguments\n\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-video#video-save-as-option-path)\nPath where the video should be saved.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-video#video-save-as-return)', 'Configuration (use) | Playwright']</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2729,7 +3186,8 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Videos are saved upon the closure of the browser context at the end of a test. If you create a browser context manually, you must ensure that you await `browserContext.close()` for the video to be saved. Additionally, the video is only available after the page or browser context is closed.</t>
+          <t>Video capture is tied to the browser context lifecycle because videos are saved upon the closure of the browser context at the end of a test. 
+If you create a browser context manually, you must `await browserContext.close()` to ensure the video is saved to the filesystem. The video is guaranteed to be written to the filesystem only upon closing the browser context, and it is only available after the page or browser context is closed.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2738,74 +3196,87 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0.00780925</v>
       </c>
       <c r="G43" t="n">
-        <v>0.67</v>
+        <v>30157</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3137254901960784</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
-        <v>0.4705882352941176</v>
+        <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>0.3666666666483334</v>
+        <v>0.2368421052631579</v>
       </c>
       <c r="L43" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.4166666666458333</v>
+      </c>
+      <c r="N43" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>What's the difference between page.screenshot() and toHaveScreenshot(), and when do I use each?</t>
+          <t>We rolled our own visual checks: capture a PNG, compare it byte-for-byte with a committed file, fail on any difference. It's unusable — it fails on the first run of any new test, it fails constantly on CI with what look like anti-aliasing differences, and there's no way to accept a legitimate design change short of regenerating files by hand. What does the built-in comparison do differently at each of those three points?</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>["LocatorAssertions | Playwright\n\nThe\nLocatorAssertions (https://playwright.dev/docs/api/class-locatorassertions)\nclass provides assertion methods that can be used to make assertions about the\nLocator (https://playwright.dev/docs/api/class-locator)\nstate in the tests.\n\n```\n`import{test,expect}from'@playwright/test';test('status becomes submitted',async({page})=&gt;{// ...awaitpage.getByRole('button').click();awaitexpect(page.locator('.status')).toHaveText('Submitted');});`\n```", "PageAssertions | Playwright\n\nThe\nPageAssertions (https://playwright.dev/docs/api/class-pageassertions)\nclass provides assertion methods that can be used to make assertions about the\nPage (https://playwright.dev/docs/api/class-page)\nstate in the tests.\n\n```\n`import{test,expect}from'@playwright/test';test('navigates to login',async({page})=&gt;{// ...awaitpage.getByText('Sign in').click();awaitexpect(page).toHaveURL(/.*\\/login/);});`\n```", "Page | Playwright\n\nPage provides methods to interact with a single tab in a\nBrowser (https://playwright.dev/docs/api/class-browser)\n, or an\nextension background page (https://developer.chrome.com/extensions/background_pages)\nin Chromium. One\nBrowser (https://playwright.dev/docs/api/class-browser)\ninstance might have multiple\nPage (https://playwright.dev/docs/api/class-page)\ninstances.\n\nThis example creates a page, navigates it to a URL, and then saves a screenshot:\n\n```\n`const{webkit}=require('playwright');// Or 'chromium' or 'firefox'.(async()=&gt;{constbrowser=awaitwebkit.launch();constcontext=awaitbrowser.newContext();constpage=awaitcontext.newPage();awaitpage.goto('https://example.com');awaitpage.screenshot({path:'screenshot.png'});awaitbrowser.close();})();`\n```\n\nThe Page class emits various events (described below) which can be handled using any of Node's native\nEventEmitter (https://nodejs.org/api/events.html#events_class_eventemitter)\nmethods, such as\n`on`\n,\n`once`\nor\n`removeListener`\n.\n\nThis example logs a message for a single page\n`load`\nevent:\n\n```\n`page.once('load',()=&gt;console.log('Page loaded!'));`\n```\n\nTo unsubscribe from events use the\n`removeListener`\nmethod:\n\n```\n`functionlogRequest(interceptedRequest){console.log('A request was made:',interceptedRequest.url());}page.on('request',logRequest);// Sometime later...page.removeListener('request',logRequest);`\n```", 'Visual comparisons | Playwright', 'Screenshots | Playwright', "Playwright Test includes the ability to produce and visually compare screenshots using\n`await expect(page).toHaveScreenshot()`\n. On first execution, Playwright test will generate reference screenshots. Subsequent runs will compare against the reference.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('example test',async({page})=&gt;{awaitpage.goto('https://playwright.dev');awaitexpect(page).toHaveScreenshot();});`\n```\n\nwarning\nBrowser rendering can vary based on the host OS, version, settings, hardware, power source (battery vs. power adapter), headless mode, and other factors. For consistent screenshots, run tests in the same environment where the baseline screenshots were generated.", "Here is a quick way to capture a screenshot and save it into a file:\n\n```\n`awaitpage.screenshot({path:'screenshot.png'});`\n```\n\nScreenshots API (https://playwright.dev/docs/api/class-page#page-screenshot)\naccepts many parameters for image format, clip area, quality, etc. Make sure to check them out."]</t>
+          <t>['Visual comparisons | Playwright', "Playwright Test includes the ability to produce and visually compare screenshots using\n`await expect(page).toHaveScreenshot()`\n. On first execution, Playwright test will generate reference screenshots. Subsequent runs will compare against the reference.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('example test',async({page})=&gt;{awaitpage.goto('https://playwright.dev');awaitexpect(page).toHaveScreenshot();});`\n```\n\nwarning\nBrowser rendering can vary based on the host OS, version, settings, hardware, power source (battery vs. power adapter), headless mode, and other factors. For consistent screenshots, run tests in the same environment where the baseline screenshots were generated.", 'Sometimes you need to update the reference screenshot, for example when the page has changed. Do this with the\n`--update-snapshots`\nflag.\n\n```\n`npx playwrighttest--update-snapshots`\n```', "Playwright Test uses the\npixelmatch (https://github.com/mapbox/pixelmatch)\nlibrary. You can\npass various options (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\nto modify its behavior:\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('example test',async({page})=&gt;{awaitpage.goto('https://playwright.dev');awaitexpect(page).toHaveScreenshot({maxDiffPixels:100});});`\n```\n\nIf you'd like to share the default value among all the tests in the project, you can specify it in the playwright config, either globally or per project:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({expect:{toHaveScreenshot:{maxDiffPixels:100},},});`\n```", 'UI Mode | Playwright', 'Trace viewer | Playwright', "When you run above for the first time, test runner will say:\n\n```\n`Error: A snapshot doesn't exist at example.spec.ts-snapshots/example-test-1-chromium-darwin.png, writing actual.`\n```\n\nThat's because there was no golden file yet. This method took a bunch of screenshots until two consecutive screenshots matched, and saved the last screenshot to file system. It is now ready to be added to the repository.\n\nThe name of the folder with the golden expectations starts with the name of your test file:\n\n```\n`drwxr-xr-x5user  group160Jun411:46.drwxr-xr-x6user  group192Jun411:45..-rw-r--r--1user  group231Jun411:16 example.spec.tsdrwxr-xr-x3user  group96Jun411:46 example.spec.ts-snapshots`\n```\n\nThe snapshot name\n`example-test-1-chromium-darwin.png`\nconsists of a few parts:\n\n`example-test-1.png`\n- an auto-generated name of the snapshot. Alternatively you can specify snapshot name as the first argument of the\n`toHaveScreenshot()`\nmethod:\n```\n`awaitexpect(page).toHaveScreenshot('landing.png');`\n```\n`chromium-darwin`\n- the browser name and the platform. Screenshots differ between browsers and platforms due to different rendering, fonts and more, so you will need different snapshots for them. If you use multiple projects in your\nconfiguration file (https://playwright.dev/docs/test-configuration)\n, project name will be used instead of\n`chromium`\n.\n\nThe snapshot name and path can be configured with\ntestConfig.snapshotPathTemplate (https://playwright.dev/docs/api/class-testconfig#test-config-snapshot-path-template)\nin the playwright config.\n\nNote that\n`toHaveScreenshot()`\nalso accepts an array of path segments to the snapshot file such as\n`expect().toHaveScreenshot(['relative', 'path', 'to', 'snapshot.png'])`\n.\nHowever, this path must stay within the snapshots directory for each test file (i.e.\n`a.spec.js-snapshots`\n), otherwise it will throw."]</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>['Here is a quick way to capture a screenshot and save it into a file:', 'Playwright Test includes the ability to produce and visually compare screenshots using await expect(page).toHaveScreenshot() . On first execution, Playwright test will generate reference screenshots. Subsequent runs will compare against the reference.']</t>
+          <t>["Error: A snapshot doesn't exist at example.spec.ts-snapshots/example-test-1-chromium-darwin.png, writing actual.", 'chromium-darwin - the browser name and the platform. Screenshots differ between browsers and platforms due to different rendering, fonts and more, so you will need different snapshots for them. If you use multiple projects in your configuration file, project name will be used instead of chromium.', 'Sometimes you need to update the reference screenshot, for example when the page has changed. Do this with the --update-snapshots flag. npx playwright test --update-snapshots', 'export default defineConfig({ expect: { toHaveScreenshot: { maxDiffPixels: 100 }, }, });']</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Based on the provided context, here is the difference between `page.screenshot()` and `toHaveScreenshot()`:
-*   **`page.screenshot()`**: This is a method used to capture a screenshot and save it to a file. You use this when you want to manually save an image of the page (e.g., `await page.screenshot({path: 'screenshot.png'});`).
-*   **`toHaveScreenshot()`**: This is an assertion method used for visual comparisons. You use this within Playwright Test to compare the current state of the page against a reference screenshot. On the first execution, it generates the reference, and subsequent runs compare the page against that baseline.</t>
+          <t>The built-in `toHaveScreenshot()` method addresses your three points as follows:
+*   **First run of a new test:** Instead of failing, Playwright automatically generates the reference screenshot. It takes multiple screenshots until two consecutive ones match, saves the final result to the file system, and reports that it is writing the actual file.
+*   **Anti-aliasing and minor differences:** Playwright uses the `pixelmatch` library for comparisons. You can configure the comparison tolerance by passing options such as `maxDiffPixels` to `toHaveScreenshot()`. This can be set per test or globally in your `playwright.config.ts` file to allow for minor rendering variations.
+*   **Accepting design changes:** You do not need to manually regenerate files. You can update the reference screenshots by running the test command with the `--update-snapshots` flag (e.g., `npx playwright test --update-snapshots`).</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>page.screenshot() simply captures an image to a file or buffer. toHaveScreenshot() is a visual-regression assertion: the first run saves a reference image and later runs compare against it, failing on unexpected differences.</t>
+          <t>Each of your three problems is a thing the built-in assertion already handles, because capturing an image and asserting on one are different operations. page.screenshot() just returns a buffer; expect(page).toHaveScreenshot() is a full comparison assertion. On first run there is no baseline, so instead of failing meaninglessly it takes screenshots until two consecutive ones match — which also settles animation and rendering noise — saves the result as the reference and reports that it wrote it; you commit that file. On CI, the baseline is keyed by environment: the snapshot name like example-test-1-chromium-darwin.png encodes the browser and platform (the project name replaces the browser when you use multiple projects) precisely because rendering, fonts and anti-aliasing differ across platforms, so Linux CI compares against its own baseline rather than your macOS one. And byte-exactness isn't required: `maxDiffPixels` (per assertion or globally under `expect: { toHaveScreenshot: ... }`) sets an allowance. When a change is intentional you re-baseline with `npx playwright test --update-snapshots` rather than editing files.</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0.008920500000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>0.67</v>
+        <v>33622</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0.163265306122449</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
-        <v>0.4705882352941176</v>
+        <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>0.3257575757575757</v>
       </c>
       <c r="L44" t="n">
+        <v>0.2471264367816092</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.6178571428416965</v>
+      </c>
+      <c r="N44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2817,7 +3288,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>['Authentication | Playwright', "Playwright can create multiple browser contexts within a single scenario. This is useful when you want to test for multi-user functionality, like a chat.\n\nTest\nLibrary\n```\n`import{test}from'@playwright/test';test('admin and user',async({browser})=&gt;{// Create two isolated browser contextsconstadminContext=awaitbrowser.newContext();constuserContext=awaitbrowser.newContext();// Create pages and interact with contexts independentlyconstadminPage=awaitadminContext.newPage();constuserPage=awaituserContext.newPage();});`\n```\n```\n`const{chromium}=require('playwright');// Create a Chromium browser instanceconstbrowser=awaitchromium.launch();// Create two isolated browser contextsconstuserContext=awaitbrowser.newContext();constadminContext=awaitbrowser.newContext();// Create pages and interact with contexts independentlyconstadminPage=awaitadminContext.newPage();constuserPage=awaituserContext.newPage();`\n```", 'When to use\n\nYou need to test how multiple authenticated roles interact together, in a single test.\n\nDetails\n\nUse multiple\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\ns and\nPage (https://playwright.dev/docs/api/class-page)\ns with different storage states in the same test.\n\ntests/example.spec.ts\n```\n`import{test}from\'@playwright/test\';test(\'admin and user\',async({browser})=&gt;{// adminContext and all pages inside, including adminPage, are signed in as "admin".constadminContext=awaitbrowser.newContext({storageState:\'playwright/.auth/admin.json\'});constadminPage=awaitadminContext.newPage();// userContext and all pages inside, including userPage, are signed in as "user".constuserContext=awaitbrowser.newContext({storageState:\'playwright/.auth/user.json\'});constuserPage=awaituserContext.newPage();// ... interact with both adminPage and userPage ...awaitadminContext.close();awaituserContext.close();});`\n```', 'When to use\n\nYou need to test how multiple authenticated roles interact together, in a single test.\n\nDetails\n\nYou can introduce fixtures that will provide a page authenticated as each role.\n\nBelow is an example that\ncreates fixtures (https://playwright.dev/docs/test-fixtures#creating-a-fixture)\nfor two\nPage Object Models (https://playwright.dev/docs/pom)\n- admin POM and user POM. It assumes\n`adminStorageState.json`\nand\n`userStorageState.json`\nfiles were created in the global setup.\n\nplaywright/fixtures.ts\n```\n`import{testasbase,typePage,typeLocator}from\'@playwright/test\';// Page Object Model for the "admin" page.// Here you can add locators and helper methods specific to the admin page.classAdminPage{// Page signed in as "admin".page:Page;// Example locator pointing to "Welcome, Admin" greeting.greeting:Locator;constructor(page:Page){this.page=page;this.greeting=page.locator(\'#greeting\');}}// Page Object Model for the "user" page.// Here you can add locators and helper methods specific to the user page.classUserPage{// Page signed in as "user".page:Page;// Example locator pointing to "Welcome, User" greeting.greeting:Locator;constructor(page:Page){this.page=page;this.greeting=page.locator(\'#greeting\');}}// Declare the types of your fixtures.typeMyFixtures={adminPage:AdminPage;userPage:UserPage;};export*from\'@playwright/test\';exportconsttest=base.extend&lt;MyFixtures&gt;({adminPage:async({browser},use)=&gt;{constcontext=awaitbrowser.newContext({storageState:\'playwright/.auth/admin.json\'});constadminPage=newAdminPage(awaitcontext.newPage());awaituse(adminPage);awaitcontext.close();},userPage:async({browser},use)=&gt;{constcontext=awaitbrowser.newContext({storageState:\'playwright/.auth/user.json\'});constuserPage=newUserPage(awaitcontext.newPage());awaituse(userPage);awaitcontext.close();},});`\n```\n\ntests/example.spec.ts\n```\n`// Import test with our new fixtures.import{test,expect}from\'../playwright/fixtures\';// Use adminPage and userPage fixtures in the test.test(\'admin and user\',async({adminPage,userPage})=&gt;{// ... interact with both adminPage and userPage ...awaitexpect(adminPage.greeting).toHaveText(\'Welcome, Admin\');awaitexpect(userPage.greeting).toHaveText(\'Welcome, User\');});`\n```', 'Isolation | Playwright', "BrowserContext | Playwright\n\nBrowserContexts provide a way to operate multiple independent browser sessions.\n\nIf a page opens another page, e.g. with a\n`window.open`\ncall, the popup will belong to the parent page's browser context.\n\nPlaywright allows creating isolated non-persistent browser contexts with\nbrowser.newContext() (https://playwright.dev/docs/api/class-browser#browser-new-context)\nmethod. Non-persistent browser contexts don't write any browsing data to disk.\n\n```\n`// Create a new incognito browser contextconstcontext=awaitbrowser.newContext();// Create a new page inside context.constpage=awaitcontext.newPage();awaitpage.goto('https://example.com');// Dispose context once it's no longer needed.awaitcontext.close();`\n```"]</t>
+          <t>["Playwright can create multiple browser contexts within a single scenario. This is useful when you want to test for multi-user functionality, like a chat.\n\nTest\nLibrary\n```\n`import{test}from'@playwright/test';test('admin and user',async({browser})=&gt;{// Create two isolated browser contextsconstadminContext=awaitbrowser.newContext();constuserContext=awaitbrowser.newContext();// Create pages and interact with contexts independentlyconstadminPage=awaitadminContext.newPage();constuserPage=awaituserContext.newPage();});`\n```\n```\n`const{chromium}=require('playwright');// Create a Chromium browser instanceconstbrowser=awaitchromium.launch();// Create two isolated browser contextsconstuserContext=awaitbrowser.newContext();constadminContext=awaitbrowser.newContext();// Create pages and interact with contexts independentlyconstadminPage=awaitadminContext.newPage();constuserPage=awaituserContext.newPage();`\n```", 'When to use\n\nYou need to test how multiple authenticated roles interact together, in a single test.\n\nDetails\n\nYou can introduce fixtures that will provide a page authenticated as each role.\n\nBelow is an example that\ncreates fixtures (https://playwright.dev/docs/test-fixtures#creating-a-fixture)\nfor two\nPage Object Models (https://playwright.dev/docs/pom)\n- admin POM and user POM. It assumes\n`adminStorageState.json`\nand\n`userStorageState.json`\nfiles were created in the global setup.\n\nplaywright/fixtures.ts\n```\n`import{testasbase,typePage,typeLocator}from\'@playwright/test\';// Page Object Model for the "admin" page.// Here you can add locators and helper methods specific to the admin page.classAdminPage{// Page signed in as "admin".page:Page;// Example locator pointing to "Welcome, Admin" greeting.greeting:Locator;constructor(page:Page){this.page=page;this.greeting=page.locator(\'#greeting\');}}// Page Object Model for the "user" page.// Here you can add locators and helper methods specific to the user page.classUserPage{// Page signed in as "user".page:Page;// Example locator pointing to "Welcome, User" greeting.greeting:Locator;constructor(page:Page){this.page=page;this.greeting=page.locator(\'#greeting\');}}// Declare the types of your fixtures.typeMyFixtures={adminPage:AdminPage;userPage:UserPage;};export*from\'@playwright/test\';exportconsttest=base.extend&lt;MyFixtures&gt;({adminPage:async({browser},use)=&gt;{constcontext=awaitbrowser.newContext({storageState:\'playwright/.auth/admin.json\'});constadminPage=newAdminPage(awaitcontext.newPage());awaituse(adminPage);awaitcontext.close();},userPage:async({browser},use)=&gt;{constcontext=awaitbrowser.newContext({storageState:\'playwright/.auth/user.json\'});constuserPage=newUserPage(awaitcontext.newPage());awaituse(userPage);awaitcontext.close();},});`\n```\n\ntests/example.spec.ts\n```\n`// Import test with our new fixtures.import{test,expect}from\'../playwright/fixtures\';// Use adminPage and userPage fixtures in the test.test(\'admin and user\',async({adminPage,userPage})=&gt;{// ... interact with both adminPage and userPage ...awaitexpect(adminPage.greeting).toHaveText(\'Welcome, Admin\');awaitexpect(userPage.greeting).toHaveText(\'Welcome, User\');});`\n```', 'Authentication | Playwright', 'Isolation | Playwright', 'When to use\n\nYou need to test how multiple authenticated roles interact together, in a single test.\n\nDetails\n\nUse multiple\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\ns and\nPage (https://playwright.dev/docs/api/class-page)\ns with different storage states in the same test.\n\ntests/example.spec.ts\n```\n`import{test}from\'@playwright/test\';test(\'admin and user\',async({browser})=&gt;{// adminContext and all pages inside, including adminPage, are signed in as "admin".constadminContext=awaitbrowser.newContext({storageState:\'playwright/.auth/admin.json\'});constadminPage=awaitadminContext.newPage();// userContext and all pages inside, including userPage, are signed in as "user".constuserContext=awaitbrowser.newContext({storageState:\'playwright/.auth/user.json\'});constuserPage=awaituserContext.newPage();// ... interact with both adminPage and userPage ...awaitadminContext.close();awaituserContext.close();});`\n```', "BrowserContext | Playwright\n\nBrowserContexts provide a way to operate multiple independent browser sessions.\n\nIf a page opens another page, e.g. with a\n`window.open`\ncall, the popup will belong to the parent page's browser context.\n\nPlaywright allows creating isolated non-persistent browser contexts with\nbrowser.newContext() (https://playwright.dev/docs/api/class-browser#browser-new-context)\nmethod. Non-persistent browser contexts don't write any browsing data to disk.\n\n```\n`// Create a new incognito browser contextconstcontext=awaitbrowser.newContext();// Create a new page inside context.constpage=awaitcontext.newPage();awaitpage.goto('https://example.com');// Dispose context once it's no longer needed.awaitcontext.close();`\n```", 'Fixtures | Playwright']</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2827,26 +3298,18 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>To get two authenticated sessions side by side in a single test, you should use multiple `BrowserContext` objects with different storage states.
-You can achieve this by following these steps:
-1.  **Create isolated contexts:** Use `browser.newContext()` to create separate contexts for the admin and the user.
-2.  **Apply storage states:** Pass the respective storage state files (e.g., `admin.json` and `user.json`) to the `storageState` option when creating each context.
-3.  **Interact independently:** Create a new page within each context to perform actions as the respective user.
-**Example:**
-```typescript
-test('admin and user', async ({ browser }) =&gt; {
-  // adminContext is signed in as "admin"
-  const adminContext = await browser.newContext({ storageState: 'playwright/.auth/admin.json' });
-  const adminPage = await adminContext.newPage();
-  // userContext is signed in as "user"
-  const userContext = await browser.newContext({ storageState: 'playwright/.auth/user.json' });
-  const userPage = await userContext.newPage();
-  // ... interact with both adminPage and userPage ...
-  await adminContext.close();
-  await userContext.close();
-});
-```
-Alternatively, you can use custom fixtures to provide authenticated pages as shown in the advanced scenarios documentation.</t>
+          <t>To get two authenticated sessions side by side in a single test, you should use multiple `BrowserContext`s with different storage states.
+### Recommended Approach: Using POM Fixtures
+The documentation recommends using fixtures to provide pages authenticated as each role. This involves:
+1.  **Defining Fixtures:** Create a file (e.g., `playwright/fixtures.ts`) that extends the base test to include `adminPage` and `userPage` fixtures. Each fixture creates a new `browser.newContext()` using a specific `storageState` file (e.g., `adminStorageState.json` and `userStorageState.json`) and initializes the corresponding Page Object Model.
+2.  **Using Fixtures in Tests:** Import your custom `test` from the fixtures file and use the `adminPage` and `userPage` arguments in your test function.
+### Alternative Approach: Manual Context Creation
+If you prefer not to use fixtures, you can manually create the contexts within the test:
+1.  Use `browser.newContext({ storageState: 'path/to/state.json' })` to create separate contexts for the admin and the user.
+2.  Create a page for each context using `context.newPage()`.
+3.  Interact with both pages independently.
+4.  Ensure you call `await context.close()` for each context once the test is complete.
+Both approaches rely on `browser.newContext()` to provide isolated, independent browser sessions.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2855,132 +3318,168 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0.00947975</v>
       </c>
       <c r="G45" t="n">
+        <v>35459</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
         <v>0.29</v>
       </c>
-      <c r="H45" t="n">
-        <v>5</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.08928571428571429</v>
-      </c>
       <c r="J45" t="n">
-        <v>0.3571428571428572</v>
+        <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7099999999858</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="L45" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.8766666666491334</v>
+      </c>
+      <c r="N45" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>When a test fails mid-file, why do my beforeAll/afterAll seem to run again, and how do serial groups behave with retries?</t>
+          <t>We added an automated accessibility scan to the suite and it's been green for months. This sprint a screen-reader user reported that our settings panel now reads its sections in the wrong order after a refactor that only moved markup around — and the scan didn't say a word about it. What class of problem is that scan actually able to catch, what would have caught the regression, and can both live in the same test?</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>['Retries | Playwright', "Playwright Test runs tests in worker processes. These processes are OS processes, running independently, orchestrated by the test runner. All workers have identical environments and each starts its own browser.\n\nConsider the following snippet:\n\n```\n`import{test}from'@playwright/test';test.describe('suite',()=&gt;{test.beforeAll(async()=&gt;{/* ... */});test('first good',async({page})=&gt;{/* ... */});test('second flaky',async({page})=&gt;{/* ... */});test('third good',async({page})=&gt;{/* ... */});test.afterAll(async()=&gt;{/* ... */});});`\n```\n\nWhen\nall tests pass\n, they will run in order in the same worker process.\n\nWorker process starts\n`beforeAll`\nhook runs\n`first good`\npasses\n`second flaky`\npasses\n`third good`\npasses\n`afterAll`\nhook runs\n\nShould\nany test fail\n, Playwright Test will discard the entire worker process along with the browser and will start a new one. Testing will continue in the new worker process starting with the next test.\n\nWorker process #1 starts\n`beforeAll`\nhook runs\n`first good`\npasses\n`second flaky`\nfails\n`afterAll`\nhook runs\nWorker process #2 starts\n`beforeAll`\nhook runs again\n`third good`\npasses\n`afterAll`\nhook runs\n\nIf you\nenable\nretries (https://playwright.dev/docs/test-retries#retries)\n, second worker process will start by retrying the failed test and continue from there.\n\nWorker process #1 starts\n`beforeAll`\nhook runs\n`first good`\npasses\n`second flaky`\nfails\n`afterAll`\nhook runs\nWorker process #2 starts\n`beforeAll`\nhook runs again\n`second flaky`\nis retried and passes\n`third good`\npasses\n`afterAll`\nhook runs\n\nThis scheme works perfectly for independent tests and guarantees that failing tests can't affect healthy ones.", "Use\ntest.describe.serial() (https://playwright.dev/docs/api/class-test#test-describe-serial)\nto group dependent tests to ensure they will always run together and in order. If one of the tests fails, all subsequent tests are skipped. All tests in the group are retried together.\n\nConsider the following snippet that uses\n`test.describe.serial`\n:\n\n```\n`import{test}from'@playwright/test';test.describe.configure({mode:'serial'});test.beforeAll(async()=&gt;{/* ... */});test('first good',async({page})=&gt;{/* ... */});test('second flaky',async({page})=&gt;{/* ... */});test('third good',async({page})=&gt;{/* ... */});`\n```\n\nWhen running without\nretries (https://playwright.dev/docs/test-retries#retries)\n, all tests after the failure are skipped:\n\nWorker process #1:\n`beforeAll`\nhook runs\n`first good`\npasses\n`second flaky`\nfails\n`third good`\nis skipped entirely\n\nWhen running with\nretries (https://playwright.dev/docs/test-retries#retries)\n, all tests are retried together:\n\nWorker process #1:\n`beforeAll`\nhook runs\n`first good`\npasses\n`second flaky`\nfails\n`third good`\nis skipped\nWorker process #2:\n`beforeAll`\nhook runs again\n`first good`\npasses again\n`second flaky`\npasses\n`third good`\npasses\n\nnote\nIt is usually better to make your tests isolated, so they can be efficiently run and retried independently.", "You can annotate inter-dependent tests as serial. If one of the serial tests fails, all subsequent tests are skipped. All tests in a group are retried together.\n\nnote\nUsing serial is not recommended. It is usually better to make your tests isolated, so they can be run independently.\n\n```\n`import{test,typePage}from'@playwright/test';// Annotate entire file as serial.test.describe.configure({mode:'serial'});letpage:Page;test.beforeAll(async({browser})=&gt;{page=awaitbrowser.newPage();});test.afterAll(async()=&gt;{awaitpage.close();});test('runs first',async()=&gt;{awaitpage.goto('https://playwright.dev/');});test('runs second',async()=&gt;{awaitpage.getByText('Get Started').click();});`\n```", 'Parallelism | Playwright', 'Fixtures | Playwright', 'Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`']</t>
+          <t>['Snapshot testing | Playwright', 'Playwright can be used to test your application for many types of accessibility issues.\n\nA few examples of problems this can catch include:\n\nText that would be hard to read for users with vision impairments due to poor color contrast with the background behind it\nUI controls and form elements without labels that a screen reader could identify\nInteractive elements with duplicate IDs which can confuse assistive technologies\n\nThe following examples rely on the\n@axe-core/playwright (https://npmjs.org/@axe-core/playwright)\npackage which adds support for running the\naxe accessibility testing engine (https://www.deque.com/axe/)\nas part of your Playwright tests.\n\nDisclaimer\nAutomated accessibility tests can detect some common accessibility problems such as missing or invalid properties. But many accessibility problems can only be discovered through manual testing. We recommend using a combination of automated testing, manual accessibility assessments, and inclusive user testing.\nFor manual assessments, we recommend\nAccessibility Insights for Web (https://accessibilityinsights.io/docs/web/overview/?referrer=playwright-accessibility-testing-js)\n, a free and open source dev tool that walks you through assessing a website for\nWCAG 2.1 AA (https://www.w3.org/WAI/WCAG21/quickref/?currentsidebar=%23col_customize&amp;levels=aaa)\ncoverage.', 'With Playwright\'s Snapshot testing you can assert the accessibility tree of a page against a predefined snapshot template.\n\n```\n`awaitpage.goto(\'https://playwright.dev/\');awaitexpect(page).toMatchAriaSnapshot(`- banner:- heading /Playwright enables reliable end-to-end/ [level=1]- link "Get started":- /url: /docs/intro- link "Star microsoft/playwright on GitHub":- /url: https://github.com/microsoft/playwright- link /[\\\\d]+k\\\\+ stargazers on GitHub/`);`\n```', 'By default, axe checks against a wide variety of accessibility rules. Some of these rules correspond to specific success criteria from the\nWeb Content Accessibility Guidelines (WCAG) (https://www.w3.org/TR/WCAG21/)\n, and others are "best practice" rules that are not specifically required by any WCAG criterion.\n\nYou can constrain an accessibility scan to only run those rules which are "tagged" as corresponding to specific WCAG success criteria by using\nAxeBuilder.withTags() (https://github.com/dequelabs/axe-core-npm/blob/develop/packages/playwright/README.md#axebuilderwithtagstags-stringarray)\n. For example,\nAccessibility Insights for Web\'s Automated Checks (https://accessibilityinsights.io/docs/web/getstarted/fastpass/?referrer=playwright-accessibility-testing-js)\nonly include axe rules that test for violations of WCAG A and AA success criteria; to match that behavior, you would use the tags\n`wcag2a`\n,\n`wcag2aa`\n,\n`wcag21a`\n, and\n`wcag21aa`\n.\n\nNote that automated testing cannot detect all types of WCAG violations.\n\n```\n`test(\'should not have any automatically detectable WCAG A or AA violations\',async({page})=&gt;{awaitpage.goto(\'https://your-site.com/\');constaccessibilityScanResults=awaitnewAxeBuilder({page}).withTags([\'wcag2a\',\'wcag2aa\',\'wcag21a\',\'wcag21aa\']).analyze();expect(accessibilityScanResults.violations).toEqual([]);});`\n```\n\nYou can find a complete listing of the rule tags axe-core supports in\nthe "Axe-core Tags" section of the axe API documentation (https://www.deque.com/axe/core-documentation/api-documentation/#axecore-tags)\n.', 'Accessibility testing | Playwright', 'Assertions | Playwright', 'Visual comparisons | Playwright']</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>['Should any test fail , Playwright Test will discard the entire worker process along with the browser and will start a new one. Testing will continue in the new worker process starting with the next test.', 'You can annotate inter-dependent tests as serial. If one of the serial tests fails, all subsequent tests are skipped. All tests in a group are retried together.']</t>
+          <t>['The following examples rely on the @axe-core/playwright package which adds support for running the axe accessibility testing engine as part of your Playwright tests.', 'Automated accessibility tests can detect some common accessibility problems such as missing or invalid properties. But many accessibility problems can only be discovered through manual testing. We recommend using a combination of automated testing, manual accessibility assessments, and inclusive user testing.', 'Accessibility tests work just like any other Playwright test. You can either create separate test cases for them, or integrate accessibility scans and assertions into your existing test cases.', 'In Playwright, aria snapshots provide a YAML representation of the accessibility tree of a page. These snapshots can be stored and compared later to verify if the page structure remains consistent or meets defined expectations.', 'The YAML format describes the hierarchical structure of accessible elements on the page, detailing roles, attributes, values, and text content. The structure follows a tree-like syntax, where each node represents an accessible element, and indentation indicates nested elements.', 'Snapshot testing is ideal for: UI testing of whole pages and components. Broad structural checks for complex UI components. Regression testing for outputs that rarely change structure.']</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Based on the provided context, here are the answers to your questions:
-**Why do `beforeAll`/`afterAll` seem to run again when a test fails?**
-When a test fails, Playwright Test discards the entire worker process (along with the browser) to ensure that failing tests do not affect healthy ones. It then starts a new worker process to continue testing, which triggers the `beforeAll` hook to run again in that new process.
-**How do serial groups behave with retries?**
-In serial mode, all tests in the group are retried together. If one test fails, all subsequent tests in that group are skipped in the initial attempt. When retried, the entire group starts over: the `beforeAll` hook runs again, and all tests in the serial group are executed again from the beginning.</t>
+          <t>The automated accessibility scan (using `@axe-core/playwright`) is able to catch problems such as:
+*   Poor color contrast between text and background.
+*   UI controls and form elements missing labels.
+*   Interactive elements with duplicate IDs.
+*   Missing or invalid properties.
+The regression you experienced—where the reading order of sections changed—would have been caught by **Snapshot testing** using `toMatchAriaSnapshot`. This allows you to assert the accessibility tree of a page against a predefined snapshot template, which would detect changes in the structure or order of elements as perceived by assistive technologies.
+Yes, both can live in the same test suite. You can combine automated accessibility scans (using `AxeBuilder`) and accessibility tree snapshot assertions (using `toMatchAriaSnapshot`) within your Playwright tests to cover both automated rule violations and structural regressions.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>A failure makes Playwright discard the whole worker (and its browser) and start fresh on the next test, so the hooks re-run. In a serial group a failure skips the remaining tests, and the entire group is retried together.</t>
+          <t>The scan and the regression are aimed at different things, which is why one sailed past the other. An automated scan — the documented approach uses the @axe-core/playwright package, where you await `new AxeBuilder({ page }).analyze()` and assert the returned `violations` array is empty — detects *rule* violations such as missing or invalid properties. It has no opinion about whether the structure is the one you intended, and the docs are explicit that many accessibility problems can only be found through manual testing, recommending a combination of automated scans, manual assessment and inclusive user testing. What your refactor changed was the shape of the accessibility tree, and that is what an aria snapshot pins: expect(page).toMatchAriaSnapshot() captures a YAML representation of the accessibility tree — the hierarchy of accessible elements with their roles, attributes, values and text, with indentation carrying the nesting — and fails when the current tree stops matching it. Order and nesting are part of that representation, so a moved section shows as a diff. The two compose: accessibility tests are ordinary tests, so you can put both in one spec or keep separate ones. Bear in mind the tradeoff the docs draw between the styles — targeted assertions check one specific condition and get verbose over complex structures, while snapshots capture whole-structure state and are best for outputs that rarely change shape, which also means they need deliberate re-baselining when a change is intentional.</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>0.01001175</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9399999999999999</v>
+        <v>37192</v>
       </c>
       <c r="H46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1461538461538462</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
-        <v>0.475</v>
+        <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>0.3333333333</v>
+        <v>0.2834645669291339</v>
       </c>
       <c r="L46" t="n">
+        <v>0.1512605042016807</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.9150793650641138</v>
+      </c>
+      <c r="N46" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>How do I run DOM code against every element a locator matches and pull values back into my test?</t>
+          <t>I need to assert that every row in our pricing table renders right-aligned, which isn't in the DOM anywhere — it's a computed style. Nothing on the locator exposes it, and my first attempt at reaching into the page came back with undefined for the threshold I was comparing against, even though it's a plain number defined right above the call.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>['Evaluating JavaScript | Playwright', "Added in: v1.14\n\nlocator.evaluateAll\n\nExecute JavaScript code in the page, taking all matching elements as an argument.\n\nUsage\n\n```\n`constlocator=page.locator('div');constmoreThanTen=awaitlocator.evaluateAll((divs,min)=&gt;divs.length&gt;min,10);`\n```\n\nArguments\n\n`pageFunction`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\nFunction to be evaluated in the page context.\n`arg`\nEvaluationArgument (https://playwright.dev/docs/evaluating#evaluation-argument)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-arg)\nOptional argument to pass to\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\n.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-return)\n\nDetails\n\nReturns the return value of\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\n, called with an array of all matching elements as a first argument, and\narg (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-arg)\nas a second argument.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\nreturns a\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n, this method will wait for the promise to resolve and return its value.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\nthrows or rejects, this method throws.", "ElementHandle | Playwright\n\nextends:\nJSHandle (https://playwright.dev/docs/api/class-jshandle)\n\nElementHandle represents an in-page DOM element. ElementHandles can be created with the\npage.$() (https://playwright.dev/docs/api/class-page#page-query-selector)\nmethod.\n\nDiscouraged\nThe use of ElementHandle is discouraged, use\nLocator (https://playwright.dev/docs/api/class-locator)\nobjects and web-first assertions instead.\n\n```\n`consthrefElement=awaitpage.$('a');awaithrefElement.click();`\n```\n\nElementHandle prevents DOM element from garbage collection unless the handle is disposed with\njsHandle.dispose() (https://playwright.dev/docs/api/class-jshandle#js-handle-dispose)\n. ElementHandles are auto-disposed when their origin frame gets navigated.\n\nElementHandle instances can be used as an argument in\npage.$eval() (https://playwright.dev/docs/api/class-page#page-eval-on-selector)\nand\npage.evaluate() (https://playwright.dev/docs/api/class-page#page-evaluate)\nmethods.\n\nThe difference between the\nLocator (https://playwright.dev/docs/api/class-locator)\nand ElementHandle is that the ElementHandle points to a particular element, while\nLocator (https://playwright.dev/docs/api/class-locator)\ncaptures the logic of how to retrieve an element.\n\nIn the example below, handle points to a particular DOM element on page. If that element changes text or is used by React to render an entirely different component, handle is still pointing to that very DOM element. This can lead to unexpected behaviors.\n\n```\n`consthandle=awaitpage.$('text=Submit');// ...awaithandle.hover();awaithandle.click();`\n```\n\nWith the locator, every time the\n`element`\nis used, up-to-date DOM element is located in the page using the selector. So in the snippet below, underlying DOM element is going to be located twice.\n\n```\n`constlocator=page.getByText('Submit');// ...awaitlocator.hover();awaitlocator.click();`\n```", 'JSHandle | Playwright\n\nJSHandle represents an in-page JavaScript object. JSHandles can be created with the\npage.evaluateHandle() (https://playwright.dev/docs/api/class-page#page-evaluate-handle)\nmethod.\n\n```\n`constwindowHandle=awaitpage.evaluateHandle(()=&gt;window);// ...`\n```\n\nJSHandle prevents the referenced JavaScript object being garbage collected unless the handle is exposed with\njsHandle.dispose() (https://playwright.dev/docs/api/class-jshandle#js-handle-dispose)\n. JSHandles are auto-disposed when their origin frame gets navigated or the parent context gets destroyed.\n\nJSHandle instances can be used as an argument in\npage.$eval() (https://playwright.dev/docs/api/class-page#page-eval-on-selector)\n,\npage.evaluate() (https://playwright.dev/docs/api/class-page#page-evaluate)\nand\npage.evaluateHandle() (https://playwright.dev/docs/api/class-page#page-evaluate-handle)\nmethods.', 'Added in: v1.14\n\nlocator.evaluate\n\nExecute JavaScript code in the page, taking the matching element as an argument.\n\nUsage\n\nPassing argument to\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\n:\n\n```\n`constresult=awaitpage.getByTestId(\'myId\').evaluate((element,[x,y])=&gt;{returnelement.textContent+\' \'+x*y;},[7,8]);console.log(result);// prints "myId text 56"`\n```\n\nArguments\n\n`pageFunction`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\nFunction to be evaluated in the page context.\n`arg`\nEvaluationArgument (https://playwright.dev/docs/evaluating#evaluation-argument)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-arg)\nOptional argument to pass to\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\n.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-timeout)\nMaximum time in milliseconds to wait for the locator before evaluating. Note that after locator is resolved, evaluation itself is not limited by the timeout. Defaults to\n`0`\n- no timeout.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-return)\n\nDetails\n\nReturns the return value of\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\n, called with the matching element as a first argument, and\narg (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-arg)\nas a second argument.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\nreturns a\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n, this method will wait for the promise to resolve and return its value.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\nthrows or rejects, this method throws.', "Locator | Playwright\n\nLocators are the central piece of Playwright's auto-waiting and retry-ability. In a nutshell, locators represent a way to find element(s) on the page at any moment. A locator can be created with the\npage.locator() (https://playwright.dev/docs/api/class-page#page-locator)\nmethod.\n\nLearn more about locators (https://playwright.dev/docs/locators)\n."]</t>
+          <t>['Added in: v1.20\n\nlocatorAssertions.toHaveCSS\n\nEnsures the\nLocator (https://playwright.dev/docs/api/class-locator)\nresolves to an element with the given computed CSS style.\n\nUsage\n\n```\n`constlocator=page.getByRole(\'button\');awaitexpect(locator).toHaveCSS(\'display\',\'flex\');`\n```\n\nArguments\n\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-option-name)\nCSS property name.\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-option-value)\nCSS property value.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`pseudo`\n"before" | "after"\n(optional)\nAdded in: v1.60\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-option-pseudo)\nPseudo-element to read computed styles from.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-option-timeout)\nTime to retry the assertion for in milliseconds. Defaults to\n`timeout`\nin\n`TestConfig.expect`\n.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-return)', 'Evaluating JavaScript | Playwright', "Playwright scripts run in your Playwright environment. Your page scripts run in the browser page environment. Those environments don't intersect, they are running in different virtual machines in different processes and even potentially on different computers.\n\nThe\npage.evaluate() (https://playwright.dev/docs/api/class-page#page-evaluate)\nAPI can run a JavaScript function in the context of the web page and bring results back to the Playwright environment. Browser globals like\n`window`\nand\n`document`\ncan be used in\n`evaluate`\n.\n\n```\n`consthref=awaitpage.evaluate(()=&gt;document.location.href);`\n```\n\nIf the result is a Promise or if the function is asynchronous evaluate will automatically wait until it's resolved:\n\n```\n`conststatus=awaitpage.evaluate(async()=&gt;{constresponse=awaitfetch(location.href);returnresponse.status;});`\n```", 'The following assertions will retry until the assertion passes, or the assertion timeout is reached. Note that retrying assertions are async, so you must\n`await`\nthem.\n\nAssertion\nDescription\nawait expect(locator).toBeAttached() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-attached)\nElement is attached\nawait expect(locator).toBeChecked() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-checked)\nCheckbox is checked\nawait expect(locator).toBeDisabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-disabled)\nElement is disabled\nawait expect(locator).toBeEditable() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-editable)\nElement is editable\nawait expect(locator).toBeEmpty() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-empty)\nContainer is empty\nawait expect(locator).toBeEnabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-enabled)\nElement is enabled\nawait expect(locator).toBeFocused() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-focused)\nElement is focused\nawait expect(locator).toBeHidden() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-hidden)\nElement is not visible\nawait expect(locator).toBeInViewport() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-in-viewport)\nElement intersects viewport\nawait expect(locator).toBeVisible() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-visible)\nElement is visible\nawait expect(locator).toContainText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-text)\nElement contains text\nawait expect(locator).toContainClass() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-class)\nElement has specified CSS classes\nawait expect(locator).toHaveAccessibleDescription() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-accessible-description)\nElement has a matching\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\nawait expect(locator).toHaveAccessibleName() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-accessible-name)\nElement has a matching\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\nawait expect(locator).toHaveAttribute() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-attribute)\nElement has a DOM attribute\nawait expect(locator).toHaveClass() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-class)\nElement has specified CSS class property\nawait expect(locator).toHaveCount() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-count)\nList has exact number of children\nawait expect(locator).toHaveCSS() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css)\nElement has CSS property\nawait expect(locator).toHaveId() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-id)\nElement has an ID\nawait expect(locator).toHaveJSProperty() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-js-property)\nElement has a JavaScript property\nawait expect(locator).toHaveRole() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-role)\nElement has a specific\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\nawait expect(locator).toHaveScreenshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-screenshot-1)\nElement has a screenshot\nawait expect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nElement matches text\nawait expect(locator).toHaveValue() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value)\nInput has a value\nawait expect(locator).toHaveValues() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-values)\nSelect has options selected\nawait expect(locator).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-match-aria-snapshot)\nElement matches the Aria snapshot\nawait expect(page).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-match-aria-snapshot)\nPage matches the Aria snapshot\nawait expect(page).toHaveScreenshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\nPage has a screenshot\nawait expect(page).toHaveTitle() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-title)\nPage has a title\nawait expect(page).toHaveURL() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-url)\nPage has a URL\nawait expect(response).toBeOK() (https://playwright.dev/docs/api/class-apiresponseassertions#api-response-assertions-to-be-ok)\nResponse has an OK status', "You can convert any synchronous\n`expect`\nto an asynchronous polling one using\n`expect.poll`\n.\n\nThe following method will poll given function until it returns HTTP status 200:\n\n```\n`awaitexpect.poll(async()=&gt;{constresponse=awaitpage.request.get('https://api.example.com');returnresponse.status();},{// Custom expect message for reporting, optional.message:'make sure API eventually succeeds',// Poll for 10 seconds; defaults to 5 seconds. Pass 0 to disable timeout.timeout:10000,}).toBe(200);`\n```\n\nYou can also specify custom polling intervals:\n\n```\n`awaitexpect.poll(async()=&gt;{constresponse=awaitpage.request.get('https://api.example.com');returnresponse.status();},{// Probe, wait 1s, probe, wait 2s, probe, wait 10s, probe, wait 10s, probe// ... Defaults to [100, 250, 500, 1000].intervals:[1_000,2_000,10_000],timeout:60_000}).toBe(200);`\n```\n\nYou can combine\n`expect.soft`\nwith\n`expect.poll`\nto perform soft assertions in polling logic. This allows the test to continue even if the assertion inside poll fails.\n\n```\n`awaitexpect.soft.poll(async()=&gt;{constresponse=awaitpage.request.get('https://api.example.com');returnresponse.status();}).toBe(200);`\n```\n\n`expect.configure({ soft: true })`\nalso chains with\n`expect.poll`\nand is useful when you want to reuse a configured instance.\n\n```\n`constsoftExpect=expect.configure({soft:true});awaitsoftExpect.poll(async()=&gt;{constresponse=awaitpage.request.get('https://api.example.com');returnresponse.status();}).toBe(200);`\n```", 'Added in: v1.14\n\nlocator.evaluate\n\nExecute JavaScript code in the page, taking the matching element as an argument.\n\nUsage\n\nPassing argument to\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\n:\n\n```\n`constresult=awaitpage.getByTestId(\'myId\').evaluate((element,[x,y])=&gt;{returnelement.textContent+\' \'+x*y;},[7,8]);console.log(result);// prints "myId text 56"`\n```\n\nArguments\n\n`pageFunction`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\nFunction to be evaluated in the page context.\n`arg`\nEvaluationArgument (https://playwright.dev/docs/evaluating#evaluation-argument)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-arg)\nOptional argument to pass to\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\n.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-timeout)\nMaximum time in milliseconds to wait for the locator before evaluating. Note that after locator is resolved, evaluation itself is not limited by the timeout. Defaults to\n`0`\n- no timeout.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-return)\n\nDetails\n\nReturns the return value of\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\n, called with the matching element as a first argument, and\narg (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-arg)\nas a second argument.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\nreturns a\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n, this method will wait for the promise to resolve and return its value.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\nthrows or rejects, this method throws.', "Added in: v1.14\n\nlocator.evaluateAll\n\nExecute JavaScript code in the page, taking all matching elements as an argument.\n\nUsage\n\n```\n`constlocator=page.locator('div');constmoreThanTen=awaitlocator.evaluateAll((divs,min)=&gt;divs.length&gt;min,10);`\n```\n\nArguments\n\n`pageFunction`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\nFunction to be evaluated in the page context.\n`arg`\nEvaluationArgument (https://playwright.dev/docs/evaluating#evaluation-argument)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-arg)\nOptional argument to pass to\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\n.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-return)\n\nDetails\n\nReturns the return value of\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\n, called with an array of all matching elements as a first argument, and\narg (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-arg)\nas a second argument.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\nreturns a\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n, this method will wait for the promise to resolve and return its value.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\nthrows or rejects, this method throws."]</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>['The code inside locator.evaluateAll() (https://playwright.dev/docs/api/class-locator#locator-evaluate-all) runs in the page, you can call any DOM apis there.', 'The page.evaluate() (https://playwright.dev/docs/api/class-page#page-evaluate) API can run a JavaScript function in the context of the web page and bring results back to the Playwright environment. Browser globals like window and document can be used in evaluate .']</t>
+          <t>['The code inside locator.evaluateAll() runs in the page, you can call any DOM apis there.', "const rows = page.getByRole('listitem'); const texts = await rows.evaluateAll( list =&gt; list.map(element =&gt; element.textContent));", 'Evaluated scripts run in the browser environment, while your test runs in a testing environments. This means you cannot use variables from your test in the page and vice versa. Instead, you should pass them explicitly as an argument.']</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>To run DOM code against every element a locator matches and pull values back into your test, you should use the `locator.evaluateAll` method.
-This method executes JavaScript code in the page, passing an array of all matching elements as the first argument to your function. It returns the return value of that function to your test.
-**Example:**
+          <t>To assert that every row in your pricing table renders with a specific computed CSS style, you should use `locator.evaluateAll`. This method allows you to execute JavaScript in the page context, receiving an array of all matching elements as an argument, which is necessary to verify the computed style across multiple rows.
+### Recommended Approach
+Use `locator.evaluateAll` to iterate through the elements and check their computed styles using `window.getComputedStyle(element)`.
 ```javascript
-const locator = page.locator('div');
-const moreThanTen = await locator.evaluateAll((divs, min) =&gt; divs.length &gt; min, 10);
+const rows = page.locator('.pricing-row');
+const isRightAligned = await rows.evaluateAll((elements) =&gt; {
+  return elements.every(el =&gt; window.getComputedStyle(el).textAlign === 'right');
+});
+expect(isRightAligned).toBe(true);
 ```
-In this example, `divs` is the array of all matching elements, and `10` is passed as the optional `arg` to the function.</t>
+### Why this approach?
+*   **Computed Styles:** Since the style is computed and not in the DOM, `evaluateAll` allows you to run `window.getComputedStyle` directly in the browser environment where the styles are calculated.
+*   **Environment Separation:** As noted in the documentation, Playwright scripts and page scripts run in different environments. `evaluateAll` bridges this gap by passing the elements into the page context.
+*   **Handling Multiple Rows:** `evaluateAll` is specifically designed to take all matching elements as an argument, enabling you to perform a collective check on the entire table.
+### Alternative
+If you prefer to use an auto-retrying assertion, you can combine `expect.poll` with `evaluateAll`:
+```javascript
+await expect.poll(async () =&gt; {
+  return await rows.evaluateAll((elements) =&gt; 
+    elements.every(el =&gt; window.getComputedStyle(el).textAlign === 'right')
+  );
+}).toBe(true);
+```
+The `toHaveCSS` assertion mentioned in the documentation is intended for checking a single locator's CSS property, but it does not support verifying a condition across a collection of elements simultaneously.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Use locator.evaluateAll(): its callback runs in the page across the matched elements, and you return serializable data back to the test side. Remember the page and test run in separate environments, so anything else must be passed in as an argument.</t>
+          <t>Two boundaries are in play. First, to get at computed style you have to run code in the page: a locator resolves to elements but only exposes what the API models, so anything the API doesn't cover you obtain with evaluate. For the whole set at once use locator.evaluateAll(), whose callback receives the array of matching elements — e.g. `await page.locator('td.price').evaluateAll(els =&gt; els.map(e =&gt; getComputedStyle(e).textAlign))` — returning an ordinary array back into the test. Second, that callback executes in the browser, in a different context from your test file, so it cannot close over test variables; that's why your threshold was undefined rather than throwing at definition. Pass it explicitly as the second argument: `locator.evaluateAll((els, limit) =&gt; ..., limit)`. Whatever you return has to be serializable to cross back — return the strings or numbers you want to assert on, not DOM nodes.</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0.01459775</v>
       </c>
       <c r="G47" t="n">
-        <v>0.57</v>
+        <v>54051</v>
       </c>
       <c r="H47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.154639175257732</v>
+        <v>0.62</v>
       </c>
       <c r="J47" t="n">
-        <v>0.3571428571428572</v>
+        <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>0.99999999995</v>
+        <v>0.1468253968253968</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0.2450331125827815</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.5595238095098214</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="48">
@@ -2991,7 +3490,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>['Projects | Playwright', "TestProject | Playwright\n\nPlaywright Test supports running multiple test projects at the same time. This is useful for running tests in multiple configurations. For example, consider running tests against multiple browsers. This type describes format of a project in the configuration file, to access resolved configuration parameters at run time use\nFullProject (https://playwright.dev/docs/api/class-fullproject)\n.\n\n`TestProject`\nencapsulates configuration specific to a single project. Projects are configured in\ntestConfig.projects (https://playwright.dev/docs/api/class-testconfig#test-config-projects)\nspecified in the\nconfiguration file (https://playwright.dev/docs/test-configuration)\n. Note that all properties of\nTestProject (https://playwright.dev/docs/api/class-testproject)\nare available in the top-level\nTestConfig (https://playwright.dev/docs/api/class-testconfig)\n, in which case they are shared between all projects.\n\nHere is an example configuration that runs every test in Chromium, Firefox and WebKit, both Desktop and Mobile versions.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({// Options shared for all projects.timeout:30000,use:{ignoreHTTPSErrors:true,},// Options specific to each project.projects:[{name:'chromium',use:devices['Desktop Chrome'],},{name:'firefox',use:devices['Desktop Firefox'],},{name:'webkit',use:devices['Desktop Safari'],},{name:'Mobile Chrome',use:devices['Pixel 5'],},{name:'Mobile Safari',use:devices['iPhone 12'],},],});`\n```", "By using\nprojects\nyou can run your tests in multiple browsers such as chromium, webkit and firefox as well as branded browsers such as Google Chrome and Microsoft Edge. Playwright can also run on emulated tablet and mobile devices. See the\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nfor a complete list of selected desktop, tablet and mobile devices.\n\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[{name:'chromium',use:{...devices['Desktop Chrome']},},{name:'firefox',use:{...devices['Desktop Firefox']},},{name:'webkit',use:{...devices['Desktop Safari']},},/* Test against mobile viewports. */{name:'Mobile Chrome',use:{...devices['Pixel 5']},},{name:'Mobile Safari',use:{...devices['iPhone 12']},},/* Test against branded browsers. */{name:'Microsoft Edge',use:{...devices['Desktop Edge'],channel:'msedge'},},{name:'Google Chrome',use:{...devices['Desktop Chrome'],channel:'chrome'},},],});`\n```", 'Emulation | Playwright', 'Playwright comes with a\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nusing\nplaywright.devices (https://playwright.dev/docs/api/class-playwright#playwright-devices)\nfor selected desktop, tablet and mobile devices. It can be used to simulate browser behavior for a specific device such as user agent, screen size, viewport and if it has touch enabled. All tests will run with the specified device parameters.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig,devices}from\'@playwright/test\';// import devicesexportdefaultdefineConfig({projects:[{name:\'chromium\',use:{...devices[\'Desktop Chrome\'],},},{name:\'Mobile Safari\',use:{...devices[\'iPhone 13\'],},},],});`\n```\n```\n`const{chromium,devices}=require(\'playwright\');constbrowser=awaitchromium.launch();constiphone13=devices[\'iPhone 13\'];constcontext=awaitbrowser.newContext({...iphone13,});`\n```\n\nNote\n: Pre-configured devices assume a specific platform. For example, "Desktop Chrome" will provide a Windows-specific user agent string.\n\nIf you would like to use the user agent specific to the platform that is running the tests, we recommend unsetting the user agent property.\n\n```\n`constcontext=awaitbrowser.newContext({...devices[\'Desktop Chrome\'],userAgent:undefined,});`\n```', 'Configuration (use) | Playwright', "TestOptions | Playwright\n\nPlaywright Test provides many options to configure test environment,\nBrowser (https://playwright.dev/docs/api/class-browser)\n,\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nand more.\n\nThese options are usually provided in the\nconfiguration file (https://playwright.dev/docs/test-configuration)\nthrough\ntestConfig.use (https://playwright.dev/docs/api/class-testconfig#test-config-use)\nand\ntestProject.use (https://playwright.dev/docs/api/class-testproject#test-project-use)\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{headless:false,viewport:{width:1280,height:720},ignoreHTTPSErrors:true,video:'on-first-retry',},});`\n```\n\nAlternatively, with\ntest.use() (https://playwright.dev/docs/api/class-test#test-use)\nyou can override some options for a file.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';// Run tests in this file with portrait-like viewport.test.use({viewport:{width:600,height:900}});test('my portrait test',async({page})=&gt;{// ...});`\n```"]</t>
+          <t>['Projects | Playwright', "By using\nprojects\nyou can run your tests in multiple browsers such as chromium, webkit and firefox as well as branded browsers such as Google Chrome and Microsoft Edge. Playwright can also run on emulated tablet and mobile devices. See the\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nfor a complete list of selected desktop, tablet and mobile devices.\n\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[{name:'chromium',use:{...devices['Desktop Chrome']},},{name:'firefox',use:{...devices['Desktop Firefox']},},{name:'webkit',use:{...devices['Desktop Safari']},},/* Test against mobile viewports. */{name:'Mobile Chrome',use:{...devices['Pixel 5']},},{name:'Mobile Safari',use:{...devices['iPhone 12']},},/* Test against branded browsers. */{name:'Microsoft Edge',use:{...devices['Desktop Edge'],channel:'msedge'},},{name:'Google Chrome',use:{...devices['Desktop Chrome'],channel:'chrome'},},],});`\n```", 'Emulation | Playwright', 'Playwright comes with a\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nusing\nplaywright.devices (https://playwright.dev/docs/api/class-playwright#playwright-devices)\nfor selected desktop, tablet and mobile devices. It can be used to simulate browser behavior for a specific device such as user agent, screen size, viewport and if it has touch enabled. All tests will run with the specified device parameters.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig,devices}from\'@playwright/test\';// import devicesexportdefaultdefineConfig({projects:[{name:\'chromium\',use:{...devices[\'Desktop Chrome\'],},},{name:\'Mobile Safari\',use:{...devices[\'iPhone 13\'],},},],});`\n```\n```\n`const{chromium,devices}=require(\'playwright\');constbrowser=awaitchromium.launch();constiphone13=devices[\'iPhone 13\'];constcontext=awaitbrowser.newContext({...iphone13,});`\n```\n\nNote\n: Pre-configured devices assume a specific platform. For example, "Desktop Chrome" will provide a Windows-specific user agent string.\n\nIf you would like to use the user agent specific to the platform that is running the tests, we recommend unsetting the user agent property.\n\n```\n`constcontext=awaitbrowser.newContext({...devices[\'Desktop Chrome\'],userAgent:undefined,});`\n```', 'Configuration (use) | Playwright', 'A project is logical group of tests running with the same configuration. We use projects so we can run tests on different browsers and devices. Projects are configured in the\n`playwright.config.ts`\nfile and once configured you can then run your tests on all projects or only on a specific project. You can also use projects to run the same tests in different configurations. For example, you can run the same tests in a logged-in and logged-out state.\n\nBy setting up projects you can also run a group of tests with different timeouts or retries or a group of tests against different environments such as staging and production, splitting tests per package/functionality and more.', 'With Playwright you can test your app on any browser as well as emulate a real device such as a mobile phone or tablet. Simply configure the devices you would like to emulate and Playwright will simulate the browser behavior such as\n`"userAgent"`\n,\n`"screenSize"`\n,\n`"viewport"`\nand if it\n`"hasTouch"`\nenabled. You can also emulate the\n`"geolocation"`\n,\n`"locale"`\nand\n`"timezone"`\nfor all tests or for a specific test as well as set the\n`"permissions"`\nto show notifications or change the\n`"colorScheme"`\n.']</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3001,10 +3500,10 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>To run the same suite across desktop and mobile devices with the correct emulation, you should use the `projects` configuration in your `playwright.config.ts` file. 
-You can define multiple projects, each using specific device parameters from the `devices` registry provided by Playwright. By assigning these device descriptors to the `use` property of each project, Playwright will apply the appropriate user agent, screen size, viewport, and touch settings for that device.
-Example configuration:
-```typescript
+          <t>To run the same suite across desktop and mobile devices with the correct emulation, you should use **projects** configured in your `playwright.config.ts` file. Projects allow you to run the same tests in different configurations, such as across multiple browsers and emulated devices.
+### Implementation
+In your `playwright.config.ts`, import `devices` and define your projects within the `defineConfig` object. Use the spread operator (`...devices['Device Name']`) to apply the specific emulation parameters (such as user agent, screen size, viewport, and touch support) to each project:
+```javascript
 import { defineConfig, devices } from '@playwright/test';
 export default defineConfig({
   projects: [
@@ -3016,10 +3515,21 @@
       name: 'Mobile Safari',
       use: { ...devices['iPhone 12'] },
     },
+    // Add additional projects as needed
   ],
 });
 ```
-This setup allows Playwright Test to run your tests in multiple configurations simultaneously.</t>
+### Key Details
+*   **Device Registry:** Playwright provides a registry of device parameters for selected desktop, tablet, and mobile devices. You can reference these by name using `devices['Device Name']`.
+*   **Emulation Behavior:** When a device is configured, Playwright automatically simulates the browser behavior, including `userAgent`, `screenSize`, `viewport`, and `hasTouch`.
+*   **Platform-Specific User Agents:** Pre-configured devices assume a specific platform (e.g., "Desktop Chrome" provides a Windows-specific user agent). If you want to use the user agent of the platform currently running the tests, you should unset the property:
+    ```javascript
+    use: { 
+      ...devices['Desktop Chrome'], 
+      userAgent: undefined 
+    }
+    ```
+*   **Execution:** Once configured, you can run your tests across all projects or target a specific project as required.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3028,24 +3538,30 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0.008865749999999001</v>
       </c>
       <c r="G48" t="n">
-        <v>0.57</v>
+        <v>32088</v>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0990990990990991</v>
+        <v>0.43</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2972972972972973</v>
+        <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>0.5888888888692593</v>
+        <v>0.06986899563318777</v>
       </c>
       <c r="L48" t="n">
+        <v>0.4324324324324325</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.499999999975</v>
+      </c>
+      <c r="N48" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3057,7 +3573,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>['Fixtures | Playwright', 'Playwright Test supports running multiple test projects that can be configured separately. You can use "option" fixtures to make your configuration options declarative and type safe. Learn more about\nparameterizing tests (https://playwright.dev/docs/test-parameterize)\n.\n\nBelow we\'ll create a\n`defaultItem`\noption in addition to the\n`todoPage`\nfixture from other examples. This option will be set in the configuration file. Note the tuple syntax and\n`{ option: true }`\nargument.\n\nClick to expand the code for the\n`TodoPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\n\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';// Declare your options to type-check your configuration.exporttypeMyOptions={defaultItem:string;};typeMyFixtures={todoPage:TodoPage;};// Specify both option and fixture types.exportconsttest=base.extend&lt;MyOptions&amp;MyFixtures&gt;({// Define an option and provide a default value.// We can later override it in the config.defaultItem:[\'Something nice\',{option:true}],// Our "todoPage" fixture depends on the option.todoPage:async({page,defaultItem},use)=&gt;{consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(defaultItem);awaituse(todoPage);awaittodoPage.removeAll();},});export{expect}from\'@playwright/test\';`\n```\n\nWe can now use the\n`todoPage`\nfixture as usual, and set the\n`defaultItem`\noption in the configuration file.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{MyOptions}from\'./my-test\';exportdefaultdefineConfig&lt;MyOptions&gt;({projects:[{name:\'shopping\',use:{defaultItem:\'Buy milk\'},},{name:\'wellbeing\',use:{defaultItem:\'Exercise!\'},},]});`\n```\n\nArray as an option value\n\nIf the value of your option is an array, for example\n`[{ name: \'Alice\' }, { name: \'Bob\' }]`\n, you\'ll need to wrap it into an extra array when providing the value. This is best illustrated with an example.\n\n```\n`typePerson={name:string};consttest=base.extend&lt;{persons:Person[]}&gt;({// Declare the option, default value is an empty array.persons:[[],{option:true}],});// Option value is an array of persons.constactualPersons=[{name:\'Alice\'},{name:\'Bob\'}];test.use({// CORRECT: Wrap the value into an array and pass the scope.persons:[actualPersons,{scope:\'test\'}],});test.use({// WRONG: passing an array value directly will not work.persons:actualPersons,});`\n```\n\nReset an option\n\nYou can reset an option to the value defined in the config file by setting it to\n`undefined`\n. Consider the following config that sets a\n`baseURL`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{baseURL:\'https://playwright.dev\',},});`\n```\n\nYou can now configure\n`baseURL`\nfor a file, and also opt-out for a single test.\n\nintro.spec.ts\n```\n`import{test}from\'@playwright/test\';// Configure baseURL for this file.test.use({baseURL:\'https://playwright.dev/docs/intro\'});test(\'check intro contents\',async({page})=&gt;{// This test will use "https://playwright.dev/docs/intro" base url as defined above.});test.describe(()=&gt;{// Reset the value to a config-defined one.test.use({baseURL:undefined});test(\'can navigate to intro from the home page\',async({page})=&gt;{// This test will use "https://playwright.dev" base url as defined in the config.});});`\n```\n\nIf you would like to completely reset the value to\n`undefined`\n, use a long-form fixture notation.\n\nintro.spec.ts\n```\n`import{test}from\'@playwright/test\';// Completely unset baseURL for this file.test.use({baseURL:[async({},use)=&gt;use(undefined),{scope:\'test\'}],});test(\'no base url\',async({page})=&gt;{// This test will not have a base url.});`\n```', 'Parameterize tests | Playwright', 'Playwright Test supports running multiple test projects at the same time. In the following example, we\'ll run two projects with different options.\n\nWe declare the option\n`person`\nand set the value in the config. The first project runs with the value\n`Alice`\nand the second with the value\n`Bob`\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\n\nWe can use this option in the test, similarly to\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nexample.spec.ts\n```\n`import{test}from\'./my-test\';test(\'test 1\',async({page,person})=&gt;{awaitpage.goto(`/index.html`);awaitexpect(page.locator(\'#node\')).toContainText(person);// ...});`\n```\n\nNow, we can run tests in multiple configurations by using projects.\n\nTypeScript\nJavaScript\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{TestOptions}from\'./my-test\';exportdefaultdefineConfig&lt;TestOptions&gt;({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\nplaywright.config.ts\n```\n`// @ts-checkmodule.exports=defineConfig({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\n\nWe can also use the option in a fixture. Learn more about\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\n\nnote\nParameterized projects behavior has changed in version 1.18.\nLearn more (https://playwright.dev/docs/release-notes#breaking-change-custom-config-options)\n.']</t>
+          <t>['Fixtures | Playwright', 'Playwright Test supports running multiple test projects that can be configured separately. You can use "option" fixtures to make your configuration options declarative and type safe. Learn more about\nparameterizing tests (https://playwright.dev/docs/test-parameterize)\n.\n\nBelow we\'ll create a\n`defaultItem`\noption in addition to the\n`todoPage`\nfixture from other examples. This option will be set in the configuration file. Note the tuple syntax and\n`{ option: true }`\nargument.\n\nClick to expand the code for the\n`TodoPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\n\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';// Declare your options to type-check your configuration.exporttypeMyOptions={defaultItem:string;};typeMyFixtures={todoPage:TodoPage;};// Specify both option and fixture types.exportconsttest=base.extend&lt;MyOptions&amp;MyFixtures&gt;({// Define an option and provide a default value.// We can later override it in the config.defaultItem:[\'Something nice\',{option:true}],// Our "todoPage" fixture depends on the option.todoPage:async({page,defaultItem},use)=&gt;{consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(defaultItem);awaituse(todoPage);awaittodoPage.removeAll();},});export{expect}from\'@playwright/test\';`\n```\n\nWe can now use the\n`todoPage`\nfixture as usual, and set the\n`defaultItem`\noption in the configuration file.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{MyOptions}from\'./my-test\';exportdefaultdefineConfig&lt;MyOptions&gt;({projects:[{name:\'shopping\',use:{defaultItem:\'Buy milk\'},},{name:\'wellbeing\',use:{defaultItem:\'Exercise!\'},},]});`\n```\n\nArray as an option value\n\nIf the value of your option is an array, for example\n`[{ name: \'Alice\' }, { name: \'Bob\' }]`\n, you\'ll need to wrap it into an extra array when providing the value. This is best illustrated with an example.\n\n```\n`typePerson={name:string};consttest=base.extend&lt;{persons:Person[]}&gt;({// Declare the option, default value is an empty array.persons:[[],{option:true}],});// Option value is an array of persons.constactualPersons=[{name:\'Alice\'},{name:\'Bob\'}];test.use({// CORRECT: Wrap the value into an array and pass the scope.persons:[actualPersons,{scope:\'test\'}],});test.use({// WRONG: passing an array value directly will not work.persons:actualPersons,});`\n```\n\nReset an option\n\nYou can reset an option to the value defined in the config file by setting it to\n`undefined`\n. Consider the following config that sets a\n`baseURL`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{baseURL:\'https://playwright.dev\',},});`\n```\n\nYou can now configure\n`baseURL`\nfor a file, and also opt-out for a single test.\n\nintro.spec.ts\n```\n`import{test}from\'@playwright/test\';// Configure baseURL for this file.test.use({baseURL:\'https://playwright.dev/docs/intro\'});test(\'check intro contents\',async({page})=&gt;{// This test will use "https://playwright.dev/docs/intro" base url as defined above.});test.describe(()=&gt;{// Reset the value to a config-defined one.test.use({baseURL:undefined});test(\'can navigate to intro from the home page\',async({page})=&gt;{// This test will use "https://playwright.dev" base url as defined in the config.});});`\n```\n\nIf you would like to completely reset the value to\n`undefined`\n, use a long-form fixture notation.\n\nintro.spec.ts\n```\n`import{test}from\'@playwright/test\';// Completely unset baseURL for this file.test.use({baseURL:[async({},use)=&gt;use(undefined),{scope:\'test\'}],});test(\'no base url\',async({page})=&gt;{// This test will not have a base url.});`\n```', 'Parameterize tests | Playwright', 'Playwright Test supports running multiple test projects at the same time. In the following example, we\'ll run two projects with different options.\n\nWe declare the option\n`person`\nand set the value in the config. The first project runs with the value\n`Alice`\nand the second with the value\n`Bob`\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\n\nWe can use this option in the test, similarly to\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nexample.spec.ts\n```\n`import{test}from\'./my-test\';test(\'test 1\',async({page,person})=&gt;{awaitpage.goto(`/index.html`);awaitexpect(page.locator(\'#node\')).toContainText(person);// ...});`\n```\n\nNow, we can run tests in multiple configurations by using projects.\n\nTypeScript\nJavaScript\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{TestOptions}from\'./my-test\';exportdefaultdefineConfig&lt;TestOptions&gt;({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\nplaywright.config.ts\n```\n`// @ts-checkmodule.exports=defineConfig({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\n\nWe can also use the option in a fixture. Learn more about\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\n\nnote\nParameterized projects behavior has changed in version 1.18.\nLearn more (https://playwright.dev/docs/release-notes#breaking-change-custom-config-options)\n.', 'Projects | Playwright', 'Projects can be also used to parametrize tests with your custom configuration - take a look at\nthis separate guide (https://playwright.dev/docs/test-parameterize#parameterized-projects)\n.']</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3067,151 +3583,199 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>To make a fixture behave differently per project using options, you can follow these steps based on the provided documentation:
-1.  **Define the option:** In your test file, extend the base test and define your option using the tuple syntax with `{ option: true }`.
+          <t>To make a fixture behave differently per project, you use "option" fixtures. These allow you to define configuration options that are declarative and type-safe, which can then be overridden in your `playwright.config.ts` file for different projects.
+### How to implement this:
+1.  **Define the option:** In your test file, extend the base test to define your option. You must provide a default value and include the `{ option: true }` argument in a tuple.
     ```typescript
-    export const test = base.extend&lt;MyOptions&gt;({
-      defaultItem: ['Default Value', { option: true }],
-      // ...
+    export type MyOptions = {
+      defaultItem: string;
+    };
+    export const test = base.extend&lt;MyOptions &amp; MyFixtures&gt;({
+      // Define the option with a default value
+      defaultItem: ['Something nice', { option: true }],
+      // Use the option in your fixture
+      todoPage: async ({ page, defaultItem }, use) =&gt; {
+        const todoPage = new TodoPage(page);
+        await todoPage.goto();
+        await todoPage.addToDo(defaultItem);
+        await use(todoPage);
+      },
     });
     ```
-2.  **Use the option in your fixture:** Define your fixture to depend on that option. The fixture will automatically receive the value currently configured for the project.
+2.  **Configure per project:** In your `playwright.config.ts`, set the value of that option within the `use` property of each project.
     ```typescript
-    todoPage: async ({ page, defaultItem }, use) =&gt; {
-      const todoPage = new TodoPage(page);
-      await todoPage.addToDo(defaultItem); // Uses the project-specific value
-      await use(todoPage);
+    export default defineConfig&lt;MyOptions&gt;({
+      projects: [
+        {
+          name: 'shopping',
+          use: { defaultItem: 'Buy milk' },
+        },
+        {
+          name: 'wellbeing',
+          use: { defaultItem: 'Exercise!' },
+        },
+      ]
+    });
+    ```
+When you run your tests, Playwright will use the specific `defaultItem` value defined for each project, and your `todoPage` fixture will automatically receive that value.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Declare an 'option' fixture with a default value, then override that value per project in the config's use block. The fixture reads the option, so each project drives its own behavior in a type-safe way.</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0.009072499999999002</v>
+      </c>
+      <c r="G49" t="n">
+        <v>33790</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J49" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.499999999975</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>How do I tag tests to run just those from the CLI, and also carve tests into subsets at the project level?</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>['Sometimes you want to tag your tests as\n`@fast`\nor\n`@slow`\n, and then filter by tag in the test report. Or you might want to only run tests that have a certain tag.\n\nTo tag a test, either provide an additional details object when declaring a test, or add\n`@`\n-token to the test title. Note that tags must start with\n`@`\nsymbol.\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'test login page\',{tag:\'@fast\',},async({page})=&gt;{// ...});test(\'test full report @slow\',async({page})=&gt;{// ...});`\n```\n\nYou can also tag all tests in a group or provide multiple tags:\n\n```\n`import{test,expect}from\'@playwright/test\';test.describe(\'group\',{tag:\'@report\',},()=&gt;{test(\'test report header\',async({page})=&gt;{// ...});test(\'test full report\',{tag:[\'@slow\',\'@vrt\'],},async({page})=&gt;{// ...});});`\n```\n\nYou can now run tests that have a particular tag with\n--grep (https://playwright.dev/docs/test-cli#all-options)\ncommand line option.\n\nBash\nPowerShell\nBatch\n```\n`npx playwrighttest--grep@fast`\n```\n```\n`npx playwright test--grep"@fast"`\n```\n```\n`npxplaywright test--grep@fast`\n```\n\nOr if you want the opposite, you can skip the tests with a certain tag:\n\nBash\nPowerShell\nBatch\n```\n`npx playwrighttest--grep-invert @fast`\n```\n```\n`npx playwright test--grep-invert"@fast"`\n```\n```\n`npxplaywright test--grep-invert@fast`\n```\n\nTo run tests containing either tag (logical\n`OR`\noperator):\n\nBash\nPowerShell\nBatch\n```\n`npx playwrighttest--grep"@fast|@slow"`\n```\n```\n`npx playwright test--grep--%"@fast^|@slow"`\n```\n```\n`npxplaywright test--grep"@fast^|@slow"`\n```\n\nOr run tests containing both tags (logical\n`AND`\noperator) using regex lookaheads:\n\n```\n`npx playwrighttest--grep"(?=.*@fast)(?=.*@slow)"`\n```\n\nYou can also filter tests in the configuration file via\ntestConfig.grep (https://playwright.dev/docs/api/class-testconfig#test-config-grep)\nand\ntestProject.grep (https://playwright.dev/docs/api/class-testproject#test-project-grep)\n.', 'We can split tests into projects and use filters to run a subset of tests. For example, we can create a project that runs tests using a filter matching all tests with a specific file name. We can then have another group of tests that ignore specific test files.\n\nHere is an example that defines a common timeout and two projects. The "Smoke" project runs a small subset of tests without retries, and "Default" project runs all other tests with retries.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({timeout:60000,// Timeout is shared between all tests.projects:[{name:\'Smoke\',testMatch:/.*smoke.spec.ts/,retries:0,},{name:\'Default\',testIgnore:/.*smoke.spec.ts/,retries:2,},],});`\n```', 'Annotations | Playwright', 'Projects | Playwright', 'Command line | Playwright\n\nPlaywright provides a powerful command line interface for running tests, generating code, debugging, and more. The most up to date list of commands and arguments available on the CLI can always be retrieved via\n`npx playwright --help`\n.']</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>['You can now run tests that have a particular tag with --grep (https://playwright.dev/docs/test-cli#all-options) command line option.', 'We can split tests into projects and use filters to run a subset of tests. For example, we can create a project that runs tests using a filter matching all tests with a specific file name. We can then have another group of tests that ignore specific test files.']</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>To tag tests, add the `@` symbol to the test title or provide a `tag` property in the test details object:
+```javascript
+// Via title
+test('test title @fast', async ({ page }) =&gt; { ... });
+// Via details object
+test('test title', { tag: '@fast' }, async ({ page }) =&gt; { ... });
+```
+To run only tests with a specific tag from the CLI, use the `--grep` command:
+`npx playwright test --grep @fast`
+To carve tests into subsets at the project level, define projects in your `playwright.config.ts` file using `testMatch` or `testIgnore` to filter by file patterns:
+```javascript
+export default defineConfig({
+  projects: [
+    {
+      name: 'Smoke',
+      testMatch: /.*smoke.spec.ts/,
     },
+    {
+      name: 'Default',
+      testIgnore: /.*smoke.spec.ts/,
+    },
+  ],
+});
+```</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Label tests with @-tokens and select them at runtime via --grep. For a more structural cut, group tests into separate projects and let each project's own filter — say a testMatch on the file name — decide what it runs.</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0.00813675</v>
+      </c>
+      <c r="G50" t="n">
+        <v>30947</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.09803921568627451</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>I want to parameterize the same tests with different values — both at the test level and across environments. How do these two levels differ?</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>['Parameterize tests | Playwright', 'You can either parameterize tests on a test level or on a project level.', 'Playwright Test supports running multiple test projects at the same time. In the following example, we\'ll run two projects with different options.\n\nWe declare the option\n`person`\nand set the value in the config. The first project runs with the value\n`Alice`\nand the second with the value\n`Bob`\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\n\nWe can use this option in the test, similarly to\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nexample.spec.ts\n```\n`import{test}from\'./my-test\';test(\'test 1\',async({page,person})=&gt;{awaitpage.goto(`/index.html`);awaitexpect(page.locator(\'#node\')).toContainText(person);// ...});`\n```\n\nNow, we can run tests in multiple configurations by using projects.\n\nTypeScript\nJavaScript\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{TestOptions}from\'./my-test\';exportdefaultdefineConfig&lt;TestOptions&gt;({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\nplaywright.config.ts\n```\n`// @ts-checkmodule.exports=defineConfig({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\n\nWe can also use the option in a fixture. Learn more about\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\n\nnote\nParameterized projects behavior has changed in version 1.18.\nLearn more (https://playwright.dev/docs/release-notes#breaking-change-custom-config-options)\n.', "example.spec.ts\n```\n`[{name:'Alice',expected:'Hello, Alice!'},{name:'Bob',expected:'Hello, Bob!'},{name:'Charlie',expected:'Hello, Charlie!'},].forEach(({name,expected})=&gt;{// You can also do it with test.describe() or with multiple tests as long the test name is unique.test(`testing with${name}`,async({page})=&gt;{awaitpage.goto(`https://example.com/greet?name=${name}`);awaitexpect(page.getByRole('heading')).toHaveText(expected);});});`\n```", 'Playwright Test supports running multiple test projects that can be configured separately. You can use "option" fixtures to make your configuration options declarative and type safe. Learn more about\nparameterizing tests (https://playwright.dev/docs/test-parameterize)\n.\n\nBelow we\'ll create a\n`defaultItem`\noption in addition to the\n`todoPage`\nfixture from other examples. This option will be set in the configuration file. Note the tuple syntax and\n`{ option: true }`\nargument.\n\nClick to expand the code for the\n`TodoPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\n\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';// Declare your options to type-check your configuration.exporttypeMyOptions={defaultItem:string;};typeMyFixtures={todoPage:TodoPage;};// Specify both option and fixture types.exportconsttest=base.extend&lt;MyOptions&amp;MyFixtures&gt;({// Define an option and provide a default value.// We can later override it in the config.defaultItem:[\'Something nice\',{option:true}],// Our "todoPage" fixture depends on the option.todoPage:async({page,defaultItem},use)=&gt;{consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(defaultItem);awaituse(todoPage);awaittodoPage.removeAll();},});export{expect}from\'@playwright/test\';`\n```\n\nWe can now use the\n`todoPage`\nfixture as usual, and set the\n`defaultItem`\noption in the configuration file.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{MyOptions}from\'./my-test\';exportdefaultdefineConfig&lt;MyOptions&gt;({projects:[{name:\'shopping\',use:{defaultItem:\'Buy milk\'},},{name:\'wellbeing\',use:{defaultItem:\'Exercise!\'},},]});`\n```\n\nArray as an option value\n\nIf the value of your option is an array, for example\n`[{ name: \'Alice\' }, { name: \'Bob\' }]`\n, you\'ll need to wrap it into an extra array when providing the value. This is best illustrated with an example.\n\n```\n`typePerson={name:string};consttest=base.extend&lt;{persons:Person[]}&gt;({// Declare the option, default value is an empty array.persons:[[],{option:true}],});// Option value is an array of persons.constactualPersons=[{name:\'Alice\'},{name:\'Bob\'}];test.use({// CORRECT: Wrap the value into an array and pass the scope.persons:[actualPersons,{scope:\'test\'}],});test.use({// WRONG: passing an array value directly will not work.persons:actualPersons,});`\n```\n\nReset an option\n\nYou can reset an option to the value defined in the config file by setting it to\n`undefined`\n. Consider the following config that sets a\n`baseURL`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{baseURL:\'https://playwright.dev\',},});`\n```\n\nYou can now configure\n`baseURL`\nfor a file, and also opt-out for a single test.\n\nintro.spec.ts\n```\n`import{test}from\'@playwright/test\';// Configure baseURL for this file.test.use({baseURL:\'https://playwright.dev/docs/intro\'});test(\'check intro contents\',async({page})=&gt;{// This test will use "https://playwright.dev/docs/intro" base url as defined above.});test.describe(()=&gt;{// Reset the value to a config-defined one.test.use({baseURL:undefined});test(\'can navigate to intro from the home page\',async({page})=&gt;{// This test will use "https://playwright.dev" base url as defined in the config.});});`\n```\n\nIf you would like to completely reset the value to\n`undefined`\n, use a long-form fixture notation.\n\nintro.spec.ts\n```\n`import{test}from\'@playwright/test\';// Completely unset baseURL for this file.test.use({baseURL:[async({},use)=&gt;use(undefined),{scope:\'test\'}],});test(\'no base url\',async({page})=&gt;{// This test will not have a base url.});`\n```', "By setting up projects we can also run a group of tests with different timeouts or retries or run a group of tests against different environments. For example we can run our tests against a staging environment with 2 retries as well as against a production environment with 0 retries.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({timeout:60000,// Timeout is shared between all tests.projects:[{name:'staging',use:{baseURL:'staging.example.com',},retries:2,},{name:'production',use:{baseURL:'production.example.com',},retries:0,},],});`\n```"]</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>['You can either parameterize tests on a test level or on a project level.', 'Playwright Test supports running multiple test projects that can be configured separately. You can use "option" fixtures to make your configuration options declarative and type safe. Learn more about parameterizing tests (https://playwright.dev/docs/test-parameterize) .']</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Playwright allows you to parameterize tests at either the test level or the project level.
+### Test Level Parameterization
+At the test level, you can iterate over a data set to generate multiple tests. This is done by using a loop (such as `.forEach()`) to call `test()` or `test.describe()` multiple times, ensuring each test name is unique.
+```typescript
+[{name:'Alice',expected:'Hello, Alice!'},{name:'Bob',expected:'Hello, Bob!'}].forEach(({name,expected})=&gt;{
+  test(`testing with ${name}`, async({page}) =&gt; {
+    await page.goto(`https://example.com/greet?name=${name}`);
+    await expect(page.getByRole('heading')).toHaveText(expected);
+  });
+});
+```
+### Project Level Parameterization
+At the project level, you use "option" fixtures to define configuration options that can be set or overridden in the `playwright.config.ts` file. This is the recommended approach for running the same tests across different environments or configurations.
+1.  **Define the option:** Extend the test object with your options, providing a default value and setting `{ option: true }`.
+    ```typescript
+    export const test = base.extend&lt;TestOptions&gt;({
+      person: ['John', { option: true }],
+    });
     ```
-3.  **Configure projects:** In your `playwright.config.ts` file, define your projects and set the specific value for the option within the `use` object for each project.
+2.  **Configure projects:** In `playwright.config.ts`, define multiple projects, each providing a different value for the option.
     ```typescript
     projects: [
-      {
-        name: 'shopping',
-        use: { defaultItem: 'Buy milk' },
-      },
-      {
-        name: 'wellbeing',
-        use: { defaultItem: 'Exercise!' },
-      },
+      { name: 'alice', use: { person: 'Alice' } },
+      { name: 'bob', use: { person: 'Bob' } },
     ]
     ```
-By setting the option in the project configuration, Playwright ensures that when the fixture is invoked, it uses the value defined for that specific project.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Declare an 'option' fixture with a default value, then override that value per project in the config's use block. The fixture reads the option, so each project drives its own behavior in a type-safe way.</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H49" t="n">
-        <v>5</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.08823529411764706</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.4054054054054054</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.499999999975</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>How do I tag tests to run just those from the CLI, and also carve tests into subsets at the project level?</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>['Annotations | Playwright', 'Projects | Playwright', 'Sometimes you want to tag your tests as\n`@fast`\nor\n`@slow`\n, and then filter by tag in the test report. Or you might want to only run tests that have a certain tag.\n\nTo tag a test, either provide an additional details object when declaring a test, or add\n`@`\n-token to the test title. Note that tags must start with\n`@`\nsymbol.\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'test login page\',{tag:\'@fast\',},async({page})=&gt;{// ...});test(\'test full report @slow\',async({page})=&gt;{// ...});`\n```\n\nYou can also tag all tests in a group or provide multiple tags:\n\n```\n`import{test,expect}from\'@playwright/test\';test.describe(\'group\',{tag:\'@report\',},()=&gt;{test(\'test report header\',async({page})=&gt;{// ...});test(\'test full report\',{tag:[\'@slow\',\'@vrt\'],},async({page})=&gt;{// ...});});`\n```\n\nYou can now run tests that have a particular tag with\n--grep (https://playwright.dev/docs/test-cli#all-options)\ncommand line option.\n\nBash\nPowerShell\nBatch\n```\n`npx playwrighttest--grep@fast`\n```\n```\n`npx playwright test--grep"@fast"`\n```\n```\n`npxplaywright test--grep@fast`\n```\n\nOr if you want the opposite, you can skip the tests with a certain tag:\n\nBash\nPowerShell\nBatch\n```\n`npx playwrighttest--grep-invert @fast`\n```\n```\n`npx playwright test--grep-invert"@fast"`\n```\n```\n`npxplaywright test--grep-invert@fast`\n```\n\nTo run tests containing either tag (logical\n`OR`\noperator):\n\nBash\nPowerShell\nBatch\n```\n`npx playwrighttest--grep"@fast|@slow"`\n```\n```\n`npx playwright test--grep--%"@fast^|@slow"`\n```\n```\n`npxplaywright test--grep"@fast^|@slow"`\n```\n\nOr run tests containing both tags (logical\n`AND`\noperator) using regex lookaheads:\n\n```\n`npx playwrighttest--grep"(?=.*@fast)(?=.*@slow)"`\n```\n\nYou can also filter tests in the configuration file via\ntestConfig.grep (https://playwright.dev/docs/api/class-testconfig#test-config-grep)\nand\ntestProject.grep (https://playwright.dev/docs/api/class-testproject#test-project-grep)\n.', 'We can split tests into projects and use filters to run a subset of tests. For example, we can create a project that runs tests using a filter matching all tests with a specific file name. We can then have another group of tests that ignore specific test files.\n\nHere is an example that defines a common timeout and two projects. The "Smoke" project runs a small subset of tests without retries, and "Default" project runs all other tests with retries.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({timeout:60000,// Timeout is shared between all tests.projects:[{name:\'Smoke\',testMatch:/.*smoke.spec.ts/,retries:0,},{name:\'Default\',testIgnore:/.*smoke.spec.ts/,retries:2,},],});`\n```', 'A project is logical group of tests running with the same configuration. We use projects so we can run tests on different browsers and devices. Projects are configured in the\n`playwright.config.ts`\nfile and once configured you can then run your tests on all projects or only on a specific project. You can also use projects to run the same tests in different configurations. For example, you can run the same tests in a logged-in and logged-out state.\n\nBy setting up projects you can also run a group of tests with different timeouts or retries or a group of tests against different environments such as staging and production, splitting tests per package/functionality and more.']</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>['You can now run tests that have a particular tag with --grep (https://playwright.dev/docs/test-cli#all-options) command line option.', 'We can split tests into projects and use filters to run a subset of tests. For example, we can create a project that runs tests using a filter matching all tests with a specific file name. We can then have another group of tests that ignore specific test files.']</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>To tag tests and run only those from the CLI, you can add a tag (starting with `@`) to the test title or within a details object when declaring the test. You can then run these tests using the `--grep` command line option:
-*   **Run tests with a specific tag:** `npx playwright test --grep @fast`
-*   **Skip tests with a specific tag:** `npx playwright test --grep-invert @fast`
-*   **Run tests with multiple tags (OR):** `npx playwright test --grep "@fast|@slow"`
-*   **Run tests with multiple tags (AND):** `npx playwright test --grep "(?=.*@fast)(?=.*@slow)"`
-To carve tests into subsets at the project level, you define projects in your `playwright.config.ts` file. You can use filters like `testMatch` (to include specific files) or `testIgnore` (to exclude specific files) to split tests into different groups. For example:
-```typescript
-projects: [
-  {
-    name: 'Smoke',
-    testMatch: /.*smoke.spec.ts/,
-  },
-  {
-    name: 'Default',
-    testIgnore: /.*smoke.spec.ts/,
-  },
-],
-```</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Label tests with @-tokens and select them at runtime via --grep. For a more structural cut, group tests into separate projects and let each project's own filter — say a testMatch on the file name — decide what it runs.</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>5</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.08275862068965517</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>I want to parameterize the same tests with different values — both at the test level and across environments. How do these two levels differ?</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>['Parameterize tests | Playwright', 'You can either parameterize tests on a test level or on a project level.', 'Playwright Test supports running multiple test projects at the same time. In the following example, we\'ll run two projects with different options.\n\nWe declare the option\n`person`\nand set the value in the config. The first project runs with the value\n`Alice`\nand the second with the value\n`Bob`\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\n\nWe can use this option in the test, similarly to\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nexample.spec.ts\n```\n`import{test}from\'./my-test\';test(\'test 1\',async({page,person})=&gt;{awaitpage.goto(`/index.html`);awaitexpect(page.locator(\'#node\')).toContainText(person);// ...});`\n```\n\nNow, we can run tests in multiple configurations by using projects.\n\nTypeScript\nJavaScript\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{TestOptions}from\'./my-test\';exportdefaultdefineConfig&lt;TestOptions&gt;({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\nplaywright.config.ts\n```\n`// @ts-checkmodule.exports=defineConfig({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\n\nWe can also use the option in a fixture. Learn more about\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\n\nnote\nParameterized projects behavior has changed in version 1.18.\nLearn more (https://playwright.dev/docs/release-notes#breaking-change-custom-config-options)\n.', "example.spec.ts\n```\n`[{name:'Alice',expected:'Hello, Alice!'},{name:'Bob',expected:'Hello, Bob!'},{name:'Charlie',expected:'Hello, Charlie!'},].forEach(({name,expected})=&gt;{// You can also do it with test.describe() or with multiple tests as long the test name is unique.test(`testing with${name}`,async({page})=&gt;{awaitpage.goto(`https://example.com/greet?name=${name}`);awaitexpect(page.getByRole('heading')).toHaveText(expected);});});`\n```", "You can use environment variables to configure tests from the command line.\n\nFor example, consider the following test file that needs a username and a password. It is usually a good idea not to store your secrets in the source code, so we'll need a way to pass secrets from outside.\n\nexample.spec.ts\n```\n`test(`example test`,async({page})=&gt;{// ...awaitpage.getByLabel('User Name').fill(process.env.USER_NAME);awaitpage.getByLabel('Password').fill(process.env.PASSWORD);});`\n```\n\nYou can run this test with your secret username and password set in the command line.\n\nBash\nPowerShell\nBatch\n```\n`USER_NAME=mePASSWORD=secret npx playwrighttest`\n```\n```\n`$env:USER_NAME=me$env:PASSWORD=secretnpx playwright test`\n```\n```\n`setUSER_NAME=mesetPASSWORD=secretnpxplaywright test`\n```\n\nSimilarly, configuration file can also read environment variables passed through the command line.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{baseURL:process.env.STAGING==='1'?'http://staging.example.test/':'http://example.test/',}});`\n```\n\nNow, you can run tests against a staging or a production environment:\n\nBash\nPowerShell\nBatch\n```\n`STAGING=1npx playwrighttest`\n```\n```\n`$env:STAGING=1npx playwright test`\n```\n```\n`setSTAGING=1npxplaywright test`\n```"]</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>['You can either parameterize tests on a test level or on a project level.', 'Playwright Test supports running multiple test projects that can be configured separately. You can use "option" fixtures to make your configuration options declarative and type safe. Learn more about parameterizing tests (https://playwright.dev/docs/test-parameterize) .']</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Based on the provided context, you can parameterize tests at either the test level or the project level.
-*   **Test level:** You can parameterize tests by iterating over an array of values (e.g., using `.forEach`) to create multiple tests or describe blocks.
-*   **Project level (across environments):** You can use parameterized projects to run multiple test projects at the same time with different options. This involves defining options in your configuration and overriding them within the `projects` array in your `playwright.config.ts` file. Additionally, you can use environment variables to configure tests or the configuration file from the command line to run tests against different environments (such as staging or production).</t>
+3.  **Use in tests:** The option can be accessed in tests or fixtures just like standard fixtures.
+Projects are also used to run groups of tests against different environments (e.g., staging vs. production) by configuring project-specific settings like `baseURL`, `retries`, or `timeout`.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3220,24 +3784,30 @@
         </is>
       </c>
       <c r="F51" t="n">
+        <v>0.009776</v>
+      </c>
+      <c r="G51" t="n">
+        <v>35629</v>
+      </c>
+      <c r="H51" t="n">
         <v>0.75</v>
       </c>
-      <c r="G51" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H51" t="n">
-        <v>5</v>
-      </c>
       <c r="I51" t="n">
-        <v>0.2162162162162162</v>
+        <v>0.31</v>
       </c>
       <c r="J51" t="n">
-        <v>0.6486486486486487</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5833333333041666</v>
+        <v>0.1129707112970711</v>
       </c>
       <c r="L51" t="n">
+        <v>0.7297297297297297</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.5888888888692593</v>
+      </c>
+      <c r="N51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3253,7 +3823,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>['Locators | Playwright', "note\nIt's usually better to find a\nmore reliable way (https://playwright.dev/docs/locators#quick-guide)\nto uniquely identify the element instead of checking the visibility.\n\nConsider a page with two buttons, the first invisible and the second\nvisible (https://playwright.dev/docs/actionability#visible)\n.\n\n```\n`&lt;buttonstyle='display:none'&gt;Invisible&lt;/button&gt;&lt;button&gt;Visible&lt;/button&gt;`\n```\n\nThis will find both buttons and throw a\nstrictness (https://playwright.dev/docs/locators#strictness)\nviolation error:\n```\n`awaitpage.locator('button').click();`\n```\nThis will only find a second button, because it is visible, and then click it.\n```\n`awaitpage.locator('button').filter({visible:true}).click();`\n```"]</t>
+          <t>["note\nIt's usually better to find a\nmore reliable way (https://playwright.dev/docs/locators#quick-guide)\nto uniquely identify the element instead of checking the visibility.\n\nConsider a page with two buttons, the first invisible and the second\nvisible (https://playwright.dev/docs/actionability#visible)\n.\n\n```\n`&lt;buttonstyle='display:none'&gt;Invisible&lt;/button&gt;&lt;button&gt;Visible&lt;/button&gt;`\n```\n\nThis will find both buttons and throw a\nstrictness (https://playwright.dev/docs/locators#strictness)\nviolation error:\n```\n`awaitpage.locator('button').click();`\n```\nThis will only find a second button, because it is visible, and then click it.\n```\n`awaitpage.locator('button').filter({visible:true}).click();`\n```", 'Locators | Playwright', "```\n`awaitpage.getByRole('button').click();`\n```\n\nOn the other hand, Playwright understands when you perform a multiple-element operation, so the following call works perfectly fine when the locator resolves to multiple elements.", "```\n`awaitpage.getByRole('button').count();`\n```\n\nYou can explicitly opt-out from strictness check by telling Playwright which element to use when multiple elements match, through\nlocator.first() (https://playwright.dev/docs/api/class-locator#locator-first)\n,\nlocator.last() (https://playwright.dev/docs/api/class-locator#locator-last)\n, and\nlocator.nth() (https://playwright.dev/docs/api/class-locator#locator-nth)\n. These methods are\nnot recommended\nbecause when your page changes, Playwright may click on an element you did not intend. Instead, follow best practices above to create a locator that uniquely identifies the target element."]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3265,9 +3835,9 @@
         <is>
           <t>To click only the visible button, use the `.filter()` method:
 ```javascript
-await page.locator('button').filter({hasNot: page.locator(':visible')}).click(); // Note: The provided context specifies the following syntax:
-await page.locator('button').filter({visible:true}).click();
-```</t>
+await page.locator('button').filter({hasNot: null, visible: true}).click();
+```
+While the documentation notes that you can opt-out of strictness using `.first()`, `.last()`, or `.nth()`, these are not recommended because they may target the wrong element if the page changes. The documentation also suggests that it is usually better to find a more reliable way to uniquely identify the element rather than checking for visibility.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3276,39 +3846,45 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0.0087235</v>
       </c>
       <c r="G52" t="n">
-        <v>0.44</v>
+        <v>33509</v>
       </c>
       <c r="H52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3513513513513514</v>
+        <v>0.22</v>
       </c>
       <c r="J52" t="n">
-        <v>0.3023255813953488</v>
+        <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>0.49999999995</v>
+        <v>0.1948051948051948</v>
       </c>
       <c r="L52" t="n">
+        <v>0.3488372093023256</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="N52" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>My test hangs forever after clicking a button that opens a confirm() dialog. Code:
+          <t>One spec in our checkout suite never finishes — the runner sits on it until the whole run is killed. It's the test that exercises the 'delete saved card' button, which is the only place in the app that asks the user to confirm before proceeding. I added a listener so I could log what the prompt says, and the message does get printed, so it's not that we're missing the event. Everything after the click is dead; the trace shows the click itself never completing.
 page.on('dialog', dialog =&gt; console.log(dialog.message()));
-await page.getByRole('button').click(); // Will hang here
-Why does it hang and how do I fix it?</t>
+await page.getByRole('button', { name: 'Delete card' }).click();  // never resolves
+Removing the confirm from the app makes the test pass, so it's clearly that. What am I not doing?</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>["Dialog | Playwright\n\nDialog (https://playwright.dev/docs/api/class-dialog)\nobjects are dispatched by page via the\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nevent.\n\nAn example of using\n`Dialog`\nclass:\n\n```\n`const{chromium}=require('playwright');// Or 'firefox' or 'webkit'.(async()=&gt;{constbrowser=awaitchromium.launch();constpage=awaitbrowser.newPage();page.on('dialog',asyncdialog=&gt;{console.log(dialog.message());awaitdialog.dismiss();});awaitpage.evaluate(()=&gt;alert('1'));awaitbrowser.close();})();`\n```\n\nnote\nDialogs are dismissed automatically, unless there is a\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nlistener. When listener is present, it\nmust\neither\ndialog.accept() (https://playwright.dev/docs/api/class-dialog#dialog-accept)\nor\ndialog.dismiss() (https://playwright.dev/docs/api/class-dialog#dialog-dismiss)\nthe dialog - otherwise the page will\nfreeze (https://developer.mozilla.org/en-US/docs/Web/JavaScript/EventLoop#never_blocking)\nwaiting for the dialog, and actions like click will never finish.", 'Dialogs | Playwright', "By default, dialogs are auto-dismissed by Playwright, so you don't have to handle them. However, you can register a dialog handler before the action that triggers the dialog to either\ndialog.accept() (https://playwright.dev/docs/api/class-dialog#dialog-accept)\nor\ndialog.dismiss() (https://playwright.dev/docs/api/class-dialog#dialog-dismiss)\nit.\n\n```\n`page.on('dialog',dialog=&gt;dialog.accept());awaitpage.getByRole('button').click();`\n```\n\nnote\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nlistener\nmust handle\nthe dialog. Otherwise your action will stall, be it\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nor something else. That's because dialogs in Web are modals and therefore block further page execution until they are handled.\n\nAs a result, the following snippet will never resolve:\n\nwarning\nWRONG!\n\n```\n`page.on('dialog',dialog=&gt;console.log(dialog.message()));awaitpage.getByRole('button').click();// Will hang here`\n```\n\nnote\nIf there is no listener for\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\n, all dialogs are automatically dismissed.", "Added before v1.9\n\ndialog.accept\n\nReturns when the dialog has been accepted.\n\nUsage\n\n```\n`awaitdialog.accept();awaitdialog.accept(promptText);`\n```\n\nArguments\n\n`promptText`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-dialog#dialog-accept-option-prompt-text)\nA text to enter in prompt. Does not cause any effects if the dialog's\n`type`\nis not prompt. Optional.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-dialog#dialog-accept-return)", 'Added before v1.9\n\ndialog.dismiss\n\nReturns when the dialog has been dismissed.\n\nUsage\n\n```\n`awaitdialog.dismiss();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-dialog#dialog-dismiss-return)']</t>
+          <t>["Auto-waiting | Playwright","Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 \u203a basic test ===========================Error: expect(received).toHaveText(expected)Expected string: \"my text\"Received string: \"\"Call log:- expect.toHaveText with timeout 5000ms- waiting for \"locator('button')\"`\n```","See a full log of your test to better understand what Playwright is doing behind the scenes such as scrolling into view, waiting for element to be visible, enabled and stable and performing actions such as click, fill, press etc.","LocatorAssertions | Playwright\n\nThe\nLocatorAssertions (https://playwright.dev/docs/api/class-locatorassertions)\nclass provides assertion methods that can be used to make assertions about the\nLocator (https://playwright.dev/docs/api/class-locator)\nstate in the tests.\n\n```\n`import{test,expect}from'@playwright/test';test('status becomes submitted',async({page})=&gt;{// ...awaitpage.getByRole('button').click();awaitexpect(page.locator('.status')).toHaveText('Submitted');});`\n```","Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`","In the Actions tab you can see what locator was used for every action and how long each one took to run. Hover over each action of your test and visually see the change in the DOM snapshot. Go back and forward in time and click an action to inspect and debug. Use the Before and After tabs to visually see what happened before and after the action.\n\nSelecting each action reveals:\n\nAction snapshots\nAction log\nSource code location","Trace viewer | Playwright"]</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3318,15 +3894,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>It hangs because dialogs are modals that block further page execution until they are handled. When you register a `page.on('dialog')` listener, you are required to either call `dialog.accept()` or `dialog.dismiss()`. If you only log the message without calling one of these methods, the page will freeze waiting for the dialog to be handled, causing your click action to never finish.
-To fix it, you must call `dialog.accept()` or `dialog.dismiss()` within your listener. For example:
-```javascript
-page.on('dialog', dialog =&gt; {
-  console.log(dialog.message());
-  dialog.accept(); // or dialog.dismiss();
-});
-await page.getByRole('button').click();
-```</t>
+          <t>The timeout that ran out is the **Expect timeout**, which has a default value of 5,000 ms. This is separate from the overall test timeout.\n\nBumping the timeout is not necessarily the right response; you may be papering over an issue. Because the assertion is auto-retrying, it is waiting for the locator to satisfy the condition within that 5-second window. If it receives an empty string, it means the element was found but did not contain the expected text within that timeframe.\n\nTo investigate why this is happening, you should use the **Trace Viewer**:\n\n*   **Check the Log:** Use the Trace Viewer to see the full log of the test. This will show you what Playwright was doing behind the scenes, such as scrolling, waiting for the element to be visible, enabled, or stable [3].\n*   **Inspect Actions:** Use the **Actions** tab to hover over actions and see the DOM snapshot change. You can use the **Before** and **After** tabs to visually inspect the state of the button at the time of the failure [6].\n\nIf you determine that the element simply requires more time to reach the desired state, you can increase the timeout for that specific assertion using:\n\n```javascript\nawait expect(page.locator('button')).toHaveText('my text', { timeout: 10000 });\n```\n\nAlternatively, you can set a global expect timeout in your configuration [5].</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3335,45 +3903,50 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0.00945725</v>
       </c>
       <c r="G53" t="n">
-        <v>0.89</v>
+        <v>35384</v>
       </c>
       <c r="H53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0.202020202020202</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0.5128205128205128</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>0.999999999975</v>
+        <v>0.02991452991452992</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0.1794871794871795</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>My assertion times out. Code:
+          <t>This assertion fails on our CI runner maybe one run in four, and never locally. The message says it received an empty string, but if I put a screenshot immediately before the assertion the button clearly has its label in the image.
 await expect(page.locator('button')).toHaveText('my text');
-Error:
 Error: expect(received).toHaveText(expected)
 Expected string: "my text"
 Received string: ""
 Call log:
   - expect.toHaveText with timeout 5000ms
   - waiting for "locator('button')"
-What is happening?</t>
+The test as a whole is nowhere near its own limit — it finishes in about eight seconds when it passes. So what ran out, and is bumping it the right response or am I papering over something?</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>['Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Error: expect(received).toHaveText(expected)Expected string: "my text"Received string: ""Call log:- expect.toHaveText with timeout 5000ms- waiting for "locator(\'button\')"`\n```', 'Auto-waiting | Playwright', 'Playwright performs a range of actionability checks on the elements before making actions to ensure these actions behave as expected. It auto-waits for all the relevant checks to pass and only then performs the requested action. If the required checks do not pass within the given\n`timeout`\n, action fails with the\n`TimeoutError`\n.\n\nFor example, for\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\n, Playwright will ensure that:\n\nlocator resolves to exactly one element\nelement is\nVisible (https://playwright.dev/docs/actionability#visible)\nelement is\nStable (https://playwright.dev/docs/actionability#stable)\n, as in not animating or completed animation\nelement\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\n, as in not obscured by other elements\nelement is\nEnabled (https://playwright.dev/docs/actionability#enabled)\n\nHere is the complete list of actionability checks performed for each action:\n\nAction\nVisible (https://playwright.dev/docs/actionability#visible)\nStable (https://playwright.dev/docs/actionability#stable)\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\nEnabled (https://playwright.dev/docs/actionability#enabled)\nEditable (https://playwright.dev/docs/actionability#editable)\nlocator.check() (https://playwright.dev/docs/api/class-locator#locator-check)\nYes\nYes\nYes\nYes\n-\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nYes\nYes\nYes\nYes\n-\nlocator.dblclick() (https://playwright.dev/docs/api/class-locator#locator-dblclick)\nYes\nYes\nYes\nYes\n-\nlocator.setChecked() (https://playwright.dev/docs/api/class-locator#locator-set-checked)\nYes\nYes\nYes\nYes\n-\nlocator.tap() (https://playwright.dev/docs/api/class-locator#locator-tap)\nYes\nYes\nYes\nYes\n-\nlocator.uncheck() (https://playwright.dev/docs/api/class-locator#locator-uncheck)\nYes\nYes\nYes\nYes\n-\nlocator.hover() (https://playwright.dev/docs/api/class-locator#locator-hover)\nYes\nYes\nYes\n-\n-\nlocator.dragTo() (https://playwright.dev/docs/api/class-locator#locator-drag-to)\nYes\nYes\nYes\n-\n-\nlocator.screenshot() (https://playwright.dev/docs/api/class-locator#locator-screenshot)\nYes\nYes\n-\n-\n-\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\nYes\n-\n-\nYes\nYes\nlocator.clear() (https://playwright.dev/docs/api/class-locator#locator-clear)\nYes\n-\n-\nYes\nYes\nlocator.selectOption() (https://playwright.dev/docs/api/class-locator#locator-select-option)\nYes\n-\n-\nYes\n-\nlocator.selectText() (https://playwright.dev/docs/api/class-locator#locator-select-text)\nYes\n-\n-\n-\n-\nlocator.scrollIntoViewIfNeeded() (https://playwright.dev/docs/api/class-locator#locator-scroll-into-view-if-needed)\n-\nYes\n-\n-\n-\nlocator.blur() (https://playwright.dev/docs/api/class-locator#locator-blur)\n-\n-\n-\n-\n-\nlocator.dispatchEvent() (https://playwright.dev/docs/api/class-locator#locator-dispatch-event)\n-\n-\n-\n-\n-\nlocator.focus() (https://playwright.dev/docs/api/class-locator#locator-focus)\n-\n-\n-\n-\n-\nlocator.press() (https://playwright.dev/docs/api/class-locator#locator-press)\n-\n-\n-\n-\n-\nlocator.pressSequentially() (https://playwright.dev/docs/api/class-locator#locator-press-sequentially)\n-\n-\n-\n-\n-\nlocator.setInputFiles() (https://playwright.dev/docs/api/class-locator#locator-set-input-files)\n-\n-\n-\n-\n-', "LocatorAssertions | Playwright\n\nThe\nLocatorAssertions (https://playwright.dev/docs/api/class-locatorassertions)\nclass provides assertion methods that can be used to make assertions about the\nLocator (https://playwright.dev/docs/api/class-locator)\nstate in the tests.\n\n```\n`import{test,expect}from'@playwright/test';test('status becomes submitted',async({page})=&gt;{// ...awaitpage.getByRole('button').click();awaitexpect(page.locator('.status')).toHaveText('Submitted');});`\n```", 'PlaywrightAssertions | Playwright\n\nPlaywright gives you Web-First Assertions with convenience methods for creating assertions that will wait and retry until the expected condition is met.\n\nConsider the following example:\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'status becomes submitted\',async({page})=&gt;{// ...awaitpage.locator(\'#submit-button\').click();awaitexpect(page.locator(\'.status\')).toHaveText(\'Submitted\');});`\n```\n\nPlaywright will be re-testing the node with the selector\n`.status`\nuntil fetched Node has the\n`"Submitted"`\ntext. It will be re-fetching the node and checking it over and over, until the condition is met or until the timeout is reached. You can pass this timeout as an option.\n\nBy default, the timeout for assertions is set to 5 seconds.', 'The following assertions will retry until the assertion passes, or the assertion timeout is reached. Note that retrying assertions are async, so you must\n`await`\nthem.\n\nAssertion\nDescription\nawait expect(locator).toBeAttached() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-attached)\nElement is attached\nawait expect(locator).toBeChecked() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-checked)\nCheckbox is checked\nawait expect(locator).toBeDisabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-disabled)\nElement is disabled\nawait expect(locator).toBeEditable() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-editable)\nElement is editable\nawait expect(locator).toBeEmpty() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-empty)\nContainer is empty\nawait expect(locator).toBeEnabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-enabled)\nElement is enabled\nawait expect(locator).toBeFocused() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-focused)\nElement is focused\nawait expect(locator).toBeHidden() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-hidden)\nElement is not visible\nawait expect(locator).toBeInViewport() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-in-viewport)\nElement intersects viewport\nawait expect(locator).toBeVisible() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-visible)\nElement is visible\nawait expect(locator).toContainText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-text)\nElement contains text\nawait expect(locator).toContainClass() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-class)\nElement has specified CSS classes\nawait expect(locator).toHaveAccessibleDescription() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-accessible-description)\nElement has a matching\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\nawait expect(locator).toHaveAccessibleName() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-accessible-name)\nElement has a matching\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\nawait expect(locator).toHaveAttribute() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-attribute)\nElement has a DOM attribute\nawait expect(locator).toHaveClass() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-class)\nElement has specified CSS class property\nawait expect(locator).toHaveCount() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-count)\nList has exact number of children\nawait expect(locator).toHaveCSS() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css)\nElement has CSS property\nawait expect(locator).toHaveId() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-id)\nElement has an ID\nawait expect(locator).toHaveJSProperty() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-js-property)\nElement has a JavaScript property\nawait expect(locator).toHaveRole() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-role)\nElement has a specific\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\nawait expect(locator).toHaveScreenshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-screenshot-1)\nElement has a screenshot\nawait expect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nElement matches text\nawait expect(locator).toHaveValue() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value)\nInput has a value\nawait expect(locator).toHaveValues() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-values)\nSelect has options selected\nawait expect(locator).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-match-aria-snapshot)\nElement matches the Aria snapshot\nawait expect(page).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-match-aria-snapshot)\nPage matches the Aria snapshot\nawait expect(page).toHaveScreenshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\nPage has a screenshot\nawait expect(page).toHaveTitle() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-title)\nPage has a title\nawait expect(page).toHaveURL() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-url)\nPage has a URL\nawait expect(response).toBeOK() (https://playwright.dev/docs/api/class-apiresponseassertions#api-response-assertions-to-be-ok)\nResponse has an OK status', "example.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('example',async({page})=&gt;{awaitexpect(locator).toHaveText('hello',{timeout:10_000});});`\n```"]</t>
+          <t>Auto-waiting | Playwright,</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3383,11 +3956,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Based on the provided context, your assertion is timing out because `toHaveText()` is an auto-retrying assertion that waits for the specified condition to be met. Playwright re-tests the locator until the condition is satisfied or the timeout is reached.
-In your case:
-*   **The condition was not met:** Playwright expected the button to have the text `"my text"`, but it received an empty string (`""`).
-*   **Timeout reached:** Because the condition was not met within the default 5-second timeout, the assertion failed.
-*   **Call log:** The log indicates that Playwright was actively waiting for the locator and checking the text, but the element did not contain the expected text before the 5000ms limit expired.</t>
+          <t>The timeout that ran out is the **Expect timeout**, which has a default value of 5,000 ms. This is separate from the overall test timeout.
+Bumping the timeout is not necessarily the right response; you may be papering over an issue. Because the assertion is auto-retrying, it is waiting for the locator to satisfy the condition within that 5-second window. If it receives an empty string, it means the element was found but did not contain the expected text within that timeframe.
+To investigate why this is happening, you should use the **Trace Viewer**:
+*   **Check the Log:** Use the Trace Viewer to see the full log of the test. This will show you what Playwright was doing behind the scenes, such as scrolling, waiting for the element to be visible, enabled, or stable [3].
+*   **Inspect Actions:** Use the **Actions** tab to hover over actions and see the DOM snapshot change. You can use the **Before** and **After** tabs to visually inspect the state of the button at the time of the failure [6].
+If you determine that the element simply requires more time to reach the desired state, you can increase the timeout for that specific assertion using:
+```javascript
+await expect(page.locator('button')).toHaveText('my text', { timeout: 10000 });
+```
+Alternatively, you can set a global expect timeout in your configuration [5].</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3396,41 +3974,47 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0.01015725</v>
       </c>
       <c r="G54" t="n">
-        <v>0.36</v>
+        <v>36549</v>
       </c>
       <c r="H54" t="n">
-        <v>5</v>
+        <v>0.75</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1592920353982301</v>
+        <v>0.48</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3214285714285715</v>
+        <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>0.81666666664625</v>
+        <v>0.09375</v>
       </c>
       <c r="L54" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.8666666666377778</v>
+      </c>
+      <c r="N54" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>My evaluate call throws because 'data' is undefined in the page. Code:
+          <t>I'm pulling a value out of our app's client-side store to assert on it, and the call blows up inside the browser rather than in my test. The variable it's complaining about is defined two lines above the call and my editor resolves it fine, so I assumed a build/transpile problem at first.
 const data = 'some data';
 const result = await page.evaluate(() =&gt; {
-  window.myApp.use(data); // ReferenceError: data is not defined
+  window.myApp.use(data);  // ReferenceError: data is not defined
 });
-How do I pass the value into the page?</t>
+Nothing else in the file has this problem. Why is this one line unable to see it?</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>['Evaluating JavaScript | Playwright', 'Evaluated scripts run in the browser environment, while your test runs in a testing environments. This means you cannot use variables from your test in the page and vice versa. Instead, you should pass them explicitly as an argument.\n\nThe following snippet is\nWRONG\nbecause it uses the variable directly:\n\n```\n`constdata=\'some data\';constresult=awaitpage.evaluate(()=&gt;{// WRONG: there is no "data" in the web page.window.myApp.use(data);});`\n```\n\nThe following snippet is\nCORRECT\nbecause it passes the value explicitly as an argument:\n\n```\n`constdata=\'some data\';// Pass |data| as a parameter.constresult=awaitpage.evaluate(data=&gt;{window.myApp.use(data);},data);`\n```', "Playwright evaluation methods like\npage.evaluate() (https://playwright.dev/docs/api/class-page#page-evaluate)\ntake a single optional argument. This argument can be a mix of\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\nvalues and\nJSHandle (https://playwright.dev/docs/api/class-jshandle)\ninstances. Handles are automatically converted to the value they represent.\n\n```\n`// A primitive value.awaitpage.evaluate(num=&gt;num,42);// An array.awaitpage.evaluate(array=&gt;array.length,[1,2,3]);// An object.awaitpage.evaluate(object=&gt;object.foo,{foo:'bar'});// A single handle.constbutton=awaitpage.evaluateHandle('window.button');awaitpage.evaluate(button=&gt;button.textContent,button);// Alternative notation using JSHandle.evaluate.awaitbutton.evaluate((button,from)=&gt;button.textContent.substring(from),5);// Object with multiple handles.constbutton1=awaitpage.evaluateHandle('window.button1');constbutton2=awaitpage.evaluateHandle('window.button2');awaitpage.evaluate(o=&gt;o.button1.textContent+o.button2.textContent,{button1,button2});// Object destructuring works. Note that property names must match// between the destructured object and the argument.// Also note the required parenthesis.awaitpage.evaluate(({button1,button2})=&gt;button1.textContent+button2.textContent,{button1,button2});// Array works as well. Arbitrary names can be used for destructuring.// Note the required parenthesis.awaitpage.evaluate(([b1,b2])=&gt;b1.textContent+b2.textContent,[button1,button2]);// Any mix of serializables and handles works.awaitpage.evaluate(x=&gt;x.button1.textContent+x.list[0].textContent+String(x.foo),{button1,list:[button2],foo:null});`\n```"]</t>
+          <t>Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 \u203a basic test ===========================Error: expect(received).toHaveText(expected)Expected string: \my text\"Received string: \"\"Call log:- expect.toHaveText with timeout 5000ms- waiting for \"locator('button')\"`\n```",</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3440,14 +4024,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>To pass the value into the page, you must pass it explicitly as an argument to the `page.evaluate` function.
-Here is the correct way to do it:
+          <t>The error occurs because the script inside `page.evaluate` runs in the browser environment, while your variable `data` exists only in your test environment. These two environments cannot share variables directly.
+To fix this, you must pass the variable explicitly as an argument to `page.evaluate`.
+**Correct approach:**
 ```javascript
 const data = 'some data';
 const result = await page.evaluate(data =&gt; {
   window.myApp.use(data);
 }, data);
-```</t>
+```
+By passing `data` as the second argument to `page.evaluate`, it becomes available as the parameter within the callback function.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3456,39 +4042,45 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0.00736275</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>28451</v>
       </c>
       <c r="H55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3409090909090909</v>
+        <v>0.89</v>
       </c>
       <c r="J55" t="n">
-        <v>0.4545454545454545</v>
+        <v>5</v>
       </c>
       <c r="K55" t="n">
+        <v>0.2738095238095238</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.696969696969697</v>
+      </c>
+      <c r="M55" t="n">
         <v>0.9999999999666667</v>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A slow test fails with:
+          <t>Our nightly regression job has one spec that imports a 30MB fixture and walks a long onboarding wizard. It genuinely takes about a minute and it is genuinely doing useful work — nothing is stuck. It fails every night with:
 example.spec.ts:3:1 › basic test ===========================
 Timeout of 30000ms exceeded.
-The test genuinely needs more time. How do I raise the timeout for just this one test?</t>
+I don't want to raise the limit for the other 400 tests, because a test that hangs should still fail fast. How do I give room to this one only?</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>['Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', "example.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('slow test',async({page})=&gt;{test.slow();// Easy way to triple the default timeout// ...});test('very slow test',async({page})=&gt;{test.setTimeout(120_000);// ...});`\n```\n\nAPI reference:\ntest.setTimeout() (https://playwright.dev/docs/api/class-test#test-set-timeout)\nand\ntest.slow() (https://playwright.dev/docs/api/class-test#test-slow)\n."]</t>
+          <t>See a full log of your test to better understand what Playwright is doing behind the scenes such as scrolling into view, waiting for element to be visible, enabled and stable and performing actions such as click, fill, press etc.,</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3498,13 +4090,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>To raise the timeout for just one test, you can use `test.setTimeout(120_000)` within the test, as shown in the provided example:
+          <t>To increase the timeout for only the specific test that requires more time, you can use `test.setTimeout()` within that test.
+In your `example.spec.ts` file, add the following line inside the test block:
 ```typescript
-test('very slow test', async ({ page }) =&gt; {
-  test.setTimeout(120_000);
-  // ...
+test('basic test', async ({ page }) =&gt; {
+  test.setTimeout(120000); // Sets the timeout to 120 seconds for this test only
+  // ... rest of your test code
 });
-```</t>
+```
+Alternatively, if you only need to triple the default timeout, you can use `test.slow()`:
+```typescript
+test('basic test', async ({ page }) =&gt; {
+  test.slow();
+  // ... rest of your test code
+});
+```
+Both methods allow you to extend the duration for a single test without affecting the 30,000ms default timeout applied to the other 400 tests.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3513,24 +4114,30 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0.007936250000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5</v>
+        <v>30235</v>
       </c>
       <c r="H56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3142857142857143</v>
+        <v>0.83</v>
       </c>
       <c r="J56" t="n">
-        <v>0.2972972972972973</v>
+        <v>5</v>
       </c>
       <c r="K56" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.4324324324324325</v>
+      </c>
+      <c r="M56" t="n">
         <v>0.99999999995</v>
       </c>
-      <c r="L56" t="n">
+      <c r="N56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3547,7 +4154,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>["Locators support an option to only select elements that have or have not a descendant matching another locator. You can therefore filter by any other locator such as a\nlocator.getByRole() (https://playwright.dev/docs/api/class-locator#locator-get-by-role)\n,\nlocator.getByTestId() (https://playwright.dev/docs/api/class-locator#locator-get-by-test-id)\n,\nlocator.getByText() (https://playwright.dev/docs/api/class-locator#locator-get-by-text)\netc.\n\nhttp://localhost:3000\nProduct 1\nAdd to cart\nProduct 2\nAdd to cart\n```\n`&lt;ul&gt;&lt;li&gt;&lt;h3&gt;Product 1&lt;/h3&gt;&lt;button&gt;Add to cart&lt;/button&gt;&lt;/li&gt;&lt;li&gt;&lt;h3&gt;Product 2&lt;/h3&gt;&lt;button&gt;Add to cart&lt;/button&gt;&lt;/li&gt;&lt;/ul&gt;`\n```\n\n```\n`awaitpage.getByRole('listitem').filter({has:page.getByRole('heading',{name:'Product 2'})}).getByRole('button',{name:'Add to cart'}).click();`\n```\n\nWe can also assert the product card to make sure there is only one:\n\n```\n`awaitexpect(page.getByRole('listitem').filter({has:page.getByRole('heading',{name:'Product 2'})})).toHaveCount(1);`\n```\n\nThe filtering locator\nmust be relative\nto the original locator and is queried starting with the original locator match, not the document root. Therefore, the following will not work, because the filtering locator starts matching from the\n`&lt;ul&gt;`\nlist element that is outside of the\n`&lt;li&gt;`\nlist item matched by the original locator:\n\n```\n`// ✖ WRONGawaitexpect(page.getByRole('listitem').filter({has:page.getByRole('list').getByText('Product 2')})).toHaveCount(1);`\n```", 'Locators | Playwright', "Locator | Playwright\n\nLocators are the central piece of Playwright's auto-waiting and retry-ability. In a nutshell, locators represent a way to find element(s) on the page at any moment. A locator can be created with the\npage.locator() (https://playwright.dev/docs/api/class-page#page-locator)\nmethod.\n\nLearn more about locators (https://playwright.dev/docs/locators)\n."]</t>
+          <t>LocatorAssertions | Playwright\n\nThe\nLocatorAssertions (https://playwright.dev/docs/api/class-locatorassertions)\nclass provides assertion methods that can be used to make assertions about the\nLocator (https://playwright.dev/docs/api/class-locator)\nstate in the tests.\n\n```\n`import{test,expect}from'@playwright/test';test('status becomes submitted',async({page})=&gt;{// ...awaitpage.getByRole('button').click();awaitexpect(page.locator('.status')).toHaveText('Submitted');});`\n```,</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3557,7 +4164,8 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>The filtering locator must be relative to the original locator and is queried starting from the original locator match, not the document root. Your code does not work because the filtering locator (`page.getByRole('list').getByText('Product 2')`) starts matching from the `&lt;ul&gt;` list element, which is outside of the `&lt;li&gt;` list item matched by the original locator.</t>
+          <t>The code does not work because the filtering locator must be relative to the original locator and is queried starting from the original locator match, not the document root. 
+In your code, `page.getByRole('list').getByText('Product 2')` starts matching from the `&lt;ul&gt;` list element, which is outside of the `&lt;li&gt;` list item matched by `page.getByRole('listitem')`. As noted in the documentation, this specific approach is incorrect.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3566,40 +4174,45 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0.008291750000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>0.86</v>
+        <v>32047</v>
       </c>
       <c r="H57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4827586206896552</v>
+        <v>0.83</v>
       </c>
       <c r="J57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="L57" t="n">
         <v>0.6222222222222222</v>
       </c>
-      <c r="K57" t="n">
-        <v>0.9999999999</v>
-      </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="N57" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>First run of my visual test fails. Code:
+          <t>A colleague added visual coverage to the checkout page and CI went red on the very first run of the new test — before anyone had changed any styling. The message doesn't read like a normal assertion failure and there's no diff image in the report, just this:
 await expect(page).toHaveScreenshot();
-Error:
 Error: A snapshot doesn't exist at example.spec.ts-snapshots/example-test-1-chromium-darwin.png, writing actual.
-Is my test broken?</t>
+Re-running the job locally doesn't produce the error. Is the test wrong, or is CI wrong?</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>['Visual comparisons | Playwright', "When you run above for the first time, test runner will say:\n\n```\n`Error: A snapshot doesn't exist at example.spec.ts-snapshots/example-test-1-chromium-darwin.png, writing actual.`\n```\n\nThat's because there was no golden file yet. This method took a bunch of screenshots until two consecutive screenshots matched, and saved the last screenshot to file system. It is now ready to be added to the repository.\n\nThe name of the folder with the golden expectations starts with the name of your test file:\n\n```\n`drwxr-xr-x5user  group160Jun411:46.drwxr-xr-x6user  group192Jun411:45..-rw-r--r--1user  group231Jun411:16 example.spec.tsdrwxr-xr-x3user  group96Jun411:46 example.spec.ts-snapshots`\n```\n\nThe snapshot name\n`example-test-1-chromium-darwin.png`\nconsists of a few parts:\n\n`example-test-1.png`\n- an auto-generated name of the snapshot. Alternatively you can specify snapshot name as the first argument of the\n`toHaveScreenshot()`\nmethod:\n```\n`awaitexpect(page).toHaveScreenshot('landing.png');`\n```\n`chromium-darwin`\n- the browser name and the platform. Screenshots differ between browsers and platforms due to different rendering, fonts and more, so you will need different snapshots for them. If you use multiple projects in your\nconfiguration file (https://playwright.dev/docs/test-configuration)\n, project name will be used instead of\n`chromium`\n.\n\nThe snapshot name and path can be configured with\ntestConfig.snapshotPathTemplate (https://playwright.dev/docs/api/class-testconfig#test-config-snapshot-path-template)\nin the playwright config.\n\nNote that\n`toHaveScreenshot()`\nalso accepts an array of path segments to the snapshot file such as\n`expect().toHaveScreenshot(['relative', 'path', 'to', 'snapshot.png'])`\n.\nHowever, this path must stay within the snapshots directory for each test file (i.e.\n`a.spec.js-snapshots`\n), otherwise it will throw.", "Playwright Test includes the ability to produce and visually compare screenshots using\n`await expect(page).toHaveScreenshot()`\n. On first execution, Playwright test will generate reference screenshots. Subsequent runs will compare against the reference.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('example test',async({page})=&gt;{awaitpage.goto('https://playwright.dev');awaitexpect(page).toHaveScreenshot();});`\n```\n\nwarning\nBrowser rendering can vary based on the host OS, version, settings, hardware, power source (battery vs. power adapter), headless mode, and other factors. For consistent screenshots, run tests in the same environment where the baseline screenshots were generated.", "SnapshotAssertions | Playwright\n\nPlaywright provides methods for comparing page and element screenshots with expected values stored in files.\n\n```\n`expect(screenshot).toMatchSnapshot('landing-page.png');`\n```"]</t>
+          <t>Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`,</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3609,7 +4222,10 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>No, your test is not broken. According to the provided context, this happens because there was no golden file yet. On the first execution, Playwright generates reference screenshots; the test runner saves the screenshot to the file system, and it is now ready to be added to the repository.</t>
+          <t>Neither the test nor CI is "wrong." The error message indicates that this is the first time the test has run and no "golden" reference file exists yet.
+When `toHaveScreenshot()` is executed for the first time, Playwright generates the actual screenshot and saves it to the file system. The error message you see is the expected behavior for this initial run, as the test runner is informing you that it has written the "actual" file because no baseline snapshot was found to compare against.
+To resolve this, you must add the generated snapshot file to your repository so that subsequent runs have a reference to compare against.
+The reason the test passes locally but fails on CI is due to differences in the environment. Visual comparisons are sensitive to the host OS, browser, and other factors. Because the snapshot name includes the platform and browser (e.g., `chromium-darwin`), a snapshot generated on your local machine cannot be used as the baseline for CI if the CI environment uses a different platform or browser configuration. For consistent results, you must ensure that the baseline screenshots are generated in the same environment where the tests run on CI.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3618,24 +4234,30 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0.0100305</v>
       </c>
       <c r="G58" t="n">
-        <v>0.71</v>
+        <v>36702</v>
       </c>
       <c r="H58" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3265306122448979</v>
+        <v>0.61</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3809523809523809</v>
+        <v>5</v>
       </c>
       <c r="K58" t="n">
+        <v>0.1015228426395939</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="M58" t="n">
         <v>0.999999999975</v>
       </c>
-      <c r="L58" t="n">
+      <c r="N58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3652,7 +4274,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>['Videos | Playwright', "Playwright Test can record videos for your tests, controlled by the\n`video`\noption in your Playwright config. By default videos are off.\n\n`'off'`\n- Do not record video.\n`'on'`\n- Record video for each test.\n`'retain-on-failure'`\n- Record video for each test, but remove all videos from successful test runs.\n`'on-first-retry'`\n- Record video only when retrying a test for the first time.\n\nVideo files will appear in the test output directory, typically\n`test-results`\n. See\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nfor advanced video configuration.\n\nVideos are saved upon\nbrowser context (https://playwright.dev/docs/browser-contexts)\nclosure at the end of a test. If you create a browser context manually, make sure to await\nbrowserContext.close() (https://playwright.dev/docs/api/class-browsercontext#browser-context-close)\n.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:'on-first-retry',},});`\n```\n```\n`constcontext=awaitbrowser.newContext({recordVideo:{dir:'videos/'}});// Make sure to await close, so that videos are saved.awaitcontext.close();`\n```\n\nYou can also specify video size and annotation. The video size defaults to the viewport size scaled down to fit 800x800. The video of the viewport is placed in the top-left corner of the output video, scaled down to fit if necessary. You may need to set the viewport size to match your desired video size.\n\nWhen\n`show: { actions }`\nis specified, each action will be visually highlighted in the video with the element outline and action title subtitle. The optional\n`duration`\nproperty controls how long each annotation is displayed (defaults to\n`500`\nms).\n\nWhen\n`show: { test }`\nis specified, video will be annotated with the current test information with configurable\n`level`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:{mode:'on-first-retry',size:{width:640,height:480},show:{actions:{duration:500,position:'top-right',fontSize:14,},test:{level:'step',position:'top-left',fontSize:12,}},},},});`\n```\n\nFor multi-page scenarios, you can access the video file associated with the page via the\npage.video() (https://playwright.dev/docs/api/class-page#page-video)\n.\n\n```\n`constpath=awaitpage.video().path();`\n```\n\nnote\nNote that the video is only available after the page or browser context is closed.", 'Video | Playwright\n\nWhen browser context is created with the\n`recordVideo`\noption, each page has a video object associated with it.\n\n```\n`console.log(awaitpage.video().path());`\n```', 'Configuration (use) | Playwright']</t>
+          <t>In the Actions tab you can see what locator was used for every action and how long each one took to run. Hover over each action of your test and visually see the change in the DOM snapshot. Go back and forward in time and click an action to inspect and debug. Use the Before and After tabs to visually see what happened before and after the action.\n\nSelecting each action reveals:\n\nAction snapshots\nAction log\nSource code location,</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3662,7 +4284,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Videos are saved upon browser context closure at the end of a test. Because you created the browser context manually, you must await `browserContext.close()` for the video to be saved.</t>
+          <t>The video files are not being created because you are not closing the browser context. Videos are saved upon browser context closure; you must call `await context.close()` to ensure the video is saved.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3671,38 +4293,44 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>0.007396750000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8</v>
+        <v>28902</v>
       </c>
       <c r="H59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.75</v>
       </c>
       <c r="J59" t="n">
-        <v>0.3055555555555556</v>
+        <v>5</v>
       </c>
       <c r="K59" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M59" t="n">
         <v>0.49999999995</v>
       </c>
-      <c r="L59" t="n">
+      <c r="N59" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>My locator matches way too many elements, including &lt;body&gt;. Code:
+          <t>This click lands somewhere completely unrelated to what I meant — sometimes it seems to hit the page background and dismiss our modal instead. When I ask how many elements it resolves to, the answer is several dozen, and the list includes &lt;body&gt; itself, which I don't understand at all since the text appears once on the page in a single card.
 await page.locator(':has-text("Playwright")').click();
-How do I scope it correctly?</t>
+How is the top-level element a match, and how do I narrow this to the one I want?</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>['Locators | Playwright', 'Locators are strict. This means that all operations on locators that imply some target DOM element will throw an exception if more than one element matches. For example, the following call throws if there are several buttons in the DOM:', "Locators support an option to only select elements that have or have not a descendant matching another locator. You can therefore filter by any other locator such as a\nlocator.getByRole() (https://playwright.dev/docs/api/class-locator#locator-get-by-role)\n,\nlocator.getByTestId() (https://playwright.dev/docs/api/class-locator#locator-get-by-test-id)\n,\nlocator.getByText() (https://playwright.dev/docs/api/class-locator#locator-get-by-text)\netc.\n\nhttp://localhost:3000\nProduct 1\nAdd to cart\nProduct 2\nAdd to cart\n```\n`&lt;ul&gt;&lt;li&gt;&lt;h3&gt;Product 1&lt;/h3&gt;&lt;button&gt;Add to cart&lt;/button&gt;&lt;/li&gt;&lt;li&gt;&lt;h3&gt;Product 2&lt;/h3&gt;&lt;button&gt;Add to cart&lt;/button&gt;&lt;/li&gt;&lt;/ul&gt;`\n```\n\n```\n`awaitpage.getByRole('listitem').filter({has:page.getByRole('heading',{name:'Product 2'})}).getByRole('button',{name:'Add to cart'}).click();`\n```\n\nWe can also assert the product card to make sure there is only one:\n\n```\n`awaitexpect(page.getByRole('listitem').filter({has:page.getByRole('heading',{name:'Product 2'})})).toHaveCount(1);`\n```\n\nThe filtering locator\nmust be relative\nto the original locator and is queried starting with the original locator match, not the document root. Therefore, the following will not work, because the filtering locator starts matching from the\n`&lt;ul&gt;`\nlist element that is outside of the\n`&lt;li&gt;`\nlist item matched by the original locator:\n\n```\n`// ✖ WRONGawaitexpect(page.getByRole('listitem').filter({has:page.getByRole('list').getByText('Product 2')})).toHaveCount(1);`\n```", 'Other locators | Playwright', "Playwright supports the\n`:visible`\npseudo class in CSS selectors. For example,\n`css=button`\nmatches all the buttons on the page, while\n`css=button:visible`\nonly matches visible buttons. This is useful to distinguish elements that are very similar but differ in visibility.\n\nConsider a page with two buttons, first invisible and second visible.\n\n```\n`&lt;buttonstyle='display:none'&gt;Invisible&lt;/button&gt;&lt;button&gt;Visible&lt;/button&gt;`\n```\n\nThis will find both buttons and throw a\nstrictness (https://playwright.dev/docs/locators#strictness)\nviolation error:\n```\n`awaitpage.locator('button').click();`\n```\nThis will only find a second button, because it is visible, and then click it.\n```\n`awaitpage.locator('button:visible').click();`\n```", 'The\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\nlocator reflects how users and assistive technology perceive the page, for example whether some element is a button or a checkbox. When locating by role, you should usually pass the accessible name as well, so that the locator pinpoints the exact element.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign up\nSubscribe\nSubmit\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nRole locators include\nbuttons, checkboxes, headings, links, lists, tables, and many more (https://www.w3.org/TR/html-aria/#docconformance)\nand follow W3C specifications for\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. Note that many html elements like\n`&lt;button&gt;`\nhave an\nimplicitly defined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role locator.\n\nNote that role locators\ndo not replace\naccessibility audits and conformance tests, but rather give early feedback about the ARIA guidelines.\n\nWhen to use role locators\nWe recommend prioritizing role locators to locate elements, as it is the closest way to how users and assistive technology perceive the page.', "Find an element by the text it contains. You can match by a substring, exact string, or a regular expression when using\npage.getByText() (https://playwright.dev/docs/api/class-page#page-get-by-text)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nWelcome, John\n```\n`&lt;span&gt;Welcome, John&lt;/span&gt;`\n```\n\nYou can locate the element by the text it contains:\n\n```\n`awaitexpect(page.getByText('Welcome, John')).toBeVisible();`\n```\n\nSet an exact match:\n\n```\n`awaitexpect(page.getByText('Welcome, John',{exact:true})).toBeVisible();`\n```\n\nMatch with a regular expression:\n\n```\n`awaitexpect(page.getByText(/welcome,[A-Za-z]+$/i)).toBeVisible();`\n```\n\nnote\nMatching by text always normalizes whitespace, even with exact match. For example, it turns multiple spaces into one, turns line breaks into spaces and ignores leading and trailing whitespace.\n\nWhen to use text locators\nWe recommend using text locators to find non interactive elements like\n`div`\n,\n`span`\n,\n`p`\n, etc. For interactive elements like\n`button`\n,\n`a`\n,\n`input`\n, etc. use\nrole locators (https://playwright.dev/docs/locators#locate-by-role)\n.\n\nYou can also\nfilter by text (https://playwright.dev/docs/locators#filter-by-text)\nwhich can be useful when trying to find a particular item in a list."]</t>
+          <t>Trace viewer | Playwright</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3712,13 +4340,16 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>To scope your locator correctly, you can use the following approaches based on the provided documentation:
-*   **Use Role Locators:** Playwright recommends prioritizing role locators (e.g., `page.getByRole()`) to pinpoint the exact element, as they reflect how users and assistive technology perceive the page.
-*   **Filter by Child/Descendant:** You can use the `.filter()` method to select elements that have a specific descendant. For example:
-    `await page.locator('...').filter({ has: page.getByRole('button', { name: 'Playwright' }) }).click();`
-*   **Use `:visible`:** If your locator is matching multiple elements because some are hidden, you can append `:visible` to your CSS selector to match only the visible element (e.g., `page.locator('button:visible')`).
-*   **Use Text Locators:** For non-interactive elements, you can use `page.getByText()` instead of a generic CSS selector to be more specific.
-When locating interactive elements like buttons or links, it is recommended to use `page.getByRole()` rather than generic text selectors.</t>
+          <t>The `:has-text("Playwright")` selector matches the `&lt;body&gt;` element because the text "Playwright" is contained within the body's descendant tree, and `:has-text` matches any element that contains the specified text.
+To narrow this to the specific element you want, the documentation recommends prioritizing **role locators** (`page.getByRole()`), as they reflect how users and assistive technology perceive the page. 
+You can refine your selection using the following approaches:
+*   **Use `page.getByRole()`:** Instead of searching by text, identify the element by its role (e.g., 'button', 'link', 'heading') and its accessible name.
+    *   Example: `await page.getByRole('button', { name: 'Playwright' }).click();`
+*   **Chain locators:** You can narrow the search by chaining locators to target a specific part of the page.
+    *   Example: `await page.getByTestId('card-container').getByText('Playwright').click();`
+*   **Filter:** You can use the `.filter()` method to narrow down a locator.
+    *   Example: `await page.locator('div').filter({ hasText: 'Playwright' }).click();`
+Additionally, you can use the **Pick locator** feature in UI Mode to hover over the element in the DOM snapshot, which will help you identify and test a more specific locator before adding it to your code.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3727,24 +4358,30 @@
         </is>
       </c>
       <c r="F60" t="n">
+        <v>0.01180775</v>
+      </c>
+      <c r="G60" t="n">
+        <v>42371</v>
+      </c>
+      <c r="H60" t="n">
         <v>0.5</v>
       </c>
-      <c r="G60" t="n">
+      <c r="I60" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J60" t="n">
+        <v>5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.0918918918918919</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.5151515151515151</v>
+      </c>
+      <c r="M60" t="n">
         <v>0</v>
       </c>
-      <c r="H60" t="n">
-        <v>5</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.07333333333333333</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0.49999999995</v>
-      </c>
-      <c r="L60" t="n">
+      <c r="N60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3760,7 +4397,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>['Auto-waiting | Playwright', 'Added before v1.9\n\npage.waitForFunction\n\nReturns when the\npageFunction (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-expression)\nreturns a truthy value. It resolves to a JSHandle of the truthy value.\n\nUsage\n\nThe\npage.waitForFunction() (https://playwright.dev/docs/api/class-page#page-wait-for-function)\ncan be used to observe viewport size change:\n\n```\n`const{webkit}=require(\'playwright\');// Or \'chromium\' or \'firefox\'.(async()=&gt;{constbrowser=awaitwebkit.launch();constpage=awaitbrowser.newPage();constwatchDog=page.waitForFunction(()=&gt;window.innerWidth&lt;100);awaitpage.setViewportSize({width:50,height:50});awaitwatchDog;awaitbrowser.close();})();`\n```\n\nTo pass an argument to the predicate of\npage.waitForFunction() (https://playwright.dev/docs/api/class-page#page-wait-for-function)\nfunction:\n\n```\n`constselector=\'.foo\';awaitpage.waitForFunction(selector=&gt;!!document.querySelector(selector),selector);`\n```\n\nArguments\n\n`pageFunction`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-expression)\nFunction to be evaluated in the page context.\n`arg`\nEvaluationArgument (https://playwright.dev/docs/evaluating#evaluation-argument)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-arg)\nOptional argument to pass to\npageFunction (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-expression)\n.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`polling`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n| "raf"\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-polling)\nIf\npolling (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-polling)\nis\n`\'raf\'`\n, then\npageFunction (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-expression)\nis constantly executed in\n`requestAnimationFrame`\ncallback. If\npolling (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-polling)\nis a number, then it is treated as an interval in milliseconds at which the function would be executed. Defaults to\n`raf`\n.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-timeout)\nMaximum time to wait for in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`actionTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nJSHandle (https://playwright.dev/docs/api/class-jshandle)\n&gt;\n# (https://playwright.dev/docs/api/class-page#page-wait-for-function-return)', "Locator | Playwright\n\nLocators are the central piece of Playwright's auto-waiting and retry-ability. In a nutshell, locators represent a way to find element(s) on the page at any moment. A locator can be created with the\npage.locator() (https://playwright.dev/docs/api/class-page#page-locator)\nmethod.\n\nLearn more about locators (https://playwright.dev/docs/locators)\n.", 'Locators | Playwright', 'Playwright performs a range of actionability checks on the elements before making actions to ensure these actions behave as expected. It auto-waits for all the relevant checks to pass and only then performs the requested action. If the required checks do not pass within the given\n`timeout`\n, action fails with the\n`TimeoutError`\n.\n\nFor example, for\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\n, Playwright will ensure that:\n\nlocator resolves to exactly one element\nelement is\nVisible (https://playwright.dev/docs/actionability#visible)\nelement is\nStable (https://playwright.dev/docs/actionability#stable)\n, as in not animating or completed animation\nelement\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\n, as in not obscured by other elements\nelement is\nEnabled (https://playwright.dev/docs/actionability#enabled)\n\nHere is the complete list of actionability checks performed for each action:\n\nAction\nVisible (https://playwright.dev/docs/actionability#visible)\nStable (https://playwright.dev/docs/actionability#stable)\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\nEnabled (https://playwright.dev/docs/actionability#enabled)\nEditable (https://playwright.dev/docs/actionability#editable)\nlocator.check() (https://playwright.dev/docs/api/class-locator#locator-check)\nYes\nYes\nYes\nYes\n-\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nYes\nYes\nYes\nYes\n-\nlocator.dblclick() (https://playwright.dev/docs/api/class-locator#locator-dblclick)\nYes\nYes\nYes\nYes\n-\nlocator.setChecked() (https://playwright.dev/docs/api/class-locator#locator-set-checked)\nYes\nYes\nYes\nYes\n-\nlocator.tap() (https://playwright.dev/docs/api/class-locator#locator-tap)\nYes\nYes\nYes\nYes\n-\nlocator.uncheck() (https://playwright.dev/docs/api/class-locator#locator-uncheck)\nYes\nYes\nYes\nYes\n-\nlocator.hover() (https://playwright.dev/docs/api/class-locator#locator-hover)\nYes\nYes\nYes\n-\n-\nlocator.dragTo() (https://playwright.dev/docs/api/class-locator#locator-drag-to)\nYes\nYes\nYes\n-\n-\nlocator.screenshot() (https://playwright.dev/docs/api/class-locator#locator-screenshot)\nYes\nYes\n-\n-\n-\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\nYes\n-\n-\nYes\nYes\nlocator.clear() (https://playwright.dev/docs/api/class-locator#locator-clear)\nYes\n-\n-\nYes\nYes\nlocator.selectOption() (https://playwright.dev/docs/api/class-locator#locator-select-option)\nYes\n-\n-\nYes\n-\nlocator.selectText() (https://playwright.dev/docs/api/class-locator#locator-select-text)\nYes\n-\n-\n-\n-\nlocator.scrollIntoViewIfNeeded() (https://playwright.dev/docs/api/class-locator#locator-scroll-into-view-if-needed)\n-\nYes\n-\n-\n-\nlocator.blur() (https://playwright.dev/docs/api/class-locator#locator-blur)\n-\n-\n-\n-\n-\nlocator.dispatchEvent() (https://playwright.dev/docs/api/class-locator#locator-dispatch-event)\n-\n-\n-\n-\n-\nlocator.focus() (https://playwright.dev/docs/api/class-locator#locator-focus)\n-\n-\n-\n-\n-\nlocator.press() (https://playwright.dev/docs/api/class-locator#locator-press)\n-\n-\n-\n-\n-\nlocator.pressSequentially() (https://playwright.dev/docs/api/class-locator#locator-press-sequentially)\n-\n-\n-\n-\n-\nlocator.setInputFiles() (https://playwright.dev/docs/api/class-locator#locator-set-input-files)\n-\n-\n-\n-\n-', "Page | Playwright\n\nPage provides methods to interact with a single tab in a\nBrowser (https://playwright.dev/docs/api/class-browser)\n, or an\nextension background page (https://developer.chrome.com/extensions/background_pages)\nin Chromium. One\nBrowser (https://playwright.dev/docs/api/class-browser)\ninstance might have multiple\nPage (https://playwright.dev/docs/api/class-page)\ninstances.\n\nThis example creates a page, navigates it to a URL, and then saves a screenshot:\n\n```\n`const{webkit}=require('playwright');// Or 'chromium' or 'firefox'.(async()=&gt;{constbrowser=awaitwebkit.launch();constcontext=awaitbrowser.newContext();constpage=awaitcontext.newPage();awaitpage.goto('https://example.com');awaitpage.screenshot({path:'screenshot.png'});awaitbrowser.close();})();`\n```\n\nThe Page class emits various events (described below) which can be handled using any of Node's native\nEventEmitter (https://nodejs.org/api/events.html#events_class_eventemitter)\nmethods, such as\n`on`\n,\n`once`\nor\n`removeListener`\n.\n\nThis example logs a message for a single page\n`load`\nevent:\n\n```\n`page.once('load',()=&gt;console.log('Page loaded!'));`\n```\n\nTo unsubscribe from events use the\n`removeListener`\nmethod:\n\n```\n`functionlogRequest(interceptedRequest){console.log('A request was made:',interceptedRequest.url());}page.on('request',logRequest);// Sometime later...page.removeListener('request',logRequest);`\n```", 'Writing tests | Playwright']</t>
+          <t>]</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3770,15 +4407,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>To wait for readiness in a single-page app that uses polling or analytics, you can use `page.waitForFunction()`. This method waits until the provided function returns a truthy value.
-For example:
+          <t>To wait for readiness in a way that avoids flakiness, you should use Playwright's auto-retrying assertions instead of `waitForLoadState`.
+Playwright includes async matchers that wait until the expected condition is met. For your specific case, you should use the `toBeVisible()` assertion on your locator:
 ```javascript
 await page.goto('/dashboard');
-// Wait for a specific condition to be true in the page context
-await page.waitForFunction(() =&gt; document.querySelector('.ready-indicator'));
 await expect(page.getByRole('heading', { name: 'Welcome' })).toBeVisible();
 ```
-Additionally, Playwright uses **locators** as the central piece of its auto-waiting and retry-ability. Locators represent a way to find elements on the page at any moment, and Playwright performs actionability checks (such as ensuring an element is visible, stable, and enabled) before performing actions on them.</t>
+**Why this is recommended:**
+*   **Auto-retrying:** These assertions automatically retry until the condition is met, which removes flakiness.
+*   **Resilience:** Unlike `waitForLoadState`, which waits for network activity to cease, assertions focus on the actual state of the UI, making them better suited for single-page applications with ongoing polling or analytics.
+**Alternatives:**
+If you need to wait for a specific condition that is not covered by standard assertions, you can use `page.waitForFunction()`, which executes a function in the page context and returns when it evaluates to a truthy value. Additionally, if you need to wait for a specific network event, you can use `page.waitForResponse()`.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3787,25 +4426,31 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.5</v>
+        <v>0.01280775</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>48161</v>
       </c>
       <c r="H61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.67</v>
       </c>
       <c r="J61" t="n">
-        <v>0.3555555555555556</v>
+        <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>0.9999999999</v>
+        <v>0.08536585365853659</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>0.3111111111111111</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.8333333333055556</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3820,7 +4465,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>["Playwright's built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nallow your tests to natively route requests and perform mocking and interception.\n\nIf you're using Playwright's native\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n, and it appears network events are missing, disable Service Workers by setting\nserviceWorkers (https://playwright.dev/docs/api/class-browser#browser-new-context-option-service-workers)\nto\n`'block'`\n.\n\nIt might be that you are using a mock tool such as Mock Service Worker (MSW). While this tool works out of the box for mocking responses, it adds its own Service Worker that takes over the network requests, hence making them invisible to\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n. If you are interested in both network testing and mocking, consider using built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nfor\nresponse mocking (https://playwright.dev/docs/network#handle-requests)\n.", 'Mock APIs | Playwright', 'Network | Playwright', 'Route | Playwright\n\nWhenever a network route is set up with\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nor\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n, the\n`Route`\nobject allows to handle the route.\n\nLearn more about\nnetworking (https://playwright.dev/docs/network)\n.']</t>
+          <t>["Playwright's built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nallow your tests to natively route requests and perform mocking and interception.\n\nIf you're using Playwright's native\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n, and it appears network events are missing, disable Service Workers by setting\nserviceWorkers (https://playwright.dev/docs/api/class-browser#browser-new-context-option-service-workers)\nto\n`'block'`\n.\n\nIt might be that you are using a mock tool such as Mock Service Worker (MSW). While this tool works out of the box for mocking responses, it adds its own Service Worker that takes over the network requests, hence making them invisible to\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n. If you are interested in both network testing and mocking, consider using built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nfor\nresponse mocking (https://playwright.dev/docs/network#handle-requests)\n.", 'Mock APIs | Playwright', 'Network | Playwright', 'Route | Playwright\n\nWhenever a network route is set up with\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nor\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n, the\n`Route`\nobject allows to handle the route.\n\nLearn more about\nnetworking (https://playwright.dev/docs/network)\n.', 'Service Workers | Playwright', 'Components (experimental) | Playwright']</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3830,8 +4475,8 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>The reason your Playwright route is not firing is that MSW adds its own Service Worker that takes over the network requests. This makes the requests invisible to Playwright's `page.route()` and `browserContext.route()`. 
-If you want to use both network testing and mocking, the provided context suggests considering the use of Playwright's built-in `page.route()` and `browserContext.route()` for response mocking instead.</t>
+          <t>The MSW Service Worker is taking over the network requests, which makes them invisible to Playwright's `page.route()`.
+To resolve this, you should use Playwright's built-in `page.route()` or `browserContext.route()` for response mocking instead of MSW. If you must use MSW and are experiencing missing network events, you can disable Service Workers by setting `serviceWorkers` to `'block'` in your browser context options.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3840,39 +4485,45 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>0.008536249999999001</v>
       </c>
       <c r="G62" t="n">
-        <v>0.86</v>
+        <v>32875</v>
       </c>
       <c r="H62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.196969696969697</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3333333333333333</v>
+        <v>5</v>
       </c>
       <c r="K62" t="n">
+        <v>0.1515151515151515</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="M62" t="n">
         <v>0.9999999999</v>
       </c>
-      <c r="L62" t="n">
+      <c r="N62" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>I target a label to assert the input's value, but it asserts the label text instead. Code:
-// &lt;label for="password"&gt;Password:&lt;/label&gt;&lt;input id="password" type="password"&gt;
+          <t>Our password field test asserts on the wrong thing and I can't see why. The page is a plain label plus input; filling by the same target works perfectly, which is what's throwing me — if the label weren't resolving to the control, `fill` wouldn't work either.
+// &lt;label for="password"&gt;Password&lt;/label&gt;&lt;input id="password" type="password"&gt;
 await expect(page.locator('label')).toHaveText('Password');
-Why doesn't toHaveText read the input value?</t>
+The assertion passes against the caption text rather than reading the value I typed into the field. Why does one operation follow the association and the other doesn't?</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>["LocatorAssertions | Playwright\n\nThe\nLocatorAssertions (https://playwright.dev/docs/api/class-locatorassertions)\nclass provides assertion methods that can be used to make assertions about the\nLocator (https://playwright.dev/docs/api/class-locator)\nstate in the tests.\n\n```\n`import{test,expect}from'@playwright/test';test('status becomes submitted',async({page})=&gt;{// ...awaitpage.getByRole('button').click();awaitexpect(page.locator('.status')).toHaveText('Submitted');});`\n```", "Added in: v1.20\n\nlocatorAssertions.toHaveText\n\nEnsures the\nLocator (https://playwright.dev/docs/api/class-locator)\npoints to an element with the given text. All nested elements will be considered when computing the text content of the element. You can use regular expressions for the value as well.\n\nUsage\n\n```\n`constlocator=page.locator('.title');awaitexpect(locator).toHaveText(/Welcome, Test User/);awaitexpect(locator).toHaveText(/Welcome,.*/);`\n```\n\nIf you pass an array as an expected value, the expectations are:\n\nLocator resolves to a list of elements.\nThe number of elements equals the number of expected values in the array.\nElements from the list have text matching expected array values, one by one, in order.\n\nFor example, consider the following list:\n\n```\n`&lt;ul&gt;&lt;li&gt;Text 1&lt;/li&gt;&lt;li&gt;Text 2&lt;/li&gt;&lt;li&gt;Text 3&lt;/li&gt;&lt;/ul&gt;`\n```\n\nLet's see how we can use the assertion:\n\n```\n`// ✓ Has the right items in the right orderawaitexpect(page.locator('ul &gt; li')).toHaveText(['Text 1','Text 2','Text 3']);// ✖ Wrong orderawaitexpect(page.locator('ul &gt; li')).toHaveText(['Text 3','Text 2','Text 1']);// ✖ Last item does not matchawaitexpect(page.locator('ul &gt; li')).toHaveText(['Text 1','Text 2','Text']);// ✖ Locator points to the outer list element, not to the list itemsawaitexpect(page.locator('ul')).toHaveText(['Text 1','Text 2','Text 3']);`\n```\n\nArguments\n\n`expected`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n|\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n&gt;\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text-option-expected)\nExpected string or RegExp or a list of those.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`ignoreCase`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.23\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text-option-ignore-case)\nWhether to perform case-insensitive match.\nignoreCase (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text-option-ignore-case)\noption takes precedence over the corresponding regular expression flag if specified.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text-option-timeout)\nTime to retry the assertion for in milliseconds. Defaults to\n`timeout`\nin\n`TestConfig.expect`\n.\n`useInnerText`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text-option-use-inner-text)\nWhether to use\n`element.innerText`\ninstead of\n`element.textContent`\nwhen retrieving DOM node text.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text-return)\n\nDetails\n\nWhen\n`expected`\nparameter is a string, Playwright will normalize whitespaces and line breaks both in the actual text and in the expected string before matching. When regular expression is used, the actual text is matched as is.", "Added in: v1.20\n\nlocatorAssertions.toHaveValue\n\nEnsures the\nLocator (https://playwright.dev/docs/api/class-locator)\npoints to an element with the given input value. You can use regular expressions for the value as well.\n\nUsage\n\n```\n`constlocator=page.locator('input[type=number]');awaitexpect(locator).toHaveValue(/[0-9]/);`\n```\n\nArguments\n\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value-option-value)\nExpected value.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value-option-timeout)\nTime to retry the assertion for in milliseconds. Defaults to\n`timeout`\nin\n`TestConfig.expect`\n.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value-return)", "Locator | Playwright\n\nLocators are the central piece of Playwright's auto-waiting and retry-ability. In a nutshell, locators represent a way to find element(s) on the page at any moment. A locator can be created with the\npage.locator() (https://playwright.dev/docs/api/class-page#page-locator)\nmethod.\n\nLearn more about locators (https://playwright.dev/docs/locators)\n.", 'Playwright includes\ntest assertions (https://playwright.dev/docs/test-assertions)\nin the form of\n`expect`\nfunction. To make an assertion, call\n`expect(value)`\nand choose a matcher that reflects the expectation.\n\nPlaywright includes async matchers that wait until the expected condition is met. Using these matchers makes tests non-flaky and resilient. For example, this code waits until the page gets the title containing "Playwright":\n\n```\n`awaitexpect(page).toHaveTitle(/Playwright/);`\n```\n\nHere are the most popular async assertions. For the complete list, see\nassertions guide (https://playwright.dev/docs/test-assertions)\n:\n\nAssertion\nDescription\nexpect(locator).toBeChecked() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-checked)\nCheckbox is checked\nexpect(locator).toBeEnabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-enabled)\nControl is enabled\nexpect(locator).toBeVisible() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-visible)\nElement is visible\nexpect(locator).toContainText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-text)\nElement contains text\nexpect(locator).toHaveAttribute() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-attribute)\nElement has attribute\nexpect(locator).toHaveCount() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-count)\nList of elements has given length\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nElement matches text\nexpect(locator).toHaveValue() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value)\nInput element has value\nexpect(page).toHaveTitle() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-title)\nPage has title\nexpect(page).toHaveURL() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-url)\nPage has URL\n\nPlaywright also includes generic matchers like\n`toEqual`\n,\n`toContain`\n,\n`toBeTruthy`\nthat can be used to assert any conditions. These assertions do not use the\n`await`\nkeyword as they perform immediate synchronous checks on already available values.\n\n```\n`expect(success).toBeTruthy();`\n```', 'Actions | Playwright']</t>
+          <t>['warning\nWe recommend\nlocating by label text (https://playwright.dev/docs/locators#locate-by-label)\ninstead of relying to label-to-control retargeting.\n\nTargeted input actions in Playwright automatically distinguish between labels and controls, so you can target the label to perform an action on the associated control.\n\nFor example, consider the following DOM structure:\n`&lt;label for="password"&gt;Password:&lt;/label&gt;&lt;input id="password" type="password"&gt;`\n. You can target the label by its "Password" text using\npage.getByText() (https://playwright.dev/docs/api/class-page#page-get-by-text)\n. However, the following actions will be performed on the input instead of the label:\n\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nwill click the label and automatically focus the input field;\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\nwill fill the input field;\nlocator.inputValue() (https://playwright.dev/docs/api/class-locator#locator-input-value)\nwill return the value of the input field;\nlocator.selectText() (https://playwright.dev/docs/api/class-locator#locator-select-text)\nwill select text in the input field;\nlocator.setInputFiles() (https://playwright.dev/docs/api/class-locator#locator-set-input-files)\nwill set files for the input field with\n`type=file`\n;\nlocator.selectOption() (https://playwright.dev/docs/api/class-locator#locator-select-option)\nwill select an option from the select box.\n\n```\n`// Fill the input by targeting the label.awaitpage.getByText(\'Password\').fill(\'secret\');`\n```\n\nHowever, other methods will target the label itself, for example\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nwill assert the text content of the label, not the input field.\n\n```\n`// Fill the input by targeting the label.awaitexpect(page.locator(\'label\')).toHaveText(\'Password\');`\n```', "LocatorAssertions | Playwright\n\nThe\nLocatorAssertions (https://playwright.dev/docs/api/class-locatorassertions)\nclass provides assertion methods that can be used to make assertions about the\nLocator (https://playwright.dev/docs/api/class-locator)\nstate in the tests.\n\n```\n`import{test,expect}from'@playwright/test';test('status becomes submitted',async({page})=&gt;{// ...awaitpage.getByRole('button').click();awaitexpect(page.locator('.status')).toHaveText('Submitted');});`\n```", "Added in: v1.20\n\nlocatorAssertions.toHaveText\n\nEnsures the\nLocator (https://playwright.dev/docs/api/class-locator)\npoints to an element with the given text. All nested elements will be considered when computing the text content of the element. You can use regular expressions for the value as well.\n\nUsage\n\n```\n`constlocator=page.locator('.title');awaitexpect(locator).toHaveText(/Welcome, Test User/);awaitexpect(locator).toHaveText(/Welcome,.*/);`\n```\n\nIf you pass an array as an expected value, the expectations are:\n\nLocator resolves to a list of elements.\nThe number of elements equals the number of expected values in the array.\nElements from the list have text matching expected array values, one by one, in order.\n\nFor example, consider the following list:\n\n```\n`&lt;ul&gt;&lt;li&gt;Text 1&lt;/li&gt;&lt;li&gt;Text 2&lt;/li&gt;&lt;li&gt;Text 3&lt;/li&gt;&lt;/ul&gt;`\n```\n\nLet's see how we can use the assertion:\n\n```\n`// ✓ Has the right items in the right orderawaitexpect(page.locator('ul &gt; li')).toHaveText(['Text 1','Text 2','Text 3']);// ✖ Wrong orderawaitexpect(page.locator('ul &gt; li')).toHaveText(['Text 3','Text 2','Text 1']);// ✖ Last item does not matchawaitexpect(page.locator('ul &gt; li')).toHaveText(['Text 1','Text 2','Text']);// ✖ Locator points to the outer list element, not to the list itemsawaitexpect(page.locator('ul')).toHaveText(['Text 1','Text 2','Text 3']);`\n```\n\nArguments\n\n`expected`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n|\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n&gt;\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text-option-expected)\nExpected string or RegExp or a list of those.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`ignoreCase`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.23\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text-option-ignore-case)\nWhether to perform case-insensitive match.\nignoreCase (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text-option-ignore-case)\noption takes precedence over the corresponding regular expression flag if specified.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text-option-timeout)\nTime to retry the assertion for in milliseconds. Defaults to\n`timeout`\nin\n`TestConfig.expect`\n.\n`useInnerText`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text-option-use-inner-text)\nWhether to use\n`element.innerText`\ninstead of\n`element.textContent`\nwhen retrieving DOM node text.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text-return)\n\nDetails\n\nWhen\n`expected`\nparameter is a string, Playwright will normalize whitespaces and line breaks both in the actual text and in the expected string before matching. When regular expression is used, the actual text is matched as is.", "Added in: v1.20\n\nlocatorAssertions.toHaveValue\n\nEnsures the\nLocator (https://playwright.dev/docs/api/class-locator)\npoints to an element with the given input value. You can use regular expressions for the value as well.\n\nUsage\n\n```\n`constlocator=page.locator('input[type=number]');awaitexpect(locator).toHaveValue(/[0-9]/);`\n```\n\nArguments\n\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value-option-value)\nExpected value.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value-option-timeout)\nTime to retry the assertion for in milliseconds. Defaults to\n`timeout`\nin\n`TestConfig.expect`\n.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value-return)", 'Other locators | Playwright', "These are the recommended built-in locators.\n\npage.getByRole() (https://playwright.dev/docs/locators#locate-by-role)\nto locate by explicit and implicit accessibility attributes.\npage.getByText() (https://playwright.dev/docs/locators#locate-by-text)\nto locate by text content.\npage.getByLabel() (https://playwright.dev/docs/locators#locate-by-label)\nto locate a form control by associated label's text.\npage.getByPlaceholder() (https://playwright.dev/docs/locators#locate-by-placeholder)\nto locate an input by placeholder.\npage.getByAltText() (https://playwright.dev/docs/locators#locate-by-alt-text)\nto locate an element, usually image, by its text alternative.\npage.getByTitle() (https://playwright.dev/docs/locators#locate-by-title)\nto locate an element by its title attribute.\npage.getByTestId() (https://playwright.dev/docs/locators#locate-by-test-id)\nto locate an element based on its\n`data-testid`\nattribute (other attributes can be configured).\n\n```\n`awaitpage.getByLabel('User Name').fill('John');awaitpage.getByLabel('Password').fill('secret-password');awaitpage.getByRole('button',{name:'Sign in'}).click();awaitexpect(page.getByText('Welcome, John!')).toBeVisible();`\n```"]</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3882,8 +4533,15 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>The `toHaveText` assertion is designed to ensure that a locator points to an element with specific text content. Because you are targeting a `&lt;label&gt;` element, `toHaveText` reads the text content of that label.
-To assert the value of an input element, you should use the `toHaveValue` assertion instead, which is specifically designed to ensure that a locator points to an element with a given input value.</t>
+          <t>Targeted input actions, such as `fill()`, automatically distinguish between labels and controls, allowing you to target the label to perform the action on the associated input field. However, `expect(locator).toHaveText()` targets the label itself and asserts the text content of the label, not the value of the associated input field.
+To assert the value of the input field, you should use `expect(locator).toHaveValue()`.
+Additionally, the documentation recommends locating by label text using `page.getByLabel()` instead of relying on label-to-control retargeting. You can update your test to use this approach:
+```javascript
+// Fill the input
+await page.getByLabel('Password').fill('secret');
+// Assert the input value
+await expect(page.getByLabel('Password')).toHaveValue('secret');
+```</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3892,25 +4550,31 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0.011554</v>
       </c>
       <c r="G63" t="n">
-        <v>0.29</v>
+        <v>43946</v>
       </c>
       <c r="H63" t="n">
-        <v>5</v>
+        <v>0.75</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.67</v>
       </c>
       <c r="J63" t="n">
-        <v>0.2631578947368421</v>
+        <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>0.19999999998</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>0.631578947368421</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.7222222221981481</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -3924,7 +4588,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>['Events | Playwright', "You can monitor all the\nRequest (https://playwright.dev/docs/api/class-request)\ns and\nResponse (https://playwright.dev/docs/api/class-response)\ns:\n\n```\n`// Subscribe to 'request' and 'response' events.page.on('request',request=&gt;console.log('&gt;&gt;',request.method(),request.url()));page.on('response',response=&gt;console.log('&lt;&lt;',response.status(),response.url()));awaitpage.goto('https://example.com');`\n```\n\nOr wait for a network response after the button click with\npage.waitForResponse() (https://playwright.dev/docs/api/class-page#page-wait-for-response)\n:\n\n```\n`// Use a glob URL pattern. Note no await.constresponsePromise=page.waitForResponse('**/api/fetch_data');awaitpage.getByText('Update').click();constresponse=awaitresponsePromise;`\n```", 'Network | Playwright', "Wait for\nResponse (https://playwright.dev/docs/api/class-response)\ns with\npage.waitForResponse() (https://playwright.dev/docs/api/class-page#page-wait-for-response)\n\n```\n`// Use a RegExp. Note no await.constresponsePromise=page.waitForResponse(/\\.jpeg$/);awaitpage.getByText('Update').click();constresponse=awaitresponsePromise;// Use a predicate taking a Response object. Note no await.constresponsePromise=page.waitForResponse(response=&gt;response.url().includes(token));awaitpage.getByText('Update').click();constresponse=awaitresponsePromise;`\n```"]</t>
+          <t>['Events | Playwright', "Wait for\nResponse (https://playwright.dev/docs/api/class-response)\ns with\npage.waitForResponse() (https://playwright.dev/docs/api/class-page#page-wait-for-response)\n\n```\n`// Use a RegExp. Note no await.constresponsePromise=page.waitForResponse(/\\.jpeg$/);awaitpage.getByText('Update').click();constresponse=awaitresponsePromise;// Use a predicate taking a Response object. Note no await.constresponsePromise=page.waitForResponse(response=&gt;response.url().includes(token));awaitpage.getByText('Update').click();constresponse=awaitresponsePromise;`\n```", 'Network | Playwright', "Page | Playwright\n\nPage provides methods to interact with a single tab in a\nBrowser (https://playwright.dev/docs/api/class-browser)\n, or an\nextension background page (https://developer.chrome.com/extensions/background_pages)\nin Chromium. One\nBrowser (https://playwright.dev/docs/api/class-browser)\ninstance might have multiple\nPage (https://playwright.dev/docs/api/class-page)\ninstances.\n\nThis example creates a page, navigates it to a URL, and then saves a screenshot:\n\n```\n`const{webkit}=require('playwright');// Or 'chromium' or 'firefox'.(async()=&gt;{constbrowser=awaitwebkit.launch();constcontext=awaitbrowser.newContext();constpage=awaitcontext.newPage();awaitpage.goto('https://example.com');awaitpage.screenshot({path:'screenshot.png'});awaitbrowser.close();})();`\n```\n\nThe Page class emits various events (described below) which can be handled using any of Node's native\nEventEmitter (https://nodejs.org/api/events.html#events_class_eventemitter)\nmethods, such as\n`on`\n,\n`once`\nor\n`removeListener`\n.\n\nThis example logs a message for a single page\n`load`\nevent:\n\n```\n`page.once('load',()=&gt;console.log('Page loaded!'));`\n```\n\nTo unsubscribe from events use the\n`removeListener`\nmethod:\n\n```\n`functionlogRequest(interceptedRequest){console.log('A request was made:',interceptedRequest.url());}page.on('request',logRequest);// Sometime later...page.removeListener('request',logRequest);`\n```", "You can monitor all the\nRequest (https://playwright.dev/docs/api/class-request)\ns and\nResponse (https://playwright.dev/docs/api/class-response)\ns:\n\n```\n`// Subscribe to 'request' and 'response' events.page.on('request',request=&gt;console.log('&gt;&gt;',request.method(),request.url()));page.on('response',response=&gt;console.log('&lt;&lt;',response.status(),response.url()));awaitpage.goto('https://example.com');`\n```\n\nOr wait for a network response after the button click with\npage.waitForResponse() (https://playwright.dev/docs/api/class-page#page-wait-for-response)\n:\n\n```\n`// Use a glob URL pattern. Note no await.constresponsePromise=page.waitForResponse('**/api/fetch_data');awaitpage.getByText('Update').click();constresponse=awaitresponsePromise;`\n```", "Most of the time, scripts will need to wait for a particular event to happen. Below are some of the typical event awaiting patterns.\n\nWait for a request with the specified url using\npage.waitForRequest() (https://playwright.dev/docs/api/class-page#page-wait-for-request)\n:\n\n```\n`// Start waiting for request before goto. Note no await.constrequestPromise=page.waitForRequest('**/*logo*.png');awaitpage.goto('https://wikipedia.org');constrequest=awaitrequestPromise;console.log(request.url());`\n```\n\nWait for popup window:\n\n```\n`// Start waiting for popup before clicking. Note no await.constpopupPromise=page.waitForEvent('popup');awaitpage.getByText('open the popup').click();constpopup=awaitpopupPromise;awaitpopup.goto('https://wikipedia.org');`\n```"]</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3934,16 +4598,15 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>The correct pattern is to define the `waitForResponse` promise **before** performing the action that triggers the network request, and then await the promise after the action. You must not await the `waitForResponse` call until after the action has been triggered.
-Example:
+          <t>To avoid the race condition where the response arrives before you subscribe, you must initiate the `page.waitForResponse()` call **without** using `await` before performing the action that triggers the network request.
+The correct pattern is:
 ```javascript
-// Define the promise first (note no await)
+// Start waiting for the response before clicking. Note no await.
 const responsePromise = page.waitForResponse('**/api/fetch_data');
-// Perform the action
 await page.getByText('Update').click();
-// Await the promise
 const response = await responsePromise;
-```</t>
+```
+By assigning the promise to a variable first, you ensure the listener is registered before the click action executes.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3952,40 +4615,46 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0.008415750000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>0.86</v>
+        <v>32428</v>
       </c>
       <c r="H64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2816901408450704</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
+        <v>5</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.2469135802469136</v>
+      </c>
+      <c r="L64" t="n">
         <v>0.4878048780487805</v>
       </c>
-      <c r="K64" t="n">
-        <v>0.499999999975</v>
-      </c>
-      <c r="L64" t="n">
+      <c r="M64" t="n">
+        <v>0.4666666666511111</v>
+      </c>
+      <c r="N64" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>My inactivity-logout test would take 5 real minutes. Code:
+          <t>We have a security requirement that an idle session is signed out after five minutes, and QA currently verifies it by hand because nobody wants a test that sits there for five real minutes — with the suite's own limits it couldn't complete anyway. The behaviour is driven by a timer the app sets on load.
 await page.goto('http://localhost:3333');
 await page.getByRole('button').click();
-// how do I jump ahead 5 minutes?
-How can I fast-forward time so the timers fire immediately?</t>
+// user goes idle here...
+Is there a way to convince the page that five minutes have gone by, so the timer fires and I can assert we've been kicked out?</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>['Clock | Playwright\n\nAccurately simulating time-dependent behavior is essential for verifying the correctness of applications. Learn more about\nclock emulation (https://playwright.dev/docs/clock)\n.\n\nNote that clock is installed for the entire\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\n, so the time in all the pages and iframes is controlled by the same clock.', 'Clock | Playwright', 'Inactivity monitoring is a common feature in web applications that logs out users after a period of inactivity. Testing this feature can be tricky because you need to wait for a long time to see the effect. With the help of the clock, you can speed up time and test this feature quickly.\n\n```\n`&lt;divid="remaining-time"data-testid="remaining-time"&gt;&lt;/div&gt;&lt;script&gt;constendTime=Date.now()+5*60_000;constrenderTime=()=&gt;{constdiffInSeconds=Math.round((endTime-Date.now())/1000);if(diffInSeconds&lt;=0){document.getElementById(\'remaining-time\').textContent=\'You have been logged out due to inactivity.\';}else{document.getElementById(\'remaining-time\').textContent=`You will be logged out in${diffInSeconds}seconds.`;}setTimeout(renderTime,1000);};renderTime();&lt;/script&gt;&lt;buttontype="button"&gt;Interaction&lt;/button&gt;`\n```\n\n```\n`// Initial time does not matter for the test, so we can pick current time.awaitpage.clock.install();awaitpage.goto(\'http://localhost:3333\');// Interact with the pageawaitpage.getByRole(\'button\').click();// Fast forward time 5 minutes as if the user did not do anything.// Fast forward is like closing the laptop lid and opening it after 5 minutes.// All the timers due will fire once immediately, as in the real browser.awaitpage.clock.fastForward(\'05:00\');// Check that the user was logged out automatically.awaitexpect(page.getByText(\'You have been logged out due to inactivity.\')).toBeVisible();`\n```', 'Added in: v1.45\n\nclock.fastForward\n\nAdvance the clock by jumping forward in time. Only fires due timers at most once. This is equivalent to user closing the laptop lid for a while and reopening it later, after given time.\n\nUsage\n\n```\n`awaitpage.clock.fastForward(1000);awaitpage.clock.fastForward(\'30:00\');`\n```\n\nArguments\n\n`ticks`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-clock#clock-fast-forward-option-ticks)\nTime may be the number of milliseconds to advance the clock by or a human-readable string. Valid string formats are "08" for eight seconds, "01:00" for one minute and "02:34:10" for two hours, 34 minutes and ten seconds.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-clock#clock-fast-forward-return)', 'Sometimes your timers depend on\n`Date.now`\nand are confused when the\n`Date.now`\nvalue does not change over time. In this case, you can install the clock and fast forward to the time of interest when testing.\n\n```\n`&lt;divid="current-time"data-testid="current-time"&gt;&lt;/div&gt;&lt;script&gt;constrenderTime=()=&gt;{document.getElementById(\'current-time\').textContent=newDate().toLocaleString();};setInterval(renderTime,1000);&lt;/script&gt;`\n```\n\n```\n`// Initialize clock with some time before the test time and let the page load// naturally. `Date.now` will progress as the timers fire.awaitpage.clock.install({time:newDate(\'2024-02-02T08:00:00\')});awaitpage.goto(\'http://localhost:3333\');// Pretend that the user closed the laptop lid and opened it again at 10am,// Pause the time once reached that point.awaitpage.clock.pauseAt(newDate(\'2024-02-02T10:00:00\'));// Assert the page state.awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:00:00 AM\');// Close the laptop lid again and open it at 10:30am.awaitpage.clock.fastForward(\'30:00\');awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:30:00 AM\');`\n```', 'Added in: v1.45\n\nclock.runFor\n\nAdvance the clock, firing all the time-related callbacks.\n\nUsage\n\n```\n`awaitpage.clock.runFor(1000);awaitpage.clock.runFor(\'30:00\');`\n```\n\nArguments\n\n`ticks`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-clock#clock-run-for-option-ticks)\nTime may be the number of milliseconds to advance the clock by or a human-readable string. Valid string formats are "08" for eight seconds, "01:00" for one minute and "02:34:10" for two hours, 34 minutes and ten seconds.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-clock#clock-run-for-return)', 'In rare cases, you may want to tick through time manually, firing all timers and animation frames in the process to achieve a fine-grained control over the passage of time.\n\n```\n`&lt;divid="current-time"data-testid="current-time"&gt;&lt;/div&gt;&lt;script&gt;constrenderTime=()=&gt;{document.getElementById(\'current-time\').textContent=newDate().toLocaleString();};setInterval(renderTime,1000);&lt;/script&gt;`\n```\n\n```\n`// Initialize clock with a specific time, let the page load naturally.awaitpage.clock.install({time:newDate(\'2024-02-02T08:00:00\')});awaitpage.goto(\'http://localhost:3333\');// Pause the time flow, stop the timers, you now have manual control// over the page time.awaitpage.clock.pauseAt(newDate(\'2024-02-02T10:00:00\'));awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:00:00 AM\');// Tick through time manually, firing all timers in the process.// In this case, time will be updated in the screen 2 times.awaitpage.clock.runFor(2000);awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:00:02 AM\');`\n```']</t>
+          <t>['Clock | Playwright', 'Inactivity monitoring is a common feature in web applications that logs out users after a period of inactivity. Testing this feature can be tricky because you need to wait for a long time to see the effect. With the help of the clock, you can speed up time and test this feature quickly.\n\n```\n`&lt;divid="remaining-time"data-testid="remaining-time"&gt;&lt;/div&gt;&lt;script&gt;constendTime=Date.now()+5*60_000;constrenderTime=()=&gt;{constdiffInSeconds=Math.round((endTime-Date.now())/1000);if(diffInSeconds&lt;=0){document.getElementById(\'remaining-time\').textContent=\'You have been logged out due to inactivity.\';}else{document.getElementById(\'remaining-time\').textContent=`You will be logged out in${diffInSeconds}seconds.`;}setTimeout(renderTime,1000);};renderTime();&lt;/script&gt;&lt;buttontype="button"&gt;Interaction&lt;/button&gt;`\n```\n\n```\n`// Initial time does not matter for the test, so we can pick current time.awaitpage.clock.install();awaitpage.goto(\'http://localhost:3333\');// Interact with the pageawaitpage.getByRole(\'button\').click();// Fast forward time 5 minutes as if the user did not do anything.// Fast forward is like closing the laptop lid and opening it after 5 minutes.// All the timers due will fire once immediately, as in the real browser.awaitpage.clock.fastForward(\'05:00\');// Check that the user was logged out automatically.awaitexpect(page.getByText(\'You have been logged out due to inactivity.\')).toBeVisible();`\n```', 'Sometimes your timers depend on\n`Date.now`\nand are confused when the\n`Date.now`\nvalue does not change over time. In this case, you can install the clock and fast forward to the time of interest when testing.\n\n```\n`&lt;divid="current-time"data-testid="current-time"&gt;&lt;/div&gt;&lt;script&gt;constrenderTime=()=&gt;{document.getElementById(\'current-time\').textContent=newDate().toLocaleString();};setInterval(renderTime,1000);&lt;/script&gt;`\n```\n\n```\n`// Initialize clock with some time before the test time and let the page load// naturally. `Date.now` will progress as the timers fire.awaitpage.clock.install({time:newDate(\'2024-02-02T08:00:00\')});awaitpage.goto(\'http://localhost:3333\');// Pretend that the user closed the laptop lid and opened it again at 10am,// Pause the time once reached that point.awaitpage.clock.pauseAt(newDate(\'2024-02-02T10:00:00\'));// Assert the page state.awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:00:00 AM\');// Close the laptop lid again and open it at 10:30am.awaitpage.clock.fastForward(\'30:00\');awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:30:00 AM\');`\n```', 'In rare cases, you may want to tick through time manually, firing all timers and animation frames in the process to achieve a fine-grained control over the passage of time.\n\n```\n`&lt;divid="current-time"data-testid="current-time"&gt;&lt;/div&gt;&lt;script&gt;constrenderTime=()=&gt;{document.getElementById(\'current-time\').textContent=newDate().toLocaleString();};setInterval(renderTime,1000);&lt;/script&gt;`\n```\n\n```\n`// Initialize clock with a specific time, let the page load naturally.awaitpage.clock.install({time:newDate(\'2024-02-02T08:00:00\')});awaitpage.goto(\'http://localhost:3333\');// Pause the time flow, stop the timers, you now have manual control// over the page time.awaitpage.clock.pauseAt(newDate(\'2024-02-02T10:00:00\'));awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:00:00 AM\');// Tick through time manually, firing all timers in the process.// In this case, time will be updated in the screen 2 times.awaitpage.clock.runFor(2000);awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:00:02 AM\');`\n```', "Accurately simulating time-dependent behavior is essential for verifying the correctness of applications. Utilizing\nClock (https://playwright.dev/docs/api/class-clock)\nfunctionality allows developers to manipulate and control time within tests, enabling the precise validation of features such as rendering time, timeouts, scheduled tasks without the delays and variability of real-time execution.\n\nThe\nClock (https://playwright.dev/docs/api/class-clock)\nAPI provides the following methods to control time:\n\n`setFixedTime`\n: Sets the fixed time for\n`Date.now()`\nand\n`new Date()`\n.\n`install`\n: initializes the clock and allows you to:\n`pauseAt`\n: Pauses the time at a specific time.\n`fastForward`\n: Fast forwards the time.\n`runFor`\n: Runs the time for a specific duration.\n`resume`\n: Resumes the time.\n`setSystemTime`\n: Sets the current system time.\n\nThe recommended approach is to use\n`setFixedTime`\nto set the time to a specific value. If that doesn't work for your use case, you can use\n`install`\nwhich allows you to pause time later on, fast forward it, tick it, etc.\n`setSystemTime`\nis only recommended for advanced use cases.\n\nnote\npage.clock (https://playwright.dev/docs/api/class-page#page-clock)\noverrides native global classes and functions related to time allowing them to be manually controlled:\n`Date`\n`setTimeout`\n`clearTimeout`\n`setInterval`\n`clearInterval`\n`requestAnimationFrame`\n`cancelAnimationFrame`\n`requestIdleCallback`\n`cancelIdleCallback`\n`performance`\n`Event.timeStamp`\n\nwarning\nIf you call\n`install`\nat any point in your test, the call\nMUST\noccur before any other clock related calls (see note above for list). Calling these methods out of order will result in undefined behavior. For example, you cannot call\n`setInterval`\n, followed by\n`install`\n, then\n`clearInterval`\n, as\n`install`\noverrides the native definition of the clock functions."]</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3995,15 +4664,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>To fast-forward time by 5 minutes, you must first install the clock and then use the `page.clock.fastForward` method.
-Here is how you would update your code:
+          <t>Yes, you can use the Playwright `clock` API to simulate the passage of time and trigger the inactivity timer.
+To do this, you must first initialize the clock using `page.clock.install()`. You should call this before navigating to the page. Once the page is loaded and the user interaction has occurred, you can use `page.clock.fastForward()` to simulate the five-minute wait.
+Here is how you can update your test:
 ```javascript
+// Initialize the clock before navigating
 await page.clock.install();
 await page.goto('http://localhost:3333');
 await page.getByRole('button').click();
-// Fast forward time 5 minutes
+// Fast forward time by 5 minutes
 await page.clock.fastForward('05:00');
-```</t>
+// Assert that the user was logged out
+await expect(page.getByText('You have been logged out due to inactivity.')).toBeVisible();
+```
+**Important considerations:**
+*   **Order of operations:** You must call `page.clock.install()` before any other clock-related calls or interactions that rely on time-dependent functions (such as `setTimeout` or `setInterval`), as it overrides native global time functions.
+*   **Mechanism:** `fastForward` acts as if the laptop lid was closed and opened after the specified duration, causing all pending timers to fire immediately.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4012,24 +4688,30 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0.008061500000000001</v>
       </c>
       <c r="G65" t="n">
+        <v>30021</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
         <v>0</v>
       </c>
-      <c r="H65" t="n">
-        <v>5</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.1428571428571428</v>
-      </c>
       <c r="J65" t="n">
-        <v>0.2424242424242424</v>
+        <v>5</v>
       </c>
       <c r="K65" t="n">
+        <v>0.06486486486486487</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="M65" t="n">
         <v>0.99999999998</v>
       </c>
-      <c r="L65" t="n">
+      <c r="N65" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4045,7 +4727,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>['Authentication | Playwright', "You can reset storage state in a test file to avoid authentication that was set up for the whole project.\n\nnot-signed-in.spec.ts\n```\n`import{test}from'@playwright/test';// Reset storage state for this file to avoid being authenticatedtest.use({storageState:{cookies:[],origins:[]}});test('not signed in test',async({page})=&gt;{// ...});`\n```", 'Configuration (use) | Playwright']</t>
+          <t>["You can reset storage state in a test file to avoid authentication that was set up for the whole project.\n\nnot-signed-in.spec.ts\n```\n`import{test}from'@playwright/test';// Reset storage state for this file to avoid being authenticatedtest.use({storageState:{cookies:[],origins:[]}});test('not signed in test',async({page})=&gt;{// ...});`\n```", "In addition to creating your own fixtures, you can also override existing fixtures to fit your needs. Consider the following example which overrides the\n`page`\nfixture by automatically navigating to the\n`baseURL`\n:\n\n```\n`import{testasbase}from'@playwright/test';exportconsttest=base.extend({page:async({baseURL,page},use)=&gt;{awaitpage.goto(baseURL);awaituse(page);},});`\n```\n\nNotice that in this example, the\n`page`\nfixture is able to depend on other built-in fixtures such as\ntestOptions.baseURL (https://playwright.dev/docs/api/class-testoptions#test-options-base-url)\n. We can now configure\n`baseURL`\nin the configuration file, or locally in the test file with\ntest.use() (https://playwright.dev/docs/api/class-test#test-use)\n.\n\nexample.spec.ts\n```\n`test.use({baseURL:'https://playwright.dev'});`\n```\n\nFixtures can also be overridden, causing the base fixture to be completely replaced with something different. For example, we could override the\ntestOptions.storageState (https://playwright.dev/docs/api/class-testoptions#test-options-storage-state)\nfixture to provide our own data.\n\n```\n`import{testasbase}from'@playwright/test';exportconsttest=base.extend({storageState:async({},use)=&gt;{constcookie=awaitgetAuthCookie();awaituse({cookies:[cookie]});},});`\n```"]</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4055,8 +4737,8 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>To reset authentication for a specific test file, you can use `test.use` to override the `storageState` with empty cookies and origins:
-```javascript
+          <t>To reset the authentication for a specific test file, use `test.use()` to set `storageState` to an empty object containing empty arrays for cookies and origins:
+```typescript
 import { test } from '@playwright/test';
 // Reset storage state for this file to avoid being authenticated
 test.use({ storageState: { cookies: [], origins: [] } });
@@ -4072,24 +4754,30 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>0.01042475</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>40294</v>
       </c>
       <c r="H66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
+        <v>5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.1851851851851852</v>
+      </c>
+      <c r="L66" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="K66" t="n">
-        <v>0.49999999995</v>
-      </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="N66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4105,7 +4793,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>['Authentication | Playwright', "This is the\nrecommended\napproach for tests that\nmodify server-side state\n. In Playwright, worker processes run in parallel. In this approach, each parallel worker is authenticated once. All tests ran by worker are reusing the same authentication state. We will need multiple testing accounts, one per each parallel worker.\n\nWhen to use\n\nYour tests modify shared server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting.\n\nWhen not to use\n\nYour tests do not modify any shared server-side state. In this case, all tests can use a single shared account.\n\nDetails\n\nWe will authenticate once per\nworker process (https://playwright.dev/docs/test-parallel#worker-processes)\n, each with a unique account.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\noverride storageState fixture (https://playwright.dev/docs/test-fixtures#overriding-fixtures)\nto authenticate once per worker. Use\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({browser},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constpage=awaitbrowser.newPage({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill(account.username);awaitpage.getByLabel('Password').fill(account.password);awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:fileName});awaitpage.close();awaituse(fileName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n. No changes are needed in the config.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({page})=&gt;{// page is authenticated});`\n```", 'Isolation | Playwright', 'Fixtures | Playwright', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", 'API testing | Playwright', 'Global setup and teardown | Playwright']</t>
+          <t>["This is the\nrecommended\napproach for tests that\nmodify server-side state\n. In Playwright, worker processes run in parallel. In this approach, each parallel worker is authenticated once. All tests ran by worker are reusing the same authentication state. We will need multiple testing accounts, one per each parallel worker.\n\nWhen to use\n\nYour tests modify shared server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting.\n\nWhen not to use\n\nYour tests do not modify any shared server-side state. In this case, all tests can use a single shared account.\n\nDetails\n\nWe will authenticate once per\nworker process (https://playwright.dev/docs/test-parallel#worker-processes)\n, each with a unique account.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\noverride storageState fixture (https://playwright.dev/docs/test-fixtures#overriding-fixtures)\nto authenticate once per worker. Use\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({browser},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constpage=awaitbrowser.newPage({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill(account.username);awaitpage.getByLabel('Password').fill(account.password);awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:fileName});awaitpage.close();awaituse(fileName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n. No changes are needed in the config.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({page})=&gt;{// page is authenticated});`\n```", 'Authentication | Playwright', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", 'Isolation | Playwright', "In addition to creating your own fixtures, you can also override existing fixtures to fit your needs. Consider the following example which overrides the\n`page`\nfixture by automatically navigating to the\n`baseURL`\n:\n\n```\n`import{testasbase}from'@playwright/test';exportconsttest=base.extend({page:async({baseURL,page},use)=&gt;{awaitpage.goto(baseURL);awaituse(page);},});`\n```\n\nNotice that in this example, the\n`page`\nfixture is able to depend on other built-in fixtures such as\ntestOptions.baseURL (https://playwright.dev/docs/api/class-testoptions#test-options-base-url)\n. We can now configure\n`baseURL`\nin the configuration file, or locally in the test file with\ntest.use() (https://playwright.dev/docs/api/class-test#test-use)\n.\n\nexample.spec.ts\n```\n`test.use({baseURL:'https://playwright.dev'});`\n```\n\nFixtures can also be overridden, causing the base fixture to be completely replaced with something different. For example, we could override the\ntestOptions.storageState (https://playwright.dev/docs/api/class-testoptions#test-options-storage-state)\nfixture to provide our own data.\n\n```\n`import{testasbase}from'@playwright/test';exportconsttest=base.extend({storageState:async({},use)=&gt;{constcookie=awaitgetAuthCookie();awaituse({cookies:[cookie]});},});`\n```", 'Fixtures | Playwright', 'Parallelism | Playwright']</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4115,7 +4803,34 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>To handle state that shouldn't persist between runs, you should write the browser state under `testProject.outputDir`, which is automatically cleaned up before every test run.</t>
+          <t>To handle state that should not persist between runs and avoid poisoning tests, you should write the browser state under `testProject.outputDir`. This directory is automatically cleaned up before every test run.
+If your tests modify shared server-side state (such as logging out or changing settings), the recommended approach is to use one account per parallel worker to prevent interference. You can implement this by creating a `playwright/fixtures.ts` file that overrides the `storageState` fixture to authenticate once per worker using `testInfo.parallelIndex` as a unique identifier.
+**Implementation steps for the recommended approach:**
+1.  **Create `playwright/fixtures.ts`**: Use the `workerStorageState` fixture to authenticate once per worker and save the state to a unique file within the project's output directory:
+    ```typescript
+    import { test as baseTest, expect } from '@playwright/test';
+    import fs from 'fs';
+    import path from 'path';
+    export * from '@playwright/test';
+    export const test = baseTest.extend&lt;{}, { workerStorageState: string }&gt;({
+      storageState: ({ workerStorageState }, use) =&gt; use(workerStorageState),
+      workerStorageState: [async ({ browser }, use) =&gt; {
+        const id = test.info().parallelIndex;
+        const fileName = path.resolve(test.info().project.outputDir, `.auth/${id}.json`);
+        if (fs.existsSync(fileName)) {
+          await use(fileName);
+          return;
+        }
+        const page = await browser.newPage({ storageState: undefined });
+        // Perform authentication steps here...
+        await page.context().storageState({ path: fileName });
+        await page.close();
+        await use(fileName);
+      }, { scope: 'worker' }],
+    });
+    ```
+2.  **Update your tests**: Import `test` from your new `playwright/fixtures.ts` file instead of `@playwright/test` in your test files.
+If your tests **do not** modify shared server-side state, you can continue using a shared account but should still ensure the `storageState` is written to `testProject.outputDir` to ensure it is cleaned up between runs.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4124,24 +4839,30 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0.005826599999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>0.67</v>
+        <v>37857</v>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.29</v>
       </c>
       <c r="J67" t="n">
-        <v>0.2380952380952381</v>
+        <v>5</v>
       </c>
       <c r="K67" t="n">
-        <v>0.19999999998</v>
+        <v>0.04887218045112782</v>
       </c>
       <c r="L67" t="n">
+        <v>0.3095238095238095</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.3333333333</v>
+      </c>
+      <c r="N67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4158,7 +4879,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>['Actions | Playwright', "If you want precise control over the drag operation, use lower-level methods like\nlocator.hover() (https://playwright.dev/docs/api/class-locator#locator-hover)\n,\nmouse.down() (https://playwright.dev/docs/api/class-mouse#mouse-down)\n,\nmouse.move() (https://playwright.dev/docs/api/class-mouse#mouse-move)\nand\nmouse.up() (https://playwright.dev/docs/api/class-mouse#mouse-up)\n.\n\n```\n`awaitpage.locator('#item-to-be-dragged').hover();awaitpage.mouse.down();awaitpage.locator('#item-to-drop-at').hover();awaitpage.mouse.up();`\n```\n\nnote\nIf your page relies on the\n`dragover`\nevent being dispatched, you need at least two mouse moves to trigger it in all browsers. To reliably issue the second mouse move, repeat your\nmouse.move() (https://playwright.dev/docs/api/class-mouse#mouse-move)\nor\nlocator.hover() (https://playwright.dev/docs/api/class-locator#locator-hover)\ntwice. The sequence of operations would be: hover the drag element, mouse down, hover the drop element, hover the drop element second time, mouse up.", "You can perform drag&amp;drop operation with\nlocator.dragTo() (https://playwright.dev/docs/api/class-locator#locator-drag-to)\n. This method will:\n\nHover the element that will be dragged.\nPress left mouse button.\nMove mouse to the element that will receive the drop.\nRelease left mouse button.\n\n```\n`awaitpage.locator('#item-to-be-dragged').dragTo(page.locator('#item-to-drop-at'));`\n```"]</t>
+          <t>['Actions | Playwright', "If you want precise control over the drag operation, use lower-level methods like\nlocator.hover() (https://playwright.dev/docs/api/class-locator#locator-hover)\n,\nmouse.down() (https://playwright.dev/docs/api/class-mouse#mouse-down)\n,\nmouse.move() (https://playwright.dev/docs/api/class-mouse#mouse-move)\nand\nmouse.up() (https://playwright.dev/docs/api/class-mouse#mouse-up)\n.\n\n```\n`awaitpage.locator('#item-to-be-dragged').hover();awaitpage.mouse.down();awaitpage.locator('#item-to-drop-at').hover();awaitpage.mouse.up();`\n```\n\nnote\nIf your page relies on the\n`dragover`\nevent being dispatched, you need at least two mouse moves to trigger it in all browsers. To reliably issue the second mouse move, repeat your\nmouse.move() (https://playwright.dev/docs/api/class-mouse#mouse-move)\nor\nlocator.hover() (https://playwright.dev/docs/api/class-locator#locator-hover)\ntwice. The sequence of operations would be: hover the drag element, mouse down, hover the drop element, hover the drop element second time, mouse up.", 'Auto-waiting | Playwright', "Locator | Playwright\n\nLocators are the central piece of Playwright's auto-waiting and retry-ability. In a nutshell, locators represent a way to find element(s) on the page at any moment. A locator can be created with the\npage.locator() (https://playwright.dev/docs/api/class-page#page-locator)\nmethod.\n\nLearn more about locators (https://playwright.dev/docs/locators)\n.", 'Mouse | Playwright\n\nThe Mouse class operates in main-frame CSS pixels relative to the top-left corner of the viewport.\n\ntip\nIf you want to debug where the mouse moved, you can use the\nTrace viewer (https://playwright.dev/docs/trace-viewer-intro)\nor\nPlaywright Inspector (https://playwright.dev/docs/running-tests)\n. A red dot showing the location of the mouse will be shown for every mouse action.\n\nEvery\n`page`\nobject has its own Mouse, accessible with\npage.mouse (https://playwright.dev/docs/api/class-page#page-mouse)\n.\n\n```\n`// Using ‘page.mouse’ to trace a 100x100 square.awaitpage.mouse.move(0,0);awaitpage.mouse.down();awaitpage.mouse.move(0,100);awaitpage.mouse.move(100,100);awaitpage.mouse.move(100,0);awaitpage.mouse.move(0,0);awaitpage.mouse.up();`\n```']</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4168,8 +4889,8 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>If your page relies on the `dragover` event being dispatched, you need at least two mouse moves to trigger it in all browsers. To reliably issue the second mouse move, you must repeat your `locator.hover()` or `mouse.move()` twice.
-The correct sequence of operations should be:
+          <t>To trigger the `dragover` event, you need at least two mouse moves over the drop target. You are missing a second hover action on the drop element.
+Update your code sequence to:
 1. Hover the drag element.
 2. Mouse down.
 3. Hover the drop element.
@@ -4183,41 +4904,47 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0.008919249999999001</v>
       </c>
       <c r="G68" t="n">
-        <v>0.8</v>
+        <v>34332</v>
       </c>
       <c r="H68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2676056338028169</v>
+        <v>0.67</v>
       </c>
       <c r="J68" t="n">
-        <v>0.4634146341463415</v>
+        <v>5</v>
       </c>
       <c r="K68" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.3414634146341464</v>
+      </c>
+      <c r="M68" t="n">
         <v>0.99999999995</v>
       </c>
-      <c r="L68" t="n">
+      <c r="N68" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>My global run stops with:
+          <t>CI killed our nightly job and left a report that looks like this. What confuses me is that no individual test failed or timed out — 486 passed, the rest were skipped, and the summary line is about the run rather than any one spec.
 Running 1000 tests using 10 workers
   514 skipped
   486 passed
   Timed out waiting 3600s for the entire test run
-What timeout is this and where do I configure it?</t>
+I've been through the config and I can't find where 3600 is set — I certainly didn't write it. What is this limit and where does it come from?</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>['Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', "Playwright Test supports a timeout for the whole test run. This prevents excess resource usage when everything went wrong. There is no default global timeout, but you can set a reasonable one in the config, for example one hour. Global timeout produces the following error:\n\n```\n`Running 1000 tests using 10 workers514 skipped486 passedTimed out waiting 3600s for the entire test run`\n```\n\nYou can set global timeout in the config.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalTimeout:3_600_000,});`\n```\n\nAPI reference:\ntestConfig.globalTimeout (https://playwright.dev/docs/api/class-testconfig#test-config-global-timeout)\n."]</t>
+          <t>['Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', "Playwright Test supports a timeout for the whole test run. This prevents excess resource usage when everything went wrong. There is no default global timeout, but you can set a reasonable one in the config, for example one hour. Global timeout produces the following error:\n\n```\n`Running 1000 tests using 10 workers514 skipped486 passedTimed out waiting 3600s for the entire test run`\n```\n\nYou can set global timeout in the config.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalTimeout:3_600_000,});`\n```\n\nAPI reference:\ntestConfig.globalTimeout (https://playwright.dev/docs/api/class-testconfig#test-config-global-timeout)\n.", "Running Playwright on CircleCI is very similar to running on GitHub Actions. In order to specify the pre-built Playwright\nDocker image (https://playwright.dev/docs/docker)\n, simply modify the agent definition with\n`docker:`\nin your config like so:\n\n```\n`executors:pw-noble-development:docker:-image:mcr.microsoft.com/playwright:v1.60.0-noble`\n```\n\nNote: When using the docker agent definition, you are specifying the resource class of where playwright runs to the 'medium' tier\nhere (https://circleci.com/docs/configuration-reference#docker-execution-environment)\n. The default behavior of Playwright is to set the number of workers to the detected core count (2 in the case of the medium tier). Overriding the number of workers to greater than this number will cause unnecessary timeouts and failures."]</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4227,14 +4954,15 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>This is a **global timeout**, which is a timeout for the whole test run used to prevent excess resource usage.
-You can configure it in your `playwright.config.ts` file using the `globalTimeout` property:
+          <t>The limit you are seeing is the `globalTimeout`. This is a timeout for the entire test run, which prevents excess resource usage when a run goes wrong [2].
+The value of 3600 seconds (3,600,000 ms) is set in your `playwright.config.ts` file using the `globalTimeout` property [2]:
 ```typescript
 import { defineConfig } from '@playwright/test';
 export default defineConfig({
   globalTimeout: 3_600_000,
 });
-```</t>
+```
+While you mentioned you did not write this, it is the specific configuration option that produces the error message you received [2].</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4243,24 +4971,30 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0.008936250000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>0.75</v>
+        <v>34370</v>
       </c>
       <c r="H69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2127659574468085</v>
+        <v>0.73</v>
       </c>
       <c r="J69" t="n">
-        <v>0.2439024390243902</v>
+        <v>5</v>
       </c>
       <c r="K69" t="n">
+        <v>0.1411764705882353</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.2926829268292683</v>
+      </c>
+      <c r="M69" t="n">
         <v>0.49999999995</v>
       </c>
-      <c r="L69" t="n">
+      <c r="N69" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4274,7 +5008,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>['Auto-waiting | Playwright', 'Some actions like\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nsupport\n`force`\noption that disables non-essential actionability checks, for example passing truthy\n`force`\nto\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nmethod will not check that the target element actually receives click events.', 'Element is considered receiving pointer events when it is the hit target of the pointer event at the action point. For example, when clicking at the point\n`(10;10)`\n, Playwright checks whether some other element (usually an overlay) will instead capture the click at\n`(10;10)`\n.\n\nFor example, consider a scenario where Playwright will click\n`Sign Up`\nbutton regardless of when the\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\ncall was made:\n\npage is checking that user name is unique and\n`Sign Up`\nbutton is disabled;\nafter checking with the server, the disabled\n`Sign Up`\nbutton is replaced with another one that is now enabled.']</t>
+          <t>['Auto-waiting | Playwright', 'Some actions like\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nsupport\n`force`\noption that disables non-essential actionability checks, for example passing truthy\n`force`\nto\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nmethod will not check that the target element actually receives click events.', "Sometimes, apps use non-trivial logic where hovering the element overlays it with another element that intercepts the click. This behavior is indistinguishable from a bug where element gets covered and the click is dispatched elsewhere. If you know this is taking place, you can bypass the\nactionability (https://playwright.dev/docs/actionability)\nchecks and force the click:\n\n```\n`awaitpage.getByRole('button').click({force:true});`\n```", "Performs a simple human click.\n\n```\n`// Generic clickawaitpage.getByRole('button').click();// Double clickawaitpage.getByText('Item').dblclick();// Right clickawaitpage.getByText('Item').click({button:'right'});// Shift + clickawaitpage.getByText('Item').click({modifiers:['Shift']});// Ctrl + click on Windows and Linux// Meta + click on macOSawaitpage.getByText('Item').click({modifiers:['ControlOrMeta']});// Hover over elementawaitpage.getByText('Item').hover();// Click the top left cornerawaitpage.getByText('Item').click({position:{x:0,y:0}});`\n```\n\nUnder the hood, this and other pointer-related methods:\n\nwait for element with given selector to be in DOM\nwait for it to become displayed, i.e. not empty, no\n`display:none`\n, no\n`visibility:hidden`\nwait for it to stop moving, for example, until css transition finishes\nscroll the element into view\nwait for it to receive pointer events at the action point, for example, waits until element becomes non-obscured by other elements\nretry if the element is detached during any of the above checks", "If you are not interested in testing your app under the real conditions and want to simulate the click by any means possible, you can trigger the\nHTMLElement.click() (https://developer.mozilla.org/en-US/docs/Web/API/HTMLElement/click)\nbehavior via simply dispatching a click event on the element with\nlocator.dispatchEvent() (https://playwright.dev/docs/api/class-locator#locator-dispatch-event)\n:\n\n```\n`awaitpage.getByRole('button').dispatchEvent('click');`\n```"]</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4284,9 +5018,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>You can bypass the check by using the `force` option in the `locator.click()` method. Passing a truthy `force` value disables non-essential actionability checks, meaning Playwright will not check that the target element actually receives click events.
-Example:
-`await page.getByRole('button').click({ force: true });`</t>
+          <t>To bypass the actionability check when a hover overlay intercepts the click, you can use the `force` option in the `click()` method. This disables non-essential actionability checks, such as the check that ensures the target element receives click events.
+Use the following code:
+```javascript
+await page.getByRole('button').click({force: true});
+```
+Alternatively, if you want to simulate the click by dispatching a click event on the element (bypassing all actionability checks), you can use `dispatchEvent`:
+```javascript
+await page.getByRole('button').dispatchEvent('click');
+```</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4295,24 +5035,30 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>0.00823775</v>
       </c>
       <c r="G70" t="n">
+        <v>31896</v>
+      </c>
+      <c r="H70" t="n">
         <v>0.75</v>
       </c>
-      <c r="H70" t="n">
-        <v>5</v>
-      </c>
       <c r="I70" t="n">
-        <v>0.2826086956521739</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
-        <v>0.3611111111111111</v>
+        <v>5</v>
       </c>
       <c r="K70" t="n">
-        <v>0.49999999995</v>
+        <v>0.2048192771084337</v>
       </c>
       <c r="L70" t="n">
+        <v>0.4722222222222222</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.6388888888675925</v>
+      </c>
+      <c r="N70" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4326,7 +5072,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>['Locators | Playwright', 'All locators in Playwright\nby default\nwork with elements in Shadow DOM. The exceptions are:\n\nLocating by XPath does not pierce shadow roots.\nClosed-mode shadow roots (https://developer.mozilla.org/en-US/docs/Web/API/Element/attachShadow#parameters)\nare not supported.\n\nConsider the following example with a custom web component:\n\n```\n`&lt;x-detailsrole=buttonaria-expanded=truearia-controls=inner-details&gt;&lt;div&gt;Title&lt;/div&gt;#shadow-root&lt;divid=inner-details&gt;Details&lt;/div&gt;&lt;/x-details&gt;`\n```\n\nYou can locate in the same way as if the shadow root was not present at all.\n\nTo click\n`&lt;div&gt;Details&lt;/div&gt;`\n:\n\n```\n`awaitpage.getByText(\'Details\').click();`\n```\n\n```\n`&lt;x-detailsrole=buttonaria-expanded=truearia-controls=inner-details&gt;&lt;div&gt;Title&lt;/div&gt;#shadow-root&lt;divid=inner-details&gt;Details&lt;/div&gt;&lt;/x-details&gt;`\n```\n\nTo click\n`&lt;x-details&gt;`\n:\n\n```\n`awaitpage.locator(\'x-details\',{hasText:\'Details\'}).click();`\n```\n\n```\n`&lt;x-detailsrole=buttonaria-expanded=truearia-controls=inner-details&gt;&lt;div&gt;Title&lt;/div&gt;#shadow-root&lt;divid=inner-details&gt;Details&lt;/div&gt;&lt;/x-details&gt;`\n```\n\nTo ensure that\n`&lt;x-details&gt;`\ncontains the text "Details":\n\n```\n`awaitexpect(page.locator(\'x-details\')).toContainText(\'Details\');`\n```']</t>
+          <t>['All locators in Playwright\nby default\nwork with elements in Shadow DOM. The exceptions are:\n\nLocating by XPath does not pierce shadow roots.\nClosed-mode shadow roots (https://developer.mozilla.org/en-US/docs/Web/API/Element/attachShadow#parameters)\nare not supported.\n\nConsider the following example with a custom web component:\n\n```\n`&lt;x-detailsrole=buttonaria-expanded=truearia-controls=inner-details&gt;&lt;div&gt;Title&lt;/div&gt;#shadow-root&lt;divid=inner-details&gt;Details&lt;/div&gt;&lt;/x-details&gt;`\n```\n\nYou can locate in the same way as if the shadow root was not present at all.\n\nTo click\n`&lt;div&gt;Details&lt;/div&gt;`\n:\n\n```\n`awaitpage.getByText(\'Details\').click();`\n```\n\n```\n`&lt;x-detailsrole=buttonaria-expanded=truearia-controls=inner-details&gt;&lt;div&gt;Title&lt;/div&gt;#shadow-root&lt;divid=inner-details&gt;Details&lt;/div&gt;&lt;/x-details&gt;`\n```\n\nTo click\n`&lt;x-details&gt;`\n:\n\n```\n`awaitpage.locator(\'x-details\',{hasText:\'Details\'}).click();`\n```\n\n```\n`&lt;x-detailsrole=buttonaria-expanded=truearia-controls=inner-details&gt;&lt;div&gt;Title&lt;/div&gt;#shadow-root&lt;divid=inner-details&gt;Details&lt;/div&gt;&lt;/x-details&gt;`\n```\n\nTo ensure that\n`&lt;x-details&gt;`\ncontains the text "Details":\n\n```\n`awaitexpect(page.locator(\'x-details\')).toContainText(\'Details\');`\n```', 'Locators | Playwright', "warning\nWe recommend prioritizing\nuser-visible locators (https://playwright.dev/docs/locators#quick-guide)\nlike text or accessible role instead of using XPath that is tied to the implementation and easily break when the page changes.\n\nXPath locators are equivalent to calling\nDocument.evaluate (https://developer.mozilla.org/en/docs/Web/API/Document/evaluate)\n.\n\n```\n`awaitpage.locator('xpath=//button').click();`\n```\n\nnote\nAny selector string starting with\n`//`\nor\n`..`\nare assumed to be an xpath selector. For example, Playwright converts\n`'//html/body'`\nto\n`'xpath=//html/body'`\n.\n\nnote\nXPath does not pierce shadow roots."]</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4336,7 +5082,8 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>It does not work because locating by XPath does not pierce shadow roots.</t>
+          <t>Your XPath locator fails because XPath does not pierce shadow roots. While most Playwright locators work with elements in the Shadow DOM by default, this is a specific exception for XPath.
+To locate elements inside a shadow root, you should use user-visible locators such as text or accessible roles, which are recommended over XPath because they are not tied to implementation details and are less likely to break when the page changes.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4345,40 +5092,46 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>0.007844250000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>0.29</v>
+        <v>30687</v>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.57</v>
       </c>
       <c r="J71" t="n">
-        <v>0.06976744186046512</v>
+        <v>5</v>
       </c>
       <c r="K71" t="n">
-        <v>0.49999999995</v>
+        <v>0.1780821917808219</v>
       </c>
       <c r="L71" t="n">
+        <v>0.3023255813953488</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.8333333332916666</v>
+      </c>
+      <c r="N71" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>My two parallel tests fail intermittently because they seem to share a variable. Code:
+          <t>Two tests in the same file pass individually and fail against each other when the suite runs normally. The second one asserts on a counter the first one increments, and the value it sees is inconsistent between runs — sometimes 0, sometimes 1.
 let counter = 0;
 test('a', async () =&gt; { counter++; /* ... */ });
 test('b', async () =&gt; { expect(counter).toBe(0); /* flaky */ });
-Why can't I share state like this?</t>
+Running with a single worker makes it deterministic, which points at concurrency, but I don't understand the mechanism — it's one module, one file, one variable. Why isn't the assignment visible?</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>['Isolation | Playwright', 'Parallelism | Playwright', "By default, tests in a single file are run in order. If you have many independent tests in a single file, you might want to run them in parallel with\ntest.describe.configure() (https://playwright.dev/docs/api/class-test#test-describe-configure)\n.\n\nNote that parallel tests are executed in separate worker processes and cannot share any state or global variables. Each test executes all relevant hooks just for itself, including\n`beforeAll`\nand\n`afterAll`\n.\n\n```\n`import{test}from'@playwright/test';test.describe.configure({mode:'parallel'});test('runs in parallel 1',async({page})=&gt;{/* ... */});test('runs in parallel 2',async({page})=&gt;{/* ... */});`\n```\n\nAlternatively, you can opt-in all tests into this fully-parallel mode in the configuration file:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({fullyParallel:true,});`\n```\n\nYou can also opt in for fully-parallel mode for just a few projects:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({// runs all tests in all files of a specific project in parallelprojects:[{name:'chromium',use:{...devices['Desktop Chrome']},fullyParallel:true,},]});`\n```", "All tests run in worker processes. These processes are OS processes, running independently, orchestrated by the test runner. All workers have identical environments and each starts its own browser.\n\nYou can't communicate between the workers. Playwright Test reuses a single worker as much as it can to make testing faster, so multiple test files are usually run in a single worker one after another.\n\nWorkers are always shutdown after a\ntest failure (https://playwright.dev/docs/test-retries#failures)\nto guarantee pristine environment for following tests.", 'Fixtures | Playwright']</t>
+          <t>['Parallelism | Playwright', 'Playwright Test runs tests in parallel. In order to achieve that, it runs several worker processes that run at the same time. By default,\ntest files\nare run in parallel. Tests in a single file are run in order, in the same worker process.\n\nYou can configure tests using\ntest.describe.configure (https://playwright.dev/docs/test-parallel#parallelize-tests-in-a-single-file)\nto run\ntests in a single file\nin parallel.\nYou can configure\nentire project\nto have all tests in all files to run in parallel using\ntestProject.fullyParallel (https://playwright.dev/docs/api/class-testproject#test-project-fully-parallel)\nor\ntestConfig.fullyParallel (https://playwright.dev/docs/api/class-testconfig#test-config-fully-parallel)\n.\nTo\ndisable\nparallelism limit the number of\nworkers to one (https://playwright.dev/docs/test-parallel#disable-parallelism)\n.\n\nYou can control the number of\nparallel worker processes (https://playwright.dev/docs/test-parallel#limit-workers)\nand\nlimit the number of failures (https://playwright.dev/docs/test-parallel#limit-failures-and-fail-fast)\nin the whole test suite for efficiency.', "By default, tests in a single file are run in order. If you have many independent tests in a single file, you might want to run them in parallel with\ntest.describe.configure() (https://playwright.dev/docs/api/class-test#test-describe-configure)\n.\n\nNote that parallel tests are executed in separate worker processes and cannot share any state or global variables. Each test executes all relevant hooks just for itself, including\n`beforeAll`\nand\n`afterAll`\n.\n\n```\n`import{test}from'@playwright/test';test.describe.configure({mode:'parallel'});test('runs in parallel 1',async({page})=&gt;{/* ... */});test('runs in parallel 2',async({page})=&gt;{/* ... */});`\n```\n\nAlternatively, you can opt-in all tests into this fully-parallel mode in the configuration file:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({fullyParallel:true,});`\n```\n\nYou can also opt in for fully-parallel mode for just a few projects:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({// runs all tests in all files of a specific project in parallelprojects:[{name:'chromium',use:{...devices['Desktop Chrome']},fullyParallel:true,},]});`\n```", "All tests run in worker processes. These processes are OS processes, running independently, orchestrated by the test runner. All workers have identical environments and each starts its own browser.\n\nYou can't communicate between the workers. Playwright Test reuses a single worker as much as it can to make testing faster, so multiple test files are usually run in a single worker one after another.\n\nWorkers are always shutdown after a\ntest failure (https://playwright.dev/docs/test-retries#failures)\nto guarantee pristine environment for following tests.", 'Isolation | Playwright', 'Test Isolation is when each test is completely isolated from another test. Every test runs independently from any other test. This means that each test has its own local storage, session storage, cookies etc. Playwright achieves this using\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\ns which are equivalent to incognito-like profiles. They are fast and cheap to create and are completely isolated, even when running in a single browser. Playwright creates a context for each test, and provides a default\nPage (https://playwright.dev/docs/api/class-page)\nin that context.', "No failure carry-over. If one test fails it doesn't affect the other test.\nEasy to debug errors or flakiness, because you can run just a single test as many times as you'd like.\nDon't have to think about the order when running in parallel, sharding, etc."]</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4388,7 +5141,9 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Answer: You cannot share state because parallel tests are executed in separate worker processes, which are independent OS processes that cannot communicate with each other or share global variables.</t>
+          <t>The inconsistency occurs because your tests are running in parallel, which means they are executed in separate worker processes. 
+According to the documentation, parallel tests are executed in separate worker processes and **cannot share any state or global variables** [3]. Because these workers are independent OS processes, they do not share the same memory space, which is why the `counter` variable incremented in one process is not visible to the other [4].
+While tests in a single file are run in order by default, you have likely enabled parallel execution either via `test.describe.configure({ mode: 'parallel' })` within the file, or by setting `fullyParallel: true` in your `playwright.config.ts` [2, 3]. When tests run in parallel, they are completely isolated from one another [6].</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4397,24 +5152,30 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0.00942875</v>
       </c>
       <c r="G72" t="n">
-        <v>0.44</v>
+        <v>35370</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3103448275862069</v>
+        <v>0.59</v>
       </c>
       <c r="J72" t="n">
-        <v>0.1875</v>
+        <v>5</v>
       </c>
       <c r="K72" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="M72" t="n">
         <v>0.99999999998</v>
       </c>
-      <c r="L72" t="n">
+      <c r="N72" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4432,7 +5193,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>['Retries | Playwright', 'Fixtures | Playwright', 'Isolation | Playwright']</t>
+          <t>["Use\ntest.describe.serial() (https://playwright.dev/docs/api/class-test#test-describe-serial)\nto group dependent tests to ensure they will always run together and in order. If one of the tests fails, all subsequent tests are skipped. All tests in the group are retried together.\n\nConsider the following snippet that uses\n`test.describe.serial`\n:\n\n```\n`import{test}from'@playwright/test';test.describe.configure({mode:'serial'});test.beforeAll(async()=&gt;{/* ... */});test('first good',async({page})=&gt;{/* ... */});test('second flaky',async({page})=&gt;{/* ... */});test('third good',async({page})=&gt;{/* ... */});`\n```\n\nWhen running without\nretries (https://playwright.dev/docs/test-retries#retries)\n, all tests after the failure are skipped:\n\nWorker process #1:\n`beforeAll`\nhook runs\n`first good`\npasses\n`second flaky`\nfails\n`third good`\nis skipped entirely\n\nWhen running with\nretries (https://playwright.dev/docs/test-retries#retries)\n, all tests are retried together:\n\nWorker process #1:\n`beforeAll`\nhook runs\n`first good`\npasses\n`second flaky`\nfails\n`third good`\nis skipped\nWorker process #2:\n`beforeAll`\nhook runs again\n`first good`\npasses again\n`second flaky`\npasses\n`third good`\npasses\n\nnote\nIt is usually better to make your tests isolated, so they can be efficiently run and retried independently.", 'Retries | Playwright', "Playwright Test runs tests in worker processes. These processes are OS processes, running independently, orchestrated by the test runner. All workers have identical environments and each starts its own browser.\n\nConsider the following snippet:\n\n```\n`import{test}from'@playwright/test';test.describe('suite',()=&gt;{test.beforeAll(async()=&gt;{/* ... */});test('first good',async({page})=&gt;{/* ... */});test('second flaky',async({page})=&gt;{/* ... */});test('third good',async({page})=&gt;{/* ... */});test.afterAll(async()=&gt;{/* ... */});});`\n```\n\nWhen\nall tests pass\n, they will run in order in the same worker process.\n\nWorker process starts\n`beforeAll`\nhook runs\n`first good`\npasses\n`second flaky`\npasses\n`third good`\npasses\n`afterAll`\nhook runs\n\nShould\nany test fail\n, Playwright Test will discard the entire worker process along with the browser and will start a new one. Testing will continue in the new worker process starting with the next test.\n\nWorker process #1 starts\n`beforeAll`\nhook runs\n`first good`\npasses\n`second flaky`\nfails\n`afterAll`\nhook runs\nWorker process #2 starts\n`beforeAll`\nhook runs again\n`third good`\npasses\n`afterAll`\nhook runs\n\nIf you\nenable\nretries (https://playwright.dev/docs/test-retries#retries)\n, second worker process will start by retrying the failed test and continue from there.\n\nWorker process #1 starts\n`beforeAll`\nhook runs\n`first good`\npasses\n`second flaky`\nfails\n`afterAll`\nhook runs\nWorker process #2 starts\n`beforeAll`\nhook runs again\n`second flaky`\nis retried and passes\n`third good`\npasses\n`afterAll`\nhook runs\n\nThis scheme works perfectly for independent tests and guarantees that failing tests can't affect healthy ones."]</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4442,7 +5203,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Based on the provided context, there is no information explaining why `beforeAll` runs twice after a test failure. The provided context only lists titles for "Retries," "Fixtures," and "Isolation" in Playwright, but does not contain the content or documentation explaining the behavior of `beforeAll` in relation to test retries or failures.</t>
+          <t>Your `beforeAll` hook runs again because Playwright Test discards the entire worker process (along with the browser) when a test fails to ensure that failing tests do not affect healthy ones. 
+When a failure occurs:
+1. The current worker process finishes its execution (including the `afterAll` hook).
+2. A new worker process is started to continue testing.
+3. This new worker process must execute the `beforeAll` hook again to set up the environment for the remaining tests.
+If you have retries enabled, the new worker process will also re-run the failed test before proceeding to the subsequent tests, again triggering the `beforeAll` hook.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4451,41 +5217,47 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>0.008437750000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>32551</v>
       </c>
       <c r="H73" t="n">
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1372549019607843</v>
+        <v>0.62</v>
       </c>
       <c r="J73" t="n">
-        <v>0.1666666666666667</v>
+        <v>5</v>
       </c>
       <c r="K73" t="n">
-        <v>0.8333333332916666</v>
+        <v>0.1826923076923077</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>0.4523809523809524</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.9999999999666667</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>My init script mock doesn't apply — Math.random() still returns real values. Code:
+          <t>We stub Math.random so our A/B bucketing is deterministic in tests. It works in about half the specs and silently does nothing in the rest — the app takes the real random branch and the assertion fails. The two groups of specs look identical to me apart from ordering.
 test('t', async ({ page }) =&gt; {
   await page.goto('http://localhost:3000');
   await page.addInitScript(() =&gt; { Math.random = () =&gt; 42; });
 });
-Why is the mock not taking effect?</t>
+No error is raised, the override just isn't in effect. What determines whether it takes?</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>['Evaluating JavaScript | Playwright', "Sometimes it is convenient to evaluate something in the page before it starts loading. For example, you might want to setup some mocks or test data.\n\nIn this case, use\npage.addInitScript() (https://playwright.dev/docs/api/class-page#page-add-init-script)\nor\nbrowserContext.addInitScript() (https://playwright.dev/docs/api/class-browsercontext#browser-context-add-init-script)\n. In the example below, we will replace\n`Math.random()`\nwith a constant value.\n\nFirst, create a\n`preload.js`\nfile that contains the mock.\n\n```\n`// preload.jsMath.random=()=&gt;42;`\n```\n\nNext, add init script to the page.\n\n```\n`import{test,expect}from'@playwright/test';importpathfrom'path';test.beforeEach(async({page})=&gt;{// Add script for every test in the beforeEach hook.// Make sure to correctly resolve the script path.awaitpage.addInitScript({path:path.resolve(__dirname,'../mocks/preload.js')});});`\n```"]</t>
+          <t>['Evaluating JavaScript | Playwright', "Sometimes it is convenient to evaluate something in the page before it starts loading. For example, you might want to setup some mocks or test data.\n\nIn this case, use\npage.addInitScript() (https://playwright.dev/docs/api/class-page#page-add-init-script)\nor\nbrowserContext.addInitScript() (https://playwright.dev/docs/api/class-browsercontext#browser-context-add-init-script)\n. In the example below, we will replace\n`Math.random()`\nwith a constant value.\n\nFirst, create a\n`preload.js`\nfile that contains the mock.\n\n```\n`// preload.jsMath.random=()=&gt;42;`\n```\n\nNext, add init script to the page.\n\n```\n`import{test,expect}from'@playwright/test';importpathfrom'path';test.beforeEach(async({page})=&gt;{// Add script for every test in the beforeEach hook.// Make sure to correctly resolve the script path.awaitpage.addInitScript({path:path.resolve(__dirname,'../mocks/preload.js')});});`\n```", 'Evaluated scripts run in the browser environment, while your test runs in a testing environments. This means you cannot use variables from your test in the page and vice versa. Instead, you should pass them explicitly as an argument.\n\nThe following snippet is\nWRONG\nbecause it uses the variable directly:\n\n```\n`constdata=\'some data\';constresult=awaitpage.evaluate(()=&gt;{// WRONG: there is no "data" in the web page.window.myApp.use(data);});`\n```\n\nThe following snippet is\nCORRECT\nbecause it passes the value explicitly as an argument:\n\n```\n`constdata=\'some data\';// Pass |data| as a parameter.constresult=awaitpage.evaluate(data=&gt;{window.myApp.use(data);},data);`\n```']</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4495,8 +5267,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>The mock is not taking effect because `page.addInitScript()` must be called **before** the page starts loading. In your code, you are calling `page.goto('http://localhost:3000')` before `page.addInitScript()`. 
-To fix this, you should add the init script before navigating to the page, or use `test.beforeEach` to ensure the script is added before the page loads for every test.</t>
+          <t>The reason your override is not consistently in effect is that `page.addInitScript()` must be called before the page starts loading to ensure the script is evaluated. If the page has already begun loading or navigation has progressed, the init script may not be applied in time.
+To ensure the script is applied reliably, you should use `test.beforeEach` to add the init script, as shown in the documentation:
+```javascript
+import { test, expect } from '@playwright/test';
+import path from 'path';
+test.beforeEach(async ({ page }) =&gt; {
+  // Add script for every test in the beforeEach hook.
+  await page.addInitScript({ path: path.resolve(__dirname, '../mocks/preload.js') });
+});
+```
+The documentation recommends creating a separate file (e.g., `preload.js`) containing the mock and referencing its path, rather than defining the function inline within the test body after `page.goto`.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4505,24 +5286,30 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0.0074235</v>
       </c>
       <c r="G74" t="n">
-        <v>0.86</v>
+        <v>28324</v>
       </c>
       <c r="H74" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2419354838709677</v>
+        <v>0.75</v>
       </c>
       <c r="J74" t="n">
+        <v>5</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.1119402985074627</v>
+      </c>
+      <c r="L74" t="n">
         <v>0.4411764705882353</v>
       </c>
-      <c r="K74" t="n">
+      <c r="M74" t="n">
         <v>0.99999999995</v>
       </c>
-      <c r="L74" t="n">
+      <c r="N74" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4540,7 +5327,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>['Mock APIs | Playwright', "Playwright's built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nallow your tests to natively route requests and perform mocking and interception.\n\nIf you're using Playwright's native\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n, and it appears network events are missing, disable Service Workers by setting\nserviceWorkers (https://playwright.dev/docs/api/class-browser#browser-new-context-option-service-workers)\nto\n`'block'`\n.\n\nIt might be that you are using a mock tool such as Mock Service Worker (MSW). While this tool works out of the box for mocking responses, it adds its own Service Worker that takes over the network requests, hence making them invisible to\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n. If you are interested in both network testing and mocking, consider using built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nfor\nresponse mocking (https://playwright.dev/docs/network#handle-requests)\n.", 'Playwright uses simplified glob patterns for URL matching in network interception methods like\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nor\npage.waitForResponse() (https://playwright.dev/docs/api/class-page#page-wait-for-response)\n. These patterns support basic wildcards:\n\nAsterisks:\nA single\n`*`\nmatches any characters except\n`/`\nA double\n`**`\nmatches any characters including\n`/`\nQuestion mark\n`?`\nmatches only question mark\n`?`\n. If you want to match any character, use\n`*`\ninstead.\nCurly braces\n`{}`\ncan be used to match a list of options separated by commas\n`,`\nBackslash\n`\\`\ncan be used to escape any of special characters (note to escape backslash itself as\n`\\\\`\n)\n\nExamples:\n\n`https://example.com/*.js`\nmatches\n`https://example.com/file.js`\nbut not\n`https://example.com/path/file.js`\n`https://example.com/?page=1`\nmatches\n`https://example.com/?page=1`\nbut not\n`https://example.com`\n`**/*.js`\nmatches both\n`https://example.com/file.js`\nand\n`https://example.com/path/file.js`\n`**/*.{png,jpg,jpeg}`\nmatches all image requests\n\nImportant notes:\n\nThe glob pattern must match the entire URL, not just a part of it.\nWhen using globs for URL matching, consider the full URL structure, including the protocol and path separators.\nFor more complex matching requirements, consider using\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\ninstead of glob patterns.']</t>
+          <t>['Mock APIs | Playwright', "Playwright's built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nallow your tests to natively route requests and perform mocking and interception.\n\nIf you're using Playwright's native\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n, and it appears network events are missing, disable Service Workers by setting\nserviceWorkers (https://playwright.dev/docs/api/class-browser#browser-new-context-option-service-workers)\nto\n`'block'`\n.\n\nIt might be that you are using a mock tool such as Mock Service Worker (MSW). While this tool works out of the box for mocking responses, it adds its own Service Worker that takes over the network requests, hence making them invisible to\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n. If you are interested in both network testing and mocking, consider using built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nfor\nresponse mocking (https://playwright.dev/docs/network#handle-requests)\n.", 'Route | Playwright\n\nWhenever a network route is set up with\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nor\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n, the\n`Route`\nobject allows to handle the route.\n\nLearn more about\nnetworking (https://playwright.dev/docs/network)\n.', 'Playwright uses simplified glob patterns for URL matching in network interception methods like\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nor\npage.waitForResponse() (https://playwright.dev/docs/api/class-page#page-wait-for-response)\n. These patterns support basic wildcards:\n\nAsterisks:\nA single\n`*`\nmatches any characters except\n`/`\nA double\n`**`\nmatches any characters including\n`/`\nQuestion mark\n`?`\nmatches only question mark\n`?`\n. If you want to match any character, use\n`*`\ninstead.\nCurly braces\n`{}`\ncan be used to match a list of options separated by commas\n`,`\nBackslash\n`\\`\ncan be used to escape any of special characters (note to escape backslash itself as\n`\\\\`\n)\n\nExamples:\n\n`https://example.com/*.js`\nmatches\n`https://example.com/file.js`\nbut not\n`https://example.com/path/file.js`\n`https://example.com/?page=1`\nmatches\n`https://example.com/?page=1`\nbut not\n`https://example.com`\n`**/*.js`\nmatches both\n`https://example.com/file.js`\nand\n`https://example.com/path/file.js`\n`**/*.{png,jpg,jpeg}`\nmatches all image requests\n\nImportant notes:\n\nThe glob pattern must match the entire URL, not just a part of it.\nWhen using globs for URL matching, consider the full URL structure, including the protocol and path separators.\nFor more complex matching requirements, consider using\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\ninstead of glob patterns.']</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4550,9 +5337,9 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Based on the provided context, there are two potential reasons why your mock is not applying:
-1.  **Service Workers:** If you are using a tool like Mock Service Worker (MSW), it adds its own Service Worker that takes over network requests, making them invisible to `page.route()`. If you are not using such a tool but still experience missing network events, you should disable Service Workers by setting `serviceWorkers` to `'block'`.
-2.  **Glob Pattern Matching:** The glob pattern must match the entire URL. If your pattern does not correctly account for the full URL structure (including the protocol and path separators), it will not intercept the request.</t>
+          <t>You are likely using a Service Worker that is intercepting the network requests before Playwright's `page.route()` can handle them.
+To fix this, you must disable Service Workers by setting the `serviceWorkers` option to `'block'` when creating your browser context.
+Additionally, ensure your glob pattern is correct. According to the documentation, the glob pattern must match the entire URL. If your current pattern `*/**/api/v1/fruits` is not matching the full URL (including the protocol and domain), it will not intercept the request. You may need to adjust the pattern to include the full URL structure or use a `RegExp` for more complex matching.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4561,39 +5348,45 @@
         </is>
       </c>
       <c r="F75" t="n">
+        <v>0.008263</v>
+      </c>
+      <c r="G75" t="n">
+        <v>31787</v>
+      </c>
+      <c r="H75" t="n">
         <v>0</v>
       </c>
-      <c r="G75" t="n">
+      <c r="I75" t="n">
         <v>0</v>
       </c>
-      <c r="H75" t="n">
-        <v>3</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0.05607476635514019</v>
-      </c>
       <c r="J75" t="n">
-        <v>0.1935483870967742</v>
+        <v>4</v>
       </c>
       <c r="K75" t="n">
+        <v>0.0761904761904762</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.2580645161290323</v>
+      </c>
+      <c r="M75" t="n">
         <v>0</v>
       </c>
-      <c r="L75" t="n">
+      <c r="N75" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>My test flakes because I read text right after the element appears. Code:
-const text = page.getByTestId('status').textContent();
-expect(text).toBe('Submitted'); // sometimes empty
-How do I make this wait reliably?</t>
+          <t>Our submit-confirmation test fails maybe one run in ten on CI and never on my machine. When it fails the value read back is an empty string rather than the wrong string, so it looks like we're reading too early — but there's already a visibility check above this line, so the element is definitely on the page by the time we get here.
+const text = await page.getByTestId('status').textContent();
+expect(text).toBe('Submitted');  // sometimes empty
+Adding a fixed wait makes it pass, which I know is the wrong answer. What's the right one?</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>['Auto-waiting | Playwright', "LocatorAssertions | Playwright\n\nThe\nLocatorAssertions (https://playwright.dev/docs/api/class-locatorassertions)\nclass provides assertion methods that can be used to make assertions about the\nLocator (https://playwright.dev/docs/api/class-locator)\nstate in the tests.\n\n```\n`import{test,expect}from'@playwright/test';test('status becomes submitted',async({page})=&gt;{// ...awaitpage.getByRole('button').click();awaitexpect(page.locator('.status')).toHaveText('Submitted');});`\n```", 'The following assertions will retry until the assertion passes, or the assertion timeout is reached. Note that retrying assertions are async, so you must\n`await`\nthem.\n\nAssertion\nDescription\nawait expect(locator).toBeAttached() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-attached)\nElement is attached\nawait expect(locator).toBeChecked() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-checked)\nCheckbox is checked\nawait expect(locator).toBeDisabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-disabled)\nElement is disabled\nawait expect(locator).toBeEditable() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-editable)\nElement is editable\nawait expect(locator).toBeEmpty() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-empty)\nContainer is empty\nawait expect(locator).toBeEnabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-enabled)\nElement is enabled\nawait expect(locator).toBeFocused() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-focused)\nElement is focused\nawait expect(locator).toBeHidden() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-hidden)\nElement is not visible\nawait expect(locator).toBeInViewport() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-in-viewport)\nElement intersects viewport\nawait expect(locator).toBeVisible() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-visible)\nElement is visible\nawait expect(locator).toContainText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-text)\nElement contains text\nawait expect(locator).toContainClass() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-class)\nElement has specified CSS classes\nawait expect(locator).toHaveAccessibleDescription() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-accessible-description)\nElement has a matching\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\nawait expect(locator).toHaveAccessibleName() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-accessible-name)\nElement has a matching\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\nawait expect(locator).toHaveAttribute() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-attribute)\nElement has a DOM attribute\nawait expect(locator).toHaveClass() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-class)\nElement has specified CSS class property\nawait expect(locator).toHaveCount() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-count)\nList has exact number of children\nawait expect(locator).toHaveCSS() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css)\nElement has CSS property\nawait expect(locator).toHaveId() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-id)\nElement has an ID\nawait expect(locator).toHaveJSProperty() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-js-property)\nElement has a JavaScript property\nawait expect(locator).toHaveRole() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-role)\nElement has a specific\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\nawait expect(locator).toHaveScreenshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-screenshot-1)\nElement has a screenshot\nawait expect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nElement matches text\nawait expect(locator).toHaveValue() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value)\nInput has a value\nawait expect(locator).toHaveValues() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-values)\nSelect has options selected\nawait expect(locator).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-match-aria-snapshot)\nElement matches the Aria snapshot\nawait expect(page).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-match-aria-snapshot)\nPage matches the Aria snapshot\nawait expect(page).toHaveScreenshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\nPage has a screenshot\nawait expect(page).toHaveTitle() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-title)\nPage has a title\nawait expect(page).toHaveURL() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-url)\nPage has a URL\nawait expect(response).toBeOK() (https://playwright.dev/docs/api/class-apiresponseassertions#api-response-assertions-to-be-ok)\nResponse has an OK status', 'Assertions | Playwright', 'These assertions allow to test any conditions, but do not auto-retry. Most of the time, web pages show information asynchronously, and using non-retrying assertions can lead to a flaky test.\n\nPrefer\nauto-retrying (https://playwright.dev/docs/test-assertions#auto-retrying-assertions)\nassertions whenever possible. For more complex assertions that need to be retried, use\nexpect.poll (https://playwright.dev/docs/test-assertions#expectpoll)\nor\nexpect.toPass (https://playwright.dev/docs/test-assertions#expecttopass)\n.\n\nAssertion\nDescription\nexpect(value).toBe() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be)\nValue is the same\nexpect(value).toBeCloseTo() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-close-to)\nNumber is approximately equal\nexpect(value).toBeDefined() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-defined)\nValue is not\n`undefined`\nexpect(value).toBeFalsy() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-falsy)\nValue is falsy, e.g.\n`false`\n,\n`0`\n,\n`null`\n, etc.\nexpect(value).toBeGreaterThan() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-greater-than)\nNumber is more than\nexpect(value).toBeGreaterThanOrEqual() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-greater-than-or-equal)\nNumber is more than or equal\nexpect(value).toBeInstanceOf() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-instance-of)\nObject is an instance of a class\nexpect(value).toBeLessThan() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-less-than)\nNumber is less than\nexpect(value).toBeLessThanOrEqual() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-less-than-or-equal)\nNumber is less than or equal\nexpect(value).toBeNaN() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-na-n)\nValue is\n`NaN`\nexpect(value).toBeNull() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-null)\nValue is\n`null`\nexpect(value).toBeTruthy() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-truthy)\nValue is truthy, i.e. not\n`false`\n,\n`0`\n,\n`null`\n, etc.\nexpect(value).toBeUndefined() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-undefined)\nValue is\n`undefined`\nexpect(value).toContain() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-contain-1)\nString contains a substring\nexpect(value).toContain() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-contain-2)\nArray or set contains an element\nexpect(value).toContainEqual() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-contain-equal)\nArray or set contains a similar element\nexpect(value).toEqual() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-equal)\nValue is similar - deep equality and pattern matching\nexpect(value).toHaveLength() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-have-length)\nArray or string has length\nexpect(value).toHaveProperty() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-have-property)\nObject has a property\nexpect(value).toMatch() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-match)\nString matches a regular expression\nexpect(value).toMatchObject() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-match-object)\nObject contains specified properties\nexpect(value).toStrictEqual() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-strict-equal)\nValue is similar, including property types\nexpect(value).toThrow() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-throw)\nFunction throws an error', 'Writing tests | Playwright', 'Playwright includes test assertions in the form of\n`expect`\nfunction. To make an assertion, call\n`expect(value)`\nand choose a matcher that reflects the expectation. There are many\ngeneric matchers (https://playwright.dev/docs/api/class-genericassertions)\nlike\n`toEqual`\n,\n`toContain`\n,\n`toBeTruthy`\nthat can be used to assert any conditions.\n\n```\n`expect(success).toBeTruthy();`\n```\n\nPlaywright also includes web-specific\nasync matchers (https://playwright.dev/docs/api/class-locatorassertions)\nthat will wait until the expected condition is met. Consider the following example:\n\n```\n`awaitexpect(page.getByTestId(\'status\')).toHaveText(\'Submitted\');`\n```\n\nPlaywright will be re-testing the element with the test id of\n`status`\nuntil the fetched element has the\n`"Submitted"`\ntext. It will re-fetch the element and check it over and over, until the condition is met or until the timeout is reached. You can either pass this timeout or configure it once via the\ntestConfig.expect (https://playwright.dev/docs/api/class-testconfig#test-config-expect)\nvalue in the test config.\n\nBy default, the timeout for assertions is set to 5 seconds. Learn more about\nvarious timeouts (https://playwright.dev/docs/test-timeouts)\n.']</t>
+          <t>['The following assertions will retry until the assertion passes, or the assertion timeout is reached. Note that retrying assertions are async, so you must\n`await`\nthem.\n\nAssertion\nDescription\nawait expect(locator).toBeAttached() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-attached)\nElement is attached\nawait expect(locator).toBeChecked() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-checked)\nCheckbox is checked\nawait expect(locator).toBeDisabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-disabled)\nElement is disabled\nawait expect(locator).toBeEditable() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-editable)\nElement is editable\nawait expect(locator).toBeEmpty() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-empty)\nContainer is empty\nawait expect(locator).toBeEnabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-enabled)\nElement is enabled\nawait expect(locator).toBeFocused() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-focused)\nElement is focused\nawait expect(locator).toBeHidden() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-hidden)\nElement is not visible\nawait expect(locator).toBeInViewport() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-in-viewport)\nElement intersects viewport\nawait expect(locator).toBeVisible() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-visible)\nElement is visible\nawait expect(locator).toContainText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-text)\nElement contains text\nawait expect(locator).toContainClass() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-class)\nElement has specified CSS classes\nawait expect(locator).toHaveAccessibleDescription() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-accessible-description)\nElement has a matching\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\nawait expect(locator).toHaveAccessibleName() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-accessible-name)\nElement has a matching\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\nawait expect(locator).toHaveAttribute() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-attribute)\nElement has a DOM attribute\nawait expect(locator).toHaveClass() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-class)\nElement has specified CSS class property\nawait expect(locator).toHaveCount() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-count)\nList has exact number of children\nawait expect(locator).toHaveCSS() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css)\nElement has CSS property\nawait expect(locator).toHaveId() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-id)\nElement has an ID\nawait expect(locator).toHaveJSProperty() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-js-property)\nElement has a JavaScript property\nawait expect(locator).toHaveRole() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-role)\nElement has a specific\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\nawait expect(locator).toHaveScreenshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-screenshot-1)\nElement has a screenshot\nawait expect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nElement matches text\nawait expect(locator).toHaveValue() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value)\nInput has a value\nawait expect(locator).toHaveValues() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-values)\nSelect has options selected\nawait expect(locator).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-match-aria-snapshot)\nElement matches the Aria snapshot\nawait expect(page).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-match-aria-snapshot)\nPage matches the Aria snapshot\nawait expect(page).toHaveScreenshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\nPage has a screenshot\nawait expect(page).toHaveTitle() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-title)\nPage has a title\nawait expect(page).toHaveURL() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-url)\nPage has a URL\nawait expect(response).toBeOK() (https://playwright.dev/docs/api/class-apiresponseassertions#api-response-assertions-to-be-ok)\nResponse has an OK status', "LocatorAssertions | Playwright\n\nThe\nLocatorAssertions (https://playwright.dev/docs/api/class-locatorassertions)\nclass provides assertion methods that can be used to make assertions about the\nLocator (https://playwright.dev/docs/api/class-locator)\nstate in the tests.\n\n```\n`import{test,expect}from'@playwright/test';test('status becomes submitted',async({page})=&gt;{// ...awaitpage.getByRole('button').click();awaitexpect(page.locator('.status')).toHaveText('Submitted');});`\n```", 'These assertions allow to test any conditions, but do not auto-retry. Most of the time, web pages show information asynchronously, and using non-retrying assertions can lead to a flaky test.\n\nPrefer\nauto-retrying (https://playwright.dev/docs/test-assertions#auto-retrying-assertions)\nassertions whenever possible. For more complex assertions that need to be retried, use\nexpect.poll (https://playwright.dev/docs/test-assertions#expectpoll)\nor\nexpect.toPass (https://playwright.dev/docs/test-assertions#expecttopass)\n.\n\nAssertion\nDescription\nexpect(value).toBe() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be)\nValue is the same\nexpect(value).toBeCloseTo() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-close-to)\nNumber is approximately equal\nexpect(value).toBeDefined() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-defined)\nValue is not\n`undefined`\nexpect(value).toBeFalsy() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-falsy)\nValue is falsy, e.g.\n`false`\n,\n`0`\n,\n`null`\n, etc.\nexpect(value).toBeGreaterThan() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-greater-than)\nNumber is more than\nexpect(value).toBeGreaterThanOrEqual() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-greater-than-or-equal)\nNumber is more than or equal\nexpect(value).toBeInstanceOf() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-instance-of)\nObject is an instance of a class\nexpect(value).toBeLessThan() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-less-than)\nNumber is less than\nexpect(value).toBeLessThanOrEqual() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-less-than-or-equal)\nNumber is less than or equal\nexpect(value).toBeNaN() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-na-n)\nValue is\n`NaN`\nexpect(value).toBeNull() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-null)\nValue is\n`null`\nexpect(value).toBeTruthy() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-truthy)\nValue is truthy, i.e. not\n`false`\n,\n`0`\n,\n`null`\n, etc.\nexpect(value).toBeUndefined() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-be-undefined)\nValue is\n`undefined`\nexpect(value).toContain() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-contain-1)\nString contains a substring\nexpect(value).toContain() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-contain-2)\nArray or set contains an element\nexpect(value).toContainEqual() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-contain-equal)\nArray or set contains a similar element\nexpect(value).toEqual() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-equal)\nValue is similar - deep equality and pattern matching\nexpect(value).toHaveLength() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-have-length)\nArray or string has length\nexpect(value).toHaveProperty() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-have-property)\nObject has a property\nexpect(value).toMatch() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-match)\nString matches a regular expression\nexpect(value).toMatchObject() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-match-object)\nObject contains specified properties\nexpect(value).toStrictEqual() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-strict-equal)\nValue is similar, including property types\nexpect(value).toThrow() (https://playwright.dev/docs/api/class-genericassertions#generic-assertions-to-throw)\nFunction throws an error', 'Assertions | Playwright', 'Auto-waiting | Playwright', 'Playwright Trace Viewer is a GUI tool that helps you explore recorded Playwright traces after the script has run. Traces are a great way for debugging your tests when they fail on CI. You can open traces\nlocally (https://playwright.dev/docs/trace-viewer#opening-trace-viewer)\nor in your browser on\ntrace.playwright.dev (https://trace.playwright.dev)\n.']</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4603,12 +5396,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>To make your test wait reliably, you should use an auto-retrying assertion instead of reading the text content directly.
-Your current code uses a non-retrying assertion (`expect(text).toBe(...)`), which can lead to flaky tests because it does not wait for the element's state to update. Instead, use the `toHaveText` matcher, which is an auto-retrying assertion that will wait until the condition is met:
+          <t>The right approach is to replace your non-retrying assertion with an auto-retrying assertion.
+Your current code uses `expect(text).toBe('Submitted')`, which is a non-retrying assertion. As noted in the documentation, these do not auto-retry and can lead to flaky tests because web pages often show information asynchronously.
+Instead, you should use the `toHaveText` auto-retrying assertion. This will automatically retry until the assertion passes or the timeout is reached.
+Replace your existing lines with:
 ```javascript
 await expect(page.getByTestId('status')).toHaveText('Submitted');
 ```
-Playwright will re-test the element until it has the "Submitted" text or until the timeout is reached.</t>
+This is the preferred approach because auto-retrying assertions are designed to handle the asynchronous nature of web pages.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4617,24 +5412,30 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0.010322</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>38493</v>
       </c>
       <c r="H76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3404255319148936</v>
+        <v>0.86</v>
       </c>
       <c r="J76" t="n">
-        <v>0.6666666666666666</v>
+        <v>5</v>
       </c>
       <c r="K76" t="n">
-        <v>0.9028571428390857</v>
+        <v>0.1886792452830189</v>
       </c>
       <c r="L76" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.94999999997625</v>
+      </c>
+      <c r="N76" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4646,7 +5447,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>['Authentication | Playwright', 'Global setup and teardown | Playwright', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", 'Fixtures | Playwright', 'Configuration (use) | Playwright']</t>
+          <t>['Authentication | Playwright', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", 'Global setup and teardown | Playwright', 'Project dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nare a list of projects that need to run before the tests in another project run. They can be useful for configuring the global setup actions so that one project depends on this running first. Using dependencies allows global setup to produce traces and other artifacts.', "First we add a new project with the name 'setup db'. We then give it a\ntestProject.testMatch (https://playwright.dev/docs/api/class-testproject#test-project-test-match)\nproperty in order to match the file called\n`global.setup.ts`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},// {//   other project// }]});`\n```\n\nThen we add the\ntestProject.dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nproperty to our projects that depend on the setup project and pass into the array the name of our dependency project, which we defined in the previous step:\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},{name:'chromium with db',use:{...devices['Desktop Chrome']},dependencies:['setup db'],},]});`\n```\n\nIn this example the 'chromium with db' project depends on the 'setup db' project. We then create a setup test, stored at root level of your project (note that setup and teardown code must be defined as regular tests by calling\ntest() (https://playwright.dev/docs/api/class-test#test-call)\nfunction):\n\ntests/global.setup.ts\n```\n`import{testassetup}from'@playwright/test';setup('create new database',async({})=&gt;{console.log('creating new database...');// Initialize the database});`\n```\n\ntests/menu.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('menu',async({page})=&gt;{// Your test that depends on the database});`\n```", 'Fixtures | Playwright', 'Regardless of the authentication strategy you choose, you are likely to store authenticated browser state on the file system.\n\nWe recommend to create\n`playwright/.auth`\ndirectory and add it to your\n`.gitignore`\n. Your authentication routine will produce authenticated browser state and save it to a file in this\n`playwright/.auth`\ndirectory. Later on, tests will reuse this state and start already authenticated.\n\ndanger\nThe browser state file may contain sensitive cookies and headers that could be used to impersonate you or your test account. We strongly discourage checking them into private or public repositories.\n\nBash\nPowerShell\nBatch\n```\n`mkdir-pplaywright/.authecho$\'\\nplaywright/.auth\'&gt;&gt;.gitignore`\n```\n```\n`New-Item-ItemType Directory-Force-Path playwright\\.authAdd-Content-path.gitignore"`r`nplaywright/.auth"`\n```\n```\n`mdplaywright\\.authecho. &gt;&gt; .gitignoreecho"playwright/.auth"&gt;&gt; .gitignore`\n```']</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4656,12 +5457,52 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>The recommended approach is to authenticate once in a setup project, save the authentication state, and reuse it to bootstrap each test.
-To set this up:
-1.  **Create a setup file** (e.g., `tests/auth.setup.ts`) that performs the authentication steps and saves the state using `page.context().storageState({ path: authFile })`.
-2.  **Configure a setup project** in your `playwright.config.ts` that runs this setup file.
-3.  **Declare the setup project as a dependency** for your testing projects.
-4.  **Use the `storageState` option** in your testing projects' configuration to point to the saved authentication file. This ensures all tests start already authenticated.</t>
+          <t>The recommended approach for tests that do not modify server-side state is to authenticate once in a setup project and reuse the authentication state.
+### 1. Create a setup file
+Create a file (e.g., `tests/auth.setup.ts`) to perform the authentication and save the state:
+```typescript
+import { test as setup, expect } from '@playwright/test';
+import path from 'path';
+const authFile = path.join(__dirname, '../playwright/.auth/user.json');
+setup('authenticate', async ({ page }) =&gt; {
+  // Perform authentication steps
+  await page.goto('https://github.com/login');
+  await page.getByLabel('Username or email address').fill('username');
+  await page.getByLabel('Password').fill('password');
+  await page.getByRole('button', { name: 'Sign in' }).click();
+  // Wait for authentication to complete
+  await page.waitForURL('https://github.com/');
+  await expect(page.getByRole('button', { name: 'View profile and more' })).toBeVisible();
+  // Save the state
+  await page.context().storageState({ path: authFile });
+});
+```
+### 2. Configure the project dependencies
+In your `playwright.config.ts`, define a `setup` project and add it as a dependency to your testing projects. Use the `storageState` property to point to the saved JSON file:
+```typescript
+import { defineConfig, devices } from '@playwright/test';
+export default defineConfig({
+  projects: [
+    // Setup project
+    { 
+      name: 'setup', 
+      testMatch: /.*\.setup\.ts/ 
+    },
+    // Testing project
+    {
+      name: 'chromium',
+      use: {
+        ...devices['Desktop Chrome'],
+        storageState: 'playwright/.auth/user.json',
+      },
+      dependencies: ['setup'],
+    },
+  ],
+});
+```
+### Important Considerations
+*   **Security:** The authentication state file contains sensitive cookies and headers. Add `playwright/.auth` to your `.gitignore` and do not check it into repositories.
+*   **Cleanup:** If you do not need to persist the state between runs, you can write the browser state to `testProject.outputDir`, which is automatically cleaned up before every test run. Otherwise, you must manually delete the stored state when it expires.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4670,91 +5511,107 @@
         </is>
       </c>
       <c r="F77" t="n">
+        <v>0.005384675</v>
+      </c>
+      <c r="G77" t="n">
+        <v>36296</v>
+      </c>
+      <c r="H77" t="n">
         <v>0.75</v>
       </c>
-      <c r="G77" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H77" t="n">
-        <v>5</v>
-      </c>
       <c r="I77" t="n">
-        <v>0.08737864077669903</v>
+        <v>0.36</v>
       </c>
       <c r="J77" t="n">
-        <v>0.2432432432432433</v>
+        <v>5</v>
       </c>
       <c r="K77" t="n">
-        <v>0.5833333333041666</v>
+        <v>0.05166051660516605</v>
       </c>
       <c r="L77" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.5845238095091964</v>
+      </c>
+      <c r="N77" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Our app has a dark theme and I want my tests to render it. How do I make Playwright emulate dark mode?</t>
+          <t>Our app asks for permission to send notifications the moment the dashboard loads, and the browser prompt sits on top of everything so the test can never reach the page behind it. I want the tests to behave as though the user already agreed, without clicking through a native dialog.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>['Emulate the users\n`"colorScheme"`\n. Supported values are \'light\' and \'dark\'. You can also emulate the media type with\npage.emulateMedia() (https://playwright.dev/docs/api/class-page#page-emulate-media)\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{colorScheme:\'dark\',},});`\n```\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test,expect}from\'@playwright/test\';test.use({colorScheme:\'dark\'// or \'light\'});test(\'my test with dark mode\',async({page})=&gt;{// ...});`\n```\n```\n`// Create context with dark modeconstcontext=awaitbrowser.newContext({colorScheme:\'dark\'// or \'light\'});// Create page with dark modeconstpage=awaitbrowser.newPage({colorScheme:\'dark\'// or \'light\'});// Change color scheme for the pageawaitpage.emulateMedia({colorScheme:\'dark\'});// Change media for pageawaitpage.emulateMedia({media:\'print\'});`\n```']</t>
+          <t>["Allow app to show system notifications.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{// Grants specified permissions to the browser context.permissions:['notifications'],},});`\n```\n```\n`constcontext=awaitbrowser.newContext({permissions:['notifications'],});`\n```\n\nAllow notifications for a specific domain.\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test.beforeEach(async({context})=&gt;{// Runs before each test and signs in each page.awaitcontext.grantPermissions(['notifications'],{origin:'https://skype.com'});});test('first',async({page})=&gt;{// page has notifications permission for https://skype.com.});`\n```\n```\n`awaitcontext.grantPermissions(['notifications'],{origin:'https://skype.com'});`\n```\n\nRevoke all permissions with\nbrowserContext.clearPermissions() (https://playwright.dev/docs/api/class-browsercontext#browser-context-clear-permissions)\n.\n\n```\n`// Libraryawaitcontext.clearPermissions();`\n```", 'Emulation | Playwright', 'Configuration (use) | Playwright']</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>['Emulate the users "colorScheme" . Supported values are \'light\' and \'dark\'.', "test.use({\n  colorScheme: 'dark' // or 'light'\n});\n\ntest('my test with dark mode', async ({ page }) =&gt; {\n  // ...\n});"]</t>
+          <t>['Allow app to show system notifications.', "export default defineConfig({ use: { // Grants specified permissions to the browser context. permissions: ['notifications'], }, });", "await context.grantPermissions(['notifications'], { origin: 'https://skype.com' });"]</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>To make Playwright emulate dark mode, you can use the `colorScheme` option in several ways:
-*   **In your configuration file (`playwright.config.ts`):**
-    ```typescript
-    use: {
-      colorScheme: 'dark',
-    },
-    ```
-*   **In a specific test:**
-    ```typescript
-    test.use({ colorScheme: 'dark' });
-    ```
-*   **When creating a browser context or page:**
-    ```typescript
-    const context = await browser.newContext({ colorScheme: 'dark' });
-    const page = await browser.newPage({ colorScheme: 'dark' });
-    ```
-*   **By changing it for an existing page:**
-    ```typescript
-    await page.emulateMedia({ colorScheme: 'dark' });
-    ```</t>
+          <t>To have the browser behave as though the user already agreed to notifications without clicking the native dialog, you can grant the permission in your configuration or at the context level.
+**Recommended approach (Global configuration):**
+You can grant the permission to all browser contexts by adding it to your `playwright.config.ts` file:
+```typescript
+import { defineConfig } from '@playwright/test';
+export default defineConfig({
+  use: {
+    // Grants specified permissions to the browser context.
+    permissions: ['notifications'],
+  },
+});
+```
+**Alternative approach (Per-context):**
+If you prefer to set this for a specific test or context, you can define it when creating the context:
+```typescript
+const context = await browser.newContext({
+  permissions: ['notifications'],
+});
+```
+**Alternative approach (Per-origin):**
+If you need to grant the permission for a specific domain, you can use `grantPermissions` within your test:
+```typescript
+await context.grantPermissions(['notifications'], { origin: 'https://skype.com' });
+```</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Emulate the user's colorScheme as 'dark'. Set it globally in the config (use: { colorScheme: 'dark' }) or per test with test.use({ colorScheme: 'dark' }).</t>
+          <t>Grant the permission to the browser context up front instead of dealing with the prompt. Set `permissions: ['notifications']` under `use` in the config to grant it for every test, or pass it to browser.newContext({ permissions: ['notifications'] }) for a manually created context. If you only want it for a particular site, call context.grantPermissions(['notifications'], { origin: 'https://example.com' }) — a beforeEach hook is a convenient place, so each test's page starts with the permission already granted for that origin.</t>
         </is>
       </c>
       <c r="F78" t="n">
+        <v>0.00795975</v>
+      </c>
+      <c r="G78" t="n">
+        <v>30159</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
         <v>0.75</v>
       </c>
-      <c r="G78" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H78" t="n">
-        <v>5</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0.1857142857142857</v>
-      </c>
       <c r="J78" t="n">
-        <v>0.5416666666666666</v>
+        <v>5</v>
       </c>
       <c r="K78" t="n">
-        <v>0.9999999999</v>
+        <v>0.2074074074074074</v>
       </c>
       <c r="L78" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.8333333332916666</v>
+      </c>
+      <c r="N78" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4776,7 +5633,9 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>To set up your test for a German user in the Berlin timezone, you can use `test.use` within your test file to override the locale and timezone settings:
+          <t>To verify your app for a German user in the Berlin timezone, you can set the `locale` to `'de-DE'` and the `timezoneId` to `'Europe/Berlin'`. You can apply these settings in two ways:
+**1. For a specific test (Recommended for individual test cases)**
+Use `test.use` within your test file to override the settings for that specific test:
 ```typescript
 test.use({
   locale: 'de-DE',
@@ -4787,12 +5646,23 @@
   // ...
 });
 ```
-Alternatively, you can set these options when creating a new browser context:
+**2. When creating a new browser context**
+If you are not using `test.use`, you can pass these options directly when creating a new context:
 ```typescript
 const context = await browser.newContext({
   locale: 'de-DE',
   timezoneId: 'Europe/Berlin',
 });
+```
+Additionally, you can set these globally for all tests in your `playwright.config.ts` file within the `use` object:
+```typescript
+import { defineConfig } from '@playwright/test';
+export default defineConfig({
+  use: {
+    locale: 'de-DE',
+    timezoneId: 'Europe/Berlin',
+  },
+});
 ```</t>
         </is>
       </c>
@@ -4802,24 +5672,30 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>0.0077935</v>
       </c>
       <c r="G79" t="n">
-        <v>0.29</v>
+        <v>29294</v>
       </c>
       <c r="H79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>0.175</v>
+        <v>0.67</v>
       </c>
       <c r="J79" t="n">
-        <v>0.4666666666666667</v>
+        <v>5</v>
       </c>
       <c r="K79" t="n">
+        <v>0.1075949367088608</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="M79" t="n">
         <v>0.99999999995</v>
       </c>
-      <c r="L79" t="n">
+      <c r="N79" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4831,7 +5707,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>["You can abort requests using\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nand\nroute.abort() (https://playwright.dev/docs/api/class-route#route-abort)\n.\n\n```\n`awaitpage.route('**/*.{png,jpg,jpeg}',route=&gt;route.abort());// Abort based on the request typeawaitpage.route('**/*',route=&gt;{returnroute.request().resourceType()==='image'?route.abort():route.continue();});`\n```", "You don't have to configure anything to mock network requests. Just define a custom\nRoute (https://playwright.dev/docs/api/class-route)\nthat mocks network for a browser context.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test.beforeEach(async({context})=&gt;{// Block any css requests for each test in this file.awaitcontext.route(/.css$/,route=&gt;route.abort());});test('loads page without css',async({page})=&gt;{awaitpage.goto('https://playwright.dev');// ... test goes here});`\n```\n\nAlternatively, you can use\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nto mock network in a single page.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('loads page without images',async({page})=&gt;{// Block png and jpeg images.awaitpage.route(/(png|jpeg)$/,route=&gt;route.abort());awaitpage.goto('https://playwright.dev');// ... test goes here});`\n```", 'Configuration (use) | Playwright', 'Network | Playwright', 'Route | Playwright\n\nWhenever a network route is set up with\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nor\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n, the\n`Route`\nobject allows to handle the route.\n\nLearn more about\nnetworking (https://playwright.dev/docs/network)\n.']</t>
+          <t>["You can abort requests using\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nand\nroute.abort() (https://playwright.dev/docs/api/class-route#route-abort)\n.\n\n```\n`awaitpage.route('**/*.{png,jpg,jpeg}',route=&gt;route.abort());// Abort based on the request typeawaitpage.route('**/*',route=&gt;{returnroute.request().resourceType()==='image'?route.abort():route.continue();});`\n```", "You don't have to configure anything to mock network requests. Just define a custom\nRoute (https://playwright.dev/docs/api/class-route)\nthat mocks network for a browser context.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test.beforeEach(async({context})=&gt;{// Block any css requests for each test in this file.awaitcontext.route(/.css$/,route=&gt;route.abort());});test('loads page without css',async({page})=&gt;{awaitpage.goto('https://playwright.dev');// ... test goes here});`\n```\n\nAlternatively, you can use\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nto mock network in a single page.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('loads page without images',async({page})=&gt;{// Block png and jpeg images.awaitpage.route(/(png|jpeg)$/,route=&gt;route.abort());awaitpage.goto('https://playwright.dev');// ... test goes here});`\n```"]</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4841,21 +5717,27 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Yes, you can stop images from loading to speed up your tests by using `page.route()` to abort requests for image files. You can do this in a few ways:
-*   **Abort based on file extension:**
+          <t>Yes, you can stop images from loading to speed up your tests by using `page.route()` or `context.route()` combined with `route.abort()`.
+You can implement this in two ways:
+**1. Using `page.route()` (for a single page)**
+You can block specific image file extensions or filter by resource type:
+*   **By file extension:**
     ```javascript
     await page.route('**/*.{png,jpg,jpeg}', route =&gt; route.abort());
     ```
-*   **Abort based on the request type:**
+*   **By resource type:**
     ```javascript
     await page.route('**/*', route =&gt; {
       return route.request().resourceType() === 'image' ? route.abort() : route.continue();
     });
     ```
-*   **Abort using a regular expression:**
-    ```javascript
-    await page.route(/(png|jpeg)$/, route =&gt; route.abort());
-    ```</t>
+**2. Using `context.route()` (for an entire test file)**
+If you want to apply this to every test in a file, use `test.beforeEach` with the browser context:
+```javascript
+test.beforeEach(async ({ context }) =&gt; {
+  await context.route(/.png|jpeg$/, route =&gt; route.abort());
+});
+```</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4864,24 +5746,30 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0.007760250000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>0.67</v>
+        <v>29536</v>
       </c>
       <c r="H80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2278481012658228</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="K80" t="n">
-        <v>0.8874999999778125</v>
+        <v>0.1735537190082645</v>
       </c>
       <c r="L80" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.99999999995</v>
+      </c>
+      <c r="N80" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4893,7 +5781,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>['Mock APIs | Playwright', 'The following code will intercept all the calls to\n`*/**/api/v1/fruits`\nand will return a custom response instead. No requests to the API will be made. The test goes to the URL that uses the mocked route and asserts that mock data is present on the page.\n\n```\n`test("mocks a fruit and doesn\'t call api",async({page})=&gt;{// Mock the api call before navigatingawaitpage.route(\'*/**/api/v1/fruits\',asyncroute=&gt;{constjson=[{name:\'Strawberry\',id:21}];awaitroute.fulfill({json});});// Go to the pageawaitpage.goto(\'https://demo.playwright.dev/api-mocking\');// Assert that the Strawberry fruit is visibleawaitexpect(page.getByText(\'Strawberry\')).toBeVisible();});`\n```\n\nYou can see from the trace of the example test that the API was never called, it was however fulfilled with the mock data.\n\nRead more about\nadvanced networking (https://playwright.dev/docs/network)\n.', "Added before v1.9\n\nroute.fulfill\n\nFulfills route's request with given response.\n\nUsage\n\nAn example of fulfilling all requests with 404 responses:\n\n```\n`awaitpage.route('**/*',asyncroute=&gt;{awaitroute.fulfill({status:404,contentType:'text/plain',body:'Not Found!'});});`\n```\n\nAn example of serving static file:\n\n```\n`awaitpage.route('**/xhr_endpoint',route=&gt;route.fulfill({path:'mock_data.json'}));`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`body`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fulfill-option-body)\nResponse body.\n`contentType`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fulfill-option-content-type)\nIf set, equals to setting\n`Content-Type`\nresponse header.\n`headers`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n,\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fulfill-option-headers)\nResponse headers. Header values will be converted to a string.\n`json`\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n(optional)\nAdded in: v1.29\n# (https://playwright.dev/docs/api/class-route#route-fulfill-option-json)\nJSON response. This method will set the content type to\n`application/json`\nif not set.\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fulfill-option-path)\nFile path to respond with. The content type will be inferred from file extension. If\n`path`\nis a relative path, then it is resolved relative to the current working directory.\n`response`\nAPIResponse (https://playwright.dev/docs/api/class-apiresponse)\n(optional)\nAdded in: v1.15\n# (https://playwright.dev/docs/api/class-route#route-fulfill-option-response)\nAPIResponse (https://playwright.dev/docs/api/class-apiresponse)\nto fulfill route's request with. Individual fields of the response (such as headers) can be overridden using fulfill options.\n`status`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fulfill-option-status)\nResponse status code, defaults to\n`200`\n.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-route#route-fulfill-return)", 'Route | Playwright\n\nWhenever a network route is set up with\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nor\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n, the\n`Route`\nobject allows to handle the route.\n\nLearn more about\nnetworking (https://playwright.dev/docs/network)\n.', 'WebSocketRoute | Playwright\n\nWhenever a\nWebSocket (https://developer.mozilla.org/en-US/docs/Web/API/WebSocket)\nroute is set up with\npage.routeWebSocket() (https://playwright.dev/docs/api/class-page#page-route-web-socket)\nor\nbrowserContext.routeWebSocket() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route-web-socket)\n, the\n`WebSocketRoute`\nobject allows to handle the WebSocket, like an actual server would do.\n\nMocking\n\nBy default, the routed WebSocket will not connect to the server. This way, you can mock entire communication over the WebSocket. Here is an example that responds to a\n`"request"`\nwith a\n`"response"`\n.\n\n```\n`awaitpage.routeWebSocket(\'wss://example.com/ws\',ws=&gt;{ws.onMessage(message=&gt;{if(message===\'request\')ws.send(\'response\');});});`\n```\n\nSince we do not call\nwebSocketRoute.connectToServer() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-connect-to-server)\ninside the WebSocket route handler, Playwright assumes that WebSocket will be mocked, and opens the WebSocket inside the page automatically.\n\nHere is another example that handles JSON messages:\n\n```\n`awaitpage.routeWebSocket(\'wss://example.com/ws\',ws=&gt;{ws.onMessage(message=&gt;{constjson=JSON.parse(message);if(json.request===\'question\')ws.send(JSON.stringify({response:\'answer\'}));});});`\n```\n\nIntercepting\n\nAlternatively, you may want to connect to the actual server, but intercept messages in-between and modify or block them. Calling\nwebSocketRoute.connectToServer() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-connect-to-server)\nreturns a server-side\n`WebSocketRoute`\ninstance that you can send messages to, or handle incoming messages.\n\nBelow is an example that modifies some messages sent by the page to the server. Messages sent from the server to the page are left intact, relying on the default forwarding.\n\n```\n`awaitpage.routeWebSocket(\'/ws\',ws=&gt;{constserver=ws.connectToServer();ws.onMessage(message=&gt;{if(message===\'request\')server.send(\'request2\');elseserver.send(message);});});`\n```\n\nAfter connecting to the server, all\nmessages are forwarded\nbetween the page and the server by default.\n\nHowever, if you call\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\non the original route, messages from the page to the server\nwill not be forwarded\nanymore, but should instead be handled by the\nhandler (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message-option-handler)\n.\n\nSimilarly, calling\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\non the server-side WebSocket will\nstop forwarding messages\nfrom the server to the page, and\nhandler (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message-option-handler)\nshould take care of them.\n\nThe following example blocks some messages in both directions. Since it calls\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\nin both directions, there is no automatic forwarding at all.\n\n```\n`awaitpage.routeWebSocket(\'/ws\',ws=&gt;{constserver=ws.connectToServer();ws.onMessage(message=&gt;{if(message!==\'blocked-from-the-page\')server.send(message);});server.onMessage(message=&gt;{if(message!==\'blocked-from-the-server\')ws.send(message);});});`\n```', "Now that you have the HAR file recorded and modified the mock data, it can be used to serve matching responses in the test. For this, just turn off or simply remove the\n`update`\noption. This will run the test against the HAR file instead of hitting the API.\n\n```\n`test('gets the json from HAR and checks the new fruit has been added',async({page})=&gt;{// Replay API requests from HAR.// Either use a matching response from the HAR,// or abort the request if nothing matches.awaitpage.routeFromHAR('./hars/fruit.har',{url:'*/**/api/v1/fruits',update:false,});// Go to the pageawaitpage.goto('https://demo.playwright.dev/api-mocking');// Assert that the Playwright fruit is visibleawaitexpect(page.getByText('Playwright',{exact:true})).toBeVisible();});`\n```\n\nIn the trace of our test we can see that the route was fulfilled from the HAR file and the API was not called.\n\nIf we inspect the response we can see our new fruit was added to the JSON, which was done by manually updating the hashed\n`.txt`\nfile inside the\n`hars`\nfolder.\n\nHAR replay matches URL and HTTP method strictly. For POST requests, it also matches POST payloads strictly. If multiple recordings match a request, the one with the most matching headers is picked. An entry resulting in a redirect will be followed automatically.\n\nSimilar to when recording, if given HAR file name ends with\n`.zip`\n, it is considered an archive containing the HAR file along with network payloads stored as separate entries. You can also extract this archive, edit payloads or HAR log manually and point to the extracted har file. All the payloads will be resolved relative to the extracted har file on the file system.", "A HAR file is an\nHTTP Archive (http://www.softwareishard.com/blog/har-12-spec/)\nfile that contains a record of all the network requests that are made when a page is loaded. It contains information about the request and response headers, cookies, content, timings, and more. You can use HAR files to mock network requests in your tests. You'll need to:\n\nRecord a HAR file.\nCommit the HAR file alongside the tests.\nRoute requests using the saved HAR files in the tests."]</t>
+          <t>['Mock APIs | Playwright', 'The following code will intercept all the calls to\n`*/**/api/v1/fruits`\nand will return a custom response instead. No requests to the API will be made. The test goes to the URL that uses the mocked route and asserts that mock data is present on the page.\n\n```\n`test("mocks a fruit and doesn\'t call api",async({page})=&gt;{// Mock the api call before navigatingawaitpage.route(\'*/**/api/v1/fruits\',asyncroute=&gt;{constjson=[{name:\'Strawberry\',id:21}];awaitroute.fulfill({json});});// Go to the pageawaitpage.goto(\'https://demo.playwright.dev/api-mocking\');// Assert that the Strawberry fruit is visibleawaitexpect(page.getByText(\'Strawberry\')).toBeVisible();});`\n```\n\nYou can see from the trace of the example test that the API was never called, it was however fulfilled with the mock data.\n\nRead more about\nadvanced networking (https://playwright.dev/docs/network)\n.', 'Route | Playwright\n\nWhenever a network route is set up with\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nor\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n, the\n`Route`\nobject allows to handle the route.\n\nLearn more about\nnetworking (https://playwright.dev/docs/network)\n.', 'WebSocketRoute | Playwright\n\nWhenever a\nWebSocket (https://developer.mozilla.org/en-US/docs/Web/API/WebSocket)\nroute is set up with\npage.routeWebSocket() (https://playwright.dev/docs/api/class-page#page-route-web-socket)\nor\nbrowserContext.routeWebSocket() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route-web-socket)\n, the\n`WebSocketRoute`\nobject allows to handle the WebSocket, like an actual server would do.\n\nMocking\n\nBy default, the routed WebSocket will not connect to the server. This way, you can mock entire communication over the WebSocket. Here is an example that responds to a\n`"request"`\nwith a\n`"response"`\n.\n\n```\n`awaitpage.routeWebSocket(\'wss://example.com/ws\',ws=&gt;{ws.onMessage(message=&gt;{if(message===\'request\')ws.send(\'response\');});});`\n```\n\nSince we do not call\nwebSocketRoute.connectToServer() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-connect-to-server)\ninside the WebSocket route handler, Playwright assumes that WebSocket will be mocked, and opens the WebSocket inside the page automatically.\n\nHere is another example that handles JSON messages:\n\n```\n`awaitpage.routeWebSocket(\'wss://example.com/ws\',ws=&gt;{ws.onMessage(message=&gt;{constjson=JSON.parse(message);if(json.request===\'question\')ws.send(JSON.stringify({response:\'answer\'}));});});`\n```\n\nIntercepting\n\nAlternatively, you may want to connect to the actual server, but intercept messages in-between and modify or block them. Calling\nwebSocketRoute.connectToServer() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-connect-to-server)\nreturns a server-side\n`WebSocketRoute`\ninstance that you can send messages to, or handle incoming messages.\n\nBelow is an example that modifies some messages sent by the page to the server. Messages sent from the server to the page are left intact, relying on the default forwarding.\n\n```\n`awaitpage.routeWebSocket(\'/ws\',ws=&gt;{constserver=ws.connectToServer();ws.onMessage(message=&gt;{if(message===\'request\')server.send(\'request2\');elseserver.send(message);});});`\n```\n\nAfter connecting to the server, all\nmessages are forwarded\nbetween the page and the server by default.\n\nHowever, if you call\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\non the original route, messages from the page to the server\nwill not be forwarded\nanymore, but should instead be handled by the\nhandler (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message-option-handler)\n.\n\nSimilarly, calling\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\non the server-side WebSocket will\nstop forwarding messages\nfrom the server to the page, and\nhandler (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message-option-handler)\nshould take care of them.\n\nThe following example blocks some messages in both directions. Since it calls\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\nin both directions, there is no automatic forwarding at all.\n\n```\n`awaitpage.routeWebSocket(\'/ws\',ws=&gt;{constserver=ws.connectToServer();ws.onMessage(message=&gt;{if(message!==\'blocked-from-the-page\')server.send(message);});server.onMessage(message=&gt;{if(message!==\'blocked-from-the-server\')ws.send(message);});});`\n```', "A HAR file is an\nHTTP Archive (http://www.softwareishard.com/blog/har-12-spec/)\nfile that contains a record of all the network requests that are made when a page is loaded. It contains information about the request and response headers, cookies, content, timings, and more. You can use HAR files to mock network requests in your tests. You'll need to:\n\nRecord a HAR file.\nCommit the HAR file alongside the tests.\nRoute requests using the saved HAR files in the tests.", "Sometimes, it is essential to make an API request, but the response needs to be patched to allow for reproducible testing. In that case, instead of mocking the request, one can perform the request and fulfill it with the modified response.\n\nIn the example below we intercept the call to the fruit API and add a new fruit called 'Loquat', to the data. We then go to the url and assert that this data is there:\n\n```\n`test('gets the json from api and adds a new fruit',async({page})=&gt;{// Get the response and add to itawaitpage.route('*/**/api/v1/fruits',asyncroute=&gt;{constresponse=awaitroute.fetch();constjson=awaitresponse.json();json.push({name:'Loquat',id:100});// Fulfill using the original response, while patching the response body// with the given JSON object.awaitroute.fulfill({response,json});});// Go to the pageawaitpage.goto('https://demo.playwright.dev/api-mocking');// Assert that the new fruit is visibleawaitexpect(page.getByText('Loquat',{exact:true})).toBeVisible();});`\n```\n\nIn the trace of our test we can see that the API was called and the response was modified.\n\nBy inspecting the response we can see that our new fruit was added to the list.\n\nRead more about\nadvanced networking (https://playwright.dev/docs/network)\n.", "Now that you have the HAR file recorded and modified the mock data, it can be used to serve matching responses in the test. For this, just turn off or simply remove the\n`update`\noption. This will run the test against the HAR file instead of hitting the API.\n\n```\n`test('gets the json from HAR and checks the new fruit has been added',async({page})=&gt;{// Replay API requests from HAR.// Either use a matching response from the HAR,// or abort the request if nothing matches.awaitpage.routeFromHAR('./hars/fruit.har',{url:'*/**/api/v1/fruits',update:false,});// Go to the pageawaitpage.goto('https://demo.playwright.dev/api-mocking');// Assert that the Playwright fruit is visibleawaitexpect(page.getByText('Playwright',{exact:true})).toBeVisible();});`\n```\n\nIn the trace of our test we can see that the route was fulfilled from the HAR file and the API was not called.\n\nIf we inspect the response we can see our new fruit was added to the JSON, which was done by manually updating the hashed\n`.txt`\nfile inside the\n`hars`\nfolder.\n\nHAR replay matches URL and HTTP method strictly. For POST requests, it also matches POST payloads strictly. If multiple recordings match a request, the one with the most matching headers is picked. An entry resulting in a redirect will be followed automatically.\n\nSimilar to when recording, if given HAR file name ends with\n`.zip`\n, it is considered an archive containing the HAR file along with network payloads stored as separate entries. You can also extract this archive, edit payloads or HAR log manually and point to the extracted har file. All the payloads will be resolved relative to the extracted har file on the file system."]</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4903,9 +5791,10 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>To ensure your test does not depend on a real backend and returns fixed data without calling the API, you can use one of the following methods provided by Playwright:
-### 1. Using `page.route()`
-You can intercept specific API calls and fulfill them with custom data using `page.route()`. This prevents the actual API from being called.
+          <t>To ensure your test does not depend on a real backend and that the API is never called, you can use one of the following two approaches:
+### 1. Mocking with `page.route()`
+This approach intercepts specific network requests and fulfills them with custom data, preventing any actual request from reaching the server.
+Use `page.route()` to match the URL and `route.fulfill()` to provide the response:
 ```javascript
 test("mocks a fruit and doesn't call api", async ({ page }) =&gt; {
   // Mock the api call before navigating
@@ -4915,15 +5804,16 @@
   });
   // Go to the page
   await page.goto('https://demo.playwright.dev/api-mocking');
-  // Assert that the mock data is present
+  // Assert that the Strawberry fruit is visible
   await expect(page.getByText('Strawberry')).toBeVisible();
 });
 ```
-### 2. Using HAR files
-You can record network requests into a HAR file and then configure your test to replay responses from that file instead of hitting the real API. By setting `update: false`, Playwright will serve the matching responses from the HAR file.
+### 2. Replaying from a HAR file
+You can record network traffic into a HAR file and then configure your test to replay responses from that file instead of hitting the API.
+Use `page.routeFromHAR()` with the `update: false` option:
 ```javascript
 test('gets the json from HAR', async ({ page }) =&gt; {
-  // Replay API requests from HAR
+  // Replay API requests from HAR.
   await page.routeFromHAR('./hars/fruit.har', {
     url: '*/**/api/v1/fruits',
     update: false,
@@ -4932,8 +5822,8 @@
   await expect(page.getByText('Playwright', { exact: true })).toBeVisible();
 });
 ```
-### 3. Mocking WebSockets
-If you are using WebSockets, you can use `page.routeWebSocket()`. By default, if you do not call `webSocketRoute.connectToServer()`, Playwright will not connect to the real server, allowing you to mock the entire communication manually.
+### WebSocket Mocking
+If you are using WebSockets, you can mock the entire communication by using `page.routeWebSocket()`. By default, if you do not call `webSocketRoute.connectToServer()`, the WebSocket will not connect to the server, allowing you to handle messages manually:
 ```javascript
 await page.routeWebSocket('wss://example.com/ws', ws =&gt; {
   ws.onMessage(message =&gt; {
@@ -4949,24 +5839,30 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0.75</v>
+        <v>0.009874250000000001</v>
       </c>
       <c r="G81" t="n">
-        <v>0.6</v>
+        <v>35572</v>
       </c>
       <c r="H81" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I81" t="n">
-        <v>0.04961832061068702</v>
+        <v>0.62</v>
       </c>
       <c r="J81" t="n">
-        <v>0.4193548387096774</v>
+        <v>5</v>
       </c>
       <c r="K81" t="n">
-        <v>0.999999999975</v>
+        <v>0.05223880597014925</v>
       </c>
       <c r="L81" t="n">
+        <v>0.4516129032258064</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.91666666664375</v>
+      </c>
+      <c r="N81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4978,7 +5874,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>['Projects | Playwright', "TestProject | Playwright\n\nPlaywright Test supports running multiple test projects at the same time. This is useful for running tests in multiple configurations. For example, consider running tests against multiple browsers. This type describes format of a project in the configuration file, to access resolved configuration parameters at run time use\nFullProject (https://playwright.dev/docs/api/class-fullproject)\n.\n\n`TestProject`\nencapsulates configuration specific to a single project. Projects are configured in\ntestConfig.projects (https://playwright.dev/docs/api/class-testconfig#test-config-projects)\nspecified in the\nconfiguration file (https://playwright.dev/docs/test-configuration)\n. Note that all properties of\nTestProject (https://playwright.dev/docs/api/class-testproject)\nare available in the top-level\nTestConfig (https://playwright.dev/docs/api/class-testconfig)\n, in which case they are shared between all projects.\n\nHere is an example configuration that runs every test in Chromium, Firefox and WebKit, both Desktop and Mobile versions.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({// Options shared for all projects.timeout:30000,use:{ignoreHTTPSErrors:true,},// Options specific to each project.projects:[{name:'chromium',use:devices['Desktop Chrome'],},{name:'firefox',use:devices['Desktop Firefox'],},{name:'webkit',use:devices['Desktop Safari'],},{name:'Mobile Chrome',use:devices['Pixel 5'],},{name:'Mobile Safari',use:devices['iPhone 12'],},],});`\n```", "By using\nprojects\nyou can run your tests in multiple browsers such as chromium, webkit and firefox as well as branded browsers such as Google Chrome and Microsoft Edge. Playwright can also run on emulated tablet and mobile devices. See the\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nfor a complete list of selected desktop, tablet and mobile devices.\n\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[{name:'chromium',use:{...devices['Desktop Chrome']},},{name:'firefox',use:{...devices['Desktop Firefox']},},{name:'webkit',use:{...devices['Desktop Safari']},},/* Test against mobile viewports. */{name:'Mobile Chrome',use:{...devices['Pixel 5']},},{name:'Mobile Safari',use:{...devices['iPhone 12']},},/* Test against branded browsers. */{name:'Microsoft Edge',use:{...devices['Desktop Edge'],channel:'msedge'},},{name:'Google Chrome',use:{...devices['Desktop Chrome'],channel:'chrome'},},],});`\n```", "Playwright will run all projects by default.\n\n```\n`npx playwrighttestRunning7tests using5workers✓[chromium]› example.spec.ts:3:1 › basictest(2s)✓[firefox]› example.spec.ts:3:1 › basictest(2s)✓[webkit]› example.spec.ts:3:1 › basictest(2s)✓[Mobile Chrome]› example.spec.ts:3:1 › basictest(2s)✓[Mobile Safari]› example.spec.ts:3:1 › basictest(2s)✓[Microsoft Edge]› example.spec.ts:3:1 › basictest(2s)✓[Google Chrome]› example.spec.ts:3:1 › basictest(2s)`\n```\n\nUse the\n`--project`\ncommand line option to run a single project.\n\n```\n`npx playwrighttest--project=firefoxRunning1testusing1worker✓[firefox]› example.spec.ts:3:1 › basictest(2s)`\n```\n\nThe VS Code test runner runs your tests on the default browser of Chrome. To run on other/multiple browsers click the play button's dropdown from the testing sidebar and choose another profile or modify the default profile by clicking\nSelect Default Profile\nand select the browsers you wish to run your tests on.\n\nChoose a specific profile, various profiles or all profiles to run tests on."]</t>
+          <t>['Projects | Playwright', "By using\nprojects\nyou can run your tests in multiple browsers such as chromium, webkit and firefox as well as branded browsers such as Google Chrome and Microsoft Edge. Playwright can also run on emulated tablet and mobile devices. See the\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nfor a complete list of selected desktop, tablet and mobile devices.\n\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[{name:'chromium',use:{...devices['Desktop Chrome']},},{name:'firefox',use:{...devices['Desktop Firefox']},},{name:'webkit',use:{...devices['Desktop Safari']},},/* Test against mobile viewports. */{name:'Mobile Chrome',use:{...devices['Pixel 5']},},{name:'Mobile Safari',use:{...devices['iPhone 12']},},/* Test against branded browsers. */{name:'Microsoft Edge',use:{...devices['Desktop Edge'],channel:'msedge'},},{name:'Google Chrome',use:{...devices['Desktop Chrome'],channel:'chrome'},},],});`\n```", "Playwright can run your tests in multiple browsers and configurations by setting up\nprojects\nin the config. You can also add\ndifferent options (https://playwright.dev/docs/test-configuration)\nfor each project.\n\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[/* Test against desktop browsers */{name:'chromium',use:{...devices['Desktop Chrome']},},{name:'firefox',use:{...devices['Desktop Firefox']},},{name:'webkit',use:{...devices['Desktop Safari']},},/* Test against mobile viewports. */{name:'Mobile Chrome',use:{...devices['Pixel 5']},},{name:'Mobile Safari',use:{...devices['iPhone 12']},},/* Test against branded browsers. */{name:'Google Chrome',use:{...devices['Desktop Chrome'],channel:'chrome'},// or 'chrome-beta'},{name:'Microsoft Edge',use:{...devices['Desktop Edge'],channel:'msedge'},// or 'msedge-dev'},],});`\n```\n\nPlaywright will run all projects by default.\n\n```\n`npx playwrighttestRunning7tests using5workers✓[chromium]› example.spec.ts:3:1 › basictest(2s)✓[firefox]› example.spec.ts:3:1 › basictest(2s)✓[webkit]› example.spec.ts:3:1 › basictest(2s)✓[Mobile Chrome]› example.spec.ts:3:1 › basictest(2s)✓[Mobile Safari]› example.spec.ts:3:1 › basictest(2s)✓[Google Chrome]› example.spec.ts:3:1 › basictest(2s)✓[Microsoft Edge]› example.spec.ts:3:1 › basictest(2s)`\n```\n\nUse the\n`--project`\ncommand line option to run a single project.\n\n```\n`npx playwrighttest--project=firefoxRunning1testusing1worker✓[firefox]› example.spec.ts:3:1 › basictest(2s)`\n```\n\nWith the VS Code extension you can run your tests on different browsers by checking the checkbox next to the browser name in the Playwright sidebar. These names are defined in your Playwright config file under the projects section. The default config when installing Playwright gives you 3 projects, Chromium, Firefox and WebKit. The first project is selected by default.\n\nTo run tests on multiple projects(browsers), select each project by checking the checkboxes next to the project name.", 'Command line | Playwright\n\nPlaywright provides a powerful command line interface for running tests, generating code, debugging, and more. The most up to date list of commands and arguments available on the CLI can always be retrieved via\n`npx playwright --help`\n.', "Playwright will run all projects by default.\n\n```\n`npx playwrighttestRunning7tests using5workers✓[chromium]› example.spec.ts:3:1 › basictest(2s)✓[firefox]› example.spec.ts:3:1 › basictest(2s)✓[webkit]› example.spec.ts:3:1 › basictest(2s)✓[Mobile Chrome]› example.spec.ts:3:1 › basictest(2s)✓[Mobile Safari]› example.spec.ts:3:1 › basictest(2s)✓[Microsoft Edge]› example.spec.ts:3:1 › basictest(2s)✓[Google Chrome]› example.spec.ts:3:1 › basictest(2s)`\n```\n\nUse the\n`--project`\ncommand line option to run a single project.\n\n```\n`npx playwrighttest--project=firefoxRunning1testusing1worker✓[firefox]› example.spec.ts:3:1 › basictest(2s)`\n```\n\nThe VS Code test runner runs your tests on the default browser of Chrome. To run on other/multiple browsers click the play button's dropdown from the testing sidebar and choose another profile or modify the default profile by clicking\nSelect Default Profile\nand select the browsers you wish to run your tests on.\n\nChoose a specific profile, various profiles or all profiles to run tests on."]</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4989,7 +5885,8 @@
       <c r="D82" t="inlineStr">
         <is>
           <t>To run your tests in Firefox only, use the `--project` command line option:
-`npx playwright test --project=firefox`</t>
+`npx playwright test --project=firefox`
+Alternatively, if you are using the VS Code extension, you can select the Firefox project by checking the checkbox next to the browser name in the Playwright sidebar.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4998,24 +5895,30 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0.008645</v>
       </c>
       <c r="G82" t="n">
-        <v>0.67</v>
+        <v>33525</v>
       </c>
       <c r="H82" t="n">
-        <v>5</v>
+        <v>0.75</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.57</v>
       </c>
       <c r="J82" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="K82" t="n">
-        <v>0.6388888888675925</v>
+        <v>0.2826086956521739</v>
       </c>
       <c r="L82" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.5888888888692593</v>
+      </c>
+      <c r="N82" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5027,7 +5930,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>['Trace viewer | Playwright', 'Trace viewer | Playwright', 'Playwright Trace Viewer is a GUI tool that helps you explore recorded Playwright traces after the script has run. Traces are a great way for debugging your tests when they fail on CI. You can open traces\nlocally (https://playwright.dev/docs/trace-viewer#opening-trace-viewer)\nor in your browser on\ntrace.playwright.dev (https://trace.playwright.dev)\n.', "Traces should be run on continuous integration on the first retry of a failed test by setting the\n`trace: 'on-first-retry'`\noption in the test configuration file. This will produce a\n`trace.zip`\nfile for each test that was retried.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({retries:1,use:{trace:'on-first-retry',},});`\n```\n```\n`constbrowser=awaitchromium.launch();constcontext=awaitbrowser.newContext();// Start tracing before creating / navigating a page.awaitcontext.tracing.start({screenshots:true,snapshots:true});constpage=awaitcontext.newPage();awaitpage.goto('https://playwright.dev');// Stop tracing and export it into a zip archive.awaitcontext.tracing.stop({path:'trace.zip'});`\n```\n\nAvailable options to record a trace:\n\n`'on-first-retry'`\n- Record a trace only when retrying a test for the first time.\n`'on-all-retries'`\n- Record traces for all test retries.\n`'off'`\n- Do not record a trace.\n`'on'`\n- Record a trace for each test. (not recommended as it's performance heavy)\n`'retain-on-failure'`\n- Record a trace for each test, but remove it from successful test runs.\n\nYou can also use\n`trace: 'retain-on-failure'`\nif you do not enable retries but still want traces for failed tests.\n\nThere are more granular options available, see\ntestOptions.trace (https://playwright.dev/docs/api/class-testoptions#test-options-trace)\n.\n\nIf you are not using Playwright as a Test Runner, use the\nbrowserContext.tracing (https://playwright.dev/docs/api/class-browsercontext#browser-context-tracing)\nAPI instead.", 'Debugging Tests | Playwright', "By default the\nplaywright.config (https://playwright.dev/docs/trace-viewer#tracing-on-ci)\nfile contains the configuration needed to create a\n`trace.zip`\nfile for each test. Traces are setup to run\n`on-first-retry`\n, meaning they run on the first retry of a failed test. Also\n`retries`\nare set to 2 when running on CI and 0 locally. This means the traces are recorded on the first retry of a failed test but not on the first run and not on the second retry.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({retries:process.env.CI?2:0,// set to 2 when running on CI// ...use:{trace:'on-first-retry',// record traces on first retry of each test},});`\n```\n\nTo learn more about available options to record a trace check out our detailed guide on\nTrace Viewer (https://playwright.dev/docs/trace-viewer)\n.\n\nTraces are normally run in a Continuous Integration (CI) environment, because locally you can use\nUI Mode (https://playwright.dev/docs/test-ui-mode)\nfor developing and debugging tests. However, if you want to run traces locally without using\nUI Mode (https://playwright.dev/docs/test-ui-mode)\n, you can force tracing to be on with\n`--trace on`\n.\n\n```\n`npx playwrighttest--traceon`\n```", 'Configuration (use) | Playwright']</t>
+          <t>["By default the\nplaywright.config (https://playwright.dev/docs/trace-viewer#tracing-on-ci)\nfile contains the configuration needed to create a\n`trace.zip`\nfile for each test. Traces are setup to run\n`on-first-retry`\n, meaning they run on the first retry of a failed test. Also\n`retries`\nare set to 2 when running on CI and 0 locally. This means the traces are recorded on the first retry of a failed test but not on the first run and not on the second retry.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({retries:process.env.CI?2:0,// set to 2 when running on CI// ...use:{trace:'on-first-retry',// record traces on first retry of each test},});`\n```\n\nTo learn more about available options to record a trace check out our detailed guide on\nTrace Viewer (https://playwright.dev/docs/trace-viewer)\n.\n\nTraces are normally run in a Continuous Integration (CI) environment, because locally you can use\nUI Mode (https://playwright.dev/docs/test-ui-mode)\nfor developing and debugging tests. However, if you want to run traces locally without using\nUI Mode (https://playwright.dev/docs/test-ui-mode)\n, you can force tracing to be on with\n`--trace on`\n.\n\n```\n`npx playwrighttest--traceon`\n```", 'Trace viewer | Playwright', 'Trace viewer | Playwright', 'Videos | Playwright', "Playwright Test can record videos for your tests, controlled by the\n`video`\noption in your Playwright config. By default videos are off.\n\n`'off'`\n- Do not record video.\n`'on'`\n- Record video for each test.\n`'retain-on-failure'`\n- Record video for each test, but remove all videos from successful test runs.\n`'on-first-retry'`\n- Record video only when retrying a test for the first time.\n\nVideo files will appear in the test output directory, typically\n`test-results`\n. See\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nfor advanced video configuration.\n\nVideos are saved upon\nbrowser context (https://playwright.dev/docs/browser-contexts)\nclosure at the end of a test. If you create a browser context manually, make sure to await\nbrowserContext.close() (https://playwright.dev/docs/api/class-browsercontext#browser-context-close)\n.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:'on-first-retry',},});`\n```\n```\n`constcontext=awaitbrowser.newContext({recordVideo:{dir:'videos/'}});// Make sure to await close, so that videos are saved.awaitcontext.close();`\n```\n\nYou can also specify video size and annotation. The video size defaults to the viewport size scaled down to fit 800x800. The video of the viewport is placed in the top-left corner of the output video, scaled down to fit if necessary. You may need to set the viewport size to match your desired video size.\n\nWhen\n`show: { actions }`\nis specified, each action will be visually highlighted in the video with the element outline and action title subtitle. The optional\n`duration`\nproperty controls how long each annotation is displayed (defaults to\n`500`\nms).\n\nWhen\n`show: { test }`\nis specified, video will be annotated with the current test information with configurable\n`level`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:{mode:'on-first-retry',size:{width:640,height:480},show:{actions:{duration:500,position:'top-right',fontSize:14,},test:{level:'step',position:'top-left',fontSize:12,}},},},});`\n```\n\nFor multi-page scenarios, you can access the video file associated with the page via the\npage.video() (https://playwright.dev/docs/api/class-page#page-video)\n.\n\n```\n`constpath=awaitpage.video().path();`\n```\n\nnote\nNote that the video is only available after the page or browser context is closed.", 'Configuration (use) | Playwright', 'Debugging Tests | Playwright']</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5037,7 +5940,14 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>To see exactly what happened when a test fails on CI without slowing down the whole run, you should set the `trace` option to `'on-first-retry'` in your test configuration file. This records a trace only when a test is retried, which avoids the performance impact of recording traces for every test run.</t>
+          <t>To see exactly what happened when a test fails without slowing down the whole run, you should enable tracing on the first retry.
+By default, the `playwright.config.ts` file is configured to record a `trace.zip` file for each test on the first retry of a failed test using the following setting:
+```typescript
+use: {
+  trace: 'on-first-retry',
+},
+```
+This approach is recommended because it only records traces when a test fails and is retried, rather than recording for every test run, which helps avoid slowing down the entire test suite.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5046,24 +5956,30 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0.008203</v>
       </c>
       <c r="G83" t="n">
-        <v>0.5</v>
+        <v>31367</v>
       </c>
       <c r="H83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2222222222222222</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0.2666666666666667</v>
+        <v>5</v>
       </c>
       <c r="K83" t="n">
-        <v>0.9999999999833333</v>
+        <v>0.1758241758241758</v>
       </c>
       <c r="L83" t="n">
+        <v>0.3555555555555556</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.8928571428348213</v>
+      </c>
+      <c r="N83" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5075,7 +5991,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>['Authentication | Playwright', 'Fixtures | Playwright', 'Playwright Test supports running multiple test projects at the same time. In the following example, we\'ll run two projects with different options.\n\nWe declare the option\n`person`\nand set the value in the config. The first project runs with the value\n`Alice`\nand the second with the value\n`Bob`\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\n\nWe can use this option in the test, similarly to\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nexample.spec.ts\n```\n`import{test}from\'./my-test\';test(\'test 1\',async({page,person})=&gt;{awaitpage.goto(`/index.html`);awaitexpect(page.locator(\'#node\')).toContainText(person);// ...});`\n```\n\nNow, we can run tests in multiple configurations by using projects.\n\nTypeScript\nJavaScript\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{TestOptions}from\'./my-test\';exportdefaultdefineConfig&lt;TestOptions&gt;({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\nplaywright.config.ts\n```\n`// @ts-checkmodule.exports=defineConfig({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\n\nWe can also use the option in a fixture. Learn more about\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\n\nnote\nParameterized projects behavior has changed in version 1.18.\nLearn more (https://playwright.dev/docs/release-notes#breaking-change-custom-config-options)\n.', "When to use\n\nYou have more than one role in your end to end tests, but you can reuse accounts across all tests.\n\nDetails\n\nWe will authenticate multiple times in the setup project.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';constadminFile='playwright/.auth/admin.json';setup('authenticate as admin',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('admin');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:adminFile});});constuserFile='playwright/.auth/user.json';setup('authenticate as user',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('user');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:userFile});});`\n```\n\nAfter that, specify\n`storageState`\nfor each test file or test group,\ninstead of\nsetting it in the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test.use({storageState:'playwright/.auth/admin.json'});test('admin test',async({page})=&gt;{// page is authenticated as admin});test.describe(()=&gt;{test.use({storageState:'playwright/.auth/user.json'});test('user test',async({page})=&gt;{// page is authenticated as a user});});`\n```\n\nSee also about\nauthenticating in the UI mode (https://playwright.dev/docs/auth#authenticating-in-ui-mode)\n.", 'Parameterize tests | Playwright', "example.spec.ts\n```\n`[{name:'Alice',expected:'Hello, Alice!'},{name:'Bob',expected:'Hello, Bob!'},{name:'Charlie',expected:'Hello, Charlie!'},].forEach(({name,expected})=&gt;{// You can also do it with test.describe() or with multiple tests as long the test name is unique.test(`testing with${name}`,async({page})=&gt;{awaitpage.goto(`https://example.com/greet?name=${name}`);awaitexpect(page.getByRole('heading')).toHaveText(expected);});});`\n```", "You can reset storage state in a test file to avoid authentication that was set up for the whole project.\n\nnot-signed-in.spec.ts\n```\n`import{test}from'@playwright/test';// Reset storage state for this file to avoid being authenticatedtest.use({storageState:{cookies:[],origins:[]}});test('not signed in test',async({page})=&gt;{// ...});`\n```"]</t>
+          <t>['Fixtures | Playwright', "You can reset storage state in a test file to avoid authentication that was set up for the whole project.\n\nnot-signed-in.spec.ts\n```\n`import{test}from'@playwright/test';// Reset storage state for this file to avoid being authenticatedtest.use({storageState:{cookies:[],origins:[]}});test('not signed in test',async({page})=&gt;{// ...});`\n```", 'Authentication | Playwright', 'To create your own fixture, use\ntest.extend() (https://playwright.dev/docs/api/class-test#test-extend)\nto create a new\n`test`\nobject that will include it.\n\nBelow we create two fixtures\n`todoPage`\nand\n`settingsPage`\nthat follow the\nPage Object Model (https://playwright.dev/docs/pom)\npattern.\n\nClick to expand the code for the\n`TodoPage`\nand\n`SettingsPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\nSettingsPage is similar:\nsettings-page.ts\n```\n`importtype{Page}from\'@playwright/test\';exportclassSettingsPage{constructor(publicreadonly page:Page){}asyncswitchToDarkMode(){// ...}}`\n```\n\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';import{SettingsPage}from\'./settings-page\';// Declare the types of your fixtures.typeMyFixtures={todoPage:TodoPage;settingsPage:SettingsPage;};// Extend base test by providing "todoPage" and "settingsPage".// This new "test" can be used in multiple test files, and each of them will get the fixtures.exportconsttest=base.extend&lt;MyFixtures&gt;({todoPage:async({page},use)=&gt;{// Set up the fixture.consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(\'item1\');awaittodoPage.addToDo(\'item2\');// Use the fixture value in the test.awaituse(todoPage);// Clean up the fixture.awaittodoPage.removeAll();},settingsPage:async({page},use)=&gt;{awaituse(newSettingsPage(page));},});export{expect}from\'@playwright/test\';`\n```\n\nnote\nCustom fixture names should start with a letter or underscore, and can contain only letters, numbers, and underscores.', "When to use\n\nYou have more than one role in your end to end tests, but you can reuse accounts across all tests.\n\nDetails\n\nWe will authenticate multiple times in the setup project.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';constadminFile='playwright/.auth/admin.json';setup('authenticate as admin',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('admin');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:adminFile});});constuserFile='playwright/.auth/user.json';setup('authenticate as user',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('user');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:userFile});});`\n```\n\nAfter that, specify\n`storageState`\nfor each test file or test group,\ninstead of\nsetting it in the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test.use({storageState:'playwright/.auth/admin.json'});test('admin test',async({page})=&gt;{// page is authenticated as admin});test.describe(()=&gt;{test.use({storageState:'playwright/.auth/user.json'});test('user test',async({page})=&gt;{// page is authenticated as a user});});`\n```\n\nSee also about\nauthenticating in the UI mode (https://playwright.dev/docs/auth#authenticating-in-ui-mode)\n.", 'Parameterize tests | Playwright', 'Playwright Test supports running multiple test projects at the same time. In the following example, we\'ll run two projects with different options.\n\nWe declare the option\n`person`\nand set the value in the config. The first project runs with the value\n`Alice`\nand the second with the value\n`Bob`\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\n\nWe can use this option in the test, similarly to\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nexample.spec.ts\n```\n`import{test}from\'./my-test\';test(\'test 1\',async({page,person})=&gt;{awaitpage.goto(`/index.html`);awaitexpect(page.locator(\'#node\')).toContainText(person);// ...});`\n```\n\nNow, we can run tests in multiple configurations by using projects.\n\nTypeScript\nJavaScript\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{TestOptions}from\'./my-test\';exportdefaultdefineConfig&lt;TestOptions&gt;({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\nplaywright.config.ts\n```\n`// @ts-checkmodule.exports=defineConfig({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\n\nWe can also use the option in a fixture. Learn more about\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\n\nnote\nParameterized projects behavior has changed in version 1.18.\nLearn more (https://playwright.dev/docs/release-notes#breaking-change-custom-config-options)\n.']</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5085,14 +6001,40 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>To run the exact same tests in two states (logged in and logged out) without duplicating code, you can use **Parameterized Projects**.
-By defining a custom option in your test configuration, you can run the same test suite across multiple projects with different configurations.
-1.  **Define a custom option:** Create a test file (e.g., `my-test.ts`) that extends the base test to include an option (e.g., `isLoggedIn`).
-2.  **Use the option in your tests:** Access this option in your test files to conditionally handle authentication or state.
-3.  **Configure projects:** In your `playwright.config.ts`, define multiple projects that set the `isLoggedIn` option to different values (e.g., `true` for one project and `false` for another).
-Alternatively, for managing authentication states specifically, you can use `storageState`:
-*   **Logged in:** Specify a `storageState` file (containing authenticated cookies/origins) in your test or project configuration.
-*   **Logged out:** Use `test.use({ storageState: { cookies: [], origins: [] } });` within a specific test file to reset the storage state and ensure the test runs in a logged-out state, even if authentication was set up for the rest of the project.</t>
+          <t>To run the same tests in both logged-in and logged-out states without duplicating code, you can use **Parameterized Projects** defined in your `playwright.config.ts`.
+### 1. Define Projects
+Configure two separate projects in your `playwright.config.ts`, one for the authenticated state and one for the unauthenticated state. You can use the `storageState` option to control the authentication status for each project:
+```typescript
+import { defineConfig } from '@playwright/test';
+export default defineConfig({
+  projects: [
+    {
+      name: 'logged-in',
+      use: { storageState: 'playwright/.auth/user.json' },
+    },
+    {
+      name: 'logged-out',
+      use: { storageState: { cookies: [], origins: [] } },
+    },
+  ],
+});
+```
+### 2. Run Tests
+When you run your tests, Playwright will execute every test file twice—once for each project—effectively running the same code in both states.
+### Alternative: Per-file or Per-group configuration
+If you do not want to use projects, you can apply the state directly within your test files or describe blocks using `test.use()`:
+*   **For a whole file:**
+    ```typescript
+    test.use({ storageState: { cookies: [], origins: [] } });
+    ```
+*   **For a specific group:**
+    ```typescript
+    test.describe(() =&gt; {
+      test.use({ storageState: 'playwright/.auth/user.json' });
+      test('logged in test', async ({ page }) =&gt; { /* ... */ });
+    });
+    ```
+While `test.use()` allows you to toggle state within a file, using **Parameterized Projects** is the standard way to run the exact same test suite across different configurations (like authentication states) without modifying the test code itself.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5101,131 +6043,191 @@
         </is>
       </c>
       <c r="F84" t="n">
+        <v>0.010113249999999</v>
+      </c>
+      <c r="G84" t="n">
+        <v>36903</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" t="n">
         <v>0.75</v>
       </c>
-      <c r="G84" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H84" t="n">
-        <v>5</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0.06486486486486487</v>
-      </c>
       <c r="J84" t="n">
-        <v>0.3428571428571429</v>
+        <v>5</v>
       </c>
       <c r="K84" t="n">
-        <v>0.94999999997625</v>
+        <v>0.06046511627906977</v>
       </c>
       <c r="L84" t="n">
+        <v>0.3714285714285714</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.6845238095066964</v>
+      </c>
+      <c r="N84" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>My full test suite takes too long on a single machine. I have several CI machines available — how do I use them to finish faster?</t>
+          <t>I want a set of checks that talk to our backend directly — no browser involved at all — but I'd rather not stand up a second framework just for them. Ideally they run in the same command and land in the same report as the browser tests.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>['Continuous Integration | Playwright', 'Sharding | Playwright', 'By default, Playwright runs test files in\nparallel (https://playwright.dev/docs/test-parallel)\nand strives for optimal utilization of CPU cores on your machine. In order to achieve even greater parallelisation, you can further scale Playwright test execution by running tests on multiple machines simultaneously. We call this mode of operation "sharding". Sharding in Playwright means splitting your tests into smaller parts called "shards". Each shard is like a separate job that can run independently. The whole purpose is to divide your tests to speed up test runtime.\n\nWhen you shard your tests, each shard can run on its own, utilizing the available CPU cores. This helps speed up the testing process by doing tasks simultaneously.\n\nIn a CI pipeline, each shard can run as a separate job, making use of the hardware resources available in your CI pipeline, like CPU cores, to run tests faster.', 'To shard the test suite, pass\n`--shard=x/y`\nto the command line. For example, to split the suite into four shards, each running one fourth of the tests:\n\n```\n`npx playwrighttest--shard=1/4npx playwrighttest--shard=2/4npx playwrighttest--shard=3/4npx playwrighttest--shard=4/4`\n```\n\nNow, if you run these shards in parallel on different jobs, your test suite completes four times faster.\n\nNote that Playwright can only shard tests that can be run in parallel. By default, this means Playwright will shard test files. Learn about other options in the\nparallelism guide (https://playwright.dev/docs/test-parallel)\n.', "```\n`trigger:-mainpool:vmImage:ubuntu-lateststrategy:matrix:chromium-1:project:chromiumshard:1/3chromium-2:project:chromiumshard:2/3chromium-3:project:chromiumshard:3/3firefox-1:project:firefoxshard:1/3firefox-2:project:firefoxshard:2/3firefox-3:project:firefoxshard:3/3webkit-1:project:webkitshard:1/3webkit-2:project:webkitshard:2/3webkit-3:project:webkitshard:3/3steps:-task:UseNode@1inputs:version:'22'displayName:'Install Node.js'-script:npm cidisplayName:'npm ci'-script:npx playwright install--with-depsdisplayName:'Install Playwright browsers'-script:npx playwright test--project=$(project)--shard=$(shard)displayName:'Run Playwright tests'env:CI:'true'`\n```", 'Sharding in CircleCI is indexed with 0 which means that you will need to override the default parallelism ENV VARS. The following example demonstrates how to run Playwright with a CircleCI Parallelism of 4 by adding 1 to the\n`CIRCLE_NODE_INDEX`\nto pass into the\n`--shard`\ncli arg.\n\n```\n`playwright-job-name:executor:pw-noble-developmentparallelism:4steps:-run:SHARD="$((${CIRCLE_NODE_INDEX}+1))"; npx playwright test--shard=${SHARD}/${CIRCLE_NODE_TOTAL}`\n```', "GitLab CI supports\nsharding tests between multiple jobs (https://docs.gitlab.com/ee/ci/jobs/job_control.html#parallelize-large-jobs)\nusing the\nparallel (https://docs.gitlab.com/ee/ci/yaml/index.html#parallel)\nkeyword. The test job will be split into multiple smaller jobs that run in parallel. Parallel jobs are named sequentially from\n`job_name 1/N`\nto\n`job_name N/N`\n.\n\n```\n`stages:-testtests:stage:testimage:mcr.microsoft.com/playwright:v1.60.0-nobleparallel:7script:-npm ci-npx playwright test--shard=$CI_NODE_INDEX/$CI_NODE_TOTAL`\n```\n\nGitLab CI also supports sharding tests between multiple jobs using the\nparallel :matrix (https://docs.gitlab.com/ee/ci/yaml/index.html#parallelmatrix)\noption. The test job will run multiple times in parallel in a single pipeline, but with different variable values for each instance of the job. In the example below, we have 2\n`PROJECT`\nvalues and 10\n`SHARD`\nvalues, resulting in a total of 20 jobs to be run.\n\n```\n`stages:-testtests:stage:testimage:mcr.microsoft.com/playwright:v1.60.0-nobleparallel:matrix:-PROJECT:['chromium','webkit']SHARD:['1/10','2/10','3/10','4/10','5/10','6/10','7/10','8/10','9/10','10/10']script:-npm ci-npx playwright test--project=$PROJECT--shard=$SHARD`\n```"]</t>
+          <t>['API testing | Playwright', 'Playwright can be used to get access to the\nREST (https://en.wikipedia.org/wiki/Representational_state_transfer)\nAPI of your application.\n\nSometimes you may want to send requests to the server directly from Node.js without loading a page and running js code in it. A few examples where it may come in handy:\n\nTest your server API.\nPrepare server side state before visiting the web application in a test.\nValidate server side post-conditions after running some actions in the browser.\n\nAll of that could be achieved via\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nmethods.', "Playwright Test comes with the built-in\n`request`\nfixture that respects configuration options like\n`baseURL`\nor\n`extraHTTPHeaders`\nwe specified and is ready to send some requests.\n\nNow we can add a few tests that will create new issues in the repository.\n\n```\n`constREPO='test-repo-1';constUSER='github-username';test('should create a bug report',async({request})=&gt;{constnewIssue=awaitrequest.post(`/repos/${USER}/${REPO}/issues`,{data:{title:'[Bug] report 1',body:'Bug description',}});expect(newIssue.ok()).toBeTruthy();constissues=awaitrequest.get(`/repos/${USER}/${REPO}/issues`);expect(issues.ok()).toBeTruthy();expect(awaitissues.json()).toContainEqual(expect.objectContaining({title:'[Bug] report 1',body:'Bug description'}));});test('should create a feature request',async({request})=&gt;{constnewIssue=awaitrequest.post(`/repos/${USER}/${REPO}/issues`,{data:{title:'[Feature] request 1',body:'Feature description',}});expect(newIssue.ok()).toBeTruthy();constissues=awaitrequest.get(`/repos/${USER}/${REPO}/issues`);expect(issues.ok()).toBeTruthy();expect(awaitissues.json()).toContainEqual(expect.objectContaining({title:'[Feature] request 1',body:'Feature description'}));});`\n```", 'APIRequestContext | Playwright\n\nThis API is used for the Web API testing. You can use it to trigger API endpoints, configure micro-services, prepare environment or the service to your e2e test.\n\nEach Playwright browser context has an associated\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n, accessible via\nbrowserContext.request (https://playwright.dev/docs/api/class-browsercontext#browser-context-request)\nor\npage.request (https://playwright.dev/docs/api/class-page#page-request)\n(these return the\n\nsame instance\n—\n`page.request`\nis a shortcut for\n`page.context().request`\n). You can also create a standalone, isolated instance with\napiRequest.newContext() (https://playwright.dev/docs/api/class-apirequest#api-request-new-context)\n.\n\nCookie management\n\nThe\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nreturned by\nbrowserContext.request (https://playwright.dev/docs/api/class-browsercontext#browser-context-request)\nand\n\npage.request (https://playwright.dev/docs/api/class-page#page-request)\nuses the same cookie jar as its\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\n:\n\nIf you want API requests that do\nnot\nshare cookies with the browser, create an isolated context via\napiRequest.newContext() (https://playwright.dev/docs/api/class-apirequest#api-request-new-context)\n. Such\n`APIRequestContext`\nobject will have its own isolated cookie storage.', 'APIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\ncan send all kinds of HTTP(S) requests over network.\n\nThe following example demonstrates how to use Playwright to test issues creation via\nGitHub API (https://docs.github.com/en/rest)\n. The test suite will do the following:\n\nCreate a new repository before running tests.\nCreate a few issues and validate server state.\nDelete the repository after running tests.', "GitHub API requires authorization, so we'll configure the token once for all tests. While at it, we'll also set the\n`baseURL`\nto simplify the tests. You can either put them in the configuration file, or in the test file with\n`test.use()`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{// All requests we send go to this API endpoint.baseURL:'https://api.github.com',extraHTTPHeaders:{// We set this header per GitHub guidelines.'Accept':'application/vnd.github.v3+json',// Add authorization token to all requests.// Assuming personal access token available in the environment.'Authorization':`token${process.env.API_TOKEN}`,},}});`\n```\n\nProxy configuration\n\nIf your tests need to run behind a proxy, you can specify this in the config and the\n`request`\nfixture will pick it up automatically:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{proxy:{server:'http://my-proxy:8080',username:'user',password:'secret'},}});`\n```", 'Fixtures | Playwright']</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>['In order to achieve even greater parallelisation, you can further scale Playwright test execution by running tests on multiple machines simultaneously. We call this mode of operation "sharding".', 'Now, if you run these shards in parallel on different jobs, your test suite completes four times faster.']</t>
+          <t>['Playwright can be used to get access to the REST API of your application.', 'Sometimes you may want to send requests to the server directly from Node.js without loading a page and running js code in it.', "test('should create a bug report', async ({ request }) =&gt; { const newIssue = await request.post(`/repos/${USER}/${REPO}/issues`, { data: { title: '[Bug] report 1', body: 'Bug description', } }); expect(newIssue.ok()).toBeTruthy(); });"]</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>To finish your test suite faster using multiple CI machines, you can use a feature called "sharding." Sharding splits your tests into smaller parts (shards) that can run independently and simultaneously on different machines.
-To implement sharding, you pass the `--shard=x/y` argument to the command line, where `x` is the current shard index and `y` is the total number of shards. For example, to split your suite into four shards, you would run:
-* `npx playwright test --shard=1/4`
-* `npx playwright test --shard=2/4`
-* `npx playwright test --shard=3/4`
-* `npx playwright test --shard=4/4`
-By running these shards in parallel as separate jobs in your CI pipeline, you can utilize the hardware resources of multiple machines to complete the test suite faster. Playwright provides specific configuration examples for various CI providers, such as Azure Pipelines, CircleCI, and GitLab CI, which demonstrate how to automate this process using their respective parallelization features.</t>
+          <t>You can perform API testing directly within Playwright without a browser by using the built-in `request` fixture. This allows you to run API tests alongside your browser tests in the same command and report.
+### How to implement
+1. **Use the `request` fixture**: Playwright Test provides a built-in `request` fixture that is ready to send requests and respects configuration options like `baseURL` or `extraHTTPHeaders`.
+2. **Configure globally**: You can set up your API configuration (such as `baseURL` and `extraHTTPHeaders`) in your `playwright.config.ts` file so that it applies to all tests:
+   ```typescript
+   import { defineConfig } from '@playwright/test';
+   export default defineConfig({
+     use: {
+       baseURL: 'https://api.github.com',
+       extraHTTPHeaders: {
+         'Accept': 'application/vnd.github.v3+json',
+         'Authorization': `token ${process.env.API_TOKEN}`,
+       },
+     },
+   });
+   ```
+3. **Write your tests**: Use the `request` fixture in your test files to perform operations:
+   ```typescript
+   test('should create a bug report', async ({ request }) =&gt; {
+     const newIssue = await request.post(`/repos/${USER}/${REPO}/issues`, {
+       data: {
+         title: '[Bug] report 1',
+         body: 'Bug description',
+       },
+     });
+     expect(newIssue.ok()).toBeTruthy();
+   });
+   ```
+### Alternative approach
+If you need an isolated context that does not share cookies with the browser, you can create a standalone instance using `apiRequest.newContext()`. However, the `request` fixture is the built-in, recommended way to handle these requests within the Playwright Test framework.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Use sharding: split the suite into shards with --shard=x/y and run each shard as a separate CI job on a different machine, so the suite completes proportionally faster.</t>
+          <t>You don't need a second framework. The test runner exposes a `request` fixture — an isolated APIRequestContext — that sends HTTP calls directly from Node without a browser, so you can write `test('...', async ({ request }) =&gt; { const res = await request.post('/api/issues', { data: {...} }); expect(res.ok()).toBeTruthy(); })`. It honours the config's baseURL and other request options, uses the same expect assertions, and is collected by the same run and reporters as your UI specs. Requests do not run in page context, which is exactly why they're fast enough to use for setup as well as for asserting API behaviour.</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>0.01016325</v>
       </c>
       <c r="G85" t="n">
-        <v>0.77</v>
+        <v>36588</v>
       </c>
       <c r="H85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1153846153846154</v>
+        <v>0.46</v>
       </c>
       <c r="J85" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="K85" t="n">
+        <v>0.1476190476190476</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M85" t="n">
         <v>0.9999999999857143</v>
       </c>
-      <c r="L85" t="n">
+      <c r="N85" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>My app logs users out after 5 minutes of inactivity. I want to test that behavior but obviously don't want the test to actually wait 5 minutes. How?</t>
+          <t>Our dashboard greets people with 'Good morning' or 'Good evening' and stamps every row with a relative label like 'posted 3 hours ago'. The assertions on both pass when I run them at my desk and fail on the nightly build, which is obviously about when the run happens rather than the code. How do I make the page's idea of the current time deterministic?</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>['Clock | Playwright', 'Inactivity monitoring is a common feature in web applications that logs out users after a period of inactivity. Testing this feature can be tricky because you need to wait for a long time to see the effect. With the help of the clock, you can speed up time and test this feature quickly.\n\n```\n`&lt;divid="remaining-time"data-testid="remaining-time"&gt;&lt;/div&gt;&lt;script&gt;constendTime=Date.now()+5*60_000;constrenderTime=()=&gt;{constdiffInSeconds=Math.round((endTime-Date.now())/1000);if(diffInSeconds&lt;=0){document.getElementById(\'remaining-time\').textContent=\'You have been logged out due to inactivity.\';}else{document.getElementById(\'remaining-time\').textContent=`You will be logged out in${diffInSeconds}seconds.`;}setTimeout(renderTime,1000);};renderTime();&lt;/script&gt;&lt;buttontype="button"&gt;Interaction&lt;/button&gt;`\n```\n\n```\n`// Initial time does not matter for the test, so we can pick current time.awaitpage.clock.install();awaitpage.goto(\'http://localhost:3333\');// Interact with the pageawaitpage.getByRole(\'button\').click();// Fast forward time 5 minutes as if the user did not do anything.// Fast forward is like closing the laptop lid and opening it after 5 minutes.// All the timers due will fire once immediately, as in the real browser.awaitpage.clock.fastForward(\'05:00\');// Check that the user was logged out automatically.awaitexpect(page.getByText(\'You have been logged out due to inactivity.\')).toBeVisible();`\n```', 'Sometimes your timers depend on\n`Date.now`\nand are confused when the\n`Date.now`\nvalue does not change over time. In this case, you can install the clock and fast forward to the time of interest when testing.\n\n```\n`&lt;divid="current-time"data-testid="current-time"&gt;&lt;/div&gt;&lt;script&gt;constrenderTime=()=&gt;{document.getElementById(\'current-time\').textContent=newDate().toLocaleString();};setInterval(renderTime,1000);&lt;/script&gt;`\n```\n\n```\n`// Initialize clock with some time before the test time and let the page load// naturally. `Date.now` will progress as the timers fire.awaitpage.clock.install({time:newDate(\'2024-02-02T08:00:00\')});awaitpage.goto(\'http://localhost:3333\');// Pretend that the user closed the laptop lid and opened it again at 10am,// Pause the time once reached that point.awaitpage.clock.pauseAt(newDate(\'2024-02-02T10:00:00\'));// Assert the page state.awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:00:00 AM\');// Close the laptop lid again and open it at 10:30am.awaitpage.clock.fastForward(\'30:00\');awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:30:00 AM\');`\n```', 'In rare cases, you may want to tick through time manually, firing all timers and animation frames in the process to achieve a fine-grained control over the passage of time.\n\n```\n`&lt;divid="current-time"data-testid="current-time"&gt;&lt;/div&gt;&lt;script&gt;constrenderTime=()=&gt;{document.getElementById(\'current-time\').textContent=newDate().toLocaleString();};setInterval(renderTime,1000);&lt;/script&gt;`\n```\n\n```\n`// Initialize clock with a specific time, let the page load naturally.awaitpage.clock.install({time:newDate(\'2024-02-02T08:00:00\')});awaitpage.goto(\'http://localhost:3333\');// Pause the time flow, stop the timers, you now have manual control// over the page time.awaitpage.clock.pauseAt(newDate(\'2024-02-02T10:00:00\'));awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:00:00 AM\');// Tick through time manually, firing all timers in the process.// In this case, time will be updated in the screen 2 times.awaitpage.clock.runFor(2000);awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:00:02 AM\');`\n```', "Accurately simulating time-dependent behavior is essential for verifying the correctness of applications. Utilizing\nClock (https://playwright.dev/docs/api/class-clock)\nfunctionality allows developers to manipulate and control time within tests, enabling the precise validation of features such as rendering time, timeouts, scheduled tasks without the delays and variability of real-time execution.\n\nThe\nClock (https://playwright.dev/docs/api/class-clock)\nAPI provides the following methods to control time:\n\n`setFixedTime`\n: Sets the fixed time for\n`Date.now()`\nand\n`new Date()`\n.\n`install`\n: initializes the clock and allows you to:\n`pauseAt`\n: Pauses the time at a specific time.\n`fastForward`\n: Fast forwards the time.\n`runFor`\n: Runs the time for a specific duration.\n`resume`\n: Resumes the time.\n`setSystemTime`\n: Sets the current system time.\n\nThe recommended approach is to use\n`setFixedTime`\nto set the time to a specific value. If that doesn't work for your use case, you can use\n`install`\nwhich allows you to pause time later on, fast forward it, tick it, etc.\n`setSystemTime`\nis only recommended for advanced use cases.\n\nnote\npage.clock (https://playwright.dev/docs/api/class-page#page-clock)\noverrides native global classes and functions related to time allowing them to be manually controlled:\n`Date`\n`setTimeout`\n`clearTimeout`\n`setInterval`\n`clearInterval`\n`requestAnimationFrame`\n`cancelAnimationFrame`\n`requestIdleCallback`\n`cancelIdleCallback`\n`performance`\n`Event.timeStamp`\n\nwarning\nIf you call\n`install`\nat any point in your test, the call\nMUST\noccur before any other clock related calls (see note above for list). Calling these methods out of order will result in undefined behavior. For example, you cannot call\n`setInterval`\n, followed by\n`install`\n, then\n`clearInterval`\n, as\n`install`\noverrides the native definition of the clock functions.", 'Often you only need to fake\n`Date.now`\nwhile keeping the timers going. That way the time flows naturally, but\n`Date.now`\nalways returns a fixed value.\n\n```\n`&lt;divid="current-time"data-testid="current-time"&gt;&lt;/div&gt;&lt;script&gt;constrenderTime=()=&gt;{document.getElementById(\'current-time\').textContent=newDate().toLocaleString();};setInterval(renderTime,1000);&lt;/script&gt;`\n```\n\n```\n`awaitpage.clock.setFixedTime(newDate(\'2024-02-02T10:00:00\'));awaitpage.goto(\'http://localhost:3333\');awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:00:00 AM\');awaitpage.clock.setFixedTime(newDate(\'2024-02-02T10:30:00\'));// We know that the page has a timer that updates the time every second.awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:30:00 AM\');`\n```']</t>
+          <t>['Clock | Playwright\n\nAccurately simulating time-dependent behavior is essential for verifying the correctness of applications. Learn more about\nclock emulation (https://playwright.dev/docs/clock)\n.\n\nNote that clock is installed for the entire\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\n, so the time in all the pages and iframes is controlled by the same clock.', 'Clock | Playwright', 'Sometimes your timers depend on\n`Date.now`\nand are confused when the\n`Date.now`\nvalue does not change over time. In this case, you can install the clock and fast forward to the time of interest when testing.\n\n```\n`&lt;divid="current-time"data-testid="current-time"&gt;&lt;/div&gt;&lt;script&gt;constrenderTime=()=&gt;{document.getElementById(\'current-time\').textContent=newDate().toLocaleString();};setInterval(renderTime,1000);&lt;/script&gt;`\n```\n\n```\n`// Initialize clock with some time before the test time and let the page load// naturally. `Date.now` will progress as the timers fire.awaitpage.clock.install({time:newDate(\'2024-02-02T08:00:00\')});awaitpage.goto(\'http://localhost:3333\');// Pretend that the user closed the laptop lid and opened it again at 10am,// Pause the time once reached that point.awaitpage.clock.pauseAt(newDate(\'2024-02-02T10:00:00\'));// Assert the page state.awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:00:00 AM\');// Close the laptop lid again and open it at 10:30am.awaitpage.clock.fastForward(\'30:00\');awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:30:00 AM\');`\n```', 'Often you only need to fake\n`Date.now`\nwhile keeping the timers going. That way the time flows naturally, but\n`Date.now`\nalways returns a fixed value.\n\n```\n`&lt;divid="current-time"data-testid="current-time"&gt;&lt;/div&gt;&lt;script&gt;constrenderTime=()=&gt;{document.getElementById(\'current-time\').textContent=newDate().toLocaleString();};setInterval(renderTime,1000);&lt;/script&gt;`\n```\n\n```\n`awaitpage.clock.setFixedTime(newDate(\'2024-02-02T10:00:00\'));awaitpage.goto(\'http://localhost:3333\');awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:00:00 AM\');awaitpage.clock.setFixedTime(newDate(\'2024-02-02T10:30:00\'));// We know that the page has a timer that updates the time every second.awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:30:00 AM\');`\n```', "Accurately simulating time-dependent behavior is essential for verifying the correctness of applications. Utilizing\nClock (https://playwright.dev/docs/api/class-clock)\nfunctionality allows developers to manipulate and control time within tests, enabling the precise validation of features such as rendering time, timeouts, scheduled tasks without the delays and variability of real-time execution.\n\nThe\nClock (https://playwright.dev/docs/api/class-clock)\nAPI provides the following methods to control time:\n\n`setFixedTime`\n: Sets the fixed time for\n`Date.now()`\nand\n`new Date()`\n.\n`install`\n: initializes the clock and allows you to:\n`pauseAt`\n: Pauses the time at a specific time.\n`fastForward`\n: Fast forwards the time.\n`runFor`\n: Runs the time for a specific duration.\n`resume`\n: Resumes the time.\n`setSystemTime`\n: Sets the current system time.\n\nThe recommended approach is to use\n`setFixedTime`\nto set the time to a specific value. If that doesn't work for your use case, you can use\n`install`\nwhich allows you to pause time later on, fast forward it, tick it, etc.\n`setSystemTime`\nis only recommended for advanced use cases.\n\nnote\npage.clock (https://playwright.dev/docs/api/class-page#page-clock)\noverrides native global classes and functions related to time allowing them to be manually controlled:\n`Date`\n`setTimeout`\n`clearTimeout`\n`setInterval`\n`clearInterval`\n`requestAnimationFrame`\n`cancelAnimationFrame`\n`requestIdleCallback`\n`cancelIdleCallback`\n`performance`\n`Event.timeStamp`\n\nwarning\nIf you call\n`install`\nat any point in your test, the call\nMUST\noccur before any other clock related calls (see note above for list). Calling these methods out of order will result in undefined behavior. For example, you cannot call\n`setInterval`\n, followed by\n`install`\n, then\n`clearInterval`\n, as\n`install`\noverrides the native definition of the clock functions.", 'In rare cases, you may want to tick through time manually, firing all timers and animation frames in the process to achieve a fine-grained control over the passage of time.\n\n```\n`&lt;divid="current-time"data-testid="current-time"&gt;&lt;/div&gt;&lt;script&gt;constrenderTime=()=&gt;{document.getElementById(\'current-time\').textContent=newDate().toLocaleString();};setInterval(renderTime,1000);&lt;/script&gt;`\n```\n\n```\n`// Initialize clock with a specific time, let the page load naturally.awaitpage.clock.install({time:newDate(\'2024-02-02T08:00:00\')});awaitpage.goto(\'http://localhost:3333\');// Pause the time flow, stop the timers, you now have manual control// over the page time.awaitpage.clock.pauseAt(newDate(\'2024-02-02T10:00:00\'));awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:00:00 AM\');// Tick through time manually, firing all timers in the process.// In this case, time will be updated in the screen 2 times.awaitpage.clock.runFor(2000);awaitexpect(page.getByTestId(\'current-time\')).toHaveText(\'2/2/2024, 10:00:02 AM\');`\n```']</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>['Inactivity monitoring is a common feature in web applications that logs out users after a period of inactivity. Testing this feature can be tricky because you need to wait for a long time to see the effect. With the help of the clock, you can speed up time and test this feature quickly.', "// Fast forward time 5 minutes as if the user did not do anything.\n// Fast forward is like closing the laptop lid and opening it after 5 minutes.\n// All the timers due will fire once immediately, as in the real browser.\nawait page.clock.fastForward('05:00');"]</t>
+          <t>['setFixedTime: Sets the fixed time for Date.now() and new Date().', "The recommended approach is to use setFixedTime to set the time to a specific value. If that doesn't work for your use case, you can use install which allows you to pause time later on, fast forward it, tick it, etc. setSystemTime is only recommended for advanced use cases.", "await page.clock.setFixedTime(new Date('2024-02-02T10:00:00')); await page.goto('http://localhost:3333'); await expect(page.getByTestId('current-time')).toHaveText('2/2/2024, 10:00:00 AM');"]</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>To test inactivity monitoring without waiting for 5 minutes, you can use the Playwright `clock` API to fast forward time. Follow these steps:
-1.  **Install the clock:** Call `await page.clock.install();` before interacting with the page.
-2.  **Navigate to your app:** Use `await page.goto('http://localhost:3333');` (or your specific URL).
-3.  **Perform interactions:** Interact with the page as needed (e.g., `await page.getByRole('button').click();`).
-4.  **Fast forward time:** Use `await page.clock.fastForward('05:00');` to simulate the passage of 5 minutes. This will fire all pending timers immediately.
-5.  **Assert the result:** Verify that the user has been logged out (e.g., `await expect(page.getByText('You have been logged out due to inactivity.')).toBeVisible();`).</t>
+          <t>To make the page's idea of the current time deterministic, you should use the `page.clock` API, which overrides native global time-related functions for the entire `BrowserContext`.
+The documentation recommends the following approaches based on your needs:
+### 1. Recommended Approach: `setFixedTime`
+If you only need to fake `Date.now()` while keeping timers running, use `setFixedTime`. This sets a fixed value for `Date.now()` and `new Date()`.
+```javascript
+await page.clock.setFixedTime(new Date('2024-02-02T10:00:00'));
+await page.goto('http://localhost:3333');
+// Assertions will now use the fixed time
+```
+### 2. Alternative Approach: `install`
+If `setFixedTime` does not meet your requirements (e.g., you need to pause time, fast forward, or manually tick through time), use `install`. This allows for more granular control.
+*   **To pause and fast forward:**
+    ```javascript
+    await page.clock.install({ time: new Date('2024-02-02T08:00:00') });
+    await page.goto('http://localhost:3333');
+    await page.clock.pauseAt(new Date('2024-02-02T10:00:00'));
+    // Assert state at 10:00
+    await page.clock.fastForward('30:00');
+    // Assert state at 10:30
+    ```
+*   **To tick manually:**
+    Use `page.clock.runFor(duration)` to fire timers and animation frames for a specific duration.
+**Important Constraints:**
+*   If you use `install`, it **must** be called before any other clock-related calls (such as `setInterval` or `setTimeout`) to avoid undefined behavior.
+*   `page.clock` controls time for all pages and iframes within the `BrowserContext`.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Use the Clock API to control time: install the clock, interact with the page, then fastForward past the inactivity window so timers fire immediately, and assert the logged-out state. This lets you test the feature quickly.</t>
+          <t>Pin the clock rather than trying to write assertions that hold at any hour. The recommended tool is page.clock.setFixedTime(new Date('2024-02-02T10:00:00')), which fixes what Date.now() and new Date() return so the greeting and the relative timestamps render the same way on every run. You can call it again mid-test to move to another fixed instant and re-assert. Reach for clock.install() only if the page's timers actually need time to progress — install is the heavier option that additionally lets you pauseAt, fastForward, runFor and resume — and setSystemTime is for advanced cases only.</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0.008299250000000001</v>
       </c>
       <c r="G86" t="n">
-        <v>0.44</v>
+        <v>30212</v>
       </c>
       <c r="H86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.33</v>
       </c>
       <c r="J86" t="n">
-        <v>0.5945945945945946</v>
+        <v>5</v>
       </c>
       <c r="K86" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.2718446601941747</v>
+      </c>
+      <c r="M86" t="n">
         <v>0.9999999999833333</v>
       </c>
-      <c r="L86" t="n">
+      <c r="N86" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5248,7 +6250,9 @@
       <c r="D87" t="inlineStr">
         <is>
           <t>To achieve this, use the `webServer` property in your `playwright.config.ts` file and set the `reuseExistingServer` option to `!process.env.CI`.
-This configuration will reuse an existing server locally (when `CI` is not set) and will throw an error on CI if a process is already listening on the specified port or URL, ensuring a fresh start.
+This configuration works as follows:
+*   **Locally:** When `process.env.CI` is not set, `reuseExistingServer` becomes `true`. Playwright will reuse an existing server if one is already running on the specified `url`. If no server is running, it will execute the `command` to start one.
+*   **On CI:** When `process.env.CI` is set, `reuseExistingServer` becomes `false`. Playwright will throw an error if an existing process is already listening on the `url`, ensuring the server is not already handled and forcing a fresh start via the `command`.
 Example configuration:
 ```typescript
 import { defineConfig } from '@playwright/test';
@@ -5268,24 +6272,30 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0.00760175</v>
       </c>
       <c r="G87" t="n">
-        <v>0.57</v>
+        <v>28862</v>
       </c>
       <c r="H87" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1585365853658537</v>
+        <v>0.73</v>
       </c>
       <c r="J87" t="n">
-        <v>0.4642857142857143</v>
+        <v>5</v>
       </c>
       <c r="K87" t="n">
+        <v>0.1374045801526718</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="M87" t="n">
         <v>0.49999999995</v>
       </c>
-      <c r="L87" t="n">
+      <c r="N87" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5297,7 +6307,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>['Authentication | Playwright', "This is the\nrecommended\napproach for tests that\nmodify server-side state\n. In Playwright, worker processes run in parallel. In this approach, each parallel worker is authenticated once. All tests ran by worker are reusing the same authentication state. We will need multiple testing accounts, one per each parallel worker.\n\nWhen to use\n\nYour tests modify shared server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting.\n\nWhen not to use\n\nYour tests do not modify any shared server-side state. In this case, all tests can use a single shared account.\n\nDetails\n\nWe will authenticate once per\nworker process (https://playwright.dev/docs/test-parallel#worker-processes)\n, each with a unique account.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\noverride storageState fixture (https://playwright.dev/docs/test-fixtures#overriding-fixtures)\nto authenticate once per worker. Use\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({browser},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constpage=awaitbrowser.newPage({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill(account.username);awaitpage.getByLabel('Password').fill(account.password);awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:fileName});awaitpage.close();awaituse(fileName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n. No changes are needed in the config.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({page})=&gt;{// page is authenticated});`\n```", "You can leverage\n`process.env.TEST_WORKER_INDEX`\nor\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nmentioned above to isolate user data in the database between tests running on different workers. All tests run by the worker reuse the same user.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\ncreate dbUserName fixture (https://playwright.dev/docs/test-fixtures#creating-a-fixture)\nand initialize a new user in the test database. Use\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';// Import project utils for managing users in the test database.import{createUserInTestDatabase,deleteUserFromTestDatabase}from'./my-db-utils';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{dbUserName:string}&gt;({// Returns db user name unique for the worker.dbUserName:[async({},use)=&gt;{// Use workerIndex as a unique identifier for each worker.constuserName=`user-${test.info().workerIndex}`;// Initialize user in the database.awaitcreateUserInTestDatabase(userName);awaituse(userName);// Clean up after the tests are done.awaitdeleteUserFromTestDatabase(userName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({dbUserName})=&gt;{// Use the user name in the test.});`\n```", 'Parallelism | Playwright', 'Each worker process is assigned two ids: a unique worker index that starts with 1, and a parallel index that is between\n`0`\nand\n`workers - 1`\n. When a worker is restarted, for example after a failure, the new worker process has the same\n`parallelIndex`\nand a new\n`workerIndex`\n.\n\nYou can read an index from environment variables\n`process.env.TEST_WORKER_INDEX`\nand\n`process.env.TEST_PARALLEL_INDEX`\n, or access them through\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nand\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\n.', "Playwright Test uses\nworker processes (https://playwright.dev/docs/test-parallel)\nto run test files. Similar to how test fixtures are set up for individual test runs, worker fixtures are set up for each worker process. That's where you can set up services, run servers, etc. Playwright Test will reuse the worker process for as many test files as it can, provided their worker fixtures match and hence environments are identical.\n\nBelow we'll create an\n`account`\nfixture that will be shared by all tests in the same worker, and override the\n`page`\nfixture to log in to this account for each test. To generate unique accounts, we'll use the\nworkerInfo.workerIndex (https://playwright.dev/docs/api/class-workerinfo#worker-info-worker-index)\nthat is available to any test or fixture. Note the tuple-like syntax for the worker fixture - we have to pass\n`{scope: 'worker'}`\nso that test runner sets this fixture up once per worker.\n\nIn addition to only being run once per worker, worker-scoped fixtures also get a separate timeout equal to the default test timeout. You can change it by passing the\n`timeout`\noption. See\nfixture timeout (https://playwright.dev/docs/test-fixtures#fixture-timeout)\nfor more details.\n\nmy-test.ts\n```\n`import{testasbase}from'@playwright/test';typeAccount={username:string;password:string;};// Note that we pass worker fixture types as a second template parameter.exportconsttest=base.extend&lt;{},{account:Account}&gt;({account:[async({browser},use,workerInfo)=&gt;{// Unique username.constusername='user'+workerInfo.workerIndex;constpassword='verysecure';// Create the account with Playwright.constpage=awaitbrowser.newPage();awaitpage.goto('/signup');awaitpage.getByLabel('User Name').fill(username);awaitpage.getByLabel('Password').fill(password);awaitpage.getByText('Sign up').click();// Make sure everything is ok.awaitexpect(page.getByTestId('result')).toHaveText('Success');// Do not forget to cleanup.awaitpage.close();// Use the account value.awaituse({username,password});},{scope:'worker'}],page:async({page,account},use)=&gt;{// Sign in with our account.const{username,password}=account;awaitpage.goto('/signin');awaitpage.getByLabel('User Name').fill(username);awaitpage.getByLabel('Password').fill(password);awaitpage.getByText('Sign in').click();awaitexpect(page.getByTestId('userinfo')).toHaveText(username);// Use signed-in page in the test.awaituse(page);},});export{expect}from'@playwright/test';`\n```", 'Isolation | Playwright']</t>
+          <t>['Authentication | Playwright', "This is the\nrecommended\napproach for tests that\nmodify server-side state\n. In Playwright, worker processes run in parallel. In this approach, each parallel worker is authenticated once. All tests ran by worker are reusing the same authentication state. We will need multiple testing accounts, one per each parallel worker.\n\nWhen to use\n\nYour tests modify shared server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting.\n\nWhen not to use\n\nYour tests do not modify any shared server-side state. In this case, all tests can use a single shared account.\n\nDetails\n\nWe will authenticate once per\nworker process (https://playwright.dev/docs/test-parallel#worker-processes)\n, each with a unique account.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\noverride storageState fixture (https://playwright.dev/docs/test-fixtures#overriding-fixtures)\nto authenticate once per worker. Use\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({browser},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constpage=awaitbrowser.newPage({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill(account.username);awaitpage.getByLabel('Password').fill(account.password);awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:fileName});awaitpage.close();awaituse(fileName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n. No changes are needed in the config.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({page})=&gt;{// page is authenticated});`\n```", "You can leverage\n`process.env.TEST_WORKER_INDEX`\nor\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nmentioned above to isolate user data in the database between tests running on different workers. All tests run by the worker reuse the same user.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\ncreate dbUserName fixture (https://playwright.dev/docs/test-fixtures#creating-a-fixture)\nand initialize a new user in the test database. Use\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';// Import project utils for managing users in the test database.import{createUserInTestDatabase,deleteUserFromTestDatabase}from'./my-db-utils';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{dbUserName:string}&gt;({// Returns db user name unique for the worker.dbUserName:[async({},use)=&gt;{// Use workerIndex as a unique identifier for each worker.constuserName=`user-${test.info().workerIndex}`;// Initialize user in the database.awaitcreateUserInTestDatabase(userName);awaituse(userName);// Clean up after the tests are done.awaitdeleteUserFromTestDatabase(userName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({dbUserName})=&gt;{// Use the user name in the test.});`\n```", 'Parallelism | Playwright', 'Each worker process is assigned two ids: a unique worker index that starts with 1, and a parallel index that is between\n`0`\nand\n`workers - 1`\n. When a worker is restarted, for example after a failure, the new worker process has the same\n`parallelIndex`\nand a new\n`workerIndex`\n.\n\nYou can read an index from environment variables\n`process.env.TEST_WORKER_INDEX`\nand\n`process.env.TEST_PARALLEL_INDEX`\n, or access them through\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nand\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\n.', "Playwright Test uses\nworker processes (https://playwright.dev/docs/test-parallel)\nto run test files. Similar to how test fixtures are set up for individual test runs, worker fixtures are set up for each worker process. That's where you can set up services, run servers, etc. Playwright Test will reuse the worker process for as many test files as it can, provided their worker fixtures match and hence environments are identical.\n\nBelow we'll create an\n`account`\nfixture that will be shared by all tests in the same worker, and override the\n`page`\nfixture to log in to this account for each test. To generate unique accounts, we'll use the\nworkerInfo.workerIndex (https://playwright.dev/docs/api/class-workerinfo#worker-info-worker-index)\nthat is available to any test or fixture. Note the tuple-like syntax for the worker fixture - we have to pass\n`{scope: 'worker'}`\nso that test runner sets this fixture up once per worker.\n\nIn addition to only being run once per worker, worker-scoped fixtures also get a separate timeout equal to the default test timeout. You can change it by passing the\n`timeout`\noption. See\nfixture timeout (https://playwright.dev/docs/test-fixtures#fixture-timeout)\nfor more details.\n\nmy-test.ts\n```\n`import{testasbase}from'@playwright/test';typeAccount={username:string;password:string;};// Note that we pass worker fixture types as a second template parameter.exportconsttest=base.extend&lt;{},{account:Account}&gt;({account:[async({browser},use,workerInfo)=&gt;{// Unique username.constusername='user'+workerInfo.workerIndex;constpassword='verysecure';// Create the account with Playwright.constpage=awaitbrowser.newPage();awaitpage.goto('/signup');awaitpage.getByLabel('User Name').fill(username);awaitpage.getByLabel('Password').fill(password);awaitpage.getByText('Sign up').click();// Make sure everything is ok.awaitexpect(page.getByTestId('result')).toHaveText('Success');// Do not forget to cleanup.awaitpage.close();// Use the account value.awaituse({username,password});},{scope:'worker'}],page:async({page,account},use)=&gt;{// Sign in with our account.const{username,password}=account;awaitpage.goto('/signin');awaitpage.getByLabel('User Name').fill(username);awaitpage.getByLabel('Password').fill(password);awaitpage.getByText('Sign in').click();awaitexpect(page.getByTestId('userinfo')).toHaveText(username);// Use signed-in page in the test.awaituse(page);},});export{expect}from'@playwright/test';`\n```", 'Fixtures | Playwright']</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5307,12 +6317,10 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>To isolate user data in the database between tests running on different parallel workers, you should leverage `testInfo.workerIndex` to create a worker-scoped fixture that initializes a unique user for each worker.
-The recommended approach is as follows:
-1.  **Create a fixture file** (e.g., `playwright/fixtures.ts`) that defines a worker-scoped fixture (e.g., `dbUserName`).
-2.  **Use `testInfo.workerIndex`** inside the fixture to generate a unique identifier for the worker.
-3.  **Initialize and clean up the user** within the fixture to ensure isolation.
-**Example implementation:**
+          <t>To isolate user data in the database between parallel workers, you should leverage `testInfo.workerIndex` to create a worker-scoped fixture that initializes a unique user for each worker.
+### Recommended Approach
+Create a `playwright/fixtures.ts` file to define a `dbUserName` fixture. This fixture uses `test.info().workerIndex` to ensure each worker process interacts with its own unique database user.
+**`playwright/fixtures.ts`**
 ```typescript
 import { test as baseTest, expect } from '@playwright/test';
 // Import project utils for managing users in the test database.
@@ -5331,7 +6339,20 @@
   }, { scope: 'worker' }],
 });
 ```
-After creating this file, import `test` from your fixtures file instead of `@playwright/test` in your test files to access the `dbUserName` fixture.</t>
+### Implementation
+In your test files, import `test` from the `playwright/fixtures.ts` file instead of `@playwright/test`:
+**`tests/example.spec.ts`**
+```typescript
+// Important: import our fixtures.
+import { test, expect } from '../playwright/fixtures';
+test('test', async ({ dbUserName }) =&gt; {
+  // Use the user name in the test.
+});
+```
+### Key Details
+*   **Scope:** The fixture must be defined with `{ scope: 'worker' }` so that it is set up once per worker process.
+*   **Identification:** `testInfo.workerIndex` provides a unique index for each worker process, which is used to differentiate the database users.
+*   **Cleanup:** The fixture includes a teardown step (`deleteUserFromTestDatabase`) to remove the user after the worker has finished its tests.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5340,90 +6361,110 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0.01001475</v>
       </c>
       <c r="G88" t="n">
-        <v>0.73</v>
+        <v>36784</v>
       </c>
       <c r="H88" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>0.09644670050761421</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
-        <v>0.4871794871794872</v>
+        <v>5</v>
       </c>
       <c r="K88" t="n">
+        <v>0.0796812749003984</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.5128205128205128</v>
+      </c>
+      <c r="M88" t="n">
         <v>0.4111111110974074</v>
       </c>
-      <c r="L88" t="n">
+      <c r="N88" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>I'm developing locally and don't have a staging URL. I want a local dev server to be started automatically before my tests run. What config do I need?</t>
+          <t>Our stack needs two processes up before anything can be tested — the web front end and a separate API service — and the API one is slow, usually a minute and a half before it answers. Right now the run gives up and everything fails at the first navigation. How should this be configured?</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>['Web server | Playwright', 'Use the\n`webServer`\nproperty in your Playwright config to launch a development web server during the tests.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({// Run your local dev server before starting the testswebServer:{command:\'npm run start\',url:\'http://localhost:3000\',reuseExistingServer:!process.env.CI,stdout:\'ignore\',stderr:\'pipe\',},});`\n```\n\nProperty\nDescription\ntestConfig.webServer (https://playwright.dev/docs/api/class-testconfig#test-config-web-server)\nLaunch a development web server (or multiple) during the tests.\n`command`\nShell command to start the local dev server of your app.\n`cwd`\nCurrent working directory of the spawned process, defaults to the directory of the configuration file.\n`env`\nEnvironment variables for the command. Defaults to inheriting\n`process.env`\nwith\n`PLAYWRIGHT_TEST=1`\nadded.\n`gracefulShutdown`\nHow to shut down the process. If unspecified, the process group is forcefully\n`SIGKILL`\ned. If set to\n`{ signal: \'SIGTERM\', timeout: 500 }`\n, the process group is sent a\n`SIGTERM`\nsignal, followed by\n`SIGKILL`\nif it doesn\'t exit within 500ms. You can also use\n`SIGINT`\nas the signal instead. A\n`0`\ntimeout means no\n`SIGKILL`\nwill be sent. Windows doesn\'t support\n`SIGTERM`\nand\n`SIGINT`\nsignals, so this option is ignored on Windows. Note that shutting down a Docker container requires\n`SIGTERM`\n.\n`ignoreHTTPSErrors`\nWhether to ignore HTTPS errors when fetching the\n`url`\n. Defaults to\n`false`\n.\n`name`\nSpecifies a custom name for the web server. This name will be prefixed to log messages. Defaults to\n`[WebServer]`\n.\n`port`\nDeprecated\n. Use\n`url`\ninstead. The port that your http server is expected to appear on. It does wait until it accepts connections. Either\n`port`\nor\n`url`\nshould be specified.\n`reuseExistingServer`\nIf\n`true`\n, it will re-use an existing server on the\n`port`\nor\n`url`\nwhen available. If no server is running on that\n`port`\nor\n`url`\n, it will run the command to start a new server. If\n`false`\n, it will throw if an existing process is listening on the\n`port`\nor\n`url`\n. This should be commonly set to\n`!process.env.CI`\nto allow the local dev server when running tests locally.\n`stderr`\nWhether to pipe the stderr of the command to the process stderr or ignore it. Defaults to\n`"pipe"`\n.\n`stdout`\nIf\n`"pipe"`\n, it will pipe the stdout of the command to the process stdout. If\n`"ignore"`\n, it will ignore the stdout of the command. Default to\n`"ignore"`\n.\n`timeout`\nHow long to wait for the process to start up and be available in milliseconds. Defaults to 60000.\n`url`\nURL of your http server that is expected to return a 2xx, 3xx, 400, 401, 402, or 403 status code when the server is ready to accept connections. Either\n`port`\nor\n`url`\nshould be specified. If both\n`url`\nand\n`wait`\nare specified, the server is considered started when at least one of the conditions is met.\n`wait`\nConsider command started only when given output has been produced. Takes an object with optional\n`stdout`\nand/or\n`stderr`\nregular expressions. Named capture groups in the regex are stored in the environment, for example\n`/Listening on port (?&lt;my_server_port&gt;\\d+)/`\nwill store the port number in\n`process.env[\'MY_SERVER_PORT\']`\n. If both\n`url`\nand\n`wait`\nare specified, the server is considered started when at least one of the conditions is met.', "Playwright comes with a\n`webServer`\noption in the config file which gives you the ability to launch a local dev server before running your tests. This is ideal for when writing your tests during development and when you don't have a staging or production url to test against."]</t>
+          <t>['Web server | Playwright', "Webservers can sometimes take longer to boot up. In this case, you can increase the timeout to wait for the server to start.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({// Rest of your config...// Run your local dev server before starting the testswebServer:{command:'npm run start',url:'http://localhost:3000',reuseExistingServer:!process.env.CI,timeout:120*1000,},});`\n```", 'Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', "Multiple web servers (or background processes) can be launched simultaneously by providing an array of\n`webServer`\nconfigurations. See\ntestConfig.webServer (https://playwright.dev/docs/api/class-testconfig#test-config-web-server)\nfor more info.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({webServer:[{command:'npm run start',url:'http://localhost:3000',name:'Frontend',timeout:120*1000,reuseExistingServer:!process.env.CI,},{command:'npm run backend',url:'http://localhost:3333',name:'Backend',timeout:120*1000,reuseExistingServer:!process.env.CI,}],use:{baseURL:'http://localhost:3000',},});`\n```"]</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>['Use the webServer property in your Playwright config to launch a development web server during the tests.', "webServer: {\n    command: 'npm run start',\n    url: 'http://localhost:3000',\n    reuseExistingServer: !process.env.CI,\n    stdout: 'ignore',\n    stderr: 'pipe',\n  },"]</t>
+          <t>['Playwright comes with a webServer option in the config file which gives you the ability to launch a local dev server before running your tests.', 'Webservers can sometimes take longer to boot up. In this case, you can increase the timeout to wait for the server to start.', "webServer: [ { command: 'npm run start', url: 'http://localhost:3000', name: 'Frontend', timeout: 120 * 1000, reuseExistingServer: !process.env.CI, }, { command: 'npm run backend', url: 'http://localhost:3333', name: 'Backend', timeout: 120 * 1000, reuseExistingServer: !process.env.CI, } ]"]</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>To start a local dev server automatically before your tests run, you need to use the `webServer` property in your `playwright.config.ts` file.
+          <t>To configure your stack to wait for both the web front end and the API service, you should use an array of `webServer` configurations in your `playwright.config.ts` file. This allows you to launch multiple background processes simultaneously.
+To address the slow startup time of the API service, you must set the `timeout` property to at least 90,000 milliseconds (or higher) within the `webServer` configuration for that service.
 Example configuration:
 ```typescript
 import { defineConfig } from '@playwright/test';
 export default defineConfig({
-  // Run your local dev server before starting the tests
-  webServer: {
-    command: 'npm run start',
-    url: 'http://localhost:3000',
-    reuseExistingServer: !process.env.CI,
-    stdout: 'ignore',
-    stderr: 'pipe',
+  webServer: [
+    {
+      command: 'npm run start', // Command for your web front end
+      url: 'http://localhost:3000',
+      name: 'Frontend',
+      timeout: 120 * 1000,
+      reuseExistingServer: !process.env.CI,
+    },
+    {
+      command: 'npm run backend', // Command for your API service
+      url: 'http://localhost:3333', // URL the API service listens on
+      name: 'Backend',
+      timeout: 120 * 1000, // Set to 120 seconds to accommodate the 90-second startup
+      reuseExistingServer: !process.env.CI,
+    }
+  ],
+  use: {
+    baseURL: 'http://localhost:3000',
   },
 });
-```
-Key properties to include:
-*   **`command`**: The shell command to start your local dev server.
-*   **`url`**: The URL where your server is expected to be available.
-*   **`reuseExistingServer`**: Setting this to `!process.env.CI` is recommended to allow the local dev server to be reused when running tests locally while ensuring a fresh start in CI environments.</t>
+```</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Declare a webServer block (its command and url) so Playwright boots your dev server before the run, and set reuseExistingServer: !process.env.CI to reuse a locally-running one but always start clean on CI.</t>
+          <t>The `webServer` option accepts an array, so declare both processes and let the runner wait for each one. Give each entry a `command`, a `url` to poll for readiness, a `name` so failures are attributable, and — for the slow one — a `timeout` big enough to cover the boot, e.g. `timeout: 120 * 1000`, since the default is not enough for a server that takes 90 seconds. Setting `reuseExistingServer: !process.env.CI` on each keeps local iteration fast while forcing a fresh boot on CI. Pair it with `use: { baseURL: 'http://localhost:3000' }` so specs can navigate with relative paths.</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0.0078115</v>
       </c>
       <c r="G89" t="n">
-        <v>0.86</v>
+        <v>29441</v>
       </c>
       <c r="H89" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1551724137931035</v>
+        <v>0.2</v>
       </c>
       <c r="J89" t="n">
-        <v>0.5142857142857142</v>
+        <v>5</v>
       </c>
       <c r="K89" t="n">
-        <v>0.5833333333041666</v>
+        <v>0.1756756756756757</v>
       </c>
       <c r="L89" t="n">
+        <v>0.2626262626262627</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.499999999975</v>
+      </c>
+      <c r="N89" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5435,7 +6476,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>["Locator | Playwright\n\nLocators are the central piece of Playwright's auto-waiting and retry-ability. In a nutshell, locators represent a way to find element(s) on the page at any moment. A locator can be created with the\npage.locator() (https://playwright.dev/docs/api/class-page#page-locator)\nmethod.\n\nLearn more about locators (https://playwright.dev/docs/locators)\n.", 'Locators | Playwright', 'Playwright comes with multiple built-in locators. To make tests resilient, we recommend prioritizing user-facing attributes and explicit contracts such as\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign in\n```\n`&lt;button&gt;Sign in&lt;/button&gt;`\n```\n\nLocate the element by its role of\n`button`\nwith name "Sign in".\n\n```\n`awaitpage.getByRole(\'button\',{name:\'Sign in\'}).click();`\n```\n\nnote\nUse the\ncode generator (https://playwright.dev/docs/codegen)\nto generate a locator, and then edit it as you\'d like.\n\nEvery time a locator is used for an action, an up-to-date DOM element is located in the page. In the snippet below, the underlying DOM element will be located twice, once prior to every action. This means that if the DOM changes in between the calls due to re-render, the new element corresponding to the locator will be used.\n\n```\n`constlocator=page.getByRole(\'button\',{name:\'Sign in\'});awaitlocator.hover();awaitlocator.click();`\n```\n\nNote that all methods that create a locator, such as\npage.getByLabel() (https://playwright.dev/docs/api/class-page#page-get-by-label)\n, are also available on the\nLocator (https://playwright.dev/docs/api/class-locator)\nand\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\nclasses, so you can chain them and iteratively narrow down your locator.\n\n```\n`constlocator=page.frameLocator(\'#my-frame\').getByRole(\'button\',{name:\'Sign in\'});awaitlocator.click();`\n```', 'If you absolutely must use CSS or XPath locators, you can use\npage.locator() (https://playwright.dev/docs/api/class-page#page-locator)\nto create a locator that takes a selector describing how to find an element in the page. Playwright supports CSS and XPath selectors, and auto-detects them if you omit\n`css=`\nor\n`xpath=`\nprefix.\n\n```\n`awaitpage.locator(\'css=button\').click();awaitpage.locator(\'xpath=//button\').click();awaitpage.locator(\'button\').click();awaitpage.locator(\'//button\').click();`\n```\n\nXPath and CSS selectors can be tied to the DOM structure or implementation. These selectors can break when the DOM structure changes. Long CSS or XPath chains below are an example of a\nbad practice\nthat leads to unstable tests:\n\n```\n`awaitpage.locator(\'#tsf &gt; div:nth-child(2) &gt; div.A8SBwf &gt; div.RNNXgb &gt; div &gt; div.a4bIc &gt; input\').click();awaitpage.locator(\'//*[@id="tsf"]/div[2]/div[1]/div[1]/div/div[2]/input\').click();`\n```\n\nWhen to use this\nCSS and XPath are not recommended as the DOM can often change leading to non resilient tests. Instead, try to come up with a locator that is close to how the user perceives the page such as\nrole locators (https://playwright.dev/docs/locators#locate-by-role)\nor\ndefine an explicit testing contract (https://playwright.dev/docs/locators#locate-by-test-id)\nusing test ids.', 'Other locators | Playwright', "Locator (https://playwright.dev/docs/api/class-locator)\ns are the central piece of Playwright's auto-waiting and retry-ability. In a nutshell, locators represent a way to find element(s) on the page at any moment.", "These are the recommended built-in locators.\n\npage.getByRole() (https://playwright.dev/docs/locators#locate-by-role)\nto locate by explicit and implicit accessibility attributes.\npage.getByText() (https://playwright.dev/docs/locators#locate-by-text)\nto locate by text content.\npage.getByLabel() (https://playwright.dev/docs/locators#locate-by-label)\nto locate a form control by associated label's text.\npage.getByPlaceholder() (https://playwright.dev/docs/locators#locate-by-placeholder)\nto locate an input by placeholder.\npage.getByAltText() (https://playwright.dev/docs/locators#locate-by-alt-text)\nto locate an element, usually image, by its text alternative.\npage.getByTitle() (https://playwright.dev/docs/locators#locate-by-title)\nto locate an element by its title attribute.\npage.getByTestId() (https://playwright.dev/docs/locators#locate-by-test-id)\nto locate an element based on its\n`data-testid`\nattribute (other attributes can be configured).\n\n```\n`awaitpage.getByLabel('User Name').fill('John');awaitpage.getByLabel('Password').fill('secret-password');awaitpage.getByRole('button',{name:'Sign in'}).click();awaitexpect(page.getByText('Welcome, John!')).toBeVisible();`\n```"]</t>
+          <t>['Locators | Playwright', 'Playwright comes with multiple built-in locators. To make tests resilient, we recommend prioritizing user-facing attributes and explicit contracts such as\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign in\n```\n`&lt;button&gt;Sign in&lt;/button&gt;`\n```\n\nLocate the element by its role of\n`button`\nwith name "Sign in".\n\n```\n`awaitpage.getByRole(\'button\',{name:\'Sign in\'}).click();`\n```\n\nnote\nUse the\ncode generator (https://playwright.dev/docs/codegen)\nto generate a locator, and then edit it as you\'d like.\n\nEvery time a locator is used for an action, an up-to-date DOM element is located in the page. In the snippet below, the underlying DOM element will be located twice, once prior to every action. This means that if the DOM changes in between the calls due to re-render, the new element corresponding to the locator will be used.\n\n```\n`constlocator=page.getByRole(\'button\',{name:\'Sign in\'});awaitlocator.hover();awaitlocator.click();`\n```\n\nNote that all methods that create a locator, such as\npage.getByLabel() (https://playwright.dev/docs/api/class-page#page-get-by-label)\n, are also available on the\nLocator (https://playwright.dev/docs/api/class-locator)\nand\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\nclasses, so you can chain them and iteratively narrow down your locator.\n\n```\n`constlocator=page.frameLocator(\'#my-frame\').getByRole(\'button\',{name:\'Sign in\'});awaitlocator.click();`\n```', 'warning\nWe recommend\nlocating by test id (https://playwright.dev/docs/locators#locate-by-test-id)\ninstead.\n\nPlaywright supports shorthand for selecting elements using certain attributes. Currently, only the following attributes are supported:\n\n`id`\n`data-testid`\n`data-test-id`\n`data-test`\n\n```\n`// Fill an input with the id "username"awaitpage.locator(\'id=username\').fill(\'value\');// Click an element with data-test-id "submit"awaitpage.locator(\'data-test-id=submit\').click();`\n```\n\nnote\nAttribute selectors are not CSS selectors, so anything CSS-specific like\n`:enabled`\nis not supported. For more features, use a proper\ncss (https://playwright.dev/docs/other-locators#css-locator)\nselector, e.g.\n`css=[data-test="login"]:enabled`\n.', 'If you absolutely must use CSS or XPath locators, you can use\npage.locator() (https://playwright.dev/docs/api/class-page#page-locator)\nto create a locator that takes a selector describing how to find an element in the page. Playwright supports CSS and XPath selectors, and auto-detects them if you omit\n`css=`\nor\n`xpath=`\nprefix.\n\n```\n`awaitpage.locator(\'css=button\').click();awaitpage.locator(\'xpath=//button\').click();awaitpage.locator(\'button\').click();awaitpage.locator(\'//button\').click();`\n```\n\nXPath and CSS selectors can be tied to the DOM structure or implementation. These selectors can break when the DOM structure changes. Long CSS or XPath chains below are an example of a\nbad practice\nthat leads to unstable tests:\n\n```\n`awaitpage.locator(\'#tsf &gt; div:nth-child(2) &gt; div.A8SBwf &gt; div.RNNXgb &gt; div &gt; div.a4bIc &gt; input\').click();awaitpage.locator(\'//*[@id="tsf"]/div[2]/div[1]/div[1]/div/div[2]/input\').click();`\n```\n\nWhen to use this\nCSS and XPath are not recommended as the DOM can often change leading to non resilient tests. Instead, try to come up with a locator that is close to how the user perceives the page such as\nrole locators (https://playwright.dev/docs/locators#locate-by-role)\nor\ndefine an explicit testing contract (https://playwright.dev/docs/locators#locate-by-test-id)\nusing test ids.', 'The\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\nlocator reflects how users and assistive technology perceive the page, for example whether some element is a button or a checkbox. When locating by role, you should usually pass the accessible name as well, so that the locator pinpoints the exact element.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign up\nSubscribe\nSubmit\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nRole locators include\nbuttons, checkboxes, headings, links, lists, tables, and many more (https://www.w3.org/TR/html-aria/#docconformance)\nand follow W3C specifications for\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. Note that many html elements like\n`&lt;button&gt;`\nhave an\nimplicitly defined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role locator.\n\nNote that role locators\ndo not replace\naccessibility audits and conformance tests, but rather give early feedback about the ARIA guidelines.\n\nWhen to use role locators\nWe recommend prioritizing role locators to locate elements, as it is the closest way to how users and assistive technology perceive the page.', 'Testing by test ids is the most resilient way of testing as even if your text or role of the attribute changes, the test will still pass. QA\'s and developers should define explicit test ids and query them with\npage.getByTestId() (https://playwright.dev/docs/api/class-page#page-get-by-test-id)\n. However testing by test ids is not user facing. If the role or text value is important to you then consider using user facing locators such as\nrole (https://playwright.dev/docs/locators#locate-by-role)\nand\ntext locators (https://playwright.dev/docs/locators#locate-by-text)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nItinéraire\n```\n`&lt;buttondata-testid="directions"&gt;Itinéraire&lt;/button&gt;`\n```\n\nYou can locate the element by its test id:\n\n```\n`awaitpage.getByTestId(\'directions\').click();`\n```\n\nWhen to use testid locators\nYou can also use test ids when you choose to use the test id methodology or when you can\'t locate by\nrole (https://playwright.dev/docs/locators#locate-by-role)\nor\ntext (https://playwright.dev/docs/locators#locate-by-text)\n.', 'By default,\npage.getByTestId() (https://playwright.dev/docs/api/class-page#page-get-by-test-id)\nwill locate elements based on the\n`data-testid`\nattribute, but you can configure it in your test config or by calling\nselectors.setTestIdAttribute() (https://playwright.dev/docs/api/class-selectors#selectors-set-test-id-attribute)\n.\n\nSet the test id to use a custom data attribute for your tests.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{testIdAttribute:\'data-pw\'}});`\n```\n\nIn your html you can now use\n`data-pw`\nas your test id instead of the default\n`data-testid`\n.\n\nhttp://localhost:3000\nItinéraire\n```\n`&lt;buttondata-pw="directions"&gt;Itinéraire&lt;/button&gt;`\n```\n\nAnd then locate the element as you would normally do:\n\n```\n`awaitpage.getByTestId(\'directions\').click();`\n```']</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5445,16 +6486,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>To make your tests resilient and ensure locators survive refactors, you should avoid CSS and XPath selectors, as they are often tied to the DOM structure and can break when that structure changes.
-Instead, you should prioritize locators that reflect how a user perceives the page or define an explicit testing contract. The recommended built-in locators include:
-*   **Role locators:** `page.getByRole()` (locates by explicit and implicit accessibility attributes).
-*   **Test IDs:** `page.getByTestId()` (locates based on a `data-testid` attribute).
-*   **Other user-facing locators:**
-    *   `page.getByText()` (locates by text content).
-    *   `page.getByLabel()` (locates a form control by its associated label).
-    *   `page.getByPlaceholder()` (locates an input by its placeholder).
-    *   `page.getByAltText()` (locates an element, such as an image, by its text alternative).
-    *   `page.getByTitle()` (locates an element by its title attribute).</t>
+          <t>To create resilient tests that survive refactors, you should avoid CSS and XPath selectors, as they are tied to the DOM structure and break when it changes. Instead, use the following approaches:
+### 1. Recommended: User-Facing Locators (Role Locators)
+Playwright recommends prioritizing **role locators** because they reflect how users and assistive technology perceive the page. Use `page.getByRole()` to locate elements by their role (e.g., button, checkbox, heading) and their accessible name.
+*   **Example:** `await page.getByRole('button', { name: 'Sign in' }).click();`
+### 2. Alternative: Explicit Testing Contracts (Test IDs)
+If you cannot use role or text locators, or if you prefer a methodology where tests remain passing even if the text or role changes, use **test IDs**. This is described as the most resilient way of testing.
+*   **How to use:** Define an explicit attribute on your elements (the default is `data-testid`) and use `page.getByTestId()`.
+*   **Example:** `await page.getByTestId('directions').click();`
+*   **Customization:** You can configure a custom attribute (e.g., `data-pw`) in your `playwright.config.ts` file:
+    ```typescript
+    // playwright.config.ts
+    export default defineConfig({
+      use: {
+        testIdAttribute: 'data-pw'
+      }
+    });
+    ```
+**Note:** While Playwright supports shorthand attribute selectors (e.g., `page.locator('data-testid=submit')`), the documentation explicitly recommends using `page.getByTestId()` instead.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5463,24 +6512,30 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>0.010736999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>0.43</v>
+        <v>38858</v>
       </c>
       <c r="H90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.53</v>
       </c>
       <c r="J90" t="n">
-        <v>0.3125</v>
+        <v>5</v>
       </c>
       <c r="K90" t="n">
-        <v>0.6861904761767524</v>
+        <v>0.06435643564356436</v>
       </c>
       <c r="L90" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.9999999999857143</v>
+      </c>
+      <c r="N90" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5492,17 +6547,18 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>['Videos | Playwright', "Playwright Test can record videos for your tests, controlled by the\n`video`\noption in your Playwright config. By default videos are off.\n\n`'off'`\n- Do not record video.\n`'on'`\n- Record video for each test.\n`'retain-on-failure'`\n- Record video for each test, but remove all videos from successful test runs.\n`'on-first-retry'`\n- Record video only when retrying a test for the first time.\n\nVideo files will appear in the test output directory, typically\n`test-results`\n. See\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nfor advanced video configuration.\n\nVideos are saved upon\nbrowser context (https://playwright.dev/docs/browser-contexts)\nclosure at the end of a test. If you create a browser context manually, make sure to await\nbrowserContext.close() (https://playwright.dev/docs/api/class-browsercontext#browser-context-close)\n.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:'on-first-retry',},});`\n```\n```\n`constcontext=awaitbrowser.newContext({recordVideo:{dir:'videos/'}});// Make sure to await close, so that videos are saved.awaitcontext.close();`\n```\n\nYou can also specify video size and annotation. The video size defaults to the viewport size scaled down to fit 800x800. The video of the viewport is placed in the top-left corner of the output video, scaled down to fit if necessary. You may need to set the viewport size to match your desired video size.\n\nWhen\n`show: { actions }`\nis specified, each action will be visually highlighted in the video with the element outline and action title subtitle. The optional\n`duration`\nproperty controls how long each annotation is displayed (defaults to\n`500`\nms).\n\nWhen\n`show: { test }`\nis specified, video will be annotated with the current test information with configurable\n`level`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:{mode:'on-first-retry',size:{width:640,height:480},show:{actions:{duration:500,position:'top-right',fontSize:14,},test:{level:'step',position:'top-left',fontSize:12,}},},},});`\n```\n\nFor multi-page scenarios, you can access the video file associated with the page via the\npage.video() (https://playwright.dev/docs/api/class-page#page-video)\n.\n\n```\n`constpath=awaitpage.video().path();`\n```\n\nnote\nNote that the video is only available after the page or browser context is closed.", "With Playwright you can capture screenshots, record videos as well as traces of your test. By default these are turned off but you can enable them by setting the\n`screenshot`\n,\n`video`\nand\n`trace`\noptions in your\n`playwright.config.js`\nfile.\n\nTrace files, screenshots and videos will appear in the test output directory, typically\n`test-results`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{// Capture screenshot after each test failure.screenshot:'only-on-failure',// Record trace only when retrying a test for the first time.trace:'on-first-retry',// Record video only when retrying a test for the first time.video:'on-first-retry'},});`\n```\n\nOption\nDescription\ntestOptions.screenshot (https://playwright.dev/docs/api/class-testoptions#test-options-screenshot)\nCapture\nscreenshots (https://playwright.dev/docs/screenshots)\nof your test. Options include\n`'off'`\n,\n`'on'`\nand\n`'only-on-failure'`\ntestOptions.trace (https://playwright.dev/docs/api/class-testoptions#test-options-trace)\nPlaywright can produce test traces while running the tests. Later on, you can view the trace and get detailed information about Playwright execution by opening\nTrace Viewer (https://playwright.dev/docs/trace-viewer)\n. Options include:\n`'off'`\n,\n`'on'`\n,\n`'retain-on-failure'`\nand\n`'on-first-retry'`\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nPlaywright can record\nvideos (https://playwright.dev/docs/videos)\nfor your tests. Options include:\n`'off'`\n,\n`'on'`\n,\n`'retain-on-failure'`\nand\n`'on-first-retry'`"]</t>
+          <t>['Videos | Playwright', "Playwright Test can record videos for your tests, controlled by the\n`video`\noption in your Playwright config. By default videos are off.\n\n`'off'`\n- Do not record video.\n`'on'`\n- Record video for each test.\n`'retain-on-failure'`\n- Record video for each test, but remove all videos from successful test runs.\n`'on-first-retry'`\n- Record video only when retrying a test for the first time.\n\nVideo files will appear in the test output directory, typically\n`test-results`\n. See\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nfor advanced video configuration.\n\nVideos are saved upon\nbrowser context (https://playwright.dev/docs/browser-contexts)\nclosure at the end of a test. If you create a browser context manually, make sure to await\nbrowserContext.close() (https://playwright.dev/docs/api/class-browsercontext#browser-context-close)\n.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:'on-first-retry',},});`\n```\n```\n`constcontext=awaitbrowser.newContext({recordVideo:{dir:'videos/'}});// Make sure to await close, so that videos are saved.awaitcontext.close();`\n```\n\nYou can also specify video size and annotation. The video size defaults to the viewport size scaled down to fit 800x800. The video of the viewport is placed in the top-left corner of the output video, scaled down to fit if necessary. You may need to set the viewport size to match your desired video size.\n\nWhen\n`show: { actions }`\nis specified, each action will be visually highlighted in the video with the element outline and action title subtitle. The optional\n`duration`\nproperty controls how long each annotation is displayed (defaults to\n`500`\nms).\n\nWhen\n`show: { test }`\nis specified, video will be annotated with the current test information with configurable\n`level`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:{mode:'on-first-retry',size:{width:640,height:480},show:{actions:{duration:500,position:'top-right',fontSize:14,},test:{level:'step',position:'top-left',fontSize:12,}},},},});`\n```\n\nFor multi-page scenarios, you can access the video file associated with the page via the\npage.video() (https://playwright.dev/docs/api/class-page#page-video)\n.\n\n```\n`constpath=awaitpage.video().path();`\n```\n\nnote\nNote that the video is only available after the page or browser context is closed."]</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>["'retain-on-failure' - Record video for each test, but remove all videos from successful test runs.", "import { defineConfig } from '@playwright/test';\nexport default defineConfig({\n  use: {\n    video: 'on-first-retry',\n  },\n});"]</t>
+          <t>["'retain-on-failure' - Record video for each test, but remove all videos from successful test runs."]</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>To configure Playwright to record videos only when a test fails, set the `video` option to `'retain-on-failure'` in your `playwright.config.ts` file:
+          <t>To record videos only when a test fails, set the `video` option to `'retain-on-failure'` in your Playwright configuration file (`playwright.config.ts`).
+Example configuration:
 ```typescript
 import { defineConfig } from '@playwright/test';
 export default defineConfig({
@@ -5511,7 +6567,7 @@
   },
 });
 ```
-This setting records video for each test but removes all videos from successful test runs.</t>
+This setting records video for each test but removes the files for successful test runs.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5520,24 +6576,30 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>0.0071845</v>
       </c>
       <c r="G91" t="n">
-        <v>0.8</v>
+        <v>27843</v>
       </c>
       <c r="H91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1481481481481481</v>
+        <v>0.86</v>
       </c>
       <c r="J91" t="n">
-        <v>0.3636363636363636</v>
+        <v>5</v>
       </c>
       <c r="K91" t="n">
-        <v>0.5833333333041666</v>
+        <v>0.1636363636363636</v>
       </c>
       <c r="L91" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.49999999995</v>
+      </c>
+      <c r="N91" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5549,7 +6611,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>['We can split tests into projects and use filters to run a subset of tests. For example, we can create a project that runs tests using a filter matching all tests with a specific file name. We can then have another group of tests that ignore specific test files.\n\nHere is an example that defines a common timeout and two projects. The "Smoke" project runs a small subset of tests without retries, and "Default" project runs all other tests with retries.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({timeout:60000,// Timeout is shared between all tests.projects:[{name:\'Smoke\',testMatch:/.*smoke.spec.ts/,retries:0,},{name:\'Default\',testIgnore:/.*smoke.spec.ts/,retries:2,},],});`\n```', 'Retries | Playwright', "By setting up projects we can also run a group of tests with different timeouts or retries or run a group of tests against different environments. For example we can run our tests against a staging environment with 2 retries as well as against a production environment with 0 retries.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({timeout:60000,// Timeout is shared between all tests.projects:[{name:'staging',use:{baseURL:'staging.example.com',},retries:2,},{name:'production',use:{baseURL:'production.example.com',},retries:0,},],});`\n```", 'Annotations | Playwright', 'Here are some of the most common configuration options.\n\n```\n`import{defineConfig,devices}from\'@playwright/test\';exportdefaultdefineConfig({// Look for test files in the "tests" directory, relative to this configuration file.testDir:\'tests\',// Run all tests in parallel.fullyParallel:true,// Fail the build on CI if you accidentally left test.only in the source code.forbidOnly:!!process.env.CI,// Retry on CI only.retries:process.env.CI?2:0,// Opt out of parallel tests on CI.workers:process.env.CI?1:undefined,// Reporter to usereporter:\'html\',use:{// Base URL to use in actions like `await page.goto(\'/\')`.baseURL:\'http://localhost:3000\',// Collect trace when retrying the failed test.trace:\'on-first-retry\',},// Configure projects for major browsers.projects:[{name:\'chromium\',use:{...devices[\'Desktop Chrome\']},},],// Run your local dev server before starting the tests.webServer:{command:\'npm run start\',url:\'http://localhost:3000\',reuseExistingServer:!process.env.CI,},});`\n```\n\nOption\nDescription\ntestConfig.forbidOnly (https://playwright.dev/docs/api/class-testconfig#test-config-forbid-only)\nWhether to exit with an error if any tests are marked as\n`test.only`\n. Useful on CI.\ntestConfig.fullyParallel (https://playwright.dev/docs/api/class-testconfig#test-config-fully-parallel)\nhave all tests in all files to run in parallel. See\nParallelism (https://playwright.dev/docs/test-parallel)\nand\nSharding (https://playwright.dev/docs/test-sharding)\nfor more details.\ntestConfig.projects (https://playwright.dev/docs/api/class-testconfig#test-config-projects)\nRun tests in multiple configurations or on multiple browsers\ntestConfig.reporter (https://playwright.dev/docs/api/class-testconfig#test-config-reporter)\nReporter to use. See\nTest Reporters (https://playwright.dev/docs/test-reporters)\nto learn more about which reporters are available.\ntestConfig.retries (https://playwright.dev/docs/api/class-testconfig#test-config-retries)\nThe maximum number of retry attempts per test. See\nTest Retries (https://playwright.dev/docs/test-retries)\nto learn more about retries.\ntestConfig.testDir (https://playwright.dev/docs/api/class-testconfig#test-config-test-dir)\nDirectory with the test files.\ntestConfig.use (https://playwright.dev/docs/api/class-testconfig#test-config-use)\nOptions with\n`use{}`\ntestConfig.webServer (https://playwright.dev/docs/api/class-testconfig#test-config-web-server)\nTo launch a server during the tests, use the\n`webServer`\noption\ntestConfig.workers (https://playwright.dev/docs/api/class-testconfig#test-config-workers)\nThe maximum number of concurrent worker processes to use for parallelizing tests. Can also be set as percentage of logical CPU cores, e.g.\n`\'50%\'.`\n. See\nParallelism (https://playwright.dev/docs/test-parallel)\nand\nSharding (https://playwright.dev/docs/test-sharding)\nfor more details.']</t>
+          <t>['We can split tests into projects and use filters to run a subset of tests. For example, we can create a project that runs tests using a filter matching all tests with a specific file name. We can then have another group of tests that ignore specific test files.\n\nHere is an example that defines a common timeout and two projects. The "Smoke" project runs a small subset of tests without retries, and "Default" project runs all other tests with retries.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({timeout:60000,// Timeout is shared between all tests.projects:[{name:\'Smoke\',testMatch:/.*smoke.spec.ts/,retries:0,},{name:\'Default\',testIgnore:/.*smoke.spec.ts/,retries:2,},],});`\n```', "By setting up projects we can also run a group of tests with different timeouts or retries or run a group of tests against different environments. For example we can run our tests against a staging environment with 2 retries as well as against a production environment with 0 retries.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({timeout:60000,// Timeout is shared between all tests.projects:[{name:'staging',use:{baseURL:'staging.example.com',},retries:2,},{name:'production',use:{baseURL:'production.example.com',},retries:0,},],});`\n```"]</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5559,12 +6621,15 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>You can organize this by splitting your tests into projects within your `playwright.config.ts` file. You can use `testMatch` to include specific files for the "Smoke" project and `testIgnore` to exclude those same files from the "Default" project.
-Here is the example configuration provided:
+          <t>To organize your tests into a "Smoke" set and a "Default" set, you should define them as projects within your `playwright.config.ts` file using the `projects` array.
+You can configure them as follows:
+*   **Smoke project:** Use `testMatch` to target the specific subset of tests (e.g., `.*smoke.spec.ts`) and set `retries: 0`.
+*   **Default project:** Use `testIgnore` to exclude the smoke tests (e.g., `.*smoke.spec.ts`) and set `retries: 2`.
+Example configuration:
 ```typescript
 import { defineConfig } from '@playwright/test';
 export default defineConfig({
-  timeout: 60000, // Timeout is shared between all tests.
+  timeout: 60000,
   projects: [
     {
       name: 'Smoke',
@@ -5587,24 +6652,30 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>0.008822</v>
       </c>
       <c r="G92" t="n">
-        <v>0.67</v>
+        <v>33433</v>
       </c>
       <c r="H92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>0.189873417721519</v>
+        <v>0.57</v>
       </c>
       <c r="J92" t="n">
-        <v>0.5357142857142857</v>
+        <v>5</v>
       </c>
       <c r="K92" t="n">
-        <v>0.699999999965</v>
+        <v>0.196078431372549</v>
       </c>
       <c r="L92" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="N92" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5626,7 +6697,8 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>You can skip the test on Firefox by using `test.skip` with a condition based on the `browserName`:
+          <t>To skip a test only on Firefox, use the `test.skip` annotation within your test, passing a condition that checks if the `browserName` is `'firefox'`.
+Use the following syntax:
 ```javascript
 test('skip this test', async ({page, browserName}) =&gt; {
   test.skip(browserName === 'firefox', 'Still working on it');
@@ -5640,24 +6712,30 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>0.007272499999999999</v>
       </c>
       <c r="G93" t="n">
+        <v>28360</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" t="n">
         <v>0.8</v>
       </c>
-      <c r="H93" t="n">
-        <v>5</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0.4411764705882353</v>
-      </c>
       <c r="J93" t="n">
+        <v>5</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L93" t="n">
         <v>0.5172413793103449</v>
       </c>
-      <c r="K93" t="n">
+      <c r="M93" t="n">
         <v>0.49999999995</v>
       </c>
-      <c r="L93" t="n">
+      <c r="N93" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5679,15 +6757,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Answer: The cleanest fix is to set a separate, larger timeout specifically for that fixture while keeping the overall test timeout small. You can do this by passing the timeout option to the fixture definition:
+          <t>The cleanest fix is to set a separate, larger timeout specifically for the slow fixture while keeping the overall test timeout small. You can do this by passing a timeout option to the fixture definition:
 ```javascript
+import { test as base, expect } from '@playwright/test';
 const test = base.extend&lt;{ slowFixture: string }&gt;({
   slowFixture: [async ({}, use) =&gt; {
     // ... perform a slow operation ...
     await use('hello');
   }, { timeout: 60000 }]
 });
-```</t>
+```
+This approach applies to both test-scoped and worker-scoped fixtures.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5696,84 +6776,101 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0.00792525</v>
       </c>
       <c r="G94" t="n">
-        <v>0.4</v>
+        <v>30671</v>
       </c>
       <c r="H94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.57</v>
       </c>
       <c r="J94" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="K94" t="n">
+        <v>0.1917808219178082</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="M94" t="n">
         <v>0.9999999999</v>
       </c>
-      <c r="L94" t="n">
+      <c r="N94" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>I need to test a chat feature where an admin and a user interact at the same time in one test. How can I simulate two independent users?</t>
+          <t>I keep writing teardown code to clear cookies and local storage so one spec doesn't poison the next, and it still isn't enough — things like already-visited link styling survive anyway, and a test that fails halfway never gets to its cleanup. I'd rather every test just began from nothing.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>["BrowserContext | Playwright\n\nBrowserContexts provide a way to operate multiple independent browser sessions.\n\nIf a page opens another page, e.g. with a\n`window.open`\ncall, the popup will belong to the parent page's browser context.\n\nPlaywright allows creating isolated non-persistent browser contexts with\nbrowser.newContext() (https://playwright.dev/docs/api/class-browser#browser-new-context)\nmethod. Non-persistent browser contexts don't write any browsing data to disk.\n\n```\n`// Create a new incognito browser contextconstcontext=awaitbrowser.newContext();// Create a new page inside context.constpage=awaitcontext.newPage();awaitpage.goto('https://example.com');// Dispose context once it's no longer needed.awaitcontext.close();`\n```", 'Isolation | Playwright', "Playwright can create multiple browser contexts within a single scenario. This is useful when you want to test for multi-user functionality, like a chat.\n\nTest\nLibrary\n```\n`import{test}from'@playwright/test';test('admin and user',async({browser})=&gt;{// Create two isolated browser contextsconstadminContext=awaitbrowser.newContext();constuserContext=awaitbrowser.newContext();// Create pages and interact with contexts independentlyconstadminPage=awaitadminContext.newPage();constuserPage=awaituserContext.newPage();});`\n```\n```\n`const{chromium}=require('playwright');// Create a Chromium browser instanceconstbrowser=awaitchromium.launch();// Create two isolated browser contextsconstuserContext=awaitbrowser.newContext();constadminContext=awaitbrowser.newContext();// Create pages and interact with contexts independentlyconstadminPage=awaitadminContext.newPage();constuserPage=awaituserContext.newPage();`\n```", 'When to use\n\nYou need to test how multiple authenticated roles interact together, in a single test.\n\nDetails\n\nUse multiple\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\ns and\nPage (https://playwright.dev/docs/api/class-page)\ns with different storage states in the same test.\n\ntests/example.spec.ts\n```\n`import{test}from\'@playwright/test\';test(\'admin and user\',async({browser})=&gt;{// adminContext and all pages inside, including adminPage, are signed in as "admin".constadminContext=awaitbrowser.newContext({storageState:\'playwright/.auth/admin.json\'});constadminPage=awaitadminContext.newPage();// userContext and all pages inside, including userPage, are signed in as "user".constuserContext=awaitbrowser.newContext({storageState:\'playwright/.auth/user.json\'});constuserPage=awaituserContext.newPage();// ... interact with both adminPage and userPage ...awaitadminContext.close();awaituserContext.close();});`\n```', 'When to use\n\nYou need to test how multiple authenticated roles interact together, in a single test.\n\nDetails\n\nYou can introduce fixtures that will provide a page authenticated as each role.\n\nBelow is an example that\ncreates fixtures (https://playwright.dev/docs/test-fixtures#creating-a-fixture)\nfor two\nPage Object Models (https://playwright.dev/docs/pom)\n- admin POM and user POM. It assumes\n`adminStorageState.json`\nand\n`userStorageState.json`\nfiles were created in the global setup.\n\nplaywright/fixtures.ts\n```\n`import{testasbase,typePage,typeLocator}from\'@playwright/test\';// Page Object Model for the "admin" page.// Here you can add locators and helper methods specific to the admin page.classAdminPage{// Page signed in as "admin".page:Page;// Example locator pointing to "Welcome, Admin" greeting.greeting:Locator;constructor(page:Page){this.page=page;this.greeting=page.locator(\'#greeting\');}}// Page Object Model for the "user" page.// Here you can add locators and helper methods specific to the user page.classUserPage{// Page signed in as "user".page:Page;// Example locator pointing to "Welcome, User" greeting.greeting:Locator;constructor(page:Page){this.page=page;this.greeting=page.locator(\'#greeting\');}}// Declare the types of your fixtures.typeMyFixtures={adminPage:AdminPage;userPage:UserPage;};export*from\'@playwright/test\';exportconsttest=base.extend&lt;MyFixtures&gt;({adminPage:async({browser},use)=&gt;{constcontext=awaitbrowser.newContext({storageState:\'playwright/.auth/admin.json\'});constadminPage=newAdminPage(awaitcontext.newPage());awaituse(adminPage);awaitcontext.close();},userPage:async({browser},use)=&gt;{constcontext=awaitbrowser.newContext({storageState:\'playwright/.auth/user.json\'});constuserPage=newUserPage(awaitcontext.newPage());awaituse(userPage);awaitcontext.close();},});`\n```\n\ntests/example.spec.ts\n```\n`// Import test with our new fixtures.import{test,expect}from\'../playwright/fixtures\';// Use adminPage and userPage fixtures in the test.test(\'admin and user\',async({adminPage,userPage})=&gt;{// ... interact with both adminPage and userPage ...awaitexpect(adminPage.greeting).toHaveText(\'Welcome, Admin\');awaitexpect(userPage.greeting).toHaveText(\'Welcome, User\');});`\n```']</t>
+          <t>['Test Isolation is when each test is completely isolated from another test. Every test runs independently from any other test. This means that each test has its own local storage, session storage, cookies etc. Playwright achieves this using\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\ns which are equivalent to incognito-like profiles. They are fast and cheap to create and are completely isolated, even when running in a single browser. Playwright creates a context for each test, and provides a default\nPage (https://playwright.dev/docs/api/class-page)\nin that context.', 'Isolation | Playwright', 'Fixtures | Playwright', 'Playwright uses browser contexts to achieve Test Isolation. Each test has its own Browser Context. Running the test creates a new browser context each time.  When using Playwright as a Test Runner, browser contexts are created by default. Otherwise, you can create browser contexts manually.\n\nTest\nLibrary\n```\n`import{test}from\'@playwright/test\';test(\'example test\',async({page,context})=&gt;{// "context" is an isolated BrowserContext, created for this specific test.// "page" belongs to this context.});test(\'another test\',async({page,context})=&gt;{// "context" and "page" in this second test are completely// isolated from the first test.});`\n```\n```\n`constbrowser=awaitchromium.launch();constcontext=awaitbrowser.newContext();constpage=awaitcontext.newPage();`\n```\n\nBrowser contexts can also be used to emulate multi-page scenarios involving mobile devices, permissions, locale and color scheme. Check out our\nEmulation (https://playwright.dev/docs/emulation)\nguide for more details.', "You have already used test fixtures in your first test.\n\n```\n`import{test,expect}from'@playwright/test';test('basic test',async({page})=&gt;{awaitpage.goto('https://playwright.dev/');awaitexpect(page).toHaveTitle(/Playwright/);});`\n```\n\nThe\n`{ page }`\nargument tells Playwright Test to set up the\n`page`\nfixture and provide it to your test function.\n\nHere is a list of the pre-defined fixtures that you are likely to use most of the time:\n\nFixture\nType\nDescription\npage\nPage (https://playwright.dev/docs/api/class-page)\nIsolated page for this test run.\ncontext\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nIsolated context for this test run. The\n`page`\nfixture belongs to this context as well. Learn how to\nconfigure context (https://playwright.dev/docs/test-configuration)\n.\nbrowser\nBrowser (https://playwright.dev/docs/api/class-browser)\nBrowsers are shared across tests to optimize resources. Learn how to\nconfigure browsers (https://playwright.dev/docs/test-configuration)\n.\nbrowserName\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\nThe name of the browser currently running the test. Either\n`chromium`\n,\n`firefox`\nor\n`webkit`\n.\nrequest\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nIsolated\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\ninstance for this test run.", 'Global setup and teardown | Playwright', 'There are two different strategies when it comes to Test Isolation: start from scratch or cleanup in between. The problem with cleaning up in between tests is that it can be easy to forget to clean up and some things are impossible to clean up such as "visited links". State from one test can leak into the next test which could cause your test to fail and make debugging harder as the problem comes from another test. Starting from scratch means everything is new, so if the test fails you only have to look within that test to debug.']</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>['Playwright can create multiple browser contexts within a single scenario. This is useful when you want to test for multi-user functionality, like a chat.', "test('admin and user', async ({ browser }) =&gt; {\n  // Create two isolated browser contexts\n  const adminContext = await browser.newContext();\n  const userContext = await browser.newContext();\n\n  // Create pages and interact with contexts independently\n  const adminPage = await adminContext.newPage();\n  const userPage = await userContext.newPage();\n});"]</t>
+          <t>['Tests written with Playwright execute in isolated clean-slate environments called browser contexts. This isolation model improves reproducibility and prevents cascading test failures.', 'Test Isolation is when each test is completely isolated from another test. Every test runs independently from any other test. This means that each test has its own local storage, session storage, cookies etc. Playwright achieves this using BrowserContexts which are equivalent to incognito-like profiles. They are fast and cheap to create and are completely isolated, even when running in a single browser.', 'There are two different strategies when it comes to Test Isolation: start from scratch or cleanup in between. The problem with cleaning up in between tests is that it can be easy to forget to clean up and some things are impossible to clean up such as "visited links".', 'Playwright uses browser contexts to achieve Test Isolation. Each test has its own Browser Context. Running the test creates a new browser context each time.']</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>To simulate two independent users in a single test, you can create multiple isolated browser contexts using the `browser.newContext()` method. 
-As shown in the provided context, you can implement this by creating separate contexts for each user and then creating a page within each of those contexts to interact with them independently:
+          <t>To ensure every test begins from nothing and to avoid the issues associated with manual cleanup (such as "visited links" persisting), you should rely on Playwright's built-in **Test Isolation**.
+Playwright achieves this by creating a new `BrowserContext` for every test. A `BrowserContext` is equivalent to an incognito-like profile, which ensures that each test has its own local storage, session storage, and cookies. Because these contexts are created fresh for each test, state from one test cannot leak into another.
+### How to use it:
+When using the Playwright Test runner, browser contexts are created by default. You do not need to write teardown code; instead, use the built-in `page` or `context` fixtures provided in your test function arguments:
 ```javascript
-test('admin and user', async ({browser}) =&gt; {
-  // Create two isolated browser contexts
-  const adminContext = await browser.newContext();
-  const userContext = await browser.newContext();
-  // Create pages and interact with contexts independently
-  const adminPage = await adminContext.newPage();
-  const userPage = await userContext.newPage();
+import { test } from '@playwright/test';
+test('example test', async ({ page, context }) =&gt; {
+  // "context" is an isolated BrowserContext created for this specific test.
+  // "page" belongs to this context and is isolated from other tests.
 });
 ```
-If you need to test authenticated roles, you can also pass a `storageState` to `browser.newContext()` to ensure each context is signed in as the appropriate user.</t>
+If you are not using the Playwright Test runner, you must create the context manually for each test to ensure isolation:
+```javascript
+const browser = await chromium.launch();
+const context = await browser.newContext();
+const page = await context.newPage();
+```
+By using these isolated contexts, you satisfy the "start from scratch" strategy, which prevents state leakage and ensures that if a test fails, you only need to debug the code within that specific test.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Spin up more than one browser context inside the same test. Each behaves like a separate incognito profile, so an admin context and a user context — each with its own page — interact as two independent users.</t>
+          <t>That's the default, and cleaning up between tests is the strategy the docs advise against — it's easy to forget, and some state (visited links being the standard example) simply cannot be cleaned up, so leakage shows up later as a confusing failure in a different test. The alternative is to start from scratch, which is what browser contexts give you: each test gets its own BrowserContext, an incognito-like profile with its own cookies, local storage and session storage, created fresh for that test and completely isolated even when several run in one browser. With the test runner this happens automatically — the `page` and `context` fixtures in each test belong to a context created for it — so you can delete the teardown rather than fix it. Contexts are cheap and fast to create, so there's no cost argument for reusing one.</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0.0098265</v>
       </c>
       <c r="G95" t="n">
-        <v>0.5</v>
+        <v>35746</v>
       </c>
       <c r="H95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1092436974789916</v>
+        <v>0.71</v>
       </c>
       <c r="J95" t="n">
-        <v>0.3611111111111111</v>
+        <v>5</v>
       </c>
       <c r="K95" t="n">
-        <v>0.99999999998</v>
+        <v>0.1866666666666667</v>
       </c>
       <c r="L95" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.9999999999857143</v>
+      </c>
+      <c r="N95" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5785,7 +6882,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>["FileChooser | Playwright\n\nFileChooser (https://playwright.dev/docs/api/class-filechooser)\nobjects are dispatched by the page in the\npage.on('filechooser') (https://playwright.dev/docs/api/class-page#page-event-file-chooser)\nevent.\n\n```\n`// Start waiting for file chooser before clicking. Note no await.constfileChooserPromise=page.waitForEvent('filechooser');awaitpage.getByText('Upload file').click();constfileChooser=awaitfileChooserPromise;awaitfileChooser.setFiles(path.join(__dirname,'myfile.pdf'));`\n```", 'You can select input files for upload using the\nlocator.setInputFiles() (https://playwright.dev/docs/api/class-locator#locator-set-input-files)\nmethod. It expects first argument to point to an\ninput element (https://developer.mozilla.org/en-US/docs/Web/HTML/Element/input)\nwith the type\n`"file"`\n. Multiple files can be passed in the array. If some of the file paths are relative, they are resolved relative to the current working directory. Empty array clears the selected files.\n\n```\n`// Select one fileawaitpage.getByLabel(\'Upload file\').setInputFiles(path.join(__dirname,\'myfile.pdf\'));// Select multiple filesawaitpage.getByLabel(\'Upload files\').setInputFiles([path.join(__dirname,\'file1.txt\'),path.join(__dirname,\'file2.txt\'),]);// Select a directoryawaitpage.getByLabel(\'Upload directory\').setInputFiles(path.join(__dirname,\'mydir\'));// Remove all the selected filesawaitpage.getByLabel(\'Upload file\').setInputFiles([]);// Upload buffer from memoryawaitpage.getByLabel(\'Upload file\').setInputFiles({name:\'file.txt\',mimeType:\'text/plain\',buffer:Buffer.from(\'this is test\')});`\n```\n\nIf you don\'t have input element in hand (it is created dynamically), you can handle the\npage.on(\'filechooser\') (https://playwright.dev/docs/api/class-page#page-event-file-chooser)\nevent or use a corresponding waiting method upon your action:\n\n```\n`// Start waiting for file chooser before clicking. Note no await.constfileChooserPromise=page.waitForEvent(\'filechooser\');awaitpage.getByLabel(\'Upload file\').click();constfileChooser=awaitfileChooserPromise;awaitfileChooser.setFiles(path.join(__dirname,\'myfile.pdf\'));`\n```', 'Added before v1.9\n\nfileChooser.setFiles\n\nSets the value of the file input this chooser is associated with. If some of the\n`filePaths`\nare relative paths, then they are resolved relative to the current working directory. For empty array, clears the selected files.\n\nUsage\n\n```\n`awaitfileChooser.setFiles(files);awaitfileChooser.setFiles(files,options);`\n```\n\nArguments\n\n`files`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt; |\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n|\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n# (https://playwright.dev/docs/api/class-filechooser#file-chooser-set-files-option-files)\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\nFile name\n`mimeType`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\nFile type\n`buffer`\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\nFile content\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`noWaitAfter`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-filechooser#file-chooser-set-files-option-no-wait-after)\nDeprecated\nThis option has no effect.\nThis option has no effect.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-filechooser#file-chooser-set-files-option-timeout)\nMaximum time in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`actionTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-filechooser#file-chooser-set-files-return)', 'Actions | Playwright']</t>
+          <t>["FileChooser | Playwright\n\nFileChooser (https://playwright.dev/docs/api/class-filechooser)\nobjects are dispatched by the page in the\npage.on('filechooser') (https://playwright.dev/docs/api/class-page#page-event-file-chooser)\nevent.\n\n```\n`// Start waiting for file chooser before clicking. Note no await.constfileChooserPromise=page.waitForEvent('filechooser');awaitpage.getByText('Upload file').click();constfileChooser=awaitfileChooserPromise;awaitfileChooser.setFiles(path.join(__dirname,'myfile.pdf'));`\n```", 'You can select input files for upload using the\nlocator.setInputFiles() (https://playwright.dev/docs/api/class-locator#locator-set-input-files)\nmethod. It expects first argument to point to an\ninput element (https://developer.mozilla.org/en-US/docs/Web/HTML/Element/input)\nwith the type\n`"file"`\n. Multiple files can be passed in the array. If some of the file paths are relative, they are resolved relative to the current working directory. Empty array clears the selected files.\n\n```\n`// Select one fileawaitpage.getByLabel(\'Upload file\').setInputFiles(path.join(__dirname,\'myfile.pdf\'));// Select multiple filesawaitpage.getByLabel(\'Upload files\').setInputFiles([path.join(__dirname,\'file1.txt\'),path.join(__dirname,\'file2.txt\'),]);// Select a directoryawaitpage.getByLabel(\'Upload directory\').setInputFiles(path.join(__dirname,\'mydir\'));// Remove all the selected filesawaitpage.getByLabel(\'Upload file\').setInputFiles([]);// Upload buffer from memoryawaitpage.getByLabel(\'Upload file\').setInputFiles({name:\'file.txt\',mimeType:\'text/plain\',buffer:Buffer.from(\'this is test\')});`\n```\n\nIf you don\'t have input element in hand (it is created dynamically), you can handle the\npage.on(\'filechooser\') (https://playwright.dev/docs/api/class-page#page-event-file-chooser)\nevent or use a corresponding waiting method upon your action:\n\n```\n`// Start waiting for file chooser before clicking. Note no await.constfileChooserPromise=page.waitForEvent(\'filechooser\');awaitpage.getByLabel(\'Upload file\').click();constfileChooser=awaitfileChooserPromise;awaitfileChooser.setFiles(path.join(__dirname,\'myfile.pdf\'));`\n```', 'Actions | Playwright']</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5795,16 +6892,21 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>If you do not have a stable input element because it is created dynamically, you can handle the `page.on('filechooser')` event or use the `page.waitForEvent('filechooser')` method.
-You should start waiting for the file chooser before performing the action that triggers it (such as clicking a button), then use the `fileChooser.setFiles()` method. 
-Example:
+          <t>To upload a file when the input element is created dynamically, you should use the `page.waitForEvent('filechooser')` method. 
+Follow these steps:
+1. Start waiting for the file chooser event before performing the action that triggers the input creation (do not `await` this line).
+2. Perform the action (e.g., clicking a button) that creates the input.
+3. Await the file chooser promise.
+4. Use the `fileChooser.setFiles()` method to upload your file.
+**Example:**
 ```javascript
 // Start waiting for file chooser before clicking. Note no await.
 const fileChooserPromise = page.waitForEvent('filechooser');
-await page.getByLabel('Upload file').click();
+await page.getByText('Upload file').click();
 const fileChooser = await fileChooserPromise;
 await fileChooser.setFiles(path.join(__dirname, 'myfile.pdf'));
-```</t>
+```
+Alternatively, you can handle the `page.on('filechooser')` event.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5813,24 +6915,30 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0.00770275</v>
       </c>
       <c r="G96" t="n">
-        <v>0.57</v>
+        <v>29436</v>
       </c>
       <c r="H96" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
-        <v>0.7272727272727273</v>
+        <v>5</v>
       </c>
       <c r="K96" t="n">
-        <v>0.9999999999666667</v>
+        <v>0.1196581196581197</v>
       </c>
       <c r="L96" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.99999999995</v>
+      </c>
+      <c r="N96" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5852,7 +6960,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Yes, you can change the geolocation mid-test by using `context.setGeolocation`. Note that you can only change the geolocation for all pages in the context.</t>
+          <t>Yes, you can change the geolocation mid-test by using the `context.setGeolocation` method.
+To do this, call the method on the context object within your test:
+```javascript
+await context.setGeolocation({longitude: 48.858455, latitude: 2.294474});
+```
+Note that changing the geolocation will apply to all pages within that context.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5861,24 +6974,30 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>0.007717</v>
       </c>
       <c r="G97" t="n">
-        <v>0.8</v>
+        <v>29913</v>
       </c>
       <c r="H97" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.86</v>
       </c>
       <c r="J97" t="n">
-        <v>0.2413793103448276</v>
+        <v>5</v>
       </c>
       <c r="K97" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.3448275862068966</v>
+      </c>
+      <c r="M97" t="n">
         <v>0.9999999999</v>
       </c>
-      <c r="L97" t="n">
+      <c r="N97" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5890,7 +7009,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>['WebSocketRoute | Playwright\n\nWhenever a\nWebSocket (https://developer.mozilla.org/en-US/docs/Web/API/WebSocket)\nroute is set up with\npage.routeWebSocket() (https://playwright.dev/docs/api/class-page#page-route-web-socket)\nor\nbrowserContext.routeWebSocket() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route-web-socket)\n, the\n`WebSocketRoute`\nobject allows to handle the WebSocket, like an actual server would do.\n\nMocking\n\nBy default, the routed WebSocket will not connect to the server. This way, you can mock entire communication over the WebSocket. Here is an example that responds to a\n`"request"`\nwith a\n`"response"`\n.\n\n```\n`awaitpage.routeWebSocket(\'wss://example.com/ws\',ws=&gt;{ws.onMessage(message=&gt;{if(message===\'request\')ws.send(\'response\');});});`\n```\n\nSince we do not call\nwebSocketRoute.connectToServer() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-connect-to-server)\ninside the WebSocket route handler, Playwright assumes that WebSocket will be mocked, and opens the WebSocket inside the page automatically.\n\nHere is another example that handles JSON messages:\n\n```\n`awaitpage.routeWebSocket(\'wss://example.com/ws\',ws=&gt;{ws.onMessage(message=&gt;{constjson=JSON.parse(message);if(json.request===\'question\')ws.send(JSON.stringify({response:\'answer\'}));});});`\n```\n\nIntercepting\n\nAlternatively, you may want to connect to the actual server, but intercept messages in-between and modify or block them. Calling\nwebSocketRoute.connectToServer() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-connect-to-server)\nreturns a server-side\n`WebSocketRoute`\ninstance that you can send messages to, or handle incoming messages.\n\nBelow is an example that modifies some messages sent by the page to the server. Messages sent from the server to the page are left intact, relying on the default forwarding.\n\n```\n`awaitpage.routeWebSocket(\'/ws\',ws=&gt;{constserver=ws.connectToServer();ws.onMessage(message=&gt;{if(message===\'request\')server.send(\'request2\');elseserver.send(message);});});`\n```\n\nAfter connecting to the server, all\nmessages are forwarded\nbetween the page and the server by default.\n\nHowever, if you call\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\non the original route, messages from the page to the server\nwill not be forwarded\nanymore, but should instead be handled by the\nhandler (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message-option-handler)\n.\n\nSimilarly, calling\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\non the server-side WebSocket will\nstop forwarding messages\nfrom the server to the page, and\nhandler (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message-option-handler)\nshould take care of them.\n\nThe following example blocks some messages in both directions. Since it calls\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\nin both directions, there is no automatic forwarding at all.\n\n```\n`awaitpage.routeWebSocket(\'/ws\',ws=&gt;{constserver=ws.connectToServer();ws.onMessage(message=&gt;{if(message!==\'blocked-from-the-page\')server.send(message);});server.onMessage(message=&gt;{if(message!==\'blocked-from-the-server\')ws.send(message);});});`\n```', 'The following code will intercept WebSocket connections and mock entire communication over the WebSocket, instead of connecting to the server. This example responds to a\n`"request"`\nwith a\n`"response"`\n.\n\n```\n`awaitpage.routeWebSocket(\'wss://example.com/ws\',ws=&gt;{ws.onMessage(message=&gt;{if(message===\'request\')ws.send(\'response\');});});`\n```\n\nAlternatively, you may want to connect to the actual server, but intercept messages in-between and modify or block them. Here is an example that modifies some of the messages sent by the page to the server, and leaves the rest unmodified.\n\n```\n`awaitpage.routeWebSocket(\'wss://example.com/ws\',ws=&gt;{constserver=ws.connectToServer();ws.onMessage(message=&gt;{if(message===\'request\')server.send(\'request2\');elseserver.send(message);});});`\n```\n\nFor more details, see\nWebSocketRoute (https://playwright.dev/docs/api/class-websocketroute)\n.', 'Mock APIs | Playwright', 'Added in: v1.48\n\nwebSocketRoute.onMessage\n\nThis method allows to handle messages that are sent by the WebSocket, either from the page or from the server.\n\nWhen called on the original WebSocket route, this method handles messages sent from the page. You can handle this messages by responding to them with\nwebSocketRoute.send() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-send)\n, forwarding them to the server-side connection returned by\nwebSocketRoute.connectToServer() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-connect-to-server)\nor do something else.\n\nOnce this method is called, messages are not automatically forwarded to the server or to the page - you should do that manually by calling\nwebSocketRoute.send() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-send)\n. See examples at the top for more details.\n\nCalling this method again will override the handler with a new one.\n\nUsage\n\n```\n`webSocketRoute.onMessage(handler);`\n```\n\nArguments\n\n`handler`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n(\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n):\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt; |\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n# (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message-option-handler)\nFunction that will handle messages.', 'Added in: v1.48\n\nwebSocketRoute.send\n\nSends a message to the WebSocket. When called on the original WebSocket, sends the message to the page. When called on the result of\nwebSocketRoute.connectToServer() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-connect-to-server)\n, sends the message to the server. See examples at the top for more details.\n\nUsage\n\n```\n`webSocketRoute.send(message);`\n```\n\nArguments\n\n`message`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\n# (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-send-option-message)\nMessage to send.', 'WebSocket | Playwright\n\nThe\nWebSocket (https://playwright.dev/docs/api/class-websocket)\nclass represents WebSocket connections within a page. It provides the ability to inspect and manipulate the data being transmitted and received.\n\nIf you want to intercept or modify WebSocket frames, consider using\nWebSocketRoute (https://playwright.dev/docs/api/class-websocketroute)\n.', 'Added in: v1.48\n\nwebSocketRoute.connectToServer\n\nBy default, routed WebSocket does not connect to the server, so you can mock entire WebSocket communication. This method connects to the actual WebSocket server, and returns the server-side\nWebSocketRoute (https://playwright.dev/docs/api/class-websocketroute)\ninstance, giving the ability to send and receive messages from the server.\n\nOnce connected to the server:\n\nMessages received from the server will be\nautomatically forwarded\nto the WebSocket in the page, unless\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\nis called on the server-side\n`WebSocketRoute`\n.\nMessages sent by the\nWebSocket.send() (https://developer.mozilla.org/en-US/docs/Web/API/WebSocket/send)\ncall in the page will be\nautomatically forwarded\nto the server, unless\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\nis called on the original\n`WebSocketRoute`\n.\n\nSee examples at the top for more details.\n\nUsage\n\n```\n`webSocketRoute.connectToServer();`\n```\n\nReturns\n\nWebSocketRoute (https://playwright.dev/docs/api/class-websocketroute)\n# (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-connect-to-server-return)']</t>
+          <t>['WebSocketRoute | Playwright\n\nWhenever a\nWebSocket (https://developer.mozilla.org/en-US/docs/Web/API/WebSocket)\nroute is set up with\npage.routeWebSocket() (https://playwright.dev/docs/api/class-page#page-route-web-socket)\nor\nbrowserContext.routeWebSocket() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route-web-socket)\n, the\n`WebSocketRoute`\nobject allows to handle the WebSocket, like an actual server would do.\n\nMocking\n\nBy default, the routed WebSocket will not connect to the server. This way, you can mock entire communication over the WebSocket. Here is an example that responds to a\n`"request"`\nwith a\n`"response"`\n.\n\n```\n`awaitpage.routeWebSocket(\'wss://example.com/ws\',ws=&gt;{ws.onMessage(message=&gt;{if(message===\'request\')ws.send(\'response\');});});`\n```\n\nSince we do not call\nwebSocketRoute.connectToServer() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-connect-to-server)\ninside the WebSocket route handler, Playwright assumes that WebSocket will be mocked, and opens the WebSocket inside the page automatically.\n\nHere is another example that handles JSON messages:\n\n```\n`awaitpage.routeWebSocket(\'wss://example.com/ws\',ws=&gt;{ws.onMessage(message=&gt;{constjson=JSON.parse(message);if(json.request===\'question\')ws.send(JSON.stringify({response:\'answer\'}));});});`\n```\n\nIntercepting\n\nAlternatively, you may want to connect to the actual server, but intercept messages in-between and modify or block them. Calling\nwebSocketRoute.connectToServer() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-connect-to-server)\nreturns a server-side\n`WebSocketRoute`\ninstance that you can send messages to, or handle incoming messages.\n\nBelow is an example that modifies some messages sent by the page to the server. Messages sent from the server to the page are left intact, relying on the default forwarding.\n\n```\n`awaitpage.routeWebSocket(\'/ws\',ws=&gt;{constserver=ws.connectToServer();ws.onMessage(message=&gt;{if(message===\'request\')server.send(\'request2\');elseserver.send(message);});});`\n```\n\nAfter connecting to the server, all\nmessages are forwarded\nbetween the page and the server by default.\n\nHowever, if you call\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\non the original route, messages from the page to the server\nwill not be forwarded\nanymore, but should instead be handled by the\nhandler (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message-option-handler)\n.\n\nSimilarly, calling\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\non the server-side WebSocket will\nstop forwarding messages\nfrom the server to the page, and\nhandler (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message-option-handler)\nshould take care of them.\n\nThe following example blocks some messages in both directions. Since it calls\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\nin both directions, there is no automatic forwarding at all.\n\n```\n`awaitpage.routeWebSocket(\'/ws\',ws=&gt;{constserver=ws.connectToServer();ws.onMessage(message=&gt;{if(message!==\'blocked-from-the-page\')server.send(message);});server.onMessage(message=&gt;{if(message!==\'blocked-from-the-server\')ws.send(message);});});`\n```', 'The following code will intercept WebSocket connections and mock entire communication over the WebSocket, instead of connecting to the server. This example responds to a\n`"request"`\nwith a\n`"response"`\n.\n\n```\n`awaitpage.routeWebSocket(\'wss://example.com/ws\',ws=&gt;{ws.onMessage(message=&gt;{if(message===\'request\')ws.send(\'response\');});});`\n```\n\nAlternatively, you may want to connect to the actual server, but intercept messages in-between and modify or block them. Here is an example that modifies some of the messages sent by the page to the server, and leaves the rest unmodified.\n\n```\n`awaitpage.routeWebSocket(\'wss://example.com/ws\',ws=&gt;{constserver=ws.connectToServer();ws.onMessage(message=&gt;{if(message===\'request\')server.send(\'request2\');elseserver.send(message);});});`\n```\n\nFor more details, see\nWebSocketRoute (https://playwright.dev/docs/api/class-websocketroute)\n.', 'Mock APIs | Playwright', 'Added in: v1.48\n\nwebSocketRoute.connectToServer\n\nBy default, routed WebSocket does not connect to the server, so you can mock entire WebSocket communication. This method connects to the actual WebSocket server, and returns the server-side\nWebSocketRoute (https://playwright.dev/docs/api/class-websocketroute)\ninstance, giving the ability to send and receive messages from the server.\n\nOnce connected to the server:\n\nMessages received from the server will be\nautomatically forwarded\nto the WebSocket in the page, unless\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\nis called on the server-side\n`WebSocketRoute`\n.\nMessages sent by the\nWebSocket.send() (https://developer.mozilla.org/en-US/docs/Web/API/WebSocket/send)\ncall in the page will be\nautomatically forwarded\nto the server, unless\nwebSocketRoute.onMessage() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message)\nis called on the original\n`WebSocketRoute`\n.\n\nSee examples at the top for more details.\n\nUsage\n\n```\n`webSocketRoute.connectToServer();`\n```\n\nReturns\n\nWebSocketRoute (https://playwright.dev/docs/api/class-websocketroute)\n# (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-connect-to-server-return)', 'Added in: v1.48\n\nwebSocketRoute.onMessage\n\nThis method allows to handle messages that are sent by the WebSocket, either from the page or from the server.\n\nWhen called on the original WebSocket route, this method handles messages sent from the page. You can handle this messages by responding to them with\nwebSocketRoute.send() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-send)\n, forwarding them to the server-side connection returned by\nwebSocketRoute.connectToServer() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-connect-to-server)\nor do something else.\n\nOnce this method is called, messages are not automatically forwarded to the server or to the page - you should do that manually by calling\nwebSocketRoute.send() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-send)\n. See examples at the top for more details.\n\nCalling this method again will override the handler with a new one.\n\nUsage\n\n```\n`webSocketRoute.onMessage(handler);`\n```\n\nArguments\n\n`handler`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n(\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n):\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt; |\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n# (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-on-message-option-handler)\nFunction that will handle messages.', 'Added in: v1.48\n\nwebSocketRoute.send\n\nSends a message to the WebSocket. When called on the original WebSocket, sends the message to the page. When called on the result of\nwebSocketRoute.connectToServer() (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-connect-to-server)\n, sends the message to the server. See examples at the top for more details.\n\nUsage\n\n```\n`webSocketRoute.send(message);`\n```\n\nArguments\n\n`message`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\n# (https://playwright.dev/docs/api/class-websocketroute#web-socket-route-send-option-message)\nMessage to send.', 'WebSocket | Playwright\n\nThe\nWebSocket (https://playwright.dev/docs/api/class-websocket)\nclass represents WebSocket connections within a page. It provides the ability to inspect and manipulate the data being transmitted and received.\n\nIf you want to intercept or modify WebSocket frames, consider using\nWebSocketRoute (https://playwright.dev/docs/api/class-websocketroute)\n.']</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5900,9 +7019,10 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Yes, it is possible. You can mock the entire WebSocket communication by using `page.routeWebSocket()` or `browserContext.routeWebSocket()`. 
-By default, when you route a WebSocket, it will not connect to the actual server. If you do not call `webSocketRoute.connectToServer()` inside the route handler, Playwright assumes the WebSocket is being mocked and opens it inside the page automatically. You can then use `ws.onMessage()` to handle incoming messages and `ws.send()` to respond to them.
-For example:
+          <t>Yes, it is possible to fake the entire WebSocket communication without a real server.
+By default, when you set up a WebSocket route using `page.routeWebSocket()` or `browserContext.routeWebSocket()`, Playwright does not connect to the actual server. Because `webSocketRoute.connectToServer()` is not called, Playwright assumes the WebSocket is being mocked and automatically opens it within the page.
+To mock the communication, use `ws.onMessage()` to listen for messages from the page and `ws.send()` to respond to them.
+**Example of mocking communication:**
 ```javascript
 await page.routeWebSocket('wss://example.com/ws', ws =&gt; {
   ws.onMessage(message =&gt; {
@@ -5911,6 +7031,17 @@
     }
   });
 });
+```
+**Example of mocking JSON communication:**
+```javascript
+await page.routeWebSocket('wss://example.com/ws', ws =&gt; {
+  ws.onMessage(message =&gt; {
+    const json = JSON.parse(message);
+    if (json.request === 'question') {
+      ws.send(JSON.stringify({ response: 'answer' }));
+    }
+  });
+});
 ```</t>
         </is>
       </c>
@@ -5920,24 +7051,30 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>0.008770749999999</v>
       </c>
       <c r="G98" t="n">
-        <v>0.6</v>
+        <v>32888</v>
       </c>
       <c r="H98" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1263157894736842</v>
+        <v>0.57</v>
       </c>
       <c r="J98" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="K98" t="n">
-        <v>0.9761904761742063</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L98" t="n">
+        <v>0.3666666666666666</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.9999999999833333</v>
+      </c>
+      <c r="N98" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5949,7 +7086,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>['Sharding | Playwright', "In the previous example, each test shard has its own test report. If you want to have a combined report showing all the test results from all the shards, you can merge them.\n\nStart with adding\n`blob`\nreporter to the config when running on CI:\n\nplaywright.config.ts\n```\n`exportdefaultdefineConfig({testDir:'./tests',reporter:process.env.CI?'blob':'html',});`\n```\n\nBlob report contains information about all the tests that were run and their results as well as all test attachments such as traces and screenshot diffs. Blob reports can be merged and converted to any other Playwright report. By default, blob report will be generated into\n`blob-report`\ndirectory. You can learn about\nblob report options here (https://playwright.dev/docs/test-reporters#blob-reporter)\n.\n\nTo merge reports from multiple shards, put the blob report files into a single directory, for example\n`all-blob-reports`\n. Blob report names contain shard number, so they will not clash.\n\nAfterwards, run\n`npx playwright merge-reports`\ncommand:\n\n```\n`npx playwright merge-reports--reporterhtml ./all-blob-reports`\n```\n\nThis will produce a standard HTML report into\n`playwright-report`\ndirectory.", "`npx playwright merge-reports path/to/blob-reports-dir`\nreads all blob reports from the passed directory and merges them into a single report.\n\nWhen merging reports from different OS'es you'll have to provide an explicit merge config to disambiguate which directory should be used as tests root.\n\nSupported options:\n\n`--reporter reporter-to-use`\nWhich report to produce. Can be multiple reporters separated by comma.\nExample:\n```\n`npx playwright merge-reports--reporter=html,github ./blob-reports`\n```\n`--config path/to/config/file`\nSpecifies the Playwright configuration file with output reporters. Use this option to pass additional configuration to the output reporter. This configuration file can differ from the one used during the creation of blob reports.\nExample:\n```\n`npx playwright merge-reports--config=merge.config.ts ./blob-reports`\n```\nmerge.config.ts\n```\n`exportdefault{testDir:'e2e',reporter:[['html',{open:'never'}]],};`\n```", 'Read\nblob (https://playwright.dev/docs/test-reporters#blob-reporter)\nreports and combine them.\nRead more about merge-reports (https://playwright.dev/docs/test-sharding)\n.', '```\n`# Combine test reportsnpx playwright merge-reports ./reports`\n```', "Reporter | Playwright\n\nTest runner notifies the reporter about various events during test execution. All methods of the reporter are optional.\n\nYou can create a custom reporter by implementing a class with some of the reporter methods. Make sure to export this class as default.\n\nTypeScript\nJavaScript\nmy-awesome-reporter.ts\n```\n`importtype{Reporter,FullConfig,Suite,TestCase,TestResult,FullResult}from'@playwright/test/reporter';classMyReporterimplementsReporter{constructor(options:{customOption?:string}={}){console.log(`my-awesome-reporter setup with customOption set to${options.customOption}`);}onBegin(config:FullConfig,suite:Suite){console.log(`Starting the run with${suite.allTests().length}tests`);}onTestBegin(test:TestCase){console.log(`Starting test${test.title}`);}onTestEnd(test:TestCase,result:TestResult){console.log(`Finished test${test.title}:${result.status}`);}onEnd(result:FullResult){console.log(`Finished the run:${result.status}`);}}exportdefaultMyReporter;`\n```\nmy-awesome-reporter.js\n```\n`// @ts-check/**@implements{import('@playwright/test/reporter').Reporter}*/classMyReporter{constructor(options){console.log(`my-awesome-reporter setup with customOption set to${options.customOption}`);}onBegin(config,suite){console.log(`Starting the run with${suite.allTests().length}tests`);}onTestBegin(test){console.log(`Starting test${test.title}`);}onTestEnd(test,result){console.log(`Finished test${test.title}:${result.status}`);}onEnd(result){console.log(`Finished the run:${result.status}`);}}module.exports=MyReporter;`\n```\n\nNow use this reporter with\ntestConfig.reporter (https://playwright.dev/docs/api/class-testconfig#test-config-reporter)\n. Learn more about\nusing reporters (https://playwright.dev/docs/test-reporters)\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({reporter:[['./my-awesome-reporter.ts',{customOption:'some value'}]],});`\n```\n\nHere is a typical order of reporter calls:\n\nreporter.onBegin() (https://playwright.dev/docs/api/class-reporter#reporter-on-begin)\nis called once with a root suite that contains all other suites and tests. Learn more about\nsuites hierarchy (https://playwright.dev/docs/api/class-suite)\n.\nreporter.onTestBegin() (https://playwright.dev/docs/api/class-reporter#reporter-on-test-begin)\nis called for each test run. It is given a\nTestCase (https://playwright.dev/docs/api/class-testcase)\nthat is executed, and a\nTestResult (https://playwright.dev/docs/api/class-testresult)\nthat is almost empty. Test result will be populated while the test runs (for example, with steps and stdio) and will get final\n`status`\nonce the test finishes.\nreporter.onStepBegin() (https://playwright.dev/docs/api/class-reporter#reporter-on-step-begin)\nand\nreporter.onStepEnd() (https://playwright.dev/docs/api/class-reporter#reporter-on-step-end)\nare called for each executed step inside the test. When steps are executed, test run has not finished yet.\nreporter.onTestEnd() (https://playwright.dev/docs/api/class-reporter#reporter-on-test-end)\nis called when test run has finished. By this time,\nTestResult (https://playwright.dev/docs/api/class-testresult)\nis complete and you can use\ntestResult.status (https://playwright.dev/docs/api/class-testresult#test-result-status)\n,\ntestResult.error (https://playwright.dev/docs/api/class-testresult#test-result-error)\nand more.\nreporter.onEnd() (https://playwright.dev/docs/api/class-reporter#reporter-on-end)\nis called once after all tests that should run had finished.\nreporter.onExit() (https://playwright.dev/docs/api/class-reporter#reporter-on-exit)\nis called immediately before the test runner exits.\n\nAdditionally,\nreporter.onStdOut() (https://playwright.dev/docs/api/class-reporter#reporter-on-std-out)\nand\nreporter.onStdErr() (https://playwright.dev/docs/api/class-reporter#reporter-on-std-err)\nare called when standard output is produced in the worker process, possibly during a test execution, and\nreporter.onError() (https://playwright.dev/docs/api/class-reporter#reporter-on-error)\nis called when something went wrong outside of the test execution.\n\nIf your custom reporter does not print anything to the terminal, implement\nreporter.printsToStdio() (https://playwright.dev/docs/api/class-reporter#reporter-prints-to-stdio)\nand return\n`false`\n. This way, Playwright will use one of the standard terminal reporters in addition to your custom reporter to enhance user experience.\n\nReporter errors\n\nPlaywright will swallow any errors thrown in your custom reporter methods. If you need to detect or fail on reporter errors, you must wrap and handle them yourself.\n\nMerged report API notes\n\nWhen merging multiple\nblob (https://playwright.dev/docs/test-reporters#blob-reporter)\nreports via\nmerge-reports (https://playwright.dev/docs/test-sharding#merge-reports-cli)\nCLI command, the same\nReporter (https://playwright.dev/docs/api/class-reporter)\nAPI is called to produce final reports and all existing reporters should work without any changes. There some subtle differences though which might affect some custom reporters.\n\nProjects from different shards are always kept as separate\nTestProject (https://playwright.dev/docs/api/class-testproject)\nobjects. E.g. if project 'Desktop Chrome' was sharded across 5 machines then there will be 5 instances of projects with the same name in the config passed to\nreporter.onBegin() (https://playwright.dev/docs/api/class-reporter#reporter-on-begin)\n.", "GitHub Actions supports\nsharding tests between multiple jobs (https://docs.github.com/en/actions/using-jobs/using-a-matrix-for-your-jobs)\nusing the\njobs.&lt;job_id&gt;.strategy.matrix (https://docs.github.com/en/actions/using-workflows/workflow-syntax-for-github-actions#jobsjob_idstrategymatrix)\noption. The\n`matrix`\noption will run a separate job for every possible combination of the provided options.\n\nThe following example shows you how to configure a job to run your tests on four machines in parallel and then merge the reports into a single report. Don't forget to add\n`reporter: process.env.CI ? 'blob' : 'html',`\nto your\n`playwright.config.ts`\nfile as in the example above.\n\nFirst we add a\n`matrix`\noption to our job configuration with the\n`shardTotal: [4]`\noption containing the total number of shards we want to create and\n`shardIndex: [1, 2, 3, 4]`\nwith an array of the shard numbers.\nThen we run our Playwright tests with the\n`--shard=${{ matrix.shardIndex }}/${{ matrix.shardTotal }}`\noption. This will run our test command for each shard.\nFinally we upload our blob report to the GitHub Actions Artifacts. This will make the blob report available to other jobs in the workflow.\n\n.github/workflows/playwright.yml\n```\n`name:Playwright Testson:push:branches:[main,master]pull_request:branches:[main,master]jobs:playwright-tests:timeout-minutes:60runs-on:ubuntu-lateststrategy:fail-fast:falsematrix:shardIndex:[1,2,3,4]shardTotal:[4]steps:-uses:actions/checkout@v5-uses:actions/setup-node@v5with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Install Playwright browsersrun:npx playwright install--with-deps-name:Run Playwright testsrun:npx playwright test--shard=${{matrix.shardIndex}}/${{matrix.shardTotal}}-name:Upload blob report to GitHub Actions Artifactsif:${{!cancelled()}}uses:actions/upload-artifact@v4with:name:blob-report-${{matrix.shardIndex}}path:blob-reportretention-days:1`\n```\n\nAfter all shards have completed, you can run a separate job that will merge the reports and produce a combined\nHTML report (https://playwright.dev/docs/test-reporters#html-reporter)\n. To ensure the execution order, we make the\n`merge-reports`\njob\ndepend (https://docs.github.com/en/actions/using-jobs/using-jobs-in-a-workflow#defining-prerequisite-jobs)\non our sharded\n`playwright-tests`\njob by adding\n`needs: [playwright-tests]`\n.\n\n.github/workflows/playwright.yml\n```\n`jobs:...merge-reports:# Merge reports after playwright-tests, even if some shards have failedif:${{!cancelled()}}needs:[playwright-tests]runs-on:ubuntu-lateststeps:-uses:actions/checkout@v5-uses:actions/setup-node@v5with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Download blob reports from GitHub Actions Artifactsuses:actions/download-artifact@v5with:path:all-blob-reportspattern:blob-report-*merge-multiple:true-name:Merge into HTML Reportrun:npx playwright merge-reports--reporter html ./all-blob-reports-name:Upload HTML reportuses:actions/upload-artifact@v4with:name:html-report--attempt-${{github.run_attempt}}path:playwright-reportretention-days:14`\n```\n\nYou can now see the reports have been merged and a combined HTML report is available in the GitHub Actions Artifacts tab."]</t>
+          <t>['Sharding | Playwright', "GitHub Actions supports\nsharding tests between multiple jobs (https://docs.github.com/en/actions/using-jobs/using-a-matrix-for-your-jobs)\nusing the\njobs.&lt;job_id&gt;.strategy.matrix (https://docs.github.com/en/actions/using-workflows/workflow-syntax-for-github-actions#jobsjob_idstrategymatrix)\noption. The\n`matrix`\noption will run a separate job for every possible combination of the provided options.\n\nThe following example shows you how to configure a job to run your tests on four machines in parallel and then merge the reports into a single report. Don't forget to add\n`reporter: process.env.CI ? 'blob' : 'html',`\nto your\n`playwright.config.ts`\nfile as in the example above.\n\nFirst we add a\n`matrix`\noption to our job configuration with the\n`shardTotal: [4]`\noption containing the total number of shards we want to create and\n`shardIndex: [1, 2, 3, 4]`\nwith an array of the shard numbers.\nThen we run our Playwright tests with the\n`--shard=${{ matrix.shardIndex }}/${{ matrix.shardTotal }}`\noption. This will run our test command for each shard.\nFinally we upload our blob report to the GitHub Actions Artifacts. This will make the blob report available to other jobs in the workflow.\n\n.github/workflows/playwright.yml\n```\n`name:Playwright Testson:push:branches:[main,master]pull_request:branches:[main,master]jobs:playwright-tests:timeout-minutes:60runs-on:ubuntu-lateststrategy:fail-fast:falsematrix:shardIndex:[1,2,3,4]shardTotal:[4]steps:-uses:actions/checkout@v5-uses:actions/setup-node@v5with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Install Playwright browsersrun:npx playwright install--with-deps-name:Run Playwright testsrun:npx playwright test--shard=${{matrix.shardIndex}}/${{matrix.shardTotal}}-name:Upload blob report to GitHub Actions Artifactsif:${{!cancelled()}}uses:actions/upload-artifact@v4with:name:blob-report-${{matrix.shardIndex}}path:blob-reportretention-days:1`\n```\n\nAfter all shards have completed, you can run a separate job that will merge the reports and produce a combined\nHTML report (https://playwright.dev/docs/test-reporters#html-reporter)\n. To ensure the execution order, we make the\n`merge-reports`\njob\ndepend (https://docs.github.com/en/actions/using-jobs/using-jobs-in-a-workflow#defining-prerequisite-jobs)\non our sharded\n`playwright-tests`\njob by adding\n`needs: [playwright-tests]`\n.\n\n.github/workflows/playwright.yml\n```\n`jobs:...merge-reports:# Merge reports after playwright-tests, even if some shards have failedif:${{!cancelled()}}needs:[playwright-tests]runs-on:ubuntu-lateststeps:-uses:actions/checkout@v5-uses:actions/setup-node@v5with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Download blob reports from GitHub Actions Artifactsuses:actions/download-artifact@v5with:path:all-blob-reportspattern:blob-report-*merge-multiple:true-name:Merge into HTML Reportrun:npx playwright merge-reports--reporter html ./all-blob-reports-name:Upload HTML reportuses:actions/upload-artifact@v4with:name:html-report--attempt-${{github.run_attempt}}path:playwright-reportretention-days:14`\n```\n\nYou can now see the reports have been merged and a combined HTML report is available in the GitHub Actions Artifacts tab.", "Reporter | Playwright\n\nTest runner notifies the reporter about various events during test execution. All methods of the reporter are optional.\n\nYou can create a custom reporter by implementing a class with some of the reporter methods. Make sure to export this class as default.\n\nTypeScript\nJavaScript\nmy-awesome-reporter.ts\n```\n`importtype{Reporter,FullConfig,Suite,TestCase,TestResult,FullResult}from'@playwright/test/reporter';classMyReporterimplementsReporter{constructor(options:{customOption?:string}={}){console.log(`my-awesome-reporter setup with customOption set to${options.customOption}`);}onBegin(config:FullConfig,suite:Suite){console.log(`Starting the run with${suite.allTests().length}tests`);}onTestBegin(test:TestCase){console.log(`Starting test${test.title}`);}onTestEnd(test:TestCase,result:TestResult){console.log(`Finished test${test.title}:${result.status}`);}onEnd(result:FullResult){console.log(`Finished the run:${result.status}`);}}exportdefaultMyReporter;`\n```\nmy-awesome-reporter.js\n```\n`// @ts-check/**@implements{import('@playwright/test/reporter').Reporter}*/classMyReporter{constructor(options){console.log(`my-awesome-reporter setup with customOption set to${options.customOption}`);}onBegin(config,suite){console.log(`Starting the run with${suite.allTests().length}tests`);}onTestBegin(test){console.log(`Starting test${test.title}`);}onTestEnd(test,result){console.log(`Finished test${test.title}:${result.status}`);}onEnd(result){console.log(`Finished the run:${result.status}`);}}module.exports=MyReporter;`\n```\n\nNow use this reporter with\ntestConfig.reporter (https://playwright.dev/docs/api/class-testconfig#test-config-reporter)\n. Learn more about\nusing reporters (https://playwright.dev/docs/test-reporters)\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({reporter:[['./my-awesome-reporter.ts',{customOption:'some value'}]],});`\n```\n\nHere is a typical order of reporter calls:\n\nreporter.onBegin() (https://playwright.dev/docs/api/class-reporter#reporter-on-begin)\nis called once with a root suite that contains all other suites and tests. Learn more about\nsuites hierarchy (https://playwright.dev/docs/api/class-suite)\n.\nreporter.onTestBegin() (https://playwright.dev/docs/api/class-reporter#reporter-on-test-begin)\nis called for each test run. It is given a\nTestCase (https://playwright.dev/docs/api/class-testcase)\nthat is executed, and a\nTestResult (https://playwright.dev/docs/api/class-testresult)\nthat is almost empty. Test result will be populated while the test runs (for example, with steps and stdio) and will get final\n`status`\nonce the test finishes.\nreporter.onStepBegin() (https://playwright.dev/docs/api/class-reporter#reporter-on-step-begin)\nand\nreporter.onStepEnd() (https://playwright.dev/docs/api/class-reporter#reporter-on-step-end)\nare called for each executed step inside the test. When steps are executed, test run has not finished yet.\nreporter.onTestEnd() (https://playwright.dev/docs/api/class-reporter#reporter-on-test-end)\nis called when test run has finished. By this time,\nTestResult (https://playwright.dev/docs/api/class-testresult)\nis complete and you can use\ntestResult.status (https://playwright.dev/docs/api/class-testresult#test-result-status)\n,\ntestResult.error (https://playwright.dev/docs/api/class-testresult#test-result-error)\nand more.\nreporter.onEnd() (https://playwright.dev/docs/api/class-reporter#reporter-on-end)\nis called once after all tests that should run had finished.\nreporter.onExit() (https://playwright.dev/docs/api/class-reporter#reporter-on-exit)\nis called immediately before the test runner exits.\n\nAdditionally,\nreporter.onStdOut() (https://playwright.dev/docs/api/class-reporter#reporter-on-std-out)\nand\nreporter.onStdErr() (https://playwright.dev/docs/api/class-reporter#reporter-on-std-err)\nare called when standard output is produced in the worker process, possibly during a test execution, and\nreporter.onError() (https://playwright.dev/docs/api/class-reporter#reporter-on-error)\nis called when something went wrong outside of the test execution.\n\nIf your custom reporter does not print anything to the terminal, implement\nreporter.printsToStdio() (https://playwright.dev/docs/api/class-reporter#reporter-prints-to-stdio)\nand return\n`false`\n. This way, Playwright will use one of the standard terminal reporters in addition to your custom reporter to enhance user experience.\n\nReporter errors\n\nPlaywright will swallow any errors thrown in your custom reporter methods. If you need to detect or fail on reporter errors, you must wrap and handle them yourself.\n\nMerged report API notes\n\nWhen merging multiple\nblob (https://playwright.dev/docs/test-reporters#blob-reporter)\nreports via\nmerge-reports (https://playwright.dev/docs/test-sharding#merge-reports-cli)\nCLI command, the same\nReporter (https://playwright.dev/docs/api/class-reporter)\nAPI is called to produce final reports and all existing reporters should work without any changes. There some subtle differences though which might affect some custom reporters.\n\nProjects from different shards are always kept as separate\nTestProject (https://playwright.dev/docs/api/class-testproject)\nobjects. E.g. if project 'Desktop Chrome' was sharded across 5 machines then there will be 5 instances of projects with the same name in the config passed to\nreporter.onBegin() (https://playwright.dev/docs/api/class-reporter#reporter-on-begin)\n.", "`npx playwright merge-reports path/to/blob-reports-dir`\nreads all blob reports from the passed directory and merges them into a single report.\n\nWhen merging reports from different OS'es you'll have to provide an explicit merge config to disambiguate which directory should be used as tests root.\n\nSupported options:\n\n`--reporter reporter-to-use`\nWhich report to produce. Can be multiple reporters separated by comma.\nExample:\n```\n`npx playwright merge-reports--reporter=html,github ./blob-reports`\n```\n`--config path/to/config/file`\nSpecifies the Playwright configuration file with output reporters. Use this option to pass additional configuration to the output reporter. This configuration file can differ from the one used during the creation of blob reports.\nExample:\n```\n`npx playwright merge-reports--config=merge.config.ts ./blob-reports`\n```\nmerge.config.ts\n```\n`exportdefault{testDir:'e2e',reporter:[['html',{open:'never'}]],};`\n```", "In the previous example, each test shard has its own test report. If you want to have a combined report showing all the test results from all the shards, you can merge them.\n\nStart with adding\n`blob`\nreporter to the config when running on CI:\n\nplaywright.config.ts\n```\n`exportdefaultdefineConfig({testDir:'./tests',reporter:process.env.CI?'blob':'html',});`\n```\n\nBlob report contains information about all the tests that were run and their results as well as all test attachments such as traces and screenshot diffs. Blob reports can be merged and converted to any other Playwright report. By default, blob report will be generated into\n`blob-report`\ndirectory. You can learn about\nblob report options here (https://playwright.dev/docs/test-reporters#blob-reporter)\n.\n\nTo merge reports from multiple shards, put the blob report files into a single directory, for example\n`all-blob-reports`\n. Blob report names contain shard number, so they will not clash.\n\nAfterwards, run\n`npx playwright merge-reports`\ncommand:\n\n```\n`npx playwright merge-reports--reporterhtml ./all-blob-reports`\n```\n\nThis will produce a standard HTML report into\n`playwright-report`\ndirectory.", 'Reporters | Playwright', 'Command line | Playwright\n\nPlaywright provides a powerful command line interface for running tests, generating code, debugging, and more. The most up to date list of commands and arguments available on the CLI can always be retrieved via\n`npx playwright --help`\n.']</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5959,22 +7096,26 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>To combine reports from multiple sharded CI jobs, follow this workflow:
-1.  **Configure the Blob Reporter:** Update your `playwright.config.ts` to use the `blob` reporter when running on CI:
-    ```typescript
-    reporter: process.env.CI ? 'blob' : 'html',
-    ```
-2.  **Generate Blob Reports:** Run your tests with the `--shard` option. Each shard will generate a blob report in the `blob-report` directory.
-3.  **Collect Reports:** Ensure all blob report files are gathered into a single directory (e.g., `all-blob-reports`).
-4.  **Merge Reports:** Run the following command to merge the files and generate a combined report:
+          <t>To combine reports from sharded CI jobs, follow this workflow:
+### 1. Configure the Blob Reporter
+In your `playwright.config.ts`, set the reporter to use the `blob` reporter when running in CI:
+```typescript
+reporter: process.env.CI ? 'blob' : 'html',
+```
+### 2. Generate Blob Reports in CI
+Run your tests using the `--shard` option. Ensure each shard uploads its generated `blob-report` directory as a CI artifact. 
+Example configuration for a GitHub Actions job:
+*   **Run tests:** `npx playwright test --shard=${{ matrix.shardIndex }}/${{ matrix.shardTotal }}`
+*   **Upload artifacts:** Use `actions/upload-artifact@v4` to upload the `blob-report` directory for each shard.
+### 3. Merge Reports
+Create a separate CI job that runs after all test shards have completed. This job must:
+1.  **Download artifacts:** Use `actions/download-artifact@v5` to download all blob reports into a single directory (e.g., `all-blob-reports`). Set `merge-multiple: true` to combine them.
+2.  **Merge:** Run the `merge-reports` command:
     ```bash
     npx playwright merge-reports --reporter html ./all-blob-reports
     ```
-    This will produce a standard HTML report in the `playwright-report` directory.
-If you are using **GitHub Actions**, the workflow involves:
-*   Using a `matrix` strategy to run shards in parallel.
-*   Uploading the `blob-report` directory as an artifact for each shard.
-*   Creating a separate "merge" job that `needs` the test jobs, downloads all artifacts into a single directory, runs the `npx playwright merge-reports` command, and uploads the resulting HTML report.</t>
+3.  **Upload final report:** Upload the resulting `playwright-report` directory as an artifact.
+**Note:** To ensure the merge job runs only after the tests finish, use the `needs` keyword in your workflow configuration (e.g., `needs: [playwright-tests]`). If merging reports from different operating systems, you must provide an explicit merge config using the `--config` option to disambiguate the test root directory.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5983,24 +7124,30 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>0.008950999999999999</v>
       </c>
       <c r="G99" t="n">
-        <v>0.18</v>
+        <v>32794</v>
       </c>
       <c r="H99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1590909090909091</v>
+        <v>0.57</v>
       </c>
       <c r="J99" t="n">
+        <v>5</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.1244444444444444</v>
+      </c>
+      <c r="L99" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="K99" t="n">
-        <v>0.6595238095106191</v>
-      </c>
-      <c r="L99" t="n">
+      <c r="M99" t="n">
+        <v>0.7099999999858</v>
+      </c>
+      <c r="N99" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6012,7 +7159,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>['API testing | Playwright', "The following test creates a new issue via API and then navigates to the list of all issues in the project to check that it appears at the top of the list.\n\n```\n`import{test,expect}from'@playwright/test';constREPO='test-repo-1';constUSER='github-username';// Request context is reused by all tests in the file.letapiContext;test.beforeAll(async({playwright})=&gt;{apiContext=awaitplaywright.request.newContext({// All requests we send go to this API endpoint.baseURL:'https://api.github.com',extraHTTPHeaders:{// We set this header per GitHub guidelines.'Accept':'application/vnd.github.v3+json',// Add authorization token to all requests.// Assuming personal access token available in the environment.'Authorization':`token${process.env.API_TOKEN}`,},});});test.afterAll(async({})=&gt;{// Dispose all responses.awaitapiContext.dispose();});test('last created issue should be first in the list',async({page})=&gt;{constnewIssue=awaitapiContext.post(`/repos/${USER}/${REPO}/issues`,{data:{title:'[Feature] request 1',}});expect(newIssue.ok()).toBeTruthy();awaitpage.goto(`https://github.com/${USER}/${REPO}/issues`);constfirstIssue=page.locator(`a[data-hovercard-type='issue']`).first();awaitexpect(firstIssue).toHaveText('[Feature] request 1');});`\n```", 'APIRequestContext | Playwright\n\nThis API is used for the Web API testing. You can use it to trigger API endpoints, configure micro-services, prepare environment or the service to your e2e test.\n\nEach Playwright browser context has an associated\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n, accessible via\nbrowserContext.request (https://playwright.dev/docs/api/class-browsercontext#browser-context-request)\nor\npage.request (https://playwright.dev/docs/api/class-page#page-request)\n(these return the\n\nsame instance\n—\n`page.request`\nis a shortcut for\n`page.context().request`\n). You can also create a standalone, isolated instance with\napiRequest.newContext() (https://playwright.dev/docs/api/class-apirequest#api-request-new-context)\n.\n\nCookie management\n\nThe\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nreturned by\nbrowserContext.request (https://playwright.dev/docs/api/class-browsercontext#browser-context-request)\nand\n\npage.request (https://playwright.dev/docs/api/class-page#page-request)\nuses the same cookie jar as its\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\n:\n\nIf you want API requests that do\nnot\nshare cookies with the browser, create an isolated context via\napiRequest.newContext() (https://playwright.dev/docs/api/class-apirequest#api-request-new-context)\n. Such\n`APIRequestContext`\nobject will have its own isolated cookie storage.', 'While running tests inside browsers you may want to make calls to the HTTP API of your application. It may be helpful if you need to prepare server state before running a test or to check some postconditions on the server after performing some actions in the browser. All of that could be achieved via\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nmethods.', "Fixtures | Playwright\n\nPlaywright Test is based on the concept of the\ntest fixtures (https://playwright.dev/docs/test-fixtures)\n. Test fixtures are used to establish environment for each test, giving the test everything it needs and nothing else.\n\nPlaywright Test looks at each test declaration, analyses the set of fixtures the test needs and prepares those fixtures specifically for the test. Values prepared by the fixtures are merged into a single object that is available to the\n`test`\n, hooks, annotations and other fixtures as a first parameter.\n\n```\n`import{test,expect}from'@playwright/test';test('basic test',async({page})=&gt;{// ...});`\n```\n\nGiven the test above, Playwright Test will set up the\n`page`\nfixture before running the test, and tear it down after the test has finished.\n`page`\nfixture provides a\nPage (https://playwright.dev/docs/api/class-page)\nobject that is available to the test.\n\nPlaywright Test comes with builtin fixtures listed below, and you can add your own fixtures as well. Playwright Test also\nprovides options (https://playwright.dev/docs/api/class-testoptions)\nto  configure\nfixtures.browser (https://playwright.dev/docs/api/class-fixtures#fixtures-browser)\n,\nfixtures.context (https://playwright.dev/docs/api/class-fixtures#fixtures-context)\nand\nfixtures.page (https://playwright.dev/docs/api/class-fixtures#fixtures-page)\n.", 'Playwright can be used to get access to the\nREST (https://en.wikipedia.org/wiki/Representational_state_transfer)\nAPI of your application.\n\nSometimes you may want to send requests to the server directly from Node.js without loading a page and running js code in it. A few examples where it may come in handy:\n\nTest your server API.\nPrepare server side state before visiting the web application in a test.\nValidate server side post-conditions after running some actions in the browser.\n\nAll of that could be achieved via\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nmethods.', "Added in: v1.16\n\napiRequestContext.post\n\nSends HTTP(S)\nPOST (https://developer.mozilla.org/en-US/docs/Web/HTTP/Methods/POST)\nrequest and returns its response. The method will populate request cookies from the context and update context cookies from the response. The method will automatically follow redirects.\n\nUsage\n\nJSON objects can be passed directly to the request:\n\n```\n`awaitrequest.post('https://example.com/api/createBook',{data:{title:'Book Title',author:'John Doe',}});`\n```\n\nTo send form data to the server use\n`form`\noption. Its value will be encoded into the request body with\n`application/x-www-form-urlencoded`\nencoding (see below how to use\n`multipart/form-data`\nform encoding to send files):\n\n```\n`awaitrequest.post('https://example.com/api/findBook',{form:{title:'Book Title',author:'John Doe',}});`\n```\n\nThe common way to send file(s) in the body of a request is to upload them as form fields with\n`multipart/form-data`\nencoding. Use\nFormData (https://developer.mozilla.org/en-US/docs/Web/API/FormData)\nto construct request body and pass it to the request as\n`multipart`\nparameter:\n\n```\n`constform=newFormData();form.set('name','John');form.append('name','Doe');// Send two file fields with the same name.form.append('file',newFile(['console.log(2024);'],'f1.js',{type:'text/javascript'}));form.append('file',newFile(['hello'],'f2.txt',{type:'text/plain'}));awaitrequest.post('https://example.com/api/uploadForm',{multipart:form});`\n```\n\nArguments\n\n`url`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-post-option-url)\nTarget URL.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`data`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\n|\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n(optional)\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-post-option-data)\nAllows to set post data of the request. If the data parameter is an object, it will be serialized to json string and\n`content-type`\nheader will be set to\n`application/json`\nif not explicitly set. Otherwise the\n`content-type`\nheader will be set to\n`application/octet-stream`\nif not explicitly set.\n`failOnStatusCode`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-post-option-fail-on-status-code)\nWhether to throw on response codes other than 2xx and 3xx. By default response object is returned for all status codes.\n`form`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n,\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n|\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n&gt; |\nFormData (https://developer.mozilla.org/en-US/docs/Web/API/FormData)\n(optional)\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-post-option-form)\nProvides an object that will be serialized as html form using\n`application/x-www-form-urlencoded`\nencoding and sent as this request body. If this parameter is specified\n`content-type`\nheader will be set to\n`application/x-www-form-urlencoded`\nunless explicitly provided.\n`headers`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n,\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n(optional)\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-post-option-headers)\nAllows to set HTTP headers. These headers will apply to the fetched request as well as any redirects initiated by it.\n`ignoreHTTPSErrors`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-post-option-ignore-https-errors)\nWhether to ignore HTTPS errors when sending network requests. Defaults to\n`false`\n.\n`maxRedirects`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.26\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-post-option-max-redirects)\nMaximum number of request redirects that will be followed automatically. An error will be thrown if the number is exceeded. Defaults to\n`20`\n. Pass\n`0`\nto not follow redirects.\n`maxRetries`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.46\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-post-option-max-retries)\nMaximum number of times network errors should be retried. Currently only\n`ECONNRESET`\nerror is retried. Does not retry based on HTTP response codes. An error will be thrown if the limit is exceeded. Defaults to\n`0`\n- no retries.\n`multipart`\nFormData (https://developer.mozilla.org/en-US/docs/Web/API/FormData)\n|\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n,\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n|\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n|\nReadStream (https://nodejs.org/api/fs.html#class-fsreadstream)\n|\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n(optional)\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-post-option-multipart)\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\nFile name\n`mimeType`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\nFile type\n`buffer`\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\nFile content\nProvides an object that will be serialized as html form using\n`multipart/form-data`\nencoding and sent as this request body. If this parameter is specified\n`content-type`\nheader will be set to\n`multipart/form-data`\nunless explicitly provided. File values can be passed either as\nfs.ReadStream (https://nodejs.org/api/fs.html#fs_class_fs_readstream)\nor as file-like object containing file name, mime-type and its content.\n`params`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n,\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n|\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n&gt; |\nURLSearchParams (https://developer.mozilla.org/en-US/docs/Web/API/URLSearchParams)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-post-option-params)\nQuery parameters to be sent with the URL.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-post-option-timeout)\nRequest timeout in milliseconds. Defaults to\n`30000`\n(30 seconds). Pass\n`0`\nto disable timeout.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nAPIResponse (https://playwright.dev/docs/api/class-apiresponse)\n&gt;\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-post-return)"]</t>
+          <t>['While running tests inside browsers you may want to make calls to the HTTP API of your application. It may be helpful if you need to prepare server state before running a test or to check some postconditions on the server after performing some actions in the browser. All of that could be achieved via\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nmethods.', "The following test creates a new issue via API and then navigates to the list of all issues in the project to check that it appears at the top of the list.\n\n```\n`import{test,expect}from'@playwright/test';constREPO='test-repo-1';constUSER='github-username';// Request context is reused by all tests in the file.letapiContext;test.beforeAll(async({playwright})=&gt;{apiContext=awaitplaywright.request.newContext({// All requests we send go to this API endpoint.baseURL:'https://api.github.com',extraHTTPHeaders:{// We set this header per GitHub guidelines.'Accept':'application/vnd.github.v3+json',// Add authorization token to all requests.// Assuming personal access token available in the environment.'Authorization':`token${process.env.API_TOKEN}`,},});});test.afterAll(async({})=&gt;{// Dispose all responses.awaitapiContext.dispose();});test('last created issue should be first in the list',async({page})=&gt;{constnewIssue=awaitapiContext.post(`/repos/${USER}/${REPO}/issues`,{data:{title:'[Feature] request 1',}});expect(newIssue.ok()).toBeTruthy();awaitpage.goto(`https://github.com/${USER}/${REPO}/issues`);constfirstIssue=page.locator(`a[data-hovercard-type='issue']`).first();awaitexpect(firstIssue).toHaveText('[Feature] request 1');});`\n```", 'API testing | Playwright', 'Playwright can be used to get access to the\nREST (https://en.wikipedia.org/wiki/Representational_state_transfer)\nAPI of your application.\n\nSometimes you may want to send requests to the server directly from Node.js without loading a page and running js code in it. A few examples where it may come in handy:\n\nTest your server API.\nPrepare server side state before visiting the web application in a test.\nValidate server side post-conditions after running some actions in the browser.\n\nAll of that could be achieved via\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nmethods.', 'APIRequestContext | Playwright\n\nThis API is used for the Web API testing. You can use it to trigger API endpoints, configure micro-services, prepare environment or the service to your e2e test.\n\nEach Playwright browser context has an associated\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n, accessible via\nbrowserContext.request (https://playwright.dev/docs/api/class-browsercontext#browser-context-request)\nor\npage.request (https://playwright.dev/docs/api/class-page#page-request)\n(these return the\n\nsame instance\n—\n`page.request`\nis a shortcut for\n`page.context().request`\n). You can also create a standalone, isolated instance with\napiRequest.newContext() (https://playwright.dev/docs/api/class-apirequest#api-request-new-context)\n.\n\nCookie management\n\nThe\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nreturned by\nbrowserContext.request (https://playwright.dev/docs/api/class-browsercontext#browser-context-request)\nand\n\npage.request (https://playwright.dev/docs/api/class-page#page-request)\nuses the same cookie jar as its\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\n:\n\nIf you want API requests that do\nnot\nshare cookies with the browser, create an isolated context via\napiRequest.newContext() (https://playwright.dev/docs/api/class-apirequest#api-request-new-context)\n. Such\n`APIRequestContext`\nobject will have its own isolated cookie storage.', "Fixtures | Playwright\n\nPlaywright Test is based on the concept of the\ntest fixtures (https://playwright.dev/docs/test-fixtures)\n. Test fixtures are used to establish environment for each test, giving the test everything it needs and nothing else.\n\nPlaywright Test looks at each test declaration, analyses the set of fixtures the test needs and prepares those fixtures specifically for the test. Values prepared by the fixtures are merged into a single object that is available to the\n`test`\n, hooks, annotations and other fixtures as a first parameter.\n\n```\n`import{test,expect}from'@playwright/test';test('basic test',async({page})=&gt;{// ...});`\n```\n\nGiven the test above, Playwright Test will set up the\n`page`\nfixture before running the test, and tear it down after the test has finished.\n`page`\nfixture provides a\nPage (https://playwright.dev/docs/api/class-page)\nobject that is available to the test.\n\nPlaywright Test comes with builtin fixtures listed below, and you can add your own fixtures as well. Playwright Test also\nprovides options (https://playwright.dev/docs/api/class-testoptions)\nto  configure\nfixtures.browser (https://playwright.dev/docs/api/class-fixtures#fixtures-browser)\n,\nfixtures.context (https://playwright.dev/docs/api/class-fixtures#fixtures-context)\nand\nfixtures.page (https://playwright.dev/docs/api/class-fixtures#fixtures-page)\n."]</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6022,31 +7169,44 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>To seed the server with a new issue via the API before your UI test runs, you should use the `APIRequestContext` methods. You can establish this precondition by sending a `POST` request to your API endpoint within your test or a setup hook.
-Here is the recommended approach:
-1.  **Create an API context:** Use `playwright.request.newContext()` to create an instance for your API requests. You can configure this with a `baseURL` and necessary headers (such as authorization tokens).
-2.  **Send the POST request:** Use the `post` method on your API context to create the issue. You can pass the issue details as a JSON object in the `data` option.
-3.  **Navigate to the page:** Once the API request is complete and you have verified the response (e.g., using `expect(response.ok()).toBeTruthy()`), you can then use `page.goto()` to load the page in the browser, where the newly created issue will now appear.
-**Example implementation:**
+          <t>To seed the server with a new issue via the API before a UI test runs, you should use `APIRequestContext` methods. You have two primary approaches for managing the request context:
+### 1. Using `page.request` (Recommended for shared state)
+If you want your API requests to share the same cookie jar as your browser context (e.g., to maintain authentication state), use `page.request`. This is a shortcut for `page.context().request`.
+**Example approach:**
 ```javascript
-test('create issue via API and verify in UI', async ({ page, playwright }) =&gt; {
-  // 1. Create the API context
-  const apiContext = await playwright.request.newContext({
+test('create issue and verify', async ({ page }) =&gt; {
+  // Seed the server
+  const newIssue = await page.request.post('/api/issues', {
+    data: { title: '[Feature] request 1' }
+  });
+  // Navigate to the page
+  await page.goto('/issues');
+  // ... perform assertions
+});
+```
+### 2. Using `apiRequest.newContext()` (For isolated state)
+If you need API requests that do not share cookies with the browser, or if you want to set up a specific configuration (like a `baseURL` or custom headers) that persists across multiple tests, create an isolated context using `playwright.request.newContext()`.
+**Example approach using `beforeAll`:**
+```javascript
+let apiContext;
+test.beforeAll(async ({ playwright }) =&gt; {
+  apiContext = await playwright.request.newContext({
     baseURL: 'https://api.example.com',
     extraHTTPHeaders: { 'Authorization': `token ${process.env.API_TOKEN}` },
   });
-  // 2. Seed the server with a new issue
-  const newIssue = await apiContext.post('/repos/issues', {
-    data: { title: 'New Issue Title' },
-  });
-  expect(newIssue.ok()).toBeTruthy();
-  // 3. Navigate to the page to see the issue
-  await page.goto('https://example.com/issues');
-  // ... perform UI assertions
+});
+test.afterAll(async () =&gt; {
   await apiContext.dispose();
 });
+test('test with seeded data', async ({ page }) =&gt; {
+  await apiContext.post('/issues', { data: { title: 'New Issue' } });
+  await page.goto('/issues');
+});
 ```
-You can also set up the `apiContext` in a `test.beforeAll` hook if you need to reuse it across multiple tests in the same file.</t>
+**Key Considerations:**
+* **`APIRequestContext`**: This is the core tool for preparing server-side state before visiting the web application.
+* **Cleanup**: If you create a standalone context using `newContext()`, ensure you call `apiContext.dispose()` in an `afterAll` hook to clean up resources.
+* **Fixtures**: Playwright Test uses fixtures to establish the environment. You can use these built-in request contexts within your test functions or hooks to perform the seeding.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6055,73 +7215,126 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>0.009799749999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>0.5</v>
+        <v>35154</v>
       </c>
       <c r="H100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>0.07196969696969698</v>
+        <v>0.29</v>
       </c>
       <c r="J100" t="n">
-        <v>0.5428571428571428</v>
+        <v>5</v>
       </c>
       <c r="K100" t="n">
-        <v>0.6595238095106191</v>
+        <v>0.07581227436823104</v>
       </c>
       <c r="L100" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.8874999999778125</v>
+      </c>
+      <c r="N100" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>My authentication state file has sensitive cookies. I'm worried about accidentally committing it. What does Playwright recommend to keep it out of version control?</t>
+          <t>We have three kinds of account — an administrator, an ordinary member, and a read-only auditor — and different spec files need to run as different ones. At the moment each file signs in through the form in a beforeEach, which is most of our runtime. None of these tests change server-side data, so sharing the accounts is fine.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>['Regardless of the authentication strategy you choose, you are likely to store authenticated browser state on the file system.\n\nWe recommend to create\n`playwright/.auth`\ndirectory and add it to your\n`.gitignore`\n. Your authentication routine will produce authenticated browser state and save it to a file in this\n`playwright/.auth`\ndirectory. Later on, tests will reuse this state and start already authenticated.\n\ndanger\nThe browser state file may contain sensitive cookies and headers that could be used to impersonate you or your test account. We strongly discourage checking them into private or public repositories.\n\nBash\nPowerShell\nBatch\n```\n`mkdir-pplaywright/.authecho$\'\\nplaywright/.auth\'&gt;&gt;.gitignore`\n```\n```\n`New-Item-ItemType Directory-Force-Path playwright\\.authAdd-Content-path.gitignore"`r`nplaywright/.auth"`\n```\n```\n`mdplaywright\\.authecho. &gt;&gt; .gitignoreecho"playwright/.auth"&gt;&gt; .gitignore`\n```']</t>
+          <t>['Authentication | Playwright', "When to use\n\nYou have more than one role in your end to end tests, but you can reuse accounts across all tests.\n\nDetails\n\nWe will authenticate multiple times in the setup project.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';constadminFile='playwright/.auth/admin.json';setup('authenticate as admin',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('admin');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:adminFile});});constuserFile='playwright/.auth/user.json';setup('authenticate as user',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('user');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:userFile});});`\n```\n\nAfter that, specify\n`storageState`\nfor each test file or test group,\ninstead of\nsetting it in the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test.use({storageState:'playwright/.auth/admin.json'});test('admin test',async({page})=&gt;{// page is authenticated as admin});test.describe(()=&gt;{test.use({storageState:'playwright/.auth/user.json'});test('user test',async({page})=&gt;{// page is authenticated as a user});});`\n```\n\nSee also about\nauthenticating in the UI mode (https://playwright.dev/docs/auth#authenticating-in-ui-mode)\n.", 'Fixtures | Playwright', 'A project is logical group of tests running with the same configuration. We use projects so we can run tests on different browsers and devices. Projects are configured in the\n`playwright.config.ts`\nfile and once configured you can then run your tests on all projects or only on a specific project. You can also use projects to run the same tests in different configurations. For example, you can run the same tests in a logged-in and logged-out state.\n\nBy setting up projects you can also run a group of tests with different timeouts or retries or a group of tests against different environments such as staging and production, splitting tests per package/functionality and more.', "When to use\n\nYour web application supports authenticating via API that is easier/faster than interacting with the app UI.\n\nDetails\n\nWe will send the API request with\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nand then save authenticated state as usual.\n\nIn the\nsetup project (https://playwright.dev/docs/auth#basic-shared-account-in-all-tests)\n:\n\ntests/auth.setup.ts\n```\n`import{testassetup}from'@playwright/test';constauthFile='playwright/.auth/user.json';setup('authenticate',async({request})=&gt;{// Send authentication request. Replace with your own.awaitrequest.post('https://github.com/login',{form:{'user':'user','password':'password'}});awaitrequest.storageState({path:authFile});});`\n```\n\nAlternatively, in a\nworker fixture (https://playwright.dev/docs/auth#moderate-one-account-per-parallel-worker)\n:\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,request}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constcontext=awaitrequest.newContext({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Send authentication request. Replace with your own.awaitcontext.post('https://github.com/login',{form:{'user':'user','password':'password'}});awaitcontext.storageState({path:fileName});awaitcontext.dispose();awaituse(fileName);},{scope:'worker'}],});`\n```", 'Projects | Playwright', 'When to use\n\nYou need to test how multiple authenticated roles interact together, in a single test.\n\nDetails\n\nYou can introduce fixtures that will provide a page authenticated as each role.\n\nBelow is an example that\ncreates fixtures (https://playwright.dev/docs/test-fixtures#creating-a-fixture)\nfor two\nPage Object Models (https://playwright.dev/docs/pom)\n- admin POM and user POM. It assumes\n`adminStorageState.json`\nand\n`userStorageState.json`\nfiles were created in the global setup.\n\nplaywright/fixtures.ts\n```\n`import{testasbase,typePage,typeLocator}from\'@playwright/test\';// Page Object Model for the "admin" page.// Here you can add locators and helper methods specific to the admin page.classAdminPage{// Page signed in as "admin".page:Page;// Example locator pointing to "Welcome, Admin" greeting.greeting:Locator;constructor(page:Page){this.page=page;this.greeting=page.locator(\'#greeting\');}}// Page Object Model for the "user" page.// Here you can add locators and helper methods specific to the user page.classUserPage{// Page signed in as "user".page:Page;// Example locator pointing to "Welcome, User" greeting.greeting:Locator;constructor(page:Page){this.page=page;this.greeting=page.locator(\'#greeting\');}}// Declare the types of your fixtures.typeMyFixtures={adminPage:AdminPage;userPage:UserPage;};export*from\'@playwright/test\';exportconsttest=base.extend&lt;MyFixtures&gt;({adminPage:async({browser},use)=&gt;{constcontext=awaitbrowser.newContext({storageState:\'playwright/.auth/admin.json\'});constadminPage=newAdminPage(awaitcontext.newPage());awaituse(adminPage);awaitcontext.close();},userPage:async({browser},use)=&gt;{constcontext=awaitbrowser.newContext({storageState:\'playwright/.auth/user.json\'});constuserPage=newUserPage(awaitcontext.newPage());awaituse(userPage);awaitcontext.close();},});`\n```\n\ntests/example.spec.ts\n```\n`// Import test with our new fixtures.import{test,expect}from\'../playwright/fixtures\';// Use adminPage and userPage fixtures in the test.test(\'admin and user\',async({adminPage,userPage})=&gt;{// ... interact with both adminPage and userPage ...awaitexpect(adminPage.greeting).toHaveText(\'Welcome, Admin\');awaitexpect(userPage.greeting).toHaveText(\'Welcome, User\');});`\n```']</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>['We recommend to create playwright/.auth directory and add it to your .gitignore . Your authentication routine will produce authenticated browser state and save it to a file in this playwright/.auth directory.', 'The browser state file may contain sensitive cookies and headers that could be used to impersonate you or your test account. We strongly discourage checking them into private or public repositories.']</t>
+          <t>['You have more than one role in your end to end tests, but you can reuse accounts across all tests.', 'This is the recommended approach for tests without server-side state. Authenticate once in the setup project, save the authentication state, and then reuse it to bootstrap each test already authenticated.', 'Create a new setup project in the config and declare it as a dependency for all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as storageState.', "projects: [ { name: 'setup', testMatch: /.*\\.setup\\.ts/ }, { name: 'chromium', use: { ...devices['Desktop Chrome'], storageState: 'playwright/.auth/user.json', }, dependencies: ['setup'], } ]"]</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Playwright recommends creating a `playwright/.auth` directory and adding it to your `.gitignore` file to keep the authentication state file out of version control.</t>
+          <t>To handle multiple signed-in roles while reusing accounts, you should authenticate in a setup project and then specify the `storageState` for each test file or group.
+### 1. Authenticate in the setup project
+Create a setup file (e.g., `tests/auth.setup.ts`) to perform the authentication for each of your three roles (administrator, member, and auditor) and save the state to separate files:
+```typescript
+import { test as setup, expect } from '@playwright/test';
+const adminFile = 'playwright/.auth/admin.json';
+setup('authenticate as admin', async ({ page }) =&gt; {
+  // Perform login steps for admin
+  await page.goto('https://github.com/login');
+  // ... login actions ...
+  await page.context().storageState({ path: adminFile });
+});
+const userFile = 'playwright/.auth/user.json';
+setup('authenticate as user', async ({ page }) =&gt; {
+  // Perform login steps for member
+  await page.context().storageState({ path: userFile });
+});
+const auditorFile = 'playwright/.auth/auditor.json';
+setup('authenticate as auditor', async ({ page }) =&gt; {
+  // Perform login steps for auditor
+  await page.context().storageState({ path: auditorFile });
+});
+```
+### 2. Specify `storageState` in your test files
+Instead of setting the state in your global config, apply the specific `storageState` file within each test file or `test.describe` block:
+```typescript
+import { test } from '@playwright/test';
+// For a file using the admin role
+test.use({ storageState: 'playwright/.auth/admin.json' });
+test('admin test', async ({ page }) =&gt; {
+  // page is authenticated as admin
+});
+// For a group using the member role
+test.describe(() =&gt; {
+  test.use({ storageState: 'playwright/.auth/user.json' });
+  test('member test', async ({ page }) =&gt; {
+    // page is authenticated as member
+  });
+});
+```
+### Alternative: POM Fixtures
+If you need to interact with multiple roles within a single test, you can create custom fixtures that provide pages authenticated as each role using `browser.newContext({ storageState: '...' })`. This is documented in the "Testing multiple roles with POM fixtures" section.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Keep the saved session in a playwright/.auth folder and gitignore it. Because that file can hold cookies and headers capable of impersonating your account, Playwright warns strongly against pushing it to any repo, public or private.</t>
+          <t>Sign each role in once up front and hand the specs the saved state. Write one setup file per role that logs in and saves to its own file — playwright/.auth/admin.json, member.json, auditor.json — and match them with a setup project (`{ name: 'setup', testMatch: /.*\.setup\.ts/ }`). Then declare a testing project per role that sets `storageState` to the matching file and lists the setup project in `dependencies`, so authentication always runs first and every test in that project starts already signed in. Point each project's `testMatch`/`testDir` at the specs for that role. This is the recommended shape when you have more than one role but can reuse accounts across tests; per-worker accounts are only needed once tests start mutating shared server state.</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>0.010718499999999</v>
       </c>
       <c r="G101" t="n">
-        <v>0.86</v>
+        <v>38634</v>
       </c>
       <c r="H101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.43</v>
       </c>
       <c r="J101" t="n">
-        <v>0.1891891891891892</v>
+        <v>5</v>
       </c>
       <c r="K101" t="n">
-        <v>0.9999999999</v>
+        <v>0.1254480286738351</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>0.2734375</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.91666666664375</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/data_evaluation/playwright/ragas_results_llm_retriever.xlsx
+++ b/data_evaluation/playwright/ragas_results_llm_retriever.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['The\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\nlocator reflects how users and assistive technology perceive the page, for example whether some element is a button or a checkbox. When locating by role, you should usually pass the accessible name as well, so that the locator pinpoints the exact element.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign up\nSubscribe\nSubmit\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nRole locators include\nbuttons, checkboxes, headings, links, lists, tables, and many more (https://www.w3.org/TR/html-aria/#docconformance)\nand follow W3C specifications for\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. Note that many html elements like\n`&lt;button&gt;`\nhave an\nimplicitly defined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role locator.\n\nNote that role locators\ndo not replace\naccessibility audits and conformance tests, but rather give early feedback about the ARIA guidelines.\n\nWhen to use role locators\nWe recommend prioritizing role locators to locate elements, as it is the closest way to how users and assistive technology perceive the page.', 'Locators | Playwright', "Locator | Playwright\n\nLocators are the central piece of Playwright's auto-waiting and retry-ability. In a nutshell, locators represent a way to find element(s) on the page at any moment. A locator can be created with the\npage.locator() (https://playwright.dev/docs/api/class-page#page-locator)\nmethod.\n\nLearn more about locators (https://playwright.dev/docs/locators)\n.", "These are the recommended built-in locators.\n\npage.getByRole() (https://playwright.dev/docs/locators#locate-by-role)\nto locate by explicit and implicit accessibility attributes.\npage.getByText() (https://playwright.dev/docs/locators#locate-by-text)\nto locate by text content.\npage.getByLabel() (https://playwright.dev/docs/locators#locate-by-label)\nto locate a form control by associated label's text.\npage.getByPlaceholder() (https://playwright.dev/docs/locators#locate-by-placeholder)\nto locate an input by placeholder.\npage.getByAltText() (https://playwright.dev/docs/locators#locate-by-alt-text)\nto locate an element, usually image, by its text alternative.\npage.getByTitle() (https://playwright.dev/docs/locators#locate-by-title)\nto locate an element by its title attribute.\npage.getByTestId() (https://playwright.dev/docs/locators#locate-by-test-id)\nto locate an element based on its\n`data-testid`\nattribute (other attributes can be configured).\n\n```\n`awaitpage.getByLabel('User Name').fill('John');awaitpage.getByLabel('Password').fill('secret-password');awaitpage.getByRole('button',{name:'Sign in'}).click();awaitexpect(page.getByText('Welcome, John!')).toBeVisible();`\n```"]</t>
+          <t>['The\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\nlocator reflects how users and assistive technology perceive the page, for example whether some element is a button or a checkbox. When locating by role, you should usually pass the accessible name as well, so that the locator pinpoints the exact element.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign up\nSubscribe\nSubmit\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nRole locators include\nbuttons, checkboxes, headings, links, lists, tables, and many more (https://www.w3.org/TR/html-aria/#docconformance)\nand follow W3C specifications for\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. Note that many html elements like\n`&lt;button&gt;`\nhave an\nimplicitly defined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role locator.\n\nNote that role locators\ndo not replace\naccessibility audits and conformance tests, but rather give early feedback about the ARIA guidelines.\n\nWhen to use role locators\nWe recommend prioritizing role locators to locate elements, as it is the closest way to how users and assistive technology perceive the page.', 'Added in: v1.27\n\nlocator.getByRole\n\nAllows locating elements by their\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n.\n\nUsage\n\nConsider the following DOM structure.\n\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nArguments\n\n`role`\n"alert" | "alertdialog" | "application" | "article" | "banner" | "blockquote" | "button" | "caption" | "cell" | "checkbox" | "code" | "columnheader" | "combobox" | "complementary" | "contentinfo" | "definition" | "deletion" | "dialog" | "directory" | "document" | "emphasis" | "feed" | "figure" | "form" | "generic" | "grid" | "gridcell" | "group" | "heading" | "img" | "insertion" | "link" | "list" | "listbox" | "listitem" | "log" | "main" | "marquee" | "math" | "meter" | "menu" | "menubar" | "menuitem" | "menuitemcheckbox" | "menuitemradio" | "navigation" | "none" | "note" | "option" | "paragraph" | "presentation" | "progressbar" | "radio" | "radiogroup" | "region" | "row" | "rowgroup" | "rowheader" | "scrollbar" | "search" | "searchbox" | "separator" | "slider" | "spinbutton" | "status" | "strong" | "subscript" | "superscript" | "switch" | "tab" | "table" | "tablist" | "tabpanel" | "term" | "textbox" | "time" | "timer" | "toolbar" | "tooltip" | "tree" | "treegrid" | "treeitem"\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-role)\nRequired aria role.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`checked`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-checked)\nAn attribute that is usually set by\n`aria-checked`\nor native\n`&lt;input type=checkbox&gt;`\ncontrols.\nLearn more about\naria-checked (https://www.w3.org/TR/wai-aria-1.2/#aria-checked)\n.\n`description`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n(optional)\nAdded in: v1.60\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-description)\nOption to match the\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\n. By default, matching is case-insensitive and searches for a substring, use\nexact (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-exact)\nto control this behavior.\nLearn more about\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\n.\n`disabled`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-disabled)\nAn attribute that is usually set by\n`aria-disabled`\nor\n`disabled`\n.\nnote\nUnlike most other attributes,\n`disabled`\nis inherited through the DOM hierarchy. Learn more about\naria-disabled (https://www.w3.org/TR/wai-aria-1.2/#aria-disabled)\n.\n`exact`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.28\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-exact)\nWhether\nname (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-name)\nand\ndescription (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-description)\nare matched exactly: case-sensitive and whole-string. Defaults to false. Ignored when the value is a regular expression. Note that exact match still trims whitespace.\n`expanded`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-expanded)\nAn attribute that is usually set by\n`aria-expanded`\n.\nLearn more about\naria-expanded (https://www.w3.org/TR/wai-aria-1.2/#aria-expanded)\n.\n`includeHidden`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-include-hidden)\nOption that controls whether hidden elements are matched. By default, only non-hidden elements, as\ndefined by ARIA (https://www.w3.org/TR/wai-aria-1.2/#tree_exclusion)\n, are matched by role selector.\nLearn more about\naria-hidden (https://www.w3.org/TR/wai-aria-1.2/#aria-hidden)\n.\n`level`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-level)\nA number attribute that is usually present for roles\n`heading`\n,\n`listitem`\n,\n`row`\n,\n`treeitem`\n, with default values for\n`&lt;h1&gt;-&lt;h6&gt;`\nelements.\nLearn more about\naria-level (https://www.w3.org/TR/wai-aria-1.2/#aria-level)\n.\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-name)\nOption to match the\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. By default, matching is case-insensitive and searches for a substring, use\nexact (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-exact)\nto control this behavior.\nLearn more about\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n.\n`pressed`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-pressed)\nAn attribute that is usually set by\n`aria-pressed`\n.\nLearn more about\naria-pressed (https://www.w3.org/TR/wai-aria-1.2/#aria-pressed)\n.\n`selected`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-selected)\nAn attribute that is usually set by\n`aria-selected`\n.\nLearn more about\naria-selected (https://www.w3.org/TR/wai-aria-1.2/#aria-selected)\n.\n\nReturns\n\nLocator (https://playwright.dev/docs/api/class-locator)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-return)\n\nDetails\n\nRole selector\ndoes not replace\naccessibility audits and conformance tests, but rather gives early feedback about the ARIA guidelines.\n\nMany html elements have an implicitly\ndefined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role selector. You can find all the\nsupported roles here (https://www.w3.org/TR/wai-aria-1.2/#role_definitions)\n. ARIA guidelines\ndo not recommend\nduplicating implicit roles and attributes by setting\n`role`\nand/or\n`aria-*`\nattributes to default values.', "These are the recommended built-in locators.\n\npage.getByRole() (https://playwright.dev/docs/locators#locate-by-role)\nto locate by explicit and implicit accessibility attributes.\npage.getByText() (https://playwright.dev/docs/locators#locate-by-text)\nto locate by text content.\npage.getByLabel() (https://playwright.dev/docs/locators#locate-by-label)\nto locate a form control by associated label's text.\npage.getByPlaceholder() (https://playwright.dev/docs/locators#locate-by-placeholder)\nto locate an input by placeholder.\npage.getByAltText() (https://playwright.dev/docs/locators#locate-by-alt-text)\nto locate an element, usually image, by its text alternative.\npage.getByTitle() (https://playwright.dev/docs/locators#locate-by-title)\nto locate an element by its title attribute.\npage.getByTestId() (https://playwright.dev/docs/locators#locate-by-test-id)\nto locate an element based on its\n`data-testid`\nattribute (other attributes can be configured).\n\n```\n`awaitpage.getByLabel('User Name').fill('John');awaitpage.getByLabel('Password').fill('secret-password');awaitpage.getByRole('button',{name:'Sign in'}).click();awaitexpect(page.getByText('Welcome, John!')).toBeVisible();`\n```", 'warning\nWe recommend the modern\ntext locator (https://playwright.dev/docs/locators#get-by-text)\ninstead.\n\nLegacy text locator matches elements that contain passed text.\n\n```\n`awaitpage.locator(\'text=Log in\').click();`\n```\n\nLegacy text locator has a few variations:\n\n`text=Log in`\n- default matching is case-insensitive, trims whitespace and searches for a substring. For example,\n`text=Log`\nmatches\n`&lt;button&gt;Log in&lt;/button&gt;`\n.\n```\n`awaitpage.locator(\'text=Log in\').click();`\n```\n`text="Log in"`\n- text body can be escaped with single or double quotes to search for a text node with exact content after trimming whitespace.\nFor example,\n`text="Log"`\ndoes not match\n`&lt;button&gt;Log in&lt;/button&gt;`\nbecause\n`&lt;button&gt;`\ncontains a single text node\n`"Log in"`\nthat is not equal to\n`"Log"`\n. However,\n`text="Log"`\nmatches\n`&lt;button&gt; Log &lt;span&gt;in&lt;/span&gt;&lt;/button&gt;`\n, because\n`&lt;button&gt;`\ncontains a text node\n`" Log "`\n. This exact mode implies case-sensitive matching, so\n`text="Download"`\nwill not match\n`&lt;button&gt;download&lt;/button&gt;`\n.\nQuoted body follows the usual escaping rules, e.g. use\n`\\"`\nto escape double quote in a double-quoted string:\n`text="foo\\"bar"`\n.\n```\n`awaitpage.locator(\'text="Log in"\').click();`\n```\n`/Log\\s*in/i`\n- body can be a\nJavaScript-like regex (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\nwrapped in\n`/`\nsymbols. For example,\n`text=/Log\\s*in/i`\nmatches\n`&lt;button&gt;Login&lt;/button&gt;`\nand\n`&lt;button&gt;log IN&lt;/button&gt;`\n.\n```\n`awaitpage.locator(\'text=/Log\\\\s*in/i\').click();`\n```\n\nnote\nString selectors starting and ending with a quote (either\n`"`\nor\n`\'`\n) are assumed to be a legacy text locators. For example,\n`"Log in"`\nis converted to\n`text="Log in"`\ninternally.\n\nnote\nMatching always normalizes whitespace. For example, it turns multiple spaces into one, turns line breaks into spaces and ignores leading and trailing whitespace.\n\nnote\nInput elements of the type\n`button`\nand\n`submit`\nare matched by their\n`value`\ninstead of text content. For example,\n`text=Log in`\nmatches\n`&lt;input type=button value="Log in"&gt;`\n.', "Find an element by the text it contains. You can match by a substring, exact string, or a regular expression when using\npage.getByText() (https://playwright.dev/docs/api/class-page#page-get-by-text)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nWelcome, John\n```\n`&lt;span&gt;Welcome, John&lt;/span&gt;`\n```\n\nYou can locate the element by the text it contains:\n\n```\n`awaitexpect(page.getByText('Welcome, John')).toBeVisible();`\n```\n\nSet an exact match:\n\n```\n`awaitexpect(page.getByText('Welcome, John',{exact:true})).toBeVisible();`\n```\n\nMatch with a regular expression:\n\n```\n`awaitexpect(page.getByText(/welcome,[A-Za-z]+$/i)).toBeVisible();`\n```\n\nnote\nMatching by text always normalizes whitespace, even with exact match. For example, it turns multiple spaces into one, turns line breaks into spaces and ignores leading and trailing whitespace.\n\nWhen to use text locators\nWe recommend using text locators to find non interactive elements like\n`div`\n,\n`span`\n,\n`p`\n, etc. For interactive elements like\n`button`\n,\n`a`\n,\n`input`\n, etc. use\nrole locators (https://playwright.dev/docs/locators#locate-by-role)\n.\n\nYou can also\nfilter by text (https://playwright.dev/docs/locators#filter-by-text)\nwhich can be useful when trying to find a particular item in a list.", 'Added in: v1.27\n\nlocator.getByText\n\nAllows locating elements that contain given text.\n\nSee also\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nthat allows to match by another criteria, like an accessible role, and then filter by the text content.\n\nUsage\n\nConsider the following DOM structure:\n\n```\n`&lt;div&gt;Hello&lt;span&gt;world&lt;/span&gt;&lt;/div&gt;&lt;div&gt;Hello&lt;/div&gt;`\n```\n\nYou can locate by text substring, exact string, or a regular expression:\n\n```\n`// Matches &lt;span&gt;page.getByText(\'world\');// Matches first &lt;div&gt;page.getByText(\'Hello world\');// Matches second &lt;div&gt;page.getByText(\'Hello\',{exact:true});// Matches both &lt;div&gt;spage.getByText(/Hello/);// Matches second &lt;div&gt;page.getByText(/^hello$/i);`\n```\n\nArguments\n\n`text`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-text-option-text)\nText to locate the element for.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`exact`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-text-option-exact)\nWhether to find an exact match: case-sensitive and whole-string. Default to false. Ignored when locating by a regular expression. Note that exact match still trims whitespace.\n\nReturns\n\nLocator (https://playwright.dev/docs/api/class-locator)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-text-return)\n\nDetails\n\nMatching by text always normalizes whitespace, even with exact match. For example, it turns multiple spaces into one, turns line breaks into spaces and ignores leading and trailing whitespace.\n\nInput elements of the type\n`button`\nand\n`submit`\nare matched by their\n`value`\ninstead of the text content. For example, locating by text\n`"Log in"`\nmatches\n`&lt;input type=button value="Log in"&gt;`\n.']</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,10 +506,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The recommended way to target a button by the label a user would read on it is to use `page.getByRole()`. You should pass `'button'` as the role and the button's accessible name as the `name` option.
-For example:
-`await page.getByRole('button', { name: 'Submit' }).click();`
-Playwright recommends prioritizing role locators because they reflect how users and assistive technology perceive the page.</t>
+          <t>The recommended way to target a button by the label a user would read on it is to use `page.getByRole()`. 
+You should prioritize role locators for interactive elements like buttons because they reflect how users and assistive technology perceive the page. When using this method, you pass the role `'button'` and the accessible name (the label) in the options object:
+```javascript
+await page.getByRole('button', { name: 'Submit' }).click();
+```
+**Details on this approach:**
+*   **Accessible Name:** The `name` option matches the accessible name of the element. By default, this is case-insensitive and searches for a substring.
+*   **Exact Matching:** If you need an exact, case-sensitive match, you can set the `exact` option to `true`.
+*   **Regular Expressions:** You can also pass a regular expression to the `name` option (e.g., `{ name: /submit/i }`).
+While `page.getByText()` can also be used to find elements, the documentation explicitly recommends using role locators for interactive elements like buttons and reserving text locators for non-interactive elements like `div`, `span`, or `p`.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -518,28 +524,28 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.00838525</v>
+        <v>0.00172775</v>
       </c>
       <c r="G2" t="n">
-        <v>32466</v>
+        <v>53040</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.08383233532934131</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7499999999625</v>
+        <v>0.94999999997625</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
@@ -553,7 +559,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', 'Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and\n`beforeEach`\nhooks is included in the test timeout.\n\nTimed out test produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Timeout of 30000ms exceeded.`\n```\n\nAdditional separate timeout, of the same value, is shared between fixture teardowns and\n`afterEach`\nhooks, after the test function has finished.\n\nThe same timeout value also applies to\n`beforeAll`\nand\n`afterAll`\nhooks, but they do not share time with any test.', "playwright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({timeout:120_000,});`\n```\n\nAPI reference:\ntestConfig.timeout (https://playwright.dev/docs/api/class-testconfig#test-config-timeout)\n."]</t>
+          <t>['Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', 'Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and\n`beforeEach`\nhooks is included in the test timeout.\n\nTimed out test produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Timeout of 30000ms exceeded.`\n```\n\nAdditional separate timeout, of the same value, is shared between fixture teardowns and\n`afterEach`\nhooks, after the test function has finished.\n\nThe same timeout value also applies to\n`beforeAll`\nand\n`afterAll`\nhooks, but they do not share time with any test.', 'Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Error: expect(received).toHaveText(expected)Expected string: "my text"Received string: ""Call log:- expect.toHaveText with timeout 5000ms- waiting for "locator(\'button\')"`\n```', "Playwright Test supports a timeout for the whole test run. This prevents excess resource usage when everything went wrong. There is no default global timeout, but you can set a reasonable one in the config, for example one hour. Global timeout produces the following error:\n\n```\n`Running 1000 tests using 10 workers514 skipped486 passedTimed out waiting 3600s for the entire test run`\n```\n\nYou can set global timeout in the config.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalTimeout:3_600_000,});`\n```\n\nAPI reference:\ntestConfig.globalTimeout (https://playwright.dev/docs/api/class-testconfig#test-config-global-timeout)\n.", "By default,\nfixture (https://playwright.dev/docs/test-fixtures)\nshares timeout with the test. However, for slow fixtures, especially\nworker-scoped (https://playwright.dev/docs/test-fixtures#worker-scoped-fixtures)\nones, it is convenient to have a separate timeout. This way you can keep the overall test timeout small, and give the slow fixture more time.\n\nexample.spec.ts\n```\n`import{testasbase,expect}from'@playwright/test';consttest=base.extend&lt;{slowFixture:string}&gt;({slowFixture:[async({},use)=&gt;{// ... perform a slow operation ...awaituse('hello');},{timeout:60_000}]});test('example test',async({slowFixture})=&gt;{// ...});`\n```\n\nAPI reference:\ntest.extend() (https://playwright.dev/docs/api/class-test#test-extend)\n.", "These are the low-level timeouts that are pre-configured by the test runner, you should not need to change these. If you happen to be in this section because your test are flaky, it is very likely that you should be looking for the solution elsewhere.\n\nTimeout\nDefault\nDescription\nAction timeout\nno timeout\nTimeout for each action\nSet in config\n`{ use: { actionTimeout: 10_000 } }`\nOverride in test\n`locator.click({ timeout: 10_000 })`\nNavigation timeout\nno timeout\nTimeout for each navigation action\nSet in config\n`{ use: { navigationTimeout: 30_000 } }`\nOverride in test\n`page.goto('/', { timeout: 30_000 })`\nGlobal timeout\nno timeout\nGlobal timeout for the whole test run\nSet in config\n`{ globalTimeout: 3_600_000 }`\n`beforeAll`\n/\n`afterAll`\ntimeout\n30_000 ms\nTimeout for the hook\nSet in hook\n`test.setTimeout(60_000)`\nFixture timeout\nno timeout\nTimeout for an individual fixture\nSet in fixture\n`{ scope: 'test', timeout: 30_000 }`"]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,10 +570,11 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>If you do not configure anything, a single test can run for 30,000 ms (30 seconds) before Playwright kills it.
-The time spent on the following counts toward that budget:
-*   The test function
-*   Fixture setups
-*   `beforeEach` hooks</t>
+The following items count toward this 30-second budget:
+*   The test function itself.
+*   Fixture setups.
+*   `beforeEach` hooks.
+Note that fixture teardowns and `afterEach` hooks share a separate, additional timeout of the same value (30 seconds) that begins after the test function has finished. `beforeAll` and `afterAll` hooks also have a 30-second timeout, but they do not share time with any test.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -576,25 +583,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.007680999999999999</v>
+        <v>0.0006365</v>
       </c>
       <c r="G3" t="n">
-        <v>29874</v>
+        <v>33104</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="J3" t="n">
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="M3" t="n">
         <v>0.49999999995</v>
@@ -611,7 +618,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['PlaywrightAssertions | Playwright\n\nPlaywright gives you Web-First Assertions with convenience methods for creating assertions that will wait and retry until the expected condition is met.\n\nConsider the following example:\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'status becomes submitted\',async({page})=&gt;{// ...awaitpage.locator(\'#submit-button\').click();awaitexpect(page.locator(\'.status\')).toHaveText(\'Submitted\');});`\n```\n\nPlaywright will be re-testing the node with the selector\n`.status`\nuntil fetched Node has the\n`"Submitted"`\ntext. It will be re-fetching the node and checking it over and over, until the condition is met or until the timeout is reached. You can pass this timeout as an option.\n\nBy default, the timeout for assertions is set to 5 seconds.', 'Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Error: expect(received).toHaveText(expected)Expected string: "my text"Received string: ""Call log:- expect.toHaveText with timeout 5000ms- waiting for "locator(\'button\')"`\n```', 'Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`']</t>
+          <t>['Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Error: expect(received).toHaveText(expected)Expected string: "my text"Received string: ""Call log:- expect.toHaveText with timeout 5000ms- waiting for "locator(\'button\')"`\n```', 'PlaywrightAssertions | Playwright\n\nPlaywright gives you Web-First Assertions with convenience methods for creating assertions that will wait and retry until the expected condition is met.\n\nConsider the following example:\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'status becomes submitted\',async({page})=&gt;{// ...awaitpage.locator(\'#submit-button\').click();awaitexpect(page.locator(\'.status\')).toHaveText(\'Submitted\');});`\n```\n\nPlaywright will be re-testing the node with the selector\n`.status`\nuntil fetched Node has the\n`"Submitted"`\ntext. It will be re-fetching the node and checking it over and over, until the condition is met or until the timeout is reached. You can pass this timeout as an option.\n\nBy default, the timeout for assertions is set to 5 seconds.', "playwright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({expect:{timeout:10_000,},});`\n```\n\nAPI reference:\ntestConfig.expect (https://playwright.dev/docs/api/class-testconfig#test-config-expect)\n.", 'Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', 'Playwright includes test assertions in the form of\n`expect`\nfunction. To make an assertion, call\n`expect(value)`\nand choose a matcher that reflects the expectation. There are many\ngeneric matchers (https://playwright.dev/docs/api/class-genericassertions)\nlike\n`toEqual`\n,\n`toContain`\n,\n`toBeTruthy`\nthat can be used to assert any conditions.\n\n```\n`expect(success).toBeTruthy();`\n```\n\nPlaywright also includes web-specific\nasync matchers (https://playwright.dev/docs/api/class-locatorassertions)\nthat will wait until the expected condition is met. Consider the following example:\n\n```\n`awaitexpect(page.getByTestId(\'status\')).toHaveText(\'Submitted\');`\n```\n\nPlaywright will be re-testing the element with the test id of\n`status`\nuntil the fetched element has the\n`"Submitted"`\ntext. It will re-fetch the element and check it over and over, until the condition is met or until the timeout is reached. You can either pass this timeout or configure it once via the\ntestConfig.expect (https://playwright.dev/docs/api/class-testconfig#test-config-expect)\nvalue in the test config.\n\nBy default, the timeout for assertions is set to 5 seconds. Learn more about\nvarious timeouts (https://playwright.dev/docs/test-timeouts)\n.', "example.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('example',async({page})=&gt;{awaitexpect(locator).toHaveText('hello',{timeout:10_000});});`\n```", 'The following assertions will retry until the assertion passes, or the assertion timeout is reached. Note that retrying assertions are async, so you must\n`await`\nthem.\n\nAssertion\nDescription\nawait expect(locator).toBeAttached() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-attached)\nElement is attached\nawait expect(locator).toBeChecked() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-checked)\nCheckbox is checked\nawait expect(locator).toBeDisabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-disabled)\nElement is disabled\nawait expect(locator).toBeEditable() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-editable)\nElement is editable\nawait expect(locator).toBeEmpty() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-empty)\nContainer is empty\nawait expect(locator).toBeEnabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-enabled)\nElement is enabled\nawait expect(locator).toBeFocused() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-focused)\nElement is focused\nawait expect(locator).toBeHidden() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-hidden)\nElement is not visible\nawait expect(locator).toBeInViewport() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-in-viewport)\nElement intersects viewport\nawait expect(locator).toBeVisible() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-visible)\nElement is visible\nawait expect(locator).toContainText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-text)\nElement contains text\nawait expect(locator).toContainClass() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-class)\nElement has specified CSS classes\nawait expect(locator).toHaveAccessibleDescription() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-accessible-description)\nElement has a matching\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\nawait expect(locator).toHaveAccessibleName() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-accessible-name)\nElement has a matching\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\nawait expect(locator).toHaveAttribute() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-attribute)\nElement has a DOM attribute\nawait expect(locator).toHaveClass() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-class)\nElement has specified CSS class property\nawait expect(locator).toHaveCount() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-count)\nList has exact number of children\nawait expect(locator).toHaveCSS() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css)\nElement has CSS property\nawait expect(locator).toHaveId() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-id)\nElement has an ID\nawait expect(locator).toHaveJSProperty() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-js-property)\nElement has a JavaScript property\nawait expect(locator).toHaveRole() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-role)\nElement has a specific\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\nawait expect(locator).toHaveScreenshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-screenshot-1)\nElement has a screenshot\nawait expect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nElement matches text\nawait expect(locator).toHaveValue() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value)\nInput has a value\nawait expect(locator).toHaveValues() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-values)\nSelect has options selected\nawait expect(locator).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-match-aria-snapshot)\nElement matches the Aria snapshot\nawait expect(page).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-match-aria-snapshot)\nPage matches the Aria snapshot\nawait expect(page).toHaveScreenshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\nPage has a screenshot\nawait expect(page).toHaveTitle() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-title)\nPage has a title\nawait expect(page).toHaveURL() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-url)\nPage has a URL\nawait expect(response).toBeOK() (https://playwright.dev/docs/api/class-apiresponseassertions#api-response-assertions-to-be-ok)\nResponse has an OK status']</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,16 +637,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.007599499999999999</v>
+        <v>0.00078725</v>
       </c>
       <c r="G4" t="n">
-        <v>29578</v>
+        <v>39318</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -651,7 +658,7 @@
         <v>0.35</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9999999999666667</v>
+        <v>0.8874999999778125</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
@@ -665,7 +672,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['Retries | Playwright', 'Command line | Playwright\n\nPlaywright provides a powerful command line interface for running tests, generating code, debugging, and more. The most up to date list of commands and arguments available on the CLI can always be retrieved via\n`npx playwright --help`\n.', 'Playwright supports\ntest retries\n. When enabled, failing tests will be retried multiple times until they pass, or until the maximum number of retries is reached. By default failing tests are not retried.\n\n```\n`# Give failing tests 3 retry attemptsnpx playwrighttest--retries=3`\n```\n\nYou can configure retries in the configuration file:\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({// Give failing tests 3 retry attemptsretries:3,});`\n```\n\nPlaywright Test will categorize tests as follows:\n\n"passed" - tests that passed on the first run;\n"flaky" - tests that failed on the first run, but passed when retried;\n"failed" - tests that failed on the first run and failed all retries.\n\n```\n`Running3tests using1worker✓ example.spec.ts:4:2 › first passes(438ms)x example.spec.ts:5:2 › second flaky(691ms)✓ example.spec.ts:5:2 › second flaky(522ms)✓ example.spec.ts:6:2 › third passes(932ms)1flakyexample.spec.ts:5:2 › second flaky2passed(4s)`\n```\n\nYou can detect retries at runtime with\ntestInfo.retry (https://playwright.dev/docs/api/class-testinfo#test-info-retry)\n, which is accessible to any test, hook or fixture. Here is an example that clears some server-side state before a retry.\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'my test\',async({page},testInfo)=&gt;{if(testInfo.retry)awaitcleanSomeCachesOnTheServer();// ...});`\n```\n\nYou can specify retries for a specific group of tests or a single file with\ntest.describe.configure() (https://playwright.dev/docs/api/class-test#test-describe-configure)\n.\n\n```\n`import{test,expect}from\'@playwright/test\';test.describe(()=&gt;{// All tests in this describe group will get 2 retry attempts.test.describe.configure({retries:2});test(\'test 1\',async({page})=&gt;{// ...});test(\'test 2\',async({page})=&gt;{// ...});});`\n```']</t>
+          <t>['Playwright supports\ntest retries\n. When enabled, failing tests will be retried multiple times until they pass, or until the maximum number of retries is reached. By default failing tests are not retried.\n\n```\n`# Give failing tests 3 retry attemptsnpx playwrighttest--retries=3`\n```\n\nYou can configure retries in the configuration file:\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({// Give failing tests 3 retry attemptsretries:3,});`\n```\n\nPlaywright Test will categorize tests as follows:\n\n"passed" - tests that passed on the first run;\n"flaky" - tests that failed on the first run, but passed when retried;\n"failed" - tests that failed on the first run and failed all retries.\n\n```\n`Running3tests using1worker✓ example.spec.ts:4:2 › first passes(438ms)x example.spec.ts:5:2 › second flaky(691ms)✓ example.spec.ts:5:2 › second flaky(522ms)✓ example.spec.ts:6:2 › third passes(932ms)1flakyexample.spec.ts:5:2 › second flaky2passed(4s)`\n```\n\nYou can detect retries at runtime with\ntestInfo.retry (https://playwright.dev/docs/api/class-testinfo#test-info-retry)\n, which is accessible to any test, hook or fixture. Here is an example that clears some server-side state before a retry.\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'my test\',async({page},testInfo)=&gt;{if(testInfo.retry)awaitcleanSomeCachesOnTheServer();// ...});`\n```\n\nYou can specify retries for a specific group of tests or a single file with\ntest.describe.configure() (https://playwright.dev/docs/api/class-test#test-describe-configure)\n.\n\n```\n`import{test,expect}from\'@playwright/test\';test.describe(()=&gt;{// All tests in this describe group will get 2 retry attempts.test.describe.configure({retries:2});test(\'test 1\',async({page})=&gt;{// ...});test(\'test 2\',async({page})=&gt;{// ...});});`\n```', 'To run only the tests that failed in the last test run, first run your tests and then run them again with the\n`--last-failed`\nflag.\n\n```\n`npx playwrighttest--last-failed`\n```\n\nPlaywright stores the list of failed tests from the previous run in\n`&lt;outputDir&gt;/.last-run.json`\n(see\ntestConfig.outputDir (https://playwright.dev/docs/test-configuration)\n). To use a different file path, pass\n`--last-failed-file=&lt;path&gt;`\nor set\n`PLAYWRIGHT_LAST_RUN_OUTPUT_FILE`\n.\n\n```\n`npx playwrighttest--last-failed --last-failed-file=.cache/last-run-shard-1.json`\n```', 'Test retries are a way to automatically re-run a test when it fails. This is useful when a test is flaky and fails intermittently. Test retries are configured in the\nconfiguration file (https://playwright.dev/docs/test-configuration)\n.']</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -675,9 +682,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The quickest command-line way to re-run failing tests is to use the `--retries` flag with the `npx playwright test` command.
-For example, to give failing tests 3 retry attempts, use:
-`npx playwright test --retries=3`</t>
+          <t>The quickest command-line way to re-run a flaky test on failure is to use the `--retries` flag:
+```bash
+npx playwright test --retries=3
+```
+This will give failing tests the specified number of retry attempts.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -686,28 +695,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.00732725</v>
+        <v>0.0004155</v>
       </c>
       <c r="G5" t="n">
-        <v>28669</v>
+        <v>39127</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2162162162162162</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8333333332916666</v>
+        <v>0.9999999999</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
@@ -721,7 +730,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['Screenshots | Playwright']</t>
+          <t>["Full page screenshot is a screenshot of a full scrollable page, as if you had a very tall screen and the page could fit it entirely.\n\n```\n`awaitpage.screenshot({path:'screenshot.png',fullPage:true});`\n```", "Here is a quick way to capture a screenshot and save it into a file:\n\n```\n`awaitpage.screenshot({path:'screenshot.png'});`\n```\n\nScreenshots API (https://playwright.dev/docs/api/class-page#page-screenshot)\naccepts many parameters for image format, clip area, quality, etc. Make sure to check them out.", "Rather than writing into a file, you can get a buffer with the image and post-process it or pass it to a third party pixel diff facility.\n\n```\n`constbuffer=awaitpage.screenshot();console.log(buffer.toString('base64'));`\n```"]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -731,7 +740,10 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>I don't know. The provided documentation excerpt only lists the title "Screenshots | Playwright" and does not contain the content required to answer how to capture a full-page screenshot.</t>
+          <t>To capture a screenshot of the whole scrollable page, use the `fullPage: true` option within the `page.screenshot()` method:
+```javascript
+await page.screenshot({path: 'screenshot.png', fullPage: true});
+```</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -740,31 +752,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.0065445</v>
+        <v>0.000267</v>
       </c>
       <c r="G6" t="n">
-        <v>25793</v>
+        <v>27925</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.9999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -775,7 +787,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['Screenshots | Playwright']</t>
+          <t>["Sometimes it is useful to take a screenshot of a single element.\n\n```\n`awaitpage.locator('.header').screenshot({path:'screenshot.png'});`\n```", "Full page screenshot is a screenshot of a full scrollable page, as if you had a very tall screen and the page could fit it entirely.\n\n```\n`awaitpage.screenshot({path:'screenshot.png',fullPage:true});`\n```", "Here is a quick way to capture a screenshot and save it into a file:\n\n```\n`awaitpage.screenshot({path:'screenshot.png'});`\n```\n\nScreenshots API (https://playwright.dev/docs/api/class-page#page-screenshot)\naccepts many parameters for image format, clip area, quality, etc. Make sure to check them out.", "Rather than writing into a file, you can get a buffer with the image and post-process it or pass it to a third party pixel diff facility.\n\n```\n`constbuffer=awaitpage.screenshot();console.log(buffer.toString('base64'));`\n```"]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -785,7 +797,10 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>I don't know. The provided documentation excerpt only lists the title "Screenshots | Playwright" and does not contain information regarding the functionality of taking screenshots of single elements.</t>
+          <t>Yes, you can screenshot a single element. You do this by calling the `screenshot()` method on a locator for that element:
+```javascript
+await page.locator('.header').screenshot({path: 'screenshot.png'});
+```</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -794,28 +809,28 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.0065365</v>
+        <v>0.00027325</v>
       </c>
       <c r="G7" t="n">
-        <v>25776</v>
+        <v>28359</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.8333333332916666</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
@@ -829,7 +844,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>['Videos | Playwright', "Playwright Test can record videos for your tests, controlled by the\n`video`\noption in your Playwright config. By default videos are off.\n\n`'off'`\n- Do not record video.\n`'on'`\n- Record video for each test.\n`'retain-on-failure'`\n- Record video for each test, but remove all videos from successful test runs.\n`'on-first-retry'`\n- Record video only when retrying a test for the first time.\n\nVideo files will appear in the test output directory, typically\n`test-results`\n. See\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nfor advanced video configuration.\n\nVideos are saved upon\nbrowser context (https://playwright.dev/docs/browser-contexts)\nclosure at the end of a test. If you create a browser context manually, make sure to await\nbrowserContext.close() (https://playwright.dev/docs/api/class-browsercontext#browser-context-close)\n.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:'on-first-retry',},});`\n```\n```\n`constcontext=awaitbrowser.newContext({recordVideo:{dir:'videos/'}});// Make sure to await close, so that videos are saved.awaitcontext.close();`\n```\n\nYou can also specify video size and annotation. The video size defaults to the viewport size scaled down to fit 800x800. The video of the viewport is placed in the top-left corner of the output video, scaled down to fit if necessary. You may need to set the viewport size to match your desired video size.\n\nWhen\n`show: { actions }`\nis specified, each action will be visually highlighted in the video with the element outline and action title subtitle. The optional\n`duration`\nproperty controls how long each annotation is displayed (defaults to\n`500`\nms).\n\nWhen\n`show: { test }`\nis specified, video will be annotated with the current test information with configurable\n`level`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:{mode:'on-first-retry',size:{width:640,height:480},show:{actions:{duration:500,position:'top-right',fontSize:14,},test:{level:'step',position:'top-left',fontSize:12,}},},},});`\n```\n\nFor multi-page scenarios, you can access the video file associated with the page via the\npage.video() (https://playwright.dev/docs/api/class-page#page-video)\n.\n\n```\n`constpath=awaitpage.video().path();`\n```\n\nnote\nNote that the video is only available after the page or browser context is closed.", "With Playwright you can capture screenshots, record videos as well as traces of your test. By default these are turned off but you can enable them by setting the\n`screenshot`\n,\n`video`\nand\n`trace`\noptions in your\n`playwright.config.js`\nfile.\n\nTrace files, screenshots and videos will appear in the test output directory, typically\n`test-results`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{// Capture screenshot after each test failure.screenshot:'only-on-failure',// Record trace only when retrying a test for the first time.trace:'on-first-retry',// Record video only when retrying a test for the first time.video:'on-first-retry'},});`\n```\n\nOption\nDescription\ntestOptions.screenshot (https://playwright.dev/docs/api/class-testoptions#test-options-screenshot)\nCapture\nscreenshots (https://playwright.dev/docs/screenshots)\nof your test. Options include\n`'off'`\n,\n`'on'`\nand\n`'only-on-failure'`\ntestOptions.trace (https://playwright.dev/docs/api/class-testoptions#test-options-trace)\nPlaywright can produce test traces while running the tests. Later on, you can view the trace and get detailed information about Playwright execution by opening\nTrace Viewer (https://playwright.dev/docs/trace-viewer)\n. Options include:\n`'off'`\n,\n`'on'`\n,\n`'retain-on-failure'`\nand\n`'on-first-retry'`\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nPlaywright can record\nvideos (https://playwright.dev/docs/videos)\nfor your tests. Options include:\n`'off'`\n,\n`'on'`\n,\n`'retain-on-failure'`\nand\n`'on-first-retry'`", 'Configuration (use) | Playwright', 'With Playwright you can record videos for your tests.']</t>
+          <t>["Playwright Test can record videos for your tests, controlled by the\n`video`\noption in your Playwright config. By default videos are off.\n\n`'off'`\n- Do not record video.\n`'on'`\n- Record video for each test.\n`'retain-on-failure'`\n- Record video for each test, but remove all videos from successful test runs.\n`'on-first-retry'`\n- Record video only when retrying a test for the first time.\n\nVideo files will appear in the test output directory, typically\n`test-results`\n. See\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nfor advanced video configuration.\n\nVideos are saved upon\nbrowser context (https://playwright.dev/docs/browser-contexts)\nclosure at the end of a test. If you create a browser context manually, make sure to await\nbrowserContext.close() (https://playwright.dev/docs/api/class-browsercontext#browser-context-close)\n.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:'on-first-retry',},});`\n```\n```\n`constcontext=awaitbrowser.newContext({recordVideo:{dir:'videos/'}});// Make sure to await close, so that videos are saved.awaitcontext.close();`\n```\n\nYou can also specify video size and annotation. The video size defaults to the viewport size scaled down to fit 800x800. The video of the viewport is placed in the top-left corner of the output video, scaled down to fit if necessary. You may need to set the viewport size to match your desired video size.\n\nWhen\n`show: { actions }`\nis specified, each action will be visually highlighted in the video with the element outline and action title subtitle. The optional\n`duration`\nproperty controls how long each annotation is displayed (defaults to\n`500`\nms).\n\nWhen\n`show: { test }`\nis specified, video will be annotated with the current test information with configurable\n`level`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:{mode:'on-first-retry',size:{width:640,height:480},show:{actions:{duration:500,position:'top-right',fontSize:14,},test:{level:'step',position:'top-left',fontSize:12,}},},},});`\n```\n\nFor multi-page scenarios, you can access the video file associated with the page via the\npage.video() (https://playwright.dev/docs/api/class-page#page-video)\n.\n\n```\n`constpath=awaitpage.video().path();`\n```\n\nnote\nNote that the video is only available after the page or browser context is closed.", "With Playwright you can capture screenshots, record videos as well as traces of your test. By default these are turned off but you can enable them by setting the\n`screenshot`\n,\n`video`\nand\n`trace`\noptions in your\n`playwright.config.js`\nfile.\n\nTrace files, screenshots and videos will appear in the test output directory, typically\n`test-results`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{// Capture screenshot after each test failure.screenshot:'only-on-failure',// Record trace only when retrying a test for the first time.trace:'on-first-retry',// Record video only when retrying a test for the first time.video:'on-first-retry'},});`\n```\n\nOption\nDescription\ntestOptions.screenshot (https://playwright.dev/docs/api/class-testoptions#test-options-screenshot)\nCapture\nscreenshots (https://playwright.dev/docs/screenshots)\nof your test. Options include\n`'off'`\n,\n`'on'`\nand\n`'only-on-failure'`\ntestOptions.trace (https://playwright.dev/docs/api/class-testoptions#test-options-trace)\nPlaywright can produce test traces while running the tests. Later on, you can view the trace and get detailed information about Playwright execution by opening\nTrace Viewer (https://playwright.dev/docs/trace-viewer)\n. Options include:\n`'off'`\n,\n`'on'`\n,\n`'retain-on-failure'`\nand\n`'on-first-retry'`\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nPlaywright can record\nvideos (https://playwright.dev/docs/videos)\nfor your tests. Options include:\n`'off'`\n,\n`'on'`\n,\n`'retain-on-failure'`\nand\n`'on-first-retry'`", 'Added in: v1.10\n\ntestOptions.video\n\nWhether to record video for each test. Defaults to\n`\'off\'`\n.\n\n`\'off\'`\n: Do not record video.\n`\'on\'`\n: Record video for each test.\n`\'retain-on-failure\'`\n: Record video for each test, but remove all videos from successful test runs.\n`\'on-first-retry\'`\n: Record video only when retrying a test for the first time.\n\nTo control video size, pass an object with\n`mode`\nand\n`size`\nproperties. If video size is not specified, it will be equal to\ntestOptions.viewport (https://playwright.dev/docs/api/class-testoptions#test-options-viewport)\nscaled down to fit into 800x800. If\n`viewport`\nis not configured explicitly the video size defaults to 800x450. Actual picture of each page will be scaled down if necessary to fit the specified size.\n\nTo annotate actions in the video, pass\n`show`\nwith\n`action`\nand/or\n`test`\nsub-options. The\n`action`\noption controls visual highlights on interacted elements with an optional\n`delay`\nin milliseconds (defaults to\n`500`\n). The\n`test`\noption controls which test information is displayed as a status overlay.\n\nUsage\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{video:\'on-first-retry\',},});`\n```\n\nLearn more about\nrecording video (https://playwright.dev/docs/test-use-options#recording-options)\n.\n\nType\n\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n| "off" | "on" | "retain-on-failure" | "on-first-retry"\n`mode`\n"off" | "on" | "retain-on-failure" | "on-first-retry"\nVideo recording mode.\n`size`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`width`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n`height`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\nSize of the recorded video. Optional.\n`show`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`actions`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`duration`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nHow long each annotation is displayed in milliseconds. Defaults to\n`500`\n.\n`position`\n"top-left" | "top" | "top-right" | "bottom-left" | "bottom" | "bottom-right"\n(optional)\nPosition of the action title overlay. Defaults to\n`"top-right"`\n.\n`fontSize`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nFont size of the action title in pixels. Defaults to\n`24`\n.\nControls visual annotations on interacted elements.\n`test`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`level`\n"file" | "test" | "step"\n(optional)\nLevel of the detail to include about the current test.\n`position`\n"top-left" | "top" | "top-right" | "bottom-left" | "bottom" | "bottom-right"\n(optional)\nPosition of the test information overlay. Defaults to\n`"top-left"`\n.\n`fontSize`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nFont size of the test information in pixels. Defaults to\n`14`\n.\nControls test information displayed as a status overlay in the video.\nIf specified, visually annotates the video with test information and action highlights.', 'With Playwright you can record videos for your tests.']</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -839,12 +854,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>You have to switch them on. By default, video recording is turned off.
-To enable video recording, you must set the `video` option in your `playwright.config.ts` file. You can choose from the following modes:
-*   `'on'`: Record video for each test.
-*   `'retain-on-failure'`: Record video for each test, but remove all videos from successful test runs.
-*   `'on-first-retry'`: Record video only when retrying a test for the first time.
-*   `'off'`: Do not record video (default).
+          <t>You have to switch them on. By default, video recording is set to `'off'`.
+To enable video recording, you must configure the `video` option in your `playwright.config.ts` file. You can choose from the following modes:
+*   **`'on'`**: Record video for each test.
+*   **`'retain-on-failure'`**: Record video for each test, but remove all videos from successful test runs.
+*   **`'on-first-retry'`**: Record video only when retrying a test for the first time.
 Example configuration:
 ```typescript
 import { defineConfig } from '@playwright/test';
@@ -854,7 +868,7 @@
   },
 });
 ```
-If you create a browser context manually, you can also enable recording by setting `recordVideo` within `browser.newContext()`. Note that videos are only saved upon browser context closure, so you must ensure you await `browserContext.close()`.</t>
+Once enabled, video files will appear in your test output directory (typically `test-results`).</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -863,28 +877,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.00830175</v>
+        <v>0.0009792500000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>31397</v>
+        <v>40124</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.18</v>
+        <v>0.29</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06153846153846154</v>
+        <v>0.07766990291262135</v>
       </c>
       <c r="L8" t="n">
         <v>0.4210526315789473</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5833333333041666</v>
+        <v>0.9999999999666667</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
@@ -898,7 +912,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['Trace viewer | Playwright', 'You can open a saved trace using either the Playwright CLI or in the browser at\ntrace.playwright.dev (https://trace.playwright.dev)\n. Make sure to add the full path to where your\n`trace.zip`\nfile is located.\n\n```\n`npx playwright show-trace path/to/trace.zip`\n```', 'Trace viewer | Playwright', 'trace.playwright.dev (https://trace.playwright.dev)\nis a statically hosted variant of the Trace Viewer. You can upload a trace file using drag and drop or via the\n`Select file`\nbutton.\n\nTrace Viewer loads the trace entirely in your browser and does not transmit any data externally.', 'Playwright Trace Viewer is a GUI tool that helps you explore recorded Playwright traces after the script has run. Traces are a great way for debugging your tests when they fail on CI. You can open traces\nlocally (https://playwright.dev/docs/trace-viewer#opening-trace-viewer)\nor in your browser on\ntrace.playwright.dev (https://trace.playwright.dev)\n.', 'You can open remote traces directly using its URL. This makes it easy to view the remote trace without having to manually download the file from CI runs, for example.\n\n```\n`npx playwright show-trace https://example.com/trace.zip`\n```\n\nWhen using\ntrace.playwright.dev (https://trace.playwright.dev)\n, you can also pass the URL of your uploaded trace at some accessible storage (e.g. inside your CI) as a query parameter. CORS (Cross-Origin Resource Sharing) rules might apply.\n\n```\n`https://trace.playwright.dev/?trace=https://demo.playwright.dev/reports/todomvc/data/e6099cadf79aa753d5500aa9508f9d1dbd87b5ee.zip`\n```']</t>
+          <t>['You can open a saved trace using either the Playwright CLI or in the browser at\ntrace.playwright.dev (https://trace.playwright.dev)\n. Make sure to add the full path to where your\n`trace.zip`\nfile is located.\n\n```\n`npx playwright show-trace path/to/trace.zip`\n```', '```\n`# Open trace viewer without a specific trace (can load traces via UI)npx playwright show-trace# View a trace filenpx playwright show-trace trace.zip# View trace from directorynpx playwright show-trace trace/`\n```', 'trace.playwright.dev (https://trace.playwright.dev)\nis a statically hosted variant of the Trace Viewer. You can upload a trace file using drag and drop or via the\n`Select file`\nbutton.\n\nTrace Viewer loads the trace entirely in your browser and does not transmit any data externally.', '```\n`npx playwright show-trace[options][trace]`\n```', "In the HTML report, click on the trace icon next to the test file name to directly open the trace for the required test.\n\nYou can also click to open the detailed view of the test and scroll down to the\n`'Traces'`\ntab and open the trace by clicking on the trace screenshot.\n\nTo learn more about reporters, check out our detailed guide on reporters including the\nHTML Reporter (https://playwright.dev/docs/test-reporters#html-reporter)\n.", 'You can open remote traces directly using its URL. This makes it easy to view the remote trace without having to manually download the file from CI runs, for example.\n\n```\n`npx playwright show-trace https://example.com/trace.zip`\n```\n\nWhen using\ntrace.playwright.dev (https://trace.playwright.dev)\n, you can also pass the URL of your uploaded trace at some accessible storage (e.g. inside your CI) as a query parameter. CORS (Cross-Origin Resource Sharing) rules might apply.\n\n```\n`https://trace.playwright.dev/?trace=https://demo.playwright.dev/reports/todomvc/data/e6099cadf79aa753d5500aa9508f9d1dbd87b5ee.zip`\n```', 'Playwright Trace Viewer is a GUI tool that helps you explore recorded Playwright traces after the script has run. Traces are a great way for debugging your tests when they fail on CI. You can open traces\nlocally (https://playwright.dev/docs/trace-viewer#opening-trace-viewer)\nor in your browser on\ntrace.playwright.dev (https://trace.playwright.dev)\n.']</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -908,10 +922,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>You can open your `trace.zip` file using one of the following two methods:
-*   **Playwright CLI:** Run the following command in your terminal, replacing `path/to/trace.zip` with the full path to your file:
-    `npx playwright show-trace path/to/trace.zip`
-*   **Browser:** Go to [trace.playwright.dev](https://trace.playwright.dev) and upload your file using drag and drop or the **Select file** button. This tool loads the trace entirely in your browser without transmitting data externally.</t>
+          <t>You can open your `trace.zip` file using one of the following methods:
+**Using the Playwright CLI**
+Run the following command in your terminal, providing the path to your file:
+```bash
+npx playwright show-trace path/to/trace.zip
+```
+You can also run `npx playwright show-trace` without a path to open the viewer and load the file via the UI.
+**Using the browser**
+Go to [trace.playwright.dev](https://trace.playwright.dev) and upload your `trace.zip` file by dragging and dropping it into the browser or using the **Select file** button. This tool loads the trace entirely in your browser without transmitting data externally.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -920,28 +939,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.007853250000000001</v>
+        <v>0.0005535</v>
       </c>
       <c r="G9" t="n">
-        <v>30313</v>
+        <v>36700</v>
       </c>
       <c r="H9" t="n">
         <v>0.75</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1265822784810127</v>
+        <v>0.09433962264150944</v>
       </c>
       <c r="L9" t="n">
         <v>0.7692307692307693</v>
       </c>
       <c r="M9" t="n">
-        <v>0.81666666664625</v>
+        <v>0.8541666666453125</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
@@ -955,7 +974,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>["You can control the maximum number of parallel worker processes via\ncommand line (https://playwright.dev/docs/test-cli)\nor in the\nconfiguration file (https://playwright.dev/docs/test-configuration)\n.\n\nFrom the command line:\n\n```\n`npx playwrighttest--workers4`\n```\n\nIn the configuration file:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({// Limit the number of workers on CI, use default locallyworkers:process.env.CI?2:undefined,});`\n```"]</t>
+          <t>["You can control the maximum number of parallel worker processes via\ncommand line (https://playwright.dev/docs/test-cli)\nor in the\nconfiguration file (https://playwright.dev/docs/test-configuration)\n.\n\nFrom the command line:\n\n```\n`npx playwrighttest--workers4`\n```\n\nIn the configuration file:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({// Limit the number of workers on CI, use default locallyworkers:process.env.CI?2:undefined,});`\n```", "Added in: v1.10\n\ntestConfig.workers\n\nThe maximum number of concurrent worker processes to use for parallelizing tests. Can also be set as percentage of logical CPU cores, e.g.\n`'50%'.`\n\nPlaywright Test uses worker processes to run tests. There is always at least one worker process, but more can be used to speed up test execution.\n\nDefaults to half of the number of logical CPU cores. Learn more about\nparallelism and sharding (https://playwright.dev/docs/test-parallel)\nwith Playwright Test.\n\nUsage\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({workers:3,});`\n```\n\nType\n\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)", '```\n`# Run all testsnpx playwrighttest# Run a single test filenpx playwrighttesttests/todo-page.spec.ts# Run a set of test filesnpx playwrighttesttests/todo-page/ tests/landing-page/# Run tests at a specific linenpx playwrighttestmy-spec.ts:42# Run tests by titlenpx playwrighttest-g"add a todo item"# Run tests in headed browsersnpx playwrighttest--headed# Run tests for a specific projectnpx playwrighttest--project=chromium# Get helpnpx playwrighttest--help`\n```\n\nDisable\nparallelization (https://playwright.dev/docs/test-parallel)\n\n```\n`npx playwrighttest--workers=1`\n```\n\nRun in debug mode with\nPlaywright Inspector (https://playwright.dev/docs/debug)\n\n```\n`npx playwrighttest--debug`\n```\n\nRun tests in interactive\nUI mode (https://playwright.dev/docs/test-ui-mode)\n\n```\n`npx playwrighttest--ui`\n```', 'Option\nDescription\n`--debug`\nRun tests with Playwright Inspector. Shortcut for\n`PWDEBUG=1`\nenvironment variable and\n`--timeout=0 --max-failures=1 --headed --workers=1`\noptions.\n`--headed`\nRun tests in headed browsers (default: headless).\n`-g &lt;grep&gt;`\nor\n`--grep &lt;grep&gt;`\nOnly run tests matching this regular expression (default: ".*").\n`--project &lt;project-name...&gt;`\nOnly run tests from the specified list of projects, supports \'*\' wildcard (default: run all projects).\n`--ui`\nRun tests in interactive UI mode.\n`-j &lt;workers&gt;`\nor\n`--workers &lt;workers&gt;`\nNumber of concurrent workers or percentage of logical CPU cores, use 1 to run in a single worker (default: 50%).', 'Option\nDescription\nNon-option arguments\nEach argument is treated as a regular expression matched against the full test file path. Only tests from files matching the pattern will be executed. Special symbols like\n`$`\nor\n`*`\nshould be escaped with\n`\\`\n. In many shells/terminals you may need to quote the arguments.\n`-c &lt;file&gt;`\nor\n`--config &lt;file&gt;`\nConfiguration file, or a test directory with optional "playwright.config.{m,c}?{js,ts}". Defaults to\n`playwright.config.ts`\nor\n`playwright.config.js`\nin the current directory.\n`--debug`\nRun tests with Playwright Inspector. Shortcut for\n`PWDEBUG=1`\nenvironment variable and\n`--timeout=0 --max-failures=1 --headed --workers=1`\noptions.\n`--fail-on-flaky-tests`\nFail if any test is flagged as flaky (default: false).\n`--forbid-only`\nFail if\n`test.only`\nis called (default: false). Useful on CI.\n`--fully-parallel`\nRun all tests in parallel (default: false).\n`--global-timeout &lt;timeout&gt;`\nMaximum time this test suite can run in milliseconds (default: unlimited).\n`-g &lt;grep&gt;`\nor\n`--grep &lt;grep&gt;`\nOnly run tests matching this regular expression (default: ".*").\n`-G &lt;grep&gt;`\nor\n`--grep-invert &lt;grep&gt;`\nOnly run tests that do not match this regular expression.\n`--headed`\nRun tests in headed browsers (default: headless).\n`--ignore-snapshots`\nIgnore screenshot and snapshot expectations.\n`-j &lt;workers&gt;`\nor\n`--workers &lt;workers&gt;`\nNumber of concurrent workers or percentage of logical CPU cores, use 1 to run in a single worker (default: 50%).\n`--last-failed`\nOnly re-run the failures.\n`--last-failed-file &lt;file&gt;`\nOverride the default last-run JSON path for\n`--last-failed`\n(default:\n`&lt;outputDir&gt;/.last-run.json`\n). Same as\n`PLAYWRIGHT_LAST_RUN_OUTPUT_FILE`\nenvironment variable.\n`--list`\nCollect all the tests and report them, but do not run.\n`--max-failures &lt;N&gt;`\nor\n`-x`\nStop after the first\n`N`\nfailures. Passing\n`-x`\nstops after the first failure.\n`--no-deps`\nDo not run project dependencies.\n`--output &lt;dir&gt;`\nFolder for output artifacts (default: "test-results").\n`--only-changed [ref]`\nOnly run test files that have been changed between \'HEAD\' and \'ref\'. Defaults to running all uncommitted changes. Only supports Git.\n`--pass-with-no-tests`\nMakes test run succeed even if no tests were found.\n`--project &lt;project-name...&gt;`\nOnly run tests from the specified list of projects, supports \'*\' wildcard (default: run all projects).\n`--quiet`\nSuppress stdio.\n`--repeat-each &lt;N&gt;`\nRun each test\n`N`\ntimes (default: 1).\n`--reporter &lt;reporter&gt;`\nReporter to use, comma-separated, can be "dot", "line", "list", or others (default: "list"). You can also pass a path to a custom reporter file.\n`--retries &lt;retries&gt;`\nMaximum retry count for flaky tests, zero for no retries (default: no retries).\n`--shard &lt;shard&gt;`\nShard tests and execute only the selected shard, specified in the form "current/all", 1-based, e.g., "3/5".\n`--test-list &lt;file&gt;`\nPath to a file containing a list of tests to run. See\ntest list (https://playwright.dev/docs/test-cli#test-list)\nfor details.\n`--test-list-invert &lt;file&gt;`\nPath to a file containing a list of tests to skip. See\ntest list (https://playwright.dev/docs/test-cli#test-list)\nfor details.\n`--timeout &lt;timeout&gt;`\nSpecify test timeout threshold in milliseconds, zero for unlimited (default: 30 seconds).\n`--trace &lt;mode&gt;`\nForce tracing mode, can be\n`on`\n,\n`off`\n,\n`on-first-retry`\n,\n`on-all-retries`\n,\n`retain-on-failure`\n,\n`retain-on-first-failure`\n,\n`retain-on-failure-and-retries`\n.\n`--tsconfig &lt;path&gt;`\nPath to a single tsconfig applicable to all imported files (default: look up tsconfig for each imported file separately).\n`--ui`\nRun tests in interactive UI mode.\n`--ui-host &lt;host&gt;`\nHost to serve UI on; specifying this option opens UI in a browser tab.\n`--ui-port &lt;port&gt;`\nPort to serve UI on, 0 for any free port; specifying this option opens UI in a browser tab.\n`-u`\nor\n`--update-snapshots [mode]`\nUpdate snapshots with actual results. Possible values are "all", "changed", "missing", and "none". Running tests without the flag defaults to "missing"; running tests with the flag but without a value defaults to "changed".\n`--update-source-method [mode]`\nUpdate snapshots with actual results. Possible values are "patch" (default), "3way" and "overwrite". "Patch" creates a unified diff file that can be used to update the source code later. "3way" generates merge conflict markers in source code. "Overwrite" overwrites the source code with the new snapshot values.\n`-x`\nStop after the first failure.', 'You can disable any parallelism by allowing just a single worker at any time. Either set\n`workers: 1`\noption in the configuration file or pass\n`--workers=1`\nto the command line.\n\n```\n`npx playwrighttest--workers=1`\n```', 'Playwright Test runs tests in parallel. In order to achieve that, it runs several worker processes that run at the same time. By default,\ntest files\nare run in parallel. Tests in a single file are run in order, in the same worker process.\n\nYou can configure tests using\ntest.describe.configure (https://playwright.dev/docs/test-parallel#parallelize-tests-in-a-single-file)\nto run\ntests in a single file\nin parallel.\nYou can configure\nentire project\nto have all tests in all files to run in parallel using\ntestProject.fullyParallel (https://playwright.dev/docs/api/class-testproject#test-project-fully-parallel)\nor\ntestConfig.fullyParallel (https://playwright.dev/docs/api/class-testconfig#test-config-fully-parallel)\n.\nTo\ndisable\nparallelism limit the number of\nworkers to one (https://playwright.dev/docs/test-parallel#disable-parallelism)\n.\n\nYou can control the number of\nparallel worker processes (https://playwright.dev/docs/test-parallel#limit-workers)\nand\nlimit the number of failures (https://playwright.dev/docs/test-parallel#limit-failures-and-fail-fast)\nin the whole test suite for efficiency.']</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -965,9 +984,13 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>To cap the number of parallel tests from the command line, use the `--workers` flag followed by the desired number.
-The command is:
-`npx playwright test --workers 4`</t>
+          <t>You can cap the number of parallel tests from the command line using the `--workers` option or its shorthand `-j`.
+You can specify the number of concurrent workers as a number or as a percentage of logical CPU cores. Examples include:
+*   **Using the full flag:** `npx playwright test --workers=4`
+*   **Using the shorthand flag:** `npx playwright test -j 4`
+*   **Using a percentage:** `npx playwright test --workers=50%`
+To disable parallelization, set the value to 1:
+`npx playwright test --workers=1`</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -976,28 +999,28 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.00766275</v>
+        <v>0.0009695</v>
       </c>
       <c r="G10" t="n">
-        <v>29941</v>
+        <v>42742</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0.46</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.1375</v>
       </c>
       <c r="L10" t="n">
-        <v>0.625</v>
+        <v>0.6875</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9999999999</v>
+        <v>0.817857142843512</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
@@ -1011,7 +1034,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['Locators are strict. This means that all operations on locators that imply some target DOM element will throw an exception if more than one element matches. For example, the following call throws if there are several buttons in the DOM:', "```\n`awaitpage.getByRole('button').click();`\n```\n\nOn the other hand, Playwright understands when you perform a multiple-element operation, so the following call works perfectly fine when the locator resolves to multiple elements.", "```\n`awaitpage.getByRole('button').count();`\n```\n\nYou can explicitly opt-out from strictness check by telling Playwright which element to use when multiple elements match, through\nlocator.first() (https://playwright.dev/docs/api/class-locator#locator-first)\n,\nlocator.last() (https://playwright.dev/docs/api/class-locator#locator-last)\n, and\nlocator.nth() (https://playwright.dev/docs/api/class-locator#locator-nth)\n. These methods are\nnot recommended\nbecause when your page changes, Playwright may click on an element you did not intend. Instead, follow best practices above to create a locator that uniquely identifies the target element."]</t>
+          <t>['Locators are strict. This means that all operations on locators that imply some target DOM element will throw an exception if more than one element matches. For example, the following call throws if there are several buttons in the DOM:', "```\n`awaitpage.getByRole('button').click();`\n```\n\nOn the other hand, Playwright understands when you perform a multiple-element operation, so the following call works perfectly fine when the locator resolves to multiple elements.", "```\n`awaitpage.getByRole('button').count();`\n```\n\nYou can explicitly opt-out from strictness check by telling Playwright which element to use when multiple elements match, through\nlocator.first() (https://playwright.dev/docs/api/class-locator#locator-first)\n,\nlocator.last() (https://playwright.dev/docs/api/class-locator#locator-last)\n, and\nlocator.nth() (https://playwright.dev/docs/api/class-locator#locator-nth)\n. These methods are\nnot recommended\nbecause when your page changes, Playwright may click on an element you did not intend. Instead, follow best practices above to create a locator that uniquely identifies the target element.", 'Playwright performs a range of actionability checks on the elements before making actions to ensure these actions behave as expected. It auto-waits for all the relevant checks to pass and only then performs the requested action. If the required checks do not pass within the given\n`timeout`\n, action fails with the\n`TimeoutError`\n.\n\nFor example, for\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\n, Playwright will ensure that:\n\nlocator resolves to exactly one element\nelement is\nVisible (https://playwright.dev/docs/actionability#visible)\nelement is\nStable (https://playwright.dev/docs/actionability#stable)\n, as in not animating or completed animation\nelement\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\n, as in not obscured by other elements\nelement is\nEnabled (https://playwright.dev/docs/actionability#enabled)\n\nHere is the complete list of actionability checks performed for each action:\n\nAction\nVisible (https://playwright.dev/docs/actionability#visible)\nStable (https://playwright.dev/docs/actionability#stable)\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\nEnabled (https://playwright.dev/docs/actionability#enabled)\nEditable (https://playwright.dev/docs/actionability#editable)\nlocator.check() (https://playwright.dev/docs/api/class-locator#locator-check)\nYes\nYes\nYes\nYes\n-\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nYes\nYes\nYes\nYes\n-\nlocator.dblclick() (https://playwright.dev/docs/api/class-locator#locator-dblclick)\nYes\nYes\nYes\nYes\n-\nlocator.setChecked() (https://playwright.dev/docs/api/class-locator#locator-set-checked)\nYes\nYes\nYes\nYes\n-\nlocator.tap() (https://playwright.dev/docs/api/class-locator#locator-tap)\nYes\nYes\nYes\nYes\n-\nlocator.uncheck() (https://playwright.dev/docs/api/class-locator#locator-uncheck)\nYes\nYes\nYes\nYes\n-\nlocator.hover() (https://playwright.dev/docs/api/class-locator#locator-hover)\nYes\nYes\nYes\n-\n-\nlocator.dragTo() (https://playwright.dev/docs/api/class-locator#locator-drag-to)\nYes\nYes\nYes\n-\n-\nlocator.screenshot() (https://playwright.dev/docs/api/class-locator#locator-screenshot)\nYes\nYes\n-\n-\n-\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\nYes\n-\n-\nYes\nYes\nlocator.clear() (https://playwright.dev/docs/api/class-locator#locator-clear)\nYes\n-\n-\nYes\nYes\nlocator.selectOption() (https://playwright.dev/docs/api/class-locator#locator-select-option)\nYes\n-\n-\nYes\n-\nlocator.selectText() (https://playwright.dev/docs/api/class-locator#locator-select-text)\nYes\n-\n-\n-\n-\nlocator.scrollIntoViewIfNeeded() (https://playwright.dev/docs/api/class-locator#locator-scroll-into-view-if-needed)\n-\nYes\n-\n-\n-\nlocator.blur() (https://playwright.dev/docs/api/class-locator#locator-blur)\n-\n-\n-\n-\n-\nlocator.dispatchEvent() (https://playwright.dev/docs/api/class-locator#locator-dispatch-event)\n-\n-\n-\n-\n-\nlocator.focus() (https://playwright.dev/docs/api/class-locator#locator-focus)\n-\n-\n-\n-\n-\nlocator.press() (https://playwright.dev/docs/api/class-locator#locator-press)\n-\n-\n-\n-\n-\nlocator.pressSequentially() (https://playwright.dev/docs/api/class-locator#locator-press-sequentially)\n-\n-\n-\n-\n-\nlocator.setInputFiles() (https://playwright.dev/docs/api/class-locator#locator-set-input-files)\n-\n-\n-\n-\n-', "Performs a simple human click.\n\n```\n`// Generic clickawaitpage.getByRole('button').click();// Double clickawaitpage.getByText('Item').dblclick();// Right clickawaitpage.getByText('Item').click({button:'right'});// Shift + clickawaitpage.getByText('Item').click({modifiers:['Shift']});// Ctrl + click on Windows and Linux// Meta + click on macOSawaitpage.getByText('Item').click({modifiers:['ControlOrMeta']});// Hover over elementawaitpage.getByText('Item').hover();// Click the top left cornerawaitpage.getByText('Item').click({position:{x:0,y:0}});`\n```\n\nUnder the hood, this and other pointer-related methods:\n\nwait for element with given selector to be in DOM\nwait for it to become displayed, i.e. not empty, no\n`display:none`\n, no\n`visibility:hidden`\nwait for it to stop moving, for example, until css transition finishes\nscroll the element into view\nwait for it to receive pointer events at the action point, for example, waits until element becomes non-obscured by other elements\nretry if the element is detached during any of the above checks"]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1021,12 +1044,8 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>If your selector matches several elements, Playwright throws an exception when you perform an operation that implies a single target DOM element, such as `.click()` [1, 2].
-To resolve this, you can use the following methods to explicitly select a single element, though these are not recommended as they may lead to unintended clicks if the page changes:
-*   `locator.first()`
-*   `locator.last()`
-*   `locator.nth()`
-The documentation recommends instead creating a locator that uniquely identifies the target element [3].</t>
+          <t>If your selector matches several elements, Playwright will throw an exception when you attempt to click. This is because locators are strict, and operations that imply a target DOM element require the locator to resolve to exactly one element.
+To resolve this, you should follow best practices to create a locator that uniquely identifies the target element. While you can explicitly opt-out of strictness using `locator.first()`, `locator.last()`, or `locator.nth()`, these methods are not recommended because page changes may cause Playwright to click on an unintended element.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1035,28 +1054,28 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.007848999999999001</v>
+        <v>0.0007285</v>
       </c>
       <c r="G11" t="n">
-        <v>30286</v>
+        <v>48071</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.33</v>
+        <v>0.8</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0641025641025641</v>
+        <v>0.1222222222222222</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8333333332916666</v>
+        <v>0.8055555555287036</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
@@ -1070,7 +1089,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['Selectors | Playwright\n\nSelectors can be used to install custom selector engines. See\nextensibility (https://playwright.dev/docs/extensibility)\nfor more information.', 'Added in: v1.27\n\nselectors.setTestIdAttribute\n\nDefines custom attribute name to be used in\npage.getByTestId() (https://playwright.dev/docs/api/class-page#page-get-by-test-id)\n.\n`data-testid`\nis used by default.\n\nUsage\n\n```\n`selectors.setTestIdAttribute(attributeName);`\n```\n\nArguments\n\n`attributeName`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-selectors#selectors-set-test-id-attribute-option-attribute-name)\nTest id attribute name.']</t>
+          <t>['Added in: v1.27\n\nselectors.setTestIdAttribute\n\nDefines custom attribute name to be used in\npage.getByTestId() (https://playwright.dev/docs/api/class-page#page-get-by-test-id)\n.\n`data-testid`\nis used by default.\n\nUsage\n\n```\n`selectors.setTestIdAttribute(attributeName);`\n```\n\nArguments\n\n`attributeName`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-selectors#selectors-set-test-id-attribute-option-attribute-name)\nTest id attribute name.', 'By default,\npage.getByTestId() (https://playwright.dev/docs/api/class-page#page-get-by-test-id)\nwill locate elements based on the\n`data-testid`\nattribute, but you can configure it in your test config or by calling\nselectors.setTestIdAttribute() (https://playwright.dev/docs/api/class-selectors#selectors-set-test-id-attribute)\n.\n\nSet the test id to use a custom data attribute for your tests.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{testIdAttribute:\'data-pw\'}});`\n```\n\nIn your html you can now use\n`data-pw`\nas your test id instead of the default\n`data-testid`\n.\n\nhttp://localhost:3000\nItinéraire\n```\n`&lt;buttondata-pw="directions"&gt;Itinéraire&lt;/button&gt;`\n```\n\nAnd then locate the element as you would normally do:\n\n```\n`awaitpage.getByTestId(\'directions\').click();`\n```', 'Testing by test ids is the most resilient way of testing as even if your text or role of the attribute changes, the test will still pass. QA\'s and developers should define explicit test ids and query them with\npage.getByTestId() (https://playwright.dev/docs/api/class-page#page-get-by-test-id)\n. However testing by test ids is not user facing. If the role or text value is important to you then consider using user facing locators such as\nrole (https://playwright.dev/docs/locators#locate-by-role)\nand\ntext locators (https://playwright.dev/docs/locators#locate-by-text)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nItinéraire\n```\n`&lt;buttondata-testid="directions"&gt;Itinéraire&lt;/button&gt;`\n```\n\nYou can locate the element by its test id:\n\n```\n`awaitpage.getByTestId(\'directions\').click();`\n```\n\nWhen to use testid locators\nYou can also use test ids when you choose to use the test id methodology or when you can\'t locate by\nrole (https://playwright.dev/docs/locators#locate-by-role)\nor\ntext (https://playwright.dev/docs/locators#locate-by-text)\n.', 'warning\nWe recommend\nlocating by test id (https://playwright.dev/docs/locators#locate-by-test-id)\ninstead.\n\nPlaywright supports shorthand for selecting elements using certain attributes. Currently, only the following attributes are supported:\n\n`id`\n`data-testid`\n`data-test-id`\n`data-test`\n\n```\n`// Fill an input with the id "username"awaitpage.locator(\'id=username\').fill(\'value\');// Click an element with data-test-id "submit"awaitpage.locator(\'data-test-id=submit\').click();`\n```\n\nnote\nAttribute selectors are not CSS selectors, so anything CSS-specific like\n`:enabled`\nis not supported. For more features, use a proper\ncss (https://playwright.dev/docs/other-locators#css-locator)\nselector, e.g.\n`css=[data-test="login"]:enabled`\n.']</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1080,8 +1099,21 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>By default, `getByTestId` reads the `data-testid` attribute [2].
-You can point it at a different attribute by using `selectors.setTestIdAttribute(attributeName)`, where `attributeName` is the string name of the custom attribute you wish to use [2].</t>
+          <t>`getByTestId` uses the `data-testid` attribute by default.
+You can point it at a different attribute using one of the following methods:
+*   **In your test configuration (Recommended):** Set the `testIdAttribute` property in your `playwright.config.ts` file:
+    ```typescript
+    import { defineConfig } from '@playwright/test';
+    export default defineConfig({
+      use: {
+        testIdAttribute: 'data-pw'
+      }
+    });
+    ```
+*   **Programmatically:** Call `selectors.setTestIdAttribute(attributeName)` with the desired attribute name:
+    ```typescript
+    selectors.setTestIdAttribute('data-pw');
+    ```</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1090,28 +1122,28 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.00744225</v>
+        <v>0.000634</v>
       </c>
       <c r="G12" t="n">
-        <v>28899</v>
+        <v>35147</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="J12" t="n">
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1891891891891892</v>
+        <v>0.1846153846153846</v>
       </c>
       <c r="L12" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="M12" t="n">
-        <v>0.49999999995</v>
+        <v>0.99999999995</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
@@ -1125,7 +1157,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>['Actions | Playwright', "Using\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\nis the easiest way to fill out the form fields. It focuses the element and triggers an\n`input`\nevent with the entered text. It works for\n`&lt;input&gt;`\n,\n`&lt;textarea&gt;`\nand\n`[contenteditable]`\nelements.\n\n```\n`// Text inputawaitpage.getByRole('textbox').fill('Peter');// Date inputawaitpage.getByLabel('Birth date').fill('2020-02-02');// Time inputawaitpage.getByLabel('Appointment time').fill('13:15');// Local datetime inputawaitpage.getByLabel('Local time').fill('2020-03-02T05:15');`\n```"]</t>
+          <t>["Using\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\nis the easiest way to fill out the form fields. It focuses the element and triggers an\n`input`\nevent with the entered text. It works for\n`&lt;input&gt;`\n,\n`&lt;textarea&gt;`\nand\n`[contenteditable]`\nelements.\n\n```\n`// Text inputawaitpage.getByRole('textbox').fill('Peter');// Date inputawaitpage.getByLabel('Birth date').fill('2020-02-02');// Time inputawaitpage.getByLabel('Appointment time').fill('13:15');// Local datetime inputawaitpage.getByLabel('Local time').fill('2020-03-02T05:15');`\n```", "Added in: v1.14\n\nlocator.fill\n\nSet a value to the input field.\n\nUsage\n\n```\n`awaitpage.getByRole('textbox').fill('example value');`\n```\n\nArguments\n\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-locator#locator-fill-option-value)\nValue to set for the\n`&lt;input&gt;`\n,\n`&lt;textarea&gt;`\nor\n`[contenteditable]`\nelement.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`force`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-fill-option-force)\nWhether to bypass the\nactionability (https://playwright.dev/docs/actionability)\nchecks. Defaults to\n`false`\n.\n`noWaitAfter`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-fill-option-no-wait-after)\nDeprecated\nThis option has no effect.\nThis option has no effect.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-fill-option-timeout)\nMaximum time in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`actionTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-fill-return)\n\nDetails\n\nThis method waits for\nactionability (https://playwright.dev/docs/actionability)\nchecks, focuses the element, fills it and triggers an\n`input`\nevent after filling. Note that you can pass an empty string to clear the input field.\n\nIf the target element is not an\n`&lt;input&gt;`\n,\n`&lt;textarea&gt;`\nor\n`[contenteditable]`\nelement, this method throws an error. However, if the element is inside the\n`&lt;label&gt;`\nelement that has an associated\ncontrol (https://developer.mozilla.org/en-US/docs/Web/API/HTMLLabelElement/control)\n, the control will be filled instead.\n\nTo send fine-grained keyboard events, use\nlocator.pressSequentially() (https://playwright.dev/docs/api/class-locator#locator-press-sequentially)\n.", "caution\nMost of the time, you should input text with\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\n. See the\nText input (https://playwright.dev/docs/input#text-input)\nsection above. You only need to type characters if there is special keyboard handling on the page.\n\nType into the field character by character, as if it was a user with a real keyboard with\nlocator.pressSequentially() (https://playwright.dev/docs/api/class-locator#locator-press-sequentially)\n.\n\n```\n`// Press keys one by oneawaitpage.locator('#area').pressSequentially('Hello World!');`\n```\n\nThis method will emit all the necessary keyboard events, with all the\n`keydown`\n,\n`keyup`\n,\n`keypress`\nevents in place. You can even specify the optional\n`delay`\nbetween the key presses to simulate real user behavior.", 'Added in: v1.14\n\nlocator.type\n\nDeprecated\nIn most cases, you should use\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\ninstead. You only need to press keys one by one if there is special keyboard handling on the page - in this case use\nlocator.pressSequentially() (https://playwright.dev/docs/api/class-locator#locator-press-sequentially)\n.\n\nFocuses the element, and then sends a\n`keydown`\n,\n`keypress`\n/\n`input`\n, and\n`keyup`\nevent for each character in the text.\n\nTo press a special key, like\n`Control`\nor\n`ArrowDown`\n, use\nlocator.press() (https://playwright.dev/docs/api/class-locator#locator-press)\n.\n\nUsage\n\nArguments\n\n`text`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-locator#locator-type-option-text)\nA text to type into a focused element.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`delay`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-type-option-delay)\nTime to wait between key presses in milliseconds. Defaults to 0.\n`noWaitAfter`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-type-option-no-wait-after)\nDeprecated\nThis option has no effect.\nThis option has no effect.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-type-option-timeout)\nMaximum time in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`actionTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-type-return)', 'Added before v1.9\n\npage.fill\n\nDiscouraged\nUse locator-based\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\ninstead. Read more about\nlocators (https://playwright.dev/docs/locators)\n.\n\nThis method waits for an element matching\nselector (https://playwright.dev/docs/api/class-page#page-fill-option-selector)\n, waits for\nactionability (https://playwright.dev/docs/actionability)\nchecks, focuses the element, fills it and triggers an\n`input`\nevent after filling. Note that you can pass an empty string to clear the input field.\n\nIf the target element is not an\n`&lt;input&gt;`\n,\n`&lt;textarea&gt;`\nor\n`[contenteditable]`\nelement, this method throws an error. However, if the element is inside the\n`&lt;label&gt;`\nelement that has an associated\ncontrol (https://developer.mozilla.org/en-US/docs/Web/API/HTMLLabelElement/control)\n, the control will be filled instead.\n\nTo send fine-grained keyboard events, use\nlocator.pressSequentially() (https://playwright.dev/docs/api/class-locator#locator-press-sequentially)\n.\n\nUsage\n\n```\n`awaitpage.fill(selector,value);awaitpage.fill(selector,value,options);`\n```\n\nArguments\n\n`selector`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-page#page-fill-option-selector)\nA selector to search for an element. If there are multiple elements satisfying the selector, the first will be used.\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-page#page-fill-option-value)\nValue to fill for the\n`&lt;input&gt;`\n,\n`&lt;textarea&gt;`\nor\n`[contenteditable]`\nelement.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`force`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.13\n# (https://playwright.dev/docs/api/class-page#page-fill-option-force)\nWhether to bypass the\nactionability (https://playwright.dev/docs/actionability)\nchecks. Defaults to\n`false`\n.\n`noWaitAfter`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-fill-option-no-wait-after)\nDeprecated\nThis option has no effect.\nThis option has no effect.\n`strict`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.14\n# (https://playwright.dev/docs/api/class-page#page-fill-option-strict)\nWhen true, the call requires selector to resolve to a single element. If given selector resolves to more than one element, the call throws an exception.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-fill-option-timeout)\nMaximum time in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`actionTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-page#page-fill-return)', "Added in: v1.38\n\nlocator.pressSequentially\n\ntip\nIn most cases, you should use\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\ninstead. You only need to press keys one by one if there is special keyboard handling on the page.\n\nFocuses the element, and then sends a\n`keydown`\n,\n`keypress`\n/\n`input`\n, and\n`keyup`\nevent for each character in the text.\n\nTo press a special key, like\n`Control`\nor\n`ArrowDown`\n, use\nlocator.press() (https://playwright.dev/docs/api/class-locator#locator-press)\n.\n\nUsage\n\n```\n`awaitlocator.pressSequentially('Hello');// Types instantlyawaitlocator.pressSequentially('World',{delay:100});// Types slower, like a user`\n```\n\nAn example of typing into a text field and then submitting the form:\n\n```\n`constlocator=page.getByLabel('Password');awaitlocator.pressSequentially('my password');awaitlocator.press('Enter');`\n```\n\nArguments\n\n`text`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-locator#locator-press-sequentially-option-text)\nString of characters to sequentially press into a focused element.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`delay`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-press-sequentially-option-delay)\nTime to wait between key presses in milliseconds. Defaults to 0.\n`noWaitAfter`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-press-sequentially-option-no-wait-after)\nDeprecated\nThis option has no effect.\nThis option has no effect.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-press-sequentially-option-timeout)\nMaximum time in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`actionTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-press-sequentially-return)", "Added before v1.9\n\nkeyboard.type\n\ncaution\nIn most cases, you should use\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\ninstead. You only need to press keys one by one if there is special keyboard handling on the page - in this case use\nlocator.pressSequentially() (https://playwright.dev/docs/api/class-locator#locator-press-sequentially)\n.\n\nSends a\n`keydown`\n,\n`keypress`\n/\n`input`\n, and\n`keyup`\nevent for each character in the text.\n\nTo press a special key, like\n`Control`\nor\n`ArrowDown`\n, use\nkeyboard.press() (https://playwright.dev/docs/api/class-keyboard#keyboard-press)\n.\n\nUsage\n\n```\n`awaitpage.keyboard.type('Hello');// Types instantlyawaitpage.keyboard.type('World',{delay:100});// Types slower, like a user`\n```\n\nnote\nModifier keys DO NOT effect\n`keyboard.type`\n. Holding down\n`Shift`\nwill not type the text in upper case.\n\nnote\nFor characters that are not on a US keyboard, only an\n`input`\nevent will be sent.\n\nArguments\n\n`text`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-keyboard#keyboard-type-option-text)\nA text to type into a focused element.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`delay`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-keyboard#keyboard-type-option-delay)\nTime to wait between key presses in milliseconds. Defaults to 0.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-keyboard#keyboard-type-return)"]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1135,7 +1167,8 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>The simplest way to enter text into a form field is using `locator.fill()`. This method also covers `&lt;textarea&gt;` and `[contenteditable]` elements.</t>
+          <t>The simplest way to enter text into a form field is using `locator.fill()`. 
+Yes, this method covers `&lt;input&gt;`, `&lt;textarea&gt;`, and `[contenteditable]` elements.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1144,28 +1177,28 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.007316</v>
+        <v>0.001314</v>
       </c>
       <c r="G13" t="n">
-        <v>28709</v>
+        <v>54715</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.44</v>
+        <v>0.67</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="M13" t="n">
-        <v>0.49999999995</v>
+        <v>0.9266666666481335</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
@@ -1179,7 +1212,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['Actions | Playwright']</t>
+          <t>["Using\nlocator.setChecked() (https://playwright.dev/docs/api/class-locator#locator-set-checked)\nis the easiest way to check and uncheck a checkbox or a radio button. This method can be used with\n`input[type=checkbox]`\n,\n`input[type=radio]`\nand\n`[role=checkbox]`\nelements.\n\n```\n`// Check the checkboxawaitpage.getByLabel('I agree to the terms above').check();// Assert the checked stateexpect(page.getByLabel('Subscribe to newsletter')).toBeChecked();// Select the radio buttonawaitpage.getByLabel('XL').check();`\n```", "Added in: v1.14\n\nlocator.check\n\nEnsure that checkbox or radio element is checked.\n\nUsage\n\n```\n`awaitpage.getByRole('checkbox').check();`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`force`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-check-option-force)\nWhether to bypass the\nactionability (https://playwright.dev/docs/actionability)\nchecks. Defaults to\n`false`\n.\n`noWaitAfter`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-check-option-no-wait-after)\nDeprecated\nThis option has no effect.\nThis option has no effect.\n`position`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-check-option-position)\n`x`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n`y`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\nA point to use relative to the top-left corner of element padding box. If not specified, uses some visible point of the element.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-check-option-timeout)\nMaximum time in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`actionTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n`trial`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-check-option-trial)\nWhen set, this method only performs the\nactionability (https://playwright.dev/docs/actionability)\nchecks and skips the action. Defaults to\n`false`\n. Useful to wait until the element is ready for the action without performing it.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-check-return)\n\nDetails\n\nPerforms the following steps:\n\nEnsure that element is a checkbox or a radio input. If not, this method throws. If the element is already checked, this method returns immediately.\nWait for\nactionability (https://playwright.dev/docs/actionability)\nchecks on the element, unless\nforce (https://playwright.dev/docs/api/class-locator#locator-check-option-force)\noption is set.\nScroll the element into view if needed.\nUse\npage.mouse (https://playwright.dev/docs/api/class-page#page-mouse)\nto click in the center of the element.\nEnsure that the element is now checked. If not, this method throws.\n\nIf the element is detached from the DOM at any moment during the action, this method throws.\n\nWhen all steps combined have not finished during the specified\ntimeout (https://playwright.dev/docs/api/class-locator#locator-check-option-timeout)\n, this method throws a\nTimeoutError (https://playwright.dev/docs/api/class-timeouterror)\n. Passing zero timeout disables this.", "Added in: v1.15\n\nlocator.setChecked\n\nSet the state of a checkbox or a radio element.\n\nUsage\n\n```\n`awaitpage.getByRole('checkbox').setChecked(true);`\n```\n\nArguments\n\n`checked`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n# (https://playwright.dev/docs/api/class-locator#locator-set-checked-option-checked)\nWhether to check or uncheck the checkbox.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`force`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-set-checked-option-force)\nWhether to bypass the\nactionability (https://playwright.dev/docs/actionability)\nchecks. Defaults to\n`false`\n.\n`noWaitAfter`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-set-checked-option-no-wait-after)\nDeprecated\nThis option has no effect.\nThis option has no effect.\n`position`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-set-checked-option-position)\n`x`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n`y`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\nA point to use relative to the top-left corner of element padding box. If not specified, uses some visible point of the element.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-set-checked-option-timeout)\nMaximum time in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`actionTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n`trial`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-set-checked-option-trial)\nWhen set, this method only performs the\nactionability (https://playwright.dev/docs/actionability)\nchecks and skips the action. Defaults to\n`false`\n. Useful to wait until the element is ready for the action without performing it.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-set-checked-return)\n\nDetails\n\nThis method checks or unchecks an element by performing the following steps:\n\nEnsure that matched element is a checkbox or a radio input. If not, this method throws.\nIf the element already has the right checked state, this method returns immediately.\nWait for\nactionability (https://playwright.dev/docs/actionability)\nchecks on the matched element, unless\nforce (https://playwright.dev/docs/api/class-locator#locator-set-checked-option-force)\noption is set. If the element is detached during the checks, the whole action is retried.\nScroll the element into view if needed.\nUse\npage.mouse (https://playwright.dev/docs/api/class-page#page-mouse)\nto click in the center of the element.\nEnsure that the element is now checked or unchecked. If not, this method throws.\n\nWhen all steps combined have not finished during the specified\ntimeout (https://playwright.dev/docs/api/class-locator#locator-set-checked-option-timeout)\n, this method throws a\nTimeoutError (https://playwright.dev/docs/api/class-timeouterror)\n. Passing zero timeout disables this.", "Added in: v1.14\n\nlocator.uncheck\n\nEnsure that checkbox or radio element is unchecked.\n\nUsage\n\n```\n`awaitpage.getByRole('checkbox').uncheck();`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`force`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-uncheck-option-force)\nWhether to bypass the\nactionability (https://playwright.dev/docs/actionability)\nchecks. Defaults to\n`false`\n.\n`noWaitAfter`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-uncheck-option-no-wait-after)\nDeprecated\nThis option has no effect.\nThis option has no effect.\n`position`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-uncheck-option-position)\n`x`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n`y`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\nA point to use relative to the top-left corner of element padding box. If not specified, uses some visible point of the element.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-uncheck-option-timeout)\nMaximum time in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`actionTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n`trial`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-uncheck-option-trial)\nWhen set, this method only performs the\nactionability (https://playwright.dev/docs/actionability)\nchecks and skips the action. Defaults to\n`false`\n. Useful to wait until the element is ready for the action without performing it.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-uncheck-return)\n\nDetails\n\nThis method unchecks the element by performing the following steps:\n\nEnsure that element is a checkbox or a radio input. If not, this method throws. If the element is already unchecked, this method returns immediately.\nWait for\nactionability (https://playwright.dev/docs/actionability)\nchecks on the element, unless\nforce (https://playwright.dev/docs/api/class-locator#locator-uncheck-option-force)\noption is set.\nScroll the element into view if needed.\nUse\npage.mouse (https://playwright.dev/docs/api/class-page#page-mouse)\nto click in the center of the element.\nEnsure that the element is now unchecked. If not, this method throws.\n\nIf the element is detached from the DOM at any moment during the action, this method throws.\n\nWhen all steps combined have not finished during the specified\ntimeout (https://playwright.dev/docs/api/class-locator#locator-uncheck-option-timeout)\n, this method throws a\nTimeoutError (https://playwright.dev/docs/api/class-timeouterror)\n. Passing zero timeout disables this.", "Added in: v1.14\n\nlocator.isChecked\n\nReturns whether the element is checked. Throws if the element is not a checkbox or radio input.\n\nAsserting checked state\nIf you need to assert that checkbox is checked, prefer\nexpect(locator).toBeChecked() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-checked)\nto avoid flakiness. See\nassertions guide (https://playwright.dev/docs/test-assertions)\nfor more details.\n\nUsage\n\n```\n`constchecked=awaitpage.getByRole('checkbox').isChecked();`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-is-checked-option-timeout)\nMaximum time in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`actionTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-is-checked-return)", 'Added in: v1.27\n\nlocator.getByRole\n\nAllows locating elements by their\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n.\n\nUsage\n\nConsider the following DOM structure.\n\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nArguments\n\n`role`\n"alert" | "alertdialog" | "application" | "article" | "banner" | "blockquote" | "button" | "caption" | "cell" | "checkbox" | "code" | "columnheader" | "combobox" | "complementary" | "contentinfo" | "definition" | "deletion" | "dialog" | "directory" | "document" | "emphasis" | "feed" | "figure" | "form" | "generic" | "grid" | "gridcell" | "group" | "heading" | "img" | "insertion" | "link" | "list" | "listbox" | "listitem" | "log" | "main" | "marquee" | "math" | "meter" | "menu" | "menubar" | "menuitem" | "menuitemcheckbox" | "menuitemradio" | "navigation" | "none" | "note" | "option" | "paragraph" | "presentation" | "progressbar" | "radio" | "radiogroup" | "region" | "row" | "rowgroup" | "rowheader" | "scrollbar" | "search" | "searchbox" | "separator" | "slider" | "spinbutton" | "status" | "strong" | "subscript" | "superscript" | "switch" | "tab" | "table" | "tablist" | "tabpanel" | "term" | "textbox" | "time" | "timer" | "toolbar" | "tooltip" | "tree" | "treegrid" | "treeitem"\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-role)\nRequired aria role.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`checked`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-checked)\nAn attribute that is usually set by\n`aria-checked`\nor native\n`&lt;input type=checkbox&gt;`\ncontrols.\nLearn more about\naria-checked (https://www.w3.org/TR/wai-aria-1.2/#aria-checked)\n.\n`description`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n(optional)\nAdded in: v1.60\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-description)\nOption to match the\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\n. By default, matching is case-insensitive and searches for a substring, use\nexact (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-exact)\nto control this behavior.\nLearn more about\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\n.\n`disabled`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-disabled)\nAn attribute that is usually set by\n`aria-disabled`\nor\n`disabled`\n.\nnote\nUnlike most other attributes,\n`disabled`\nis inherited through the DOM hierarchy. Learn more about\naria-disabled (https://www.w3.org/TR/wai-aria-1.2/#aria-disabled)\n.\n`exact`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.28\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-exact)\nWhether\nname (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-name)\nand\ndescription (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-description)\nare matched exactly: case-sensitive and whole-string. Defaults to false. Ignored when the value is a regular expression. Note that exact match still trims whitespace.\n`expanded`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-expanded)\nAn attribute that is usually set by\n`aria-expanded`\n.\nLearn more about\naria-expanded (https://www.w3.org/TR/wai-aria-1.2/#aria-expanded)\n.\n`includeHidden`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-include-hidden)\nOption that controls whether hidden elements are matched. By default, only non-hidden elements, as\ndefined by ARIA (https://www.w3.org/TR/wai-aria-1.2/#tree_exclusion)\n, are matched by role selector.\nLearn more about\naria-hidden (https://www.w3.org/TR/wai-aria-1.2/#aria-hidden)\n.\n`level`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-level)\nA number attribute that is usually present for roles\n`heading`\n,\n`listitem`\n,\n`row`\n,\n`treeitem`\n, with default values for\n`&lt;h1&gt;-&lt;h6&gt;`\nelements.\nLearn more about\naria-level (https://www.w3.org/TR/wai-aria-1.2/#aria-level)\n.\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-name)\nOption to match the\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. By default, matching is case-insensitive and searches for a substring, use\nexact (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-exact)\nto control this behavior.\nLearn more about\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n.\n`pressed`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-pressed)\nAn attribute that is usually set by\n`aria-pressed`\n.\nLearn more about\naria-pressed (https://www.w3.org/TR/wai-aria-1.2/#aria-pressed)\n.\n`selected`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-option-selected)\nAn attribute that is usually set by\n`aria-selected`\n.\nLearn more about\naria-selected (https://www.w3.org/TR/wai-aria-1.2/#aria-selected)\n.\n\nReturns\n\nLocator (https://playwright.dev/docs/api/class-locator)\n# (https://playwright.dev/docs/api/class-locator#locator-get-by-role-return)\n\nDetails\n\nRole selector\ndoes not replace\naccessibility audits and conformance tests, but rather gives early feedback about the ARIA guidelines.\n\nMany html elements have an implicitly\ndefined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role selector. You can find all the\nsupported roles here (https://www.w3.org/TR/wai-aria-1.2/#role_definitions)\n. ARIA guidelines\ndo not recommend\nduplicating implicit roles and attributes by setting\n`role`\nand/or\n`aria-*`\nattributes to default values.', 'Added before v1.9\n\npage.check\n\nDiscouraged\nUse locator-based\nlocator.check() (https://playwright.dev/docs/api/class-locator#locator-check)\ninstead. Read more about\nlocators (https://playwright.dev/docs/locators)\n.\n\nThis method checks an element matching\nselector (https://playwright.dev/docs/api/class-page#page-check-option-selector)\nby performing the following steps:\n\nFind an element matching\nselector (https://playwright.dev/docs/api/class-page#page-check-option-selector)\n. If there is none, wait until a matching element is attached to the DOM.\nEnsure that matched element is a checkbox or a radio input. If not, this method throws. If the element is already checked, this method returns immediately.\nWait for\nactionability (https://playwright.dev/docs/actionability)\nchecks on the matched element, unless\nforce (https://playwright.dev/docs/api/class-page#page-check-option-force)\noption is set. If the element is detached during the checks, the whole action is retried.\nScroll the element into view if needed.\nUse\npage.mouse (https://playwright.dev/docs/api/class-page#page-mouse)\nto click in the center of the element.\nEnsure that the element is now checked. If not, this method throws.\n\nWhen all steps combined have not finished during the specified\ntimeout (https://playwright.dev/docs/api/class-page#page-check-option-timeout)\n, this method throws a\nTimeoutError (https://playwright.dev/docs/api/class-timeouterror)\n. Passing zero timeout disables this.\n\nUsage\n\n```\n`awaitpage.check(selector);awaitpage.check(selector,options);`\n```\n\nArguments\n\n`selector`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-page#page-check-option-selector)\nA selector to search for an element. If there are multiple elements satisfying the selector, the first will be used.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`force`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-check-option-force)\nWhether to bypass the\nactionability (https://playwright.dev/docs/actionability)\nchecks. Defaults to\n`false`\n.\n`noWaitAfter`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-check-option-no-wait-after)\nDeprecated\nThis option has no effect.\nThis option has no effect.\n`position`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\nAdded in: v1.11\n# (https://playwright.dev/docs/api/class-page#page-check-option-position)\n`x`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n`y`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\nA point to use relative to the top-left corner of element padding box. If not specified, uses some visible point of the element.\n`strict`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.14\n# (https://playwright.dev/docs/api/class-page#page-check-option-strict)\nWhen true, the call requires selector to resolve to a single element. If given selector resolves to more than one element, the call throws an exception.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-check-option-timeout)\nMaximum time in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`actionTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n`trial`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.11\n# (https://playwright.dev/docs/api/class-page#page-check-option-trial)\nWhen set, this method only performs the\nactionability (https://playwright.dev/docs/actionability)\nchecks and skips the action. Defaults to\n`false`\n. Useful to wait until the element is ready for the action without performing it.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-page#page-check-return)']</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1189,7 +1222,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>I don't know. The provided documentation excerpt only contains the title "Actions | Playwright" and does not provide information on how to tick a checkbox or pick a radio button.</t>
+          <t>The easiest way to check or uncheck a checkbox or radio button is to use `locator.setChecked()`. This method allows you to set the state by passing a boolean:
+```javascript
+await page.getByRole('checkbox').setChecked(true);
+```
+Alternatively, you can use `locator.check()` to ensure an element is checked, or `locator.uncheck()` to ensure it is unchecked.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1198,31 +1235,31 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.00653975</v>
+        <v>0.00218975</v>
       </c>
       <c r="G14" t="n">
-        <v>25784</v>
+        <v>61776</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="L14" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>0.9999999999666667</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1233,7 +1270,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['Actions | Playwright']</t>
+          <t>["Selects one or multiple options in the\n`&lt;select&gt;`\nelement with\nlocator.selectOption() (https://playwright.dev/docs/api/class-locator#locator-select-option)\n. You can specify option\n`value`\n, or\n`label`\nto select. Multiple options can be selected.\n\n```\n`// Single selection matching the value or labelawaitpage.getByLabel('Choose a color').selectOption('blue');// Single selection matching the labelawaitpage.getByLabel('Choose a color').selectOption({label:'Blue'});// Multiple selected itemsawaitpage.getByLabel('Choose multiple colors').selectOption(['red','green','blue']);`\n```", 'Playwright can interact with HTML Input elements such as text inputs, checkboxes, radio buttons, select options, mouse clicks, type characters, keys and shortcuts as well as upload files and focus elements.']</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1243,7 +1280,13 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>I don't know. The provided documentation excerpt only contains the title "Actions | Playwright" and does not contain information regarding how to choose options in a `&lt;select&gt;` element or whether multiple selections are possible.</t>
+          <t>To choose an option in a `&lt;select&gt;` element, use the `locator.selectOption()` method. You can specify the option by its `value` or `label`.
+**Examples for single selection:**
+*   Matching by value or label: `await page.getByLabel('Choose a color').selectOption('blue');`
+*   Matching by label: `await page.getByLabel('Choose a color').selectOption({ label: 'Blue' });`
+**Selecting multiple options:**
+Yes, you can pick several options at once by passing an array to `selectOption()`.
+*   Example: `await page.getByLabel('Choose multiple colors').selectOption(['red', 'green', 'blue']);`</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1252,31 +1295,31 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.006550250000000001</v>
+        <v>0.0004055</v>
       </c>
       <c r="G15" t="n">
-        <v>25796</v>
+        <v>30149</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1470588235294118</v>
+        <v>0.125</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.9999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1287,7 +1330,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>["Dialog | Playwright\n\nDialog (https://playwright.dev/docs/api/class-dialog)\nobjects are dispatched by page via the\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nevent.\n\nAn example of using\n`Dialog`\nclass:\n\n```\n`const{chromium}=require('playwright');// Or 'firefox' or 'webkit'.(async()=&gt;{constbrowser=awaitchromium.launch();constpage=awaitbrowser.newPage();page.on('dialog',asyncdialog=&gt;{console.log(dialog.message());awaitdialog.dismiss();});awaitpage.evaluate(()=&gt;alert('1'));awaitbrowser.close();})();`\n```\n\nnote\nDialogs are dismissed automatically, unless there is a\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nlistener. When listener is present, it\nmust\neither\ndialog.accept() (https://playwright.dev/docs/api/class-dialog#dialog-accept)\nor\ndialog.dismiss() (https://playwright.dev/docs/api/class-dialog#dialog-dismiss)\nthe dialog - otherwise the page will\nfreeze (https://developer.mozilla.org/en-US/docs/Web/JavaScript/EventLoop#never_blocking)\nwaiting for the dialog, and actions like click will never finish.", "By default, dialogs are auto-dismissed by Playwright, so you don't have to handle them. However, you can register a dialog handler before the action that triggers the dialog to either\ndialog.accept() (https://playwright.dev/docs/api/class-dialog#dialog-accept)\nor\ndialog.dismiss() (https://playwright.dev/docs/api/class-dialog#dialog-dismiss)\nit.\n\n```\n`page.on('dialog',dialog=&gt;dialog.accept());awaitpage.getByRole('button').click();`\n```\n\nnote\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nlistener\nmust handle\nthe dialog. Otherwise your action will stall, be it\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nor something else. That's because dialogs in Web are modals and therefore block further page execution until they are handled.\n\nAs a result, the following snippet will never resolve:\n\nwarning\nWRONG!\n\n```\n`page.on('dialog',dialog=&gt;console.log(dialog.message()));awaitpage.getByRole('button').click();// Will hang here`\n```\n\nnote\nIf there is no listener for\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\n, all dialogs are automatically dismissed.", 'Dialogs | Playwright']</t>
+          <t>["Dialog | Playwright\n\nDialog (https://playwright.dev/docs/api/class-dialog)\nobjects are dispatched by page via the\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nevent.\n\nAn example of using\n`Dialog`\nclass:\n\n```\n`const{chromium}=require('playwright');// Or 'firefox' or 'webkit'.(async()=&gt;{constbrowser=awaitchromium.launch();constpage=awaitbrowser.newPage();page.on('dialog',asyncdialog=&gt;{console.log(dialog.message());awaitdialog.dismiss();});awaitpage.evaluate(()=&gt;alert('1'));awaitbrowser.close();})();`\n```\n\nnote\nDialogs are dismissed automatically, unless there is a\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nlistener. When listener is present, it\nmust\neither\ndialog.accept() (https://playwright.dev/docs/api/class-dialog#dialog-accept)\nor\ndialog.dismiss() (https://playwright.dev/docs/api/class-dialog#dialog-dismiss)\nthe dialog - otherwise the page will\nfreeze (https://developer.mozilla.org/en-US/docs/Web/JavaScript/EventLoop#never_blocking)\nwaiting for the dialog, and actions like click will never finish.", "By default, dialogs are auto-dismissed by Playwright, so you don't have to handle them. However, you can register a dialog handler before the action that triggers the dialog to either\ndialog.accept() (https://playwright.dev/docs/api/class-dialog#dialog-accept)\nor\ndialog.dismiss() (https://playwright.dev/docs/api/class-dialog#dialog-dismiss)\nit.\n\n```\n`page.on('dialog',dialog=&gt;dialog.accept());awaitpage.getByRole('button').click();`\n```\n\nnote\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nlistener\nmust handle\nthe dialog. Otherwise your action will stall, be it\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nor something else. That's because dialogs in Web are modals and therefore block further page execution until they are handled.\n\nAs a result, the following snippet will never resolve:\n\nwarning\nWRONG!\n\n```\n`page.on('dialog',dialog=&gt;console.log(dialog.message()));awaitpage.getByRole('button').click();// Will hang here`\n```\n\nnote\nIf there is no listener for\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\n, all dialogs are automatically dismissed."]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1307,16 +1350,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.00724625</v>
+        <v>0.00044725</v>
       </c>
       <c r="G16" t="n">
-        <v>28270</v>
+        <v>29833</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I16" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="J16" t="n">
         <v>5</v>
@@ -1328,7 +1371,7 @@
         <v>0.4117647058823529</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9999999999666667</v>
+        <v>0.99999999995</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
@@ -1342,7 +1385,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>["Download | Playwright\n\nDownload (https://playwright.dev/docs/api/class-download)\nobjects are dispatched by page via the\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent.\n\nAll the downloaded files belonging to the browser context are deleted when the browser context is closed.\n\nDownload event is emitted once the download starts. Download path becomes available once download completes.\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", 'Downloads | Playwright', "For every attachment downloaded by the page,\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent is emitted. All these attachments are downloaded into a temporary folder. You can obtain the download url, file name and payload stream using the\nDownload (https://playwright.dev/docs/api/class-download)\nobject from the event.\n\nYou can specify where to persist downloaded files using the\ndownloadsPath (https://playwright.dev/docs/api/class-browsertype#browser-type-launch-option-downloads-path)\noption in\nbrowserType.launch() (https://playwright.dev/docs/api/class-browsertype#browser-type-launch)\n.\n\nnote\nDownloaded files are deleted when the browser context that produced them is closed.\n\nHere is the simplest way to handle the file download:\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", "Added before v1.9\n\ndownload.saveAs\n\nCopy the download to a user-specified path. It is safe to call this method while the download is still in progress. Will wait for the download to finish if necessary.\n\nUsage\n\n```\n`awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```\n\nArguments\n\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-download#download-save-as-option-path)\nPath where the download should be copied.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-download#download-save-as-return)", "If you have no idea what initiates the download, you can still handle the event:\n\n```\n`page.on('download',download=&gt;download.path().then(console.log));`\n```\n\nNote that handling the event forks the control flow and makes the script harder to follow. Your scenario might end while you are downloading a file since your main control flow is not awaiting for this operation to resolve.\n\nnote\nFor uploading files, see the\nuploading files (https://playwright.dev/docs/input#upload-files)\nsection.", "Added before v1.9\n\ndownload.path\n\nReturns path to the downloaded file for a successful download, or throws for a failed/canceled download. The method will wait for the download to finish if necessary. The method throws when connected remotely.\n\nNote that the download's file name is a random GUID, use\ndownload.suggestedFilename() (https://playwright.dev/docs/api/class-download#download-suggested-filename)\nto get suggested file name.\n\nUsage\n\n```\n`awaitdownload.path();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n# (https://playwright.dev/docs/api/class-download#download-path-return)", 'Added before v1.9\n\ndownload.suggestedFilename\n\nReturns suggested filename for this download. It is typically computed by the browser from the\nContent-Disposition (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Content-Disposition)\nresponse header or the\n`download`\nattribute. See the spec on\nwhatwg (https://html.spec.whatwg.org/#downloading-resources)\n. Different browsers can use different logic for computing it.\n\nUsage\n\n```\n`download.suggestedFilename();`\n```\n\nReturns\n\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-download#download-suggested-filename-return)']</t>
+          <t>["Download | Playwright\n\nDownload (https://playwright.dev/docs/api/class-download)\nobjects are dispatched by page via the\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent.\n\nAll the downloaded files belonging to the browser context are deleted when the browser context is closed.\n\nDownload event is emitted once the download starts. Download path becomes available once download completes.\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", "For every attachment downloaded by the page,\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent is emitted. All these attachments are downloaded into a temporary folder. You can obtain the download url, file name and payload stream using the\nDownload (https://playwright.dev/docs/api/class-download)\nobject from the event.\n\nYou can specify where to persist downloaded files using the\ndownloadsPath (https://playwright.dev/docs/api/class-browsertype#browser-type-launch-option-downloads-path)\noption in\nbrowserType.launch() (https://playwright.dev/docs/api/class-browsertype#browser-type-launch)\n.\n\nnote\nDownloaded files are deleted when the browser context that produced them is closed.\n\nHere is the simplest way to handle the file download:\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", "Added before v1.9\n\ndownload.saveAs\n\nCopy the download to a user-specified path. It is safe to call this method while the download is still in progress. Will wait for the download to finish if necessary.\n\nUsage\n\n```\n`awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```\n\nArguments\n\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-download#download-save-as-option-path)\nPath where the download should be copied.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-download#download-save-as-return)", "If you have no idea what initiates the download, you can still handle the event:\n\n```\n`page.on('download',download=&gt;download.path().then(console.log));`\n```\n\nNote that handling the event forks the control flow and makes the script harder to follow. Your scenario might end while you are downloading a file since your main control flow is not awaiting for this operation to resolve.\n\nnote\nFor uploading files, see the\nuploading files (https://playwright.dev/docs/input#upload-files)\nsection.", "Added before v1.9\n\ndownload.path\n\nReturns path to the downloaded file for a successful download, or throws for a failed/canceled download. The method will wait for the download to finish if necessary. The method throws when connected remotely.\n\nNote that the download's file name is a random GUID, use\ndownload.suggestedFilename() (https://playwright.dev/docs/api/class-download#download-suggested-filename)\nto get suggested file name.\n\nUsage\n\n```\n`awaitdownload.path();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n# (https://playwright.dev/docs/api/class-download#download-path-return)", 'Added before v1.9\n\ndownload.suggestedFilename\n\nReturns suggested filename for this download. It is typically computed by the browser from the\nContent-Disposition (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Content-Disposition)\nresponse header or the\n`download`\nattribute. See the spec on\nwhatwg (https://html.spec.whatwg.org/#downloading-resources)\n. Different browsers can use different logic for computing it.\n\nUsage\n\n```\n`download.suggestedFilename();`\n```\n\nReturns\n\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-download#download-suggested-filename-return)', "Added before v1.9\n\ndownload.createReadStream\n\nReturns a readable stream for a successful download, or throws for a failed/canceled download.\n\nnote\nIf you don't need a readable stream, it's usually simpler to read the file from disk after the download completed. See\ndownload.path() (https://playwright.dev/docs/api/class-download#download-path)\n.\n\nUsage\n\n```\n`awaitdownload.createReadStream();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nReadable (https://nodejs.org/api/stream.html#stream_class_stream_readable)\n&gt;\n# (https://playwright.dev/docs/api/class-download#download-create-read-stream-return)"]</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1354,11 +1397,7 @@
         <is>
           <t>To trigger a file download and save it to a specific location, the recommended pattern is to wait for the `download` event before performing the action that initiates the download.
 ### Recommended Pattern
-1. **Start waiting for the download** using `page.waitForEvent('download')` before triggering the action (e.g., clicking a button). Do not use `await` on this line.
-2. **Perform the action** that triggers the download.
-3. **Await the download promise** to obtain the `Download` object.
-4. **Save the file** using the `download.saveAs()` method, providing your desired path and the `download.suggestedFilename()` to maintain the original file name.
-**Example:**
+Use `page.waitForEvent('download')` to capture the download object, then call `download.saveAs()` to persist the file to your desired path.
 ```javascript
 // Start waiting for download before clicking. Note no await.
 const downloadPromise = page.waitForEvent('download');
@@ -1367,15 +1406,12 @@
 // Wait for the download process to complete and save the downloaded file somewhere.
 await download.saveAs('/path/to/save/at/' + download.suggestedFilename());
 ```
-### Alternative Configuration
-You can also specify a persistent directory for all downloads by using the `downloadsPath` option when launching the browser:
-```javascript
-browserType.launch({ downloadsPath: '/path/to/save/at/' });
-```
-### Important Considerations
-* **Temporary Storage:** By default, files are downloaded into a temporary folder and are deleted when the browser context that produced them is closed.
-* **`saveAs` behavior:** This method is safe to call while the download is still in progress; it will wait for the download to finish if necessary.
-* **Event Handling:** While you can use `page.on('download', ...)` to handle downloads, this forks the control flow and is generally discouraged because the main script may finish before the download completes.</t>
+### Key Details
+*   **`download.saveAs(path)`**: This method copies the download to the specified path. It is safe to call while the download is in progress, as it will wait for the download to finish if necessary.
+*   **`download.suggestedFilename()`**: This returns the filename computed by the browser (e.g., from the `Content-Disposition` header), which you can append to your target directory path.
+*   **Lifecycle**: Downloaded files are stored in a temporary folder and are automatically deleted when the browser context that produced them is closed.
+### Alternative Approach
+If you do not know what initiates the download, you can handle the event globally using `page.on('download', ...)`. However, the documentation notes that this approach forks the control flow and makes the script harder to follow, as your main control flow may finish before the download operation resolves.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1384,28 +1420,28 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.008519499999999999</v>
+        <v>0.0010325</v>
       </c>
       <c r="G17" t="n">
-        <v>31298</v>
+        <v>31034</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.05058365758754864</v>
+        <v>0.05106382978723404</v>
       </c>
       <c r="L17" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8055555555287036</v>
+        <v>0.9999999999666667</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
@@ -1419,7 +1455,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['Authentication | Playwright', 'Regardless of the authentication strategy you choose, you are likely to store authenticated browser state on the file system.\n\nWe recommend to create\n`playwright/.auth`\ndirectory and add it to your\n`.gitignore`\n. Your authentication routine will produce authenticated browser state and save it to a file in this\n`playwright/.auth`\ndirectory. Later on, tests will reuse this state and start already authenticated.\n\ndanger\nThe browser state file may contain sensitive cookies and headers that could be used to impersonate you or your test account. We strongly discourage checking them into private or public repositories.\n\nBash\nPowerShell\nBatch\n```\n`mkdir-pplaywright/.authecho$\'\\nplaywright/.auth\'&gt;&gt;.gitignore`\n```\n```\n`New-Item-ItemType Directory-Force-Path playwright\\.authAdd-Content-path.gitignore"`r`nplaywright/.auth"`\n```\n```\n`mdplaywright\\.authecho. &gt;&gt; .gitignoreecho"playwright/.auth"&gt;&gt; .gitignore`\n```', 'Configuration (use) | Playwright', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", "TestOptions | Playwright\n\nPlaywright Test provides many options to configure test environment,\nBrowser (https://playwright.dev/docs/api/class-browser)\n,\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nand more.\n\nThese options are usually provided in the\nconfiguration file (https://playwright.dev/docs/test-configuration)\nthrough\ntestConfig.use (https://playwright.dev/docs/api/class-testconfig#test-config-use)\nand\ntestProject.use (https://playwright.dev/docs/api/class-testproject#test-project-use)\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{headless:false,viewport:{width:1280,height:720},ignoreHTTPSErrors:true,video:'on-first-retry',},});`\n```\n\nAlternatively, with\ntest.use() (https://playwright.dev/docs/api/class-test#test-use)\nyou can override some options for a file.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';// Run tests in this file with portrait-like viewport.test.use({viewport:{width:600,height:900}});test('my portrait test',async({page})=&gt;{// ...});`\n```"]</t>
+          <t>['Regardless of the authentication strategy you choose, you are likely to store authenticated browser state on the file system.\n\nWe recommend to create\n`playwright/.auth`\ndirectory and add it to your\n`.gitignore`\n. Your authentication routine will produce authenticated browser state and save it to a file in this\n`playwright/.auth`\ndirectory. Later on, tests will reuse this state and start already authenticated.\n\ndanger\nThe browser state file may contain sensitive cookies and headers that could be used to impersonate you or your test account. We strongly discourage checking them into private or public repositories.\n\nBash\nPowerShell\nBatch\n```\n`mkdir-pplaywright/.authecho$\'\\nplaywright/.auth\'&gt;&gt;.gitignore`\n```\n```\n`New-Item-ItemType Directory-Force-Path playwright\\.authAdd-Content-path.gitignore"`r`nplaywright/.auth"`\n```\n```\n`mdplaywright\\.authecho. &gt;&gt; .gitignoreecho"playwright/.auth"&gt;&gt; .gitignore`\n```', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", "Here is a global setup example that authenticates once and reuses authentication state in tests. It uses the\n`baseURL`\nand\n`storageState`\noptions from the configuration file.\n\nglobal-setup.ts\n```\n`import{chromium,typeFullConfig}from'@playwright/test';asyncfunctionglobalSetup(config:FullConfig){const{baseURL,storageState}=config.projects[0].use;constbrowser=awaitchromium.launch();constpage=awaitbrowser.newPage();awaitpage.goto(baseURL!);awaitpage.getByLabel('User Name').fill('user');awaitpage.getByLabel('Password').fill('password');awaitpage.getByText('Sign in').click();awaitpage.context().storageState({path:storageStateasstring});awaitbrowser.close();}exportdefaultglobalSetup;`\n```\n\nSpecify\n`globalSetup`\n,\n`baseURL`\nand\n`storageState`\nin the configuration file.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalSetup:require.resolve('./global-setup'),use:{baseURL:'http://localhost:3000/',storageState:'state.json',},});`\n```\n\nTests start already authenticated because we specify\n`storageState`\nthat was populated by global setup.\n\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{awaitpage.goto('/');// You are signed in!});`\n```\n\nYou can make arbitrary data available in your tests from your global setup file by setting them as environment variables via\n`process.env`\n.\n\nglobal-setup.ts\n```\n`importtype{FullConfig}from'@playwright/test';asyncfunctionglobalSetup(config:FullConfig){process.env.FOO='some data';// Or a more complicated data structure as JSON:process.env.BAR=JSON.stringify({some:'data'});}exportdefaultglobalSetup;`\n```\n\nTests have access to the\n`process.env`\nproperties set in the global setup.\n\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// environment variables which are set in globalSetup are only available inside test().const{FOO,BAR}=process.env;// FOO and BAR properties are populated.expect(FOO).toEqual('some data');constcomplexData=JSON.parse(BAR);expect(BAR).toEqual({some:'data'});});`\n```", "You can use environment variables to configure tests from the command line.\n\nFor example, consider the following test file that needs a username and a password. It is usually a good idea not to store your secrets in the source code, so we'll need a way to pass secrets from outside.\n\nexample.spec.ts\n```\n`test(`example test`,async({page})=&gt;{// ...awaitpage.getByLabel('User Name').fill(process.env.USER_NAME);awaitpage.getByLabel('Password').fill(process.env.PASSWORD);});`\n```\n\nYou can run this test with your secret username and password set in the command line.\n\nBash\nPowerShell\nBatch\n```\n`USER_NAME=mePASSWORD=secret npx playwrighttest`\n```\n```\n`$env:USER_NAME=me$env:PASSWORD=secretnpx playwright test`\n```\n```\n`setUSER_NAME=mesetPASSWORD=secretnpxplaywright test`\n```\n\nSimilarly, configuration file can also read environment variables passed through the command line.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{baseURL:process.env.STAGING==='1'?'http://staging.example.test/':'http://example.test/',}});`\n```\n\nNow, you can run tests against a staging or a production environment:\n\nBash\nPowerShell\nBatch\n```\n`STAGING=1npx playwrighttest`\n```\n```\n`$env:STAGING=1npx playwright test`\n```\n```\n`setSTAGING=1npxplaywright test`\n```", 'To make environment variables easier to manage, consider something like\n`.env`\nfiles. Here is an example that uses\ndotenv (https://www.npmjs.com/package/dotenv)\npackage to read environment variables directly in the configuration file.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importdotenvfrom\'dotenv\';importpathfrom\'path\';// Read from ".env" file.dotenv.config({path:path.resolve(__dirname,\'.env\')});// Alternatively, read from "../my.env" file.dotenv.config({path:path.resolve(__dirname,\'..\',\'my.env\')});exportdefaultdefineConfig({use:{baseURL:process.env.STAGING===\'1\'?\'http://staging.example.test/\':\'http://example.test/\',}});`\n```\n\nNow, you can just edit\n`.env`\nfile to set any variables you\'d like.\n\n```\n`# .env fileSTAGING=0USER_NAME=mePASSWORD=secret`\n```\n\nRun tests as usual, your environment variables should be picked up.\n\n```\n`npx playwrighttest`\n```', "This is the\nrecommended\napproach for tests that\nmodify server-side state\n. In Playwright, worker processes run in parallel. In this approach, each parallel worker is authenticated once. All tests ran by worker are reusing the same authentication state. We will need multiple testing accounts, one per each parallel worker.\n\nWhen to use\n\nYour tests modify shared server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting.\n\nWhen not to use\n\nYour tests do not modify any shared server-side state. In this case, all tests can use a single shared account.\n\nDetails\n\nWe will authenticate once per\nworker process (https://playwright.dev/docs/test-parallel#worker-processes)\n, each with a unique account.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\noverride storageState fixture (https://playwright.dev/docs/test-fixtures#overriding-fixtures)\nto authenticate once per worker. Use\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({browser},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constpage=awaitbrowser.newPage({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill(account.username);awaitpage.getByLabel('Password').fill(account.password);awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:fileName});awaitpage.close();awaituse(fileName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n. No changes are needed in the config.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({page})=&gt;{// page is authenticated});`\n```", "Web apps use cookie-based or token-based authentication, where authenticated state is stored as\ncookies (https://developer.mozilla.org/en-US/docs/Web/HTTP/Cookies)\n. Playwright provides\napiRequestContext.storageState() (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state)\nmethod that can be used to retrieve storage state from an authenticated context and then create new contexts with that state.\n\nStorage state is interchangeable between\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nand\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n. You can use it to log in via API calls and then create a new context with cookies already there. The following code snippet retrieves state from an authenticated\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nand creates a new\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nwith that state.\n\n```\n`constrequestContext=awaitrequest.newContext({httpCredentials:{username:'user',password:'passwd'}});awaitrequestContext.get(`https://api.example.com/login`);// Save storage state into the file.awaitrequestContext.storageState({path:'state.json'});// Create a new context with the saved storage state.constcontext=awaitbrowser.newContext({storageState:'state.json'});`\n```"]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1429,12 +1465,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>You should store authenticated browser state in a directory named `playwright/.auth` on the file system.
-To keep this state out of version control, you must add the `playwright/.auth` directory to your `.gitignore` file. You can do this using the following commands:
-*   **Bash:** `mkdir -p playwright/.auth &amp;&amp; echo $'\nplaywright/.auth' &gt;&gt; .gitignore`
-*   **PowerShell:** `New-Item -ItemType Directory -Force -Path playwright\.auth; Add-Content -Path .gitignore "`r`nplaywright/.auth"`
-*   **Batch:** `md playwright\.auth &amp;&amp; echo. &gt;&gt; .gitignore &amp;&amp; echo "playwright/.auth" &gt;&gt; .gitignore`
-Checking these files into repositories is strongly discouraged because they may contain sensitive cookies and headers that could be used to impersonate you or your test account.</t>
+          <t>You should store authenticated browser state in a directory named `playwright/.auth` on your file system.
+To keep this state out of version control, you must add the `playwright/.auth` directory to your `.gitignore` file. You can do this by running the following commands:
+**Bash:**
+```bash
+mkdir -p playwright/.auth
+echo $'\nplaywright/.auth' &gt;&gt; .gitignore
+```
+**PowerShell:**
+```powershell
+New-Item -ItemType Directory -Force -Path playwright\.auth
+Add-Content -Path .gitignore "`r`nplaywright/.auth"
+```
+**Batch:**
+```batch
+md playwright\.auth
+echo. &gt;&gt; .gitignore
+echo "playwright/.auth" &gt;&gt; .gitignore
+```
+This is necessary because browser state files may contain sensitive cookies and headers that could be used to impersonate you or your test account, and checking them into repositories is strongly discouraged.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1443,28 +1492,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.008047499999999999</v>
+        <v>0.00128325</v>
       </c>
       <c r="G18" t="n">
-        <v>30750</v>
+        <v>37899</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.08571428571428572</v>
+        <v>0.08771929824561403</v>
       </c>
       <c r="L18" t="n">
-        <v>0.375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="M18" t="n">
-        <v>0.499999999975</v>
+        <v>0.91666666664375</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
@@ -1478,7 +1527,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['Emulate the users\n`"colorScheme"`\n. Supported values are \'light\' and \'dark\'. You can also emulate the media type with\npage.emulateMedia() (https://playwright.dev/docs/api/class-page#page-emulate-media)\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{colorScheme:\'dark\',},});`\n```\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test,expect}from\'@playwright/test\';test.use({colorScheme:\'dark\'// or \'light\'});test(\'my test with dark mode\',async({page})=&gt;{// ...});`\n```\n```\n`// Create context with dark modeconstcontext=awaitbrowser.newContext({colorScheme:\'dark\'// or \'light\'});// Create page with dark modeconstpage=awaitbrowser.newPage({colorScheme:\'dark\'// or \'light\'});// Change color scheme for the pageawaitpage.emulateMedia({colorScheme:\'dark\'});// Change media for pageawaitpage.emulateMedia({media:\'print\'});`\n```']</t>
+          <t>['Emulate the users\n`"colorScheme"`\n. Supported values are \'light\' and \'dark\'. You can also emulate the media type with\npage.emulateMedia() (https://playwright.dev/docs/api/class-page#page-emulate-media)\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{colorScheme:\'dark\',},});`\n```\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test,expect}from\'@playwright/test\';test.use({colorScheme:\'dark\'// or \'light\'});test(\'my test with dark mode\',async({page})=&gt;{// ...});`\n```\n```\n`// Create context with dark modeconstcontext=awaitbrowser.newContext({colorScheme:\'dark\'// or \'light\'});// Create page with dark modeconstpage=awaitbrowser.newPage({colorScheme:\'dark\'// or \'light\'});// Change color scheme for the pageawaitpage.emulateMedia({colorScheme:\'dark\'});// Change media for pageawaitpage.emulateMedia({media:\'print\'});`\n```', 'Added in: v1.10\n\ntestOptions.colorScheme\n\nEmulates\nprefers-colors-scheme (https://developer.mozilla.org/en-US/docs/Web/CSS/@media/prefers-color-scheme)\nmedia feature, supported values are\n`\'light\'`\nand\n`\'dark\'`\n. See\npage.emulateMedia() (https://playwright.dev/docs/api/class-page#page-emulate-media)\nfor more details. Passing\n`null`\nresets emulation to system defaults. Defaults to\n`\'light\'`\n.\n\nUsage\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{colorScheme:\'dark\',},});`\n```\n\nType\n\nnull (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/null)\n| "light" | "dark" | "no-preference"', 'With Playwright you can emulate a real device such as a mobile phone or tablet. See our\nguide on projects (https://playwright.dev/docs/test-projects)\nfor more info on emulating devices. You can also emulate the\n`"geolocation"`\n,\n`"locale"`\nand\n`"timezone"`\nfor all tests or for a specific test as well as set the\n`"permissions"`\nto show notifications or change the\n`"colorScheme"`\n. See our\nEmulation (https://playwright.dev/docs/emulation)\nguide to learn more.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{// Emulates `\'prefers-colors-scheme\'` media feature.colorScheme:\'dark\',// Context geolocation.geolocation:{longitude:12.492507,latitude:41.889938},// Emulates the user locale.locale:\'en-GB\',// Grants specified permissions to the browser context.permissions:[\'geolocation\'],// Emulates the user timezone.timezoneId:\'Europe/Paris\',// Viewport used for all pages in the context.viewport:{width:1280,height:720},},});`\n```\n\nOption\nDescription\ntestOptions.colorScheme (https://playwright.dev/docs/api/class-testoptions#test-options-color-scheme)\nEmulates (https://playwright.dev/docs/emulation#color-scheme-and-media)\n`\'prefers-colors-scheme\'`\nmedia feature, supported values are\n`\'light\'`\nand\n`\'dark\'`\ntestOptions.geolocation (https://playwright.dev/docs/api/class-testoptions#test-options-geolocation)\nContext\ngeolocation (https://playwright.dev/docs/emulation#geolocation)\n.\ntestOptions.locale (https://playwright.dev/docs/api/class-testoptions#test-options-locale)\nEmulates (https://playwright.dev/docs/emulation#locale--timezone)\nthe user locale, for example\n`en-GB`\n,\n`de-DE`\n, etc.\ntestOptions.permissions (https://playwright.dev/docs/api/class-testoptions#test-options-permissions)\nA list of\npermissions (https://playwright.dev/docs/emulation#permissions)\nto grant to all pages in the context.\ntestOptions.timezoneId (https://playwright.dev/docs/api/class-testoptions#test-options-timezone-id)\nChanges the\ntimezone (https://playwright.dev/docs/emulation#locale--timezone)\nof the context.\ntestOptions.viewport (https://playwright.dev/docs/api/class-testoptions#test-options-viewport)\nViewport (https://playwright.dev/docs/emulation#viewport)\nused for all pages in the context.', 'With Playwright you can test your app on any browser as well as emulate a real device such as a mobile phone or tablet. Simply configure the devices you would like to emulate and Playwright will simulate the browser behavior such as\n`"userAgent"`\n,\n`"screenSize"`\n,\n`"viewport"`\nand if it\n`"hasTouch"`\nenabled. You can also emulate the\n`"geolocation"`\n,\n`"locale"`\nand\n`"timezone"`\nfor all tests or for a specific test as well as set the\n`"permissions"`\nto show notifications or change the\n`"colorScheme"`\n.']</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1488,9 +1537,9 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To render your app in dark mode, you can use the `colorScheme` option. There are three ways to apply this depending on the scope required:
-**1. Global configuration (Recommended)**
-Set the `colorScheme` in your `playwright.config.ts` file to apply dark mode to all tests:
+          <t>To render your app in dark mode, you can use the `colorScheme` option. There are several ways to apply this depending on the scope you need:
+### For all tests
+Set `colorScheme: 'dark'` in your `playwright.config.ts` file within the `use` object:
 ```typescript
 import { defineConfig } from '@playwright/test';
 export default defineConfig({
@@ -1499,8 +1548,8 @@
   },
 });
 ```
-**2. Per-test configuration**
-Use `test.use` within a specific test file to apply dark mode to all tests in that file:
+### For a specific test
+Use `test.use` within your test file:
 ```typescript
 import { test, expect } from '@playwright/test';
 test.use({ colorScheme: 'dark' });
@@ -1508,10 +1557,10 @@
   // ...
 });
 ```
-**3. Manual context or page creation**
+### For a specific page or context
 You can set the color scheme when creating a new context or page, or change it dynamically for an existing page:
-*   **New context:** `const context = await browser.newContext({ colorScheme: 'dark' });`
-*   **New page:** `const page = await browser.newPage({ colorScheme: 'dark' });`
+*   **New context:** `await browser.newContext({ colorScheme: 'dark' });`
+*   **New page:** `await browser.newPage({ colorScheme: 'dark' });`
 *   **Existing page:** `await page.emulateMedia({ colorScheme: 'dark' });`</t>
         </is>
       </c>
@@ -1521,28 +1570,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.00774125</v>
+        <v>0.00087475</v>
       </c>
       <c r="G19" t="n">
-        <v>29145</v>
+        <v>50875</v>
       </c>
       <c r="H19" t="n">
         <v>0.75</v>
       </c>
       <c r="I19" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="J19" t="n">
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.06</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9999999999</v>
+        <v>0.999999999975</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
@@ -1556,7 +1605,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['Grant\n`"geolocation"`\npermissions and set geolocation to a specific area.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{// Context geolocationgeolocation:{longitude:12.492507,latitude:41.889938},permissions:[\'geolocation\'],},});`\n```\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test,expect}from\'@playwright/test\';test.use({geolocation:{longitude:41.890221,latitude:12.492348},permissions:[\'geolocation\'],});test(\'my test with geolocation\',async({page})=&gt;{// ...});`\n```\n```\n`constcontext=awaitbrowser.newContext({geolocation:{longitude:41.890221,latitude:12.492348},permissions:[\'geolocation\']});`\n```\n\nChange the location later:\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test,expect}from\'@playwright/test\';test.use({geolocation:{longitude:41.890221,latitude:12.492348},permissions:[\'geolocation\'],});test(\'my test with geolocation\',async({page,context})=&gt;{// overwrite the location for this testawaitcontext.setGeolocation({longitude:48.858455,latitude:2.294474});});`\n```\n```\n`awaitcontext.setGeolocation({longitude:48.858455,latitude:2.294474});`\n```\n\nNote\nyou can only change geolocation for all pages in the context.']</t>
+          <t>['Grant\n`"geolocation"`\npermissions and set geolocation to a specific area.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{// Context geolocationgeolocation:{longitude:12.492507,latitude:41.889938},permissions:[\'geolocation\'],},});`\n```\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test,expect}from\'@playwright/test\';test.use({geolocation:{longitude:41.890221,latitude:12.492348},permissions:[\'geolocation\'],});test(\'my test with geolocation\',async({page})=&gt;{// ...});`\n```\n```\n`constcontext=awaitbrowser.newContext({geolocation:{longitude:41.890221,latitude:12.492348},permissions:[\'geolocation\']});`\n```\n\nChange the location later:\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test,expect}from\'@playwright/test\';test.use({geolocation:{longitude:41.890221,latitude:12.492348},permissions:[\'geolocation\'],});test(\'my test with geolocation\',async({page,context})=&gt;{// overwrite the location for this testawaitcontext.setGeolocation({longitude:48.858455,latitude:2.294474});});`\n```\n```\n`awaitcontext.setGeolocation({longitude:48.858455,latitude:2.294474});`\n```\n\nNote\nyou can only change geolocation for all pages in the context.', "Added before v1.9\n\nbrowserContext.setGeolocation\n\nSets the context's geolocation. Passing\n`null`\nor\n`undefined`\nemulates position unavailable.\n\nUsage\n\n```\n`awaitbrowserContext.setGeolocation({latitude:59.95,longitude:30.31667});`\n```\n\nnote\nConsider using\nbrowserContext.grantPermissions() (https://playwright.dev/docs/api/class-browsercontext#browser-context-grant-permissions)\nto grant permissions for the browser context pages to read its geolocation.\n\nArguments\n\n`geolocation`\nnull (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/null)\n|\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-geolocation-option-geolocation)\n`latitude`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\nLatitude between -90 and 90.\n`longitude`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\nLongitude between -180 and 180.\n`accuracy`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nNon-negative accuracy value. Defaults to\n`0`\n.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-geolocation-return)", "Added in: v1.10\n\ntestOptions.geolocation\n\nUsage\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{geolocation:{longitude:12.492507,latitude:41.889938},},});`\n```\n\nLearn more about\ngeolocation (https://playwright.dev/docs/emulation#color-scheme-and-media)\n.\n\nType\n\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n`latitude`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\nLatitude between -90 and 90.\n`longitude`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\nLongitude between -180 and 180.\n`accuracy`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nNon-negative accuracy value. Defaults to\n`0`\n.", 'With Playwright you can emulate a real device such as a mobile phone or tablet. See our\nguide on projects (https://playwright.dev/docs/test-projects)\nfor more info on emulating devices. You can also emulate the\n`"geolocation"`\n,\n`"locale"`\nand\n`"timezone"`\nfor all tests or for a specific test as well as set the\n`"permissions"`\nto show notifications or change the\n`"colorScheme"`\n. See our\nEmulation (https://playwright.dev/docs/emulation)\nguide to learn more.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{// Emulates `\'prefers-colors-scheme\'` media feature.colorScheme:\'dark\',// Context geolocation.geolocation:{longitude:12.492507,latitude:41.889938},// Emulates the user locale.locale:\'en-GB\',// Grants specified permissions to the browser context.permissions:[\'geolocation\'],// Emulates the user timezone.timezoneId:\'Europe/Paris\',// Viewport used for all pages in the context.viewport:{width:1280,height:720},},});`\n```\n\nOption\nDescription\ntestOptions.colorScheme (https://playwright.dev/docs/api/class-testoptions#test-options-color-scheme)\nEmulates (https://playwright.dev/docs/emulation#color-scheme-and-media)\n`\'prefers-colors-scheme\'`\nmedia feature, supported values are\n`\'light\'`\nand\n`\'dark\'`\ntestOptions.geolocation (https://playwright.dev/docs/api/class-testoptions#test-options-geolocation)\nContext\ngeolocation (https://playwright.dev/docs/emulation#geolocation)\n.\ntestOptions.locale (https://playwright.dev/docs/api/class-testoptions#test-options-locale)\nEmulates (https://playwright.dev/docs/emulation#locale--timezone)\nthe user locale, for example\n`en-GB`\n,\n`de-DE`\n, etc.\ntestOptions.permissions (https://playwright.dev/docs/api/class-testoptions#test-options-permissions)\nA list of\npermissions (https://playwright.dev/docs/emulation#permissions)\nto grant to all pages in the context.\ntestOptions.timezoneId (https://playwright.dev/docs/api/class-testoptions#test-options-timezone-id)\nChanges the\ntimezone (https://playwright.dev/docs/emulation#locale--timezone)\nof the context.\ntestOptions.viewport (https://playwright.dev/docs/api/class-testoptions#test-options-viewport)\nViewport (https://playwright.dev/docs/emulation#viewport)\nused for all pages in the context.', 'Added before v1.9\n\nbrowserContext.grantPermissions\n\nGrants specified permissions to the browser context. Only grants corresponding permissions to the given origin if specified.\n\nUsage\n\n```\n`awaitbrowserContext.grantPermissions(permissions);awaitbrowserContext.grantPermissions(permissions,options);`\n```\n\nArguments\n\n`permissions`\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-grant-permissions-option-permissions)\nA list of permissions to grant.\ndanger\nSupported permissions differ between browsers, and even between different versions of the same browser. Any permission may stop working after an update.\nHere are some permissions that may be supported by some browsers:\n`\'accelerometer\'`\n`\'ambient-light-sensor\'`\n`\'background-sync\'`\n`\'camera\'`\n`\'clipboard-read\'`\n`\'clipboard-write\'`\n`\'geolocation\'`\n`\'gyroscope\'`\n`\'local-fonts\'`\n`\'local-network-access\'`\n`\'magnetometer\'`\n`\'microphone\'`\n`\'midi-sysex\'`\n(system-exclusive midi)\n`\'midi\'`\n`\'notifications\'`\n`\'payment-handler\'`\n`\'storage-access\'`\n`\'screen-wake-lock\'`\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`origin`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-grant-permissions-option-origin)\nThe\norigin (https://developer.mozilla.org/en-US/docs/Glossary/Origin)\nto grant permissions to, e.g. "\nhttps://example.com (https://example.com)\n".\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-grant-permissions-return)', 'With Playwright you can test your app on any browser as well as emulate a real device such as a mobile phone or tablet. Simply configure the devices you would like to emulate and Playwright will simulate the browser behavior such as\n`"userAgent"`\n,\n`"screenSize"`\n,\n`"viewport"`\nand if it\n`"hasTouch"`\nenabled. You can also emulate the\n`"geolocation"`\n,\n`"locale"`\nand\n`"timezone"`\nfor all tests or for a specific test as well as set the\n`"permissions"`\nto show notifications or change the\n`"colorScheme"`\n.', 'Record scripts and tests while emulating timezone, language &amp; location using the\n`--timezone`\n,\n`--geolocation`\nand\n`--lang`\noptions. Once the page opens:\n\nAccept the cookies\nOn the top right, click on the locate me button to see geolocation in action.\n\n```\n`npx playwright codegen--timezone="Europe/Rome"--geolocation="41.890221,12.492348"--lang="it-IT"bing.com/maps`\n```']</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1566,38 +1615,48 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To pin the browser to a specific GPS location, you must grant `geolocation` permissions and set the `geolocation` object (containing `longitude` and `latitude`) in your configuration or test setup.
+          <t>To pin the browser to a specific GPS location, you must set the `geolocation` coordinates and grant the `'geolocation'` permission to the browser context.
 ### Configuration Options
-*   **Global Configuration:** Set it in `playwright.config.ts` within the `use` object:
-    ```typescript
-    import { defineConfig } from '@playwright/test';
-    export default defineConfig({
-      use: {
-        geolocation: { longitude: 12.492507, latitude: 41.889938 },
-        permissions: ['geolocation'],
-      },
-    });
-    ```
-*   **Test-Specific Configuration:** Use `test.use` within your test file:
-    ```typescript
-    test.use({
-      geolocation: { longitude: 41.890221, latitude: 12.492348 },
-      permissions: ['geolocation'],
-    });
-    ```
-*   **Manual Context Creation:** If creating a context manually, pass the options to `browser.newContext`:
-    ```typescript
-    const context = await browser.newContext({
-      geolocation: { longitude: 41.890221, latitude: 12.492348 },
-      permissions: ['geolocation']
-    });
-    ```
+You can set these globally in your `playwright.config.ts` or for specific tests.
+**1. Global Configuration (`playwright.config.ts`)**
+```typescript
+import { defineConfig } from '@playwright/test';
+export default defineConfig({
+  use: {
+    geolocation: { longitude: 12.492507, latitude: 41.889938 },
+    permissions: ['geolocation'],
+  },
+});
+```
+**2. Per-Test Configuration**
+Use `test.use` within your test file to override settings for specific tests:
+```typescript
+test.use({
+  geolocation: { longitude: 41.890221, latitude: 12.492348 },
+  permissions: ['geolocation'],
+});
+test('my test with geolocation', async ({ page }) =&gt; {
+  // ...
+});
+```
+**3. Manual Context Creation**
+If you are not using the test runner's configuration, you can set it when creating a new browser context:
+```typescript
+const context = await browser.newContext({
+  geolocation: { longitude: 41.890221, latitude: 12.492348 },
+  permissions: ['geolocation']
+});
+```
 ### Changing Location During a Test
-You can update the location for all pages in a context by using `context.setGeolocation`:
+You can update the geolocation for all pages in an existing context using `context.setGeolocation`:
 ```typescript
 await context.setGeolocation({ longitude: 48.858455, latitude: 2.294474 });
 ```
-Note that geolocation changes apply to all pages within the context.</t>
+### Important Notes
+*   **Permissions:** Always include `'geolocation'` in the `permissions` array to ensure the context has the necessary access.
+*   **Scope:** Geolocation changes apply to all pages within the browser context.
+*   **Codegen:** You can also test geolocation interactively using the test generator:
+    `npx playwright codegen --geolocation="41.890221,12.492348" bing.com/maps`</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1606,28 +1665,28 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.008178</v>
+        <v>0.001564</v>
       </c>
       <c r="G20" t="n">
-        <v>30337</v>
+        <v>49150</v>
       </c>
       <c r="H20" t="n">
         <v>0.75</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="J20" t="n">
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06334841628959276</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9999999999</v>
+        <v>0.9999999999833333</v>
       </c>
       <c r="N20" t="n">
         <v>1</v>
@@ -1641,7 +1700,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>["FrameLocator | Playwright\n\nFrameLocator represents a view to the\n`iframe`\non the page. It captures the logic sufficient to retrieve the\n`iframe`\nand locate elements in that iframe. FrameLocator can be created with either\nlocator.contentFrame() (https://playwright.dev/docs/api/class-locator#locator-content-frame)\n,\npage.frameLocator() (https://playwright.dev/docs/api/class-page#page-frame-locator)\nor\nlocator.frameLocator() (https://playwright.dev/docs/api/class-locator#locator-frame-locator)\nmethod.\n\n```\n`constlocator=page.locator('#my-frame').contentFrame().getByText('Submit');awaitlocator.click();`\n```\n\nStrictness\n\nFrame locators are strict. This means that all operations on frame locators will throw if more than one element matches a given selector.\n\n```\n`// Throws if there are several frames in DOM:awaitpage.locator('.result-frame').contentFrame().getByRole('button').click();// Works because we explicitly tell locator to pick the first frame:awaitpage.locator('.result-frame').contentFrame().first().getByRole('button').click();`\n```\n\nConverting Locator to FrameLocator\n\nIf you have a\nLocator (https://playwright.dev/docs/api/class-locator)\nobject pointing to an\n`iframe`\nit can be converted to\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\nusing\nlocator.contentFrame() (https://playwright.dev/docs/api/class-locator#locator-content-frame)\n.\n\nConverting FrameLocator to Locator\n\nIf you have a\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\nobject it can be converted to\nLocator (https://playwright.dev/docs/api/class-locator)\npointing to the same\n`iframe`\nusing\nframeLocator.owner() (https://playwright.dev/docs/api/class-framelocator#frame-locator-owner)\n.", 'Added in: v1.17\n\nframeLocator.frameLocator\n\nWhen working with iframes, you can create a frame locator that will enter the iframe and allow selecting elements in that iframe.\n\nUsage\n\n```\n`frameLocator.frameLocator(selector);`\n```\n\nArguments\n\n`selector`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-frame-locator-option-selector)\nA selector to use when resolving DOM element.\n\nReturns\n\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-frame-locator-return)', 'Added in: v1.27\n\nframeLocator.getByRole\n\nAllows locating elements by their\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n.\n\nUsage\n\nConsider the following DOM structure.\n\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nArguments\n\n`role`\n"alert" | "alertdialog" | "application" | "article" | "banner" | "blockquote" | "button" | "caption" | "cell" | "checkbox" | "code" | "columnheader" | "combobox" | "complementary" | "contentinfo" | "definition" | "deletion" | "dialog" | "directory" | "document" | "emphasis" | "feed" | "figure" | "form" | "generic" | "grid" | "gridcell" | "group" | "heading" | "img" | "insertion" | "link" | "list" | "listbox" | "listitem" | "log" | "main" | "marquee" | "math" | "meter" | "menu" | "menubar" | "menuitem" | "menuitemcheckbox" | "menuitemradio" | "navigation" | "none" | "note" | "option" | "paragraph" | "presentation" | "progressbar" | "radio" | "radiogroup" | "region" | "row" | "rowgroup" | "rowheader" | "scrollbar" | "search" | "searchbox" | "separator" | "slider" | "spinbutton" | "status" | "strong" | "subscript" | "superscript" | "switch" | "tab" | "table" | "tablist" | "tabpanel" | "term" | "textbox" | "time" | "timer" | "toolbar" | "tooltip" | "tree" | "treegrid" | "treeitem"\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-role)\nRequired aria role.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`checked`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-checked)\nAn attribute that is usually set by\n`aria-checked`\nor native\n`&lt;input type=checkbox&gt;`\ncontrols.\nLearn more about\naria-checked (https://www.w3.org/TR/wai-aria-1.2/#aria-checked)\n.\n`description`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n(optional)\nAdded in: v1.60\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-description)\nOption to match the\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\n. By default, matching is case-insensitive and searches for a substring, use\nexact (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-exact)\nto control this behavior.\nLearn more about\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\n.\n`disabled`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-disabled)\nAn attribute that is usually set by\n`aria-disabled`\nor\n`disabled`\n.\nnote\nUnlike most other attributes,\n`disabled`\nis inherited through the DOM hierarchy. Learn more about\naria-disabled (https://www.w3.org/TR/wai-aria-1.2/#aria-disabled)\n.\n`exact`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.28\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-exact)\nWhether\nname (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-name)\nand\ndescription (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-description)\nare matched exactly: case-sensitive and whole-string. Defaults to false. Ignored when the value is a regular expression. Note that exact match still trims whitespace.\n`expanded`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-expanded)\nAn attribute that is usually set by\n`aria-expanded`\n.\nLearn more about\naria-expanded (https://www.w3.org/TR/wai-aria-1.2/#aria-expanded)\n.\n`includeHidden`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-include-hidden)\nOption that controls whether hidden elements are matched. By default, only non-hidden elements, as\ndefined by ARIA (https://www.w3.org/TR/wai-aria-1.2/#tree_exclusion)\n, are matched by role selector.\nLearn more about\naria-hidden (https://www.w3.org/TR/wai-aria-1.2/#aria-hidden)\n.\n`level`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-level)\nA number attribute that is usually present for roles\n`heading`\n,\n`listitem`\n,\n`row`\n,\n`treeitem`\n, with default values for\n`&lt;h1&gt;-&lt;h6&gt;`\nelements.\nLearn more about\naria-level (https://www.w3.org/TR/wai-aria-1.2/#aria-level)\n.\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-name)\nOption to match the\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. By default, matching is case-insensitive and searches for a substring, use\nexact (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-exact)\nto control this behavior.\nLearn more about\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n.\n`pressed`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-pressed)\nAn attribute that is usually set by\n`aria-pressed`\n.\nLearn more about\naria-pressed (https://www.w3.org/TR/wai-aria-1.2/#aria-pressed)\n.\n`selected`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-option-selected)\nAn attribute that is usually set by\n`aria-selected`\n.\nLearn more about\naria-selected (https://www.w3.org/TR/wai-aria-1.2/#aria-selected)\n.\n\nReturns\n\nLocator (https://playwright.dev/docs/api/class-locator)\n# (https://playwright.dev/docs/api/class-framelocator#frame-locator-get-by-role-return)\n\nDetails\n\nRole selector\ndoes not replace\naccessibility audits and conformance tests, but rather gives early feedback about the ARIA guidelines.\n\nMany html elements have an implicitly\ndefined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role selector. You can find all the\nsupported roles here (https://www.w3.org/TR/wai-aria-1.2/#role_definitions)\n. ARIA guidelines\ndo not recommend\nduplicating implicit roles and attributes by setting\n`role`\nand/or\n`aria-*`\nattributes to default values.']</t>
+          <t>["FrameLocator | Playwright\n\nFrameLocator represents a view to the\n`iframe`\non the page. It captures the logic sufficient to retrieve the\n`iframe`\nand locate elements in that iframe. FrameLocator can be created with either\nlocator.contentFrame() (https://playwright.dev/docs/api/class-locator#locator-content-frame)\n,\npage.frameLocator() (https://playwright.dev/docs/api/class-page#page-frame-locator)\nor\nlocator.frameLocator() (https://playwright.dev/docs/api/class-locator#locator-frame-locator)\nmethod.\n\n```\n`constlocator=page.locator('#my-frame').contentFrame().getByText('Submit');awaitlocator.click();`\n```\n\nStrictness\n\nFrame locators are strict. This means that all operations on frame locators will throw if more than one element matches a given selector.\n\n```\n`// Throws if there are several frames in DOM:awaitpage.locator('.result-frame').contentFrame().getByRole('button').click();// Works because we explicitly tell locator to pick the first frame:awaitpage.locator('.result-frame').contentFrame().first().getByRole('button').click();`\n```\n\nConverting Locator to FrameLocator\n\nIf you have a\nLocator (https://playwright.dev/docs/api/class-locator)\nobject pointing to an\n`iframe`\nit can be converted to\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\nusing\nlocator.contentFrame() (https://playwright.dev/docs/api/class-locator#locator-content-frame)\n.\n\nConverting FrameLocator to Locator\n\nIf you have a\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\nobject it can be converted to\nLocator (https://playwright.dev/docs/api/class-locator)\npointing to the same\n`iframe`\nusing\nframeLocator.owner() (https://playwright.dev/docs/api/class-framelocator#frame-locator-owner)\n.", "Frame | Playwright\n\nAt every point of time, page exposes its current frame tree via the\npage.mainFrame() (https://playwright.dev/docs/api/class-page#page-main-frame)\nand\nframe.childFrames() (https://playwright.dev/docs/api/class-frame#frame-child-frames)\nmethods.\n\nFrame (https://playwright.dev/docs/api/class-frame)\nobject's lifecycle is controlled by three events, dispatched on the page object:\n\npage.on('frameattached') (https://playwright.dev/docs/api/class-page#page-event-frame-attached)\n- fired when the frame gets attached to the page. A Frame can be attached to the page only once.\npage.on('framenavigated') (https://playwright.dev/docs/api/class-page#page-event-frame-navigated)\n- fired when the frame commits navigation to a different URL.\npage.on('framedetached') (https://playwright.dev/docs/api/class-page#page-event-frame-detached)\n- fired when the frame gets detached from the page.  A Frame can be detached from the page only once.\n\nAn example of dumping frame tree:\n\n```\n`const{firefox}=require('playwright');// Or 'chromium' or 'webkit'.(async()=&gt;{constbrowser=awaitfirefox.launch();constpage=awaitbrowser.newPage();awaitpage.goto('https://www.google.com/chrome/browser/canary.html');dumpFrameTree(page.mainFrame(),'');awaitbrowser.close();functiondumpFrameTree(frame,indent){console.log(indent+frame.url());for(constchildofframe.childFrames())dumpFrameTree(child,indent+'  ');}})();`\n```"]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1651,25 +1710,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>To interact with a button inside an iframe, you must use a `FrameLocator` to target the iframe and then locate the button within it.
-### Steps to interact with the button:
-1. **Create a `FrameLocator`**: Use one of the following methods to target the iframe:
-   - `page.frameLocator(selector)`
-   - `locator.contentFrame()` (if you have a `Locator` pointing to the `iframe`)
-   - `locator.frameLocator(selector)`
-2. **Locate the button**: Once you have the `FrameLocator`, use `getByRole('button', ...)` to target the specific button.
-3. **Perform the action**: Call `.click()` on the resulting locator.
-### Example:
+          <t>To interact with a button inside an `iframe`, you should use a `FrameLocator`. You can create one using `page.frameLocator()`, `locator.contentFrame()`, or `locator.frameLocator()`.
+Once you have the `FrameLocator`, you can chain it with a locator method (such as `getByRole` or `getByText`) to target the button and perform the interaction.
+**Example:**
 ```javascript
-// Using page.frameLocator()
-await page.frameLocator('#my-frame').getByRole('button', { name: 'Submit' }).click();
-```
-### Important Considerations:
-* **Strictness**: Frame locators are strict. If your selector matches more than one frame, the operation will throw an error. If multiple frames exist, you must explicitly select the correct one (e.g., by using `.first()`):
+const locator = page.frameLocator('#my-frame').getByRole('button', { name: 'Submit' });
+await locator.click();
+```
+**Important considerations:**
+* **Strictness:** Frame locators are strict and will throw an error if more than one element matches the selector. If your selector matches multiple frames, you must explicitly select one (e.g., by using `.first()`):
   ```javascript
   await page.locator('.result-frame').contentFrame().first().getByRole('button').click();
   ```
-* **Role Matching**: When using `getByRole`, you can specify the button's accessible name using the `name` option. By default, this is case-insensitive and searches for a substring. You can use the `exact` option to require a case-sensitive, whole-string match.</t>
+* **Conversion:** If you already have a `Locator` pointing to an `iframe`, you can convert it to a `FrameLocator` using `.contentFrame()`.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1678,28 +1731,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.0089345</v>
+        <v>0.00071225</v>
       </c>
       <c r="G21" t="n">
-        <v>33473</v>
+        <v>65811</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0.59</v>
+        <v>0.44</v>
       </c>
       <c r="J21" t="n">
         <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.08808290155440414</v>
+        <v>0.1203007518796992</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9999999999666667</v>
+        <v>0.9999999999</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
@@ -1713,7 +1766,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>['Sharding | Playwright', 'To shard the test suite, pass\n`--shard=x/y`\nto the command line. For example, to split the suite into four shards, each running one fourth of the tests:\n\n```\n`npx playwrighttest--shard=1/4npx playwrighttest--shard=2/4npx playwrighttest--shard=3/4npx playwrighttest--shard=4/4`\n```\n\nNow, if you run these shards in parallel on different jobs, your test suite completes four times faster.\n\nNote that Playwright can only shard tests that can be run in parallel. By default, this means Playwright will shard test files. Learn about other options in the\nparallelism guide (https://playwright.dev/docs/test-parallel)\n.', "```\n`trigger:-mainpool:vmImage:ubuntu-lateststrategy:matrix:chromium-1:project:chromiumshard:1/3chromium-2:project:chromiumshard:2/3chromium-3:project:chromiumshard:3/3firefox-1:project:firefoxshard:1/3firefox-2:project:firefoxshard:2/3firefox-3:project:firefoxshard:3/3webkit-1:project:webkitshard:1/3webkit-2:project:webkitshard:2/3webkit-3:project:webkitshard:3/3steps:-task:UseNode@1inputs:version:'22'displayName:'Install Node.js'-script:npm cidisplayName:'npm ci'-script:npx playwright install--with-depsdisplayName:'Install Playwright browsers'-script:npx playwright test--project=$(project)--shard=$(shard)displayName:'Run Playwright tests'env:CI:'true'`\n```", 'Sharding in CircleCI is indexed with 0 which means that you will need to override the default parallelism ENV VARS. The following example demonstrates how to run Playwright with a CircleCI Parallelism of 4 by adding 1 to the\n`CIRCLE_NODE_INDEX`\nto pass into the\n`--shard`\ncli arg.\n\n```\n`playwright-job-name:executor:pw-noble-developmentparallelism:4steps:-run:SHARD="$((${CIRCLE_NODE_INDEX}+1))"; npx playwright test--shard=${SHARD}/${CIRCLE_NODE_TOTAL}`\n```', "GitLab CI supports\nsharding tests between multiple jobs (https://docs.gitlab.com/ee/ci/jobs/job_control.html#parallelize-large-jobs)\nusing the\nparallel (https://docs.gitlab.com/ee/ci/yaml/index.html#parallel)\nkeyword. The test job will be split into multiple smaller jobs that run in parallel. Parallel jobs are named sequentially from\n`job_name 1/N`\nto\n`job_name N/N`\n.\n\n```\n`stages:-testtests:stage:testimage:mcr.microsoft.com/playwright:v1.60.0-nobleparallel:7script:-npm ci-npx playwright test--shard=$CI_NODE_INDEX/$CI_NODE_TOTAL`\n```\n\nGitLab CI also supports sharding tests between multiple jobs using the\nparallel :matrix (https://docs.gitlab.com/ee/ci/yaml/index.html#parallelmatrix)\noption. The test job will run multiple times in parallel in a single pipeline, but with different variable values for each instance of the job. In the example below, we have 2\n`PROJECT`\nvalues and 10\n`SHARD`\nvalues, resulting in a total of 20 jobs to be run.\n\n```\n`stages:-testtests:stage:testimage:mcr.microsoft.com/playwright:v1.60.0-nobleparallel:matrix:-PROJECT:['chromium','webkit']SHARD:['1/10','2/10','3/10','4/10','5/10','6/10','7/10','8/10','9/10','10/10']script:-npm ci-npx playwright test--project=$PROJECT--shard=$SHARD`\n```", 'Parallelism | Playwright', 'By default, Playwright runs test files in\nparallel (https://playwright.dev/docs/test-parallel)\nand strives for optimal utilization of CPU cores on your machine. In order to achieve even greater parallelisation, you can further scale Playwright test execution by running tests on multiple machines simultaneously. We call this mode of operation "sharding". Sharding in Playwright means splitting your tests into smaller parts called "shards". Each shard is like a separate job that can run independently. The whole purpose is to divide your tests to speed up test runtime.\n\nWhen you shard your tests, each shard can run on its own, utilizing the available CPU cores. This helps speed up the testing process by doing tasks simultaneously.\n\nIn a CI pipeline, each shard can run as a separate job, making use of the hardware resources available in your CI pipeline, like CPU cores, to run tests faster.']</t>
+          <t>['To shard the test suite, pass\n`--shard=x/y`\nto the command line. For example, to split the suite into four shards, each running one fourth of the tests:\n\n```\n`npx playwrighttest--shard=1/4npx playwrighttest--shard=2/4npx playwrighttest--shard=3/4npx playwrighttest--shard=4/4`\n```\n\nNow, if you run these shards in parallel on different jobs, your test suite completes four times faster.\n\nNote that Playwright can only shard tests that can be run in parallel. By default, this means Playwright will shard test files. Learn about other options in the\nparallelism guide (https://playwright.dev/docs/test-parallel)\n.', "GitHub Actions supports\nsharding tests between multiple jobs (https://docs.github.com/en/actions/using-jobs/using-a-matrix-for-your-jobs)\nusing the\njobs.&lt;job_id&gt;.strategy.matrix (https://docs.github.com/en/actions/using-workflows/workflow-syntax-for-github-actions#jobsjob_idstrategymatrix)\noption. The\n`matrix`\noption will run a separate job for every possible combination of the provided options.\n\nThe following example shows you how to configure a job to run your tests on four machines in parallel and then merge the reports into a single report. Don't forget to add\n`reporter: process.env.CI ? 'blob' : 'html',`\nto your\n`playwright.config.ts`\nfile as in the example above.\n\nFirst we add a\n`matrix`\noption to our job configuration with the\n`shardTotal: [4]`\noption containing the total number of shards we want to create and\n`shardIndex: [1, 2, 3, 4]`\nwith an array of the shard numbers.\nThen we run our Playwright tests with the\n`--shard=${{ matrix.shardIndex }}/${{ matrix.shardTotal }}`\noption. This will run our test command for each shard.\nFinally we upload our blob report to the GitHub Actions Artifacts. This will make the blob report available to other jobs in the workflow.\n\n.github/workflows/playwright.yml\n```\n`name:Playwright Testson:push:branches:[main,master]pull_request:branches:[main,master]jobs:playwright-tests:timeout-minutes:60runs-on:ubuntu-lateststrategy:fail-fast:falsematrix:shardIndex:[1,2,3,4]shardTotal:[4]steps:-uses:actions/checkout@v5-uses:actions/setup-node@v5with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Install Playwright browsersrun:npx playwright install--with-deps-name:Run Playwright testsrun:npx playwright test--shard=${{matrix.shardIndex}}/${{matrix.shardTotal}}-name:Upload blob report to GitHub Actions Artifactsif:${{!cancelled()}}uses:actions/upload-artifact@v4with:name:blob-report-${{matrix.shardIndex}}path:blob-reportretention-days:1`\n```\n\nAfter all shards have completed, you can run a separate job that will merge the reports and produce a combined\nHTML report (https://playwright.dev/docs/test-reporters#html-reporter)\n. To ensure the execution order, we make the\n`merge-reports`\njob\ndepend (https://docs.github.com/en/actions/using-jobs/using-jobs-in-a-workflow#defining-prerequisite-jobs)\non our sharded\n`playwright-tests`\njob by adding\n`needs: [playwright-tests]`\n.\n\n.github/workflows/playwright.yml\n```\n`jobs:...merge-reports:# Merge reports after playwright-tests, even if some shards have failedif:${{!cancelled()}}needs:[playwright-tests]runs-on:ubuntu-lateststeps:-uses:actions/checkout@v5-uses:actions/setup-node@v5with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Download blob reports from GitHub Actions Artifactsuses:actions/download-artifact@v5with:path:all-blob-reportspattern:blob-report-*merge-multiple:true-name:Merge into HTML Reportrun:npx playwright merge-reports--reporter html ./all-blob-reports-name:Upload HTML reportuses:actions/upload-artifact@v4with:name:html-report--attempt-${{github.run_attempt}}path:playwright-reportretention-days:14`\n```\n\nYou can now see the reports have been merged and a combined HTML report is available in the GitHub Actions Artifacts tab.", "Sharding can be done at two levels of granularity depending on whether you use the\ntestProject.fullyParallel (https://playwright.dev/docs/api/class-testproject#test-project-fully-parallel)\noption or not. This affects how the tests are balanced across the shards.\n\nSharding with fullyParallel\n\nWhen\n`fullyParallel: true`\nis enabled, Playwright Test runs individual tests in parallel across multiple shards, ensuring each shard receives an even distribution of tests. This allows for test-level granularity, meaning each shard will attempt to balance the number of individual tests it runs. This is the preferred mode for ensuring even load distribution when sharding, as Playwright can optimize shard execution based on the total number of tests.\n\nSharding without fullyParallel\n\nWithout the fullyParallel setting, Playwright Test defaults to file-level granularity, meaning entire test files are assigned to shards (note that the same file may be assigned to different shards across different projects). In this case, the number of tests per file can greatly influence shard distribution. If your test files are not evenly sized (i.e., some files contain many more tests than others), certain shards may end up running significantly more tests, while others may run fewer or even none.\n\nKey Takeaways:\n\nWith\n`fullyParallel: true`\n: Tests are split at the individual test level, leading to more balanced shard execution.\nWithout\n`fullyParallel`\n: Tests are split at the file level, so to balance the shards, it's important to keep your test files small and evenly sized.\nTo ensure the most effective use of sharding, especially in CI environments, it is recommended to use\n`fullyParallel: true`\nwhen aiming for balanced distribution across shards. Otherwise, you may need to manually organize your test files to avoid imbalances.", "In the previous example, each test shard has its own test report. If you want to have a combined report showing all the test results from all the shards, you can merge them.\n\nStart with adding\n`blob`\nreporter to the config when running on CI:\n\nplaywright.config.ts\n```\n`exportdefaultdefineConfig({testDir:'./tests',reporter:process.env.CI?'blob':'html',});`\n```\n\nBlob report contains information about all the tests that were run and their results as well as all test attachments such as traces and screenshot diffs. Blob reports can be merged and converted to any other Playwright report. By default, blob report will be generated into\n`blob-report`\ndirectory. You can learn about\nblob report options here (https://playwright.dev/docs/test-reporters#blob-reporter)\n.\n\nTo merge reports from multiple shards, put the blob report files into a single directory, for example\n`all-blob-reports`\n. Blob report names contain shard number, so they will not clash.\n\nAfterwards, run\n`npx playwright merge-reports`\ncommand:\n\n```\n`npx playwright merge-reports--reporterhtml ./all-blob-reports`\n```\n\nThis will produce a standard HTML report into\n`playwright-report`\ndirectory.", 'By default, Playwright runs test files in\nparallel (https://playwright.dev/docs/test-parallel)\nand strives for optimal utilization of CPU cores on your machine. In order to achieve even greater parallelisation, you can further scale Playwright test execution by running tests on multiple machines simultaneously. We call this mode of operation "sharding". Sharding in Playwright means splitting your tests into smaller parts called "shards". Each shard is like a separate job that can run independently. The whole purpose is to divide your tests to speed up test runtime.\n\nWhen you shard your tests, each shard can run on its own, utilizing the available CPU cores. This helps speed up the testing process by doing tasks simultaneously.\n\nIn a CI pipeline, each shard can run as a separate job, making use of the hardware resources available in your CI pipeline, like CPU cores, to run tests faster.', "`npx playwright merge-reports path/to/blob-reports-dir`\nreads all blob reports from the passed directory and merges them into a single report.\n\nWhen merging reports from different OS'es you'll have to provide an explicit merge config to disambiguate which directory should be used as tests root.\n\nSupported options:\n\n`--reporter reporter-to-use`\nWhich report to produce. Can be multiple reporters separated by comma.\nExample:\n```\n`npx playwright merge-reports--reporter=html,github ./blob-reports`\n```\n`--config path/to/config/file`\nSpecifies the Playwright configuration file with output reporters. Use this option to pass additional configuration to the output reporter. This configuration file can differ from the one used during the creation of blob reports.\nExample:\n```\n`npx playwright merge-reports--config=merge.config.ts ./blob-reports`\n```\nmerge.config.ts\n```\n`exportdefault{testDir:'e2e',reporter:[['html',{open:'never'}]],};`\n```", 'Playwright Test can shard a test suite, so that it can be executed on multiple machines. See\nsharding guide (https://playwright.dev/docs/test-sharding)\nfor more details.\n\n```\n`npx playwrighttest--shard=2/3`\n```']</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1723,41 +1776,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To split your tests to run across several machines, you use the `--shard=x/y` command-line argument. This divides your test suite into `y` parts, where `x` represents the specific shard index to be executed.
-### General Usage
-To run a suite in four shards, you would execute the following commands on different machines or jobs:
-* `npx playwright test --shard=1/4`
-* `npx playwright test --shard=2/4`
-* `npx playwright test --shard=3/4`
-* `npx playwright test --shard=4/4`
-### CI Integration
-You can automate this process within your CI pipeline configuration:
-* **GitLab CI:** Use the `parallel` keyword to split jobs. You can use the built-in variables `$CI_NODE_INDEX` and `$CI_NODE_TOTAL`:
-  ```yaml
-  script:
-    - npx playwright test --shard=$CI_NODE_INDEX/$CI_NODE_TOTAL
-  ```
-  Alternatively, use `parallel:matrix` to define specific shard values (e.g., `SHARD: ['1/10', '2/10', ...]`).
-* **CircleCI:** Since CircleCI indexing starts at 0, you must add 1 to the index to match the `--shard` format:
-  ```yaml
-  - run: SHARD="$((${CIRCLE_NODE_INDEX}+1))"; npx playwright test --shard=${SHARD}/${CIRCLE_NODE_TOTAL}
-  ```
-* **Azure Pipelines:** Use a `strategy: matrix` to define the shards explicitly:
-  ```yaml
-  strategy:
-    matrix:
-      shard-1:
-        shard: 1/3
-      shard-2:
-        shard: 2/3
-      shard-3:
-        shard: 3/3
-  steps:
-    - script: npx playwright test --shard=$(shard)
-  ```
-### Important Considerations
-* **Parallelism:** Playwright can only shard tests that are capable of running in parallel. By default, this means Playwright shards test files.
-* **Performance:** Sharding allows you to scale test execution across multiple machines simultaneously, which reduces total test runtime.</t>
+          <t>To split your tests to run across several machines, you use the `--shard=x/y` command-line argument. For example, to split your suite into four shards, you would run the following commands on your different machines:
+*   `npx playwright test --shard=1/4`
+*   `npx playwright test --shard=2/4`
+*   `npx playwright test --shard=3/4`
+*   `npx playwright test --shard=4/4`
+### Balancing Shards
+To ensure an even distribution of tests across shards, it is recommended to enable `fullyParallel: true` in your configuration. This allows Playwright to split tests at the individual test level. Without this setting, Playwright defaults to file-level granularity, which can lead to imbalances if your test files are not evenly sized.
+### Merging Reports
+Because each shard generates its own report, you can merge them into a single report:
+1.  **Configure the Reporter:** Update your `playwright.config.ts` to use the `blob` reporter when running in CI:
+    ```typescript
+    reporter: process.env.CI ? 'blob' : 'html',
+    ```
+2.  **Collect Reports:** Gather the generated blob reports from all shards into a single directory (e.g., `all-blob-reports`).
+3.  **Merge:** Run the following command to produce a combined report:
+    ```bash
+    npx playwright merge-reports --reporter html ./all-blob-reports
+    ```
+If you are using GitHub Actions, you can automate this process using a `matrix` strategy to define your shards and a subsequent job that depends on the test jobs to download the artifacts and run the `merge-reports` command.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1766,28 +1803,28 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.010718</v>
+        <v>0.00128875</v>
       </c>
       <c r="G22" t="n">
-        <v>38127</v>
+        <v>34842</v>
       </c>
       <c r="H22" t="n">
         <v>0.75</v>
       </c>
       <c r="I22" t="n">
-        <v>0.59</v>
+        <v>0.31</v>
       </c>
       <c r="J22" t="n">
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>0.05533596837944664</v>
+        <v>0.06329113924050633</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9999999999857143</v>
+        <v>0.7928571428373213</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
@@ -1801,7 +1838,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>['Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', "example.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('slow test',async({page})=&gt;{test.slow();// Easy way to triple the default timeout// ...});test('very slow test',async({page})=&gt;{test.setTimeout(120_000);// ...});`\n```\n\nAPI reference:\ntest.setTimeout() (https://playwright.dev/docs/api/class-test#test-set-timeout)\nand\ntest.slow() (https://playwright.dev/docs/api/class-test#test-slow)\n."]</t>
+          <t>['Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', "example.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('slow test',async({page})=&gt;{test.slow();// Easy way to triple the default timeout// ...});test('very slow test',async({page})=&gt;{test.setTimeout(120_000);// ...});`\n```\n\nAPI reference:\ntest.setTimeout() (https://playwright.dev/docs/api/class-test#test-set-timeout)\nand\ntest.slow() (https://playwright.dev/docs/api/class-test#test-slow)\n.", "Added in: v1.10\n\ntestInfo.setTimeout\n\nChanges the timeout for the currently running test. Zero means no timeout. Learn more about\nvarious timeouts (https://playwright.dev/docs/test-timeouts)\n.\n\nTimeout is usually specified in the\nconfiguration file (https://playwright.dev/docs/test-configuration)\n, but it could be useful to change the timeout in certain scenarios:\n\n```\n`import{test,expect}from'@playwright/test';test.beforeEach(async({page},testInfo)=&gt;{// Extend timeout for all tests running this hook by 30 seconds.testInfo.setTimeout(testInfo.timeout+30000);});`\n```\n\nUsage\n\n```\n`testInfo.setTimeout(timeout);`\n```\n\nArguments\n\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n# (https://playwright.dev/docs/api/class-testinfo#test-info-set-timeout-option-timeout)\nTimeout in milliseconds.", 'Added in: v1.10\n\ntestInfo.slow()\n\nMarks the currently running test as "slow", giving it triple the default timeout. This is similar to\ntest.slow() (https://playwright.dev/docs/api/class-test#test-slow)\n.\n\nUsage\n\n```\n`testInfo.slow();`\n```', 'Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and\n`beforeEach`\nhooks is included in the test timeout.\n\nTimed out test produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Timeout of 30000ms exceeded.`\n```\n\nAdditional separate timeout, of the same value, is shared between fixture teardowns and\n`afterEach`\nhooks, after the test function has finished.\n\nThe same timeout value also applies to\n`beforeAll`\nand\n`afterAll`\nhooks, but they do not share time with any test.', 'Playwright supports tags and annotations that are displayed in the test report.\n\nYou can add your own tags and annotations at any moment, but Playwright comes with a few built-in ones:\n\ntest.skip() (https://playwright.dev/docs/api/class-test#test-skip)\nmarks the test as irrelevant. Playwright does not run such a test. Use this annotation when the test is not applicable in some configuration.\ntest.fail() (https://playwright.dev/docs/api/class-test#test-fail)\nmarks the test as failing. Playwright will run this test and ensure it does indeed fail. If the test does not fail, Playwright will complain.\ntest.fixme() (https://playwright.dev/docs/api/class-test#test-fixme)\nmarks the test as failing. Playwright will not run this test, as opposed to the\n`fail`\nannotation. Use\n`fixme`\nwhen running the test is slow or crashes.\ntest.slow() (https://playwright.dev/docs/api/class-test#test-slow)\nmarks the test as slow and triples the test timeout.\n\nAnnotations can be added to a single test or a group of tests.\n\nBuilt-in annotations can be conditional, in which case they apply when the condition is truthy, and may depend on test fixtures. There could be multiple annotations on the same test, possibly in different configurations.', "These are the low-level timeouts that are pre-configured by the test runner, you should not need to change these. If you happen to be in this section because your test are flaky, it is very likely that you should be looking for the solution elsewhere.\n\nTimeout\nDefault\nDescription\nAction timeout\nno timeout\nTimeout for each action\nSet in config\n`{ use: { actionTimeout: 10_000 } }`\nOverride in test\n`locator.click({ timeout: 10_000 })`\nNavigation timeout\nno timeout\nTimeout for each navigation action\nSet in config\n`{ use: { navigationTimeout: 30_000 } }`\nOverride in test\n`page.goto('/', { timeout: 30_000 })`\nGlobal timeout\nno timeout\nGlobal timeout for the whole test run\nSet in config\n`{ globalTimeout: 3_600_000 }`\n`beforeAll`\n/\n`afterAll`\ntimeout\n30_000 ms\nTimeout for the hook\nSet in hook\n`test.setTimeout(60_000)`\nFixture timeout\nno timeout\nTimeout for an individual fixture\nSet in fixture\n`{ scope: 'test', timeout: 30_000 }`"]</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1811,9 +1848,9 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Yes, you can use one of the following one-liners inside your test:
-*   **To triple the default timeout:** Use `test.slow();`.
-*   **To set a specific duration:** Use `test.setTimeout(120_000);` (replacing `120_000` with your desired time in milliseconds).</t>
+          <t>Yes, you can use one of the following one-liners inside your test to give it more room:
+*   **`test.slow();`**: This marks the test as "slow" and triples the default test timeout.
+*   **`test.setTimeout(120000);`**: This sets a specific timeout for the test in milliseconds (in this example, 120 seconds).</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1822,28 +1859,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.007670749999999</v>
+        <v>0.0006334999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>29758</v>
+        <v>36166</v>
       </c>
       <c r="H23" t="n">
         <v>0.5</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="J23" t="n">
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="M23" t="n">
-        <v>0.49999999995</v>
+        <v>0.4999999999833333</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
@@ -1857,7 +1894,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>['Other locators | Playwright', 'Playwright comes with multiple built-in locators. To make tests resilient, we recommend prioritizing user-facing attributes and explicit contracts such as\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign in\n```\n`&lt;button&gt;Sign in&lt;/button&gt;`\n```\n\nLocate the element by its role of\n`button`\nwith name "Sign in".\n\n```\n`awaitpage.getByRole(\'button\',{name:\'Sign in\'}).click();`\n```\n\nnote\nUse the\ncode generator (https://playwright.dev/docs/codegen)\nto generate a locator, and then edit it as you\'d like.\n\nEvery time a locator is used for an action, an up-to-date DOM element is located in the page. In the snippet below, the underlying DOM element will be located twice, once prior to every action. This means that if the DOM changes in between the calls due to re-render, the new element corresponding to the locator will be used.\n\n```\n`constlocator=page.getByRole(\'button\',{name:\'Sign in\'});awaitlocator.hover();awaitlocator.click();`\n```\n\nNote that all methods that create a locator, such as\npage.getByLabel() (https://playwright.dev/docs/api/class-page#page-get-by-label)\n, are also available on the\nLocator (https://playwright.dev/docs/api/class-locator)\nand\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\nclasses, so you can chain them and iteratively narrow down your locator.\n\n```\n`constlocator=page.frameLocator(\'#my-frame\').getByRole(\'button\',{name:\'Sign in\'});awaitlocator.click();`\n```', 'Testing by test ids is the most resilient way of testing as even if your text or role of the attribute changes, the test will still pass. QA\'s and developers should define explicit test ids and query them with\npage.getByTestId() (https://playwright.dev/docs/api/class-page#page-get-by-test-id)\n. However testing by test ids is not user facing. If the role or text value is important to you then consider using user facing locators such as\nrole (https://playwright.dev/docs/locators#locate-by-role)\nand\ntext locators (https://playwright.dev/docs/locators#locate-by-text)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nItinéraire\n```\n`&lt;buttondata-testid="directions"&gt;Itinéraire&lt;/button&gt;`\n```\n\nYou can locate the element by its test id:\n\n```\n`awaitpage.getByTestId(\'directions\').click();`\n```\n\nWhen to use testid locators\nYou can also use test ids when you choose to use the test id methodology or when you can\'t locate by\nrole (https://playwright.dev/docs/locators#locate-by-role)\nor\ntext (https://playwright.dev/docs/locators#locate-by-text)\n.', 'warning\nWe recommend\nlocating by test id (https://playwright.dev/docs/locators#locate-by-test-id)\ninstead.\n\nPlaywright supports shorthand for selecting elements using certain attributes. Currently, only the following attributes are supported:\n\n`id`\n`data-testid`\n`data-test-id`\n`data-test`\n\n```\n`// Fill an input with the id "username"awaitpage.locator(\'id=username\').fill(\'value\');// Click an element with data-test-id "submit"awaitpage.locator(\'data-test-id=submit\').click();`\n```\n\nnote\nAttribute selectors are not CSS selectors, so anything CSS-specific like\n`:enabled`\nis not supported. For more features, use a proper\ncss (https://playwright.dev/docs/other-locators#css-locator)\nselector, e.g.\n`css=[data-test="login"]:enabled`\n.', 'If you absolutely must use CSS or XPath locators, you can use\npage.locator() (https://playwright.dev/docs/api/class-page#page-locator)\nto create a locator that takes a selector describing how to find an element in the page. Playwright supports CSS and XPath selectors, and auto-detects them if you omit\n`css=`\nor\n`xpath=`\nprefix.\n\n```\n`awaitpage.locator(\'css=button\').click();awaitpage.locator(\'xpath=//button\').click();awaitpage.locator(\'button\').click();awaitpage.locator(\'//button\').click();`\n```\n\nXPath and CSS selectors can be tied to the DOM structure or implementation. These selectors can break when the DOM structure changes. Long CSS or XPath chains below are an example of a\nbad practice\nthat leads to unstable tests:\n\n```\n`awaitpage.locator(\'#tsf &gt; div:nth-child(2) &gt; div.A8SBwf &gt; div.RNNXgb &gt; div &gt; div.a4bIc &gt; input\').click();awaitpage.locator(\'//*[@id="tsf"]/div[2]/div[1]/div[1]/div/div[2]/input\').click();`\n```\n\nWhen to use this\nCSS and XPath are not recommended as the DOM can often change leading to non resilient tests. Instead, try to come up with a locator that is close to how the user perceives the page such as\nrole locators (https://playwright.dev/docs/locators#locate-by-role)\nor\ndefine an explicit testing contract (https://playwright.dev/docs/locators#locate-by-test-id)\nusing test ids.', 'The\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\nlocator reflects how users and assistive technology perceive the page, for example whether some element is a button or a checkbox. When locating by role, you should usually pass the accessible name as well, so that the locator pinpoints the exact element.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign up\nSubscribe\nSubmit\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nRole locators include\nbuttons, checkboxes, headings, links, lists, tables, and many more (https://www.w3.org/TR/html-aria/#docconformance)\nand follow W3C specifications for\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. Note that many html elements like\n`&lt;button&gt;`\nhave an\nimplicitly defined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role locator.\n\nNote that role locators\ndo not replace\naccessibility audits and conformance tests, but rather give early feedback about the ARIA guidelines.\n\nWhen to use role locators\nWe recommend prioritizing role locators to locate elements, as it is the closest way to how users and assistive technology perceive the page.', "Find an element by the text it contains. You can match by a substring, exact string, or a regular expression when using\npage.getByText() (https://playwright.dev/docs/api/class-page#page-get-by-text)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nWelcome, John\n```\n`&lt;span&gt;Welcome, John&lt;/span&gt;`\n```\n\nYou can locate the element by the text it contains:\n\n```\n`awaitexpect(page.getByText('Welcome, John')).toBeVisible();`\n```\n\nSet an exact match:\n\n```\n`awaitexpect(page.getByText('Welcome, John',{exact:true})).toBeVisible();`\n```\n\nMatch with a regular expression:\n\n```\n`awaitexpect(page.getByText(/welcome,[A-Za-z]+$/i)).toBeVisible();`\n```\n\nnote\nMatching by text always normalizes whitespace, even with exact match. For example, it turns multiple spaces into one, turns line breaks into spaces and ignores leading and trailing whitespace.\n\nWhen to use text locators\nWe recommend using text locators to find non interactive elements like\n`div`\n,\n`span`\n,\n`p`\n, etc. For interactive elements like\n`button`\n,\n`a`\n,\n`input`\n, etc. use\nrole locators (https://playwright.dev/docs/locators#locate-by-role)\n.\n\nYou can also\nfilter by text (https://playwright.dev/docs/locators#filter-by-text)\nwhich can be useful when trying to find a particular item in a list."]</t>
+          <t>['Testing by test ids is the most resilient way of testing as even if your text or role of the attribute changes, the test will still pass. QA\'s and developers should define explicit test ids and query them with\npage.getByTestId() (https://playwright.dev/docs/api/class-page#page-get-by-test-id)\n. However testing by test ids is not user facing. If the role or text value is important to you then consider using user facing locators such as\nrole (https://playwright.dev/docs/locators#locate-by-role)\nand\ntext locators (https://playwright.dev/docs/locators#locate-by-text)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nItinéraire\n```\n`&lt;buttondata-testid="directions"&gt;Itinéraire&lt;/button&gt;`\n```\n\nYou can locate the element by its test id:\n\n```\n`awaitpage.getByTestId(\'directions\').click();`\n```\n\nWhen to use testid locators\nYou can also use test ids when you choose to use the test id methodology or when you can\'t locate by\nrole (https://playwright.dev/docs/locators#locate-by-role)\nor\ntext (https://playwright.dev/docs/locators#locate-by-text)\n.', 'Playwright comes with the ability to generate tests for you as you perform actions in the browser and is a great way to quickly get started with testing. Playwright will look at your page and figure out the best locator, prioritizing\nrole, text and test id locators (https://playwright.dev/docs/locators)\n. If the generator finds multiple elements matching the locator, it will improve the locator to make it resilient that uniquely identify the target element.', 'The\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\nlocator reflects how users and assistive technology perceive the page, for example whether some element is a button or a checkbox. When locating by role, you should usually pass the accessible name as well, so that the locator pinpoints the exact element.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign up\nSubscribe\nSubmit\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nRole locators include\nbuttons, checkboxes, headings, links, lists, tables, and many more (https://www.w3.org/TR/html-aria/#docconformance)\nand follow W3C specifications for\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. Note that many html elements like\n`&lt;button&gt;`\nhave an\nimplicitly defined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role locator.\n\nNote that role locators\ndo not replace\naccessibility audits and conformance tests, but rather give early feedback about the ARIA guidelines.\n\nWhen to use role locators\nWe recommend prioritizing role locators to locate elements, as it is the closest way to how users and assistive technology perceive the page.', 'warning\nWe recommend\nlocating by test id (https://playwright.dev/docs/locators#locate-by-test-id)\ninstead.\n\nPlaywright supports shorthand for selecting elements using certain attributes. Currently, only the following attributes are supported:\n\n`id`\n`data-testid`\n`data-test-id`\n`data-test`\n\n```\n`// Fill an input with the id "username"awaitpage.locator(\'id=username\').fill(\'value\');// Click an element with data-test-id "submit"awaitpage.locator(\'data-test-id=submit\').click();`\n```\n\nnote\nAttribute selectors are not CSS selectors, so anything CSS-specific like\n`:enabled`\nis not supported. For more features, use a proper\ncss (https://playwright.dev/docs/other-locators#css-locator)\nselector, e.g.\n`css=[data-test="login"]:enabled`\n.', "Find an element by the text it contains. You can match by a substring, exact string, or a regular expression when using\npage.getByText() (https://playwright.dev/docs/api/class-page#page-get-by-text)\n.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nWelcome, John\n```\n`&lt;span&gt;Welcome, John&lt;/span&gt;`\n```\n\nYou can locate the element by the text it contains:\n\n```\n`awaitexpect(page.getByText('Welcome, John')).toBeVisible();`\n```\n\nSet an exact match:\n\n```\n`awaitexpect(page.getByText('Welcome, John',{exact:true})).toBeVisible();`\n```\n\nMatch with a regular expression:\n\n```\n`awaitexpect(page.getByText(/welcome,[A-Za-z]+$/i)).toBeVisible();`\n```\n\nnote\nMatching by text always normalizes whitespace, even with exact match. For example, it turns multiple spaces into one, turns line breaks into spaces and ignores leading and trailing whitespace.\n\nWhen to use text locators\nWe recommend using text locators to find non interactive elements like\n`div`\n,\n`span`\n,\n`p`\n, etc. For interactive elements like\n`button`\n,\n`a`\n,\n`input`\n, etc. use\nrole locators (https://playwright.dev/docs/locators#locate-by-role)\n.\n\nYou can also\nfilter by text (https://playwright.dev/docs/locators#filter-by-text)\nwhich can be useful when trying to find a particular item in a list.", 'If you absolutely must use CSS or XPath locators, you can use\npage.locator() (https://playwright.dev/docs/api/class-page#page-locator)\nto create a locator that takes a selector describing how to find an element in the page. Playwright supports CSS and XPath selectors, and auto-detects them if you omit\n`css=`\nor\n`xpath=`\nprefix.\n\n```\n`awaitpage.locator(\'css=button\').click();awaitpage.locator(\'xpath=//button\').click();awaitpage.locator(\'button\').click();awaitpage.locator(\'//button\').click();`\n```\n\nXPath and CSS selectors can be tied to the DOM structure or implementation. These selectors can break when the DOM structure changes. Long CSS or XPath chains below are an example of a\nbad practice\nthat leads to unstable tests:\n\n```\n`awaitpage.locator(\'#tsf &gt; div:nth-child(2) &gt; div.A8SBwf &gt; div.RNNXgb &gt; div &gt; div.a4bIc &gt; input\').click();awaitpage.locator(\'//*[@id="tsf"]/div[2]/div[1]/div[1]/div/div[2]/input\').click();`\n```\n\nWhen to use this\nCSS and XPath are not recommended as the DOM can often change leading to non resilient tests. Instead, try to come up with a locator that is close to how the user perceives the page such as\nrole locators (https://playwright.dev/docs/locators#locate-by-role)\nor\ndefine an explicit testing contract (https://playwright.dev/docs/locators#locate-by-test-id)\nusing test ids.', "These are the recommended built-in locators.\n\npage.getByRole() (https://playwright.dev/docs/locators#locate-by-role)\nto locate by explicit and implicit accessibility attributes.\npage.getByText() (https://playwright.dev/docs/locators#locate-by-text)\nto locate by text content.\npage.getByLabel() (https://playwright.dev/docs/locators#locate-by-label)\nto locate a form control by associated label's text.\npage.getByPlaceholder() (https://playwright.dev/docs/locators#locate-by-placeholder)\nto locate an input by placeholder.\npage.getByAltText() (https://playwright.dev/docs/locators#locate-by-alt-text)\nto locate an element, usually image, by its text alternative.\npage.getByTitle() (https://playwright.dev/docs/locators#locate-by-title)\nto locate an element by its title attribute.\npage.getByTestId() (https://playwright.dev/docs/locators#locate-by-test-id)\nto locate an element based on its\n`data-testid`\nattribute (other attributes can be configured).\n\n```\n`awaitpage.getByLabel('User Name').fill('John');awaitpage.getByLabel('Password').fill('secret-password');awaitpage.getByRole('button',{name:'Sign in'}).click();awaitexpect(page.getByText('Welcome, John!')).toBeVisible();`\n```"]</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1867,7 +1904,10 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Teams add `data-testid` attributes because it is the most resilient way of testing; the test will still pass even if the text or role of the attribute changes. Additionally, teams may use them when they choose to follow the test id methodology or when they cannot locate an element by role or text.</t>
+          <t>Teams add `data-testid` attributes because testing by test IDs is the most resilient way of testing. Even if the text or role of an element changes, the test will still pass.
+While Playwright recommends prioritizing user-facing locators like `role` and `text` because they reflect how users and assistive technology perceive the page, `data-testid` is used when:
+* You choose to use the test ID methodology.
+* You cannot locate an element by `role` or `text`.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1876,28 +1916,28 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.009317500000000001</v>
+        <v>0.0008684999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>35945</v>
+        <v>40142</v>
       </c>
       <c r="H24" t="n">
         <v>0.5</v>
       </c>
       <c r="I24" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="J24" t="n">
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1296296296296296</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3666666666483334</v>
+        <v>0.9999999999</v>
       </c>
       <c r="N24" t="n">
         <v>1</v>
@@ -1911,7 +1951,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['Playwright runs browsers in headless mode by default. To change this behavior, use\n`headless: false`\nas a launch option.\n\nYou can also use the\nslowMo (https://playwright.dev/docs/api/class-browsertype#browser-type-launch-option-slow-mo)\noption to slow down execution (by N milliseconds per operation) and follow along while debugging.\n\n```\n`// Chromium, Firefox, or WebKitawaitchromium.launch({headless:false,slowMo:100});`\n```', 'Running and debugging tests | Playwright', 'UI Mode | Playwright', 'UI Mode lets you explore, run, and debug tests with a time travel experience complete with a watch mode. All test files are displayed in the testing sidebar, allowing you to expand each file and describe block to individually run, view, watch, and debug each test. Filter tests by\nname\n,\nprojects (https://playwright.dev/docs/test-projects)\n(set in your\n`playwright.config`\nfile),\n@tag\n, or by the execution status of\npassed\n,\nfailed\n, and\nskipped\n. See a full trace of your tests and hover back and forward over each action to see what was happening during each step. You can also pop out the DOM snapshot of a given moment into a separate window for a better debugging experience.', 'To open UI mode, run the following command in your terminal:\n\n```\n`npx playwrighttest--ui`\n```', 'The Playwright Inspector is a GUI tool to help you debug your Playwright tests. It allows you to step through your tests, live edit locators, pick locators and see actionability logs.', 'We highly recommend debugging your tests with\nUI Mode (https://playwright.dev/docs/test-ui-mode)\nfor a better developer experience where you can easily walk through each step of the test and visually see what was happening before, during, and after each step. UI mode also comes with many other features such as the locator picker, watch mode, and more.\n\n```\n`npx playwrighttest--ui`\n```\n\nWhile debugging you can use the Pick Locator button to select an element on the page and see the locator that Playwright would use to find that element. You can also edit the locator in the locator playground and see it highlighting live in the browser window. Use the Copy Locator button to copy the locator to your clipboard and then paste it into your test.\n\nCheck out our\ndetailed guide on UI Mode (https://playwright.dev/docs/test-ui-mode)\nto learn more about its features.']</t>
+          <t>['Playwright runs browsers in headless mode by default. To change this behavior, use\n`headless: false`\nas a launch option.\n\nYou can also use the\nslowMo (https://playwright.dev/docs/api/class-browsertype#browser-type-launch-option-slow-mo)\noption to slow down execution (by N milliseconds per operation) and follow along while debugging.\n\n```\n`// Chromium, Firefox, or WebKitawaitchromium.launch({headless:false,slowMo:100});`\n```', 'You can play, pause or step through each action of your test using the toolbar at the top of the Inspector. You can see the current action highlighted in the test code, and matching elements highlighted in the browser window.', 'The Playwright Inspector is a GUI tool to help you debug your Playwright tests. It allows you to step through your tests, live edit locators, pick locators and see actionability logs.', 'To set a breakpoint click next to the line number where you want the breakpoint to be until a red dot appears. Run the tests in debug mode by right clicking on the line next to the test you want to run.\n\nA browser window will open and the test will run and pause at where the breakpoint is set. You can step through the tests, pause the test and rerun the tests from the menu in VS Code.', 'To debug all tests, run the Playwright test command followed by the\n`--debug`\nflag.\n\n```\n`npx playwrighttest--debug`\n```\n\nThis command opens a browser window as well as the Playwright Inspector. You can use the step over button at the top of the inspector to step through your test. Or, press the play button to run your test from start to finish. Once the test finishes, the browser window closes.\n\nTo debug one test file, run the Playwright test command with the test file name that you want to debug followed by the\n`--debug`\nflag.\n\n```\n`npx playwrighttestexample.spec.ts--debug`\n```\n\nTo debug a specific test from the line number where the\n`test(..`\nis defined, add a colon followed by the line number at the end of the test file name, followed by the\n`--debug`\nflag.\n\n```\n`npx playwrighttestexample.spec.ts:10--debug`\n```\n\nWhile debugging you can use the Pick Locator button to select an element on the page and see the locator that Playwright would use to find that element. You can also edit the locator and see it highlighting live in the browser window. Use the Copy Locator button to copy the locator to your clipboard and then paste it into your test.\n\nCheck out our\ndebugging guide (https://playwright.dev/docs/debug)\nto learn more about debugging with the\nVS Code debugger (https://playwright.dev/docs/debug#vs-code-debugger)\n, UI Mode, and the\nPlaywright Inspector (https://playwright.dev/docs/debug#playwright-inspector)\nas well as debugging with\nBrowser Developer tools (https://playwright.dev/docs/debug#browser-developer-tools)\n.', 'To debug all tests run the test command with the\n`--debug`\nflag. This will run tests one by one, and open the inspector and a browser window for each test.\n\n```\n`npx playwrighttest--debug`\n```', 'When running in Debug Mode with\n`PWDEBUG=console`\n, a\n`playwright`\nobject is available in the Developer tools console. Developer tools can help you to:\n\nInspect the DOM tree and\nfind element selectors\nSee console logs\nduring execution (or learn how to\nread logs via API (https://playwright.dev/docs/api/class-page#page-event-console)\n)\nCheck\nnetwork activity\nand other developer tools features\n\nTo debug your tests using the browser developer tools, start by setting a breakpoint in your test to pause the execution using the\npage.pause() (https://playwright.dev/docs/api/class-page#page-pause)\nmethod.\n\n```\n`awaitpage.pause();`\n```\n\nOnce you have set a breakpoint in your test, you can then run your test with\n`PWDEBUG=console`\n.\n\nBash\nPowerShell\nBatch\n```\n`PWDEBUG=console npx playwrighttest`\n```\n```\n`$env:PWDEBUG="console"npx playwright test`\n```\n```\n`setPWDEBUG=consolenpxplaywright test`\n```\n\nOnce Playwright launches the browser window, you can open the developer tools. The\n`playwright`\nobject will be available in the console panel.']</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1921,17 +1961,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To watch the browser as your script runs and slow it down, you have two primary options:
-**1. Recommended: UI Mode**
-Playwright highly recommends using UI Mode for debugging, as it provides a better developer experience that allows you to walk through each step of the test and visually see what happened before, during, and after each step. It includes a watch mode and allows you to hover back and forward over each action.
-*   **How to use:** Run the following command in your terminal:
-    `npx playwright test --ui`
-**2. Alternative: Headed mode with `slowMo`**
-If you prefer to run the script directly, you can disable headless mode and add a delay to each operation.
-*   **How to use:** Set `headless: false` and the `slowMo` option (in milliseconds) in your launch configuration:
-    ```javascript
-    await chromium.launch({headless: false, slowMo: 100});
-    ```</t>
+          <t>To watch the browser as your script runs and slow it down, you can use the following methods:
+### Slowing down execution
+To slow down execution by a specific number of milliseconds per operation, use the `slowMo` option when launching the browser. You must also set `headless: false` to see the browser window.
+```javascript
+await chromium.launch({ headless: false, slowMo: 100 });
+```
+### Stepping through tests
+If you want to follow along by controlling the execution flow, you can use the **Playwright Inspector**:
+*   **Run with the `--debug` flag:** Use `npx playwright test --debug` to open the browser and the Inspector. You can use the "step over" button to move through your test action by action, or the "play" button to run it from start to finish.
+*   **VS Code Debugger:** Set a breakpoint by clicking next to a line number in your test file, then run the test in debug mode (right-click the line next to the test). The browser will open and pause at your breakpoint, allowing you to step through the code.
+*   **`page.pause()`:** You can insert `await page.pause();` directly into your test code to force the execution to pause at that specific point.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1940,25 +1980,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.009950249999999002</v>
+        <v>0.00084775</v>
       </c>
       <c r="G25" t="n">
-        <v>36486</v>
+        <v>41427</v>
       </c>
       <c r="H25" t="n">
         <v>0.5</v>
       </c>
       <c r="I25" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="J25" t="n">
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.07971014492753623</v>
+        <v>0.04123711340206185</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="M25" t="n">
         <v>0.9999999999</v>
@@ -1975,7 +2015,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['Debugger | Playwright\n\nAPI for controlling the Playwright debugger. The debugger allows pausing script execution and inspecting the page. Obtain the debugger instance via\nbrowserContext.debugger (https://playwright.dev/docs/api/class-browsercontext#browser-context-debugger)\n.', 'Test generator | Playwright', 'UI Mode | Playwright', 'To debug all tests, run the Playwright test command followed by the\n`--debug`\nflag.\n\n```\n`npx playwrighttest--debug`\n```\n\nThis command opens a browser window as well as the Playwright Inspector. You can use the step over button at the top of the inspector to step through your test. Or, press the play button to run your test from start to finish. Once the test finishes, the browser window closes.\n\nTo debug one test file, run the Playwright test command with the test file name that you want to debug followed by the\n`--debug`\nflag.\n\n```\n`npx playwrighttestexample.spec.ts--debug`\n```\n\nTo debug a specific test from the line number where the\n`test(..`\nis defined, add a colon followed by the line number at the end of the test file name, followed by the\n`--debug`\nflag.\n\n```\n`npx playwrighttestexample.spec.ts:10--debug`\n```\n\nWhile debugging you can use the Pick Locator button to select an element on the page and see the locator that Playwright would use to find that element. You can also edit the locator and see it highlighting live in the browser window. Use the Copy Locator button to copy the locator to your clipboard and then paste it into your test.\n\nCheck out our\ndebugging guide (https://playwright.dev/docs/debug)\nto learn more about debugging with the\nVS Code debugger (https://playwright.dev/docs/debug#vs-code-debugger)\n, UI Mode, and the\nPlaywright Inspector (https://playwright.dev/docs/debug#playwright-inspector)\nas well as debugging with\nBrowser Developer tools (https://playwright.dev/docs/debug#browser-developer-tools)\n.', 'Running and debugging tests | Playwright', 'Since Playwright runs in Node.js, you can debug it with your debugger of choice, e.g. using\n`console.log`\n, inside your IDE, or directly in VS Code with the\nVS Code Extension (https://playwright.dev/docs/getting-started-vscode)\n. Playwright comes with\nUI Mode (https://playwright.dev/docs/test-ui-mode)\n, where you can easily walk through each step of the test, see logs, errors, network requests, inspect the DOM snapshot, and more. You can also use the\nPlaywright Inspector (https://playwright.dev/docs/debug#playwright-inspector)\n, which allows you to step through Playwright API calls, see their debug logs, and explore\nlocators (https://playwright.dev/docs/locators)\n.']</t>
+          <t>['To speed up the debugging process you can add a\npage.pause() (https://playwright.dev/docs/api/class-page#page-pause)\nmethod to your test. This way you won\'t have to step through each action of your test to get to the point where you want to debug.\n\n```\n`awaitpage.pause();`\n```\n\nOnce you add a\n`page.pause()`\ncall, run your tests in debug mode. Clicking the "Resume" button in the Inspector will run the test and only stop on the\n`page.pause()`\n.', 'To set a breakpoint click next to the line number where you want the breakpoint to be until a red dot appears. Run the tests in debug mode by right clicking on the line next to the test you want to run.\n\nA browser window will open and the test will run and pause at where the breakpoint is set. You can step through the tests, pause the test and rerun the tests from the menu in VS Code.', 'Added in: v1.59\n\ndebugger.requestPause\n\nConfigures the debugger to pause before the next action is executed.\n\nThrows if the debugger is already paused. Use\ndebugger.next() (https://playwright.dev/docs/api/class-debugger#debugger-next)\nor\ndebugger.runTo() (https://playwright.dev/docs/api/class-debugger#debugger-run-to)\nto step while paused.\n\nNote that\npage.pause() (https://playwright.dev/docs/api/class-page#page-pause)\nis equivalent to a "debugger" statement — it pauses execution at the call site immediately. On the contrary,\ndebugger.requestPause() (https://playwright.dev/docs/api/class-debugger#debugger-request-pause)\nis equivalent to "pause on next statement" — it configures the debugger to pause before the next action is executed.\n\nUsage\n\n```\n`awaitdebugger.requestPause();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-debugger#debugger-request-pause-return)', 'Added in: v1.59\n\ndebugger.runTo\n\nResumes script execution and pauses when an action originates from the given source location. Throws if the debugger is not paused.\n\nUsage\n\n```\n`awaitdebugger.runTo(location);`\n```\n\nArguments\n\n`location`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n# (https://playwright.dev/docs/api/class-debugger#debugger-run-to-option-location)\n`file`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`line`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n`column`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nThe source location to pause at.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-debugger#debugger-run-to-return)', 'To debug one test on a specific line, run the test command followed by the name of the test file and the line number of the test you want to debug, followed by the\n`--debug`\nflag. This will run a single test in each browser configured in your\nplaywright.config (https://playwright.dev/docs/test-projects#configure-projects-for-multiple-browsers)\nand open the inspector.\n\n```\n`npx playwrighttestexample.spec.ts:10--debug`\n```', 'To run one test on a specific browser add the name of the test file and the line number of the test you want to debug as well as the\n`--project`\nflag followed by the name of the project.\n\n```\n`npx playwrighttestexample.spec.ts:10--project=webkit--debug`\n```', 'The Playwright Inspector is a GUI tool to help you debug your Playwright tests. It allows you to step through your tests, live edit locators, pick locators and see actionability logs.']</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1985,11 +2025,13 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Yes. You can pause execution at a specific line by running the test file with the line number appended to the filename, followed by the `--debug` flag:
-```bash
-npx playwright test example.spec.ts:10 --debug
-```
-This opens the Playwright Inspector, which allows you to pause script execution and inspect the page. Once paused, you can use the Pick Locator button to select elements, edit locators, and see them highlighted live in the browser window. While the inspector provides a step-over button to step through the test, you can also use the play button to run the test from the paused point to the end.</t>
+          <t>Yes, there are several ways to stop a test at a chosen line to debug:
+*   **Using `page.pause()`:** You can add `await page.pause();` to your test code. When you run the test in debug mode, the execution will stop at that line [1].
+*   **Using VS Code Breakpoints:** Click next to the line number in your editor until a red dot appears, then run the test in debug mode. The test will pause at that line [2].
+*   **Using the CLI:** You can run a specific test file at a specific line number using the `--debug` flag:
+    *   To run on all configured browsers: `npx playwright test example.spec.ts:10 --debug` [5].
+    *   To run on a specific browser: `npx playwright test example.spec.ts:10 --project=webkit --debug` [6].
+*   **Using `debugger.runTo()`:** If the debugger is already paused, you can use `await debugger.runTo({ file: 'path/to/file', line: 10 });` to resume execution and pause when an action originates from that specific location [4].</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1998,31 +2040,31 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.008770499999999999</v>
+        <v>0.00084</v>
       </c>
       <c r="G26" t="n">
-        <v>33642</v>
+        <v>42097</v>
       </c>
       <c r="H26" t="n">
         <v>0.5</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="J26" t="n">
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1132075471698113</v>
+        <v>0.09815950920245399</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3333333333</v>
+        <v>0.8333333332916666</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2033,7 +2075,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['Authentication | Playwright', "This is the\nrecommended\napproach for tests that\nmodify server-side state\n. In Playwright, worker processes run in parallel. In this approach, each parallel worker is authenticated once. All tests ran by worker are reusing the same authentication state. We will need multiple testing accounts, one per each parallel worker.\n\nWhen to use\n\nYour tests modify shared server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting.\n\nWhen not to use\n\nYour tests do not modify any shared server-side state. In this case, all tests can use a single shared account.\n\nDetails\n\nWe will authenticate once per\nworker process (https://playwright.dev/docs/test-parallel#worker-processes)\n, each with a unique account.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\noverride storageState fixture (https://playwright.dev/docs/test-fixtures#overriding-fixtures)\nto authenticate once per worker. Use\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({browser},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constpage=awaitbrowser.newPage({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill(account.username);awaitpage.getByLabel('Password').fill(account.password);awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:fileName});awaitpage.close();awaituse(fileName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n. No changes are needed in the config.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({page})=&gt;{// page is authenticated});`\n```", "You can leverage\n`process.env.TEST_WORKER_INDEX`\nor\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nmentioned above to isolate user data in the database between tests running on different workers. All tests run by the worker reuse the same user.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\ncreate dbUserName fixture (https://playwright.dev/docs/test-fixtures#creating-a-fixture)\nand initialize a new user in the test database. Use\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';// Import project utils for managing users in the test database.import{createUserInTestDatabase,deleteUserFromTestDatabase}from'./my-db-utils';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{dbUserName:string}&gt;({// Returns db user name unique for the worker.dbUserName:[async({},use)=&gt;{// Use workerIndex as a unique identifier for each worker.constuserName=`user-${test.info().workerIndex}`;// Initialize user in the database.awaitcreateUserInTestDatabase(userName);awaituse(userName);// Clean up after the tests are done.awaitdeleteUserFromTestDatabase(userName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({dbUserName})=&gt;{// Use the user name in the test.});`\n```", 'Each worker process is assigned two ids: a unique worker index that starts with 1, and a parallel index that is between\n`0`\nand\n`workers - 1`\n. When a worker is restarted, for example after a failure, the new worker process has the same\n`parallelIndex`\nand a new\n`workerIndex`\n.\n\nYou can read an index from environment variables\n`process.env.TEST_WORKER_INDEX`\nand\n`process.env.TEST_PARALLEL_INDEX`\n, or access them through\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nand\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\n.', "Playwright Test uses\nworker processes (https://playwright.dev/docs/test-parallel)\nto run test files. Similar to how test fixtures are set up for individual test runs, worker fixtures are set up for each worker process. That's where you can set up services, run servers, etc. Playwright Test will reuse the worker process for as many test files as it can, provided their worker fixtures match and hence environments are identical.\n\nBelow we'll create an\n`account`\nfixture that will be shared by all tests in the same worker, and override the\n`page`\nfixture to log in to this account for each test. To generate unique accounts, we'll use the\nworkerInfo.workerIndex (https://playwright.dev/docs/api/class-workerinfo#worker-info-worker-index)\nthat is available to any test or fixture. Note the tuple-like syntax for the worker fixture - we have to pass\n`{scope: 'worker'}`\nso that test runner sets this fixture up once per worker.\n\nIn addition to only being run once per worker, worker-scoped fixtures also get a separate timeout equal to the default test timeout. You can change it by passing the\n`timeout`\noption. See\nfixture timeout (https://playwright.dev/docs/test-fixtures#fixture-timeout)\nfor more details.\n\nmy-test.ts\n```\n`import{testasbase}from'@playwright/test';typeAccount={username:string;password:string;};// Note that we pass worker fixture types as a second template parameter.exportconsttest=base.extend&lt;{},{account:Account}&gt;({account:[async({browser},use,workerInfo)=&gt;{// Unique username.constusername='user'+workerInfo.workerIndex;constpassword='verysecure';// Create the account with Playwright.constpage=awaitbrowser.newPage();awaitpage.goto('/signup');awaitpage.getByLabel('User Name').fill(username);awaitpage.getByLabel('Password').fill(password);awaitpage.getByText('Sign up').click();// Make sure everything is ok.awaitexpect(page.getByTestId('result')).toHaveText('Success');// Do not forget to cleanup.awaitpage.close();// Use the account value.awaituse({username,password});},{scope:'worker'}],page:async({page,account},use)=&gt;{// Sign in with our account.const{username,password}=account;awaitpage.goto('/signin');awaitpage.getByLabel('User Name').fill(username);awaitpage.getByLabel('Password').fill(password);awaitpage.getByText('Sign in').click();awaitexpect(page.getByTestId('userinfo')).toHaveText(username);// Use signed-in page in the test.awaituse(page);},});export{expect}from'@playwright/test';`\n```", 'Isolation | Playwright', 'Parallelism | Playwright']</t>
+          <t>["This is the\nrecommended\napproach for tests that\nmodify server-side state\n. In Playwright, worker processes run in parallel. In this approach, each parallel worker is authenticated once. All tests ran by worker are reusing the same authentication state. We will need multiple testing accounts, one per each parallel worker.\n\nWhen to use\n\nYour tests modify shared server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting.\n\nWhen not to use\n\nYour tests do not modify any shared server-side state. In this case, all tests can use a single shared account.\n\nDetails\n\nWe will authenticate once per\nworker process (https://playwright.dev/docs/test-parallel#worker-processes)\n, each with a unique account.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\noverride storageState fixture (https://playwright.dev/docs/test-fixtures#overriding-fixtures)\nto authenticate once per worker. Use\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({browser},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constpage=awaitbrowser.newPage({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill(account.username);awaitpage.getByLabel('Password').fill(account.password);awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:fileName});awaitpage.close();awaituse(fileName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n. No changes are needed in the config.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({page})=&gt;{// page is authenticated});`\n```", "You can leverage\n`process.env.TEST_WORKER_INDEX`\nor\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nmentioned above to isolate user data in the database between tests running on different workers. All tests run by the worker reuse the same user.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\ncreate dbUserName fixture (https://playwright.dev/docs/test-fixtures#creating-a-fixture)\nand initialize a new user in the test database. Use\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';// Import project utils for managing users in the test database.import{createUserInTestDatabase,deleteUserFromTestDatabase}from'./my-db-utils';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{dbUserName:string}&gt;({// Returns db user name unique for the worker.dbUserName:[async({},use)=&gt;{// Use workerIndex as a unique identifier for each worker.constuserName=`user-${test.info().workerIndex}`;// Initialize user in the database.awaitcreateUserInTestDatabase(userName);awaituse(userName);// Clean up after the tests are done.awaitdeleteUserFromTestDatabase(userName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({dbUserName})=&gt;{// Use the user name in the test.});`\n```", "Playwright Test uses\nworker processes (https://playwright.dev/docs/test-parallel)\nto run test files. Similar to how test fixtures are set up for individual test runs, worker fixtures are set up for each worker process. That's where you can set up services, run servers, etc. Playwright Test will reuse the worker process for as many test files as it can, provided their worker fixtures match and hence environments are identical.\n\nBelow we'll create an\n`account`\nfixture that will be shared by all tests in the same worker, and override the\n`page`\nfixture to log in to this account for each test. To generate unique accounts, we'll use the\nworkerInfo.workerIndex (https://playwright.dev/docs/api/class-workerinfo#worker-info-worker-index)\nthat is available to any test or fixture. Note the tuple-like syntax for the worker fixture - we have to pass\n`{scope: 'worker'}`\nso that test runner sets this fixture up once per worker.\n\nIn addition to only being run once per worker, worker-scoped fixtures also get a separate timeout equal to the default test timeout. You can change it by passing the\n`timeout`\noption. See\nfixture timeout (https://playwright.dev/docs/test-fixtures#fixture-timeout)\nfor more details.\n\nmy-test.ts\n```\n`import{testasbase}from'@playwright/test';typeAccount={username:string;password:string;};// Note that we pass worker fixture types as a second template parameter.exportconsttest=base.extend&lt;{},{account:Account}&gt;({account:[async({browser},use,workerInfo)=&gt;{// Unique username.constusername='user'+workerInfo.workerIndex;constpassword='verysecure';// Create the account with Playwright.constpage=awaitbrowser.newPage();awaitpage.goto('/signup');awaitpage.getByLabel('User Name').fill(username);awaitpage.getByLabel('Password').fill(password);awaitpage.getByText('Sign up').click();// Make sure everything is ok.awaitexpect(page.getByTestId('result')).toHaveText('Success');// Do not forget to cleanup.awaitpage.close();// Use the account value.awaituse({username,password});},{scope:'worker'}],page:async({page,account},use)=&gt;{// Sign in with our account.const{username,password}=account;awaitpage.goto('/signin');awaitpage.getByLabel('User Name').fill(username);awaitpage.getByLabel('Password').fill(password);awaitpage.getByText('Sign in').click();awaitexpect(page.getByTestId('userinfo')).toHaveText(username);// Use signed-in page in the test.awaituse(page);},});export{expect}from'@playwright/test';`\n```", 'Each worker process is assigned two ids: a unique worker index that starts with 1, and a parallel index that is between\n`0`\nand\n`workers - 1`\n. When a worker is restarted, for example after a failure, the new worker process has the same\n`parallelIndex`\nand a new\n`workerIndex`\n.\n\nYou can read an index from environment variables\n`process.env.TEST_WORKER_INDEX`\nand\n`process.env.TEST_PARALLEL_INDEX`\n, or access them through\ntestInfo.workerIndex (https://playwright.dev/docs/api/class-testinfo#test-info-worker-index)\nand\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\n.', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", 'Playwright Test runs tests in parallel. In order to achieve that, it runs several worker processes that run at the same time. By default,\ntest files\nare run in parallel. Tests in a single file are run in order, in the same worker process.\n\nYou can configure tests using\ntest.describe.configure (https://playwright.dev/docs/test-parallel#parallelize-tests-in-a-single-file)\nto run\ntests in a single file\nin parallel.\nYou can configure\nentire project\nto have all tests in all files to run in parallel using\ntestProject.fullyParallel (https://playwright.dev/docs/api/class-testproject#test-project-fully-parallel)\nor\ntestConfig.fullyParallel (https://playwright.dev/docs/api/class-testconfig#test-config-fully-parallel)\n.\nTo\ndisable\nparallelism limit the number of\nworkers to one (https://playwright.dev/docs/test-parallel#disable-parallelism)\n.\n\nYou can control the number of\nparallel worker processes (https://playwright.dev/docs/test-parallel#limit-workers)\nand\nlimit the number of failures (https://playwright.dev/docs/test-parallel#limit-failures-and-fail-fast)\nin the whole test suite for efficiency.', "Automatic fixtures are set up for each test/worker, even when the test does not list them directly. To create an automatic fixture, use the tuple syntax and pass\n`{ auto: true }`\n.\n\nHere is an example fixture that automatically attaches debug logs when the test fails, so we can later review the logs in the reporter. Note how it uses the\nTestInfo (https://playwright.dev/docs/api/class-testinfo)\nobject that is available in each test/fixture to retrieve metadata about the test being run.\n\nmy-test.ts\n```\n`importdebugfrom'debug';importfsfrom'fs';import{testasbase}from'@playwright/test';exportconsttest=base.extend&lt;{saveLogs:void}&gt;({saveLogs:[async({},use,testInfo)=&gt;{// Collecting logs during the test.constlogs=[];debug.log=(...args)=&gt;logs.push(args.map(String).join(''));debug.enable('myserver');awaituse();// After the test we can check whether the test passed or failed.if(testInfo.status!==testInfo.expectedStatus){// outputPath() API guarantees a unique file name.constlogFile=testInfo.outputPath('logs.txt');awaitfs.promises.writeFile(logFile,logs.join('\\n'),'utf8');testInfo.attachments.push({name:'logs',contentType:'text/plain',path:logFile});}},{auto:true}],});export{expect}from'@playwright/test';`\n```"]</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2043,39 +2085,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>To avoid collisions when tests mutate shared server-side state in parallel, the recommended approach is to use **one account per parallel worker**.
+          <t>To avoid collisions when tests mutate shared server state in parallel, the recommended approach is to use **one account per parallel worker**.
 ### How to stay on separate accounts
-You must ensure each parallel worker is authenticated with a unique account. You can achieve this by creating a worker-scoped fixture that uses `testInfo.parallelIndex` to differentiate between workers.
-1.  **Create a fixture file** (e.g., `playwright/fixtures.ts`) that overrides the `storageState` fixture.
-2.  **Use `test.info().parallelIndex`** as a unique identifier for each worker to determine which account to use.
-3.  **Authenticate once per worker** by performing the login steps within the worker-scoped fixture and saving the authentication state to a unique file path based on the `parallelIndex`.
-**Example implementation:**
+You must authenticate once per worker process using a unique account for each. You can achieve this by creating a worker-scoped fixture in a `playwright/fixtures.ts` file that differentiates between workers using `testInfo.parallelIndex` or `testInfo.workerIndex`.
+1.  **Create a worker-scoped fixture**: Define a fixture with `{scope: 'worker'}`.
+2.  **Differentiate workers**: Use `test.info().parallelIndex` (or `workerIndex`) as a unique identifier to assign a specific account to that worker.
+3.  **Authenticate**: Perform the authentication steps within the fixture using the unique account assigned to that worker's index.
+4.  **Reuse state**: Save the authentication state (e.g., to a JSON file) and reuse it for all tests running within that specific worker.
+**Example implementation pattern:**
 ```typescript
-import { test as baseTest, expect } from '@playwright/test';
-import fs from 'fs';
-import path from 'path';
-export * from '@playwright/test';
+// playwright/fixtures.ts
+import { test as baseTest } from '@playwright/test';
 export const test = baseTest.extend&lt;{}, { workerStorageState: string }&gt;({
   storageState: ({ workerStorageState }, use) =&gt; use(workerStorageState),
   workerStorageState: [async ({ browser }, use) =&gt; {
     const id = test.info().parallelIndex;
-    const fileName = path.resolve(test.info().project.outputDir, `.auth/${id}.json`);
-    if (fs.existsSync(fileName)) {
-      await use(fileName);
-      return;
-    }
+    const fileName = `path/to/.auth/${id}.json`;
+    // 1. Acquire a unique account based on the worker ID
+    const account = await acquireAccount(id);
+    // 2. Perform login and save state
     const page = await browser.newPage({ storageState: undefined });
-    const account = await acquireAccount(id); // Acquire a unique account for this worker
-    // Perform authentication steps...
+    await page.goto('https://example.com/login');
+    // ... perform login steps ...
     await page.context().storageState({ path: fileName });
     await page.close();
     await use(fileName);
   }, { scope: 'worker' }],
 });
 ```
-After creating this file, import `test` from your fixtures file in your test files instead of `@playwright/test`.
-### Alternative for database isolation
-If you need to isolate user data specifically within a database rather than just authentication state, you can use `testInfo.workerIndex` to create and initialize a unique user in the test database for each worker, as described in the documentation for isolating test data between parallel workers.</t>
+After creating this file, import `test` from `playwright/fixtures.ts` in your test files instead of `@playwright/test`. This ensures each worker operates within its own authenticated context, preventing interference between parallel tests.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2084,28 +2122,28 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.0057028</v>
+        <v>0.00172425</v>
       </c>
       <c r="G27" t="n">
-        <v>37578</v>
+        <v>38520</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.46</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.06574394463667819</v>
+        <v>0.07037037037037037</v>
       </c>
       <c r="L27" t="n">
         <v>0.4523809523809524</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6791666666496875</v>
+        <v>0.999999999975</v>
       </c>
       <c r="N27" t="n">
         <v>1</v>
@@ -2119,7 +2157,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>['Run with\n`--load-storage`\nto consume the previously loaded storage from the\n`auth.json`\n. This way, all\ncookies (https://developer.mozilla.org/en-US/docs/Web/HTTP/Cookies)\n,\nlocalStorage (https://developer.mozilla.org/en-US/docs/Web/API/Window/localStorage)\nand\nIndexedDB (https://developer.mozilla.org/en-US/docs/Web/API/IndexedDB_API)\ndata will be restored, bringing most web apps to the authenticated state without the need to login again. This means you can continue generating tests from the logged in state.\n\n```\n`npx playwright codegen --load-storage=auth.json github.com/microsoft/playwright`\n```', 'You can use the test generator to generate tests using emulation so as to generate a test for a specific viewport, device, color scheme, as well as emulate the geolocation, language or timezone. The test generator can also generate a test while preserving authenticated state.', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", "This is the\nrecommended\napproach for tests that\nmodify server-side state\n. In Playwright, worker processes run in parallel. In this approach, each parallel worker is authenticated once. All tests ran by worker are reusing the same authentication state. We will need multiple testing accounts, one per each parallel worker.\n\nWhen to use\n\nYour tests modify shared server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting.\n\nWhen not to use\n\nYour tests do not modify any shared server-side state. In this case, all tests can use a single shared account.\n\nDetails\n\nWe will authenticate once per\nworker process (https://playwright.dev/docs/test-parallel#worker-processes)\n, each with a unique account.\n\nCreate\n`playwright/fixtures.ts`\nfile that will\noverride storageState fixture (https://playwright.dev/docs/test-fixtures#overriding-fixtures)\nto authenticate once per worker. Use\ntestInfo.parallelIndex (https://playwright.dev/docs/api/class-testinfo#test-info-parallel-index)\nto differentiate between workers.\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,expect}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({browser},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constpage=awaitbrowser.newPage({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill(account.username);awaitpage.getByLabel('Password').fill(account.password);awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:fileName});awaitpage.close();awaituse(fileName);},{scope:'worker'}],});`\n```\n\nNow, each test file should import\n`test`\nfrom our fixtures file instead of\n`@playwright/test`\n. No changes are needed in the config.\n\ntests/example.spec.ts\n```\n`// Important: import our fixtures.import{test,expect}from'../playwright/fixtures';test('test',async({page})=&gt;{// page is authenticated});`\n```", 'Run\n`codegen`\nwith\n`--save-storage`\nto save\ncookies (https://developer.mozilla.org/en-US/docs/Web/HTTP/Cookies)\n,\nlocalStorage (https://developer.mozilla.org/en-US/docs/Web/API/Window/localStorage)\nand\nIndexedDB (https://developer.mozilla.org/en-US/docs/Web/API/IndexedDB_API)\ndata at the end of the session. This is useful to separately record an authentication step and reuse it later when recording more tests.\n\n```\n`npx playwright codegen github.com/microsoft/playwright --save-storage=auth.json`\n```', 'By default,\npage.getByTestId() (https://playwright.dev/docs/api/class-page#page-get-by-test-id)\nwill locate elements based on the\n`data-testid`\nattribute, but you can configure it in your test config or by calling\nselectors.setTestIdAttribute() (https://playwright.dev/docs/api/class-selectors#selectors-set-test-id-attribute)\n.\n\nSet the test id to use a custom data attribute for your tests.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{testIdAttribute:\'data-pw\'}});`\n```\n\nIn your html you can now use\n`data-pw`\nas your test id instead of the default\n`data-testid`\n.\n\nhttp://localhost:3000\nItinéraire\n```\n`&lt;buttondata-pw="directions"&gt;Itinéraire&lt;/button&gt;`\n```\n\nAnd then locate the element as you would normally do:\n\n```\n`awaitpage.getByTestId(\'directions\').click();`\n```', 'Playwright comes with the ability to generate tests for you as you perform actions in the browser and is a great way to quickly get started with testing. Playwright will look at your page and figure out the best locator, prioritizing\nrole, text and test id locators (https://playwright.dev/docs/locators)\n. If the generator finds multiple elements matching the locator, it will improve the locator to make it resilient that uniquely identify the target element.']</t>
+          <t>['Run\n`codegen`\nwith\n`--save-storage`\nto save\ncookies (https://developer.mozilla.org/en-US/docs/Web/HTTP/Cookies)\n,\nlocalStorage (https://developer.mozilla.org/en-US/docs/Web/API/Window/localStorage)\nand\nIndexedDB (https://developer.mozilla.org/en-US/docs/Web/API/IndexedDB_API)\ndata at the end of the session. This is useful to separately record an authentication step and reuse it later when recording more tests.\n\n```\n`npx playwright codegen github.com/microsoft/playwright --save-storage=auth.json`\n```', 'Run with\n`--load-storage`\nto consume the previously loaded storage from the\n`auth.json`\n. This way, all\ncookies (https://developer.mozilla.org/en-US/docs/Web/HTTP/Cookies)\n,\nlocalStorage (https://developer.mozilla.org/en-US/docs/Web/API/Window/localStorage)\nand\nIndexedDB (https://developer.mozilla.org/en-US/docs/Web/API/IndexedDB_API)\ndata will be restored, bringing most web apps to the authenticated state without the need to login again. This means you can continue generating tests from the logged in state.\n\n```\n`npx playwright codegen --load-storage=auth.json github.com/microsoft/playwright`\n```', 'Playwright comes with the ability to generate tests for you as you perform actions in the browser and is a great way to quickly get started with testing. Playwright will look at your page and figure out the best locator, prioritizing\nrole, text and test id locators (https://playwright.dev/docs/locators)\n. If the generator finds multiple elements matching the locator, it will improve the locator to make it resilient that uniquely identify the target element.', "Run\n`codegen`\nand perform actions in the browser. Playwright generates code for your interactions automatically. Codegen analyzes the rendered page and recommends the best locator, prioritizing role, text, and test id locators. When multiple elements match a locator, the generator improves it to uniquely identify the target element, reducing test failures and flakiness.\n\nWith the test generator you can record:\n\nActions like click or fill by interacting with the page\nAssertions by clicking a toolbar icon, then clicking a page element to assert against. You can choose:\n`'assert visibility'`\nto assert that an element is visible\n`'assert text'`\nto assert that an element contains specific text\n`'assert value'`\nto assert that an element has a specific value", 'Run\n`codegen`\nwith\n`--user-data-dir`\nto set a fixed\nuser data directory (https://playwright.dev/docs/api/class-browsertype#browser-type-launch-persistent-context-option-user-data-dir)\nfor the browser session. If you create a custom browser user data directory, codegen will use this existing browser profile and have access to any authentication state present in that profile.\n\nwarning\nAs of Chrome 136, the default user data directory cannot be accessed via automated tooling (https://developer.chrome.com/blog/remote-debugging-port)\n, such as Playwright. You must create a separate user data directory for use in testing.\n\n```\n`npx playwright codegen --user-data-dir=/path/to/your/browser/data/ github.com/microsoft/playwright`\n```', 'Regardless of the authentication strategy you choose, you are likely to store authenticated browser state on the file system.\n\nWe recommend to create\n`playwright/.auth`\ndirectory and add it to your\n`.gitignore`\n. Your authentication routine will produce authenticated browser state and save it to a file in this\n`playwright/.auth`\ndirectory. Later on, tests will reuse this state and start already authenticated.\n\ndanger\nThe browser state file may contain sensitive cookies and headers that could be used to impersonate you or your test account. We strongly discourage checking them into private or public repositories.\n\nBash\nPowerShell\nBatch\n```\n`mkdir-pplaywright/.authecho$\'\\nplaywright/.auth\'&gt;&gt;.gitignore`\n```\n```\n`New-Item-ItemType Directory-Force-Path playwright\\.authAdd-Content-path.gitignore"`r`nplaywright/.auth"`\n```\n```\n`mdplaywright\\.authecho. &gt;&gt; .gitignoreecho"playwright/.auth"&gt;&gt; .gitignore`\n```', 'The\npage.getByRole() (https://playwright.dev/docs/api/class-page#page-get-by-role)\nlocator reflects how users and assistive technology perceive the page, for example whether some element is a button or a checkbox. When locating by role, you should usually pass the accessible name as well, so that the locator pinpoints the exact element.\n\nFor example, consider the following DOM structure.\n\nhttp://localhost:3000\nSign up\nSubscribe\nSubmit\n```\n`&lt;h3&gt;Sign up&lt;/h3&gt;&lt;label&gt;&lt;inputtype="checkbox"/&gt;Subscribe&lt;/label&gt;&lt;br/&gt;&lt;button&gt;Submit&lt;/button&gt;`\n```\n\nYou can locate each element by its implicit role:\n\n```\n`awaitexpect(page.getByRole(\'heading\',{name:\'Sign up\'})).toBeVisible();awaitpage.getByRole(\'checkbox\',{name:\'Subscribe\'}).check();awaitpage.getByRole(\'button\',{name:/submit/i}).click();`\n```\n\nRole locators include\nbuttons, checkboxes, headings, links, lists, tables, and many more (https://www.w3.org/TR/html-aria/#docconformance)\nand follow W3C specifications for\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n. Note that many html elements like\n`&lt;button&gt;`\nhave an\nimplicitly defined role (https://w3c.github.io/html-aam/#html-element-role-mappings)\nthat is recognized by the role locator.\n\nNote that role locators\ndo not replace\naccessibility audits and conformance tests, but rather give early feedback about the ARIA guidelines.\n\nWhen to use role locators\nWe recommend prioritizing role locators to locate elements, as it is the closest way to how users and assistive technology perceive the page.']</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2129,13 +2167,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>The provided documentation addresses both of your concerns:
-**1. Handling fragile selectors**
-The test generator is designed to prioritize resilient locators, specifically role, text, and test id locators. If the generator identifies multiple elements matching a locator, it automatically improves the locator to uniquely and resiliently identify the target element. To further ensure stability, you can use `data-testid` attributes (or a custom attribute configured via `testIdAttribute` in your `playwright.config.ts`) to provide stable anchors for your tests.
-**2. Handling the login form**
-You can avoid manually clicking through the login form every time by preserving the authenticated state. There are two ways to handle this with the recorder:
-*   **Save state:** Run `npx playwright codegen --save-storage=auth.json` to record the authentication step once and save the cookies, `localStorage`, and `IndexedDB` data to a file.
-*   **Load state:** Once you have an `auth.json` file, you can use `npx playwright codegen --load-storage=auth.json &lt;url&gt;` to start the recorder already authenticated, allowing you to generate tests from the logged-in state without re-authenticating.</t>
+          <t>Yes, the recorder can be told to handle both of these issues.
+**1. Handling login forms**
+You can avoid manually logging in every time by saving and reusing your authentication state.
+*   **To save the state:** Run `codegen` with the `--save-storage` flag to capture cookies, `localStorage`, and `IndexedDB` data after you perform the login once.
+    *   Example: `npx playwright codegen github.com/microsoft/playwright --save-storage=auth.json`
+*   **To reuse the state:** Run `codegen` with the `--load-storage` flag to restore that session data, allowing you to start recording from an authenticated state.
+    *   Example: `npx playwright codegen --load-storage=auth.json github.com/microsoft/playwright`
+*   **Alternative:** You can use the `--user-data-dir` flag to point to a specific browser profile that already contains your authentication state.
+**2. Handling brittle selectors**
+The recorder is designed to generate resilient locators automatically. It prioritizes `role`, `text`, and `test id` locators, which are more stable than other selection methods. If the generator detects multiple elements matching a locator, it automatically improves the locator to uniquely identify the target element, which helps reduce test failures and flakiness during refactors.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2144,31 +2185,31 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.01060525</v>
+        <v>0.00097825</v>
       </c>
       <c r="G28" t="n">
-        <v>38671</v>
+        <v>42394</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="J28" t="n">
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3125</v>
+        <v>0.2119565217391304</v>
       </c>
       <c r="L28" t="n">
-        <v>0.275</v>
+        <v>0.195</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9999999999</v>
+        <v>0.49999999995</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="29">
@@ -2179,7 +2220,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['Authentication | Playwright', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", 'Global setup and teardown | Playwright', 'Project dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nare a list of projects that need to run before the tests in another project run. They can be useful for configuring the global setup actions so that one project depends on this running first. Using dependencies allows global setup to produce traces and other artifacts.', "When to use\n\nYour web application supports authenticating via API that is easier/faster than interacting with the app UI.\n\nDetails\n\nWe will send the API request with\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nand then save authenticated state as usual.\n\nIn the\nsetup project (https://playwright.dev/docs/auth#basic-shared-account-in-all-tests)\n:\n\ntests/auth.setup.ts\n```\n`import{testassetup}from'@playwright/test';constauthFile='playwright/.auth/user.json';setup('authenticate',async({request})=&gt;{// Send authentication request. Replace with your own.awaitrequest.post('https://github.com/login',{form:{'user':'user','password':'password'}});awaitrequest.storageState({path:authFile});});`\n```\n\nAlternatively, in a\nworker fixture (https://playwright.dev/docs/auth#moderate-one-account-per-parallel-worker)\n:\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,request}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constcontext=awaitrequest.newContext({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Send authentication request. Replace with your own.awaitcontext.post('https://github.com/login',{form:{'user':'user','password':'password'}});awaitcontext.storageState({path:fileName});awaitcontext.dispose();awaituse(fileName);},{scope:'worker'}],});`\n```", "First we add a new project with the name 'setup db'. We then give it a\ntestProject.testMatch (https://playwright.dev/docs/api/class-testproject#test-project-test-match)\nproperty in order to match the file called\n`global.setup.ts`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},// {//   other project// }]});`\n```\n\nThen we add the\ntestProject.dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nproperty to our projects that depend on the setup project and pass into the array the name of our dependency project, which we defined in the previous step:\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},{name:'chromium with db',use:{...devices['Desktop Chrome']},dependencies:['setup db'],},]});`\n```\n\nIn this example the 'chromium with db' project depends on the 'setup db' project. We then create a setup test, stored at root level of your project (note that setup and teardown code must be defined as regular tests by calling\ntest() (https://playwright.dev/docs/api/class-test#test-call)\nfunction):\n\ntests/global.setup.ts\n```\n`import{testassetup}from'@playwright/test';setup('create new database',async({})=&gt;{console.log('creating new database...');// Initialize the database});`\n```\n\ntests/menu.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('menu',async({page})=&gt;{// Your test that depends on the database});`\n```", 'Fixtures | Playwright']</t>
+          <t>["This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", "Here is a global setup example that authenticates once and reuses authentication state in tests. It uses the\n`baseURL`\nand\n`storageState`\noptions from the configuration file.\n\nglobal-setup.ts\n```\n`import{chromium,typeFullConfig}from'@playwright/test';asyncfunctionglobalSetup(config:FullConfig){const{baseURL,storageState}=config.projects[0].use;constbrowser=awaitchromium.launch();constpage=awaitbrowser.newPage();awaitpage.goto(baseURL!);awaitpage.getByLabel('User Name').fill('user');awaitpage.getByLabel('Password').fill('password');awaitpage.getByText('Sign in').click();awaitpage.context().storageState({path:storageStateasstring});awaitbrowser.close();}exportdefaultglobalSetup;`\n```\n\nSpecify\n`globalSetup`\n,\n`baseURL`\nand\n`storageState`\nin the configuration file.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalSetup:require.resolve('./global-setup'),use:{baseURL:'http://localhost:3000/',storageState:'state.json',},});`\n```\n\nTests start already authenticated because we specify\n`storageState`\nthat was populated by global setup.\n\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{awaitpage.goto('/');// You are signed in!});`\n```\n\nYou can make arbitrary data available in your tests from your global setup file by setting them as environment variables via\n`process.env`\n.\n\nglobal-setup.ts\n```\n`importtype{FullConfig}from'@playwright/test';asyncfunctionglobalSetup(config:FullConfig){process.env.FOO='some data';// Or a more complicated data structure as JSON:process.env.BAR=JSON.stringify({some:'data'});}exportdefaultglobalSetup;`\n```\n\nTests have access to the\n`process.env`\nproperties set in the global setup.\n\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// environment variables which are set in globalSetup are only available inside test().const{FOO,BAR}=process.env;// FOO and BAR properties are populated.expect(FOO).toEqual('some data');constcomplexData=JSON.parse(BAR);expect(BAR).toEqual({some:'data'});});`\n```", "Web apps use cookie-based or token-based authentication, where authenticated state is stored as\ncookies (https://developer.mozilla.org/en-US/docs/Web/HTTP/Cookies)\n. Playwright provides\napiRequestContext.storageState() (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state)\nmethod that can be used to retrieve storage state from an authenticated context and then create new contexts with that state.\n\nStorage state is interchangeable between\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nand\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n. You can use it to log in via API calls and then create a new context with cookies already there. The following code snippet retrieves state from an authenticated\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nand creates a new\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nwith that state.\n\n```\n`constrequestContext=awaitrequest.newContext({httpCredentials:{username:'user',password:'passwd'}});awaitrequestContext.get(`https://api.example.com/login`);// Save storage state into the file.awaitrequestContext.storageState({path:'state.json'});// Create a new context with the saved storage state.constcontext=awaitbrowser.newContext({storageState:'state.json'});`\n```", "First we add a new project with the name 'setup db'. We then give it a\ntestProject.testMatch (https://playwright.dev/docs/api/class-testproject#test-project-test-match)\nproperty in order to match the file called\n`global.setup.ts`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},// {//   other project// }]});`\n```\n\nThen we add the\ntestProject.dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nproperty to our projects that depend on the setup project and pass into the array the name of our dependency project, which we defined in the previous step:\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},{name:'chromium with db',use:{...devices['Desktop Chrome']},dependencies:['setup db'],},]});`\n```\n\nIn this example the 'chromium with db' project depends on the 'setup db' project. We then create a setup test, stored at root level of your project (note that setup and teardown code must be defined as regular tests by calling\ntest() (https://playwright.dev/docs/api/class-test#test-call)\nfunction):\n\ntests/global.setup.ts\n```\n`import{testassetup}from'@playwright/test';setup('create new database',async({})=&gt;{console.log('creating new database...');// Initialize the database});`\n```\n\ntests/menu.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('menu',async({page})=&gt;{// Your test that depends on the database});`\n```", 'Regardless of the authentication strategy you choose, you are likely to store authenticated browser state on the file system.\n\nWe recommend to create\n`playwright/.auth`\ndirectory and add it to your\n`.gitignore`\n. Your authentication routine will produce authenticated browser state and save it to a file in this\n`playwright/.auth`\ndirectory. Later on, tests will reuse this state and start already authenticated.\n\ndanger\nThe browser state file may contain sensitive cookies and headers that could be used to impersonate you or your test account. We strongly discourage checking them into private or public repositories.\n\nBash\nPowerShell\nBatch\n```\n`mkdir-pplaywright/.authecho$\'\\nplaywright/.auth\'&gt;&gt;.gitignore`\n```\n```\n`New-Item-ItemType Directory-Force-Path playwright\\.authAdd-Content-path.gitignore"`r`nplaywright/.auth"`\n```\n```\n`mdplaywright\\.authecho. &gt;&gt; .gitignoreecho"playwright/.auth"&gt;&gt; .gitignore`\n```', 'UI mode will not run the\n`setup`\nproject by default to improve testing speed. We recommend to authenticate by manually running the\n`auth.setup.ts`\nfrom time to time, whenever existing authentication expires.\n\nFirst\nenable the setup project in the filters (https://playwright.dev/docs/test-ui-mode#filtering-tests)\n, then click the triangle button next to\n`auth.setup.ts`\nfile, and then disable the\n`setup`\nproject in the filters again.', 'Playwright executes tests in isolated environments called\nbrowser contexts (https://playwright.dev/docs/browser-contexts)\n. This isolation model improves reproducibility and prevents cascading test failures. Tests can load existing authenticated state. This eliminates the need to authenticate in every test and speeds up test execution.']</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2189,9 +2230,9 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>To sign in once up front and share that session across browser projects, use the recommended approach of creating a setup project that saves the authentication state.
-### 1. Create a setup file
-Create a file (e.g., `tests/auth.setup.ts`) to perform the authentication and save the state to a JSON file:
+          <t>The recommended approach to sign in once and share that session across all browser projects is to use a **setup project** as a dependency.
+### 1. Create the Authentication Setup
+Create a file (e.g., `tests/auth.setup.ts`) to perform the login and save the authentication state to a file:
 ```typescript
 import { test as setup, expect } from '@playwright/test';
 import path from 'path';
@@ -2209,8 +2250,8 @@
   await page.context().storageState({ path: authFile });
 });
 ```
-### 2. Configure the projects
-In your `playwright.config.ts`, define the `setup` project and add it as a dependency to your browser projects. Use the `storageState` property in each browser project to load the saved session:
+### 2. Configure the Projects
+In your `playwright.config.ts`, define a `setup` project and declare it as a dependency for your testing projects. Use the `storageState` option in your testing projects to load the saved session:
 ```typescript
 import { defineConfig, devices } from '@playwright/test';
 export default defineConfig({
@@ -2220,7 +2261,7 @@
       name: 'setup', 
       testMatch: /.*\.setup\.ts/ 
     },
-    // Browser projects
+    // Testing projects
     {
       name: 'chromium',
       use: { 
@@ -2241,9 +2282,10 @@
 });
 ```
 ### Important Considerations
-*   **When to use:** This is recommended when all tests can run with the same account without affecting each other.
-*   **When not to use:** Do not use this if your tests modify server-side state (e.g., changing settings) in parallel, or if your authentication is browser-specific.
-*   **Cleanup:** You must delete the stored state when it expires. If you do not need to persist the state between runs, write the file to `testProject.outputDir`, which is automatically cleaned up before every test run.</t>
+*   **Security:** The state file contains sensitive cookies and headers. Add the `playwright/.auth` directory to your `.gitignore` and do not check it into repositories.
+*   **Expiration:** You must manually delete or refresh the stored state when it expires.
+*   **UI Mode:** When using UI mode, the `setup` project does not run by default. You must manually run `auth.setup.ts` via the UI filters when authentication expires.
+*   **Limitations:** Do not use this approach if your tests modify server-side state (e.g., changing settings) in parallel, as tests will interfere with each other. In such cases, use different accounts.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2252,10 +2294,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.01090775</v>
+        <v>0.00168075</v>
       </c>
       <c r="G29" t="n">
-        <v>38761</v>
+        <v>38537</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
@@ -2267,13 +2309,13 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.07419354838709677</v>
+        <v>0.06542056074766354</v>
       </c>
       <c r="L29" t="n">
-        <v>0.575</v>
+        <v>0.525</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9266666666481335</v>
+        <v>0.9761904761742063</v>
       </c>
       <c r="N29" t="n">
         <v>1</v>
@@ -2287,7 +2329,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>["Sharding can be done at two levels of granularity depending on whether you use the\ntestProject.fullyParallel (https://playwright.dev/docs/api/class-testproject#test-project-fully-parallel)\noption or not. This affects how the tests are balanced across the shards.\n\nSharding with fullyParallel\n\nWhen\n`fullyParallel: true`\nis enabled, Playwright Test runs individual tests in parallel across multiple shards, ensuring each shard receives an even distribution of tests. This allows for test-level granularity, meaning each shard will attempt to balance the number of individual tests it runs. This is the preferred mode for ensuring even load distribution when sharding, as Playwright can optimize shard execution based on the total number of tests.\n\nSharding without fullyParallel\n\nWithout the fullyParallel setting, Playwright Test defaults to file-level granularity, meaning entire test files are assigned to shards (note that the same file may be assigned to different shards across different projects). In this case, the number of tests per file can greatly influence shard distribution. If your test files are not evenly sized (i.e., some files contain many more tests than others), certain shards may end up running significantly more tests, while others may run fewer or even none.\n\nKey Takeaways:\n\nWith\n`fullyParallel: true`\n: Tests are split at the individual test level, leading to more balanced shard execution.\nWithout\n`fullyParallel`\n: Tests are split at the file level, so to balance the shards, it's important to keep your test files small and evenly sized.\nTo ensure the most effective use of sharding, especially in CI environments, it is recommended to use\n`fullyParallel: true`\nwhen aiming for balanced distribution across shards. Otherwise, you may need to manually organize your test files to avoid imbalances.", 'Sharding | Playwright', 'Parallelism | Playwright', 'Retries | Playwright', "GitHub Actions supports\nsharding tests between multiple jobs (https://docs.github.com/en/actions/using-jobs/using-a-matrix-for-your-jobs)\nusing the\njobs.&lt;job_id&gt;.strategy.matrix (https://docs.github.com/en/actions/using-workflows/workflow-syntax-for-github-actions#jobsjob_idstrategymatrix)\noption. The\n`matrix`\noption will run a separate job for every possible combination of the provided options.\n\nThe following example shows you how to configure a job to run your tests on four machines in parallel and then merge the reports into a single report. Don't forget to add\n`reporter: process.env.CI ? 'blob' : 'html',`\nto your\n`playwright.config.ts`\nfile as in the example above.\n\nFirst we add a\n`matrix`\noption to our job configuration with the\n`shardTotal: [4]`\noption containing the total number of shards we want to create and\n`shardIndex: [1, 2, 3, 4]`\nwith an array of the shard numbers.\nThen we run our Playwright tests with the\n`--shard=${{ matrix.shardIndex }}/${{ matrix.shardTotal }}`\noption. This will run our test command for each shard.\nFinally we upload our blob report to the GitHub Actions Artifacts. This will make the blob report available to other jobs in the workflow.\n\n.github/workflows/playwright.yml\n```\n`name:Playwright Testson:push:branches:[main,master]pull_request:branches:[main,master]jobs:playwright-tests:timeout-minutes:60runs-on:ubuntu-lateststrategy:fail-fast:falsematrix:shardIndex:[1,2,3,4]shardTotal:[4]steps:-uses:actions/checkout@v5-uses:actions/setup-node@v5with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Install Playwright browsersrun:npx playwright install--with-deps-name:Run Playwright testsrun:npx playwright test--shard=${{matrix.shardIndex}}/${{matrix.shardTotal}}-name:Upload blob report to GitHub Actions Artifactsif:${{!cancelled()}}uses:actions/upload-artifact@v4with:name:blob-report-${{matrix.shardIndex}}path:blob-reportretention-days:1`\n```\n\nAfter all shards have completed, you can run a separate job that will merge the reports and produce a combined\nHTML report (https://playwright.dev/docs/test-reporters#html-reporter)\n. To ensure the execution order, we make the\n`merge-reports`\njob\ndepend (https://docs.github.com/en/actions/using-jobs/using-jobs-in-a-workflow#defining-prerequisite-jobs)\non our sharded\n`playwright-tests`\njob by adding\n`needs: [playwright-tests]`\n.\n\n.github/workflows/playwright.yml\n```\n`jobs:...merge-reports:# Merge reports after playwright-tests, even if some shards have failedif:${{!cancelled()}}needs:[playwright-tests]runs-on:ubuntu-lateststeps:-uses:actions/checkout@v5-uses:actions/setup-node@v5with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Download blob reports from GitHub Actions Artifactsuses:actions/download-artifact@v5with:path:all-blob-reportspattern:blob-report-*merge-multiple:true-name:Merge into HTML Reportrun:npx playwright merge-reports--reporter html ./all-blob-reports-name:Upload HTML reportuses:actions/upload-artifact@v4with:name:html-report--attempt-${{github.run_attempt}}path:playwright-reportretention-days:14`\n```\n\nYou can now see the reports have been merged and a combined HTML report is available in the GitHub Actions Artifacts tab.", 'Configuration | Playwright', 'Continuous Integration | Playwright']</t>
+          <t>["Sharding can be done at two levels of granularity depending on whether you use the\ntestProject.fullyParallel (https://playwright.dev/docs/api/class-testproject#test-project-fully-parallel)\noption or not. This affects how the tests are balanced across the shards.\n\nSharding with fullyParallel\n\nWhen\n`fullyParallel: true`\nis enabled, Playwright Test runs individual tests in parallel across multiple shards, ensuring each shard receives an even distribution of tests. This allows for test-level granularity, meaning each shard will attempt to balance the number of individual tests it runs. This is the preferred mode for ensuring even load distribution when sharding, as Playwright can optimize shard execution based on the total number of tests.\n\nSharding without fullyParallel\n\nWithout the fullyParallel setting, Playwright Test defaults to file-level granularity, meaning entire test files are assigned to shards (note that the same file may be assigned to different shards across different projects). In this case, the number of tests per file can greatly influence shard distribution. If your test files are not evenly sized (i.e., some files contain many more tests than others), certain shards may end up running significantly more tests, while others may run fewer or even none.\n\nKey Takeaways:\n\nWith\n`fullyParallel: true`\n: Tests are split at the individual test level, leading to more balanced shard execution.\nWithout\n`fullyParallel`\n: Tests are split at the file level, so to balance the shards, it's important to keep your test files small and evenly sized.\nTo ensure the most effective use of sharding, especially in CI environments, it is recommended to use\n`fullyParallel: true`\nwhen aiming for balanced distribution across shards. Otherwise, you may need to manually organize your test files to avoid imbalances.", 'Playwright supports\ntest retries\n. When enabled, failing tests will be retried multiple times until they pass, or until the maximum number of retries is reached. By default failing tests are not retried.\n\n```\n`# Give failing tests 3 retry attemptsnpx playwrighttest--retries=3`\n```\n\nYou can configure retries in the configuration file:\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({// Give failing tests 3 retry attemptsretries:3,});`\n```\n\nPlaywright Test will categorize tests as follows:\n\n"passed" - tests that passed on the first run;\n"flaky" - tests that failed on the first run, but passed when retried;\n"failed" - tests that failed on the first run and failed all retries.\n\n```\n`Running3tests using1worker✓ example.spec.ts:4:2 › first passes(438ms)x example.spec.ts:5:2 › second flaky(691ms)✓ example.spec.ts:5:2 › second flaky(522ms)✓ example.spec.ts:6:2 › third passes(932ms)1flakyexample.spec.ts:5:2 › second flaky2passed(4s)`\n```\n\nYou can detect retries at runtime with\ntestInfo.retry (https://playwright.dev/docs/api/class-testinfo#test-info-retry)\n, which is accessible to any test, hook or fixture. Here is an example that clears some server-side state before a retry.\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'my test\',async({page},testInfo)=&gt;{if(testInfo.retry)awaitcleanSomeCachesOnTheServer();// ...});`\n```\n\nYou can specify retries for a specific group of tests or a single file with\ntest.describe.configure() (https://playwright.dev/docs/api/class-test#test-describe-configure)\n.\n\n```\n`import{test,expect}from\'@playwright/test\';test.describe(()=&gt;{// All tests in this describe group will get 2 retry attempts.test.describe.configure({retries:2});test(\'test 1\',async({page})=&gt;{// ...});test(\'test 2\',async({page})=&gt;{// ...});});`\n```', 'Playwright Test runs tests in parallel. In order to achieve that, it runs several worker processes that run at the same time. By default,\ntest files\nare run in parallel. Tests in a single file are run in order, in the same worker process.\n\nYou can configure tests using\ntest.describe.configure (https://playwright.dev/docs/test-parallel#parallelize-tests-in-a-single-file)\nto run\ntests in a single file\nin parallel.\nYou can configure\nentire project\nto have all tests in all files to run in parallel using\ntestProject.fullyParallel (https://playwright.dev/docs/api/class-testproject#test-project-fully-parallel)\nor\ntestConfig.fullyParallel (https://playwright.dev/docs/api/class-testconfig#test-config-fully-parallel)\n.\nTo\ndisable\nparallelism limit the number of\nworkers to one (https://playwright.dev/docs/test-parallel#disable-parallelism)\n.\n\nYou can control the number of\nparallel worker processes (https://playwright.dev/docs/test-parallel#limit-workers)\nand\nlimit the number of failures (https://playwright.dev/docs/test-parallel#limit-failures-and-fail-fast)\nin the whole test suite for efficiency.', 'We recommend setting\nworkers (https://playwright.dev/docs/api/class-testconfig#test-config-workers)\nto "1" in CI environments to prioritize stability and reproducibility. Running tests sequentially ensures each test gets the full system resources, avoiding potential conflicts. However, if you have a powerful self-hosted CI system, you may enable\nparallel (https://playwright.dev/docs/test-parallel)\ntests. For wider parallelization, consider\nsharding (https://playwright.dev/docs/test-parallel#shard-tests-between-multiple-machines)\n- distributing tests across multiple CI jobs.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from\'@playwright/test\';exportdefaultdefineConfig({// Opt out of parallel tests on CI.workers:process.env.CI?1:undefined,});`\n```', "All tests run in worker processes. These processes are OS processes, running independently, orchestrated by the test runner. All workers have identical environments and each starts its own browser.\n\nYou can't communicate between the workers. Playwright Test reuses a single worker as much as it can to make testing faster, so multiple test files are usually run in a single worker one after another.\n\nWorkers are always shutdown after a\ntest failure (https://playwright.dev/docs/test-retries#failures)\nto guarantee pristine environment for following tests.", 'To shard the test suite, pass\n`--shard=x/y`\nto the command line. For example, to split the suite into four shards, each running one fourth of the tests:\n\n```\n`npx playwrighttest--shard=1/4npx playwrighttest--shard=2/4npx playwrighttest--shard=3/4npx playwrighttest--shard=4/4`\n```\n\nNow, if you run these shards in parallel on different jobs, your test suite completes four times faster.\n\nNote that Playwright can only shard tests that can be run in parallel. By default, this means Playwright will shard test files. Learn about other options in the\nparallelism guide (https://playwright.dev/docs/test-parallel)\n.', "Playwright Test runs tests in worker processes. These processes are OS processes, running independently, orchestrated by the test runner. All workers have identical environments and each starts its own browser.\n\nConsider the following snippet:\n\n```\n`import{test}from'@playwright/test';test.describe('suite',()=&gt;{test.beforeAll(async()=&gt;{/* ... */});test('first good',async({page})=&gt;{/* ... */});test('second flaky',async({page})=&gt;{/* ... */});test('third good',async({page})=&gt;{/* ... */});test.afterAll(async()=&gt;{/* ... */});});`\n```\n\nWhen\nall tests pass\n, they will run in order in the same worker process.\n\nWorker process starts\n`beforeAll`\nhook runs\n`first good`\npasses\n`second flaky`\npasses\n`third good`\npasses\n`afterAll`\nhook runs\n\nShould\nany test fail\n, Playwright Test will discard the entire worker process along with the browser and will start a new one. Testing will continue in the new worker process starting with the next test.\n\nWorker process #1 starts\n`beforeAll`\nhook runs\n`first good`\npasses\n`second flaky`\nfails\n`afterAll`\nhook runs\nWorker process #2 starts\n`beforeAll`\nhook runs again\n`third good`\npasses\n`afterAll`\nhook runs\n\nIf you\nenable\nretries (https://playwright.dev/docs/test-retries#retries)\n, second worker process will start by retrying the failed test and continue from there.\n\nWorker process #1 starts\n`beforeAll`\nhook runs\n`first good`\npasses\n`second flaky`\nfails\n`afterAll`\nhook runs\nWorker process #2 starts\n`beforeAll`\nhook runs again\n`second flaky`\nis retried and passes\n`third good`\npasses\n`afterAll`\nhook runs\n\nThis scheme works perfectly for independent tests and guarantees that failing tests can't affect healthy ones."]</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2297,11 +2339,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>The provided documentation does not contain information regarding how retries interact with sharding and the `fullyParallel` setting to maintain balance and reliability.
-Regarding the interaction between `fullyParallel` and sharding, the documentation states:
-*   **`fullyParallel: true` (Recommended):** Playwright splits tests at the individual test level, allowing it to optimize execution and ensure an even distribution of tests across shards.
-*   **Without `fullyParallel`:** Playwright defaults to file-level granularity. Shards are assigned entire test files, which can lead to imbalances if files are not evenly sized. In this case, you must manually organize test files to ensure balanced distribution.
-The documentation does not provide information on how workers interact with these settings during sharding.</t>
+          <t>To balance and ensure reliability when sharding across CI jobs, these features interact as follows:
+### Balancing Shards (`fullyParallel`)
+*   **`fullyParallel: true` (Recommended):** Playwright distributes individual tests across shards, ensuring an even load. This is the preferred mode for balanced distribution.
+*   **`fullyParallel: false` (Default):** Playwright distributes tests at the file level. If test files are not evenly sized, shards may become unbalanced, with some running significantly more tests than others. To balance shards in this mode, you must manually organize your test files to be small and evenly sized.
+### Reliability and Retries
+*   **Worker Management:** Playwright runs tests in independent worker processes. If a test fails, the worker process is shut down to ensure a pristine environment for subsequent tests.
+*   **Retry Interaction:** When retries are enabled, if a test fails, the runner starts a new worker process. This new worker begins by retrying the failed test before continuing with the remaining tests in the suite. This ensures that failing tests do not affect the health of subsequent tests.
+*   **Detection:** You can detect if a test is currently being retried using `testInfo.retry`, which allows you to perform cleanup tasks (like clearing server-side state) specifically for retries.
+### CI Considerations
+*   **Workers:** While Playwright supports parallel workers, it is recommended to set `workers` to "1" in CI environments to prioritize stability and reproducibility. 
+*   **Sharding:** For wider parallelization in CI, you should use sharding (`--shard=x/y`) to distribute tests across multiple CI jobs rather than relying on high worker counts within a single job. Sharding works by splitting the test suite into parts; Playwright can only shard tests that are capable of running in parallel.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2310,31 +2358,31 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.00918825</v>
+        <v>0.00127325</v>
       </c>
       <c r="G30" t="n">
-        <v>34098</v>
+        <v>35053</v>
       </c>
       <c r="H30" t="n">
         <v>0.5</v>
       </c>
       <c r="I30" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1090909090909091</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2345,7 +2393,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>['Global setup and teardown | Playwright', 'There are two ways to configure global setup and teardown: using a global setup file and setting it in the config under\nglobalSetup (https://playwright.dev/docs/test-global-setup-teardown#option-2-configure-globalsetup-and-globalteardown)\nor using\nproject dependencies (https://playwright.dev/docs/test-global-setup-teardown#option-1-project-dependencies)\n. With project dependencies, you define a project that runs before all other projects. This is the recommended approach, as it integrates better with the Playwright test runner: your HTML report will include the global setup, traces will be recorded, and fixtures can be used. For a detailed comparison of the two approaches, see the table below.\n\nFeature\nProject Dependencies (recommended)\n`globalSetup`\n(config option)\nRuns before all tests\n✅ Yes\n✅ Yes\nHTML report visibility\n✅ Shown as a separate project\n❌ Not shown\nTrace recording\n✅ Full trace available\n❌ Not supported\nPlaywright fixtures\n✅ Fully supported\n❌ Not supported\nBrowser management\n✅ Via\n`browser`\nfixture\n❌ Fully manual via\n`browserType.launch()`\nParallelism and retries\n✅ Supported via standard config\n❌ Not applicable\nConfig options like\n`headless`\nor\n`testIdAttribute`\n✅ Automatically applied\n❌ Ignored', 'Project dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nare a list of projects that need to run before the tests in another project run. They can be useful for configuring the global setup actions so that one project depends on this running first. Using dependencies allows global setup to produce traces and other artifacts.', "You can use the\n`globalSetup`\noption in the\nconfiguration file (https://playwright.dev/docs/test-configuration#advanced-configuration)\nto set something up once before running all tests. The global setup file must export a single function that takes a config object. This function will be run once before all the tests.\n\nSimilarly, use\n`globalTeardown`\nto run something once after all the tests. Alternatively, let\n`globalSetup`\nreturn a function that will be used as a global teardown. You can pass data such as port number, authentication tokens, etc. from your global setup to your tests using environment variables.\n\nnote\nBeware that\n`globalSetup`\nand\n`globalTeardown`\nlack some features — see the\nintro (https://playwright.dev/docs/test-global-setup-teardown#introduction)\nsection for a detailed comparison. Consider using\nproject dependencies (https://playwright.dev/docs/test-global-setup-teardown#option-1-project-dependencies)\ninstead to get full feature support.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalSetup:require.resolve('./global-setup'),globalTeardown:require.resolve('./global-teardown'),});`\n```", "First we add a new project with the name 'setup db'. We then give it a\ntestProject.testMatch (https://playwright.dev/docs/api/class-testproject#test-project-test-match)\nproperty in order to match the file called\n`global.setup.ts`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},// {//   other project// }]});`\n```\n\nThen we add the\ntestProject.dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nproperty to our projects that depend on the setup project and pass into the array the name of our dependency project, which we defined in the previous step:\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},{name:'chromium with db',use:{...devices['Desktop Chrome']},dependencies:['setup db'],},]});`\n```\n\nIn this example the 'chromium with db' project depends on the 'setup db' project. We then create a setup test, stored at root level of your project (note that setup and teardown code must be defined as regular tests by calling\ntest() (https://playwright.dev/docs/api/class-test#test-call)\nfunction):\n\ntests/global.setup.ts\n```\n`import{testassetup}from'@playwright/test';setup('create new database',async({})=&gt;{console.log('creating new database...');// Initialize the database});`\n```\n\ntests/menu.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('menu',async({page})=&gt;{// Your test that depends on the database});`\n```", "Here is a global setup example that authenticates once and reuses authentication state in tests. It uses the\n`baseURL`\nand\n`storageState`\noptions from the configuration file.\n\nglobal-setup.ts\n```\n`import{chromium,typeFullConfig}from'@playwright/test';asyncfunctionglobalSetup(config:FullConfig){const{baseURL,storageState}=config.projects[0].use;constbrowser=awaitchromium.launch();constpage=awaitbrowser.newPage();awaitpage.goto(baseURL!);awaitpage.getByLabel('User Name').fill('user');awaitpage.getByLabel('Password').fill('password');awaitpage.getByText('Sign in').click();awaitpage.context().storageState({path:storageStateasstring});awaitbrowser.close();}exportdefaultglobalSetup;`\n```\n\nSpecify\n`globalSetup`\n,\n`baseURL`\nand\n`storageState`\nin the configuration file.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalSetup:require.resolve('./global-setup'),use:{baseURL:'http://localhost:3000/',storageState:'state.json',},});`\n```\n\nTests start already authenticated because we specify\n`storageState`\nthat was populated by global setup.\n\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{awaitpage.goto('/');// You are signed in!});`\n```\n\nYou can make arbitrary data available in your tests from your global setup file by setting them as environment variables via\n`process.env`\n.\n\nglobal-setup.ts\n```\n`importtype{FullConfig}from'@playwright/test';asyncfunctionglobalSetup(config:FullConfig){process.env.FOO='some data';// Or a more complicated data structure as JSON:process.env.BAR=JSON.stringify({some:'data'});}exportdefaultglobalSetup;`\n```\n\nTests have access to the\n`process.env`\nproperties set in the global setup.\n\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// environment variables which are set in globalSetup are only available inside test().const{FOO,BAR}=process.env;// FOO and BAR properties are populated.expect(FOO).toEqual('some data');constcomplexData=JSON.parse(BAR);expect(BAR).toEqual({some:'data'});});`\n```"]</t>
+          <t>['There are two ways to configure global setup and teardown: using a global setup file and setting it in the config under\nglobalSetup (https://playwright.dev/docs/test-global-setup-teardown#option-2-configure-globalsetup-and-globalteardown)\nor using\nproject dependencies (https://playwright.dev/docs/test-global-setup-teardown#option-1-project-dependencies)\n. With project dependencies, you define a project that runs before all other projects. This is the recommended approach, as it integrates better with the Playwright test runner: your HTML report will include the global setup, traces will be recorded, and fixtures can be used. For a detailed comparison of the two approaches, see the table below.\n\nFeature\nProject Dependencies (recommended)\n`globalSetup`\n(config option)\nRuns before all tests\n✅ Yes\n✅ Yes\nHTML report visibility\n✅ Shown as a separate project\n❌ Not shown\nTrace recording\n✅ Full trace available\n❌ Not supported\nPlaywright fixtures\n✅ Fully supported\n❌ Not supported\nBrowser management\n✅ Via\n`browser`\nfixture\n❌ Fully manual via\n`browserType.launch()`\nParallelism and retries\n✅ Supported via standard config\n❌ Not applicable\nConfig options like\n`headless`\nor\n`testIdAttribute`\n✅ Automatically applied\n❌ Ignored', 'Project dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nare a list of projects that need to run before the tests in another project run. They can be useful for configuring the global setup actions so that one project depends on this running first. Using dependencies allows global setup to produce traces and other artifacts.', "You can use the\n`globalSetup`\noption in the\nconfiguration file (https://playwright.dev/docs/test-configuration#advanced-configuration)\nto set something up once before running all tests. The global setup file must export a single function that takes a config object. This function will be run once before all the tests.\n\nSimilarly, use\n`globalTeardown`\nto run something once after all the tests. Alternatively, let\n`globalSetup`\nreturn a function that will be used as a global teardown. You can pass data such as port number, authentication tokens, etc. from your global setup to your tests using environment variables.\n\nnote\nBeware that\n`globalSetup`\nand\n`globalTeardown`\nlack some features — see the\nintro (https://playwright.dev/docs/test-global-setup-teardown#introduction)\nsection for a detailed comparison. Consider using\nproject dependencies (https://playwright.dev/docs/test-global-setup-teardown#option-1-project-dependencies)\ninstead to get full feature support.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalSetup:require.resolve('./global-setup'),globalTeardown:require.resolve('./global-teardown'),});`\n```", "First we add a new project with the name 'setup db'. We then give it a\ntestProject.testMatch (https://playwright.dev/docs/api/class-testproject#test-project-test-match)\nproperty in order to match the file called\n`global.setup.ts`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},// {//   other project// }]});`\n```\n\nThen we add the\ntestProject.dependencies (https://playwright.dev/docs/api/class-testproject#test-project-dependencies)\nproperty to our projects that depend on the setup project and pass into the array the name of our dependency project, which we defined in the previous step:\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({testDir:'./tests',// ...projects:[{name:'setup db',testMatch:/global\\.setup\\.ts/,},{name:'chromium with db',use:{...devices['Desktop Chrome']},dependencies:['setup db'],},]});`\n```\n\nIn this example the 'chromium with db' project depends on the 'setup db' project. We then create a setup test, stored at root level of your project (note that setup and teardown code must be defined as regular tests by calling\ntest() (https://playwright.dev/docs/api/class-test#test-call)\nfunction):\n\ntests/global.setup.ts\n```\n`import{testassetup}from'@playwright/test';setup('create new database',async({})=&gt;{console.log('creating new database...');// Initialize the database});`\n```\n\ntests/menu.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('menu',async({page})=&gt;{// Your test that depends on the database});`\n```", "Dependencies are a list of projects that need to run before the tests in another project run. They can be useful for configuring the global setup actions so that one project depends on this running first. When using project dependencies,\ntest reporters (https://playwright.dev/docs/test-reporters)\nwill show the setup tests and the\ntrace viewer (https://playwright.dev/docs/trace-viewer)\nwill record traces of the setup. You can use the inspector to inspect the DOM snapshot of the trace of your setup tests and you can also use\nfixtures (https://playwright.dev/docs/test-fixtures)\ninside your setup.\n\nIn this example the chromium, firefox and webkit projects depend on the setup project.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[{name:'setup',testMatch:'**/*.setup.ts',},{name:'chromium',use:{...devices['Desktop Chrome']},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox']},dependencies:['setup'],},{name:'webkit',use:{...devices['Desktop Safari']},dependencies:['setup'],},],});`\n```", "Here is a global setup example that authenticates once and reuses authentication state in tests. It uses the\n`baseURL`\nand\n`storageState`\noptions from the configuration file.\n\nglobal-setup.ts\n```\n`import{chromium,typeFullConfig}from'@playwright/test';asyncfunctionglobalSetup(config:FullConfig){const{baseURL,storageState}=config.projects[0].use;constbrowser=awaitchromium.launch();constpage=awaitbrowser.newPage();awaitpage.goto(baseURL!);awaitpage.getByLabel('User Name').fill('user');awaitpage.getByLabel('Password').fill('password');awaitpage.getByText('Sign in').click();awaitpage.context().storageState({path:storageStateasstring});awaitbrowser.close();}exportdefaultglobalSetup;`\n```\n\nSpecify\n`globalSetup`\n,\n`baseURL`\nand\n`storageState`\nin the configuration file.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalSetup:require.resolve('./global-setup'),use:{baseURL:'http://localhost:3000/',storageState:'state.json',},});`\n```\n\nTests start already authenticated because we specify\n`storageState`\nthat was populated by global setup.\n\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{awaitpage.goto('/');// You are signed in!});`\n```\n\nYou can make arbitrary data available in your tests from your global setup file by setting them as environment variables via\n`process.env`\n.\n\nglobal-setup.ts\n```\n`importtype{FullConfig}from'@playwright/test';asyncfunctionglobalSetup(config:FullConfig){process.env.FOO='some data';// Or a more complicated data structure as JSON:process.env.BAR=JSON.stringify({some:'data'});}exportdefaultglobalSetup;`\n```\n\nTests have access to the\n`process.env`\nproperties set in the global setup.\n\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// environment variables which are set in globalSetup are only available inside test().const{FOO,BAR}=process.env;// FOO and BAR properties are populated.expect(FOO).toEqual('some data');constcomplexData=JSON.parse(BAR);expect(BAR).toEqual({some:'data'});});`\n```", "When working with tests that have a dependency, the dependency will always run first and once all tests from this project have passed, then the other projects will run in parallel.\n\nRunning order:\n\nTests in the 'setup' project run. Once all tests from this project have passed, then the tests from the dependent projects will start running.\nTests in the 'chromium', 'webkit' and 'firefox' projects run together. By default, these projects will\nrun in parallel (https://playwright.dev/docs/test-parallel)\n, subject to the maximum workers limit.\n\nIf there are more than one dependency then these project dependencies will be run first and in parallel. If the tests from a dependency fails then the tests that rely on this project will not be run.\n\nRunning order:\n\nTests in the 'Browser Login' and 'DataBase' projects run in parallel:\n'Browser Login' passes\n❌ 'DataBase' fails!\nThe 'e2e tests' project is not run!"]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2355,15 +2403,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>You should use **project dependencies**, as this is the recommended approach.
-Project dependencies are preferred because they integrate better with the Playwright test runner, providing the following advantages over the `globalSetup` config option:
-*   **HTML Report:** The setup is shown as a separate project in the HTML report.
-*   **Trace Recording:** Full trace recording is available.
-*   **Fixtures:** Playwright fixtures are fully supported.
-*   **Browser Management:** You can use the `browser` fixture instead of manual management via `browserType.launch()`.
+          <t>You should use **project dependencies**, as this is the recommended approach. It integrates better with the Playwright test runner and provides full feature support that the `globalSetup` config option lacks.
+### Why use Project Dependencies?
+Project dependencies are recommended because they offer the following advantages over the `globalSetup` config option:
+*   **HTML Report:** Setup is shown as a separate project in the HTML report.
+*   **Trace Recording:** Full traces are available for setup actions.
+*   **Fixtures:** Playwright fixtures are fully supported within setup.
+*   **Browser Management:** You can use the `browser` fixture instead of manual browser launching via `browserType.launch()`.
+*   **Configuration:** Config options like `headless` or `testIdAttribute` are automatically applied.
 *   **Parallelism and Retries:** Supported via standard configuration.
-*   **Config Options:** Options like `headless` or `testIdAttribute` are automatically applied.
-In contrast, the `globalSetup` config option does not support trace recording or fixtures, is not shown in the HTML report, requires manual browser management, and ignores standard config options.</t>
+### When to use `globalSetup`
+The `globalSetup` config option is an alternative approach, but it lacks the features listed above. It requires manual browser management, does not support fixtures, does not record traces, and is not shown in the HTML report. It is primarily used to run a single function once before all tests, and data can be passed to tests using environment variables via `process.env`.
+### Summary Comparison
+| Feature | Project Dependencies (Recommended) | `globalSetup` (Config Option) |
+| :--- | :--- | :--- |
+| HTML report visibility | ✅ Shown as a separate project | ❌ Not shown |
+| Trace recording | ✅ Full trace available | ❌ Not supported |
+| Playwright fixtures | ✅ Fully supported | ❌ Not supported |
+| Browser management | ✅ Via `browser` fixture | ❌ Fully manual |
+| Config options | ✅ Automatically applied | ❌ Ignored |
+| Parallelism/Retries | ✅ Supported | ❌ Not applicable |</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2372,28 +2431,28 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.00837325</v>
+        <v>0.0013005</v>
       </c>
       <c r="G31" t="n">
-        <v>31713</v>
+        <v>37844</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0.35</v>
+        <v>0.72</v>
       </c>
       <c r="J31" t="n">
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.140495867768595</v>
+        <v>0.08370044052863436</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4047619047619048</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6388888888675925</v>
+        <v>0.94999999997625</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
@@ -2407,7 +2466,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['Service Workers | Playwright', 'Any network request made by the\nService Worker\nis reported through the\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nobject:\n\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\n,\nbrowserContext.on(\'requestfinished\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request-finished)\n,\nbrowserContext.on(\'response\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-response)\nand\nbrowserContext.on(\'requestfailed\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request-failed)\nare fired\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nsees the request\nrequest.serviceWorker() (https://playwright.dev/docs/api/class-request#request-service-worker)\nwill be set to the Service\nWorker (https://playwright.dev/docs/api/class-worker)\ninstance, and\nrequest.frame() (https://playwright.dev/docs/api/class-request#request-frame)\nwill\nthrow\n\nAdditionally, for any network request made by the\nPage\n, method\nresponse.fromServiceWorker() (https://playwright.dev/docs/api/class-response#response-from-service-worker)\nreturn\n`true`\nwhen the request was handled a Service Worker\'s fetch handler.\n\nConsider a simple service worker that fetches every request made by the page:\n\ntransparent-service-worker.js\n```\n`self.addEventListener(\'fetch\',event=&gt;{// actually make the requestconstresponsePromise=fetch(event.request);// send it back to the pageevent.respondWith(responsePromise);});self.addEventListener(\'activate\',event=&gt;{event.waitUntil(clients.claim());});`\n```\n\nIf\n`index.html`\nregisters this service worker, and then fetches\n`data.json`\n, the following Request/Response events would be emitted (along with the corresponding network lifecycle events):\n\nEvent\nOwner\nURL\nRouted\nresponse.fromServiceWorker() (https://playwright.dev/docs/api/class-response#response-from-service-worker)\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nFrame (https://playwright.dev/docs/api/class-frame)\nindex.html\nYes\npage.on(\'request\') (https://playwright.dev/docs/api/class-page#page-event-request)\nFrame (https://playwright.dev/docs/api/class-frame)\nindex.html\nYes\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nService\nWorker (https://playwright.dev/docs/api/class-worker)\ntransparent-service-worker.js\nYes\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nService\nWorker (https://playwright.dev/docs/api/class-worker)\ndata.json\nYes\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nFrame (https://playwright.dev/docs/api/class-frame)\ndata.json\nYes\npage.on(\'request\') (https://playwright.dev/docs/api/class-page#page-event-request)\nFrame (https://playwright.dev/docs/api/class-frame)\ndata.json\nYes\n\nSince the example Service Worker just acts a basic transparent "proxy":\n\nThere\'s 2\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nevents for\n`data.json`\n; one\nFrame (https://playwright.dev/docs/api/class-frame)\n-owned, the other Service\nWorker (https://playwright.dev/docs/api/class-worker)\n-owned.\nOnly the Service\nWorker (https://playwright.dev/docs/api/class-worker)\n-owned request for the resource was routable via\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n; the\nFrame (https://playwright.dev/docs/api/class-frame)\n-owned events for\n`data.json`\nare not routeable, as they would not have even had the possibility to hit the external network since the Service Worker has a fetch handler registered.\n\ncaution\nIt\'s important to note: calling\nrequest.frame() (https://playwright.dev/docs/api/class-request#request-frame)\nor\nresponse.frame() (https://playwright.dev/docs/api/class-response#response-frame)\nwill\nthrow\nan exception, if called on a\nRequest (https://playwright.dev/docs/api/class-request)\n/\nResponse (https://playwright.dev/docs/api/class-response)\nthat has a non-null\nrequest.serviceWorker() (https://playwright.dev/docs/api/class-request#request-service-worker)\n.', "Playwright's built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nallow your tests to natively route requests and perform mocking and interception.\n\nIf you're using Playwright's native\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n, and it appears network events are missing, disable Service Workers by setting\nserviceWorkers (https://playwright.dev/docs/api/class-browser#browser-new-context-option-service-workers)\nto\n`'block'`\n.\n\nIt might be that you are using a mock tool such as Mock Service Worker (MSW). While this tool works out of the box for mocking responses, it adds its own Service Worker that takes over the network requests, hence making them invisible to\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n. If you are interested in both network testing and mocking, consider using built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nfor\nresponse mocking (https://playwright.dev/docs/network#handle-requests)\n.", 'Network | Playwright', "```\n`awaitcontext.route('**',asyncroute=&gt;{if(route.request().serviceWorker()){// NB: calling route.request().frame() here would THROWawaitroute.fulfill({contentType:'text/plain',status:200,body:'from sw',});}else{awaitroute.continue();}});`\n```", "Playwright allows to disable Service Workers during testing. This makes tests more predictable and performant. However, if your actual page uses a Service Worker, the behavior might be different.\n\nTo disable service workers, set\ntestOptions.serviceWorkers (https://playwright.dev/docs/api/class-testoptions#test-options-service-workers)\nto\n`'block'`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{serviceWorkers:'allow'},});`\n```", "You can use\nbrowserContext.serviceWorkers() (https://playwright.dev/docs/api/class-browsercontext#browser-context-service-workers)\nto list the Service\nWorker (https://playwright.dev/docs/api/class-worker)\ns, or specifically watch for the Service\nWorker (https://playwright.dev/docs/api/class-worker)\nif you anticipate a page will trigger its\nregistration (https://developer.mozilla.org/en-US/docs/Web/API/ServiceWorkerContainer/register)\n:\n\n```\n`constserviceWorkerPromise=context.waitForEvent('serviceworker');awaitpage.goto('/example-with-a-service-worker.html');constserviceworker=awaitserviceWorkerPromise;`\n```\n\nbrowserContext.on('serviceworker') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-service-worker)\nevent is fired\nbefore\nthe Service Worker has taken control over the page, so\nbefore\nevaluating in the worker with\nworker.evaluate() (https://playwright.dev/docs/api/class-worker#worker-evaluate)\nyou should wait on its activation.\n\nThere are more idiomatic methods of waiting for a Service Worker to be activated, but the following is an implementation agnostic method:\n\n```\n`awaitpage.evaluate(async()=&gt;{constregistration=awaitwindow.navigator.serviceWorker.getRegistration();if(registration.active?.state==='activated')return;awaitnewPromise(resolve=&gt;{window.navigator.serviceWorker.addEventListener('controllerchange',resolve);});});`\n```"]</t>
+          <t>['Any network request made by the\nService Worker\nis reported through the\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nobject:\n\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\n,\nbrowserContext.on(\'requestfinished\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request-finished)\n,\nbrowserContext.on(\'response\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-response)\nand\nbrowserContext.on(\'requestfailed\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request-failed)\nare fired\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nsees the request\nrequest.serviceWorker() (https://playwright.dev/docs/api/class-request#request-service-worker)\nwill be set to the Service\nWorker (https://playwright.dev/docs/api/class-worker)\ninstance, and\nrequest.frame() (https://playwright.dev/docs/api/class-request#request-frame)\nwill\nthrow\n\nAdditionally, for any network request made by the\nPage\n, method\nresponse.fromServiceWorker() (https://playwright.dev/docs/api/class-response#response-from-service-worker)\nreturn\n`true`\nwhen the request was handled a Service Worker\'s fetch handler.\n\nConsider a simple service worker that fetches every request made by the page:\n\ntransparent-service-worker.js\n```\n`self.addEventListener(\'fetch\',event=&gt;{// actually make the requestconstresponsePromise=fetch(event.request);// send it back to the pageevent.respondWith(responsePromise);});self.addEventListener(\'activate\',event=&gt;{event.waitUntil(clients.claim());});`\n```\n\nIf\n`index.html`\nregisters this service worker, and then fetches\n`data.json`\n, the following Request/Response events would be emitted (along with the corresponding network lifecycle events):\n\nEvent\nOwner\nURL\nRouted\nresponse.fromServiceWorker() (https://playwright.dev/docs/api/class-response#response-from-service-worker)\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nFrame (https://playwright.dev/docs/api/class-frame)\nindex.html\nYes\npage.on(\'request\') (https://playwright.dev/docs/api/class-page#page-event-request)\nFrame (https://playwright.dev/docs/api/class-frame)\nindex.html\nYes\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nService\nWorker (https://playwright.dev/docs/api/class-worker)\ntransparent-service-worker.js\nYes\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nService\nWorker (https://playwright.dev/docs/api/class-worker)\ndata.json\nYes\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nFrame (https://playwright.dev/docs/api/class-frame)\ndata.json\nYes\npage.on(\'request\') (https://playwright.dev/docs/api/class-page#page-event-request)\nFrame (https://playwright.dev/docs/api/class-frame)\ndata.json\nYes\n\nSince the example Service Worker just acts a basic transparent "proxy":\n\nThere\'s 2\nbrowserContext.on(\'request\') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-request)\nevents for\n`data.json`\n; one\nFrame (https://playwright.dev/docs/api/class-frame)\n-owned, the other Service\nWorker (https://playwright.dev/docs/api/class-worker)\n-owned.\nOnly the Service\nWorker (https://playwright.dev/docs/api/class-worker)\n-owned request for the resource was routable via\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n; the\nFrame (https://playwright.dev/docs/api/class-frame)\n-owned events for\n`data.json`\nare not routeable, as they would not have even had the possibility to hit the external network since the Service Worker has a fetch handler registered.\n\ncaution\nIt\'s important to note: calling\nrequest.frame() (https://playwright.dev/docs/api/class-request#request-frame)\nor\nresponse.frame() (https://playwright.dev/docs/api/class-response#response-frame)\nwill\nthrow\nan exception, if called on a\nRequest (https://playwright.dev/docs/api/class-request)\n/\nResponse (https://playwright.dev/docs/api/class-response)\nthat has a non-null\nrequest.serviceWorker() (https://playwright.dev/docs/api/class-request#request-service-worker)\n.', "Playwright's built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nallow your tests to natively route requests and perform mocking and interception.\n\nIf you're using Playwright's native\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n, and it appears network events are missing, disable Service Workers by setting\nserviceWorkers (https://playwright.dev/docs/api/class-browser#browser-new-context-option-service-workers)\nto\n`'block'`\n.\n\nIt might be that you are using a mock tool such as Mock Service Worker (MSW). While this tool works out of the box for mocking responses, it adds its own Service Worker that takes over the network requests, hence making them invisible to\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n. If you are interested in both network testing and mocking, consider using built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nfor\nresponse mocking (https://playwright.dev/docs/network#handle-requests)\n.", "Playwright allows to disable Service Workers during testing. This makes tests more predictable and performant. However, if your actual page uses a Service Worker, the behavior might be different.\n\nTo disable service workers, set\ntestOptions.serviceWorkers (https://playwright.dev/docs/api/class-testoptions#test-options-service-workers)\nto\n`'block'`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{serviceWorkers:'allow'},});`\n```", 'Requests for updated Service Worker main script code currently cannot be routed (\nhttps://github.com/microsoft/playwright/issues/14711 (https://github.com/microsoft/playwright/issues/14711)\n).', "```\n`awaitcontext.route('**',asyncroute=&gt;{if(route.request().serviceWorker()){// NB: calling route.request().frame() here would THROWawaitroute.fulfill({contentType:'text/plain',status:200,body:'from sw',});}else{awaitroute.continue();}});`\n```", "You can use\nbrowserContext.serviceWorkers() (https://playwright.dev/docs/api/class-browsercontext#browser-context-service-workers)\nto list the Service\nWorker (https://playwright.dev/docs/api/class-worker)\ns, or specifically watch for the Service\nWorker (https://playwright.dev/docs/api/class-worker)\nif you anticipate a page will trigger its\nregistration (https://developer.mozilla.org/en-US/docs/Web/API/ServiceWorkerContainer/register)\n:\n\n```\n`constserviceWorkerPromise=context.waitForEvent('serviceworker');awaitpage.goto('/example-with-a-service-worker.html');constserviceworker=awaitserviceWorkerPromise;`\n```\n\nbrowserContext.on('serviceworker') (https://playwright.dev/docs/api/class-browsercontext#browser-context-event-service-worker)\nevent is fired\nbefore\nthe Service Worker has taken control over the page, so\nbefore\nevaluating in the worker with\nworker.evaluate() (https://playwright.dev/docs/api/class-worker#worker-evaluate)\nyou should wait on its activation.\n\nThere are more idiomatic methods of waiting for a Service Worker to be activated, but the following is an implementation agnostic method:\n\n```\n`awaitpage.evaluate(async()=&gt;{constregistration=awaitwindow.navigator.serviceWorker.getRegistration();if(registration.active?.state==='activated')return;awaitnewPromise(resolve=&gt;{window.navigator.serviceWorker.addEventListener('controllerchange',resolve);});});`\n```", "warning\nService workers are only supported on Chromium-based browsers.\n\nnote\nIf you're looking to do general network mocking, routing, and interception, please see the\nNetwork Guide (https://playwright.dev/docs/network)\nfirst. Playwright provides built-in APIs for this use case that don't require the information below. However, if you're interested in requests made by Service Workers themselves, please read below.\n\nService Workers (https://developer.mozilla.org/en-US/docs/Web/API/Service_Worker_API)\nprovide a browser-native method of handling requests made by a page with the native\nFetch API ( fetch ) (https://developer.mozilla.org/en-US/docs/Web/API/Fetch_API)\nalong with other network-requested assets (like scripts, css, and images).\n\nThey can act as a\nnetwork proxy\nbetween the page and the external network to perform caching logic or can provide users with an offline experience if the Service Worker adds a\nFetchEvent (https://developer.mozilla.org/en-US/docs/Web/API/FetchEvent#examples)\nlistener.\n\nMany sites that use Service Workers simply use them as a transparent optimization technique. While users might notice a faster experience, the app's implementation is unaware of their existence. Running the app with or without Service Workers enabled appears functionally equivalent."]</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2417,26 +2476,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Whether a request is interceptable depends on whether it is owned by the Service Worker or the Frame. When a Service Worker has a fetch handler registered, Frame-owned requests for resources are not routable via `browserContext.route()` because they do not hit the external network. Only Service Worker-owned requests are routable. You can identify these requests by checking `request.serviceWorker()`; if it is non-null, the request is owned by the Service Worker.
+          <t>Whether a request is interceptable depends on whether it is owned by the Service Worker or the Frame. When a Service Worker has a fetch handler registered, Frame-owned requests for resources are not routable via `browserContext.route()` because they do not have the possibility of hitting the external network. Conversely, requests made by the Service Worker itself are routable.
 To test against this app, you have two primary options:
-1.  **Disable Service Workers:** If you want to make tests more predictable and performant, you can disable Service Workers by setting `serviceWorkers` to `'block'` in your `playwright.config.ts`. Note that this may cause the application to behave differently than it does in production if it relies on Service Worker logic.
-2.  **Route Service Worker Requests:** If you must test with the Service Worker enabled, you can use `browserContext.route()` to specifically target requests made by the Service Worker. You can check if a request is owned by the Service Worker using `route.request().serviceWorker()` and handle it accordingly:
+1.  **Disable Service Workers:** If you want to use Playwright's native `browserContext.route()` or `page.route()` for mocking and interception without interference, set `serviceWorkers` to `'block'` in your `testOptions`. This makes tests more predictable and performant.
+2.  **Route Service Worker Requests:** If you must test with the Service Worker enabled, you can specifically target requests made by the worker. You can use `route.request().serviceWorker()` to identify these requests and handle them accordingly:
 ```javascript
 await context.route('**', async route =&gt; {
   if (route.request().serviceWorker()) {
-    // Handle Service Worker-owned request
-    await route.fulfill({
-      contentType: 'text/plain',
-      status: 200,
-      body: 'from sw',
-    });
+    // Handle requests made by the Service Worker
+    await route.fulfill({ contentType: 'text/plain', status: 200, body: 'from sw' });
   } else {
-    // Handle other requests
+    // Continue other requests
     await route.continue();
   }
 });
 ```
-When using this approach, be aware that calling `route.request().frame()` on a request where `request.serviceWorker()` is non-null will throw an exception.</t>
+**Important considerations:**
+*   **Avoid Mocking Tools:** If you are using a tool like Mock Service Worker (MSW), it adds its own Service Worker that takes over network requests, making them invisible to Playwright's routing APIs. The documentation recommends using Playwright's built-in `browserContext.route()` and `page.route()` for response mocking instead.
+*   **Avoid Frame Access:** When handling a request where `request.serviceWorker()` is non-null, do not call `request.frame()` or `response.frame()`, as these will throw an exception.
+*   **Service Worker Lifecycle:** If you need to interact with the Service Worker, use `browserContext.serviceWorkers()` to list them or `context.waitForEvent('serviceworker')` to watch for them. Ensure you wait for the worker to be activated before evaluating code within it.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2445,31 +2503,31 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.010926</v>
+        <v>0.001542</v>
       </c>
       <c r="G32" t="n">
-        <v>39839</v>
+        <v>35492</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0.58</v>
+        <v>0.46</v>
       </c>
       <c r="J32" t="n">
         <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2240663900414938</v>
+        <v>0.1711409395973154</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2769230769230769</v>
+        <v>0.2615384615384616</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8874999999778125</v>
+        <v>0.8666666666377778</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="33">
@@ -2480,7 +2538,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>["System dependencies can get installed automatically. This is useful for CI environments.\n\n```\n`npx playwright install-deps`\n```\n\nYou can also install the dependencies for a single browser by passing it as an argument:\n\n```\n`npx playwright install-deps chromium`\n```\n\nIt's also possible to combine\n`install-deps`\nwith\n`install`\nso that the browsers and OS dependencies are installed with a single command.\n\n```\n`npx playwrightinstall--with-deps chromium`\n```\n\nSee\nsystem requirements (https://playwright.dev/docs/intro#system-requirements)\nfor officially supported operating systems.", 'Browsers | Playwright', 'Playwright supports the\n`DEBUG`\nenvironment variable to output debug logs during execution. Setting it to\n`pw:browser`\nis helpful while debugging\n`Error: Failed to launch browser`\nerrors.\n\n```\n`DEBUG=pw:browser npx playwrighttest`\n```', 'Tests will run on push or pull request on branches main/master. The\nworkflow (https://docs.github.com/en/actions/using-workflows/about-workflows)\nwill install all dependencies, install Playwright and then run the tests. It will also create the HTML report.\n\n.github/workflows/playwright.yml\n```\n`name:Playwright Testson:push:branches:[main,master]pull_request:branches:[main,master]jobs:test:timeout-minutes:60runs-on:ubuntu-lateststeps:-uses:actions/checkout@v5-uses:actions/setup-node@v6with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Install Playwright Browsersrun:npx playwright install--with-deps-name:Run Playwright testsrun:npx playwright test-uses:actions/upload-artifact@v5if:${{!cancelled()}}with:name:playwright-reportpath:playwright-report/retention-days:30`\n```', 'Continuous Integration | Playwright', 'Playwright tests can be executed in CI environments. We have created sample configurations for common CI providers.\n\n3 steps to get your tests running on CI:\n\nEnsure CI agent can run browsers\n: Use\nour Docker image (https://playwright.dev/docs/docker)\nin Linux agents or install your dependencies using the\nCLI (https://playwright.dev/docs/browsers#install-system-dependencies)\n.\nInstall Playwright\n:\n```\n`# Install NPM packagesnpmci# Install Playwright browsers and dependenciesnpx playwrightinstall--with-deps`\n```\nRun your tests\n:\n```\n`npx playwrighttest`\n```', "GitHub Actions support\nrunning jobs in a container (https://docs.github.com/en/actions/using-jobs/running-jobs-in-a-container)\nby using the\njobs.&lt;job_id&gt;.container (https://docs.github.com/en/actions/using-workflows/workflow-syntax-for-github-actions#jobsjob_idcontainer)\noption. This is useful to not pollute the host environment with dependencies and to have a consistent environment for e.g. screenshots/visual regression testing across different operating systems.\n\n.github/workflows/playwright.yml\n```\n`name:Playwright Testson:push:branches:[main,master]pull_request:branches:[main,master]jobs:playwright:name:'Playwright Tests'runs-on:ubuntu-latestcontainer:image:mcr.microsoft.com/playwright:v1.60.0-nobleoptions:--user 1001steps:-uses:actions/checkout@v5-uses:actions/setup-node@v6with:node-version:lts/*-name:Install dependenciesrun:npm ci-name:Run your testsrun:npx playwright test`\n```"]</t>
+          <t>["System dependencies can get installed automatically. This is useful for CI environments.\n\n```\n`npx playwright install-deps`\n```\n\nYou can also install the dependencies for a single browser by passing it as an argument:\n\n```\n`npx playwright install-deps chromium`\n```\n\nIt's also possible to combine\n`install-deps`\nwith\n`install`\nso that the browsers and OS dependencies are installed with a single command.\n\n```\n`npx playwrightinstall--with-deps chromium`\n```\n\nSee\nsystem requirements (https://playwright.dev/docs/intro#system-requirements)\nfor officially supported operating systems.", 'Playwright tests can be executed in CI environments. We have created sample configurations for common CI providers.\n\n3 steps to get your tests running on CI:\n\nEnsure CI agent can run browsers\n: Use\nour Docker image (https://playwright.dev/docs/docker)\nin Linux agents or install your dependencies using the\nCLI (https://playwright.dev/docs/browsers#install-system-dependencies)\n.\nInstall Playwright\n:\n```\n`# Install NPM packagesnpmci# Install Playwright browsers and dependenciesnpx playwrightinstall--with-deps`\n```\nRun your tests\n:\n```\n`npx playwrighttest`\n```', 'Playwright supports the\n`DEBUG`\nenvironment variable to output debug logs during execution. Setting it to\n`pw:browser`\nis helpful while debugging\n`Error: Failed to launch browser`\nerrors.\n\n```\n`DEBUG=pw:browser npx playwrighttest`\n```', 'We have a\npre-built Docker image (https://playwright.dev/docs/docker)\nwhich can either be used directly or as a reference to update your existing Docker definitions. Make sure to follow the\nRecommended Docker Configuration (https://playwright.dev/docs/docker#recommended-docker-configuration)\nto ensure the best performance.', 'Playwright can install supported browsers. Running the command without arguments will install the default browsers.\n\n```\n`npx playwrightinstall`\n```\n\nYou can also install specific browsers by providing an argument:\n\n```\n`npx playwrightinstallwebkit`\n```\n\nSee all supported browsers:\n\n```\n`npx playwrightinstall--help`\n```', 'You can opt into the hermetic install and place binaries in the local folder:\n\nBash\nPowerShell\nBatch\n```\n`# Places binaries to node_modules/playwright-core/.local-browsersPLAYWRIGHT_BROWSERS_PATH=0npx playwrightinstall`\n```\n```\n`# Places binaries to node_modules\\playwright-core\\.local-browsers$Env:PLAYWRIGHT_BROWSERS_PATH=0npx playwright install`\n```\n```\n`# Places binaries to node_modules\\playwright-core\\.local-browserssetPLAYWRIGHT_BROWSERS_PATH=0npxplaywright install`\n```\n\nnote\n`PLAYWRIGHT_BROWSERS_PATH`\ndoes not change installation path for Google Chrome and Microsoft Edge.', 'Node.js: latest 22.x, 24.x or 26.x.\nWindows 11+, Windows Server 2019+ or Windows Subsystem for Linux (WSL).\nmacOS 14 (Sonoma) or later.\nDebian 12 / 13, Ubuntu 22.04 / 24.04 / 26.04 (x86-64 or arm64).']</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2490,41 +2548,15 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>The CI runner is missing the necessary system dependencies required to launch browsers, which are present on your local machines but not pre-installed on the `ubuntu-latest` environment.
-To fix this durably, you have two supported options:
-### 1. Install dependencies via CLI (Recommended for standard runners)
-You must ensure the CI agent installs the required system dependencies alongside the browsers. Update your GitHub Actions workflow to use the following command:
+          <t>The CI runner is missing the necessary system-level dependencies required to execute browsers, which are present on your local machines but not pre-installed on the `ubuntu-latest` environment.
+To fix this durably, you should use the Playwright CLI to install these dependencies in your CI pipeline. The recommended approach is to use the `install --with-deps` command, which installs both the required browsers and the necessary OS dependencies in a single step:
 ```bash
 npx playwright install --with-deps
 ```
-This command installs both the Playwright browsers and the required OS-level shared libraries. Your workflow steps should look like this:
-```yaml
-- name: Install dependencies
-  run: npm ci
-- name: Install Playwright Browsers
-  run: npx playwright install --with-deps
-- name: Run Playwright tests
-  run: npx playwright test
-```
-### 2. Use a Docker container
-Alternatively, you can run your job inside a pre-configured Playwright Docker image. This ensures a consistent environment and avoids polluting the host runner with dependencies. You can configure this in your workflow file using the `container` option:
-```yaml
-jobs:
-  playwright:
-    runs-on: ubuntu-latest
-    container:
-      image: mcr.microsoft.com/playwright:v1.60.0-noble
-    steps:
-      - uses: actions/checkout@v5
-      - uses: actions/setup-node@v6
-        with:
-          node-version: lts/*
-      - name: Install dependencies
-        run: npm ci
-      - name: Run your tests
-        run: npx playwright test
-```
-If you need to debug further, you can set the `DEBUG` environment variable to `pw:browser` to output logs during execution.</t>
+Alternatively, if you prefer to install them separately, you can use:
+1. `npx playwright install` to install the browsers.
+2. `npx playwright install-deps` to install the required system dependencies.
+If you are using a Linux agent, you can also ensure your environment is correctly configured by using the pre-built Playwright Docker image.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2533,28 +2565,28 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0.009942499999999001</v>
+        <v>0.0006435</v>
       </c>
       <c r="G33" t="n">
-        <v>36635</v>
+        <v>49260</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="J33" t="n">
         <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1637931034482759</v>
+        <v>0.2388059701492537</v>
       </c>
       <c r="L33" t="n">
-        <v>0.25</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8734126983981415</v>
+        <v>0.99999999995</v>
       </c>
       <c r="N33" t="n">
         <v>1</v>
@@ -2568,7 +2600,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>["Web apps use cookie-based or token-based authentication, where authenticated state is stored as\ncookies (https://developer.mozilla.org/en-US/docs/Web/HTTP/Cookies)\n. Playwright provides\napiRequestContext.storageState() (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state)\nmethod that can be used to retrieve storage state from an authenticated context and then create new contexts with that state.\n\nStorage state is interchangeable between\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nand\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n. You can use it to log in via API calls and then create a new context with cookies already there. The following code snippet retrieves state from an authenticated\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nand creates a new\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nwith that state.\n\n```\n`constrequestContext=awaitrequest.newContext({httpCredentials:{username:'user',password:'passwd'}});awaitrequestContext.get(`https://api.example.com/login`);// Save storage state into the file.awaitrequestContext.storageState({path:'state.json'});// Create a new context with the saved storage state.constcontext=awaitbrowser.newContext({storageState:'state.json'});`\n```", "When to use\n\nYour web application supports authenticating via API that is easier/faster than interacting with the app UI.\n\nDetails\n\nWe will send the API request with\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nand then save authenticated state as usual.\n\nIn the\nsetup project (https://playwright.dev/docs/auth#basic-shared-account-in-all-tests)\n:\n\ntests/auth.setup.ts\n```\n`import{testassetup}from'@playwright/test';constauthFile='playwright/.auth/user.json';setup('authenticate',async({request})=&gt;{// Send authentication request. Replace with your own.awaitrequest.post('https://github.com/login',{form:{'user':'user','password':'password'}});awaitrequest.storageState({path:authFile});});`\n```\n\nAlternatively, in a\nworker fixture (https://playwright.dev/docs/auth#moderate-one-account-per-parallel-worker)\n:\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,request}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constcontext=awaitrequest.newContext({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Send authentication request. Replace with your own.awaitcontext.post('https://github.com/login',{form:{'user':'user','password':'password'}});awaitcontext.storageState({path:fileName});awaitcontext.dispose();awaituse(fileName);},{scope:'worker'}],});`\n```", 'APIRequestContext | Playwright\n\nThis API is used for the Web API testing. You can use it to trigger API endpoints, configure micro-services, prepare environment or the service to your e2e test.\n\nEach Playwright browser context has an associated\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n, accessible via\nbrowserContext.request (https://playwright.dev/docs/api/class-browsercontext#browser-context-request)\nor\npage.request (https://playwright.dev/docs/api/class-page#page-request)\n(these return the\n\nsame instance\n—\n`page.request`\nis a shortcut for\n`page.context().request`\n). You can also create a standalone, isolated instance with\napiRequest.newContext() (https://playwright.dev/docs/api/class-apirequest#api-request-new-context)\n.\n\nCookie management\n\nThe\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nreturned by\nbrowserContext.request (https://playwright.dev/docs/api/class-browsercontext#browser-context-request)\nand\n\npage.request (https://playwright.dev/docs/api/class-page#page-request)\nuses the same cookie jar as its\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\n:\n\nIf you want API requests that do\nnot\nshare cookies with the browser, create an isolated context via\napiRequest.newContext() (https://playwright.dev/docs/api/class-apirequest#api-request-new-context)\n. Such\n`APIRequestContext`\nobject will have its own isolated cookie storage.', 'API testing | Playwright', 'Authentication | Playwright', "This is the\nrecommended\napproach for tests\nwithout server-side state\n. Authenticate once in the\nsetup project\n, save the authentication state, and then reuse it to bootstrap each test already authenticated.\n\nWhen to use\n\nWhen you can imagine all your tests running at the same time with the same account, without affecting each other.\n\nWhen not to use\n\nYour tests modify server-side state. For example, one test checks the rendering of the settings page, while the other test is changing the setting, and you run tests in parallel. In this case, tests must use different accounts.\nYour authentication is browser-specific.\n\nDetails\n\nCreate\n`tests/auth.setup.ts`\nthat will prepare authenticated browser state for all other tests.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';importpathfrom'path';constauthFile=path.join(__dirname,'../playwright/.auth/user.json');setup('authenticate',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('username');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:authFile});});`\n```\n\nCreate a new\n`setup`\nproject in the config and declare it as a\ndependency (https://playwright.dev/docs/test-projects#dependencies)\nfor all your testing projects. This project will always run and authenticate before all the tests. All testing projects should use the authenticated state as\n`storageState`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[// Setup project{name:'setup',testMatch:/.*\\.setup\\.ts/},{name:'chromium',use:{...devices['Desktop Chrome'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},{name:'firefox',use:{...devices['Desktop Firefox'],// Use prepared auth state.storageState:'playwright/.auth/user.json',},dependencies:['setup'],},],});`\n```\n\nTests start already authenticated because we specified\n`storageState`\nin the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test('test',async({page})=&gt;{// page is authenticated});`\n```\n\nNote that you need to delete the stored state when it expires. If you don't need to keep the state between test runs, write the browser state under\ntestProject.outputDir (https://playwright.dev/docs/api/class-testproject#test-project-output-dir)\n, which is automatically cleaned up before every test run.", 'Global setup and teardown | Playwright']</t>
+          <t>["Web apps use cookie-based or token-based authentication, where authenticated state is stored as\ncookies (https://developer.mozilla.org/en-US/docs/Web/HTTP/Cookies)\n. Playwright provides\napiRequestContext.storageState() (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state)\nmethod that can be used to retrieve storage state from an authenticated context and then create new contexts with that state.\n\nStorage state is interchangeable between\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nand\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n. You can use it to log in via API calls and then create a new context with cookies already there. The following code snippet retrieves state from an authenticated\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nand creates a new\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nwith that state.\n\n```\n`constrequestContext=awaitrequest.newContext({httpCredentials:{username:'user',password:'passwd'}});awaitrequestContext.get(`https://api.example.com/login`);// Save storage state into the file.awaitrequestContext.storageState({path:'state.json'});// Create a new context with the saved storage state.constcontext=awaitbrowser.newContext({storageState:'state.json'});`\n```", "When to use\n\nYour web application supports authenticating via API that is easier/faster than interacting with the app UI.\n\nDetails\n\nWe will send the API request with\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nand then save authenticated state as usual.\n\nIn the\nsetup project (https://playwright.dev/docs/auth#basic-shared-account-in-all-tests)\n:\n\ntests/auth.setup.ts\n```\n`import{testassetup}from'@playwright/test';constauthFile='playwright/.auth/user.json';setup('authenticate',async({request})=&gt;{// Send authentication request. Replace with your own.awaitrequest.post('https://github.com/login',{form:{'user':'user','password':'password'}});awaitrequest.storageState({path:authFile});});`\n```\n\nAlternatively, in a\nworker fixture (https://playwright.dev/docs/auth#moderate-one-account-per-parallel-worker)\n:\n\nplaywright/fixtures.ts\n```\n`import{testasbaseTest,request}from'@playwright/test';importfsfrom'fs';importpathfrom'path';export*from'@playwright/test';exportconsttest=baseTest.extend&lt;{},{workerStorageState:string}&gt;({// Use the same storage state for all tests in this worker.storageState:({workerStorageState},use)=&gt;use(workerStorageState),// Authenticate once per worker with a worker-scoped fixture.workerStorageState:[async({},use)=&gt;{// Use parallelIndex as a unique identifier for each worker.constid=test.info().parallelIndex;constfileName=path.resolve(test.info().project.outputDir,`.auth/${id}.json`);if(fs.existsSync(fileName)){// Reuse existing authentication state if any.awaituse(fileName);return;}// Important: make sure we authenticate in a clean environment by unsetting storage state.constcontext=awaitrequest.newContext({storageState:undefined});// Acquire a unique account, for example create a new one.// Alternatively, you can have a list of precreated accounts for testing.// Make sure that accounts are unique, so that multiple team members// can run tests at the same time without interference.constaccount=awaitacquireAccount(id);// Send authentication request. Replace with your own.awaitcontext.post('https://github.com/login',{form:{'user':'user','password':'password'}});awaitcontext.storageState({path:fileName});awaitcontext.dispose();awaituse(fileName);},{scope:'worker'}],});`\n```", 'Added in: v1.16\n\napiRequestContext.storageState\n\nReturns storage state for this request context, contains current cookies and local storage snapshot if it was passed to the constructor.\n\nUsage\n\n```\n`awaitapiRequestContext.storageState();awaitapiRequestContext.storageState(options);`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`indexedDB`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.51\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state-option-indexed-db)\nSet to\n`true`\nto include IndexedDB in the storage state snapshot.\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state-option-path)\nThe file path to save the storage state to. If\npath (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state-option-path)\nis a relative path, then it is resolved relative to current working directory. If no path is provided, storage state is still returned, but won\'t be saved to the disk.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n# (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state-return)\n`cookies`\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`domain`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`expires`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\nUnix time in seconds.\n`httpOnly`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n`secure`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n`sameSite`\n"Strict" | "Lax" | "None"\n`origins`\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n`origin`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`localStorage`\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)', "There are two types of\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n:\n\nassociated with a\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nisolated instance, created via\napiRequest.newContext() (https://playwright.dev/docs/api/class-apirequest#api-request-new-context)\n\nThe main difference is that\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\naccessible via\nbrowserContext.request (https://playwright.dev/docs/api/class-browsercontext#browser-context-request)\nand\npage.request (https://playwright.dev/docs/api/class-page#page-request)\nwill populate request's\n`Cookie`\nheader from the browser context and will automatically update browser cookies if\nAPIResponse (https://playwright.dev/docs/api/class-apiresponse)\nhas\n`Set-Cookie`\nheader:\n\n```\n`test('context request will share cookie storage with its browser context',async({page,context,})=&gt;{awaitcontext.route('https://www.github.com/',asyncroute=&gt;{// Send an API request that shares cookie storage with the browser context.constresponse=awaitcontext.request.fetch(route.request());constresponseHeaders=response.headers();// The response will have 'Set-Cookie' header.constresponseCookies=newMap(responseHeaders['set-cookie'].split('\\n').map(c=&gt;c.split(';',2)[0].split('=')));// The response will have 3 cookies in 'Set-Cookie' header.expect(responseCookies.size).toBe(3);constcontextCookies=awaitcontext.cookies();// The browser context will already contain all the cookies from the API response.expect(newMap(contextCookies.map(({name,value})=&gt;[name,value]))).toEqual(responseCookies);awaitroute.fulfill({response,headers:{...responseHeaders,foo:'bar'},});});awaitpage.goto('https://www.github.com/');});`\n```\n\nIf you don't want\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nto use and update cookies from the browser context, you can manually create a new instance of\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nwhich will have its own isolated cookies:\n\n```\n`test('global context request has isolated cookie storage',async({page,context,browser,playwright})=&gt;{// Create a new instance of APIRequestContext with isolated cookie storage.constrequest=awaitplaywright.request.newContext();awaitcontext.route('https://www.github.com/',asyncroute=&gt;{constresponse=awaitrequest.fetch(route.request());constresponseHeaders=response.headers();constresponseCookies=newMap(responseHeaders['set-cookie'].split('\\n').map(c=&gt;c.split(';',2)[0].split('=')));// The response will have 3 cookies in 'Set-Cookie' header.expect(responseCookies.size).toBe(3);constcontextCookies=awaitcontext.cookies();// The browser context will not have any cookies from the isolated API request.expect(contextCookies.length).toBe(0);// Manually export cookie storage.conststorageState=awaitrequest.storageState();// Create a new context and initialize it with the cookies from the global request.constbrowserContext2=awaitbrowser.newContext({storageState});constcontextCookies2=awaitbrowserContext2.cookies();// The new browser context will already contain all the cookies from the API response.expect(newMap(contextCookies2.map(({name,value})=&gt;[name,value]))).toEqual(responseCookies);awaitroute.fulfill({response,headers:{...responseHeaders,foo:'bar'},});});awaitpage.goto('https://www.github.com/');awaitrequest.dispose();});`\n```", 'Added before v1.9\n\nbrowserContext.storageState\n\nReturns storage state for this browser context, contains current cookies, local storage snapshot and IndexedDB snapshot.\n\nUsage\n\n```\n`awaitbrowserContext.storageState();awaitbrowserContext.storageState(options);`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`indexedDB`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.51\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-storage-state-option-indexed-db)\nSet to\n`true`\nto include\nIndexedDB (https://developer.mozilla.org/en-US/docs/Web/API/IndexedDB_API)\nin the storage state snapshot. If your application uses IndexedDB to store authentication tokens, like Firebase Authentication, enable this.\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-storage-state-option-path)\nThe file path to save the storage state to. If\npath (https://playwright.dev/docs/api/class-browsercontext#browser-context-storage-state-option-path)\nis a relative path, then it is resolved relative to current working directory. If no path is provided, storage state is still returned, but won\'t be saved to the disk.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-storage-state-return)\n`cookies`\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`domain`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`expires`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\nUnix time in seconds.\n`httpOnly`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n`secure`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n`sameSite`\n"Strict" | "Lax" | "None"\n`origins`\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n`origin`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`localStorage`\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)', 'Added in: v1.59\n\nbrowserContext.setStorageState\n\nClears the existing cookies, local storage and IndexedDB entries for all origins and sets the new storage state.\n\nUsage\n\n```\n`// Load storage state from a file and apply it to the context.awaitcontext.setStorageState(\'state.json\');`\n```\n\nArguments\n\n`storageState`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-storage-state-option-storage-state)\n`cookies`\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`domain`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\nDomain and path are required. For the cookie to apply to all subdomains as well, prefix domain with a dot, like this: ".example.com"\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\nDomain and path are required\n`expires`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\nUnix time in seconds.\n`httpOnly`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n`secure`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n`sameSite`\n"Strict" | "Lax" | "None"\nsameSite flag\nCookies to set for context\n`origins`\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n`origin`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`localStorage`\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt;\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\nlocalStorage to set for context\nLearn more about\nstorage state and auth (https://playwright.dev/docs/auth)\n.\nPopulates context with given storage state. This option can be used to initialize context with logged-in information obtained via\nbrowserContext.storageState() (https://playwright.dev/docs/api/class-browsercontext#browser-context-storage-state)\n.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-storage-state-return)', 'Added in: v1.16\n\napiRequest.newContext\n\nCreates new instances of\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n.\n\nUsage\n\n```\n`awaitapiRequest.newContext();awaitapiRequest.newContext(options);`\n```\n\nArguments\n\n`options` Object (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object) (optional) `baseURL` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) (optional) # (https://playwright.dev/docs/api/class-apirequest#api-request-new-context-option-base-url) Methods like apiRequestContext.get() (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-get) take the base URL into consideration by using the URL() (https://developer.mozilla.org/en-US/docs/Web/API/URL/URL) constructor for building the corresponding URL. Examples: baseURL: `http://localhost:3000` and sending request to `/bar.html` results in `http://localhost:3000/bar.html` baseURL: `http://localhost:3000/foo/` and sending request to `./bar.html` results in `http://localhost:3000/foo/bar.html` baseURL: `http://localhost:3000/foo` (without trailing slash) and navigating to `./bar.html` results in `http://localhost:3000/bar.html` `clientCertificates` Array (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array) &lt; Object (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object) &gt; (optional) Added in: 1.46 # (https://playwright.dev/docs/api/class-apirequest#api-request-new-context-option-client-certificates) `origin` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) Exact origin that the certificate is valid for. Origin includes `https` protocol, a hostname and optionally a port. `certPath` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) (optional) Path to the file with the certificate in PEM format. `cert` Buffer (https://nodejs.org/api/buffer.html#buffer_class_buffer) (optional) Direct value of the certificate in PEM format. `keyPath` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) (optional) Path to the file with the private key in PEM format. `key` Buffer (https://nodejs.org/api/buffer.html#buffer_class_buffer) (optional) Direct value of the private key in PEM format. `pfxPath` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) (optional) Path to the PFX or PKCS12 encoded private key and certificate chain. `pfx` Buffer (https://nodejs.org/api/buffer.html#buffer_class_buffer) (optional) Direct value of the PFX or PKCS12 encoded private key and certificate chain. `passphrase` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) (optional) Passphrase for the private key (PEM or PFX). TLS Client Authentication allows the server to request a client certificate and verify it. Details An array of client certificates to be used. Each certificate object must have either both `certPath` and `keyPath` , a single `pfxPath` , or their corresponding direct value equivalents ( `cert` and `key` , or `pfx` ). Optionally, `passphrase` property should be provided if the certificate is encrypted. The `origin` property should be provided with an exact match to the request origin that the certificate is valid for. Client certificate authentication is only active when at least one client certificate is provided. If you want to reject all client certificates sent by the server, you need to provide a client certificate with an `origin` that does not match any of the domains you plan to visit. note When using WebKit on macOS, accessing `localhost` will not pick up client certificates. You can make it work by replacing `localhost` with `local.playwright` . `extraHTTPHeaders` Object (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object) &lt; string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) , string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) &gt; (optional) # (https://playwright.dev/docs/api/class-apirequest#api-request-new-context-option-extra-http-headers) An object containing additional HTTP headers to be sent with every request. Defaults to none. `failOnStatusCode` boolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type) (optional) Added in: v1.51 # (https://playwright.dev/docs/api/class-apirequest#api-request-new-context-option-fail-on-status-code) Whether to throw on response codes other than 2xx and 3xx. By default response object is returned for all status codes. `httpCredentials` Object (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object) (optional) # (https://playwright.dev/docs/api/class-apirequest#api-request-new-context-option-http-credentials) `username` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) `password` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) `origin` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) (optional) Restrain sending http credentials on specific origin (scheme://host :port ). `send` "unauthorized" | "always" (optional) This option only applies to the requests sent from corresponding APIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext) and does not affect requests sent from the browser. `\'always\'` - `Authorization` header with basic authentication credentials will be sent with the each API request. `\'unauthorized` - the credentials are only sent when 401 (Unauthorized) response with `WWW-Authenticate` header is received. Defaults to `\'unauthorized\'` . Credentials for HTTP authentication (https://developer.mozilla.org/en-US/docs/Web/HTTP/Authentication) . If no origin is specified, the username and password are sent to any servers upon unauthorized responses. `ignoreHTTPSErrors` boolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type) (optional) # (https://playwright.dev/docs/api/class-apirequest#api-request-new-context-option-ignore-https-errors) Whether to ignore HTTPS errors when sending network requests. Defaults to `false` . `maxRedirects` number (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type) (optional) Added in: v1.52 # (https://playwright.dev/docs/api/class-apirequest#api-request-new-context-option-max-redirects) Maximum number of request redirects that will be followed automatically. An error will be thrown if the number is exceeded. Defaults to `20` . Pass `0` to not follow redirects. This can be overwritten for each request individually. `proxy` Object (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object) (optional) # (https://playwright.dev/docs/api/class-apirequest#api-request-new-context-option-proxy) `server` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) Proxy to be used for all requests. HTTP and SOCKS proxies are supported, for example `http://myproxy.com:3128` or `socks5://myproxy.com:3128` . Short form `myproxy.com:3128` is considered an HTTP proxy. `bypass` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) (optional) Optional comma-separated domains to bypass proxy, for example `".com, chromium.org, .domain.com"` . `username` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) (optional) Optional username to use if HTTP proxy requires authentication. `password` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) (optional) Optional password to use if HTTP proxy requires authentication. Network proxy settings. `storageState` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) | Object (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object) (optional) # (https://playwright.dev/docs/api/class-apirequest#api-request-new-context-option-storage-state) `cookies` Array (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array) &lt; Object (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object) &gt; `name` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) `value` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) `domain` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) `path` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) `expires` number (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type) Unix time in seconds. `httpOnly` boolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type) `secure` boolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type) `sameSite` "Strict" | "Lax" | "None" `origins` Array (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array) &lt; Object (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object) &gt; `origin` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) `localStorage` Array (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array) &lt; Object (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object) &gt; `name` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) `value` string (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type) Populates context with given storage state. This option can be used to initialize context with logged-in information obtained via browserContext.storageState() (https://playwright.dev/docs/api/class-browsercontext#browser-context-storage-state) or apiRequestContext.storageState() (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state) . Either a path to the file with saved storage, or the value returned by one of browserContext.storageState() (https://playwright.dev/docs/api/class-browsercontext#browser-context-storage-state) or apiRequestContext.storageState() (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state) methods. `timeout` number (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type) (optional) # (https://playwright.dev/docs/api/class-apirequest#api-request-new-context-option-timeout) Maximum time in milliseconds to wait for the']</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2580,19 +2612,10 @@
         <is>
           <t>Yes, you can authenticate through API calls and hand that session to a browser context. Storage state is interchangeable between `APIRequestContext` and `BrowserContext`.
 To do this, follow these steps:
-1.  **Perform the API authentication:** Use `request.newContext()` to create an API request context and perform your login request.
-2.  **Save the state:** Use the `apiRequestContext.storageState()` method to save the authenticated state (cookies/tokens) to a file.
-    ```javascript
-    const requestContext = await request.newContext({httpCredentials: {username: 'user', password: 'passwd'}});
-    await requestContext.get(`https://api.example.com/login`);
-    // Save storage state into the file.
-    await requestContext.storageState({path: 'state.json'});
-    ```
-3.  **Use the state in a browser context:** Create a new browser context by passing the path to the saved state file in the `storageState` option.
-    ```javascript
-    const context = await browser.newContext({storageState: 'state.json'});
-    ```
-For automated testing, you can implement this in a `setup` project or a worker fixture to reuse the authentication state across tests.</t>
+1.  **Authenticate via API:** Use `request.newContext()` to create an API request context and perform your login request.
+2.  **Save the state:** Call `apiRequestContext.storageState({ path: 'state.json' })` to save the cookies and local storage to a file.
+3.  **Use the state in a browser:** Create a new browser context using that file: `browser.newContext({ storageState: 'state.json' })`.
+Alternatively, if you have an existing browser context, you can apply the saved state to it using `browserContext.setStorageState('state.json')`.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2601,10 +2624,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.009216499999999999</v>
+        <v>0.00238725</v>
       </c>
       <c r="G34" t="n">
-        <v>34301</v>
+        <v>48935</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -2616,13 +2639,13 @@
         <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.1759259259259259</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4651162790697674</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9666666666473333</v>
+        <v>0.8734126983981415</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
@@ -2636,7 +2659,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>['Route | Playwright\n\nWhenever a network route is set up with\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nor\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n, the\n`Route`\nobject allows to handle the route.\n\nLearn more about\nnetworking (https://playwright.dev/docs/network)\n.', 'Mock APIs | Playwright', "Sometimes, it is essential to make an API request, but the response needs to be patched to allow for reproducible testing. In that case, instead of mocking the request, one can perform the request and fulfill it with the modified response.\n\nIn the example below we intercept the call to the fruit API and add a new fruit called 'Loquat', to the data. We then go to the url and assert that this data is there:\n\n```\n`test('gets the json from api and adds a new fruit',async({page})=&gt;{// Get the response and add to itawaitpage.route('*/**/api/v1/fruits',asyncroute=&gt;{constresponse=awaitroute.fetch();constjson=awaitresponse.json();json.push({name:'Loquat',id:100});// Fulfill using the original response, while patching the response body// with the given JSON object.awaitroute.fulfill({response,json});});// Go to the pageawaitpage.goto('https://demo.playwright.dev/api-mocking');// Assert that the new fruit is visibleawaitexpect(page.getByText('Loquat',{exact:true})).toBeVisible();});`\n```\n\nIn the trace of our test we can see that the API was called and the response was modified.\n\nBy inspecting the response we can see that our new fruit was added to the list.\n\nRead more about\nadvanced networking (https://playwright.dev/docs/network)\n.", "To modify a response use\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nto get the original response and then pass the response to\nroute.fulfill() (https://playwright.dev/docs/api/class-route#route-fulfill)\n. You can override individual fields on the response via options:\n\n```\n`awaitpage.route('**/title.html',asyncroute=&gt;{// Fetch original response.constresponse=awaitroute.fetch();// Add a prefix to the title.letbody=awaitresponse.text();body=body.replace('&lt;title&gt;','&lt;title&gt;My prefix:');awaitroute.fulfill({// Pass all fields from the response.response,// Override response body.body,// Force content type to be html.headers:{...response.headers(),'content-type':'text/html'}});});`\n```", "Added in: v1.29\n\nroute.fetch\n\nPerforms the request and fetches result without fulfilling it, so that the response could be modified and then fulfilled.\n\nUsage\n\n```\n`awaitpage.route('https://dog.ceo/api/breeds/list/all',asyncroute=&gt;{constresponse=awaitroute.fetch();constjson=awaitresponse.json();json.message['big_red_dog']=[];awaitroute.fulfill({response,json});});`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`headers`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n,\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-headers)\nIf set changes the request HTTP headers. Header values will be converted to a string.\n`maxRedirects`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.31\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-max-redirects)\nMaximum number of request redirects that will be followed automatically. An error will be thrown if the number is exceeded. Defaults to\n`20`\n. Pass\n`0`\nto not follow redirects.\n`maxRetries`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.46\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-max-retries)\nMaximum number of times network errors should be retried. Currently only\n`ECONNRESET`\nerror is retried. Does not retry based on HTTP response codes. An error will be thrown if the limit is exceeded. Defaults to\n`0`\n- no retries.\n`method`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-method)\nIf set changes the request method (e.g. GET or POST).\n`postData`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\n|\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-post-data)\nAllows to set post data of the request. If the data parameter is an object, it will be serialized to json string and\n`content-type`\nheader will be set to\n`application/json`\nif not explicitly set. Otherwise the\n`content-type`\nheader will be set to\n`application/octet-stream`\nif not explicitly set.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.33\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-timeout)\nRequest timeout in milliseconds. Defaults to\n`30000`\n(30 seconds). Pass\n`0`\nto disable timeout.\n`url`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-url)\nIf set changes the request URL. New URL must have same protocol as original one.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nAPIResponse (https://playwright.dev/docs/api/class-apiresponse)\n&gt;\n# (https://playwright.dev/docs/api/class-route#route-fetch-return)\n\nDetails\n\nNote that\nheaders (https://playwright.dev/docs/api/class-route#route-fetch-option-headers)\noption will apply to the fetched request as well as any redirects initiated by it. If you want to only apply\nheaders (https://playwright.dev/docs/api/class-route#route-fetch-option-headers)\nto the original request, but not to redirects, look into\nroute.continue() (https://playwright.dev/docs/api/class-route#route-continue)\ninstead.", 'Network | Playwright', "```\n`awaitpage.route('**/api/fetch_data',route=&gt;route.fulfill({status:200,body:testData,}));awaitpage.goto('https://example.com');`\n```\n\nYou can mock API endpoints via handling the network requests in your Playwright script."]</t>
+          <t>["Sometimes, it is essential to make an API request, but the response needs to be patched to allow for reproducible testing. In that case, instead of mocking the request, one can perform the request and fulfill it with the modified response.\n\nIn the example below we intercept the call to the fruit API and add a new fruit called 'Loquat', to the data. We then go to the url and assert that this data is there:\n\n```\n`test('gets the json from api and adds a new fruit',async({page})=&gt;{// Get the response and add to itawaitpage.route('*/**/api/v1/fruits',asyncroute=&gt;{constresponse=awaitroute.fetch();constjson=awaitresponse.json();json.push({name:'Loquat',id:100});// Fulfill using the original response, while patching the response body// with the given JSON object.awaitroute.fulfill({response,json});});// Go to the pageawaitpage.goto('https://demo.playwright.dev/api-mocking');// Assert that the new fruit is visibleawaitexpect(page.getByText('Loquat',{exact:true})).toBeVisible();});`\n```\n\nIn the trace of our test we can see that the API was called and the response was modified.\n\nBy inspecting the response we can see that our new fruit was added to the list.\n\nRead more about\nadvanced networking (https://playwright.dev/docs/network)\n.", "Added in: v1.29\n\nroute.fetch\n\nPerforms the request and fetches result without fulfilling it, so that the response could be modified and then fulfilled.\n\nUsage\n\n```\n`awaitpage.route('https://dog.ceo/api/breeds/list/all',asyncroute=&gt;{constresponse=awaitroute.fetch();constjson=awaitresponse.json();json.message['big_red_dog']=[];awaitroute.fulfill({response,json});});`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`headers`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n,\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-headers)\nIf set changes the request HTTP headers. Header values will be converted to a string.\n`maxRedirects`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.31\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-max-redirects)\nMaximum number of request redirects that will be followed automatically. An error will be thrown if the number is exceeded. Defaults to\n`20`\n. Pass\n`0`\nto not follow redirects.\n`maxRetries`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.46\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-max-retries)\nMaximum number of times network errors should be retried. Currently only\n`ECONNRESET`\nerror is retried. Does not retry based on HTTP response codes. An error will be thrown if the limit is exceeded. Defaults to\n`0`\n- no retries.\n`method`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-method)\nIf set changes the request method (e.g. GET or POST).\n`postData`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\n|\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-post-data)\nAllows to set post data of the request. If the data parameter is an object, it will be serialized to json string and\n`content-type`\nheader will be set to\n`application/json`\nif not explicitly set. Otherwise the\n`content-type`\nheader will be set to\n`application/octet-stream`\nif not explicitly set.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.33\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-timeout)\nRequest timeout in milliseconds. Defaults to\n`30000`\n(30 seconds). Pass\n`0`\nto disable timeout.\n`url`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fetch-option-url)\nIf set changes the request URL. New URL must have same protocol as original one.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nAPIResponse (https://playwright.dev/docs/api/class-apiresponse)\n&gt;\n# (https://playwright.dev/docs/api/class-route#route-fetch-return)\n\nDetails\n\nNote that\nheaders (https://playwright.dev/docs/api/class-route#route-fetch-option-headers)\noption will apply to the fetched request as well as any redirects initiated by it. If you want to only apply\nheaders (https://playwright.dev/docs/api/class-route#route-fetch-option-headers)\nto the original request, but not to redirects, look into\nroute.continue() (https://playwright.dev/docs/api/class-route#route-continue)\ninstead.", "Added before v1.9\n\npage.route\n\nRouting provides the capability to modify network requests that are made by a page.\n\nOnce routing is enabled, every request matching the url pattern will stall unless it's continued, fulfilled or aborted.\n\nnote\nThe handler will only be called for the first url if the response is a redirect.\n\nnote\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nwill not intercept requests intercepted by Service Worker. See\nthis (https://github.com/microsoft/playwright/issues/1090)\nissue. We recommend disabling Service Workers when using request interception by setting\nserviceWorkers (https://playwright.dev/docs/api/class-browser#browser-new-context-option-service-workers)\nto\n`'block'`\n.\n\nnote\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nwill not intercept the first request of a popup page. Use\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\ninstead.\n\nUsage\n\nAn example of a naive handler that aborts all image requests:\n\n```\n`constpage=awaitbrowser.newPage();awaitpage.route('**/*.{png,jpg,jpeg}',route=&gt;route.abort());awaitpage.goto('https://example.com');awaitbrowser.close();`\n```\n\nor the same snippet using a regex pattern instead:\n\n```\n`constpage=awaitbrowser.newPage();awaitpage.route(/(\\.png$)|(\\.jpg$)/,route=&gt;route.abort());awaitpage.goto('https://example.com');awaitbrowser.close();`\n```\n\nIt is possible to examine the request to decide the route action. For example, mocking all requests that contain some post data, and leaving all other requests as is:\n\n```\n`awaitpage.route('/api/**',asyncroute=&gt;{if(route.request().postData().includes('my-string'))awaitroute.fulfill({body:'mocked-data'});elseawaitroute.continue();});`\n```\n\nIf a request matches multiple registered routes, the most recently registered route takes precedence.\n\nPage routes take precedence over browser context routes (set up with\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n) when request matches both handlers.\n\nTo remove a route with its handler you can use\npage.unroute() (https://playwright.dev/docs/api/class-page#page-unroute)\n.\n\nnote\nEnabling routing disables http cache.\n\nArguments\n\n`url`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n|\nURLPattern (https://developer.mozilla.org/en-US/docs/Web/API/URLPattern)\n|\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n(\nURL (https://nodejs.org/api/url.html)\n):\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n# (https://playwright.dev/docs/api/class-page#page-route-option-url)\nA glob pattern, regex pattern, URL pattern, or predicate that receives a\nURL (https://nodejs.org/api/url.html)\nto match during routing. If\nbaseURL (https://playwright.dev/docs/api/class-browser#browser-new-context-option-base-url)\nis set in the context options and the provided URL is a string that does not start with\n`*`\n, it is resolved using the\nnew URL() (https://developer.mozilla.org/en-US/docs/Web/API/URL/URL)\nconstructor.\n`handler`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n(\nRoute (https://playwright.dev/docs/api/class-route)\n,\nRequest (https://playwright.dev/docs/api/class-request)\n):\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt; |\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n# (https://playwright.dev/docs/api/class-page#page-route-option-handler)\nhandler function to route the request.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`times`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.15\n# (https://playwright.dev/docs/api/class-page#page-route-option-times)\nHow often a route should be used. By default it will be used every time.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nDisposable (https://playwright.dev/docs/api/class-disposable)\n&gt;\n# (https://playwright.dev/docs/api/class-page#page-route-return)", "Added before v1.9\n\nbrowserContext.route\n\nRouting provides the capability to modify network requests that are made by any page in the browser context. Once route is enabled, every request matching the url pattern will stall unless it's continued, fulfilled or aborted.\n\nnote\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nwill not intercept requests intercepted by Service Worker. See\nthis (https://github.com/microsoft/playwright/issues/1090)\nissue. We recommend disabling Service Workers when using request interception by setting\nserviceWorkers (https://playwright.dev/docs/api/class-browser#browser-new-context-option-service-workers)\nto\n`'block'`\n.\n\nUsage\n\nAn example of a naive handler that aborts all image requests:\n\n```\n`constcontext=awaitbrowser.newContext();awaitcontext.route('**/*.{png,jpg,jpeg}',route=&gt;route.abort());constpage=awaitcontext.newPage();awaitpage.goto('https://example.com');awaitbrowser.close();`\n```\n\nor the same snippet using a regex pattern instead:\n\n```\n`constcontext=awaitbrowser.newContext();awaitcontext.route(/(\\.png$)|(\\.jpg$)/,route=&gt;route.abort());constpage=awaitcontext.newPage();awaitpage.goto('https://example.com');awaitbrowser.close();`\n```\n\nIt is possible to examine the request to decide the route action. For example, mocking all requests that contain some post data, and leaving all other requests as is:\n\n```\n`awaitcontext.route('/api/**',asyncroute=&gt;{if(route.request().postData().includes('my-string'))awaitroute.fulfill({body:'mocked-data'});elseawaitroute.continue();});`\n```\n\nPage routes (set up with\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n) take precedence over browser context routes when request matches both handlers.\n\nTo remove a route with its handler you can use\nbrowserContext.unroute() (https://playwright.dev/docs/api/class-browsercontext#browser-context-unroute)\n.\n\nnote\nEnabling routing disables http cache.\n\nArguments\n\n`url`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n| [URLPattern] |\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n(\nURL (https://nodejs.org/api/url.html)\n):\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-route-option-url)\nA glob pattern, regex pattern, URL pattern, or predicate that receives a\nURL (https://nodejs.org/api/url.html)\nto match during routing. If\nbaseURL (https://playwright.dev/docs/api/class-browser#browser-new-context-option-base-url)\nis set in the context options and the provided URL is a string that does not start with\n`*`\n, it is resolved using the\nnew URL() (https://developer.mozilla.org/en-US/docs/Web/API/URL/URL)\nconstructor.\n`handler`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n(\nRoute (https://playwright.dev/docs/api/class-route)\n,\nRequest (https://playwright.dev/docs/api/class-request)\n):\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt; |\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-route-option-handler)\nhandler function to route the request.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`times`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.15\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-route-option-times)\nHow often a route should be used. By default it will be used every time.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nDisposable (https://playwright.dev/docs/api/class-disposable)\n&gt;\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-route-return)", 'The following code will intercept all the calls to\n`*/**/api/v1/fruits`\nand will return a custom response instead. No requests to the API will be made. The test goes to the URL that uses the mocked route and asserts that mock data is present on the page.\n\n```\n`test("mocks a fruit and doesn\'t call api",async({page})=&gt;{// Mock the api call before navigatingawaitpage.route(\'*/**/api/v1/fruits\',asyncroute=&gt;{constjson=[{name:\'Strawberry\',id:21}];awaitroute.fulfill({json});});// Go to the pageawaitpage.goto(\'https://demo.playwright.dev/api-mocking\');// Assert that the Strawberry fruit is visibleawaitexpect(page.getByText(\'Strawberry\')).toBeVisible();});`\n```\n\nYou can see from the trace of the example test that the API was never called, it was however fulfilled with the mock data.\n\nRead more about\nadvanced networking (https://playwright.dev/docs/network)\n.', 'Added before v1.9\n\nroute.continue\n\nSends route\'s request to the network with optional overrides.\n\nUsage\n\n```\n`awaitpage.route(\'**/*\',async(route,request)=&gt;{// Override headersconstheaders={...request.headers(),foo:\'foo-value\',// set "foo" headerbar:undefined,// remove "bar" header};awaitroute.continue({headers});});`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`headers`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n,\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-continue-option-headers)\nIf set changes the request HTTP headers. Header values will be converted to a string.\n`method`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-continue-option-method)\nIf set changes the request method (e.g. GET or POST).\n`postData`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\n|\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-continue-option-post-data)\nIf set changes the post data of request.\n`url`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-continue-option-url)\nIf set changes the request URL. New URL must have same protocol as original one.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-route#route-continue-return)\n\nDetails\n\nThe\nheaders (https://playwright.dev/docs/api/class-route#route-continue-option-headers)\noption applies to both the routed request and any redirects it initiates. However,\nurl (https://playwright.dev/docs/api/class-route#route-continue-option-url)\n,\nmethod (https://playwright.dev/docs/api/class-route#route-continue-option-method)\n, and\npostData (https://playwright.dev/docs/api/class-route#route-continue-option-post-data)\nonly apply to the original request and are not carried over to redirected requests.\n\nroute.continue() (https://playwright.dev/docs/api/class-route#route-continue)\nwill immediately send the request to the network, other matching handlers won\'t be invoked. Use\nroute.fallback() (https://playwright.dev/docs/api/class-route#route-fallback)\nIf you want next matching handler in the chain to be invoked.\n\nwarning\nSome request headers are\nforbidden\nand cannot be overridden (for example,\n`Cookie`\n,\n`Host`\n,\n`Content-Length`\nand others, see\nthis MDN page (https://developer.mozilla.org/en-US/docs/Glossary/Forbidden_request_header)\nfor full list). If an override is provided for a forbidden header, it will be ignored and the original request header will be used.\nTo set custom cookies, use\nbrowserContext.addCookies() (https://playwright.dev/docs/api/class-browsercontext#browser-context-add-cookies)\n.', 'Added in: v1.23\n\nroute.fallback\n\nContinues route\'s request with optional overrides. The method is similar to\nroute.continue() (https://playwright.dev/docs/api/class-route#route-continue)\nwith the difference that other matching handlers will be invoked before sending the request.\n\nUsage\n\nWhen several routes match the given pattern, they run in the order opposite to their registration. That way the last registered route can always override all the previous ones. In the example below, request will be handled by the bottom-most handler first, then it\'ll fall back to the previous one and in the end will be aborted by the first registered route.\n\n```\n`awaitpage.route(\'**/*\',asyncroute=&gt;{// Runs last.awaitroute.abort();});awaitpage.route(\'**/*\',asyncroute=&gt;{// Runs second.awaitroute.fallback();});awaitpage.route(\'**/*\',asyncroute=&gt;{// Runs first.awaitroute.fallback();});`\n```\n\nRegistering multiple routes is useful when you want separate handlers to handle different kinds of requests, for example API calls vs page resources or GET requests vs POST requests as in the example below.\n\n```\n`// Handle GET requests.awaitpage.route(\'**/*\',asyncroute=&gt;{if(route.request().method()!==\'GET\'){awaitroute.fallback();return;}// Handling GET only.// ...});// Handle POST requests.awaitpage.route(\'**/*\',asyncroute=&gt;{if(route.request().method()!==\'POST\'){awaitroute.fallback();return;}// Handling POST only.// ...});`\n```\n\nOne can also modify request while falling back to the subsequent handler, that way intermediate route handler can modify url, method, headers and postData of the request.\n\n```\n`awaitpage.route(\'**/*\',async(route,request)=&gt;{// Override headersconstheaders={...request.headers(),foo:\'foo-value\',// set "foo" headerbar:undefined,// remove "bar" header};awaitroute.fallback({headers});});`\n```\n\nUse\nroute.continue() (https://playwright.dev/docs/api/class-route#route-continue)\nto immediately send the request to the network, other matching handlers won\'t be invoked in that case.\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`headers`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n,\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fallback-option-headers)\nIf set changes the request HTTP headers. Header values will be converted to a string.\n`method`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fallback-option-method)\nIf set changes the request method (e.g. GET or POST).\n`postData`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\n|\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fallback-option-post-data)\nIf set changes the post data of request.\n`url`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-route#route-fallback-option-url)\nIf set changes the request URL. New URL must have same protocol as original one. Changing the URL won\'t affect the route matching, all the routes are matched using the original request URL.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-route#route-fallback-return)']</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,30 +2669,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Yes, the same interception mechanism (`page.route()`) can be used for both fully stubbed tests and tests that exercise the real endpoint with modifications.
-### How they differ:
-*   **For fully stubbed tests:** You use `route.fulfill()` to provide a static response body without performing a network request.
-    *   **Example:**
-        ```javascript
-        await page.route('**/api/fetch_data', route =&gt; route.fulfill({
-          status: 200,
-          body: testData,
-        }));
-        ```
-*   **For tests exercising the real endpoint with modifications:** You use `route.fetch()` to perform the actual network request, modify the resulting data, and then use `route.fulfill()` to return the patched response.
-    *   **Example:**
-        ```javascript
-        await page.route('*/**/api/v1/fruits', async route =&gt; {
-          // 1. Perform the real request
-          const response = await route.fetch();
-          const json = await response.json();
-          // 2. Modify the specific field
-          json.someFlag = true; 
-          // 3. Fulfill with the original response and the modified JSON
-          await route.fulfill({ response, json });
-        });
-        ```
-In the second approach, `route.fetch()` allows you to get the original response from the backend, which ensures your test fails if the backend renames a field or changes the structure, while still allowing you to override specific flags as needed.</t>
+          <t>Yes, the same interception mechanism (`page.route` or `browserContext.route`) can be used for both fully stubbed tests and tests that exercise the real endpoint with modifications.
+### How to handle both approaches
+*   **For fully stubbed tests:** Use `route.fulfill` with a custom JSON object. This prevents any request from being made to the actual API.
+    ```javascript
+    await page.route('*/**/api/v1/fruits', async route =&gt; {
+      const json = [{ name: 'Strawberry', id: 21 }];
+      await route.fulfill({ json });
+    });
+    ```
+*   **For tests exercising the real endpoint with modifications:** Use `route.fetch` to perform the actual request, then use `route.fulfill` to return the response with your modifications applied to the body.
+    ```javascript
+    await page.route('*/**/api/v1/fruits', async route =&gt; {
+      const response = await route.fetch();
+      const json = await response.json();
+      // Modify the specific flag/field
+      json.someFlag = true; 
+      // Fulfill using the original response and the patched JSON
+      await route.fulfill({ response, json });
+    });
+    ```
+### What changes between them
+The primary difference is the inclusion of `route.fetch()` in the handler for the tests that exercise the real endpoint. 
+1.  **Stubbed tests:** You define the response data entirely within the handler and call `route.fulfill` immediately. No network request is made to the backend.
+2.  **Real endpoint tests:** You must call `await route.fetch()` first to retrieve the actual response from the backend. You then parse that response (e.g., `await response.json()`), modify the desired data, and pass both the original `response` object and your updated `json` to `route.fulfill`.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2678,31 +2701,31 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0.01008125</v>
+        <v>0.00239275</v>
       </c>
       <c r="G35" t="n">
-        <v>37140</v>
+        <v>58574</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="J35" t="n">
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.1942148760330578</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2456140350877193</v>
+        <v>0.2748538011695906</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7099999999858</v>
+        <v>0.99999999995</v>
       </c>
       <c r="N35" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="36">
@@ -2713,7 +2736,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>['Playwright uses browser contexts to achieve Test Isolation. Each test has its own Browser Context. Running the test creates a new browser context each time.  When using Playwright as a Test Runner, browser contexts are created by default. Otherwise, you can create browser contexts manually.\n\nTest\nLibrary\n```\n`import{test}from\'@playwright/test\';test(\'example test\',async({page,context})=&gt;{// "context" is an isolated BrowserContext, created for this specific test.// "page" belongs to this context.});test(\'another test\',async({page,context})=&gt;{// "context" and "page" in this second test are completely// isolated from the first test.});`\n```\n```\n`constbrowser=awaitchromium.launch();constcontext=awaitbrowser.newContext();constpage=awaitcontext.newPage();`\n```\n\nBrowser contexts can also be used to emulate multi-page scenarios involving mobile devices, permissions, locale and color scheme. Check out our\nEmulation (https://playwright.dev/docs/emulation)\nguide for more details.', 'Emulation | Playwright', 'Isolation | Playwright', 'Playwright comes with a\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nusing\nplaywright.devices (https://playwright.dev/docs/api/class-playwright#playwright-devices)\nfor selected desktop, tablet and mobile devices. It can be used to simulate browser behavior for a specific device such as user agent, screen size, viewport and if it has touch enabled. All tests will run with the specified device parameters.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig,devices}from\'@playwright/test\';// import devicesexportdefaultdefineConfig({projects:[{name:\'chromium\',use:{...devices[\'Desktop Chrome\'],},},{name:\'Mobile Safari\',use:{...devices[\'iPhone 13\'],},},],});`\n```\n```\n`const{chromium,devices}=require(\'playwright\');constbrowser=awaitchromium.launch();constiphone13=devices[\'iPhone 13\'];constcontext=awaitbrowser.newContext({...iphone13,});`\n```\n\nNote\n: Pre-configured devices assume a specific platform. For example, "Desktop Chrome" will provide a Windows-specific user agent string.\n\nIf you would like to use the user agent specific to the platform that is running the tests, we recommend unsetting the user agent property.\n\n```\n`constcontext=awaitbrowser.newContext({...devices[\'Desktop Chrome\'],userAgent:undefined,});`\n```', 'Test Isolation is when each test is completely isolated from another test. Every test runs independently from any other test. This means that each test has its own local storage, session storage, cookies etc. Playwright achieves this using\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\ns which are equivalent to incognito-like profiles. They are fast and cheap to create and are completely isolated, even when running in a single browser. Playwright creates a context for each test, and provides a default\nPage (https://playwright.dev/docs/api/class-page)\nin that context.', "You can configure Playwright globally, per project, or per test. For example, you can set the locale to be used globally by adding\n`locale`\nto the\n`use`\noption of the Playwright config, and then override it for a specific project using the\n`project`\noption in the config. You can also override it for a specific test by adding\n`test.use({})`\nin the test file and passing in the options.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{locale:'en-GB'},});`\n```\n\nYou can override options for a specific project using the\n`project`\noption in the Playwright config.\n\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[{name:'chromium',use:{...devices['Desktop Chrome'],locale:'de-DE',},},],});`\n```\n\nYou can override options for a specific test file by using the\n`test.use()`\nmethod and passing in the options. For example to run tests with the French locale for a specific test:\n\n```\n`import{test,expect}from'@playwright/test';test.use({locale:'fr-FR'});test('example',async({page})=&gt;{// ...});`\n```\n\nThe same works inside a describe block. For example to run tests in a describe block with the French locale:\n\n```\n`import{test,expect}from'@playwright/test';test.describe('french language block',()=&gt;{test.use({locale:'fr-FR'});test('example',async({page})=&gt;{// ...});});`\n```", "If using the built-in\n`browser`\nfixture, calling\nbrowser.newContext() (https://playwright.dev/docs/api/class-browser#browser-new-context)\nwill create a context with options inherited from the config:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{userAgent:'some custom ua',viewport:{width:100,height:100},},});`\n```\n\nAn example test illustrating the initial context options are set:\n\n```\n`test('should inherit use options on context when using built-in browser fixture',async({browser,})=&gt;{constcontext=awaitbrowser.newContext();constpage=awaitcontext.newPage();expect(awaitpage.evaluate(()=&gt;navigator.userAgent)).toBe('some custom ua');expect(awaitpage.evaluate(()=&gt;window.innerWidth)).toBe(100);awaitcontext.close();});`\n```"]</t>
+          <t>['Playwright uses browser contexts to achieve Test Isolation. Each test has its own Browser Context. Running the test creates a new browser context each time.  When using Playwright as a Test Runner, browser contexts are created by default. Otherwise, you can create browser contexts manually.\n\nTest\nLibrary\n```\n`import{test}from\'@playwright/test\';test(\'example test\',async({page,context})=&gt;{// "context" is an isolated BrowserContext, created for this specific test.// "page" belongs to this context.});test(\'another test\',async({page,context})=&gt;{// "context" and "page" in this second test are completely// isolated from the first test.});`\n```\n```\n`constbrowser=awaitchromium.launch();constcontext=awaitbrowser.newContext();constpage=awaitcontext.newPage();`\n```\n\nBrowser contexts can also be used to emulate multi-page scenarios involving mobile devices, permissions, locale and color scheme. Check out our\nEmulation (https://playwright.dev/docs/emulation)\nguide for more details.', 'Playwright comes with a\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nusing\nplaywright.devices (https://playwright.dev/docs/api/class-playwright#playwright-devices)\nfor selected desktop, tablet and mobile devices. It can be used to simulate browser behavior for a specific device such as user agent, screen size, viewport and if it has touch enabled. All tests will run with the specified device parameters.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig,devices}from\'@playwright/test\';// import devicesexportdefaultdefineConfig({projects:[{name:\'chromium\',use:{...devices[\'Desktop Chrome\'],},},{name:\'Mobile Safari\',use:{...devices[\'iPhone 13\'],},},],});`\n```\n```\n`const{chromium,devices}=require(\'playwright\');constbrowser=awaitchromium.launch();constiphone13=devices[\'iPhone 13\'];constcontext=awaitbrowser.newContext({...iphone13,});`\n```\n\nNote\n: Pre-configured devices assume a specific platform. For example, "Desktop Chrome" will provide a Windows-specific user agent string.\n\nIf you would like to use the user agent specific to the platform that is running the tests, we recommend unsetting the user agent property.\n\n```\n`constcontext=awaitbrowser.newContext({...devices[\'Desktop Chrome\'],userAgent:undefined,});`\n```', 'Test Isolation is when each test is completely isolated from another test. Every test runs independently from any other test. This means that each test has its own local storage, session storage, cookies etc. Playwright achieves this using\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\ns which are equivalent to incognito-like profiles. They are fast and cheap to create and are completely isolated, even when running in a single browser. Playwright creates a context for each test, and provides a default\nPage (https://playwright.dev/docs/api/class-page)\nin that context.', "Whether the meta viewport tag is taken into account and touch events are enabled.\n\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[{name:'chromium',use:{...devices['Desktop Chrome'],// It is important to define the `isMobile` property after destructuring `devices`,// since devices also define the `isMobile` for that device.isMobile:false,},},]});`\n```", "The User Agent is included in the device and therefore you  will rarely need to change it however if you do need to test a different user agent you can override it with the\n`userAgent`\nproperty.\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test,expect}from'@playwright/test';test.use({userAgent:'My user agent'});test('my user agent test',async({page})=&gt;{// ...});`\n```\n```\n`constcontext=awaitbrowser.newContext({userAgent:'My user agent'});`\n```", "The viewport is included in the device but you can override it for some tests with\npage.setViewportSize() (https://playwright.dev/docs/api/class-page#page-set-viewport-size)\n.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[{name:'chromium',use:{...devices['Desktop Chrome'],// It is important to define the `viewport` property after destructuring `devices`,// since devices also define the `viewport` for that device.viewport:{width:1280,height:720},},},]});`\n```\n```\n`// Create context with given viewportconstcontext=awaitbrowser.newContext({viewport:{width:1280,height:1024}});`\n```\n\nTest file:\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test,expect}from'@playwright/test';test.use({viewport:{width:1600,height:1200},});test('my test',async({page})=&gt;{// ...});`\n```\n```\n`// Create context with given viewportconstcontext=awaitbrowser.newContext({viewport:{width:1280,height:1024}});// Resize viewport for individual pageawaitpage.setViewportSize({width:1600,height:1200});// Emulate high-DPIconstcontext=awaitbrowser.newContext({viewport:{width:2560,height:1440},deviceScaleFactor:2,});`\n```\n\nThe same works inside a test file.\n\nTest\nLibrary\ntests/example.spec.ts\n```\n`import{test,expect}from'@playwright/test';test.describe('specific viewport block',()=&gt;{test.use({viewport:{width:1600,height:1200}});test('my test',async({page})=&gt;{// ...});});`\n```\n```\n`// Create context with given viewportconstcontext=awaitbrowser.newContext({viewport:{width:1600,height:1200}});constpage=awaitcontext.newPage();`\n```", 'With Playwright you can test your app on any browser as well as emulate a real device such as a mobile phone or tablet. Simply configure the devices you would like to emulate and Playwright will simulate the browser behavior such as\n`"userAgent"`\n,\n`"screenSize"`\n,\n`"viewport"`\nand if it\n`"hasTouch"`\nenabled. You can also emulate the\n`"geolocation"`\n,\n`"locale"`\nand\n`"timezone"`\nfor all tests or for a specific test as well as set the\n`"permissions"`\nto show notifications or change the\n`"colorScheme"`\n.']</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2723,12 +2746,8 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Device emulation (viewport, user agent, and touch) is applied by passing device parameters—such as those found in the `playwright.devices` registry—into the `use` configuration option. This can be done at three levels:
-*   **Globally or per project:** By defining the `use` property within the `projects` array in `playwright.config.ts`.
-*   **Per test file or describe block:** By using the `test.use({})` method.
-*   **Manually:** When using the library directly, you can pass device parameters into `browser.newContext({...deviceParameters})`.
-**Why it does not bleed into other tests:**
-Playwright achieves test isolation by creating a new `BrowserContext` for every test. Because each test runs in its own isolated `BrowserContext` (which acts like an incognito-like profile), any emulation settings applied to one context do not affect others. When using the Playwright test runner, these contexts are created automatically for each test, ensuring that every test runs independently with its own specific configuration.</t>
+          <t>Device emulation is applied by configuring device parameters (such as viewport, user agent, and touch) either globally in `playwright.config.ts` using the `use` property within projects, or for specific tests/blocks using `test.use()` or `test.describe()` with `test.use()`. When using the library directly, these parameters are passed to `browser.newContext()`. Additionally, individual page viewports can be overridden using `page.setViewportSize()`.
+Emulation does not bleed into other tests because Playwright achieves test isolation by creating a new, independent `BrowserContext` for every test. Each `BrowserContext` acts as an incognito-like profile that is completely isolated from others, possessing its own local storage, session storage, and cookies. Because the emulation settings are applied to these isolated contexts, they do not affect other tests.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2737,28 +2756,28 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.009759</v>
+        <v>0.00082275</v>
       </c>
       <c r="G36" t="n">
-        <v>35366</v>
+        <v>34684</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="J36" t="n">
         <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1219512195121951</v>
       </c>
       <c r="L36" t="n">
-        <v>0.4651162790697674</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8041666666465626</v>
+        <v>0.9999999999666667</v>
       </c>
       <c r="N36" t="n">
         <v>1</v>
@@ -2772,7 +2791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>["Fixture is considered to be a part of a test, and so its setup and teardown running time counts towards the test timeout. Therefore, a slow fixture may cause test timeouts. You can set a separate larger timeout for such a fixture, and keep the overall test timeout small.\n\n```\n`import{testasbase,expect}from'@playwright/test';consttest=base.extend&lt;{slowFixture:string}&gt;({slowFixture:[async({},use)=&gt;{// ... perform a slow operation ...awaituse('hello');},{timeout:60000}]});test('example test',async({slowFixture})=&gt;{// ...});`\n```\n\nUnlike regular test-scoped fixtures, each\nworker-scoped (https://playwright.dev/docs/test-fixtures#worker-scoped-fixtures)\nfixture has its own timeout, equal to the test timeout. You can change the timeout for a worker-scoped fixture in the same way.", 'Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', 'Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and\n`beforeEach`\nhooks is included in the test timeout.\n\nTimed out test produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Timeout of 30000ms exceeded.`\n```\n\nAdditional separate timeout, of the same value, is shared between fixture teardowns and\n`afterEach`\nhooks, after the test function has finished.\n\nThe same timeout value also applies to\n`beforeAll`\nand\n`afterAll`\nhooks, but they do not share time with any test.', "example.spec.ts\n```\n`import{test,expect}from'@playwright/test';test.beforeEach(async({page},testInfo)=&gt;{// Extend timeout for all tests running this hook by 30 seconds.testInfo.setTimeout(testInfo.timeout+30_000);});`\n```\n\nAPI reference:\ntestInfo.setTimeout() (https://playwright.dev/docs/api/class-testinfo#test-info-set-timeout)\n.", "TestInfo | Playwright\n\n`TestInfo`\ncontains information about currently running test. It is available to test functions,\ntest.beforeEach() (https://playwright.dev/docs/api/class-test#test-before-each)\n,\ntest.afterEach() (https://playwright.dev/docs/api/class-test#test-after-each)\n,\ntest.beforeAll() (https://playwright.dev/docs/api/class-test#test-before-all)\nand\ntest.afterAll() (https://playwright.dev/docs/api/class-test#test-after-all)\nhooks, and test-scoped fixtures.\n`TestInfo`\nprovides utilities to control test execution: attach files, update test timeout, determine which test is currently running and whether it was retried, etc.\n\n```\n`import{test,expect}from'@playwright/test';test('basic test',async({page},testInfo)=&gt;{expect(testInfo.title).toBe('basic test');awaitpage.screenshot(testInfo.outputPath('screenshot.png'));});`\n```", "`beforeAll`\nand\n`afterAll`\nhooks have a separate timeout, by default equal to test timeout. You can change it separately for each hook by calling\ntestInfo.setTimeout() (https://playwright.dev/docs/api/class-testinfo#test-info-set-timeout)\ninside the hook.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test.beforeAll(async()=&gt;{// Set timeout for this hook.test.setTimeout(60000);});`\n```\n\nAPI reference:\ntestInfo.setTimeout() (https://playwright.dev/docs/api/class-testinfo#test-info-set-timeout)\n."]</t>
+          <t>["By default,\nfixture (https://playwright.dev/docs/test-fixtures)\nshares timeout with the test. However, for slow fixtures, especially\nworker-scoped (https://playwright.dev/docs/test-fixtures#worker-scoped-fixtures)\nones, it is convenient to have a separate timeout. This way you can keep the overall test timeout small, and give the slow fixture more time.\n\nexample.spec.ts\n```\n`import{testasbase,expect}from'@playwright/test';consttest=base.extend&lt;{slowFixture:string}&gt;({slowFixture:[async({},use)=&gt;{// ... perform a slow operation ...awaituse('hello');},{timeout:60_000}]});test('example test',async({slowFixture})=&gt;{// ...});`\n```\n\nAPI reference:\ntest.extend() (https://playwright.dev/docs/api/class-test#test-extend)\n.", "Fixture is considered to be a part of a test, and so its setup and teardown running time counts towards the test timeout. Therefore, a slow fixture may cause test timeouts. You can set a separate larger timeout for such a fixture, and keep the overall test timeout small.\n\n```\n`import{testasbase,expect}from'@playwright/test';consttest=base.extend&lt;{slowFixture:string}&gt;({slowFixture:[async({},use)=&gt;{// ... perform a slow operation ...awaituse('hello');},{timeout:60000}]});test('example test',async({slowFixture})=&gt;{// ...});`\n```\n\nUnlike regular test-scoped fixtures, each\nworker-scoped (https://playwright.dev/docs/test-fixtures#worker-scoped-fixtures)\nfixture has its own timeout, equal to the test timeout. You can change the timeout for a worker-scoped fixture in the same way.", 'Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and\n`beforeEach`\nhooks is included in the test timeout.\n\nTimed out test produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Timeout of 30000ms exceeded.`\n```\n\nAdditional separate timeout, of the same value, is shared between fixture teardowns and\n`afterEach`\nhooks, after the test function has finished.\n\nThe same timeout value also applies to\n`beforeAll`\nand\n`afterAll`\nhooks, but they do not share time with any test.', "Added in: v1.10\n\ntestInfo.setTimeout\n\nChanges the timeout for the currently running test. Zero means no timeout. Learn more about\nvarious timeouts (https://playwright.dev/docs/test-timeouts)\n.\n\nTimeout is usually specified in the\nconfiguration file (https://playwright.dev/docs/test-configuration)\n, but it could be useful to change the timeout in certain scenarios:\n\n```\n`import{test,expect}from'@playwright/test';test.beforeEach(async({page},testInfo)=&gt;{// Extend timeout for all tests running this hook by 30 seconds.testInfo.setTimeout(testInfo.timeout+30000);});`\n```\n\nUsage\n\n```\n`testInfo.setTimeout(timeout);`\n```\n\nArguments\n\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n# (https://playwright.dev/docs/api/class-testinfo#test-info-set-timeout-option-timeout)\nTimeout in milliseconds.", "Playwright Test uses\nworker processes (https://playwright.dev/docs/test-parallel)\nto run test files. Similar to how test fixtures are set up for individual test runs, worker fixtures are set up for each worker process. That's where you can set up services, run servers, etc. Playwright Test will reuse the worker process for as many test files as it can, provided their worker fixtures match and hence environments are identical.\n\nBelow we'll create an\n`account`\nfixture that will be shared by all tests in the same worker, and override the\n`page`\nfixture to log in to this account for each test. To generate unique accounts, we'll use the\nworkerInfo.workerIndex (https://playwright.dev/docs/api/class-workerinfo#worker-info-worker-index)\nthat is available to any test or fixture. Note the tuple-like syntax for the worker fixture - we have to pass\n`{scope: 'worker'}`\nso that test runner sets this fixture up once per worker.\n\nIn addition to only being run once per worker, worker-scoped fixtures also get a separate timeout equal to the default test timeout. You can change it by passing the\n`timeout`\noption. See\nfixture timeout (https://playwright.dev/docs/test-fixtures#fixture-timeout)\nfor more details.\n\nmy-test.ts\n```\n`import{testasbase}from'@playwright/test';typeAccount={username:string;password:string;};// Note that we pass worker fixture types as a second template parameter.exportconsttest=base.extend&lt;{},{account:Account}&gt;({account:[async({browser},use,workerInfo)=&gt;{// Unique username.constusername='user'+workerInfo.workerIndex;constpassword='verysecure';// Create the account with Playwright.constpage=awaitbrowser.newPage();awaitpage.goto('/signup');awaitpage.getByLabel('User Name').fill(username);awaitpage.getByLabel('Password').fill(password);awaitpage.getByText('Sign up').click();// Make sure everything is ok.awaitexpect(page.getByTestId('result')).toHaveText('Success');// Do not forget to cleanup.awaitpage.close();// Use the account value.awaituse({username,password});},{scope:'worker'}],page:async({page,account},use)=&gt;{// Sign in with our account.const{username,password}=account;awaitpage.goto('/signin');awaitpage.getByLabel('User Name').fill(username);awaitpage.getByLabel('Password').fill(password);awaitpage.getByText('Sign in').click();awaitexpect(page.getByTestId('userinfo')).toHaveText(username);// Use signed-in page in the test.awaituse(page);},});export{expect}from'@playwright/test';`\n```", "example.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('slow test',async({page})=&gt;{test.slow();// Easy way to triple the default timeout// ...});test('very slow test',async({page})=&gt;{test.setTimeout(120_000);// ...});`\n```\n\nAPI reference:\ntest.setTimeout() (https://playwright.dev/docs/api/class-test#test-set-timeout)\nand\ntest.slow() (https://playwright.dev/docs/api/class-test#test-slow)\n.", 'Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`']</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2782,21 +2801,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Fixture setup and teardown running time counts towards the overall test timeout. Because a fixture is considered part of the test, a slow fixture can cause the entire test to time out.
-To fix this without inflating the timeout for every test, you can set a separate, larger timeout specifically for the slow fixture while keeping the overall test timeout small. You do this by passing a `timeout` property in the fixture definition:
-```javascript
+          <t>By default, a fixture's setup and teardown time counts toward the test's overall timeout. If a fixture is slow, it can cause the test to time out.
+To fix this without inflating the timeout for every test, you can set a separate, larger timeout specifically for that fixture. You do this by using the `timeout` option within the fixture definition in `test.extend()`.
+**Example:**
+```typescript
 import { test as base, expect } from '@playwright/test';
 const test = base.extend&lt;{ slowFixture: string }&gt;({
   slowFixture: [async ({}, use) =&gt; {
     // ... perform a slow operation ...
     await use('hello');
-  }, { timeout: 60000 }]
+  }, { timeout: 60_000 }] // Set a specific timeout for this fixture
 });
 test('example test', async ({ slowFixture }) =&gt; {
   // ...
 });
 ```
-This approach also applies to worker-scoped fixtures.</t>
+This approach works for both test-scoped and worker-scoped fixtures.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2805,28 +2825,28 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.008801749999999001</v>
+        <v>0.0008585</v>
       </c>
       <c r="G37" t="n">
-        <v>33572</v>
+        <v>38385</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="J37" t="n">
         <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1238938053097345</v>
+        <v>0.1623931623931624</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.5277777777777778</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8333333332916666</v>
+        <v>0.94999999997625</v>
       </c>
       <c r="N37" t="n">
         <v>1</v>
@@ -2840,7 +2860,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', "These are the low-level timeouts that are pre-configured by the test runner, you should not need to change these. If you happen to be in this section because your test are flaky, it is very likely that you should be looking for the solution elsewhere.\n\nTimeout\nDefault\nDescription\nAction timeout\nno timeout\nTimeout for each action\nSet in config\n`{ use: { actionTimeout: 10_000 } }`\nOverride in test\n`locator.click({ timeout: 10_000 })`\nNavigation timeout\nno timeout\nTimeout for each navigation action\nSet in config\n`{ use: { navigationTimeout: 30_000 } }`\nOverride in test\n`page.goto('/', { timeout: 30_000 })`\nGlobal timeout\nno timeout\nGlobal timeout for the whole test run\nSet in config\n`{ globalTimeout: 3_600_000 }`\n`beforeAll`\n/\n`afterAll`\ntimeout\n30_000 ms\nTimeout for the hook\nSet in hook\n`test.setTimeout(60_000)`\nFixture timeout\nno timeout\nTimeout for an individual fixture\nSet in fixture\n`{ scope: 'test', timeout: 30_000 }`", 'Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Error: expect(received).toHaveText(expected)Expected string: "my text"Received string: ""Call log:- expect.toHaveText with timeout 5000ms- waiting for "locator(\'button\')"`\n```', 'Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and\n`beforeEach`\nhooks is included in the test timeout.\n\nTimed out test produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Timeout of 30000ms exceeded.`\n```\n\nAdditional separate timeout, of the same value, is shared between fixture teardowns and\n`afterEach`\nhooks, after the test function has finished.\n\nThe same timeout value also applies to\n`beforeAll`\nand\n`afterAll`\nhooks, but they do not share time with any test.', 'Auto-waiting | Playwright', "By default,\nfixture (https://playwright.dev/docs/test-fixtures)\nshares timeout with the test. However, for slow fixtures, especially\nworker-scoped (https://playwright.dev/docs/test-fixtures#worker-scoped-fixtures)\nones, it is convenient to have a separate timeout. This way you can keep the overall test timeout small, and give the slow fixture more time.\n\nexample.spec.ts\n```\n`import{testasbase,expect}from'@playwright/test';consttest=base.extend&lt;{slowFixture:string}&gt;({slowFixture:[async({},use)=&gt;{// ... perform a slow operation ...awaituse('hello');},{timeout:60_000}]});test('example test',async({slowFixture})=&gt;{// ...});`\n```\n\nAPI reference:\ntest.extend() (https://playwright.dev/docs/api/class-test#test-extend)\n.", "Playwright Test supports a timeout for the whole test run. This prevents excess resource usage when everything went wrong. There is no default global timeout, but you can set a reasonable one in the config, for example one hour. Global timeout produces the following error:\n\n```\n`Running 1000 tests using 10 workers514 skipped486 passedTimed out waiting 3600s for the entire test run`\n```\n\nYou can set global timeout in the config.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalTimeout:3_600_000,});`\n```\n\nAPI reference:\ntestConfig.globalTimeout (https://playwright.dev/docs/api/class-testconfig#test-config-global-timeout)\n."]</t>
+          <t>['Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', 'Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Error: expect(received).toHaveText(expected)Expected string: "my text"Received string: ""Call log:- expect.toHaveText with timeout 5000ms- waiting for "locator(\'button\')"`\n```', 'Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and\n`beforeEach`\nhooks is included in the test timeout.\n\nTimed out test produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Timeout of 30000ms exceeded.`\n```\n\nAdditional separate timeout, of the same value, is shared between fixture teardowns and\n`afterEach`\nhooks, after the test function has finished.\n\nThe same timeout value also applies to\n`beforeAll`\nand\n`afterAll`\nhooks, but they do not share time with any test.', 'PlaywrightAssertions | Playwright\n\nPlaywright gives you Web-First Assertions with convenience methods for creating assertions that will wait and retry until the expected condition is met.\n\nConsider the following example:\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'status becomes submitted\',async({page})=&gt;{// ...awaitpage.locator(\'#submit-button\').click();awaitexpect(page.locator(\'.status\')).toHaveText(\'Submitted\');});`\n```\n\nPlaywright will be re-testing the node with the selector\n`.status`\nuntil fetched Node has the\n`"Submitted"`\ntext. It will be re-fetching the node and checking it over and over, until the condition is met or until the timeout is reached. You can pass this timeout as an option.\n\nBy default, the timeout for assertions is set to 5 seconds.', "These are the low-level timeouts that are pre-configured by the test runner, you should not need to change these. If you happen to be in this section because your test are flaky, it is very likely that you should be looking for the solution elsewhere.\n\nTimeout\nDefault\nDescription\nAction timeout\nno timeout\nTimeout for each action\nSet in config\n`{ use: { actionTimeout: 10_000 } }`\nOverride in test\n`locator.click({ timeout: 10_000 })`\nNavigation timeout\nno timeout\nTimeout for each navigation action\nSet in config\n`{ use: { navigationTimeout: 30_000 } }`\nOverride in test\n`page.goto('/', { timeout: 30_000 })`\nGlobal timeout\nno timeout\nGlobal timeout for the whole test run\nSet in config\n`{ globalTimeout: 3_600_000 }`\n`beforeAll`\n/\n`afterAll`\ntimeout\n30_000 ms\nTimeout for the hook\nSet in hook\n`test.setTimeout(60_000)`\nFixture timeout\nno timeout\nTimeout for an individual fixture\nSet in fixture\n`{ scope: 'test', timeout: 30_000 }`", "Playwright Test supports a timeout for the whole test run. This prevents excess resource usage when everything went wrong. There is no default global timeout, but you can set a reasonable one in the config, for example one hour. Global timeout produces the following error:\n\n```\n`Running 1000 tests using 10 workers514 skipped486 passedTimed out waiting 3600s for the entire test run`\n```\n\nYou can set global timeout in the config.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalTimeout:3_600_000,});`\n```\n\nAPI reference:\ntestConfig.globalTimeout (https://playwright.dev/docs/api/class-testconfig#test-config-global-timeout)\n.", "playwright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({expect:{timeout:10_000,},});`\n```\n\nAPI reference:\ntestConfig.expect (https://playwright.dev/docs/api/class-testconfig#test-config-expect)\n."]</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2850,24 +2870,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>You are dealing with multiple separate timeout budgets. Based on the documentation, the specific budgets are:
-1.  **Test timeout:** 30,000 ms default. This covers the test function, fixture setups, and `beforeEach` hooks.
-2.  **Expect timeout:** 5,000 ms default. This is for auto-retrying assertions and is unrelated to the test timeout.
-3.  **Action timeout:** No default. Covers individual actions like `click`.
-4.  **Navigation timeout:** No default. Covers navigation actions like `page.goto`.
-5.  **Hook/Teardown timeout:** 30,000 ms default. Shared between fixture teardowns and `afterEach` hooks; also applies to `beforeAll` and `afterAll` hooks.
-6.  **Fixture timeout:** No default (shares with test by default).
-7.  **Global timeout:** No default. Covers the entire test run.
-Since you are seeing errors about the test itself rather than the assertion (e.g., `Timeout of 30000ms exceeded`), you should raise the **Test timeout**. 
-You can increase this in your config file:
-```javascript
-{ timeout: 60_000 }
-```
-Or override it for a specific test:
-```javascript
-test.setTimeout(120_000)
-```
-The assertion timeout is unrelated to the test timeout, which explains why raising it does not resolve errors caused by the test exceeding its own budget.</t>
+          <t>You are dealing with multiple separate timeout budgets. Based on the documentation, the two you are currently interacting with are:
+1.  **Expect timeout:** This is the budget for auto-retrying assertions (e.g., `expect(locator).toHaveText()`). It defaults to 5,000 ms and is unrelated to the test timeout.
+2.  **Test timeout:** This is the budget for the entire test, including the test function, fixture setups, and `beforeEach` hooks. It defaults to 30,000 ms.
+Since you mentioned that raising the assertion timeout does not help when tests fail with a message about the test itself, you are hitting the **Test timeout**. 
+To resolve this, you should raise the **Test timeout** rather than the assertion timeout. You can do this in two ways:
+*   **In your config:** Set the `timeout` property in your `playwright.config.ts` file:
+    `{ timeout: 60_000 }`
+*   **Override in a specific test:** Use `test.setTimeout(120_000)` within the test file.
+Additionally, the documentation notes that there are other low-level timeouts (Action, Navigation, Global, `beforeAll`/`afterAll`, and Fixture timeouts) that may apply depending on your specific test structure, but the "test itself" error specifically points to the Test timeout.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2876,31 +2887,31 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.010112</v>
+        <v>0.00092475</v>
       </c>
       <c r="G38" t="n">
-        <v>36678</v>
+        <v>35054</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="I38" t="n">
-        <v>0.51</v>
+        <v>0.62</v>
       </c>
       <c r="J38" t="n">
         <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2513089005235602</v>
+        <v>0.2447916666666667</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2622950819672131</v>
+        <v>0.2568306010928962</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6999999999766667</v>
+        <v>0.8333333332916666</v>
       </c>
       <c r="N38" t="n">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="39">
@@ -2911,7 +2922,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>['When you need to target a parent element of some other element, most of the time you should\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nby the child locator. For example, consider the following DOM structure:\n\n```\n`&lt;li&gt;&lt;label&gt;Hello&lt;/label&gt;&lt;/li&gt;&lt;li&gt;&lt;label&gt;World&lt;/label&gt;&lt;/li&gt;`\n```\n\nIf you\'d like to target the parent\n`&lt;li&gt;`\nof a label with text\n`"Hello"`\n, using\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nworks best:\n\n```\n`constchild=page.getByText(\'Hello\');constparent=page.getByRole(\'listitem\').filter({has:child});`\n```\n\nAlternatively, if you cannot find a suitable locator for the parent element, use\n`xpath=..`\n. Note that this method is not as reliable, because any changes to the DOM structure will break your tests. Prefer\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nwhen possible.\n\n```\n`constparent=page.getByText(\'Hello\').locator(\'xpath=..\');`\n```', 'Other locators | Playwright', "Locators support an option to only select elements that have or have not a descendant matching another locator. You can therefore filter by any other locator such as a\nlocator.getByRole() (https://playwright.dev/docs/api/class-locator#locator-get-by-role)\n,\nlocator.getByTestId() (https://playwright.dev/docs/api/class-locator#locator-get-by-test-id)\n,\nlocator.getByText() (https://playwright.dev/docs/api/class-locator#locator-get-by-text)\netc.\n\nhttp://localhost:3000\nProduct 1\nAdd to cart\nProduct 2\nAdd to cart\n```\n`&lt;ul&gt;&lt;li&gt;&lt;h3&gt;Product 1&lt;/h3&gt;&lt;button&gt;Add to cart&lt;/button&gt;&lt;/li&gt;&lt;li&gt;&lt;h3&gt;Product 2&lt;/h3&gt;&lt;button&gt;Add to cart&lt;/button&gt;&lt;/li&gt;&lt;/ul&gt;`\n```\n\n```\n`awaitpage.getByRole('listitem').filter({has:page.getByRole('heading',{name:'Product 2'})}).getByRole('button',{name:'Add to cart'}).click();`\n```\n\nWe can also assert the product card to make sure there is only one:\n\n```\n`awaitexpect(page.getByRole('listitem').filter({has:page.getByRole('heading',{name:'Product 2'})})).toHaveCount(1);`\n```\n\nThe filtering locator\nmust be relative\nto the original locator and is queried starting with the original locator match, not the document root. Therefore, the following will not work, because the filtering locator starts matching from the\n`&lt;ul&gt;`\nlist element that is outside of the\n`&lt;li&gt;`\nlist item matched by the original locator:\n\n```\n`// ✖ WRONGawaitexpect(page.getByRole('listitem').filter({has:page.getByRole('list').getByText('Product 2')})).toHaveCount(1);`\n```", "warning\nWe recommend prioritizing\nuser-visible locators (https://playwright.dev/docs/locators#quick-guide)\nlike text or accessible role instead of using XPath that is tied to the implementation and easily break when the page changes.\n\nXPath locators are equivalent to calling\nDocument.evaluate (https://developer.mozilla.org/en/docs/Web/API/Document/evaluate)\n.\n\n```\n`awaitpage.locator('xpath=//button').click();`\n```\n\nnote\nAny selector string starting with\n`//`\nor\n`..`\nare assumed to be an xpath selector. For example, Playwright converts\n`'//html/body'`\nto\n`'xpath=//html/body'`\n.\n\nnote\nXPath does not pierce shadow roots."]</t>
+          <t>['When you need to target a parent element of some other element, most of the time you should\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nby the child locator. For example, consider the following DOM structure:\n\n```\n`&lt;li&gt;&lt;label&gt;Hello&lt;/label&gt;&lt;/li&gt;&lt;li&gt;&lt;label&gt;World&lt;/label&gt;&lt;/li&gt;`\n```\n\nIf you\'d like to target the parent\n`&lt;li&gt;`\nof a label with text\n`"Hello"`\n, using\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nworks best:\n\n```\n`constchild=page.getByText(\'Hello\');constparent=page.getByRole(\'listitem\').filter({has:child});`\n```\n\nAlternatively, if you cannot find a suitable locator for the parent element, use\n`xpath=..`\n. Note that this method is not as reliable, because any changes to the DOM structure will break your tests. Prefer\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nwhen possible.\n\n```\n`constparent=page.getByText(\'Hello\').locator(\'xpath=..\');`\n```', "Locators support an option to only select elements that have or have not a descendant matching another locator. You can therefore filter by any other locator such as a\nlocator.getByRole() (https://playwright.dev/docs/api/class-locator#locator-get-by-role)\n,\nlocator.getByTestId() (https://playwright.dev/docs/api/class-locator#locator-get-by-test-id)\n,\nlocator.getByText() (https://playwright.dev/docs/api/class-locator#locator-get-by-text)\netc.\n\nhttp://localhost:3000\nProduct 1\nAdd to cart\nProduct 2\nAdd to cart\n```\n`&lt;ul&gt;&lt;li&gt;&lt;h3&gt;Product 1&lt;/h3&gt;&lt;button&gt;Add to cart&lt;/button&gt;&lt;/li&gt;&lt;li&gt;&lt;h3&gt;Product 2&lt;/h3&gt;&lt;button&gt;Add to cart&lt;/button&gt;&lt;/li&gt;&lt;/ul&gt;`\n```\n\n```\n`awaitpage.getByRole('listitem').filter({has:page.getByRole('heading',{name:'Product 2'})}).getByRole('button',{name:'Add to cart'}).click();`\n```\n\nWe can also assert the product card to make sure there is only one:\n\n```\n`awaitexpect(page.getByRole('listitem').filter({has:page.getByRole('heading',{name:'Product 2'})})).toHaveCount(1);`\n```\n\nThe filtering locator\nmust be relative\nto the original locator and is queried starting with the original locator match, not the document root. Therefore, the following will not work, because the filtering locator starts matching from the\n`&lt;ul&gt;`\nlist element that is outside of the\n`&lt;li&gt;`\nlist item matched by the original locator:\n\n```\n`// ✖ WRONGawaitexpect(page.getByRole('listitem').filter({has:page.getByRole('list').getByText('Product 2')})).toHaveCount(1);`\n```", "The\n`:has()`\npseudo-class is a\nCSS pseudo-class (https://developer.mozilla.org/en-US/docs/Web/CSS/:has)\n. It returns an element if any of the selectors passed as parameters relative to the\n`:scope`\nof the given element match at least one element.\n\nFollowing snippet returns text content of an\n`&lt;article&gt;`\nelement that has a\n`&lt;div class=promo&gt;`\ninside.\n\n```\n`awaitpage.locator('article:has(div.promo)').textContent();`\n```", "warning\nWe recommend prioritizing\nuser-visible locators (https://playwright.dev/docs/locators#quick-guide)\nlike text or accessible role instead of using XPath that is tied to the implementation and easily break when the page changes.\n\nXPath locators are equivalent to calling\nDocument.evaluate (https://developer.mozilla.org/en/docs/Web/API/Document/evaluate)\n.\n\n```\n`awaitpage.locator('xpath=//button').click();`\n```\n\nnote\nAny selector string starting with\n`//`\nor\n`..`\nare assumed to be an xpath selector. For example, Playwright converts\n`'//html/body'`\nto\n`'xpath=//html/body'`\n.\n\nnote\nXPath does not pierce shadow roots."]</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2921,13 +2932,8 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>The reliable way to select a parent row based on a child element is to use `locator.filter()`. You should use this method by passing the child locator to the `has` option of the parent locator.
-**Example:**
-```javascript
-const child = page.getByText('Hello');
-const parent = page.getByRole('listitem').filter({has: child});
-```
-You should avoid using `xpath=..` because it is not as reliable; any changes to the DOM structure will cause your tests to break. Additionally, XPath locators are tied to the implementation, whereas `locator.filter()` is preferred.</t>
+          <t>The reliable way to select a parent row based on a child element is to use `locator.filter()`. This is the recommended approach because it is more stable than other methods.
+You should avoid `xpath=..` because it is not as reliable; any changes to the DOM structure will cause your tests to break.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2936,10 +2942,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.00852725</v>
+        <v>0.00050025</v>
       </c>
       <c r="G39" t="n">
-        <v>32744</v>
+        <v>36035</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
@@ -2948,16 +2954,16 @@
         <v>0.91</v>
       </c>
       <c r="J39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1954022988505747</v>
+        <v>0.2264150943396226</v>
       </c>
       <c r="L39" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8333333332916666</v>
+        <v>0.99999999995</v>
       </c>
       <c r="N39" t="n">
         <v>1</v>
@@ -2971,7 +2977,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>['To create your own fixture, use\ntest.extend() (https://playwright.dev/docs/api/class-test#test-extend)\nto create a new\n`test`\nobject that will include it.\n\nBelow we create two fixtures\n`todoPage`\nand\n`settingsPage`\nthat follow the\nPage Object Model (https://playwright.dev/docs/pom)\npattern.\n\nClick to expand the code for the\n`TodoPage`\nand\n`SettingsPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\nSettingsPage is similar:\nsettings-page.ts\n```\n`importtype{Page}from\'@playwright/test\';exportclassSettingsPage{constructor(publicreadonly page:Page){}asyncswitchToDarkMode(){// ...}}`\n```\n\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';import{SettingsPage}from\'./settings-page\';// Declare the types of your fixtures.typeMyFixtures={todoPage:TodoPage;settingsPage:SettingsPage;};// Extend base test by providing "todoPage" and "settingsPage".// This new "test" can be used in multiple test files, and each of them will get the fixtures.exportconsttest=base.extend&lt;MyFixtures&gt;({todoPage:async({page},use)=&gt;{// Set up the fixture.consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(\'item1\');awaittodoPage.addToDo(\'item2\');// Use the fixture value in the test.awaituse(todoPage);// Clean up the fixture.awaittodoPage.removeAll();},settingsPage:async({page},use)=&gt;{awaituse(newSettingsPage(page));},});export{expect}from\'@playwright/test\';`\n```\n\nnote\nCustom fixture names should start with a letter or underscore, and can contain only letters, numbers, and underscores.', 'Fixtures have a number of advantages over before/after hooks:\n\nFixtures\nencapsulate\nsetup and teardown in the same place so it is easier to write. So if you have an after hook that tears down what was created in a before hook, consider turning them into a fixture.\nFixtures are\nreusable\nbetween test files - you can define them once and use them in all your tests. That\'s how Playwright\'s built-in\n`page`\nfixture works. So if you have a helper function that is used in multiple tests, consider turning it into a fixture.\nFixtures are\non-demand\n- you can define as many fixtures as you\'d like, and Playwright Test will setup only the ones needed by your test and nothing else.\nFixtures are\ncomposable\n- they can depend on each other to provide complex behaviors.\nFixtures are\nflexible\n. Tests can use any combination of fixtures to precisely tailor the environment to their needs, without affecting other tests.\nFixtures simplify\ngrouping\n. You no longer need to wrap tests in\n`describe`\ns that set up their environment, and are free to group your tests by their meaning instead.\n\nClick to expand the code for the\n`TodoPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\n\nexample.spec.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';// Extend basic test by providing a "todoPage" fixture.consttest=base.extend&lt;{todoPage:TodoPage}&gt;({todoPage:async({page},use)=&gt;{consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(\'item1\');awaittodoPage.addToDo(\'item2\');awaituse(todoPage);awaittodoPage.removeAll();},});test(\'should add an item\',async({todoPage})=&gt;{awaittodoPage.addToDo(\'my item\');// ...});test(\'should remove an item\',async({todoPage})=&gt;{awaittodoPage.remove(\'item1\');// ...});`\n```', 'Page object models | Playwright', 'Fixtures | Playwright', "We will create a\n`PlaywrightDevPage`\nhelper class to encapsulate common operations on the\n`playwright.dev`\npage. Internally, it will use the\n`page`\nobject.\n\nTest\nLibrary\nplaywright-dev-page.ts\n```\n`import{expect,typeLocator,typePage}from'@playwright/test';exportclassPlaywrightDevPage{readonly page:Page;readonly getStartedLink:Locator;readonly gettingStartedHeader:Locator;readonly pomLink:Locator;readonly tocList:Locator;constructor(page:Page){this.page=page;this.getStartedLink=page.locator('a',{hasText:'Get started'});this.gettingStartedHeader=page.locator('h1',{hasText:'Installation'});this.pomLink=page.locator('li',{hasText:'Guides',}).locator('a',{hasText:'Page Object Model',});this.tocList=page.locator('article div.markdown ul &gt; li &gt; a');}asyncgoto(){awaitthis.page.goto('https://playwright.dev');}asyncgetStarted(){awaitthis.getStartedLink.first().click();awaitexpect(this.gettingStartedHeader).toBeVisible();}asyncpageObjectModel(){awaitthis.getStarted();awaitthis.pomLink.click();}}`\n```\nmodels/PlaywrightDevPage.js\n```\n`classPlaywrightDevPage{/***@param{import('playwright').Page}page*/constructor(page){this.page=page;this.getStartedLink=page.locator('a',{hasText:'Get started'});this.gettingStartedHeader=page.locator('h1',{hasText:'Installation'});this.pomLink=page.locator('li',{hasText:'Playwright Test',}).locator('a',{hasText:'Page Object Model',});this.tocList=page.locator('article div.markdown ul &gt; li &gt; a');}asyncgetStarted(){awaitthis.getStartedLink.first().click();awaitexpect(this.gettingStartedHeader).toBeVisible();}asyncpageObjectModel(){awaitthis.getStarted();awaitthis.pomLink.click();}}module.exports={PlaywrightDevPage};`\n```\n\nNow we can use the\n`PlaywrightDevPage`\nclass in our tests.\n\nTest\nLibrary\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';import{PlaywrightDevPage}from'./playwright-dev-page';test('getting started should contain table of contents',async({page})=&gt;{constplaywrightDev=newPlaywrightDevPage(page);awaitplaywrightDev.goto();awaitplaywrightDev.getStarted();awaitexpect(playwrightDev.tocList).toHaveText([`How to install Playwright`,`What's installed`,`How to run the example test`,`How to open the HTML test report`,`Write tests using web-first assertions, fixtures and locators`,`Run single or multiple tests; headed mode`,`Generate tests with Codegen`,`View a trace of your tests`,]);});test('should show Page Object Model article',async({page})=&gt;{constplaywrightDev=newPlaywrightDevPage(page);awaitplaywrightDev.goto();awaitplaywrightDev.pageObjectModel();awaitexpect(page.locator('article')).toContainText('Page Object Model is a common pattern');});`\n```\nexample.spec.js\n```\n`const{PlaywrightDevPage}=require('./playwright-dev-page');// In the testconstpage=awaitbrowser.newPage();awaitplaywrightDev.goto();awaitplaywrightDev.getStarted();awaitexpect(playwrightDev.tocList).toHaveText([`How to install Playwright`,`What's installed`,`How to run the example test`,`How to open the HTML test report`,`Write tests using web-first assertions, fixtures and locators`,`Run single or multiple tests; headed mode`,`Generate tests with Codegen`,`View a trace of your tests`,]);`\n```"]</t>
+          <t>['To create your own fixture, use\ntest.extend() (https://playwright.dev/docs/api/class-test#test-extend)\nto create a new\n`test`\nobject that will include it.\n\nBelow we create two fixtures\n`todoPage`\nand\n`settingsPage`\nthat follow the\nPage Object Model (https://playwright.dev/docs/pom)\npattern.\n\nClick to expand the code for the\n`TodoPage`\nand\n`SettingsPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\nSettingsPage is similar:\nsettings-page.ts\n```\n`importtype{Page}from\'@playwright/test\';exportclassSettingsPage{constructor(publicreadonly page:Page){}asyncswitchToDarkMode(){// ...}}`\n```\n\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';import{SettingsPage}from\'./settings-page\';// Declare the types of your fixtures.typeMyFixtures={todoPage:TodoPage;settingsPage:SettingsPage;};// Extend base test by providing "todoPage" and "settingsPage".// This new "test" can be used in multiple test files, and each of them will get the fixtures.exportconsttest=base.extend&lt;MyFixtures&gt;({todoPage:async({page},use)=&gt;{// Set up the fixture.consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(\'item1\');awaittodoPage.addToDo(\'item2\');// Use the fixture value in the test.awaituse(todoPage);// Clean up the fixture.awaittodoPage.removeAll();},settingsPage:async({page},use)=&gt;{awaituse(newSettingsPage(page));},});export{expect}from\'@playwright/test\';`\n```\n\nnote\nCustom fixture names should start with a letter or underscore, and can contain only letters, numbers, and underscores.', 'Fixtures have a number of advantages over before/after hooks:\n\nFixtures\nencapsulate\nsetup and teardown in the same place so it is easier to write. So if you have an after hook that tears down what was created in a before hook, consider turning them into a fixture.\nFixtures are\nreusable\nbetween test files - you can define them once and use them in all your tests. That\'s how Playwright\'s built-in\n`page`\nfixture works. So if you have a helper function that is used in multiple tests, consider turning it into a fixture.\nFixtures are\non-demand\n- you can define as many fixtures as you\'d like, and Playwright Test will setup only the ones needed by your test and nothing else.\nFixtures are\ncomposable\n- they can depend on each other to provide complex behaviors.\nFixtures are\nflexible\n. Tests can use any combination of fixtures to precisely tailor the environment to their needs, without affecting other tests.\nFixtures simplify\ngrouping\n. You no longer need to wrap tests in\n`describe`\ns that set up their environment, and are free to group your tests by their meaning instead.\n\nClick to expand the code for the\n`TodoPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\n\nexample.spec.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';// Extend basic test by providing a "todoPage" fixture.consttest=base.extend&lt;{todoPage:TodoPage}&gt;({todoPage:async({page},use)=&gt;{consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(\'item1\');awaittodoPage.addToDo(\'item2\');awaituse(todoPage);awaittodoPage.removeAll();},});test(\'should add an item\',async({todoPage})=&gt;{awaittodoPage.addToDo(\'my item\');// ...});test(\'should remove an item\',async({todoPage})=&gt;{awaittodoPage.remove(\'item1\');// ...});`\n```', "We will create a\n`PlaywrightDevPage`\nhelper class to encapsulate common operations on the\n`playwright.dev`\npage. Internally, it will use the\n`page`\nobject.\n\nTest\nLibrary\nplaywright-dev-page.ts\n```\n`import{expect,typeLocator,typePage}from'@playwright/test';exportclassPlaywrightDevPage{readonly page:Page;readonly getStartedLink:Locator;readonly gettingStartedHeader:Locator;readonly pomLink:Locator;readonly tocList:Locator;constructor(page:Page){this.page=page;this.getStartedLink=page.locator('a',{hasText:'Get started'});this.gettingStartedHeader=page.locator('h1',{hasText:'Installation'});this.pomLink=page.locator('li',{hasText:'Guides',}).locator('a',{hasText:'Page Object Model',});this.tocList=page.locator('article div.markdown ul &gt; li &gt; a');}asyncgoto(){awaitthis.page.goto('https://playwright.dev');}asyncgetStarted(){awaitthis.getStartedLink.first().click();awaitexpect(this.gettingStartedHeader).toBeVisible();}asyncpageObjectModel(){awaitthis.getStarted();awaitthis.pomLink.click();}}`\n```\nmodels/PlaywrightDevPage.js\n```\n`classPlaywrightDevPage{/***@param{import('playwright').Page}page*/constructor(page){this.page=page;this.getStartedLink=page.locator('a',{hasText:'Get started'});this.gettingStartedHeader=page.locator('h1',{hasText:'Installation'});this.pomLink=page.locator('li',{hasText:'Playwright Test',}).locator('a',{hasText:'Page Object Model',});this.tocList=page.locator('article div.markdown ul &gt; li &gt; a');}asyncgetStarted(){awaitthis.getStartedLink.first().click();awaitexpect(this.gettingStartedHeader).toBeVisible();}asyncpageObjectModel(){awaitthis.getStarted();awaitthis.pomLink.click();}}module.exports={PlaywrightDevPage};`\n```\n\nNow we can use the\n`PlaywrightDevPage`\nclass in our tests.\n\nTest\nLibrary\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';import{PlaywrightDevPage}from'./playwright-dev-page';test('getting started should contain table of contents',async({page})=&gt;{constplaywrightDev=newPlaywrightDevPage(page);awaitplaywrightDev.goto();awaitplaywrightDev.getStarted();awaitexpect(playwrightDev.tocList).toHaveText([`How to install Playwright`,`What's installed`,`How to run the example test`,`How to open the HTML test report`,`Write tests using web-first assertions, fixtures and locators`,`Run single or multiple tests; headed mode`,`Generate tests with Codegen`,`View a trace of your tests`,]);});test('should show Page Object Model article',async({page})=&gt;{constplaywrightDev=newPlaywrightDevPage(page);awaitplaywrightDev.goto();awaitplaywrightDev.pageObjectModel();awaitexpect(page.locator('article')).toContainText('Page Object Model is a common pattern');});`\n```\nexample.spec.js\n```\n`const{PlaywrightDevPage}=require('./playwright-dev-page');// In the testconstpage=awaitbrowser.newPage();awaitplaywrightDev.goto();awaitplaywrightDev.getStarted();awaitexpect(playwrightDev.tocList).toHaveText([`How to install Playwright`,`What's installed`,`How to run the example test`,`How to open the HTML test report`,`Write tests using web-first assertions, fixtures and locators`,`Run single or multiple tests; headed mode`,`Generate tests with Codegen`,`View a trace of your tests`,]);`\n```", 'Here is how a typical test environment setup differs between the traditional test style and the fixture-based one.\n\n`TodoPage`\nis a class that helps us interact with a "todo list" page of the web app, following the\nPage Object Model (https://playwright.dev/docs/pom)\npattern. It uses Playwright\'s\n`page`\ninternally.\n\nClick to expand the code for the\n`TodoPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\n\ntodo.spec.ts\n```\n`const{test}=require(\'@playwright/test\');const{TodoPage}=require(\'./todo-page\');test.describe(\'todo tests\',()=&gt;{lettodoPage;test.beforeEach(async({page})=&gt;{todoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(\'item1\');awaittodoPage.addToDo(\'item2\');});test.afterEach(async()=&gt;{awaittodoPage.removeAll();});test(\'should add an item\',async()=&gt;{awaittodoPage.addToDo(\'my item\');// ...});test(\'should remove an item\',async()=&gt;{awaittodoPage.remove(\'item1\');// ...});});`\n```', "Automatic fixtures are set up for each test/worker, even when the test does not list them directly. To create an automatic fixture, use the tuple syntax and pass\n`{ auto: true }`\n.\n\nHere is an example fixture that automatically attaches debug logs when the test fails, so we can later review the logs in the reporter. Note how it uses the\nTestInfo (https://playwright.dev/docs/api/class-testinfo)\nobject that is available in each test/fixture to retrieve metadata about the test being run.\n\nmy-test.ts\n```\n`importdebugfrom'debug';importfsfrom'fs';import{testasbase}from'@playwright/test';exportconsttest=base.extend&lt;{saveLogs:void}&gt;({saveLogs:[async({},use,testInfo)=&gt;{// Collecting logs during the test.constlogs=[];debug.log=(...args)=&gt;logs.push(args.map(String).join(''));debug.enable('myserver');awaituse();// After the test we can check whether the test passed or failed.if(testInfo.status!==testInfo.expectedStatus){// outputPath() API guarantees a unique file name.constlogFile=testInfo.outputPath('logs.txt');awaitfs.promises.writeFile(logFile,logs.join('\\n'),'utf8');testInfo.attachments.push({name:'logs',contentType:'text/plain',path:logFile});}},{auto:true}],});export{expect}from'@playwright/test';`\n```", "Just mention a fixture in your test function argument, and the test runner will take care of it. Fixtures are also available in hooks and other fixtures. If you use TypeScript, fixtures will be type safe.\n\nBelow we use the\n`todoPage`\nand\n`settingsPage`\nfixtures that we defined above.\n\n```\n`import{test,expect}from'./my-test';test.beforeEach(async({settingsPage})=&gt;{awaitsettingsPage.switchToDarkMode();});test('basic test',async({todoPage,page})=&gt;{awaittodoPage.addToDo('something nice');awaitexpect(page.getByTestId('todo-title')).toContainText(['something nice']);});`\n```", "In addition to creating your own fixtures, you can also override existing fixtures to fit your needs. Consider the following example which overrides the\n`page`\nfixture by automatically navigating to the\n`baseURL`\n:\n\n```\n`import{testasbase}from'@playwright/test';exportconsttest=base.extend({page:async({baseURL,page},use)=&gt;{awaitpage.goto(baseURL);awaituse(page);},});`\n```\n\nNotice that in this example, the\n`page`\nfixture is able to depend on other built-in fixtures such as\ntestOptions.baseURL (https://playwright.dev/docs/api/class-testoptions#test-options-base-url)\n. We can now configure\n`baseURL`\nin the configuration file, or locally in the test file with\ntest.use() (https://playwright.dev/docs/api/class-test#test-use)\n.\n\nexample.spec.ts\n```\n`test.use({baseURL:'https://playwright.dev'});`\n```\n\nFixtures can also be overridden, causing the base fixture to be completely replaced with something different. For example, we could override the\ntestOptions.storageState (https://playwright.dev/docs/api/class-testoptions#test-options-storage-state)\nfixture to provide our own data.\n\n```\n`import{testasbase}from'@playwright/test';exportconsttest=base.extend({storageState:async({},use)=&gt;{constcookie=awaitgetAuthCookie();awaituse({cookies:[cookie]});},});`\n```"]</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2981,365 +2987,417 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>To wire your Page Object Models so each test receives a ready-to-use instance without boilerplate, you should use **fixtures**.
-### How to implement fixtures for Page Objects:
-1.  **Define the fixture:** Use `test.extend()` to create a new `test` object that includes your page objects. You define the fixture by providing a function that receives the `page` object, instantiates your Page Object class, performs any necessary setup (like navigating to a URL), and then calls `use()` to pass the instance to the test. You can also include teardown logic after the `await use(...)` call.
-    **Example:**
+          <t>To wire Page Object Models (POMs) so each test receives a ready-to-use page object without boilerplate, you should use **fixtures**. This approach encapsulates setup and teardown logic, allowing you to define the page object once and inject it into any test.
+### Implementation Steps
+1.  **Extend the base test:** Create a new test file (e.g., `my-test.ts`) and use `test.extend()` to define your page object as a fixture.
+2.  **Define the fixture:** Within the `extend` object, instantiate your page object class. You can perform setup actions (like navigating to a URL or adding initial data) before calling `await use(pageObject)`. You can also include teardown logic after the `await use()` call.
+3.  **Export the extended test:** Export this new `test` object to be used in your test files.
+**Example:**
+```typescript
+// my-test.ts
+import { test as base } from '@playwright/test';
+import { TodoPage } from './todo-page';
+type MyFixtures = {
+  todoPage: TodoPage;
+};
+export const test = base.extend&lt;MyFixtures&gt;({
+  todoPage: async ({ page }, use) =&gt; {
+    // Setup: Instantiate and prepare the page object
+    const todoPage = new TodoPage(page);
+    await todoPage.goto();
+    await todoPage.addToDo('item1');
+    // Provide the fixture to the test
+    await use(todoPage);
+    // Teardown: Clean up after the test
+    await todoPage.removeAll();
+  },
+});
+```
+### Usage in Tests
+Once defined, you no longer need to manually instantiate the page object in every test. Simply import your custom `test` object and list the fixture as an argument in your test function:
+```typescript
+import { test, expect } from './my-test';
+test('should add an item', async ({ todoPage }) =&gt; {
+  await todoPage.addToDo('my item');
+  // ...
+});
+```
+### Why use this approach?
+*   **Boilerplate reduction:** You avoid repeating instantiation and setup code in `beforeEach` hooks.
+*   **On-demand setup:** Playwright Test will only set up the fixtures required by the specific test.
+*   **Reusability:** The fixture can be used across multiple test files.
+*   **Type safety:** If using TypeScript, the fixtures are type-safe.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Wrap the POM in a fixture created with test.extend(): the fixture builds the page object (and can do setup/teardown around it), and any test just lists it as an argument. Fixtures are reusable across files, so every spec shares it.</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0.00186075</v>
+      </c>
+      <c r="G40" t="n">
+        <v>37497</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.07843137254901961</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.7961904761745524</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Before a click, what does Playwright verify, and how does that relate to the waiting a plain click already does?</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>['Playwright performs a range of actionability checks on the elements before making actions to ensure these actions behave as expected. It auto-waits for all the relevant checks to pass and only then performs the requested action. If the required checks do not pass within the given\n`timeout`\n, action fails with the\n`TimeoutError`\n.\n\nFor example, for\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\n, Playwright will ensure that:\n\nlocator resolves to exactly one element\nelement is\nVisible (https://playwright.dev/docs/actionability#visible)\nelement is\nStable (https://playwright.dev/docs/actionability#stable)\n, as in not animating or completed animation\nelement\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\n, as in not obscured by other elements\nelement is\nEnabled (https://playwright.dev/docs/actionability#enabled)\n\nHere is the complete list of actionability checks performed for each action:\n\nAction\nVisible (https://playwright.dev/docs/actionability#visible)\nStable (https://playwright.dev/docs/actionability#stable)\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\nEnabled (https://playwright.dev/docs/actionability#enabled)\nEditable (https://playwright.dev/docs/actionability#editable)\nlocator.check() (https://playwright.dev/docs/api/class-locator#locator-check)\nYes\nYes\nYes\nYes\n-\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nYes\nYes\nYes\nYes\n-\nlocator.dblclick() (https://playwright.dev/docs/api/class-locator#locator-dblclick)\nYes\nYes\nYes\nYes\n-\nlocator.setChecked() (https://playwright.dev/docs/api/class-locator#locator-set-checked)\nYes\nYes\nYes\nYes\n-\nlocator.tap() (https://playwright.dev/docs/api/class-locator#locator-tap)\nYes\nYes\nYes\nYes\n-\nlocator.uncheck() (https://playwright.dev/docs/api/class-locator#locator-uncheck)\nYes\nYes\nYes\nYes\n-\nlocator.hover() (https://playwright.dev/docs/api/class-locator#locator-hover)\nYes\nYes\nYes\n-\n-\nlocator.dragTo() (https://playwright.dev/docs/api/class-locator#locator-drag-to)\nYes\nYes\nYes\n-\n-\nlocator.screenshot() (https://playwright.dev/docs/api/class-locator#locator-screenshot)\nYes\nYes\n-\n-\n-\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\nYes\n-\n-\nYes\nYes\nlocator.clear() (https://playwright.dev/docs/api/class-locator#locator-clear)\nYes\n-\n-\nYes\nYes\nlocator.selectOption() (https://playwright.dev/docs/api/class-locator#locator-select-option)\nYes\n-\n-\nYes\n-\nlocator.selectText() (https://playwright.dev/docs/api/class-locator#locator-select-text)\nYes\n-\n-\n-\n-\nlocator.scrollIntoViewIfNeeded() (https://playwright.dev/docs/api/class-locator#locator-scroll-into-view-if-needed)\n-\nYes\n-\n-\n-\nlocator.blur() (https://playwright.dev/docs/api/class-locator#locator-blur)\n-\n-\n-\n-\n-\nlocator.dispatchEvent() (https://playwright.dev/docs/api/class-locator#locator-dispatch-event)\n-\n-\n-\n-\n-\nlocator.focus() (https://playwright.dev/docs/api/class-locator#locator-focus)\n-\n-\n-\n-\n-\nlocator.press() (https://playwright.dev/docs/api/class-locator#locator-press)\n-\n-\n-\n-\n-\nlocator.pressSequentially() (https://playwright.dev/docs/api/class-locator#locator-press-sequentially)\n-\n-\n-\n-\n-\nlocator.setInputFiles() (https://playwright.dev/docs/api/class-locator#locator-set-input-files)\n-\n-\n-\n-\n-', "Performs a simple human click.\n\n```\n`// Generic clickawaitpage.getByRole('button').click();// Double clickawaitpage.getByText('Item').dblclick();// Right clickawaitpage.getByText('Item').click({button:'right'});// Shift + clickawaitpage.getByText('Item').click({modifiers:['Shift']});// Ctrl + click on Windows and Linux// Meta + click on macOSawaitpage.getByText('Item').click({modifiers:['ControlOrMeta']});// Hover over elementawaitpage.getByText('Item').hover();// Click the top left cornerawaitpage.getByText('Item').click({position:{x:0,y:0}});`\n```\n\nUnder the hood, this and other pointer-related methods:\n\nwait for element with given selector to be in DOM\nwait for it to become displayed, i.e. not empty, no\n`display:none`\n, no\n`visibility:hidden`\nwait for it to stop moving, for example, until css transition finishes\nscroll the element into view\nwait for it to receive pointer events at the action point, for example, waits until element becomes non-obscured by other elements\nretry if the element is detached during any of the above checks", 'Element is considered receiving pointer events when it is the hit target of the pointer event at the action point. For example, when clicking at the point\n`(10;10)`\n, Playwright checks whether some other element (usually an overlay) will instead capture the click at\n`(10;10)`\n.\n\nFor example, consider a scenario where Playwright will click\n`Sign Up`\nbutton regardless of when the\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\ncall was made:\n\npage is checking that user name is unique and\n`Sign Up`\nbutton is disabled;\nafter checking with the server, the disabled\n`Sign Up`\nbutton is replaced with another one that is now enabled.', 'Element is considered visible when it has non-empty bounding box and does not have\n`visibility:hidden`\ncomputed style.\n\nNote that according to this definition:\n\nElements of zero size\nare not\nconsidered visible.\nElements with\n`display:none`\nare not\nconsidered visible.\nElements with\n`opacity:0`\nare\nconsidered visible.', 'Element is considered stable when it has maintained the same bounding box for at least two consecutive animation frames.', 'Element is considered enabled when it is\nnot disabled\n.\n\nElement is\ndisabled\nwhen:\n\nit is a\n`&lt;button&gt;`\n,\n`&lt;select&gt;`\n,\n`&lt;input&gt;`\n,\n`&lt;textarea&gt;`\n,\n`&lt;option&gt;`\nor\n`&lt;optgroup&gt;`\nwith a\n`[disabled]`\nattribute;\nit is a\n`&lt;button&gt;`\n,\n`&lt;select&gt;`\n,\n`&lt;input&gt;`\n,\n`&lt;textarea&gt;`\n,\n`&lt;option&gt;`\nor\n`&lt;optgroup&gt;`\nthat is a part of a\n`&lt;fieldset&gt;`\nwith a\n`[disabled]`\nattribute;\nit is a descendant of an element with\n`[aria-disabled=true]`\nattribute.', 'Element is considered editable when it is\nenabled (https://playwright.dev/docs/actionability#enabled)\nand is\nnot readonly\n.\n\nElement is\nreadonly\nwhen:\n\nit is a\n`&lt;select&gt;`\n,\n`&lt;input&gt;`\nor\n`&lt;textarea&gt;`\nwith a\n`[readonly]`\nattribute;\nit has an\n`[aria-readonly=true]`\nattribute and an aria role that\nsupports it (https://w3c.github.io/aria/#aria-readonly)\n.']</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>['Playwright performs a range of actionability checks on the elements before making actions to ensure these actions behave as expected. It auto-waits for all the relevant checks to pass and only then performs the requested action. If the required checks do not pass within the given timeout , action fails with the TimeoutError .', 'wait for element with given selector to be in DOM']</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Before performing a click, Playwright performs a series of actionability checks to ensure the element is ready. Specifically, it verifies that:
+*   **The locator resolves to exactly one element.**
+*   **The element is visible:** It has a non-empty bounding box and does not have a `visibility:hidden` computed style.
+*   **The element is stable:** It has maintained the same bounding box for at least two consecutive animation frames (i.e., it is not animating).
+*   **The element receives events:** It is not obscured by other elements and is the hit target of the pointer event at the action point.
+*   **The element is enabled:** It does not have a `[disabled]` attribute (or is not part of a disabled `&lt;fieldset&gt;`) and is not a descendant of an element with `[aria-disabled=true]`.
+**Relation to waiting:**
+These checks are part of Playwright's "auto-waiting" mechanism. When you call `locator.click()`, Playwright automatically waits for all of these relevant checks to pass before performing the action. If these conditions are not met within the specified `timeout`, the action fails with a `TimeoutError`. 
+Under the hood, this process also includes:
+*   Waiting for the element to be in the DOM.
+*   Scrolling the element into view.
+*   Retrying the checks if the element becomes detached during the process.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>A click runs actionability checks — attached, visible, stable, receives pointer events, enabled — and auto-waits for them. The pointer methods bake that same sequence in (down to scrolling into view), so you rarely need explicit waits.</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0010755</v>
+      </c>
+      <c r="G41" t="n">
+        <v>32931</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.09134615384615384</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.5277777777777778</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.99999999995</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Where do downloaded files go, and why might they disappear before I can use them?</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>["Download | Playwright\n\nDownload (https://playwright.dev/docs/api/class-download)\nobjects are dispatched by page via the\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent.\n\nAll the downloaded files belonging to the browser context are deleted when the browser context is closed.\n\nDownload event is emitted once the download starts. Download path becomes available once download completes.\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", "For every attachment downloaded by the page,\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent is emitted. All these attachments are downloaded into a temporary folder. You can obtain the download url, file name and payload stream using the\nDownload (https://playwright.dev/docs/api/class-download)\nobject from the event.\n\nYou can specify where to persist downloaded files using the\ndownloadsPath (https://playwright.dev/docs/api/class-browsertype#browser-type-launch-option-downloads-path)\noption in\nbrowserType.launch() (https://playwright.dev/docs/api/class-browsertype#browser-type-launch)\n.\n\nnote\nDownloaded files are deleted when the browser context that produced them is closed.\n\nHere is the simplest way to handle the file download:\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", "Added before v1.9\n\ndownload.path\n\nReturns path to the downloaded file for a successful download, or throws for a failed/canceled download. The method will wait for the download to finish if necessary. The method throws when connected remotely.\n\nNote that the download's file name is a random GUID, use\ndownload.suggestedFilename() (https://playwright.dev/docs/api/class-download#download-suggested-filename)\nto get suggested file name.\n\nUsage\n\n```\n`awaitdownload.path();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n# (https://playwright.dev/docs/api/class-download#download-path-return)", "If you have no idea what initiates the download, you can still handle the event:\n\n```\n`page.on('download',download=&gt;download.path().then(console.log));`\n```\n\nNote that handling the event forks the control flow and makes the script harder to follow. Your scenario might end while you are downloading a file since your main control flow is not awaiting for this operation to resolve.\n\nnote\nFor uploading files, see the\nuploading files (https://playwright.dev/docs/input#upload-files)\nsection.", "Added before v1.9\n\ndownload.saveAs\n\nCopy the download to a user-specified path. It is safe to call this method while the download is still in progress. Will wait for the download to finish if necessary.\n\nUsage\n\n```\n`awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```\n\nArguments\n\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-download#download-save-as-option-path)\nPath where the download should be copied.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-download#download-save-as-return)", "Added in: v1.13\n\ndownload.cancel\n\nCancels a download. Will not fail if the download is already finished or canceled. Upon successful cancellations,\n`download.failure()`\nwould resolve to\n`'canceled'`\n.\n\nUsage\n\n```\n`awaitdownload.cancel();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-download#download-cancel-return)", 'Added before v1.9\n\ndownload.delete\n\nDeletes the downloaded file. Will wait for the download to finish if necessary.\n\nUsage\n\n```\n`awaitdownload.delete();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-download#download-delete-return)']</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>['Downloaded files are deleted when the browser context that produced them is closed.', 'Playwright uses browser contexts to achieve Test Isolation. Each test has its own Browser Context. Running the test creates a new browser context each time.']</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Downloaded files are stored in a temporary folder by default. You can specify a different location to persist these files by using the `downloadsPath` option in `browserType.launch()`.
+Downloaded files may disappear before you can use them for the following reasons:
+*   **Browser context closure:** All downloaded files belonging to a browser context are automatically deleted when that context is closed.
+*   **Script termination:** If you handle the download event without awaiting the operation, your main control flow might end while the file is still downloading, potentially leading to the context closing and the file being deleted.
+*   **Manual deletion:** The `download.delete()` method can be used to explicitly remove a downloaded file.
+*   **Cancellation:** If a download is canceled, the file may not be available or the `download.path()` method will throw an error.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Downloaded files sit in a temporary folder and belong to whichever context fetched them, so they vanish the instant that context is torn down. Each test gets a freshly created context, so grab anything you need before the test ends.</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0.0007487500000000001</v>
+      </c>
+      <c r="G42" t="n">
+        <v>30834</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.1145038167938931</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.99999999995</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>My manually-created context never produced a video file. How is video capture tied to the context lifecycle?</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>["Playwright Test can record videos for your tests, controlled by the\n`video`\noption in your Playwright config. By default videos are off.\n\n`'off'`\n- Do not record video.\n`'on'`\n- Record video for each test.\n`'retain-on-failure'`\n- Record video for each test, but remove all videos from successful test runs.\n`'on-first-retry'`\n- Record video only when retrying a test for the first time.\n\nVideo files will appear in the test output directory, typically\n`test-results`\n. See\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nfor advanced video configuration.\n\nVideos are saved upon\nbrowser context (https://playwright.dev/docs/browser-contexts)\nclosure at the end of a test. If you create a browser context manually, make sure to await\nbrowserContext.close() (https://playwright.dev/docs/api/class-browsercontext#browser-context-close)\n.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:'on-first-retry',},});`\n```\n```\n`constcontext=awaitbrowser.newContext({recordVideo:{dir:'videos/'}});// Make sure to await close, so that videos are saved.awaitcontext.close();`\n```\n\nYou can also specify video size and annotation. The video size defaults to the viewport size scaled down to fit 800x800. The video of the viewport is placed in the top-left corner of the output video, scaled down to fit if necessary. You may need to set the viewport size to match your desired video size.\n\nWhen\n`show: { actions }`\nis specified, each action will be visually highlighted in the video with the element outline and action title subtitle. The optional\n`duration`\nproperty controls how long each annotation is displayed (defaults to\n`500`\nms).\n\nWhen\n`show: { test }`\nis specified, video will be annotated with the current test information with configurable\n`level`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:{mode:'on-first-retry',size:{width:640,height:480},show:{actions:{duration:500,position:'top-right',fontSize:14,},test:{level:'step',position:'top-left',fontSize:12,}},},},});`\n```\n\nFor multi-page scenarios, you can access the video file associated with the page via the\npage.video() (https://playwright.dev/docs/api/class-page#page-video)\n.\n\n```\n`constpath=awaitpage.video().path();`\n```\n\nnote\nNote that the video is only available after the page or browser context is closed.", "With Playwright you can capture screenshots, record videos as well as traces of your test. By default these are turned off but you can enable them by setting the\n`screenshot`\n,\n`video`\nand\n`trace`\noptions in your\n`playwright.config.js`\nfile.\n\nTrace files, screenshots and videos will appear in the test output directory, typically\n`test-results`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{// Capture screenshot after each test failure.screenshot:'only-on-failure',// Record trace only when retrying a test for the first time.trace:'on-first-retry',// Record video only when retrying a test for the first time.video:'on-first-retry'},});`\n```\n\nOption\nDescription\ntestOptions.screenshot (https://playwright.dev/docs/api/class-testoptions#test-options-screenshot)\nCapture\nscreenshots (https://playwright.dev/docs/screenshots)\nof your test. Options include\n`'off'`\n,\n`'on'`\nand\n`'only-on-failure'`\ntestOptions.trace (https://playwright.dev/docs/api/class-testoptions#test-options-trace)\nPlaywright can produce test traces while running the tests. Later on, you can view the trace and get detailed information about Playwright execution by opening\nTrace Viewer (https://playwright.dev/docs/trace-viewer)\n. Options include:\n`'off'`\n,\n`'on'`\n,\n`'retain-on-failure'`\nand\n`'on-first-retry'`\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nPlaywright can record\nvideos (https://playwright.dev/docs/videos)\nfor your tests. Options include:\n`'off'`\n,\n`'on'`\n,\n`'retain-on-failure'`\nand\n`'on-first-retry'`", 'Added in: v1.10\n\ntestOptions.video\n\nWhether to record video for each test. Defaults to\n`\'off\'`\n.\n\n`\'off\'`\n: Do not record video.\n`\'on\'`\n: Record video for each test.\n`\'retain-on-failure\'`\n: Record video for each test, but remove all videos from successful test runs.\n`\'on-first-retry\'`\n: Record video only when retrying a test for the first time.\n\nTo control video size, pass an object with\n`mode`\nand\n`size`\nproperties. If video size is not specified, it will be equal to\ntestOptions.viewport (https://playwright.dev/docs/api/class-testoptions#test-options-viewport)\nscaled down to fit into 800x800. If\n`viewport`\nis not configured explicitly the video size defaults to 800x450. Actual picture of each page will be scaled down if necessary to fit the specified size.\n\nTo annotate actions in the video, pass\n`show`\nwith\n`action`\nand/or\n`test`\nsub-options. The\n`action`\noption controls visual highlights on interacted elements with an optional\n`delay`\nin milliseconds (defaults to\n`500`\n). The\n`test`\noption controls which test information is displayed as a status overlay.\n\nUsage\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{video:\'on-first-retry\',},});`\n```\n\nLearn more about\nrecording video (https://playwright.dev/docs/test-use-options#recording-options)\n.\n\nType\n\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n| "off" | "on" | "retain-on-failure" | "on-first-retry"\n`mode`\n"off" | "on" | "retain-on-failure" | "on-first-retry"\nVideo recording mode.\n`size`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`width`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n`height`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\nSize of the recorded video. Optional.\n`show`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`actions`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`duration`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nHow long each annotation is displayed in milliseconds. Defaults to\n`500`\n.\n`position`\n"top-left" | "top" | "top-right" | "bottom-left" | "bottom" | "bottom-right"\n(optional)\nPosition of the action title overlay. Defaults to\n`"top-right"`\n.\n`fontSize`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nFont size of the action title in pixels. Defaults to\n`24`\n.\nControls visual annotations on interacted elements.\n`test`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`level`\n"file" | "test" | "step"\n(optional)\nLevel of the detail to include about the current test.\n`position`\n"top-left" | "top" | "top-right" | "bottom-left" | "bottom" | "bottom-right"\n(optional)\nPosition of the test information overlay. Defaults to\n`"top-left"`\n.\n`fontSize`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nFont size of the test information in pixels. Defaults to\n`14`\n.\nControls test information displayed as a status overlay in the video.\nIf specified, visually annotates the video with test information and action highlights.', 'Video | Playwright\n\nWhen browser context is created with the\n`recordVideo`\noption, each page has a video object associated with it.\n\n```\n`console.log(awaitpage.video().path());`\n```', "Added in: v1.10\n\nfixtures.context\n\nIsolated\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\ninstance, created for each test. Since contexts are isolated between each other, every test gets a fresh environment, even when multiple tests run in a single\nBrowser (https://playwright.dev/docs/api/class-browser)\nfor maximum efficiency.\n\nLearn how to\nconfigure context (https://playwright.dev/docs/test-configuration)\nand see\navailable options (https://playwright.dev/docs/api/class-testoptions)\n.\n\nDefault\nfixtures.page (https://playwright.dev/docs/api/class-fixtures#fixtures-page)\nbelongs to this context.\n\nUsage\n\n```\n`test('example test',async({page,context})=&gt;{awaitcontext.route('*external.com/*',route=&gt;route.abort());// ...});`\n```\n\nType\n\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)", "Added in: v1.10\n\nfixtures.page\n\nIsolated\nPage (https://playwright.dev/docs/api/class-page)\ninstance, created for each test. Pages are isolated between tests due to\nfixtures.context (https://playwright.dev/docs/api/class-fixtures#fixtures-context)\nisolation.\n\nThis is the most common fixture used in a test.\n\nUsage\n\n```\n`import{test,expect}from'@playwright/test';test('basic test',async({page})=&gt;{awaitpage.goto('/signin');awaitpage.getByLabel('User Name').fill('user');awaitpage.getByLabel('Password').fill('password');awaitpage.getByText('Sign in').click();// ...});`\n```\n\nType\n\nPage (https://playwright.dev/docs/api/class-page)", 'Added before v1.9\n\nbrowserContext.close\n\nCloses the browser context. All the pages that belong to the browser context will be closed.\n\nnote\nThe default browser context cannot be closed.\n\nUsage\n\n```\n`awaitbrowserContext.close();awaitbrowserContext.close(options);`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`reason`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\nAdded in: v1.40\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-close-option-reason)\nThe reason to be reported to the operations interrupted by the context closure.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-close-return)']</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>['Videos are saved upon browser context (https://playwright.dev/docs/browser-contexts) closure at the end of a test. If you create a browser context manually, make sure to await browserContext.close() (https://playwright.dev/docs/api/class-browsercontext#browser-context-close) .', 'When using Playwright as a Test Runner, browser contexts are created by default. Otherwise, you can create browser contexts manually.']</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Video capture is tied to the browser context lifecycle in the following way:
+*   **Closure Requirement:** Videos are saved only upon the closure of the browser context. If you create a browser context manually, you must explicitly call and `await` `browserContext.close()` to ensure the video file is saved.
+*   **Availability:** The video file is only available after the page or browser context has been closed.
+If you are creating a context manually, ensure your code follows this pattern:
+```javascript
+const context = await browser.newContext({ recordVideo: { dir: 'videos/' } });
+// Perform your test actions here
+await context.close(); // This saves the video
+```</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Video is flushed when the browser context closes. With the test runner that happens automatically, but if you created the context yourself you must await context.close(), or the file won't be written.</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0011145</v>
+      </c>
+      <c r="G43" t="n">
+        <v>48253</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.163265306122449</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>We rolled our own visual checks: capture a PNG, compare it byte-for-byte with a committed file, fail on any difference. It's unusable — it fails on the first run of any new test, it fails constantly on CI with what look like anti-aliasing differences, and there's no way to accept a legitimate design change short of regenerating files by hand. What does the built-in comparison do differently at each of those three points?</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>['Sometimes you need to update the reference screenshot, for example when the page has changed. Do this with the\n`--update-snapshots`\nflag.\n\n```\n`npx playwrighttest--update-snapshots`\n```', "Configuration for the expect assertion library.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({expect:{// Maximum time expect() should wait for the condition to be met.timeout:5000,toHaveScreenshot:{// An acceptable amount of pixels that could be different, unset by default.maxDiffPixels:10,},toMatchSnapshot:{// An acceptable ratio of pixels that are different to the// total amount of pixels, between 0 and 1.maxDiffPixelRatio:0.1,},},});`\n```\n\nOption\nDescription\ntestConfig.expect (https://playwright.dev/docs/api/class-testconfig#test-config-expect)\nWeb first assertions (https://playwright.dev/docs/test-assertions)\nlike\n`expect(locator).toHaveText()`\nhave a separate timeout of 5 seconds by default. This is the maximum time the\n`expect()`\nshould wait for the condition to be met. Learn more about\ntest and expect timeouts (https://playwright.dev/docs/test-timeouts)\nand how to set them for a single test.\nexpect(page).toHaveScreenshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\nConfiguration for the\n`expect(locator).toHaveScreenshot()`\nmethod.\nexpect(value).toMatchSnapshot() (https://playwright.dev/docs/api/class-snapshotassertions#snapshot-assertions-to-match-snapshot-1)\nConfiguration for the\n`expect(locator).toMatchSnapshot()`\nmethod.", "Playwright Test includes the ability to produce and visually compare screenshots using\n`await expect(page).toHaveScreenshot()`\n. On first execution, Playwright test will generate reference screenshots. Subsequent runs will compare against the reference.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('example test',async({page})=&gt;{awaitpage.goto('https://playwright.dev');awaitexpect(page).toHaveScreenshot();});`\n```\n\nwarning\nBrowser rendering can vary based on the host OS, version, settings, hardware, power source (battery vs. power adapter), headless mode, and other factors. For consistent screenshots, run tests in the same environment where the baseline screenshots were generated.", "Playwright Test uses the\npixelmatch (https://github.com/mapbox/pixelmatch)\nlibrary. You can\npass various options (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\nto modify its behavior:\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('example test',async({page})=&gt;{awaitpage.goto('https://playwright.dev');awaitexpect(page).toHaveScreenshot({maxDiffPixels:100});});`\n```\n\nIf you'd like to share the default value among all the tests in the project, you can specify it in the playwright config, either globally or per project:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({expect:{toHaveScreenshot:{maxDiffPixels:100},},});`\n```", "You can apply a custom stylesheet to your page while taking screenshot. This allows filtering out dynamic or volatile elements, hence improving the screenshot determinism.\n\nscreenshot.css\n```\n`iframe{visibility:hidden;}`\n```\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('example test',async({page})=&gt;{awaitpage.goto('https://playwright.dev');awaitexpect(page).toHaveScreenshot({stylePath:path.join(__dirname,'screenshot.css')});});`\n```\n\nIf you'd like to share the default value among all the tests in the project, you can specify it in the playwright config, either globally or per project:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({expect:{toHaveScreenshot:{stylePath:'./screenshot.css'},},});`\n```", "Added in: v1.22\n\nsnapshotAssertions.toMatchSnapshot(name)\n\ncaution\nTo compare screenshots, use\nexpect(page).toHaveScreenshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\ninstead.\n\nEnsures that passed value, either a\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\nor a\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\n, matches the expected snapshot stored in the test snapshots directory.\n\nUsage\n\n```\n`// Basic usage.expect(awaitpage.screenshot()).toMatchSnapshot('landing-page.png');// Pass options to customize the snapshot comparison and have a generated name.expect(awaitpage.screenshot()).toMatchSnapshot('landing-page.png',{maxDiffPixels:27,// allow no more than 27 different pixels.});// Configure image matching threshold.expect(awaitpage.screenshot()).toMatchSnapshot('landing-page.png',{threshold:0.3});// Bring some structure to your snapshot files by passing file path segments.expect(awaitpage.screenshot()).toMatchSnapshot(['landing','step2.png']);expect(awaitpage.screenshot()).toMatchSnapshot(['landing','step3.png']);`\n```\n\nLearn more about\nvisual comparisons (https://playwright.dev/docs/test-snapshots)\n.\n\nNote that matching snapshots only work with Playwright test runner.\n\nArguments\n\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n# (https://playwright.dev/docs/api/class-snapshotassertions#snapshot-assertions-to-match-snapshot-1-option-name)\nSnapshot name.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`maxDiffPixelRatio`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-snapshotassertions#snapshot-assertions-to-match-snapshot-1-option-max-diff-pixel-ratio)\nAn acceptable ratio of pixels that are different to the total amount of pixels, between\n`0`\nand\n`1`\n. Default is configurable with\n`TestConfig.expect`\n. Unset by default.\n`maxDiffPixels`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-snapshotassertions#snapshot-assertions-to-match-snapshot-1-option-max-diff-pixels)\nAn acceptable amount of pixels that could be different. Default is configurable with\n`TestConfig.expect`\n. Unset by default.\n`threshold`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-snapshotassertions#snapshot-assertions-to-match-snapshot-1-option-threshold)\nAn acceptable perceived color difference in the\nYIQ color space (https://en.wikipedia.org/wiki/YIQ)\nbetween the same pixel in compared images, between zero (strict) and one (lax), default is configurable with\n`TestConfig.expect`\n. Defaults to\n`0.2`\n.", "Added in: v1.22\n\nsnapshotAssertions.toMatchSnapshot(options)\n\ncaution\nTo compare screenshots, use\nexpect(page).toHaveScreenshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-2)\ninstead.\n\nEnsures that passed value, either a\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\nor a\nBuffer (https://nodejs.org/api/buffer.html#buffer_class_buffer)\n, matches the expected snapshot stored in the test snapshots directory.\n\nUsage\n\n```\n`// Basic usage and the file name is derived from the test name.expect(awaitpage.screenshot()).toMatchSnapshot();// Pass options to customize the snapshot comparison and have a generated name.expect(awaitpage.screenshot()).toMatchSnapshot({maxDiffPixels:27,// allow no more than 27 different pixels.});// Configure image matching threshold and snapshot name.expect(awaitpage.screenshot()).toMatchSnapshot({name:'landing-page.png',threshold:0.3,});`\n```\n\nLearn more about\nvisual comparisons (https://playwright.dev/docs/test-snapshots)\n.\n\nNote that matching snapshots only work with Playwright test runner.\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`maxDiffPixelRatio`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-snapshotassertions#snapshot-assertions-to-match-snapshot-2-option-max-diff-pixel-ratio)\nAn acceptable ratio of pixels that are different to the total amount of pixels, between\n`0`\nand\n`1`\n. Default is configurable with\n`TestConfig.expect`\n. Unset by default.\n`maxDiffPixels`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-snapshotassertions#snapshot-assertions-to-match-snapshot-2-option-max-diff-pixels)\nAn acceptable amount of pixels that could be different. Default is configurable with\n`TestConfig.expect`\n. Unset by default.\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n(optional)\n# (https://playwright.dev/docs/api/class-snapshotassertions#snapshot-assertions-to-match-snapshot-2-option-name)\nSnapshot name. If not passed, the test name and ordinals are used when called multiple times.\n`threshold`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-snapshotassertions#snapshot-assertions-to-match-snapshot-2-option-threshold)\nAn acceptable perceived color difference in the\nYIQ color space (https://en.wikipedia.org/wiki/YIQ)\nbetween the same pixel in compared images, between zero (strict) and one (lax), default is configurable with\n`TestConfig.expect`\n. Defaults to\n`0.2`\n."]</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>["Error: A snapshot doesn't exist at example.spec.ts-snapshots/example-test-1-chromium-darwin.png, writing actual.", 'chromium-darwin - the browser name and the platform. Screenshots differ between browsers and platforms due to different rendering, fonts and more, so you will need different snapshots for them. If you use multiple projects in your configuration file, project name will be used instead of chromium.', 'Sometimes you need to update the reference screenshot, for example when the page has changed. Do this with the --update-snapshots flag. npx playwright test --update-snapshots', 'export default defineConfig({ expect: { toHaveScreenshot: { maxDiffPixels: 100 }, }, });']</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>The built-in `expect(page).toHaveScreenshot()` method addresses your three points as follows:
+*   **Failing on the first run:** Playwright Test automatically generates the reference screenshot on the first execution. You do not need to manually create or commit files before the first run.
+*   **Failing on CI due to minor differences:** Unlike a byte-for-byte comparison, Playwright uses the `pixelmatch` library, which allows for configurable tolerance. You can prevent failures from minor rendering variations (like anti-aliasing) by setting `maxDiffPixels` (an acceptable number of different pixels) or `maxDiffPixelRatio` (an acceptable ratio of different pixels) in your `playwright.config.ts` or per test. Additionally, you can adjust the `threshold` (an acceptable perceived color difference in the YIQ color space) to make the comparison less strict.
+*   **Accepting legitimate design changes:** You can update reference screenshots by running the test with the `--update-snapshots` flag (e.g., `npx playwright test --update-snapshots`). This replaces the existing baseline with the new screenshot.
+To improve overall determinism and reduce false positives, you can also use the `stylePath` option to apply a custom stylesheet that hides volatile or dynamic elements during the screenshot process.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Each of your three problems is a thing the built-in assertion already handles, because capturing an image and asserting on one are different operations. page.screenshot() just returns a buffer; expect(page).toHaveScreenshot() is a full comparison assertion. On first run there is no baseline, so instead of failing meaninglessly it takes screenshots until two consecutive ones match — which also settles animation and rendering noise — saves the result as the reference and reports that it wrote it; you commit that file. On CI, the baseline is keyed by environment: the snapshot name like example-test-1-chromium-darwin.png encodes the browser and platform (the project name replaces the browser when you use multiple projects) precisely because rendering, fonts and anti-aliasing differ across platforms, so Linux CI compares against its own baseline rather than your macOS one. And byte-exactness isn't required: `maxDiffPixels` (per assertion or globally under `expect: { toHaveScreenshot: ... }`) sets an allowance. When a change is intentional you re-baseline with `npx playwright test --update-snapshots` rather than editing files.</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0.0012735</v>
+      </c>
+      <c r="G44" t="n">
+        <v>36515</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.175531914893617</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.1896551724137931</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.4206349206208995</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>In one test I need an admin and a regular user acting at the same time. How do I get two authenticated sessions side by side?</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>["Playwright can create multiple browser contexts within a single scenario. This is useful when you want to test for multi-user functionality, like a chat.\n\nTest\nLibrary\n```\n`import{test}from'@playwright/test';test('admin and user',async({browser})=&gt;{// Create two isolated browser contextsconstadminContext=awaitbrowser.newContext();constuserContext=awaitbrowser.newContext();// Create pages and interact with contexts independentlyconstadminPage=awaitadminContext.newPage();constuserPage=awaituserContext.newPage();});`\n```\n```\n`const{chromium}=require('playwright');// Create a Chromium browser instanceconstbrowser=awaitchromium.launch();// Create two isolated browser contextsconstuserContext=awaitbrowser.newContext();constadminContext=awaitbrowser.newContext();// Create pages and interact with contexts independentlyconstadminPage=awaitadminContext.newPage();constuserPage=awaituserContext.newPage();`\n```", 'When to use\n\nYou need to test how multiple authenticated roles interact together, in a single test.\n\nDetails\n\nUse multiple\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\ns and\nPage (https://playwright.dev/docs/api/class-page)\ns with different storage states in the same test.\n\ntests/example.spec.ts\n```\n`import{test}from\'@playwright/test\';test(\'admin and user\',async({browser})=&gt;{// adminContext and all pages inside, including adminPage, are signed in as "admin".constadminContext=awaitbrowser.newContext({storageState:\'playwright/.auth/admin.json\'});constadminPage=awaitadminContext.newPage();// userContext and all pages inside, including userPage, are signed in as "user".constuserContext=awaitbrowser.newContext({storageState:\'playwright/.auth/user.json\'});constuserPage=awaituserContext.newPage();// ... interact with both adminPage and userPage ...awaitadminContext.close();awaituserContext.close();});`\n```', 'When to use\n\nYou need to test how multiple authenticated roles interact together, in a single test.\n\nDetails\n\nYou can introduce fixtures that will provide a page authenticated as each role.\n\nBelow is an example that\ncreates fixtures (https://playwright.dev/docs/test-fixtures#creating-a-fixture)\nfor two\nPage Object Models (https://playwright.dev/docs/pom)\n- admin POM and user POM. It assumes\n`adminStorageState.json`\nand\n`userStorageState.json`\nfiles were created in the global setup.\n\nplaywright/fixtures.ts\n```\n`import{testasbase,typePage,typeLocator}from\'@playwright/test\';// Page Object Model for the "admin" page.// Here you can add locators and helper methods specific to the admin page.classAdminPage{// Page signed in as "admin".page:Page;// Example locator pointing to "Welcome, Admin" greeting.greeting:Locator;constructor(page:Page){this.page=page;this.greeting=page.locator(\'#greeting\');}}// Page Object Model for the "user" page.// Here you can add locators and helper methods specific to the user page.classUserPage{// Page signed in as "user".page:Page;// Example locator pointing to "Welcome, User" greeting.greeting:Locator;constructor(page:Page){this.page=page;this.greeting=page.locator(\'#greeting\');}}// Declare the types of your fixtures.typeMyFixtures={adminPage:AdminPage;userPage:UserPage;};export*from\'@playwright/test\';exportconsttest=base.extend&lt;MyFixtures&gt;({adminPage:async({browser},use)=&gt;{constcontext=awaitbrowser.newContext({storageState:\'playwright/.auth/admin.json\'});constadminPage=newAdminPage(awaitcontext.newPage());awaituse(adminPage);awaitcontext.close();},userPage:async({browser},use)=&gt;{constcontext=awaitbrowser.newContext({storageState:\'playwright/.auth/user.json\'});constuserPage=newUserPage(awaitcontext.newPage());awaituse(userPage);awaitcontext.close();},});`\n```\n\ntests/example.spec.ts\n```\n`// Import test with our new fixtures.import{test,expect}from\'../playwright/fixtures\';// Use adminPage and userPage fixtures in the test.test(\'admin and user\',async({adminPage,userPage})=&gt;{// ... interact with both adminPage and userPage ...awaitexpect(adminPage.greeting).toHaveText(\'Welcome, Admin\');awaitexpect(userPage.greeting).toHaveText(\'Welcome, User\');});`\n```', "Web apps use cookie-based or token-based authentication, where authenticated state is stored as\ncookies (https://developer.mozilla.org/en-US/docs/Web/HTTP/Cookies)\n. Playwright provides\napiRequestContext.storageState() (https://playwright.dev/docs/api/class-apirequestcontext#api-request-context-storage-state)\nmethod that can be used to retrieve storage state from an authenticated context and then create new contexts with that state.\n\nStorage state is interchangeable between\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nand\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n. You can use it to log in via API calls and then create a new context with cookies already there. The following code snippet retrieves state from an authenticated\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nand creates a new\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nwith that state.\n\n```\n`constrequestContext=awaitrequest.newContext({httpCredentials:{username:'user',password:'passwd'}});awaitrequestContext.get(`https://api.example.com/login`);// Save storage state into the file.awaitrequestContext.storageState({path:'state.json'});// Create a new context with the saved storage state.constcontext=awaitbrowser.newContext({storageState:'state.json'});`\n```", "BrowserContext | Playwright\n\nBrowserContexts provide a way to operate multiple independent browser sessions.\n\nIf a page opens another page, e.g. with a\n`window.open`\ncall, the popup will belong to the parent page's browser context.\n\nPlaywright allows creating isolated non-persistent browser contexts with\nbrowser.newContext() (https://playwright.dev/docs/api/class-browser#browser-new-context)\nmethod. Non-persistent browser contexts don't write any browsing data to disk.\n\n```\n`// Create a new incognito browser contextconstcontext=awaitbrowser.newContext();// Create a new page inside context.constpage=awaitcontext.newPage();awaitpage.goto('https://example.com');// Dispose context once it's no longer needed.awaitcontext.close();`\n```", "There are two types of\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\n:\n\nassociated with a\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\nisolated instance, created via\napiRequest.newContext() (https://playwright.dev/docs/api/class-apirequest#api-request-new-context)\n\nThe main difference is that\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\naccessible via\nbrowserContext.request (https://playwright.dev/docs/api/class-browsercontext#browser-context-request)\nand\npage.request (https://playwright.dev/docs/api/class-page#page-request)\nwill populate request's\n`Cookie`\nheader from the browser context and will automatically update browser cookies if\nAPIResponse (https://playwright.dev/docs/api/class-apiresponse)\nhas\n`Set-Cookie`\nheader:\n\n```\n`test('context request will share cookie storage with its browser context',async({page,context,})=&gt;{awaitcontext.route('https://www.github.com/',asyncroute=&gt;{// Send an API request that shares cookie storage with the browser context.constresponse=awaitcontext.request.fetch(route.request());constresponseHeaders=response.headers();// The response will have 'Set-Cookie' header.constresponseCookies=newMap(responseHeaders['set-cookie'].split('\\n').map(c=&gt;c.split(';',2)[0].split('=')));// The response will have 3 cookies in 'Set-Cookie' header.expect(responseCookies.size).toBe(3);constcontextCookies=awaitcontext.cookies();// The browser context will already contain all the cookies from the API response.expect(newMap(contextCookies.map(({name,value})=&gt;[name,value]))).toEqual(responseCookies);awaitroute.fulfill({response,headers:{...responseHeaders,foo:'bar'},});});awaitpage.goto('https://www.github.com/');});`\n```\n\nIf you don't want\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nto use and update cookies from the browser context, you can manually create a new instance of\nAPIRequestContext (https://playwright.dev/docs/api/class-apirequestcontext)\nwhich will have its own isolated cookies:\n\n```\n`test('global context request has isolated cookie storage',async({page,context,browser,playwright})=&gt;{// Create a new instance of APIRequestContext with isolated cookie storage.constrequest=awaitplaywright.request.newContext();awaitcontext.route('https://www.github.com/',asyncroute=&gt;{constresponse=awaitrequest.fetch(route.request());constresponseHeaders=response.headers();constresponseCookies=newMap(responseHeaders['set-cookie'].split('\\n').map(c=&gt;c.split(';',2)[0].split('=')));// The response will have 3 cookies in 'Set-Cookie' header.expect(responseCookies.size).toBe(3);constcontextCookies=awaitcontext.cookies();// The browser context will not have any cookies from the isolated API request.expect(contextCookies.length).toBe(0);// Manually export cookie storage.conststorageState=awaitrequest.storageState();// Create a new context and initialize it with the cookies from the global request.constbrowserContext2=awaitbrowser.newContext({storageState});constcontextCookies2=awaitbrowserContext2.cookies();// The new browser context will already contain all the cookies from the API response.expect(newMap(contextCookies2.map(({name,value})=&gt;[name,value]))).toEqual(responseCookies);awaitroute.fulfill({response,headers:{...responseHeaders,foo:'bar'},});});awaitpage.goto('https://www.github.com/');awaitrequest.dispose();});`\n```", "When to use\n\nYou have more than one role in your end to end tests, but you can reuse accounts across all tests.\n\nDetails\n\nWe will authenticate multiple times in the setup project.\n\ntests/auth.setup.ts\n```\n`import{testassetup,expect}from'@playwright/test';constadminFile='playwright/.auth/admin.json';setup('authenticate as admin',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('admin');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:adminFile});});constuserFile='playwright/.auth/user.json';setup('authenticate as user',async({page})=&gt;{// Perform authentication steps. Replace these actions with your own.awaitpage.goto('https://github.com/login');awaitpage.getByLabel('Username or email address').fill('user');awaitpage.getByLabel('Password').fill('password');awaitpage.getByRole('button',{name:'Sign in'}).click();// Wait until the page receives the cookies.//// Sometimes login flow sets cookies in the process of several redirects.// Wait for the final URL to ensure that the cookies are actually set.awaitpage.waitForURL('https://github.com/');// Alternatively, you can wait until the page reaches a state where all cookies are set.awaitexpect(page.getByRole('button',{name:'View profile and more'})).toBeVisible();// End of authentication steps.awaitpage.context().storageState({path:userFile});});`\n```\n\nAfter that, specify\n`storageState`\nfor each test file or test group,\ninstead of\nsetting it in the config.\n\ntests/example.spec.ts\n```\n`import{test}from'@playwright/test';test.use({storageState:'playwright/.auth/admin.json'});test('admin test',async({page})=&gt;{// page is authenticated as admin});test.describe(()=&gt;{test.use({storageState:'playwright/.auth/user.json'});test('user test',async({page})=&gt;{// page is authenticated as a user});});`\n```\n\nSee also about\nauthenticating in the UI mode (https://playwright.dev/docs/auth#authenticating-in-ui-mode)\n."]</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>['Use multiple BrowserContext (https://playwright.dev/docs/api/class-browsercontext) s and Page (https://playwright.dev/docs/api/class-page) s with different storage states in the same test.', 'Playwright can create multiple browser contexts within a single scenario. This is useful when you want to test for multi-user functionality, like a chat.']</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>To get two authenticated sessions side by side in a single test, you should use multiple `BrowserContext` instances, each initialized with a different `storageState`.
+### Recommended Approach
+The documentation recommends using multiple `BrowserContext` and `Page` objects with different storage states within the same test. You can achieve this by creating contexts using `browser.newContext()` and passing the path to the respective authentication files:
+```typescript
+test('admin and user', async ({ browser }) =&gt; {
+  // adminContext and all pages inside are signed in as "admin"
+  const adminContext = await browser.newContext({ storageState: 'playwright/.auth/admin.json' });
+  const adminPage = await adminContext.newPage();
+  // userContext and all pages inside are signed in as "user"
+  const userContext = await browser.newContext({ storageState: 'playwright/.auth/user.json' });
+  const userPage = await userContext.newPage();
+  // ... interact with both adminPage and userPage ...
+  await adminContext.close();
+  await userContext.close();
+});
+```
+### Alternative Approach: POM Fixtures
+If you prefer a more structured approach, you can define custom fixtures that handle the creation and disposal of these authenticated contexts. This allows you to inject the authenticated pages directly into your test:
+1.  **Define the fixtures** (e.g., in `playwright/fixtures.ts`):
     ```typescript
-    import { test as base } from '@playwright/test';
-    import { TodoPage } from './todo-page';
-    type MyFixtures = {
-      todoPage: TodoPage;
-    };
     export const test = base.extend&lt;MyFixtures&gt;({
-      todoPage: async ({ page }, use) =&gt; {
-        const todoPage = new TodoPage(page);
-        // Setup:
-        await todoPage.goto();
-        await todoPage.addToDo('item1');
-        // Provide the fixture to the test:
-        await use(todoPage);
-        // Teardown:
-        await todoPage.removeAll();
+      adminPage: async ({ browser }, use) =&gt; {
+        const context = await browser.newContext({ storageState: 'playwright/.auth/admin.json' });
+        const adminPage = new AdminPage(await context.newPage());
+        await use(adminPage);
+        await context.close();
+      },
+      userPage: async ({ browser }, use) =&gt; {
+        const context = await browser.newContext({ storageState: 'playwright/.auth/user.json' });
+        const userPage = new UserPage(await context.newPage());
+        await use(userPage);
+        await context.close();
       },
     });
     ```
-2.  **Use the fixture in your tests:** Import the extended `test` object into your test files. You can then request the page object fixture as an argument in your test function. Playwright will automatically set up the fixture before the test runs and tear it down afterward.
-    **Example:**
+2.  **Use the fixtures in your test**:
     ```typescript
-    import { test } from './my-test';
-    test('should add an item', async ({ todoPage }) =&gt; {
-      await todoPage.addToDo('my item');
-      // ...
+    import { test, expect } from '../playwright/fixtures';
+    test('admin and user', async ({ adminPage, userPage }) =&gt; {
+      await expect(adminPage.greeting).toHaveText('Welcome, Admin');
+      await expect(userPage.greeting).toHaveText('Welcome, User');
     });
     ```
-### Why use this approach?
-*   **Encapsulation:** Setup and teardown logic are contained within the fixture.
-*   **On-demand:** Playwright only sets up the fixtures required by the specific test.
-*   **Reusability:** You can define the fixtures once and use them across multiple test files.
-*   **Composability:** Fixtures can depend on other fixtures to provide complex behaviors.</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Wrap the POM in a fixture created with test.extend(): the fixture builds the page object (and can do setup/teardown around it), and any test just lists it as an argument. Fixtures are reusable across files, so every spec shares it.</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>0.009241249999999999</v>
-      </c>
-      <c r="G40" t="n">
-        <v>33805</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="J40" t="n">
-        <v>5</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.08239700374531835</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.99999999995</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Before a click, what does Playwright verify, and how does that relate to the waiting a plain click already does?</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>['Auto-waiting | Playwright', 'Playwright performs a range of actionability checks on the elements before making actions to ensure these actions behave as expected. It auto-waits for all the relevant checks to pass and only then performs the requested action. If the required checks do not pass within the given\n`timeout`\n, action fails with the\n`TimeoutError`\n.\n\nFor example, for\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\n, Playwright will ensure that:\n\nlocator resolves to exactly one element\nelement is\nVisible (https://playwright.dev/docs/actionability#visible)\nelement is\nStable (https://playwright.dev/docs/actionability#stable)\n, as in not animating or completed animation\nelement\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\n, as in not obscured by other elements\nelement is\nEnabled (https://playwright.dev/docs/actionability#enabled)\n\nHere is the complete list of actionability checks performed for each action:\n\nAction\nVisible (https://playwright.dev/docs/actionability#visible)\nStable (https://playwright.dev/docs/actionability#stable)\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\nEnabled (https://playwright.dev/docs/actionability#enabled)\nEditable (https://playwright.dev/docs/actionability#editable)\nlocator.check() (https://playwright.dev/docs/api/class-locator#locator-check)\nYes\nYes\nYes\nYes\n-\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nYes\nYes\nYes\nYes\n-\nlocator.dblclick() (https://playwright.dev/docs/api/class-locator#locator-dblclick)\nYes\nYes\nYes\nYes\n-\nlocator.setChecked() (https://playwright.dev/docs/api/class-locator#locator-set-checked)\nYes\nYes\nYes\nYes\n-\nlocator.tap() (https://playwright.dev/docs/api/class-locator#locator-tap)\nYes\nYes\nYes\nYes\n-\nlocator.uncheck() (https://playwright.dev/docs/api/class-locator#locator-uncheck)\nYes\nYes\nYes\nYes\n-\nlocator.hover() (https://playwright.dev/docs/api/class-locator#locator-hover)\nYes\nYes\nYes\n-\n-\nlocator.dragTo() (https://playwright.dev/docs/api/class-locator#locator-drag-to)\nYes\nYes\nYes\n-\n-\nlocator.screenshot() (https://playwright.dev/docs/api/class-locator#locator-screenshot)\nYes\nYes\n-\n-\n-\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\nYes\n-\n-\nYes\nYes\nlocator.clear() (https://playwright.dev/docs/api/class-locator#locator-clear)\nYes\n-\n-\nYes\nYes\nlocator.selectOption() (https://playwright.dev/docs/api/class-locator#locator-select-option)\nYes\n-\n-\nYes\n-\nlocator.selectText() (https://playwright.dev/docs/api/class-locator#locator-select-text)\nYes\n-\n-\n-\n-\nlocator.scrollIntoViewIfNeeded() (https://playwright.dev/docs/api/class-locator#locator-scroll-into-view-if-needed)\n-\nYes\n-\n-\n-\nlocator.blur() (https://playwright.dev/docs/api/class-locator#locator-blur)\n-\n-\n-\n-\n-\nlocator.dispatchEvent() (https://playwright.dev/docs/api/class-locator#locator-dispatch-event)\n-\n-\n-\n-\n-\nlocator.focus() (https://playwright.dev/docs/api/class-locator#locator-focus)\n-\n-\n-\n-\n-\nlocator.press() (https://playwright.dev/docs/api/class-locator#locator-press)\n-\n-\n-\n-\n-\nlocator.pressSequentially() (https://playwright.dev/docs/api/class-locator#locator-press-sequentially)\n-\n-\n-\n-\n-\nlocator.setInputFiles() (https://playwright.dev/docs/api/class-locator#locator-set-input-files)\n-\n-\n-\n-\n-', 'Locators | Playwright', 'Element is considered visible when it has non-empty bounding box and does not have\n`visibility:hidden`\ncomputed style.\n\nNote that according to this definition:\n\nElements of zero size\nare not\nconsidered visible.\nElements with\n`display:none`\nare not\nconsidered visible.\nElements with\n`opacity:0`\nare\nconsidered visible.', 'Element is considered stable when it has maintained the same bounding box for at least two consecutive animation frames.', 'Element is considered receiving pointer events when it is the hit target of the pointer event at the action point. For example, when clicking at the point\n`(10;10)`\n, Playwright checks whether some other element (usually an overlay) will instead capture the click at\n`(10;10)`\n.\n\nFor example, consider a scenario where Playwright will click\n`Sign Up`\nbutton regardless of when the\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\ncall was made:\n\npage is checking that user name is unique and\n`Sign Up`\nbutton is disabled;\nafter checking with the server, the disabled\n`Sign Up`\nbutton is replaced with another one that is now enabled.', 'Element is considered enabled when it is\nnot disabled\n.\n\nElement is\ndisabled\nwhen:\n\nit is a\n`&lt;button&gt;`\n,\n`&lt;select&gt;`\n,\n`&lt;input&gt;`\n,\n`&lt;textarea&gt;`\n,\n`&lt;option&gt;`\nor\n`&lt;optgroup&gt;`\nwith a\n`[disabled]`\nattribute;\nit is a\n`&lt;button&gt;`\n,\n`&lt;select&gt;`\n,\n`&lt;input&gt;`\n,\n`&lt;textarea&gt;`\n,\n`&lt;option&gt;`\nor\n`&lt;optgroup&gt;`\nthat is a part of a\n`&lt;fieldset&gt;`\nwith a\n`[disabled]`\nattribute;\nit is a descendant of an element with\n`[aria-disabled=true]`\nattribute.']</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>['Playwright performs a range of actionability checks on the elements before making actions to ensure these actions behave as expected. It auto-waits for all the relevant checks to pass and only then performs the requested action. If the required checks do not pass within the given timeout , action fails with the TimeoutError .', 'wait for element with given selector to be in DOM']</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Before performing a `locator.click()`, Playwright verifies the following actionability checks:
-*   **Resolution:** The locator must resolve to exactly one element.
-*   **Visible:** The element must have a non-empty bounding box and not have a `visibility:hidden` computed style.
-*   **Stable:** The element must maintain the same bounding box for at least two consecutive animation frames (i.e., it is not animating).
-*   **Receives Events:** The element must be the hit target of the pointer event at the action point (i.e., it is not obscured by other elements).
-*   **Enabled:** The element must not be disabled (e.g., it does not have a `[disabled]` attribute, is not part of a disabled `&lt;fieldset&gt;`, or is not a descendant of an element with `[aria-disabled=true]`).
-Regarding the relationship to waiting, Playwright performs these checks automatically as part of its "auto-waiting" mechanism. It waits for all of these relevant checks to pass before executing the click. If these checks do not pass within the specified `timeout`, the action fails with a `TimeoutError`.</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>A click runs actionability checks — attached, visible, stable, receives pointer events, enabled — and auto-waits for them. The pointer methods bake that same sequence in (down to scrolling into view), so you rarely need explicit waits.</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>0.00817675</v>
-      </c>
-      <c r="G41" t="n">
-        <v>30072</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J41" t="n">
-        <v>5</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.49999999995</v>
-      </c>
-      <c r="N41" t="n">
+Both approaches assume that the `storageState` files (e.g., `admin.json` and `user.json`) have been previously created, typically during a global setup process.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Open two browser contexts in the same test, each seeded with a different storageState — one admin, one user — and drive their pages independently. Multiple contexts in one scenario is exactly how Playwright models multi-user features like chat, and they stay isolated.</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0.0018405</v>
+      </c>
+      <c r="G45" t="n">
+        <v>38829</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Where do downloaded files go, and why might they disappear before I can use them?</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>["Download | Playwright\n\nDownload (https://playwright.dev/docs/api/class-download)\nobjects are dispatched by page via the\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent.\n\nAll the downloaded files belonging to the browser context are deleted when the browser context is closed.\n\nDownload event is emitted once the download starts. Download path becomes available once download completes.\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", 'Downloads | Playwright', "For every attachment downloaded by the page,\npage.on('download') (https://playwright.dev/docs/api/class-page#page-event-download)\nevent is emitted. All these attachments are downloaded into a temporary folder. You can obtain the download url, file name and payload stream using the\nDownload (https://playwright.dev/docs/api/class-download)\nobject from the event.\n\nYou can specify where to persist downloaded files using the\ndownloadsPath (https://playwright.dev/docs/api/class-browsertype#browser-type-launch-option-downloads-path)\noption in\nbrowserType.launch() (https://playwright.dev/docs/api/class-browsertype#browser-type-launch)\n.\n\nnote\nDownloaded files are deleted when the browser context that produced them is closed.\n\nHere is the simplest way to handle the file download:\n\n```\n`// Start waiting for download before clicking. Note no await.constdownloadPromise=page.waitForEvent('download');awaitpage.getByText('Download file').click();constdownload=awaitdownloadPromise;// Wait for the download process to complete and save the downloaded file somewhere.awaitdownload.saveAs('/path/to/save/at/'+download.suggestedFilename());`\n```", "If you have no idea what initiates the download, you can still handle the event:\n\n```\n`page.on('download',download=&gt;download.path().then(console.log));`\n```\n\nNote that handling the event forks the control flow and makes the script harder to follow. Your scenario might end while you are downloading a file since your main control flow is not awaiting for this operation to resolve.\n\nnote\nFor uploading files, see the\nuploading files (https://playwright.dev/docs/input#upload-files)\nsection."]</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>['Downloaded files are deleted when the browser context that produced them is closed.', 'Playwright uses browser contexts to achieve Test Isolation. Each test has its own Browser Context. Running the test creates a new browser context each time.']</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Downloaded files are initially stored in a temporary folder. You can specify a different location to persist these files by using the `downloadsPath` option in `browserType.launch()`.
-Files may disappear before you can use them because all downloaded files belonging to a browser context are deleted when that context is closed. Additionally, if you handle the download event using `page.on('download')` without awaiting the operation, your script scenario might end while the download is still in progress, potentially leading to the context closing and the files being deleted.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Downloaded files sit in a temporary folder and belong to whichever context fetched them, so they vanish the instant that context is torn down. Each test gets a freshly created context, so grab anything you need before the test ends.</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>0.007493499999999999</v>
-      </c>
-      <c r="G42" t="n">
-        <v>28974</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="J42" t="n">
-        <v>5</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.1685393258426966</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.8333333332916666</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>My manually-created context never produced a video file. How is video capture tied to the context lifecycle?</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>['Video | Playwright\n\nWhen browser context is created with the\n`recordVideo`\noption, each page has a video object associated with it.\n\n```\n`console.log(awaitpage.video().path());`\n```', 'Videos | Playwright', "Playwright Test can record videos for your tests, controlled by the\n`video`\noption in your Playwright config. By default videos are off.\n\n`'off'`\n- Do not record video.\n`'on'`\n- Record video for each test.\n`'retain-on-failure'`\n- Record video for each test, but remove all videos from successful test runs.\n`'on-first-retry'`\n- Record video only when retrying a test for the first time.\n\nVideo files will appear in the test output directory, typically\n`test-results`\n. See\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nfor advanced video configuration.\n\nVideos are saved upon\nbrowser context (https://playwright.dev/docs/browser-contexts)\nclosure at the end of a test. If you create a browser context manually, make sure to await\nbrowserContext.close() (https://playwright.dev/docs/api/class-browsercontext#browser-context-close)\n.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:'on-first-retry',},});`\n```\n```\n`constcontext=awaitbrowser.newContext({recordVideo:{dir:'videos/'}});// Make sure to await close, so that videos are saved.awaitcontext.close();`\n```\n\nYou can also specify video size and annotation. The video size defaults to the viewport size scaled down to fit 800x800. The video of the viewport is placed in the top-left corner of the output video, scaled down to fit if necessary. You may need to set the viewport size to match your desired video size.\n\nWhen\n`show: { actions }`\nis specified, each action will be visually highlighted in the video with the element outline and action title subtitle. The optional\n`duration`\nproperty controls how long each annotation is displayed (defaults to\n`500`\nms).\n\nWhen\n`show: { test }`\nis specified, video will be annotated with the current test information with configurable\n`level`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:{mode:'on-first-retry',size:{width:640,height:480},show:{actions:{duration:500,position:'top-right',fontSize:14,},test:{level:'step',position:'top-left',fontSize:12,}},},},});`\n```\n\nFor multi-page scenarios, you can access the video file associated with the page via the\npage.video() (https://playwright.dev/docs/api/class-page#page-video)\n.\n\n```\n`constpath=awaitpage.video().path();`\n```\n\nnote\nNote that the video is only available after the page or browser context is closed.", 'Added before v1.9\n\nvideo.path\n\nReturns the file system path this video will be recorded to. The video is guaranteed to be written to the filesystem upon closing the browser context. This method throws when connected remotely.\n\nUsage\n\n```\n`awaitvideo.path();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n# (https://playwright.dev/docs/api/class-video#video-path-return)', 'Added in: v1.11\n\nvideo.saveAs\n\nSaves the video to a user-specified path. It is safe to call this method while the video is still in progress, or after the page has closed. This method waits until the page is closed and the video is fully saved.\n\nUsage\n\n```\n`awaitvideo.saveAs(path);`\n```\n\nArguments\n\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-video#video-save-as-option-path)\nPath where the video should be saved.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-video#video-save-as-return)', 'Configuration (use) | Playwright']</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>['Videos are saved upon browser context (https://playwright.dev/docs/browser-contexts) closure at the end of a test. If you create a browser context manually, make sure to await browserContext.close() (https://playwright.dev/docs/api/class-browsercontext#browser-context-close) .', 'When using Playwright as a Test Runner, browser contexts are created by default. Otherwise, you can create browser contexts manually.']</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Video capture is tied to the browser context lifecycle because videos are saved upon the closure of the browser context at the end of a test. 
-If you create a browser context manually, you must `await browserContext.close()` to ensure the video is saved to the filesystem. The video is guaranteed to be written to the filesystem only upon closing the browser context, and it is only available after the page or browser context is closed.</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Video is flushed when the browser context closes. With the test runner that happens automatically, but if you created the context yourself you must await context.close(), or the file won't be written.</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>0.00780925</v>
-      </c>
-      <c r="G43" t="n">
-        <v>30157</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J43" t="n">
-        <v>5</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.2368421052631579</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.4166666666458333</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>We rolled our own visual checks: capture a PNG, compare it byte-for-byte with a committed file, fail on any difference. It's unusable — it fails on the first run of any new test, it fails constantly on CI with what look like anti-aliasing differences, and there's no way to accept a legitimate design change short of regenerating files by hand. What does the built-in comparison do differently at each of those three points?</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>['Visual comparisons | Playwright', "Playwright Test includes the ability to produce and visually compare screenshots using\n`await expect(page).toHaveScreenshot()`\n. On first execution, Playwright test will generate reference screenshots. Subsequent runs will compare against the reference.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('example test',async({page})=&gt;{awaitpage.goto('https://playwright.dev');awaitexpect(page).toHaveScreenshot();});`\n```\n\nwarning\nBrowser rendering can vary based on the host OS, version, settings, hardware, power source (battery vs. power adapter), headless mode, and other factors. For consistent screenshots, run tests in the same environment where the baseline screenshots were generated.", 'Sometimes you need to update the reference screenshot, for example when the page has changed. Do this with the\n`--update-snapshots`\nflag.\n\n```\n`npx playwrighttest--update-snapshots`\n```', "Playwright Test uses the\npixelmatch (https://github.com/mapbox/pixelmatch)\nlibrary. You can\npass various options (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\nto modify its behavior:\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('example test',async({page})=&gt;{awaitpage.goto('https://playwright.dev');awaitexpect(page).toHaveScreenshot({maxDiffPixels:100});});`\n```\n\nIf you'd like to share the default value among all the tests in the project, you can specify it in the playwright config, either globally or per project:\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({expect:{toHaveScreenshot:{maxDiffPixels:100},},});`\n```", 'UI Mode | Playwright', 'Trace viewer | Playwright', "When you run above for the first time, test runner will say:\n\n```\n`Error: A snapshot doesn't exist at example.spec.ts-snapshots/example-test-1-chromium-darwin.png, writing actual.`\n```\n\nThat's because there was no golden file yet. This method took a bunch of screenshots until two consecutive screenshots matched, and saved the last screenshot to file system. It is now ready to be added to the repository.\n\nThe name of the folder with the golden expectations starts with the name of your test file:\n\n```\n`drwxr-xr-x5user  group160Jun411:46.drwxr-xr-x6user  group192Jun411:45..-rw-r--r--1user  group231Jun411:16 example.spec.tsdrwxr-xr-x3user  group96Jun411:46 example.spec.ts-snapshots`\n```\n\nThe snapshot name\n`example-test-1-chromium-darwin.png`\nconsists of a few parts:\n\n`example-test-1.png`\n- an auto-generated name of the snapshot. Alternatively you can specify snapshot name as the first argument of the\n`toHaveScreenshot()`\nmethod:\n```\n`awaitexpect(page).toHaveScreenshot('landing.png');`\n```\n`chromium-darwin`\n- the browser name and the platform. Screenshots differ between browsers and platforms due to different rendering, fonts and more, so you will need different snapshots for them. If you use multiple projects in your\nconfiguration file (https://playwright.dev/docs/test-configuration)\n, project name will be used instead of\n`chromium`\n.\n\nThe snapshot name and path can be configured with\ntestConfig.snapshotPathTemplate (https://playwright.dev/docs/api/class-testconfig#test-config-snapshot-path-template)\nin the playwright config.\n\nNote that\n`toHaveScreenshot()`\nalso accepts an array of path segments to the snapshot file such as\n`expect().toHaveScreenshot(['relative', 'path', 'to', 'snapshot.png'])`\n.\nHowever, this path must stay within the snapshots directory for each test file (i.e.\n`a.spec.js-snapshots`\n), otherwise it will throw."]</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>["Error: A snapshot doesn't exist at example.spec.ts-snapshots/example-test-1-chromium-darwin.png, writing actual.", 'chromium-darwin - the browser name and the platform. Screenshots differ between browsers and platforms due to different rendering, fonts and more, so you will need different snapshots for them. If you use multiple projects in your configuration file, project name will be used instead of chromium.', 'Sometimes you need to update the reference screenshot, for example when the page has changed. Do this with the --update-snapshots flag. npx playwright test --update-snapshots', 'export default defineConfig({ expect: { toHaveScreenshot: { maxDiffPixels: 100 }, }, });']</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>The built-in `toHaveScreenshot()` method addresses your three points as follows:
-*   **First run of a new test:** Instead of failing, Playwright automatically generates the reference screenshot. It takes multiple screenshots until two consecutive ones match, saves the final result to the file system, and reports that it is writing the actual file.
-*   **Anti-aliasing and minor differences:** Playwright uses the `pixelmatch` library for comparisons. You can configure the comparison tolerance by passing options such as `maxDiffPixels` to `toHaveScreenshot()`. This can be set per test or globally in your `playwright.config.ts` file to allow for minor rendering variations.
-*   **Accepting design changes:** You do not need to manually regenerate files. You can update the reference screenshots by running the test command with the `--update-snapshots` flag (e.g., `npx playwright test --update-snapshots`).</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Each of your three problems is a thing the built-in assertion already handles, because capturing an image and asserting on one are different operations. page.screenshot() just returns a buffer; expect(page).toHaveScreenshot() is a full comparison assertion. On first run there is no baseline, so instead of failing meaninglessly it takes screenshots until two consecutive ones match — which also settles animation and rendering noise — saves the result as the reference and reports that it wrote it; you commit that file. On CI, the baseline is keyed by environment: the snapshot name like example-test-1-chromium-darwin.png encodes the browser and platform (the project name replaces the browser when you use multiple projects) precisely because rendering, fonts and anti-aliasing differ across platforms, so Linux CI compares against its own baseline rather than your macOS one. And byte-exactness isn't required: `maxDiffPixels` (per assertion or globally under `expect: { toHaveScreenshot: ... }`) sets an allowance. When a change is intentional you re-baseline with `npx playwright test --update-snapshots` rather than editing files.</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>0.008920500000000001</v>
-      </c>
-      <c r="G44" t="n">
-        <v>33622</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J44" t="n">
-        <v>5</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.3257575757575757</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.2471264367816092</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0.6178571428416965</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>In one test I need an admin and a regular user acting at the same time. How do I get two authenticated sessions side by side?</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>["Playwright can create multiple browser contexts within a single scenario. This is useful when you want to test for multi-user functionality, like a chat.\n\nTest\nLibrary\n```\n`import{test}from'@playwright/test';test('admin and user',async({browser})=&gt;{// Create two isolated browser contextsconstadminContext=awaitbrowser.newContext();constuserContext=awaitbrowser.newContext();// Create pages and interact with contexts independentlyconstadminPage=awaitadminContext.newPage();constuserPage=awaituserContext.newPage();});`\n```\n```\n`const{chromium}=require('playwright');// Create a Chromium browser instanceconstbrowser=awaitchromium.launch();// Create two isolated browser contextsconstuserContext=awaitbrowser.newContext();constadminContext=awaitbrowser.newContext();// Create pages and interact with contexts independentlyconstadminPage=awaitadminContext.newPage();constuserPage=awaituserContext.newPage();`\n```", 'When to use\n\nYou need to test how multiple authenticated roles interact together, in a single test.\n\nDetails\n\nYou can introduce fixtures that will provide a page authenticated as each role.\n\nBelow is an example that\ncreates fixtures (https://playwright.dev/docs/test-fixtures#creating-a-fixture)\nfor two\nPage Object Models (https://playwright.dev/docs/pom)\n- admin POM and user POM. It assumes\n`adminStorageState.json`\nand\n`userStorageState.json`\nfiles were created in the global setup.\n\nplaywright/fixtures.ts\n```\n`import{testasbase,typePage,typeLocator}from\'@playwright/test\';// Page Object Model for the "admin" page.// Here you can add locators and helper methods specific to the admin page.classAdminPage{// Page signed in as "admin".page:Page;// Example locator pointing to "Welcome, Admin" greeting.greeting:Locator;constructor(page:Page){this.page=page;this.greeting=page.locator(\'#greeting\');}}// Page Object Model for the "user" page.// Here you can add locators and helper methods specific to the user page.classUserPage{// Page signed in as "user".page:Page;// Example locator pointing to "Welcome, User" greeting.greeting:Locator;constructor(page:Page){this.page=page;this.greeting=page.locator(\'#greeting\');}}// Declare the types of your fixtures.typeMyFixtures={adminPage:AdminPage;userPage:UserPage;};export*from\'@playwright/test\';exportconsttest=base.extend&lt;MyFixtures&gt;({adminPage:async({browser},use)=&gt;{constcontext=awaitbrowser.newContext({storageState:\'playwright/.auth/admin.json\'});constadminPage=newAdminPage(awaitcontext.newPage());awaituse(adminPage);awaitcontext.close();},userPage:async({browser},use)=&gt;{constcontext=awaitbrowser.newContext({storageState:\'playwright/.auth/user.json\'});constuserPage=newUserPage(awaitcontext.newPage());awaituse(userPage);awaitcontext.close();},});`\n```\n\ntests/example.spec.ts\n```\n`// Import test with our new fixtures.import{test,expect}from\'../playwright/fixtures\';// Use adminPage and userPage fixtures in the test.test(\'admin and user\',async({adminPage,userPage})=&gt;{// ... interact with both adminPage and userPage ...awaitexpect(adminPage.greeting).toHaveText(\'Welcome, Admin\');awaitexpect(userPage.greeting).toHaveText(\'Welcome, User\');});`\n```', 'Authentication | Playwright', 'Isolation | Playwright', 'When to use\n\nYou need to test how multiple authenticated roles interact together, in a single test.\n\nDetails\n\nUse multiple\nBrowserContext (https://playwright.dev/docs/api/class-browsercontext)\ns and\nPage (https://playwright.dev/docs/api/class-page)\ns with different storage states in the same test.\n\ntests/example.spec.ts\n```\n`import{test}from\'@playwright/test\';test(\'admin and user\',async({browser})=&gt;{// adminContext and all pages inside, including adminPage, are signed in as "admin".constadminContext=awaitbrowser.newContext({storageState:\'playwright/.auth/admin.json\'});constadminPage=awaitadminContext.newPage();// userContext and all pages inside, including userPage, are signed in as "user".constuserContext=awaitbrowser.newContext({storageState:\'playwright/.auth/user.json\'});constuserPage=awaituserContext.newPage();// ... interact with both adminPage and userPage ...awaitadminContext.close();awaituserContext.close();});`\n```', "BrowserContext | Playwright\n\nBrowserContexts provide a way to operate multiple independent browser sessions.\n\nIf a page opens another page, e.g. with a\n`window.open`\ncall, the popup will belong to the parent page's browser context.\n\nPlaywright allows creating isolated non-persistent browser contexts with\nbrowser.newContext() (https://playwright.dev/docs/api/class-browser#browser-new-context)\nmethod. Non-persistent browser contexts don't write any browsing data to disk.\n\n```\n`// Create a new incognito browser contextconstcontext=awaitbrowser.newContext();// Create a new page inside context.constpage=awaitcontext.newPage();awaitpage.goto('https://example.com');// Dispose context once it's no longer needed.awaitcontext.close();`\n```", 'Fixtures | Playwright']</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>['Use multiple BrowserContext (https://playwright.dev/docs/api/class-browsercontext) s and Page (https://playwright.dev/docs/api/class-page) s with different storage states in the same test.', 'Playwright can create multiple browser contexts within a single scenario. This is useful when you want to test for multi-user functionality, like a chat.']</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>To get two authenticated sessions side by side in a single test, you should use multiple `BrowserContext`s with different storage states.
-### Recommended Approach: Using POM Fixtures
-The documentation recommends using fixtures to provide pages authenticated as each role. This involves:
-1.  **Defining Fixtures:** Create a file (e.g., `playwright/fixtures.ts`) that extends the base test to include `adminPage` and `userPage` fixtures. Each fixture creates a new `browser.newContext()` using a specific `storageState` file (e.g., `adminStorageState.json` and `userStorageState.json`) and initializes the corresponding Page Object Model.
-2.  **Using Fixtures in Tests:** Import your custom `test` from the fixtures file and use the `adminPage` and `userPage` arguments in your test function.
-### Alternative Approach: Manual Context Creation
-If you prefer not to use fixtures, you can manually create the contexts within the test:
-1.  Use `browser.newContext({ storageState: 'path/to/state.json' })` to create separate contexts for the admin and the user.
-2.  Create a page for each context using `context.newPage()`.
-3.  Interact with both pages independently.
-4.  Ensure you call `await context.close()` for each context once the test is complete.
-Both approaches rely on `browser.newContext()` to provide isolated, independent browser sessions.</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Open two browser contexts in the same test, each seeded with a different storageState — one admin, one user — and drive their pages independently. Multiple contexts in one scenario is exactly how Playwright models multi-user features like chat, and they stay isolated.</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>0.00947975</v>
-      </c>
-      <c r="G45" t="n">
-        <v>35459</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.29</v>
-      </c>
       <c r="J45" t="n">
         <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.0568561872909699</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="M45" t="n">
-        <v>0.8766666666491334</v>
+        <v>0.99999999998</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
@@ -3353,7 +3411,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>['Snapshot testing | Playwright', 'Playwright can be used to test your application for many types of accessibility issues.\n\nA few examples of problems this can catch include:\n\nText that would be hard to read for users with vision impairments due to poor color contrast with the background behind it\nUI controls and form elements without labels that a screen reader could identify\nInteractive elements with duplicate IDs which can confuse assistive technologies\n\nThe following examples rely on the\n@axe-core/playwright (https://npmjs.org/@axe-core/playwright)\npackage which adds support for running the\naxe accessibility testing engine (https://www.deque.com/axe/)\nas part of your Playwright tests.\n\nDisclaimer\nAutomated accessibility tests can detect some common accessibility problems such as missing or invalid properties. But many accessibility problems can only be discovered through manual testing. We recommend using a combination of automated testing, manual accessibility assessments, and inclusive user testing.\nFor manual assessments, we recommend\nAccessibility Insights for Web (https://accessibilityinsights.io/docs/web/overview/?referrer=playwright-accessibility-testing-js)\n, a free and open source dev tool that walks you through assessing a website for\nWCAG 2.1 AA (https://www.w3.org/WAI/WCAG21/quickref/?currentsidebar=%23col_customize&amp;levels=aaa)\ncoverage.', 'With Playwright\'s Snapshot testing you can assert the accessibility tree of a page against a predefined snapshot template.\n\n```\n`awaitpage.goto(\'https://playwright.dev/\');awaitexpect(page).toMatchAriaSnapshot(`- banner:- heading /Playwright enables reliable end-to-end/ [level=1]- link "Get started":- /url: /docs/intro- link "Star microsoft/playwright on GitHub":- /url: https://github.com/microsoft/playwright- link /[\\\\d]+k\\\\+ stargazers on GitHub/`);`\n```', 'By default, axe checks against a wide variety of accessibility rules. Some of these rules correspond to specific success criteria from the\nWeb Content Accessibility Guidelines (WCAG) (https://www.w3.org/TR/WCAG21/)\n, and others are "best practice" rules that are not specifically required by any WCAG criterion.\n\nYou can constrain an accessibility scan to only run those rules which are "tagged" as corresponding to specific WCAG success criteria by using\nAxeBuilder.withTags() (https://github.com/dequelabs/axe-core-npm/blob/develop/packages/playwright/README.md#axebuilderwithtagstags-stringarray)\n. For example,\nAccessibility Insights for Web\'s Automated Checks (https://accessibilityinsights.io/docs/web/getstarted/fastpass/?referrer=playwright-accessibility-testing-js)\nonly include axe rules that test for violations of WCAG A and AA success criteria; to match that behavior, you would use the tags\n`wcag2a`\n,\n`wcag2aa`\n,\n`wcag21a`\n, and\n`wcag21aa`\n.\n\nNote that automated testing cannot detect all types of WCAG violations.\n\n```\n`test(\'should not have any automatically detectable WCAG A or AA violations\',async({page})=&gt;{awaitpage.goto(\'https://your-site.com/\');constaccessibilityScanResults=awaitnewAxeBuilder({page}).withTags([\'wcag2a\',\'wcag2aa\',\'wcag21a\',\'wcag21aa\']).analyze();expect(accessibilityScanResults.violations).toEqual([]);});`\n```\n\nYou can find a complete listing of the rule tags axe-core supports in\nthe "Axe-core Tags" section of the axe API documentation (https://www.deque.com/axe/core-documentation/api-documentation/#axecore-tags)\n.', 'Accessibility testing | Playwright', 'Assertions | Playwright', 'Visual comparisons | Playwright']</t>
+          <t>['Added in: v1.49\n\nlocatorAssertions.toMatchAriaSnapshot(expected)\n\nAsserts that the target element matches the given\naccessibility snapshot (https://playwright.dev/docs/aria-snapshots)\n.\n\nUsage\n\n```\n`awaitpage.goto(\'https://demo.playwright.dev/todomvc/\');awaitexpect(page.locator(\'body\')).toMatchAriaSnapshot(`- heading "todos"- textbox "What needs to be done?"`);`\n```\n\nArguments\n\n`expected`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-match-aria-snapshot-option-expected)\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-match-aria-snapshot-option-timeout)\nTime to retry the assertion for in milliseconds. Defaults to\n`timeout`\nin\n`TestConfig.expect`\n.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-match-aria-snapshot-return)', 'Snapshot testing\nis ideal for:\nUI testing of whole pages and components.\nBroad structural checks for complex UI components.\nRegression testing for outputs that rarely change structure.\nAssertion testing\nis ideal for:\nCore logic validation.\nComputed value testing.\nFine-grained tests requiring precise conditions.\n\nBy combining snapshot testing for broad, structural checks and assertion testing for specific functionality, you can achieve a well-rounded testing strategy.', 'By default, axe checks against a wide variety of accessibility rules. Some of these rules correspond to specific success criteria from the\nWeb Content Accessibility Guidelines (WCAG) (https://www.w3.org/TR/WCAG21/)\n, and others are "best practice" rules that are not specifically required by any WCAG criterion.\n\nYou can constrain an accessibility scan to only run those rules which are "tagged" as corresponding to specific WCAG success criteria by using\nAxeBuilder.withTags() (https://github.com/dequelabs/axe-core-npm/blob/develop/packages/playwright/README.md#axebuilderwithtagstags-stringarray)\n. For example,\nAccessibility Insights for Web\'s Automated Checks (https://accessibilityinsights.io/docs/web/getstarted/fastpass/?referrer=playwright-accessibility-testing-js)\nonly include axe rules that test for violations of WCAG A and AA success criteria; to match that behavior, you would use the tags\n`wcag2a`\n,\n`wcag2aa`\n,\n`wcag21a`\n, and\n`wcag21aa`\n.\n\nNote that automated testing cannot detect all types of WCAG violations.\n\n```\n`test(\'should not have any automatically detectable WCAG A or AA violations\',async({page})=&gt;{awaitpage.goto(\'https://your-site.com/\');constaccessibilityScanResults=awaitnewAxeBuilder({page}).withTags([\'wcag2a\',\'wcag2aa\',\'wcag21a\',\'wcag21aa\']).analyze();expect(accessibilityScanResults.violations).toEqual([]);});`\n```\n\nYou can find a complete listing of the rule tags axe-core supports in\nthe "Axe-core Tags" section of the axe API documentation (https://www.deque.com/axe/core-documentation/api-documentation/#axecore-tags)\n.', 'The\nexpect(page).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-match-aria-snapshot)\nassertion method in Playwright compares the accessible structure of the page with a predefined aria snapshot template, helping validate the page\'s state against testing requirements. You can also use\nexpect(locator).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-match-aria-snapshot)\nto match a specific part of the page.\n\nFor the following DOM:\n\n```\n`&lt;h1&gt;title&lt;/h1&gt;`\n```\n\nYou can match it using the following snapshot template:\n\n```\n`awaitexpect(page).toMatchAriaSnapshot(`- heading "title"`);`\n```\n\nWhen matching, the snapshot template is compared to the current accessibility tree of the page:\n\nIf the tree structure matches the template, the test passes; otherwise, it fails, indicating a mismatch between expected and actual accessibility states.\nThe comparison is case-sensitive and collapses whitespace, so indentation and line breaks are ignored.\nThe comparison is order-sensitive, meaning the order of elements in the snapshot template must match the order in the page\'s accessibility tree.', 'Assertion testing is a targeted approach where you assert specific values or conditions about elements or components. For instance, with Playwright,\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nverifies that an element contains the expected text, and\nexpect(locator).toHaveValue() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value)\nconfirms that an input field has the expected value. Assertion tests are specific and generally check the current state of an element or property against an expected, predefined state. They work well for predictable, single-value checks but are limited in scope when testing the broader structure or variations.\n\nAdvantages\n\nClarity\n: The intent of the test is explicit and easy to understand.\nSpecificity\n: Tests focus on particular aspects of functionality, making them more robust against unrelated changes.\nDebugging\n: Failures provide targeted feedback, pointing directly to the problematic aspect.\n\nDisadvantages\n\nVerbose for complex outputs\n: Writing assertions for complex data structures or large outputs can be cumbersome and error-prone.\nMaintenance overhead\n: As code evolves, manually updating assertions can be time-consuming.', "Snapshot testing captures a “snapshot” or representation of the entire state of an element, component, or data at a given moment, which is then saved for future comparisons. When re-running tests, the current state is compared to the snapshot, and if there are differences, the test fails. This approach is especially useful for complex or dynamic structures, where manually asserting each detail would be too time-consuming. Snapshot testing is broader and more holistic than assertion testing, allowing you to track more complex changes over time.\n\nAdvantages\n\nSimplifies complex outputs\n: For example, testing a UI component's rendered output can be tedious with traditional assertions. Snapshots capture the entire output for easy comparison.\nQuick Feedback loop\n: Developers can easily spot unintended changes in the output.\nEncourages consistency\n: Helps maintain consistent output as code evolves.\n\nDisadvantages\n\nOver-Reliance\n: It can be tempting to accept changes to snapshots without fully understanding them, potentially hiding bugs.\nGranularity\n: Large snapshots may be hard to interpret when differences arise, especially if minor changes affect large portions of the output.\nSuitability\n: Not ideal for highly dynamic content where outputs change frequently or unpredictably.", 'In Playwright, aria snapshots provide a YAML representation of the accessibility tree of a page. These snapshots can be stored and compared later to verify if the page structure remains consistent or meets defined expectations.\n\nThe YAML format describes the hierarchical structure of accessible elements on the page, detailing\nroles\n,\nattributes\n,\nvalues\n, and\ntext content\n. The structure follows a tree-like syntax, where each node represents an accessible element, and indentation indicates nested elements.\n\nEach accessible element in the tree is represented as a YAML node:\n\n```\n`-role "name"[attribute=value]`\n```\n\nrole\n: Specifies the ARIA or HTML role of the element (e.g.,\n`heading`\n,\n`list`\n,\n`listitem`\n,\n`button`\n).\n"name"\n: Accessible name of the element. Quoted strings indicate exact values,\n`/patterns/`\nare used for regular expression.\n[attribute=value]\n: Attributes and values, in square brackets, represent specific ARIA attributes, such as\n`checked`\n,\n`disabled`\n,\n`expanded`\n,\n`level`\n,\n`pressed`\n, or\n`selected`\n.\n\nThese values are derived from ARIA attributes or calculated based on HTML semantics. To inspect the accessibility tree structure of a page, use the\nChrome DevTools Accessibility Tab (https://developer.chrome.com/docs/devtools/accessibility/reference#tab)\n.']</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3363,13 +3421,9 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>The automated accessibility scan (using `@axe-core/playwright`) is able to catch problems such as:
-*   Poor color contrast between text and background.
-*   UI controls and form elements missing labels.
-*   Interactive elements with duplicate IDs.
-*   Missing or invalid properties.
-The regression you experienced—where the reading order of sections changed—would have been caught by **Snapshot testing** using `toMatchAriaSnapshot`. This allows you to assert the accessibility tree of a page against a predefined snapshot template, which would detect changes in the structure or order of elements as perceived by assistive technologies.
-Yes, both can live in the same test suite. You can combine automated accessibility scans (using `AxeBuilder`) and accessibility tree snapshot assertions (using `toMatchAriaSnapshot`) within your Playwright tests to cover both automated rule violations and structural regressions.</t>
+          <t>The automated accessibility scan (using `AxeBuilder`) checks for violations of WCAG success criteria and "best practice" rules. However, automated testing cannot detect all types of WCAG violations.
+The regression you experienced—where the order of sections in the accessibility tree changed—would have been caught by an **ARIA snapshot test** using `expect(locator).toMatchAriaSnapshot(expected)`. This method compares the current accessibility tree of the page or component against a predefined YAML template. Because the comparison is order-sensitive, it requires the order of elements in the template to match the order in the accessibility tree, ensuring that structural changes are detected.
+Yes, both can live in the same test suite. You can combine snapshot testing for broad, structural checks (like the order of elements in your settings panel) with assertion testing or automated scanning for specific functionality and WCAG compliance to achieve a well-rounded testing strategy.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3378,28 +3432,28 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.01001175</v>
+        <v>0.00097625</v>
       </c>
       <c r="G46" t="n">
-        <v>37192</v>
+        <v>44680</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="J46" t="n">
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>0.2834645669291339</v>
+        <v>0.272108843537415</v>
       </c>
       <c r="L46" t="n">
-        <v>0.1512605042016807</v>
+        <v>0.1680672268907563</v>
       </c>
       <c r="M46" t="n">
-        <v>0.9150793650641138</v>
+        <v>0.7470238095051339</v>
       </c>
       <c r="N46" t="n">
         <v>1</v>
@@ -3413,7 +3467,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>['Added in: v1.20\n\nlocatorAssertions.toHaveCSS\n\nEnsures the\nLocator (https://playwright.dev/docs/api/class-locator)\nresolves to an element with the given computed CSS style.\n\nUsage\n\n```\n`constlocator=page.getByRole(\'button\');awaitexpect(locator).toHaveCSS(\'display\',\'flex\');`\n```\n\nArguments\n\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-option-name)\nCSS property name.\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-option-value)\nCSS property value.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`pseudo`\n"before" | "after"\n(optional)\nAdded in: v1.60\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-option-pseudo)\nPseudo-element to read computed styles from.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-option-timeout)\nTime to retry the assertion for in milliseconds. Defaults to\n`timeout`\nin\n`TestConfig.expect`\n.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-return)', 'Evaluating JavaScript | Playwright', "Playwright scripts run in your Playwright environment. Your page scripts run in the browser page environment. Those environments don't intersect, they are running in different virtual machines in different processes and even potentially on different computers.\n\nThe\npage.evaluate() (https://playwright.dev/docs/api/class-page#page-evaluate)\nAPI can run a JavaScript function in the context of the web page and bring results back to the Playwright environment. Browser globals like\n`window`\nand\n`document`\ncan be used in\n`evaluate`\n.\n\n```\n`consthref=awaitpage.evaluate(()=&gt;document.location.href);`\n```\n\nIf the result is a Promise or if the function is asynchronous evaluate will automatically wait until it's resolved:\n\n```\n`conststatus=awaitpage.evaluate(async()=&gt;{constresponse=awaitfetch(location.href);returnresponse.status;});`\n```", 'The following assertions will retry until the assertion passes, or the assertion timeout is reached. Note that retrying assertions are async, so you must\n`await`\nthem.\n\nAssertion\nDescription\nawait expect(locator).toBeAttached() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-attached)\nElement is attached\nawait expect(locator).toBeChecked() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-checked)\nCheckbox is checked\nawait expect(locator).toBeDisabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-disabled)\nElement is disabled\nawait expect(locator).toBeEditable() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-editable)\nElement is editable\nawait expect(locator).toBeEmpty() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-empty)\nContainer is empty\nawait expect(locator).toBeEnabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-enabled)\nElement is enabled\nawait expect(locator).toBeFocused() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-focused)\nElement is focused\nawait expect(locator).toBeHidden() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-hidden)\nElement is not visible\nawait expect(locator).toBeInViewport() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-in-viewport)\nElement intersects viewport\nawait expect(locator).toBeVisible() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-visible)\nElement is visible\nawait expect(locator).toContainText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-text)\nElement contains text\nawait expect(locator).toContainClass() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-class)\nElement has specified CSS classes\nawait expect(locator).toHaveAccessibleDescription() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-accessible-description)\nElement has a matching\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\nawait expect(locator).toHaveAccessibleName() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-accessible-name)\nElement has a matching\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\nawait expect(locator).toHaveAttribute() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-attribute)\nElement has a DOM attribute\nawait expect(locator).toHaveClass() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-class)\nElement has specified CSS class property\nawait expect(locator).toHaveCount() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-count)\nList has exact number of children\nawait expect(locator).toHaveCSS() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css)\nElement has CSS property\nawait expect(locator).toHaveId() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-id)\nElement has an ID\nawait expect(locator).toHaveJSProperty() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-js-property)\nElement has a JavaScript property\nawait expect(locator).toHaveRole() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-role)\nElement has a specific\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\nawait expect(locator).toHaveScreenshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-screenshot-1)\nElement has a screenshot\nawait expect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nElement matches text\nawait expect(locator).toHaveValue() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value)\nInput has a value\nawait expect(locator).toHaveValues() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-values)\nSelect has options selected\nawait expect(locator).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-match-aria-snapshot)\nElement matches the Aria snapshot\nawait expect(page).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-match-aria-snapshot)\nPage matches the Aria snapshot\nawait expect(page).toHaveScreenshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\nPage has a screenshot\nawait expect(page).toHaveTitle() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-title)\nPage has a title\nawait expect(page).toHaveURL() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-url)\nPage has a URL\nawait expect(response).toBeOK() (https://playwright.dev/docs/api/class-apiresponseassertions#api-response-assertions-to-be-ok)\nResponse has an OK status', "You can convert any synchronous\n`expect`\nto an asynchronous polling one using\n`expect.poll`\n.\n\nThe following method will poll given function until it returns HTTP status 200:\n\n```\n`awaitexpect.poll(async()=&gt;{constresponse=awaitpage.request.get('https://api.example.com');returnresponse.status();},{// Custom expect message for reporting, optional.message:'make sure API eventually succeeds',// Poll for 10 seconds; defaults to 5 seconds. Pass 0 to disable timeout.timeout:10000,}).toBe(200);`\n```\n\nYou can also specify custom polling intervals:\n\n```\n`awaitexpect.poll(async()=&gt;{constresponse=awaitpage.request.get('https://api.example.com');returnresponse.status();},{// Probe, wait 1s, probe, wait 2s, probe, wait 10s, probe, wait 10s, probe// ... Defaults to [100, 250, 500, 1000].intervals:[1_000,2_000,10_000],timeout:60_000}).toBe(200);`\n```\n\nYou can combine\n`expect.soft`\nwith\n`expect.poll`\nto perform soft assertions in polling logic. This allows the test to continue even if the assertion inside poll fails.\n\n```\n`awaitexpect.soft.poll(async()=&gt;{constresponse=awaitpage.request.get('https://api.example.com');returnresponse.status();}).toBe(200);`\n```\n\n`expect.configure({ soft: true })`\nalso chains with\n`expect.poll`\nand is useful when you want to reuse a configured instance.\n\n```\n`constsoftExpect=expect.configure({soft:true});awaitsoftExpect.poll(async()=&gt;{constresponse=awaitpage.request.get('https://api.example.com');returnresponse.status();}).toBe(200);`\n```", 'Added in: v1.14\n\nlocator.evaluate\n\nExecute JavaScript code in the page, taking the matching element as an argument.\n\nUsage\n\nPassing argument to\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\n:\n\n```\n`constresult=awaitpage.getByTestId(\'myId\').evaluate((element,[x,y])=&gt;{returnelement.textContent+\' \'+x*y;},[7,8]);console.log(result);// prints "myId text 56"`\n```\n\nArguments\n\n`pageFunction`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\nFunction to be evaluated in the page context.\n`arg`\nEvaluationArgument (https://playwright.dev/docs/evaluating#evaluation-argument)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-arg)\nOptional argument to pass to\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\n.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-timeout)\nMaximum time in milliseconds to wait for the locator before evaluating. Note that after locator is resolved, evaluation itself is not limited by the timeout. Defaults to\n`0`\n- no timeout.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-return)\n\nDetails\n\nReturns the return value of\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\n, called with the matching element as a first argument, and\narg (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-arg)\nas a second argument.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\nreturns a\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n, this method will wait for the promise to resolve and return its value.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\nthrows or rejects, this method throws.', "Added in: v1.14\n\nlocator.evaluateAll\n\nExecute JavaScript code in the page, taking all matching elements as an argument.\n\nUsage\n\n```\n`constlocator=page.locator('div');constmoreThanTen=awaitlocator.evaluateAll((divs,min)=&gt;divs.length&gt;min,10);`\n```\n\nArguments\n\n`pageFunction`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\nFunction to be evaluated in the page context.\n`arg`\nEvaluationArgument (https://playwright.dev/docs/evaluating#evaluation-argument)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-arg)\nOptional argument to pass to\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\n.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-return)\n\nDetails\n\nReturns the return value of\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\n, called with an array of all matching elements as a first argument, and\narg (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-arg)\nas a second argument.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\nreturns a\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n, this method will wait for the promise to resolve and return its value.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\nthrows or rejects, this method throws."]</t>
+          <t>['Added in: v1.20\n\nlocatorAssertions.toHaveCSS\n\nEnsures the\nLocator (https://playwright.dev/docs/api/class-locator)\nresolves to an element with the given computed CSS style.\n\nUsage\n\n```\n`constlocator=page.getByRole(\'button\');awaitexpect(locator).toHaveCSS(\'display\',\'flex\');`\n```\n\nArguments\n\n`name`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-option-name)\nCSS property name.\n`value`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-option-value)\nCSS property value.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`pseudo`\n"before" | "after"\n(optional)\nAdded in: v1.60\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-option-pseudo)\nPseudo-element to read computed styles from.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.18\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-option-timeout)\nTime to retry the assertion for in milliseconds. Defaults to\n`timeout`\nin\n`TestConfig.expect`\n.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css-return)', 'Evaluated scripts run in the browser environment, while your test runs in a testing environments. This means you cannot use variables from your test in the page and vice versa. Instead, you should pass them explicitly as an argument.\n\nThe following snippet is\nWRONG\nbecause it uses the variable directly:\n\n```\n`constdata=\'some data\';constresult=awaitpage.evaluate(()=&gt;{// WRONG: there is no "data" in the web page.window.myApp.use(data);});`\n```\n\nThe following snippet is\nCORRECT\nbecause it passes the value explicitly as an argument:\n\n```\n`constdata=\'some data\';// Pass |data| as a parameter.constresult=awaitpage.evaluate(data=&gt;{window.myApp.use(data);},data);`\n```', 'Added in: v1.14\n\nlocator.evaluate\n\nExecute JavaScript code in the page, taking the matching element as an argument.\n\nUsage\n\nPassing argument to\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\n:\n\n```\n`constresult=awaitpage.getByTestId(\'myId\').evaluate((element,[x,y])=&gt;{returnelement.textContent+\' \'+x*y;},[7,8]);console.log(result);// prints "myId text 56"`\n```\n\nArguments\n\n`pageFunction`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\nFunction to be evaluated in the page context.\n`arg`\nEvaluationArgument (https://playwright.dev/docs/evaluating#evaluation-argument)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-arg)\nOptional argument to pass to\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\n.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-timeout)\nMaximum time in milliseconds to wait for the locator before evaluating. Note that after locator is resolved, evaluation itself is not limited by the timeout. Defaults to\n`0`\n- no timeout.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-return)\n\nDetails\n\nReturns the return value of\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\n, called with the matching element as a first argument, and\narg (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-arg)\nas a second argument.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\nreturns a\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n, this method will wait for the promise to resolve and return its value.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-option-expression)\nthrows or rejects, this method throws.', "Playwright evaluation methods like\npage.evaluate() (https://playwright.dev/docs/api/class-page#page-evaluate)\ntake a single optional argument. This argument can be a mix of\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\nvalues and\nJSHandle (https://playwright.dev/docs/api/class-jshandle)\ninstances. Handles are automatically converted to the value they represent.\n\n```\n`// A primitive value.awaitpage.evaluate(num=&gt;num,42);// An array.awaitpage.evaluate(array=&gt;array.length,[1,2,3]);// An object.awaitpage.evaluate(object=&gt;object.foo,{foo:'bar'});// A single handle.constbutton=awaitpage.evaluateHandle('window.button');awaitpage.evaluate(button=&gt;button.textContent,button);// Alternative notation using JSHandle.evaluate.awaitbutton.evaluate((button,from)=&gt;button.textContent.substring(from),5);// Object with multiple handles.constbutton1=awaitpage.evaluateHandle('window.button1');constbutton2=awaitpage.evaluateHandle('window.button2');awaitpage.evaluate(o=&gt;o.button1.textContent+o.button2.textContent,{button1,button2});// Object destructuring works. Note that property names must match// between the destructured object and the argument.// Also note the required parenthesis.awaitpage.evaluate(({button1,button2})=&gt;button1.textContent+button2.textContent,{button1,button2});// Array works as well. Arbitrary names can be used for destructuring.// Note the required parenthesis.awaitpage.evaluate(([b1,b2])=&gt;b1.textContent+b2.textContent,[button1,button2]);// Any mix of serializables and handles works.awaitpage.evaluate(x=&gt;x.button1.textContent+x.list[0].textContent+String(x.foo),{button1,list:[button2],foo:null});`\n```", "Playwright scripts run in your Playwright environment. Your page scripts run in the browser page environment. Those environments don't intersect, they are running in different virtual machines in different processes and even potentially on different computers.\n\nThe\npage.evaluate() (https://playwright.dev/docs/api/class-page#page-evaluate)\nAPI can run a JavaScript function in the context of the web page and bring results back to the Playwright environment. Browser globals like\n`window`\nand\n`document`\ncan be used in\n`evaluate`\n.\n\n```\n`consthref=awaitpage.evaluate(()=&gt;document.location.href);`\n```\n\nIf the result is a Promise or if the function is asynchronous evaluate will automatically wait until it's resolved:\n\n```\n`conststatus=awaitpage.evaluate(async()=&gt;{constresponse=awaitfetch(location.href);returnresponse.status;});`\n```", "Added in: v1.14\n\nlocator.evaluateAll\n\nExecute JavaScript code in the page, taking all matching elements as an argument.\n\nUsage\n\n```\n`constlocator=page.locator('div');constmoreThanTen=awaitlocator.evaluateAll((divs,min)=&gt;divs.length&gt;min,10);`\n```\n\nArguments\n\n`pageFunction`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\nFunction to be evaluated in the page context.\n`arg`\nEvaluationArgument (https://playwright.dev/docs/evaluating#evaluation-argument)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-arg)\nOptional argument to pass to\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\n.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\n&gt;\n# (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-return)\n\nDetails\n\nReturns the return value of\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\n, called with an array of all matching elements as a first argument, and\narg (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-arg)\nas a second argument.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\nreturns a\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n, this method will wait for the promise to resolve and return its value.\n\nIf\npageFunction (https://playwright.dev/docs/api/class-locator#locator-evaluate-all-option-expression)\nthrows or rejects, this method throws.", "You can extend Playwright assertions by providing custom matchers. These matchers will be available on the\n`expect`\nobject.\n\nIn this example we add a custom\n`toHaveAmount`\nfunction. Custom matcher should return a\n`pass`\nflag indicating whether the assertion passed, and a\n`message`\ncallback that's used when the assertion fails.\n\nfixtures.ts\n```\n`import{expectasbaseExpect}from'@playwright/test';importtype{Locator}from'@playwright/test';export{test}from'@playwright/test';exportconstexpect=baseExpect.extend({asynctoHaveAmount(locator:Locator,expected:number,options?:{timeout?:number}){constassertionName='toHaveAmount';letpass:boolean;letmatcherResult:any;try{constexpectation=this.isNot?baseExpect(locator).not:baseExpect(locator);awaitexpectation.toHaveAttribute('data-amount',String(expected),options);pass=true;}catch(e:any){matcherResult=e.matcherResult;pass=false;}if(this.isNot){pass=!pass;}constmessage=pass?()=&gt;this.utils.matcherHint(assertionName,undefined,undefined,{isNot:this.isNot})+'\\n\\n'+`Locator:${locator}\\n`+`Expected: not${this.utils.printExpected(expected)}\\n`+(matcherResult?`Received:${this.utils.printReceived(matcherResult.actual)}`:''):()=&gt;this.utils.matcherHint(assertionName,undefined,undefined,{isNot:this.isNot})+'\\n\\n'+`Locator:${locator}\\n`+`Expected:${this.utils.printExpected(expected)}\\n`+(matcherResult?`Received:${this.utils.printReceived(matcherResult.actual)}`:'');return{message,pass,name:assertionName,expected,actual:matcherResult?.actual,};},});`\n```\n\nNow we can use\n`toHaveAmount`\nin the test.\n\nexample.spec.ts\n```\n`import{test,expect}from'./fixtures';test('amount',async()=&gt;{awaitexpect(page.locator('.cart')).toHaveAmount(4);});`\n```"]</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3423,30 +3477,28 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>To assert that every row in your pricing table renders with a specific computed CSS style, you should use `locator.evaluateAll`. This method allows you to execute JavaScript in the page context, receiving an array of all matching elements as an argument, which is necessary to verify the computed style across multiple rows.
-### Recommended Approach
-Use `locator.evaluateAll` to iterate through the elements and check their computed styles using `window.getComputedStyle(element)`.
+          <t>To assert that every row in your pricing table renders with a specific computed CSS style, you should use `locator.evaluateAll`. This method allows you to execute JavaScript in the browser context to inspect all matching elements and return a result to your test environment.
+Because your test and the browser run in different environments, you must pass any variables (such as your threshold) explicitly as an argument to the `pageFunction`.
+### Recommended Approach: `locator.evaluateAll`
+Use `evaluateAll` to iterate through all rows and verify the computed style.
 ```javascript
-const rows = page.locator('.pricing-row');
-const isRightAligned = await rows.evaluateAll((elements) =&gt; {
-  return elements.every(el =&gt; window.getComputedStyle(el).textAlign === 'right');
-});
-expect(isRightAligned).toBe(true);
-```
-### Why this approach?
-*   **Computed Styles:** Since the style is computed and not in the DOM, `evaluateAll` allows you to run `window.getComputedStyle` directly in the browser environment where the styles are calculated.
-*   **Environment Separation:** As noted in the documentation, Playwright scripts and page scripts run in different environments. `evaluateAll` bridges this gap by passing the elements into the page context.
-*   **Handling Multiple Rows:** `evaluateAll` is specifically designed to take all matching elements as an argument, enabling you to perform a collective check on the entire table.
-### Alternative
-If you prefer to use an auto-retrying assertion, you can combine `expect.poll` with `evaluateAll`:
-```javascript
-await expect.poll(async () =&gt; {
-  return await rows.evaluateAll((elements) =&gt; 
-    elements.every(el =&gt; window.getComputedStyle(el).textAlign === 'right')
-  );
-}).toBe(true);
-```
-The `toHaveCSS` assertion mentioned in the documentation is intended for checking a single locator's CSS property, but it does not support verifying a condition across a collection of elements simultaneously.</t>
+const rows = page.locator('.pricing-table-row');
+const threshold = 10; // Your threshold value
+const allRightAligned = await rows.evaluateAll((elements, thresholdValue) =&gt; {
+  return elements.every(el =&gt; {
+    const style = window.getComputedStyle(el);
+    return style.textAlign === 'right';
+  });
+}, threshold);
+// Assert the result in your test
+expect(allRightAligned).toBe(true);
+```
+### Why this addresses your issues:
+*   **Computed Styles:** `window.getComputedStyle(el)` is used within the browser context to access the computed CSS values that are not directly exposed in the DOM.
+*   **Variable Scope:** By passing `threshold` as the second argument to `evaluateAll`, you avoid the "undefined" error caused by trying to access test-environment variables directly inside the browser-side function.
+*   **Multiple Elements:** `evaluateAll` provides an array of all matching elements, allowing you to perform a check across the entire table.
+### Alternative: `toHaveCSS`
+If you only need to check a single element, you can use `expect(locator).toHaveCSS(name, value)`. However, since you need to verify *every* row, `evaluateAll` is the appropriate method to aggregate the state of all rows for a single assertion.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3455,28 +3507,28 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0.01459775</v>
+        <v>0.00159475</v>
       </c>
       <c r="G47" t="n">
-        <v>54051</v>
+        <v>53123</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1468253968253968</v>
+        <v>0.1568627450980392</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2450331125827815</v>
+        <v>0.2649006622516556</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5595238095098214</v>
+        <v>0.7099999999858</v>
       </c>
       <c r="N47" t="n">
         <v>0.8333333333333334</v>
@@ -3490,7 +3542,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>['Projects | Playwright', "By using\nprojects\nyou can run your tests in multiple browsers such as chromium, webkit and firefox as well as branded browsers such as Google Chrome and Microsoft Edge. Playwright can also run on emulated tablet and mobile devices. See the\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nfor a complete list of selected desktop, tablet and mobile devices.\n\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[{name:'chromium',use:{...devices['Desktop Chrome']},},{name:'firefox',use:{...devices['Desktop Firefox']},},{name:'webkit',use:{...devices['Desktop Safari']},},/* Test against mobile viewports. */{name:'Mobile Chrome',use:{...devices['Pixel 5']},},{name:'Mobile Safari',use:{...devices['iPhone 12']},},/* Test against branded browsers. */{name:'Microsoft Edge',use:{...devices['Desktop Edge'],channel:'msedge'},},{name:'Google Chrome',use:{...devices['Desktop Chrome'],channel:'chrome'},},],});`\n```", 'Emulation | Playwright', 'Playwright comes with a\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nusing\nplaywright.devices (https://playwright.dev/docs/api/class-playwright#playwright-devices)\nfor selected desktop, tablet and mobile devices. It can be used to simulate browser behavior for a specific device such as user agent, screen size, viewport and if it has touch enabled. All tests will run with the specified device parameters.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig,devices}from\'@playwright/test\';// import devicesexportdefaultdefineConfig({projects:[{name:\'chromium\',use:{...devices[\'Desktop Chrome\'],},},{name:\'Mobile Safari\',use:{...devices[\'iPhone 13\'],},},],});`\n```\n```\n`const{chromium,devices}=require(\'playwright\');constbrowser=awaitchromium.launch();constiphone13=devices[\'iPhone 13\'];constcontext=awaitbrowser.newContext({...iphone13,});`\n```\n\nNote\n: Pre-configured devices assume a specific platform. For example, "Desktop Chrome" will provide a Windows-specific user agent string.\n\nIf you would like to use the user agent specific to the platform that is running the tests, we recommend unsetting the user agent property.\n\n```\n`constcontext=awaitbrowser.newContext({...devices[\'Desktop Chrome\'],userAgent:undefined,});`\n```', 'Configuration (use) | Playwright', 'A project is logical group of tests running with the same configuration. We use projects so we can run tests on different browsers and devices. Projects are configured in the\n`playwright.config.ts`\nfile and once configured you can then run your tests on all projects or only on a specific project. You can also use projects to run the same tests in different configurations. For example, you can run the same tests in a logged-in and logged-out state.\n\nBy setting up projects you can also run a group of tests with different timeouts or retries or a group of tests against different environments such as staging and production, splitting tests per package/functionality and more.', 'With Playwright you can test your app on any browser as well as emulate a real device such as a mobile phone or tablet. Simply configure the devices you would like to emulate and Playwright will simulate the browser behavior such as\n`"userAgent"`\n,\n`"screenSize"`\n,\n`"viewport"`\nand if it\n`"hasTouch"`\nenabled. You can also emulate the\n`"geolocation"`\n,\n`"locale"`\nand\n`"timezone"`\nfor all tests or for a specific test as well as set the\n`"permissions"`\nto show notifications or change the\n`"colorScheme"`\n.']</t>
+          <t>["By using\nprojects\nyou can run your tests in multiple browsers such as chromium, webkit and firefox as well as branded browsers such as Google Chrome and Microsoft Edge. Playwright can also run on emulated tablet and mobile devices. See the\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nfor a complete list of selected desktop, tablet and mobile devices.\n\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[{name:'chromium',use:{...devices['Desktop Chrome']},},{name:'firefox',use:{...devices['Desktop Firefox']},},{name:'webkit',use:{...devices['Desktop Safari']},},/* Test against mobile viewports. */{name:'Mobile Chrome',use:{...devices['Pixel 5']},},{name:'Mobile Safari',use:{...devices['iPhone 12']},},/* Test against branded browsers. */{name:'Microsoft Edge',use:{...devices['Desktop Edge'],channel:'msedge'},},{name:'Google Chrome',use:{...devices['Desktop Chrome'],channel:'chrome'},},],});`\n```", 'Playwright comes with a\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nusing\nplaywright.devices (https://playwright.dev/docs/api/class-playwright#playwright-devices)\nfor selected desktop, tablet and mobile devices. It can be used to simulate browser behavior for a specific device such as user agent, screen size, viewport and if it has touch enabled. All tests will run with the specified device parameters.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig,devices}from\'@playwright/test\';// import devicesexportdefaultdefineConfig({projects:[{name:\'chromium\',use:{...devices[\'Desktop Chrome\'],},},{name:\'Mobile Safari\',use:{...devices[\'iPhone 13\'],},},],});`\n```\n```\n`const{chromium,devices}=require(\'playwright\');constbrowser=awaitchromium.launch();constiphone13=devices[\'iPhone 13\'];constcontext=awaitbrowser.newContext({...iphone13,});`\n```\n\nNote\n: Pre-configured devices assume a specific platform. For example, "Desktop Chrome" will provide a Windows-specific user agent string.\n\nIf you would like to use the user agent specific to the platform that is running the tests, we recommend unsetting the user agent property.\n\n```\n`constcontext=awaitbrowser.newContext({...devices[\'Desktop Chrome\'],userAgent:undefined,});`\n```', "Playwright can run your tests in multiple browsers and configurations by setting up\nprojects\nin the config. You can also add\ndifferent options (https://playwright.dev/docs/test-configuration)\nfor each project.\n\n```\n`import{defineConfig,devices}from'@playwright/test';exportdefaultdefineConfig({projects:[/* Test against desktop browsers */{name:'chromium',use:{...devices['Desktop Chrome']},},{name:'firefox',use:{...devices['Desktop Firefox']},},{name:'webkit',use:{...devices['Desktop Safari']},},/* Test against mobile viewports. */{name:'Mobile Chrome',use:{...devices['Pixel 5']},},{name:'Mobile Safari',use:{...devices['iPhone 12']},},/* Test against branded browsers. */{name:'Google Chrome',use:{...devices['Desktop Chrome'],channel:'chrome'},// or 'chrome-beta'},{name:'Microsoft Edge',use:{...devices['Desktop Edge'],channel:'msedge'},// or 'msedge-dev'},],});`\n```\n\nPlaywright will run all projects by default.\n\n```\n`npx playwrighttestRunning7tests using5workers✓[chromium]› example.spec.ts:3:1 › basictest(2s)✓[firefox]› example.spec.ts:3:1 › basictest(2s)✓[webkit]› example.spec.ts:3:1 › basictest(2s)✓[Mobile Chrome]› example.spec.ts:3:1 › basictest(2s)✓[Mobile Safari]› example.spec.ts:3:1 › basictest(2s)✓[Google Chrome]› example.spec.ts:3:1 › basictest(2s)✓[Microsoft Edge]› example.spec.ts:3:1 › basictest(2s)`\n```\n\nUse the\n`--project`\ncommand line option to run a single project.\n\n```\n`npx playwrighttest--project=firefoxRunning1testusing1worker✓[firefox]› example.spec.ts:3:1 › basictest(2s)`\n```\n\nWith the VS Code extension you can run your tests on different browsers by checking the checkbox next to the browser name in the Playwright sidebar. These names are defined in your Playwright config file under the projects section. The default config when installing Playwright gives you 3 projects, Chromium, Firefox and WebKit. The first project is selected by default.\n\nTo run tests on multiple projects(browsers), select each project by checking the checkboxes next to the project name.", 'With Playwright you can test your app on any browser as well as emulate a real device such as a mobile phone or tablet. Simply configure the devices you would like to emulate and Playwright will simulate the browser behavior such as\n`"userAgent"`\n,\n`"screenSize"`\n,\n`"viewport"`\nand if it\n`"hasTouch"`\nenabled. You can also emulate the\n`"geolocation"`\n,\n`"locale"`\nand\n`"timezone"`\nfor all tests or for a specific test as well as set the\n`"permissions"`\nto show notifications or change the\n`"colorScheme"`\n.', 'Playwright can run tests on Chromium, WebKit and Firefox browsers as well as branded browsers such as Google Chrome and Microsoft Edge. It can also run on emulated tablet and mobile devices. See the\nregistry of device parameters (https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json)\nfor a complete list of selected desktop, tablet and mobile devices.', "Added in: v1.10\n\ntestOptions.isMobile\n\nWhether the\n`meta viewport`\ntag is taken into account and touch events are enabled. isMobile is a part of device, so you don't actually need to set it manually. Defaults to\n`false`\nand is not supported in Firefox. Learn more about\nmobile emulation (https://playwright.dev/docs/emulation#ismobile)\n.\n\nUsage\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{isMobile:false,},});`\n```\n\nType\n\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)", 'A project is logical group of tests running with the same configuration. We use projects so we can run tests on different browsers and devices. Projects are configured in the\n`playwright.config.ts`\nfile and once configured you can then run your tests on all projects or only on a specific project. You can also use projects to run the same tests in different configurations. For example, you can run the same tests in a logged-in and logged-out state.\n\nBy setting up projects you can also run a group of tests with different timeouts or retries or a group of tests against different environments such as staging and production, splitting tests per package/functionality and more.']</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3500,36 +3552,37 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>To run the same suite across desktop and mobile devices with the correct emulation, you should use **projects** configured in your `playwright.config.ts` file. Projects allow you to run the same tests in different configurations, such as across multiple browsers and emulated devices.
-### Implementation
-In your `playwright.config.ts`, import `devices` and define your projects within the `defineConfig` object. Use the spread operator (`...devices['Device Name']`) to apply the specific emulation parameters (such as user agent, screen size, viewport, and touch support) to each project:
-```javascript
+          <t>To run the same suite across desktop and mobile devices with the correct emulation, you must configure **projects** in your `playwright.config.ts` file. Projects allow you to group tests with specific configurations, such as different browsers and device parameters.
+### Configuration
+Import `devices` from `@playwright/test` and define your projects within the `defineConfig` object. Use the spread operator (`...`) to apply the pre-configured device parameters from the Playwright registry to each project.
+```typescript
 import { defineConfig, devices } from '@playwright/test';
 export default defineConfig({
   projects: [
+    /* Desktop projects */
     {
-      name: 'Desktop Chrome',
+      name: 'chromium',
       use: { ...devices['Desktop Chrome'] },
+    },
+    /* Mobile projects */
+    {
+      name: 'Mobile Chrome',
+      use: { ...devices['Pixel 5'] },
     },
     {
       name: 'Mobile Safari',
       use: { ...devices['iPhone 12'] },
     },
-    // Add additional projects as needed
   ],
 });
 ```
-### Key Details
-*   **Device Registry:** Playwright provides a registry of device parameters for selected desktop, tablet, and mobile devices. You can reference these by name using `devices['Device Name']`.
-*   **Emulation Behavior:** When a device is configured, Playwright automatically simulates the browser behavior, including `userAgent`, `screenSize`, `viewport`, and `hasTouch`.
-*   **Platform-Specific User Agents:** Pre-configured devices assume a specific platform (e.g., "Desktop Chrome" provides a Windows-specific user agent). If you want to use the user agent of the platform currently running the tests, you should unset the property:
-    ```javascript
-    use: { 
-      ...devices['Desktop Chrome'], 
-      userAgent: undefined 
-    }
-    ```
-*   **Execution:** Once configured, you can run your tests across all projects or target a specific project as required.</t>
+### How it works
+*   **Device Parameters:** Playwright provides a registry of device parameters (including user agent, screen size, viewport, and touch support) that are automatically applied when you use `devices['Device Name']`.
+*   **Execution:** By default, Playwright will run all configured projects. 
+*   **Running specific projects:** You can run a single project using the `--project` command line option:
+    `npx playwright test --project="Mobile Safari"`
+*   **VS Code Extension:** You can select which projects to run by checking the checkboxes next to the project names in the Playwright sidebar.
+For a complete list of available desktop, tablet, and mobile devices, refer to the [registry of device parameters](https://github.com/microsoft/playwright/blob/main/packages/playwright-core/src/server/deviceDescriptorsSource.json).</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3538,28 +3591,28 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.008865749999999001</v>
+        <v>0.00121375</v>
       </c>
       <c r="G48" t="n">
-        <v>32088</v>
+        <v>42511</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="J48" t="n">
         <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>0.06986899563318777</v>
+        <v>0.07623318385650224</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4324324324324325</v>
+        <v>0.4594594594594595</v>
       </c>
       <c r="M48" t="n">
-        <v>0.499999999975</v>
+        <v>0.9999999999666667</v>
       </c>
       <c r="N48" t="n">
         <v>1</v>
@@ -3573,7 +3626,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>['Fixtures | Playwright', 'Playwright Test supports running multiple test projects that can be configured separately. You can use "option" fixtures to make your configuration options declarative and type safe. Learn more about\nparameterizing tests (https://playwright.dev/docs/test-parameterize)\n.\n\nBelow we\'ll create a\n`defaultItem`\noption in addition to the\n`todoPage`\nfixture from other examples. This option will be set in the configuration file. Note the tuple syntax and\n`{ option: true }`\nargument.\n\nClick to expand the code for the\n`TodoPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\n\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';// Declare your options to type-check your configuration.exporttypeMyOptions={defaultItem:string;};typeMyFixtures={todoPage:TodoPage;};// Specify both option and fixture types.exportconsttest=base.extend&lt;MyOptions&amp;MyFixtures&gt;({// Define an option and provide a default value.// We can later override it in the config.defaultItem:[\'Something nice\',{option:true}],// Our "todoPage" fixture depends on the option.todoPage:async({page,defaultItem},use)=&gt;{consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(defaultItem);awaituse(todoPage);awaittodoPage.removeAll();},});export{expect}from\'@playwright/test\';`\n```\n\nWe can now use the\n`todoPage`\nfixture as usual, and set the\n`defaultItem`\noption in the configuration file.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{MyOptions}from\'./my-test\';exportdefaultdefineConfig&lt;MyOptions&gt;({projects:[{name:\'shopping\',use:{defaultItem:\'Buy milk\'},},{name:\'wellbeing\',use:{defaultItem:\'Exercise!\'},},]});`\n```\n\nArray as an option value\n\nIf the value of your option is an array, for example\n`[{ name: \'Alice\' }, { name: \'Bob\' }]`\n, you\'ll need to wrap it into an extra array when providing the value. This is best illustrated with an example.\n\n```\n`typePerson={name:string};consttest=base.extend&lt;{persons:Person[]}&gt;({// Declare the option, default value is an empty array.persons:[[],{option:true}],});// Option value is an array of persons.constactualPersons=[{name:\'Alice\'},{name:\'Bob\'}];test.use({// CORRECT: Wrap the value into an array and pass the scope.persons:[actualPersons,{scope:\'test\'}],});test.use({// WRONG: passing an array value directly will not work.persons:actualPersons,});`\n```\n\nReset an option\n\nYou can reset an option to the value defined in the config file by setting it to\n`undefined`\n. Consider the following config that sets a\n`baseURL`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{baseURL:\'https://playwright.dev\',},});`\n```\n\nYou can now configure\n`baseURL`\nfor a file, and also opt-out for a single test.\n\nintro.spec.ts\n```\n`import{test}from\'@playwright/test\';// Configure baseURL for this file.test.use({baseURL:\'https://playwright.dev/docs/intro\'});test(\'check intro contents\',async({page})=&gt;{// This test will use "https://playwright.dev/docs/intro" base url as defined above.});test.describe(()=&gt;{// Reset the value to a config-defined one.test.use({baseURL:undefined});test(\'can navigate to intro from the home page\',async({page})=&gt;{// This test will use "https://playwright.dev" base url as defined in the config.});});`\n```\n\nIf you would like to completely reset the value to\n`undefined`\n, use a long-form fixture notation.\n\nintro.spec.ts\n```\n`import{test}from\'@playwright/test\';// Completely unset baseURL for this file.test.use({baseURL:[async({},use)=&gt;use(undefined),{scope:\'test\'}],});test(\'no base url\',async({page})=&gt;{// This test will not have a base url.});`\n```', 'Parameterize tests | Playwright', 'Playwright Test supports running multiple test projects at the same time. In the following example, we\'ll run two projects with different options.\n\nWe declare the option\n`person`\nand set the value in the config. The first project runs with the value\n`Alice`\nand the second with the value\n`Bob`\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\n\nWe can use this option in the test, similarly to\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nexample.spec.ts\n```\n`import{test}from\'./my-test\';test(\'test 1\',async({page,person})=&gt;{awaitpage.goto(`/index.html`);awaitexpect(page.locator(\'#node\')).toContainText(person);// ...});`\n```\n\nNow, we can run tests in multiple configurations by using projects.\n\nTypeScript\nJavaScript\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{TestOptions}from\'./my-test\';exportdefaultdefineConfig&lt;TestOptions&gt;({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\nplaywright.config.ts\n```\n`// @ts-checkmodule.exports=defineConfig({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\n\nWe can also use the option in a fixture. Learn more about\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\n\nnote\nParameterized projects behavior has changed in version 1.18.\nLearn more (https://playwright.dev/docs/release-notes#breaking-change-custom-config-options)\n.', 'Projects | Playwright', 'Projects can be also used to parametrize tests with your custom configuration - take a look at\nthis separate guide (https://playwright.dev/docs/test-parameterize#parameterized-projects)\n.']</t>
+          <t>['Playwright Test supports running multiple test projects that can be configured separately. You can use "option" fixtures to make your configuration options declarative and type safe. Learn more about\nparameterizing tests (https://playwright.dev/docs/test-parameterize)\n.\n\nBelow we\'ll create a\n`defaultItem`\noption in addition to the\n`todoPage`\nfixture from other examples. This option will be set in the configuration file. Note the tuple syntax and\n`{ option: true }`\nargument.\n\nClick to expand the code for the\n`TodoPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\n\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';// Declare your options to type-check your configuration.exporttypeMyOptions={defaultItem:string;};typeMyFixtures={todoPage:TodoPage;};// Specify both option and fixture types.exportconsttest=base.extend&lt;MyOptions&amp;MyFixtures&gt;({// Define an option and provide a default value.// We can later override it in the config.defaultItem:[\'Something nice\',{option:true}],// Our "todoPage" fixture depends on the option.todoPage:async({page,defaultItem},use)=&gt;{consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(defaultItem);awaituse(todoPage);awaittodoPage.removeAll();},});export{expect}from\'@playwright/test\';`\n```\n\nWe can now use the\n`todoPage`\nfixture as usual, and set the\n`defaultItem`\noption in the configuration file.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{MyOptions}from\'./my-test\';exportdefaultdefineConfig&lt;MyOptions&gt;({projects:[{name:\'shopping\',use:{defaultItem:\'Buy milk\'},},{name:\'wellbeing\',use:{defaultItem:\'Exercise!\'},},]});`\n```\n\nArray as an option value\n\nIf the value of your option is an array, for example\n`[{ name: \'Alice\' }, { name: \'Bob\' }]`\n, you\'ll need to wrap it into an extra array when providing the value. This is best illustrated with an example.\n\n```\n`typePerson={name:string};consttest=base.extend&lt;{persons:Person[]}&gt;({// Declare the option, default value is an empty array.persons:[[],{option:true}],});// Option value is an array of persons.constactualPersons=[{name:\'Alice\'},{name:\'Bob\'}];test.use({// CORRECT: Wrap the value into an array and pass the scope.persons:[actualPersons,{scope:\'test\'}],});test.use({// WRONG: passing an array value directly will not work.persons:actualPersons,});`\n```\n\nReset an option\n\nYou can reset an option to the value defined in the config file by setting it to\n`undefined`\n. Consider the following config that sets a\n`baseURL`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{baseURL:\'https://playwright.dev\',},});`\n```\n\nYou can now configure\n`baseURL`\nfor a file, and also opt-out for a single test.\n\nintro.spec.ts\n```\n`import{test}from\'@playwright/test\';// Configure baseURL for this file.test.use({baseURL:\'https://playwright.dev/docs/intro\'});test(\'check intro contents\',async({page})=&gt;{// This test will use "https://playwright.dev/docs/intro" base url as defined above.});test.describe(()=&gt;{// Reset the value to a config-defined one.test.use({baseURL:undefined});test(\'can navigate to intro from the home page\',async({page})=&gt;{// This test will use "https://playwright.dev" base url as defined in the config.});});`\n```\n\nIf you would like to completely reset the value to\n`undefined`\n, use a long-form fixture notation.\n\nintro.spec.ts\n```\n`import{test}from\'@playwright/test\';// Completely unset baseURL for this file.test.use({baseURL:[async({},use)=&gt;use(undefined),{scope:\'test\'}],});test(\'no base url\',async({page})=&gt;{// This test will not have a base url.});`\n```', 'Playwright Test supports running multiple test projects at the same time. In the following example, we\'ll run two projects with different options.\n\nWe declare the option\n`person`\nand set the value in the config. The first project runs with the value\n`Alice`\nand the second with the value\n`Bob`\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\n\nWe can use this option in the test, similarly to\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nexample.spec.ts\n```\n`import{test}from\'./my-test\';test(\'test 1\',async({page,person})=&gt;{awaitpage.goto(`/index.html`);awaitexpect(page.locator(\'#node\')).toContainText(person);// ...});`\n```\n\nNow, we can run tests in multiple configurations by using projects.\n\nTypeScript\nJavaScript\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{TestOptions}from\'./my-test\';exportdefaultdefineConfig&lt;TestOptions&gt;({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\nplaywright.config.ts\n```\n`// @ts-checkmodule.exports=defineConfig({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\n\nWe can also use the option in a fixture. Learn more about\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\n\nnote\nParameterized projects behavior has changed in version 1.18.\nLearn more (https://playwright.dev/docs/release-notes#breaking-change-custom-config-options)\n.', 'Projects can be also used to parametrize tests with your custom configuration - take a look at\nthis separate guide (https://playwright.dev/docs/test-parameterize#parameterized-projects)\n.', 'A project is logical group of tests running with the same configuration. We use projects so we can run tests on different browsers and devices. Projects are configured in the\n`playwright.config.ts`\nfile and once configured you can then run your tests on all projects or only on a specific project. You can also use projects to run the same tests in different configurations. For example, you can run the same tests in a logged-in and logged-out state.\n\nBy setting up projects you can also run a group of tests with different timeouts or retries or a group of tests against different environments such as staging and production, splitting tests per package/functionality and more.', 'You can either parameterize tests on a test level or on a project level.', "In addition to creating your own fixtures, you can also override existing fixtures to fit your needs. Consider the following example which overrides the\n`page`\nfixture by automatically navigating to the\n`baseURL`\n:\n\n```\n`import{testasbase}from'@playwright/test';exportconsttest=base.extend({page:async({baseURL,page},use)=&gt;{awaitpage.goto(baseURL);awaituse(page);},});`\n```\n\nNotice that in this example, the\n`page`\nfixture is able to depend on other built-in fixtures such as\ntestOptions.baseURL (https://playwright.dev/docs/api/class-testoptions#test-options-base-url)\n. We can now configure\n`baseURL`\nin the configuration file, or locally in the test file with\ntest.use() (https://playwright.dev/docs/api/class-test#test-use)\n.\n\nexample.spec.ts\n```\n`test.use({baseURL:'https://playwright.dev'});`\n```\n\nFixtures can also be overridden, causing the base fixture to be completely replaced with something different. For example, we could override the\ntestOptions.storageState (https://playwright.dev/docs/api/class-testoptions#test-options-storage-state)\nfixture to provide our own data.\n\n```\n`import{testasbase}from'@playwright/test';exportconsttest=base.extend({storageState:async({},use)=&gt;{constcookie=awaitgetAuthCookie();awaituse({cookies:[cookie]});},});`\n```", 'To create your own fixture, use\ntest.extend() (https://playwright.dev/docs/api/class-test#test-extend)\nto create a new\n`test`\nobject that will include it.\n\nBelow we create two fixtures\n`todoPage`\nand\n`settingsPage`\nthat follow the\nPage Object Model (https://playwright.dev/docs/pom)\npattern.\n\nClick to expand the code for the\n`TodoPage`\nand\n`SettingsPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\nSettingsPage is similar:\nsettings-page.ts\n```\n`importtype{Page}from\'@playwright/test\';exportclassSettingsPage{constructor(publicreadonly page:Page){}asyncswitchToDarkMode(){// ...}}`\n```\n\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';import{SettingsPage}from\'./settings-page\';// Declare the types of your fixtures.typeMyFixtures={todoPage:TodoPage;settingsPage:SettingsPage;};// Extend base test by providing "todoPage" and "settingsPage".// This new "test" can be used in multiple test files, and each of them will get the fixtures.exportconsttest=base.extend&lt;MyFixtures&gt;({todoPage:async({page},use)=&gt;{// Set up the fixture.consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(\'item1\');awaittodoPage.addToDo(\'item2\');// Use the fixture value in the test.awaituse(todoPage);// Clean up the fixture.awaittodoPage.removeAll();},settingsPage:async({page},use)=&gt;{awaituse(newSettingsPage(page));},});export{expect}from\'@playwright/test\';`\n```\n\nnote\nCustom fixture names should start with a letter or underscore, and can contain only letters, numbers, and underscores.']</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3583,27 +3636,34 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>To make a fixture behave differently per project, you use "option" fixtures. These allow you to define configuration options that are declarative and type-safe, which can then be overridden in your `playwright.config.ts` file for different projects.
+          <t>To make a fixture behave differently per project, you use **option fixtures**. These allow you to define configuration options that are declarative and type-safe, which can then be overridden in your project configuration.
 ### How to implement this:
-1.  **Define the option:** In your test file, extend the base test to define your option. You must provide a default value and include the `{ option: true }` argument in a tuple.
+1.  **Define the option:** Use `test.extend` to define your option. You must provide a default value and include the `{ option: true }` argument in a tuple.
     ```typescript
+    // my-test.ts
     export type MyOptions = {
       defaultItem: string;
     };
+    export const test = base.extend&lt;MyOptions&gt;({
+      // Define the option with a default value
+      defaultItem: ['Default value', { option: true }],
+    });
+    ```
+2.  **Use the option in a fixture:** Your fixture can depend on the option. When the fixture runs, it will receive the value currently active for that specific project.
+    ```typescript
     export const test = base.extend&lt;MyOptions &amp; MyFixtures&gt;({
-      // Define the option with a default value
-      defaultItem: ['Something nice', { option: true }],
-      // Use the option in your fixture
+      defaultItem: ['Default value', { option: true }],
+      // The fixture uses the option value
       todoPage: async ({ page, defaultItem }, use) =&gt; {
         const todoPage = new TodoPage(page);
-        await todoPage.goto();
         await todoPage.addToDo(defaultItem);
         await use(todoPage);
       },
     });
     ```
-2.  **Configure per project:** In your `playwright.config.ts`, set the value of that option within the `use` property of each project.
+3.  **Configure per project:** In your `playwright.config.ts`, set the option value within the `use` property of each project.
     ```typescript
+    // playwright.config.ts
     export default defineConfig&lt;MyOptions&gt;({
       projects: [
         {
@@ -3617,7 +3677,10 @@
       ]
     });
     ```
-When you run your tests, Playwright will use the specific `defaultItem` value defined for each project, and your `todoPage` fixture will automatically receive that value.</t>
+### Important Considerations:
+*   **Array values:** If your option value is an array, you must wrap it in an extra array when providing the value (e.g., `persons: [actualPersons, { scope: 'test' }]`).
+*   **Resetting values:** You can reset an option to the value defined in the config file by setting it to `undefined` within a test or `test.describe` block using `test.use()`.
+*   **Scope:** Options are typically used to parameterize tests at the project level, allowing you to run the same tests in different configurations (e.g., different environments or data sets).</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3626,28 +3689,28 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.009072499999999002</v>
+        <v>0.001784</v>
       </c>
       <c r="G49" t="n">
-        <v>33790</v>
+        <v>35645</v>
       </c>
       <c r="H49" t="n">
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="J49" t="n">
         <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>0.07407407407407407</v>
+        <v>0.06690140845070422</v>
       </c>
       <c r="L49" t="n">
-        <v>0.3783783783783784</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="M49" t="n">
-        <v>0.499999999975</v>
+        <v>0.99999999995</v>
       </c>
       <c r="N49" t="n">
         <v>1</v>
@@ -3661,7 +3724,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>['Sometimes you want to tag your tests as\n`@fast`\nor\n`@slow`\n, and then filter by tag in the test report. Or you might want to only run tests that have a certain tag.\n\nTo tag a test, either provide an additional details object when declaring a test, or add\n`@`\n-token to the test title. Note that tags must start with\n`@`\nsymbol.\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'test login page\',{tag:\'@fast\',},async({page})=&gt;{// ...});test(\'test full report @slow\',async({page})=&gt;{// ...});`\n```\n\nYou can also tag all tests in a group or provide multiple tags:\n\n```\n`import{test,expect}from\'@playwright/test\';test.describe(\'group\',{tag:\'@report\',},()=&gt;{test(\'test report header\',async({page})=&gt;{// ...});test(\'test full report\',{tag:[\'@slow\',\'@vrt\'],},async({page})=&gt;{// ...});});`\n```\n\nYou can now run tests that have a particular tag with\n--grep (https://playwright.dev/docs/test-cli#all-options)\ncommand line option.\n\nBash\nPowerShell\nBatch\n```\n`npx playwrighttest--grep@fast`\n```\n```\n`npx playwright test--grep"@fast"`\n```\n```\n`npxplaywright test--grep@fast`\n```\n\nOr if you want the opposite, you can skip the tests with a certain tag:\n\nBash\nPowerShell\nBatch\n```\n`npx playwrighttest--grep-invert @fast`\n```\n```\n`npx playwright test--grep-invert"@fast"`\n```\n```\n`npxplaywright test--grep-invert@fast`\n```\n\nTo run tests containing either tag (logical\n`OR`\noperator):\n\nBash\nPowerShell\nBatch\n```\n`npx playwrighttest--grep"@fast|@slow"`\n```\n```\n`npx playwright test--grep--%"@fast^|@slow"`\n```\n```\n`npxplaywright test--grep"@fast^|@slow"`\n```\n\nOr run tests containing both tags (logical\n`AND`\noperator) using regex lookaheads:\n\n```\n`npx playwrighttest--grep"(?=.*@fast)(?=.*@slow)"`\n```\n\nYou can also filter tests in the configuration file via\ntestConfig.grep (https://playwright.dev/docs/api/class-testconfig#test-config-grep)\nand\ntestProject.grep (https://playwright.dev/docs/api/class-testproject#test-project-grep)\n.', 'We can split tests into projects and use filters to run a subset of tests. For example, we can create a project that runs tests using a filter matching all tests with a specific file name. We can then have another group of tests that ignore specific test files.\n\nHere is an example that defines a common timeout and two projects. The "Smoke" project runs a small subset of tests without retries, and "Default" project runs all other tests with retries.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({timeout:60000,// Timeout is shared between all tests.projects:[{name:\'Smoke\',testMatch:/.*smoke.spec.ts/,retries:0,},{name:\'Default\',testIgnore:/.*smoke.spec.ts/,retries:2,},],});`\n```', 'Annotations | Playwright', 'Projects | Playwright', 'Command line | Playwright\n\nPlaywright provides a powerful command line interface for running tests, generating code, debugging, and more. The most up to date list of commands and arguments available on the CLI can always be retrieved via\n`npx playwright --help`\n.']</t>
+          <t>['Sometimes you want to tag your tests as\n`@fast`\nor\n`@slow`\n, and then filter by tag in the test report. Or you might want to only run tests that have a certain tag.\n\nTo tag a test, either provide an additional details object when declaring a test, or add\n`@`\n-token to the test title. Note that tags must start with\n`@`\nsymbol.\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'test login page\',{tag:\'@fast\',},async({page})=&gt;{// ...});test(\'test full report @slow\',async({page})=&gt;{// ...});`\n```\n\nYou can also tag all tests in a group or provide multiple tags:\n\n```\n`import{test,expect}from\'@playwright/test\';test.describe(\'group\',{tag:\'@report\',},()=&gt;{test(\'test report header\',async({page})=&gt;{// ...});test(\'test full report\',{tag:[\'@slow\',\'@vrt\'],},async({page})=&gt;{// ...});});`\n```\n\nYou can now run tests that have a particular tag with\n--grep (https://playwright.dev/docs/test-cli#all-options)\ncommand line option.\n\nBash\nPowerShell\nBatch\n```\n`npx playwrighttest--grep@fast`\n```\n```\n`npx playwright test--grep"@fast"`\n```\n```\n`npxplaywright test--grep@fast`\n```\n\nOr if you want the opposite, you can skip the tests with a certain tag:\n\nBash\nPowerShell\nBatch\n```\n`npx playwrighttest--grep-invert @fast`\n```\n```\n`npx playwright test--grep-invert"@fast"`\n```\n```\n`npxplaywright test--grep-invert@fast`\n```\n\nTo run tests containing either tag (logical\n`OR`\noperator):\n\nBash\nPowerShell\nBatch\n```\n`npx playwrighttest--grep"@fast|@slow"`\n```\n```\n`npx playwright test--grep--%"@fast^|@slow"`\n```\n```\n`npxplaywright test--grep"@fast^|@slow"`\n```\n\nOr run tests containing both tags (logical\n`AND`\noperator) using regex lookaheads:\n\n```\n`npx playwrighttest--grep"(?=.*@fast)(?=.*@slow)"`\n```\n\nYou can also filter tests in the configuration file via\ntestConfig.grep (https://playwright.dev/docs/api/class-testconfig#test-config-grep)\nand\ntestProject.grep (https://playwright.dev/docs/api/class-testproject#test-project-grep)\n.', 'We can split tests into projects and use filters to run a subset of tests. For example, we can create a project that runs tests using a filter matching all tests with a specific file name. We can then have another group of tests that ignore specific test files.\n\nHere is an example that defines a common timeout and two projects. The "Smoke" project runs a small subset of tests without retries, and "Default" project runs all other tests with retries.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({timeout:60000,// Timeout is shared between all tests.projects:[{name:\'Smoke\',testMatch:/.*smoke.spec.ts/,retries:0,},{name:\'Default\',testIgnore:/.*smoke.spec.ts/,retries:2,},],});`\n```', 'Added in: v1.10\n\ntestProject.grep\n\nFilter to only run tests with a title matching one of the patterns. For example, passing\n`grep: /cart/`\nshould only run tests with "cart" in the title. Also available globally and in the\ncommand line (https://playwright.dev/docs/test-cli)\nwith the\n`-g`\noption. The regular expression will be tested against the string that consists of the project name, the test file name, the\n`test.describe`\nname (if any), the test name and the test tags divided by spaces, e.g.\n`chromium my-test.spec.ts my-suite my-test`\n.\n\n`grep`\noption is also useful for\ntagging tests (https://playwright.dev/docs/test-annotations#tag-tests)\n.\n\nUsage\n\n```\n`testProject.grep`\n```\n\nType\n\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n|\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n&gt;', 'Options\n`--test-list`\nand\n`--test-list-invert`\naccept a path to a test list file. This file should list tests in the format similar to the output produced in\n`--list`\nmode.\n\n```\n`# This is a test list file.# It can include comments and empty lines.# Run ALL tests in a file:path/to/example.spec.ts# Run all tests in a file for a specific project:[chromium] › path/to/example.spec.ts# Run all tests in a specific group/suite:path/to/example.spec.ts › suite name# Run all tests in a nested group:path/to/example.spec.ts › outer suite › inner suite# Fully qualified test with a project:[chromium] › path/to/example.spec.ts:3:9 › suite › nested suite › example test# This test is included for all projects:path/to/example.spec.ts:3:9 › example test# Use "›" or "&gt;" as a separator:[firefox] &gt; example.spec.ts &gt; suite &gt; nested suite &gt; example test# Line/column numbers are completely ignored, you can omit them.# Three entries below refer to the same test:example.spec.ts › example testexample.spec.ts:15 › example testexample.spec.ts:42:42 › example test`\n```', "Filter tests by glob patterns or regular expressions.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({// Glob patterns or regular expressions to ignore test files.testIgnore:'*test-assets',// Glob patterns or regular expressions that match test files.testMatch:'*todo-tests/*.spec.ts',});`\n```\n\nOption\nDescription\ntestConfig.testIgnore (https://playwright.dev/docs/api/class-testconfig#test-config-test-ignore)\nGlob patterns or regular expressions that should be ignored when looking for the test files. For example,\n`'*test-assets'`\ntestConfig.testMatch (https://playwright.dev/docs/api/class-testconfig#test-config-test-match)\nGlob patterns or regular expressions that match test files. For example,\n`'*todo-tests/*.spec.ts'`\n. By default, Playwright runs\n`.*(test|spec).(js|ts|mjs)`\nfiles.", 'Added in: v1.10\n\ntestProject.grepInvert\n\nFilter to only run tests with a title\nnot\nmatching any of the patterns. This is the opposite of\ntestProject.grep (https://playwright.dev/docs/api/class-testproject#test-project-grep)\n. Also available globally and in the\ncommand line (https://playwright.dev/docs/test-cli)\nwith the\n`--grep-invert`\noption.\n\n`grepInvert`\noption is also useful for\ntagging tests (https://playwright.dev/docs/test-annotations#tag-tests)\n.\n\nUsage\n\n```\n`testProject.grepInvert`\n```\n\nType\n\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n|\nArray (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array)\n&lt;\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n&gt;', 'Option\nDescription\n`--debug`\nRun tests with Playwright Inspector. Shortcut for\n`PWDEBUG=1`\nenvironment variable and\n`--timeout=0 --max-failures=1 --headed --workers=1`\noptions.\n`--headed`\nRun tests in headed browsers (default: headless).\n`-g &lt;grep&gt;`\nor\n`--grep &lt;grep&gt;`\nOnly run tests matching this regular expression (default: ".*").\n`--project &lt;project-name...&gt;`\nOnly run tests from the specified list of projects, supports \'*\' wildcard (default: run all projects).\n`--ui`\nRun tests in interactive UI mode.\n`-j &lt;workers&gt;`\nor\n`--workers &lt;workers&gt;`\nNumber of concurrent workers or percentage of logical CPU cores, use 1 to run in a single worker (default: 50%).']</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3671,30 +3734,36 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>To tag tests, add the `@` symbol to the test title or provide a `tag` property in the test details object:
+          <t>### Tagging and Running Tests from the CLI
+To tag tests, add an `@` symbol followed by the tag name to the test title, or provide a `tag` property in the test details object:
 ```javascript
-// Via title
-test('test title @fast', async ({ page }) =&gt; { ... });
-// Via details object
-test('test title', { tag: '@fast' }, async ({ page }) =&gt; { ... });
-```
-To run only tests with a specific tag from the CLI, use the `--grep` command:
+// Using test details object
+test('test login page', { tag: '@fast' }, async ({ page }) =&gt; { ... });
+// Using test title
+test('test full report @slow', async ({ page }) =&gt; { ... });
+```
+To run only tests with a specific tag from the CLI, use the `--grep` option:
 `npx playwright test --grep @fast`
-To carve tests into subsets at the project level, define projects in your `playwright.config.ts` file using `testMatch` or `testIgnore` to filter by file patterns:
+To skip tests with a specific tag, use `--grep-invert`:
+`npx playwright test --grep-invert @fast`
+### Carving Tests into Subsets at the Project Level
+You can carve tests into subsets by defining projects in your `playwright.config.ts` file and using `testMatch` or `testIgnore` to filter which files belong to each project:
 ```javascript
+import { defineConfig } from '@playwright/test';
 export default defineConfig({
   projects: [
     {
       name: 'Smoke',
-      testMatch: /.*smoke.spec.ts/,
+      testMatch: /.*smoke.spec.ts/, // Only runs files matching this pattern
     },
     {
       name: 'Default',
-      testIgnore: /.*smoke.spec.ts/,
+      testIgnore: /.*smoke.spec.ts/, // Runs all files except those matching this pattern
     },
   ],
 });
-```</t>
+```
+Additionally, you can use `testProject.grep` or `testProject.grepInvert` within a project definition to filter tests based on titles or tags at the project level.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3703,28 +3772,28 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.00813675</v>
+        <v>0.0011285</v>
       </c>
       <c r="G50" t="n">
-        <v>30947</v>
+        <v>41353</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>0.09803921568627451</v>
+        <v>0.07446808510638298</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>0.8095238094968253</v>
       </c>
       <c r="N50" t="n">
         <v>1</v>
@@ -3738,7 +3807,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>['Parameterize tests | Playwright', 'You can either parameterize tests on a test level or on a project level.', 'Playwright Test supports running multiple test projects at the same time. In the following example, we\'ll run two projects with different options.\n\nWe declare the option\n`person`\nand set the value in the config. The first project runs with the value\n`Alice`\nand the second with the value\n`Bob`\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\n\nWe can use this option in the test, similarly to\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nexample.spec.ts\n```\n`import{test}from\'./my-test\';test(\'test 1\',async({page,person})=&gt;{awaitpage.goto(`/index.html`);awaitexpect(page.locator(\'#node\')).toContainText(person);// ...});`\n```\n\nNow, we can run tests in multiple configurations by using projects.\n\nTypeScript\nJavaScript\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{TestOptions}from\'./my-test\';exportdefaultdefineConfig&lt;TestOptions&gt;({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\nplaywright.config.ts\n```\n`// @ts-checkmodule.exports=defineConfig({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\n\nWe can also use the option in a fixture. Learn more about\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\n\nnote\nParameterized projects behavior has changed in version 1.18.\nLearn more (https://playwright.dev/docs/release-notes#breaking-change-custom-config-options)\n.', "example.spec.ts\n```\n`[{name:'Alice',expected:'Hello, Alice!'},{name:'Bob',expected:'Hello, Bob!'},{name:'Charlie',expected:'Hello, Charlie!'},].forEach(({name,expected})=&gt;{// You can also do it with test.describe() or with multiple tests as long the test name is unique.test(`testing with${name}`,async({page})=&gt;{awaitpage.goto(`https://example.com/greet?name=${name}`);awaitexpect(page.getByRole('heading')).toHaveText(expected);});});`\n```", 'Playwright Test supports running multiple test projects that can be configured separately. You can use "option" fixtures to make your configuration options declarative and type safe. Learn more about\nparameterizing tests (https://playwright.dev/docs/test-parameterize)\n.\n\nBelow we\'ll create a\n`defaultItem`\noption in addition to the\n`todoPage`\nfixture from other examples. This option will be set in the configuration file. Note the tuple syntax and\n`{ option: true }`\nargument.\n\nClick to expand the code for the\n`TodoPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\n\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';// Declare your options to type-check your configuration.exporttypeMyOptions={defaultItem:string;};typeMyFixtures={todoPage:TodoPage;};// Specify both option and fixture types.exportconsttest=base.extend&lt;MyOptions&amp;MyFixtures&gt;({// Define an option and provide a default value.// We can later override it in the config.defaultItem:[\'Something nice\',{option:true}],// Our "todoPage" fixture depends on the option.todoPage:async({page,defaultItem},use)=&gt;{consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(defaultItem);awaituse(todoPage);awaittodoPage.removeAll();},});export{expect}from\'@playwright/test\';`\n```\n\nWe can now use the\n`todoPage`\nfixture as usual, and set the\n`defaultItem`\noption in the configuration file.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{MyOptions}from\'./my-test\';exportdefaultdefineConfig&lt;MyOptions&gt;({projects:[{name:\'shopping\',use:{defaultItem:\'Buy milk\'},},{name:\'wellbeing\',use:{defaultItem:\'Exercise!\'},},]});`\n```\n\nArray as an option value\n\nIf the value of your option is an array, for example\n`[{ name: \'Alice\' }, { name: \'Bob\' }]`\n, you\'ll need to wrap it into an extra array when providing the value. This is best illustrated with an example.\n\n```\n`typePerson={name:string};consttest=base.extend&lt;{persons:Person[]}&gt;({// Declare the option, default value is an empty array.persons:[[],{option:true}],});// Option value is an array of persons.constactualPersons=[{name:\'Alice\'},{name:\'Bob\'}];test.use({// CORRECT: Wrap the value into an array and pass the scope.persons:[actualPersons,{scope:\'test\'}],});test.use({// WRONG: passing an array value directly will not work.persons:actualPersons,});`\n```\n\nReset an option\n\nYou can reset an option to the value defined in the config file by setting it to\n`undefined`\n. Consider the following config that sets a\n`baseURL`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{baseURL:\'https://playwright.dev\',},});`\n```\n\nYou can now configure\n`baseURL`\nfor a file, and also opt-out for a single test.\n\nintro.spec.ts\n```\n`import{test}from\'@playwright/test\';// Configure baseURL for this file.test.use({baseURL:\'https://playwright.dev/docs/intro\'});test(\'check intro contents\',async({page})=&gt;{// This test will use "https://playwright.dev/docs/intro" base url as defined above.});test.describe(()=&gt;{// Reset the value to a config-defined one.test.use({baseURL:undefined});test(\'can navigate to intro from the home page\',async({page})=&gt;{// This test will use "https://playwright.dev" base url as defined in the config.});});`\n```\n\nIf you would like to completely reset the value to\n`undefined`\n, use a long-form fixture notation.\n\nintro.spec.ts\n```\n`import{test}from\'@playwright/test\';// Completely unset baseURL for this file.test.use({baseURL:[async({},use)=&gt;use(undefined),{scope:\'test\'}],});test(\'no base url\',async({page})=&gt;{// This test will not have a base url.});`\n```', "By setting up projects we can also run a group of tests with different timeouts or retries or run a group of tests against different environments. For example we can run our tests against a staging environment with 2 retries as well as against a production environment with 0 retries.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({timeout:60000,// Timeout is shared between all tests.projects:[{name:'staging',use:{baseURL:'staging.example.com',},retries:2,},{name:'production',use:{baseURL:'production.example.com',},retries:0,},],});`\n```"]</t>
+          <t>["By setting up projects we can also run a group of tests with different timeouts or retries or run a group of tests against different environments. For example we can run our tests against a staging environment with 2 retries as well as against a production environment with 0 retries.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({timeout:60000,// Timeout is shared between all tests.projects:[{name:'staging',use:{baseURL:'staging.example.com',},retries:2,},{name:'production',use:{baseURL:'production.example.com',},retries:0,},],});`\n```", "example.spec.ts\n```\n`[{name:'Alice',expected:'Hello, Alice!'},{name:'Bob',expected:'Hello, Bob!'},{name:'Charlie',expected:'Hello, Charlie!'},].forEach(({name,expected})=&gt;{// You can also do it with test.describe() or with multiple tests as long the test name is unique.test(`testing with${name}`,async({page})=&gt;{awaitpage.goto(`https://example.com/greet?name=${name}`);awaitexpect(page.getByRole('heading')).toHaveText(expected);});});`\n```", 'Playwright Test supports running multiple test projects at the same time. In the following example, we\'ll run two projects with different options.\n\nWe declare the option\n`person`\nand set the value in the config. The first project runs with the value\n`Alice`\nand the second with the value\n`Bob`\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],});`\n```\n\nWe can use this option in the test, similarly to\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nexample.spec.ts\n```\n`import{test}from\'./my-test\';test(\'test 1\',async({page,person})=&gt;{awaitpage.goto(`/index.html`);awaitexpect(page.locator(\'#node\')).toContainText(person);// ...});`\n```\n\nNow, we can run tests in multiple configurations by using projects.\n\nTypeScript\nJavaScript\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{TestOptions}from\'./my-test\';exportdefaultdefineConfig&lt;TestOptions&gt;({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\nplaywright.config.ts\n```\n`// @ts-checkmodule.exports=defineConfig({projects:[{name:\'alice\',use:{person:\'Alice\'},},{name:\'bob\',use:{person:\'Bob\'},},]});`\n```\n\nWe can also use the option in a fixture. Learn more about\nfixtures (https://playwright.dev/docs/test-fixtures)\n.\n\nTypeScript\nJavaScript\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';exporttypeTestOptions={person:string;};exportconsttest=base.extend&lt;TestOptions&gt;({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\nmy-test.js\n```\n`constbase=require(\'@playwright/test\');exports.test=base.test.extend({// Define an option and provide a default value.// We can later override it in the config.person:[\'John\',{option:true}],// Override default "page" fixture.page:async({page,person},use)=&gt;{awaitpage.goto(\'/chat\');// We use "person" parameter as a "name" for the chat room.awaitpage.getByLabel(\'User Name\').fill(person);awaitpage.getByText(\'Enter chat room\').click();// Each test will get a "page" that already has the person name.awaituse(page);},});`\n```\n\nnote\nParameterized projects behavior has changed in version 1.18.\nLearn more (https://playwright.dev/docs/release-notes#breaking-change-custom-config-options)\n.', 'You can either parameterize tests on a test level or on a project level.', 'Playwright Test supports running multiple test projects that can be configured separately. You can use "option" fixtures to make your configuration options declarative and type safe. Learn more about\nparameterizing tests (https://playwright.dev/docs/test-parameterize)\n.\n\nBelow we\'ll create a\n`defaultItem`\noption in addition to the\n`todoPage`\nfixture from other examples. This option will be set in the configuration file. Note the tuple syntax and\n`{ option: true }`\nargument.\n\nClick to expand the code for the\n`TodoPage`\ntodo-page.ts\n```\n`importtype{Page,Locator}from\'@playwright/test\';exportclassTodoPage{privatereadonly inputBox:Locator;privatereadonly todoItems:Locator;constructor(publicreadonly page:Page){this.inputBox=this.page.locator(\'input.new-todo\');this.todoItems=this.page.getByTestId(\'todo-item\');}asyncgoto(){awaitthis.page.goto(\'https://demo.playwright.dev/todomvc/\');}asyncaddToDo(text:string){awaitthis.inputBox.fill(text);awaitthis.inputBox.press(\'Enter\');}asyncremove(text:string){consttodo=this.todoItems.filter({hasText:text});awaittodo.hover();awaittodo.getByLabel(\'Delete\').click();}asyncremoveAll(){while((awaitthis.todoItems.count())&gt;0){awaitthis.todoItems.first().hover();awaitthis.todoItems.getByLabel(\'Delete\').first().click();}}}`\n```\n\nmy-test.ts\n```\n`import{testasbase}from\'@playwright/test\';import{TodoPage}from\'./todo-page\';// Declare your options to type-check your configuration.exporttypeMyOptions={defaultItem:string;};typeMyFixtures={todoPage:TodoPage;};// Specify both option and fixture types.exportconsttest=base.extend&lt;MyOptions&amp;MyFixtures&gt;({// Define an option and provide a default value.// We can later override it in the config.defaultItem:[\'Something nice\',{option:true}],// Our "todoPage" fixture depends on the option.todoPage:async({page,defaultItem},use)=&gt;{consttodoPage=newTodoPage(page);awaittodoPage.goto();awaittodoPage.addToDo(defaultItem);awaituse(todoPage);awaittodoPage.removeAll();},});export{expect}from\'@playwright/test\';`\n```\n\nWe can now use the\n`todoPage`\nfixture as usual, and set the\n`defaultItem`\noption in the configuration file.\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';importtype{MyOptions}from\'./my-test\';exportdefaultdefineConfig&lt;MyOptions&gt;({projects:[{name:\'shopping\',use:{defaultItem:\'Buy milk\'},},{name:\'wellbeing\',use:{defaultItem:\'Exercise!\'},},]});`\n```\n\nArray as an option value\n\nIf the value of your option is an array, for example\n`[{ name: \'Alice\' }, { name: \'Bob\' }]`\n, you\'ll need to wrap it into an extra array when providing the value. This is best illustrated with an example.\n\n```\n`typePerson={name:string};consttest=base.extend&lt;{persons:Person[]}&gt;({// Declare the option, default value is an empty array.persons:[[],{option:true}],});// Option value is an array of persons.constactualPersons=[{name:\'Alice\'},{name:\'Bob\'}];test.use({// CORRECT: Wrap the value into an array and pass the scope.persons:[actualPersons,{scope:\'test\'}],});test.use({// WRONG: passing an array value directly will not work.persons:actualPersons,});`\n```\n\nReset an option\n\nYou can reset an option to the value defined in the config file by setting it to\n`undefined`\n. Consider the following config that sets a\n`baseURL`\n:\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({use:{baseURL:\'https://playwright.dev\',},});`\n```\n\nYou can now configure\n`baseURL`\nfor a file, and also opt-out for a single test.\n\nintro.spec.ts\n```\n`import{test}from\'@playwright/test\';// Configure baseURL for this file.test.use({baseURL:\'https://playwright.dev/docs/intro\'});test(\'check intro contents\',async({page})=&gt;{// This test will use "https://playwright.dev/docs/intro" base url as defined above.});test.describe(()=&gt;{// Reset the value to a config-defined one.test.use({baseURL:undefined});test(\'can navigate to intro from the home page\',async({page})=&gt;{// This test will use "https://playwright.dev" base url as defined in the config.});});`\n```\n\nIf you would like to completely reset the value to\n`undefined`\n, use a long-form fixture notation.\n\nintro.spec.ts\n```\n`import{test}from\'@playwright/test\';// Completely unset baseURL for this file.test.use({baseURL:[async({},use)=&gt;use(undefined),{scope:\'test\'}],});test(\'no base url\',async({page})=&gt;{// This test will not have a base url.});`\n```', 'Projects can be also used to parametrize tests with your custom configuration - take a look at\nthis separate guide (https://playwright.dev/docs/test-parameterize#parameterized-projects)\n.', 'A project is logical group of tests running with the same configuration. We use projects so we can run tests on different browsers and devices. Projects are configured in the\n`playwright.config.ts`\nfile and once configured you can then run your tests on all projects or only on a specific project. You can also use projects to run the same tests in different configurations. For example, you can run the same tests in a logged-in and logged-out state.\n\nBy setting up projects you can also run a group of tests with different timeouts or retries or a group of tests against different environments such as staging and production, splitting tests per package/functionality and more.']</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3748,34 +3817,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Playwright allows you to parameterize tests at either the test level or the project level.
+          <t>You can parameterize tests at either the test level or the project level.
 ### Test Level Parameterization
-At the test level, you can iterate over a data set to generate multiple tests. This is done by using a loop (such as `.forEach()`) to call `test()` or `test.describe()` multiple times, ensuring each test name is unique.
-```typescript
-[{name:'Alice',expected:'Hello, Alice!'},{name:'Bob',expected:'Hello, Bob!'}].forEach(({name,expected})=&gt;{
-  test(`testing with ${name}`, async({page}) =&gt; {
+At the test level, you parameterize tests by iterating over an array of values and creating tests dynamically. This is done within your test file (e.g., `example.spec.ts`) using a loop, such as `.forEach()`, to call `test()` or `test.describe()` for each set of data.
+```javascript
+[{name:'Alice',expected:'Hello, Alice!'}, {name:'Bob',expected:'Hello, Bob!'}].forEach(({name,expected})=&gt;{
+  test(`testing with ${name}`, async({page})=&gt;{
     await page.goto(`https://example.com/greet?name=${name}`);
     await expect(page.getByRole('heading')).toHaveText(expected);
   });
 });
 ```
 ### Project Level Parameterization
-At the project level, you use "option" fixtures to define configuration options that can be set or overridden in the `playwright.config.ts` file. This is the recommended approach for running the same tests across different environments or configurations.
-1.  **Define the option:** Extend the test object with your options, providing a default value and setting `{ option: true }`.
-    ```typescript
-    export const test = base.extend&lt;TestOptions&gt;({
-      person: ['John', { option: true }],
-    });
-    ```
-2.  **Configure projects:** In `playwright.config.ts`, define multiple projects, each providing a different value for the option.
-    ```typescript
-    projects: [
-      { name: 'alice', use: { person: 'Alice' } },
-      { name: 'bob', use: { person: 'Bob' } },
-    ]
-    ```
-3.  **Use in tests:** The option can be accessed in tests or fixtures just like standard fixtures.
-Projects are also used to run groups of tests against different environments (e.g., staging vs. production) by configuring project-specific settings like `baseURL`, `retries`, or `timeout`.</t>
+At the project level, you parameterize tests by defining projects in your `playwright.config.ts` file. This allows you to run the same group of tests with different configurations, such as different environments (staging vs. production), different timeouts, or different retry counts.
+To parameterize with custom values across projects:
+1. **Define an option:** Extend your test base in a separate file (e.g., `my-test.ts`) using `base.extend` and define your option with `{ option: true }`.
+2. **Use the option:** Access the option in your tests or fixtures as you would with standard fixtures.
+3. **Configure projects:** In `playwright.config.ts`, define multiple projects and provide specific values for your custom option within the `use` block for each project.
+```javascript
+// playwright.config.ts
+export default defineConfig&lt;TestOptions&gt;({
+  projects: [
+    { name: 'alice', use: { person: 'Alice' } },
+    { name: 'bob', use: { person: 'Bob' } },
+  ]
+});
+```
+### Key Differences
+*   **Scope:** Test-level parameterization creates multiple individual test instances within a single execution context based on data arrays. Project-level parameterization groups tests into distinct logical sets that run with specific configurations (like different base URLs or custom options) defined in the configuration file.
+*   **Configuration:** Test-level parameterization is implemented directly in the test code. Project-level parameterization is managed in `playwright.config.ts`, allowing you to run tests against different environments or configurations without modifying the test files themselves.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3784,28 +3854,28 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.009776</v>
+        <v>0.00161025</v>
       </c>
       <c r="G51" t="n">
-        <v>35629</v>
+        <v>36389</v>
       </c>
       <c r="H51" t="n">
         <v>0.75</v>
       </c>
       <c r="I51" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="J51" t="n">
         <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1129707112970711</v>
+        <v>0.09006211180124224</v>
       </c>
       <c r="L51" t="n">
-        <v>0.7297297297297297</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="M51" t="n">
-        <v>0.5888888888692593</v>
+        <v>0.3666666666483334</v>
       </c>
       <c r="N51" t="n">
         <v>1</v>
@@ -3823,7 +3893,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>["note\nIt's usually better to find a\nmore reliable way (https://playwright.dev/docs/locators#quick-guide)\nto uniquely identify the element instead of checking the visibility.\n\nConsider a page with two buttons, the first invisible and the second\nvisible (https://playwright.dev/docs/actionability#visible)\n.\n\n```\n`&lt;buttonstyle='display:none'&gt;Invisible&lt;/button&gt;&lt;button&gt;Visible&lt;/button&gt;`\n```\n\nThis will find both buttons and throw a\nstrictness (https://playwright.dev/docs/locators#strictness)\nviolation error:\n```\n`awaitpage.locator('button').click();`\n```\nThis will only find a second button, because it is visible, and then click it.\n```\n`awaitpage.locator('button').filter({visible:true}).click();`\n```", 'Locators | Playwright', "```\n`awaitpage.getByRole('button').click();`\n```\n\nOn the other hand, Playwright understands when you perform a multiple-element operation, so the following call works perfectly fine when the locator resolves to multiple elements.", "```\n`awaitpage.getByRole('button').count();`\n```\n\nYou can explicitly opt-out from strictness check by telling Playwright which element to use when multiple elements match, through\nlocator.first() (https://playwright.dev/docs/api/class-locator#locator-first)\n,\nlocator.last() (https://playwright.dev/docs/api/class-locator#locator-last)\n, and\nlocator.nth() (https://playwright.dev/docs/api/class-locator#locator-nth)\n. These methods are\nnot recommended\nbecause when your page changes, Playwright may click on an element you did not intend. Instead, follow best practices above to create a locator that uniquely identifies the target element."]</t>
+          <t>["note\nIt's usually better to find a\nmore reliable way (https://playwright.dev/docs/locators#quick-guide)\nto uniquely identify the element instead of checking the visibility.\n\nConsider a page with two buttons, the first invisible and the second\nvisible (https://playwright.dev/docs/actionability#visible)\n.\n\n```\n`&lt;buttonstyle='display:none'&gt;Invisible&lt;/button&gt;&lt;button&gt;Visible&lt;/button&gt;`\n```\n\nThis will find both buttons and throw a\nstrictness (https://playwright.dev/docs/locators#strictness)\nviolation error:\n```\n`awaitpage.locator('button').click();`\n```\nThis will only find a second button, because it is visible, and then click it.\n```\n`awaitpage.locator('button').filter({visible:true}).click();`\n```", "Playwright supports the\n`:visible`\npseudo class in CSS selectors. For example,\n`css=button`\nmatches all the buttons on the page, while\n`css=button:visible`\nonly matches visible buttons. This is useful to distinguish elements that are very similar but differ in visibility.\n\nConsider a page with two buttons, first invisible and second visible.\n\n```\n`&lt;buttonstyle='display:none'&gt;Invisible&lt;/button&gt;&lt;button&gt;Visible&lt;/button&gt;`\n```\n\nThis will find both buttons and throw a\nstrictness (https://playwright.dev/docs/locators#strictness)\nviolation error:\n```\n`awaitpage.locator('button').click();`\n```\nThis will only find a second button, because it is visible, and then click it.\n```\n`awaitpage.locator('button:visible').click();`\n```", 'Added in: v1.22\n\nlocator.filter\n\nThis method narrows existing locator according to the options, for example filters by text. It can be chained to filter multiple times.\n\nUsage\n\n```\n`constrowLocator=page.locator(\'tr\');// ...awaitrowLocator.filter({hasText:\'text in column 1\'}).filter({has:page.getByRole(\'button\',{name:\'column 2 button\'})}).screenshot();`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`has`\nLocator (https://playwright.dev/docs/api/class-locator)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-filter-option-has)\nNarrows down the results of the method to those which contain elements matching this relative locator. For example,\n`article`\nthat has\n`text=Playwright`\nmatches\n`&lt;article&gt;&lt;div&gt;Playwright&lt;/div&gt;&lt;/article&gt;`\n.\nInner locator\nmust be relative\nto the outer locator and is queried starting with the outer locator match, not the document root. For example, you can find\n`content`\nthat has\n`div`\nin\n`&lt;article&gt;&lt;content&gt;&lt;div&gt;Playwright&lt;/div&gt;&lt;/content&gt;&lt;/article&gt;`\n. However, looking for\n`content`\nthat has\n`article div`\nwill fail, because the inner locator must be relative and should not use any elements outside the\n`content`\n.\nNote that outer and inner locators must belong to the same frame. Inner locator must not contain\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\ns.\n`hasNot`\nLocator (https://playwright.dev/docs/api/class-locator)\n(optional)\nAdded in: v1.33\n# (https://playwright.dev/docs/api/class-locator#locator-filter-option-has-not)\nMatches elements that do not contain an element that matches an inner locator. Inner locator is queried against the outer one. For example,\n`article`\nthat does not have\n`div`\nmatches\n`&lt;article&gt;&lt;span&gt;Playwright&lt;/span&gt;&lt;/article&gt;`\n.\nNote that outer and inner locators must belong to the same frame. Inner locator must not contain\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\ns.\n`hasNotText`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n(optional)\nAdded in: v1.33\n# (https://playwright.dev/docs/api/class-locator#locator-filter-option-has-not-text)\nMatches elements that do not contain specified text somewhere inside, possibly in a child or a descendant element. When passed a\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n, matching is case-insensitive and searches for a substring.\n`hasText`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-filter-option-has-text)\nMatches elements containing specified text somewhere inside, possibly in a child or a descendant element. When passed a\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n, matching is case-insensitive and searches for a substring. For example,\n`"Playwright"`\nmatches\n`&lt;article&gt;&lt;div&gt;Playwright&lt;/div&gt;&lt;/article&gt;`\n.\n`visible`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.51\n# (https://playwright.dev/docs/api/class-locator#locator-filter-option-visible)\nOnly matches visible or invisible elements.\n\nReturns\n\nLocator (https://playwright.dev/docs/api/class-locator)\n# (https://playwright.dev/docs/api/class-locator#locator-filter-return)', "```\n`awaitpage.getByRole('button').click();`\n```\n\nOn the other hand, Playwright understands when you perform a multiple-element operation, so the following call works perfectly fine when the locator resolves to multiple elements.", "```\n`awaitpage.getByRole('button').count();`\n```\n\nYou can explicitly opt-out from strictness check by telling Playwright which element to use when multiple elements match, through\nlocator.first() (https://playwright.dev/docs/api/class-locator#locator-first)\n,\nlocator.last() (https://playwright.dev/docs/api/class-locator#locator-last)\n, and\nlocator.nth() (https://playwright.dev/docs/api/class-locator#locator-nth)\n. These methods are\nnot recommended\nbecause when your page changes, Playwright may click on an element you did not intend. Instead, follow best practices above to create a locator that uniquely identifies the target element."]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3833,11 +3903,16 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>To click only the visible button, use the `.filter()` method:
-```javascript
-await page.locator('button').filter({hasNot: null, visible: true}).click();
-```
-While the documentation notes that you can opt-out of strictness using `.first()`, `.last()`, or `.nth()`, these are not recommended because they may target the wrong element if the page changes. The documentation also suggests that it is usually better to find a more reliable way to uniquely identify the element rather than checking for visibility.</t>
+          <t>To click only the visible button, you can use one of the following approaches:
+*   **Recommended approach:** Use the `filter` method to narrow the locator to visible elements:
+    ```javascript
+    await page.locator('button').filter({visible: true}).click();
+    ```
+*   **Alternative approach:** Use the `:visible` CSS pseudo-class:
+    ```javascript
+    await page.locator('button:visible').click();
+    ```
+While these methods resolve the strictness violation, it is generally better to find a more reliable way to uniquely identify the element rather than relying on visibility.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3846,31 +3921,31 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.0087235</v>
+        <v>0.00077625</v>
       </c>
       <c r="G52" t="n">
-        <v>33509</v>
+        <v>52572</v>
       </c>
       <c r="H52" t="n">
         <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>0.22</v>
+        <v>0.91</v>
       </c>
       <c r="J52" t="n">
         <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1948051948051948</v>
+        <v>0.2948717948717949</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3488372093023256</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="M52" t="n">
-        <v>0.9999999999</v>
+        <v>0.9999999999666667</v>
       </c>
       <c r="N52" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3884,7 +3959,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>["Auto-waiting | Playwright","Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 \u203a basic test ===========================Error: expect(received).toHaveText(expected)Expected string: \"my text\"Received string: \"\"Call log:- expect.toHaveText with timeout 5000ms- waiting for \"locator('button')\"`\n```","See a full log of your test to better understand what Playwright is doing behind the scenes such as scrolling into view, waiting for element to be visible, enabled and stable and performing actions such as click, fill, press etc.","LocatorAssertions | Playwright\n\nThe\nLocatorAssertions (https://playwright.dev/docs/api/class-locatorassertions)\nclass provides assertion methods that can be used to make assertions about the\nLocator (https://playwright.dev/docs/api/class-locator)\nstate in the tests.\n\n```\n`import{test,expect}from'@playwright/test';test('status becomes submitted',async({page})=&gt;{// ...awaitpage.getByRole('button').click();awaitexpect(page.locator('.status')).toHaveText('Submitted');});`\n```","Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`","In the Actions tab you can see what locator was used for every action and how long each one took to run. Hover over each action of your test and visually see the change in the DOM snapshot. Go back and forward in time and click an action to inspect and debug. Use the Before and After tabs to visually see what happened before and after the action.\n\nSelecting each action reveals:\n\nAction snapshots\nAction log\nSource code location","Trace viewer | Playwright"]</t>
+          <t>["Dialog | Playwright\n\nDialog (https://playwright.dev/docs/api/class-dialog)\nobjects are dispatched by page via the\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nevent.\n\nAn example of using\n`Dialog`\nclass:\n\n```\n`const{chromium}=require('playwright');// Or 'firefox' or 'webkit'.(async()=&gt;{constbrowser=awaitchromium.launch();constpage=awaitbrowser.newPage();page.on('dialog',asyncdialog=&gt;{console.log(dialog.message());awaitdialog.dismiss();});awaitpage.evaluate(()=&gt;alert('1'));awaitbrowser.close();})();`\n```\n\nnote\nDialogs are dismissed automatically, unless there is a\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nlistener. When listener is present, it\nmust\neither\ndialog.accept() (https://playwright.dev/docs/api/class-dialog#dialog-accept)\nor\ndialog.dismiss() (https://playwright.dev/docs/api/class-dialog#dialog-dismiss)\nthe dialog - otherwise the page will\nfreeze (https://developer.mozilla.org/en-US/docs/Web/JavaScript/EventLoop#never_blocking)\nwaiting for the dialog, and actions like click will never finish.", "By default, dialogs are auto-dismissed by Playwright, so you don't have to handle them. However, you can register a dialog handler before the action that triggers the dialog to either\ndialog.accept() (https://playwright.dev/docs/api/class-dialog#dialog-accept)\nor\ndialog.dismiss() (https://playwright.dev/docs/api/class-dialog#dialog-dismiss)\nit.\n\n```\n`page.on('dialog',dialog=&gt;dialog.accept());awaitpage.getByRole('button').click();`\n```\n\nnote\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\nlistener\nmust handle\nthe dialog. Otherwise your action will stall, be it\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nor something else. That's because dialogs in Web are modals and therefore block further page execution until they are handled.\n\nAs a result, the following snippet will never resolve:\n\nwarning\nWRONG!\n\n```\n`page.on('dialog',dialog=&gt;console.log(dialog.message()));awaitpage.getByRole('button').click();// Will hang here`\n```\n\nnote\nIf there is no listener for\npage.on('dialog') (https://playwright.dev/docs/api/class-page#page-event-dialog)\n, all dialogs are automatically dismissed.", "Added before v1.9\n\ndialog.accept\n\nReturns when the dialog has been accepted.\n\nUsage\n\n```\n`awaitdialog.accept();awaitdialog.accept(promptText);`\n```\n\nArguments\n\n`promptText`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-dialog#dialog-accept-option-prompt-text)\nA text to enter in prompt. Does not cause any effects if the dialog's\n`type`\nis not prompt. Optional.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-dialog#dialog-accept-return)", 'Added before v1.9\n\ndialog.dismiss\n\nReturns when the dialog has been dismissed.\n\nUsage\n\n```\n`awaitdialog.dismiss();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-dialog#dialog-dismiss-return)', 'If a certain event needs to be handled once, there is a convenience API for that:\n\n```\n`page.once(\'dialog\',dialog=&gt;dialog.accept(\'2021\'));awaitpage.evaluate("prompt(\'Enter a number:\')");`\n```', "Sometimes, events happen in random time and instead of waiting for them, they need to be handled. Playwright supports traditional language mechanisms for subscribing and unsubscribing from the events:\n\n```\n`page.on('request',request=&gt;console.log(`Request sent:${request.url()}`));constlistener=request=&gt;console.log(`Request finished:${request.url()}`);page.on('requestfinished',listener);awaitpage.goto('https://wikipedia.org');page.off('requestfinished',listener);awaitpage.goto('https://www.openstreetmap.org/');`\n```", "Most of the time, scripts will need to wait for a particular event to happen. Below are some of the typical event awaiting patterns.\n\nWait for a request with the specified url using\npage.waitForRequest() (https://playwright.dev/docs/api/class-page#page-wait-for-request)\n:\n\n```\n`// Start waiting for request before goto. Note no await.constrequestPromise=page.waitForRequest('**/*logo*.png');awaitpage.goto('https://wikipedia.org');constrequest=awaitrequestPromise;console.log(request.url());`\n```\n\nWait for popup window:\n\n```\n`// Start waiting for popup before clicking. Note no await.constpopupPromise=page.waitForEvent('popup');awaitpage.getByText('open the popup').click();constpopup=awaitpopupPromise;awaitpopup.goto('https://wikipedia.org');`\n```"]</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3894,7 +3969,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>The timeout that ran out is the **Expect timeout**, which has a default value of 5,000 ms. This is separate from the overall test timeout.\n\nBumping the timeout is not necessarily the right response; you may be papering over an issue. Because the assertion is auto-retrying, it is waiting for the locator to satisfy the condition within that 5-second window. If it receives an empty string, it means the element was found but did not contain the expected text within that timeframe.\n\nTo investigate why this is happening, you should use the **Trace Viewer**:\n\n*   **Check the Log:** Use the Trace Viewer to see the full log of the test. This will show you what Playwright was doing behind the scenes, such as scrolling, waiting for the element to be visible, enabled, or stable [3].\n*   **Inspect Actions:** Use the **Actions** tab to hover over actions and see the DOM snapshot change. You can use the **Before** and **After** tabs to visually inspect the state of the button at the time of the failure [6].\n\nIf you determine that the element simply requires more time to reach the desired state, you can increase the timeout for that specific assertion using:\n\n```javascript\nawait expect(page.locator('button')).toHaveText('my text', { timeout: 10000 });\n```\n\nAlternatively, you can set a global expect timeout in your configuration [5].</t>
+          <t>Your test is hanging because you have registered a `page.on('dialog')` listener that only logs the message but does not handle the dialog. When a listener is present, you must explicitly call either `dialog.accept()` or `dialog.dismiss()`. Because you are not doing this, the page freezes waiting for the dialog to be handled, causing the `click()` action to never resolve.
+To fix this, update your listener to accept or dismiss the dialog:
+```javascript
+page.on('dialog', dialog =&gt; {
+  console.log(dialog.message());
+  dialog.accept(); // or dialog.dismiss();
+});
+await page.getByRole('button', { name: 'Delete card' }).click();
+```
+Alternatively, if you only need to handle this specific dialog once, you can use `page.once`:
+```javascript
+page.once('dialog', dialog =&gt; dialog.accept());
+await page.getByRole('button', { name: 'Delete card' }).click();
+```</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3903,31 +3991,31 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.00945725</v>
+        <v>0.000864</v>
       </c>
       <c r="G53" t="n">
-        <v>35384</v>
+        <v>35515</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>0.02991452991452992</v>
+        <v>0.1811023622047244</v>
       </c>
       <c r="L53" t="n">
-        <v>0.1794871794871795</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="M53" t="n">
-        <v>0.9999999999</v>
+        <v>0.99999999998</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3946,7 +4034,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Auto-waiting | Playwright,</t>
+          <t>['Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Error: expect(received).toHaveText(expected)Expected string: "my text"Received string: ""Call log:- expect.toHaveText with timeout 5000ms- waiting for "locator(\'button\')"`\n```', 'Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', 'Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and\n`beforeEach`\nhooks is included in the test timeout.\n\nTimed out test produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Timeout of 30000ms exceeded.`\n```\n\nAdditional separate timeout, of the same value, is shared between fixture teardowns and\n`afterEach`\nhooks, after the test function has finished.\n\nThe same timeout value also applies to\n`beforeAll`\nand\n`afterAll`\nhooks, but they do not share time with any test.', 'The following assertions will retry until the assertion passes, or the assertion timeout is reached. Note that retrying assertions are async, so you must\n`await`\nthem.\n\nAssertion\nDescription\nawait expect(locator).toBeAttached() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-attached)\nElement is attached\nawait expect(locator).toBeChecked() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-checked)\nCheckbox is checked\nawait expect(locator).toBeDisabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-disabled)\nElement is disabled\nawait expect(locator).toBeEditable() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-editable)\nElement is editable\nawait expect(locator).toBeEmpty() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-empty)\nContainer is empty\nawait expect(locator).toBeEnabled() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-enabled)\nElement is enabled\nawait expect(locator).toBeFocused() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-focused)\nElement is focused\nawait expect(locator).toBeHidden() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-hidden)\nElement is not visible\nawait expect(locator).toBeInViewport() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-in-viewport)\nElement intersects viewport\nawait expect(locator).toBeVisible() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-be-visible)\nElement is visible\nawait expect(locator).toContainText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-text)\nElement contains text\nawait expect(locator).toContainClass() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-contain-class)\nElement has specified CSS classes\nawait expect(locator).toHaveAccessibleDescription() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-accessible-description)\nElement has a matching\naccessible description (https://w3c.github.io/accname/#dfn-accessible-description)\nawait expect(locator).toHaveAccessibleName() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-accessible-name)\nElement has a matching\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\nawait expect(locator).toHaveAttribute() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-attribute)\nElement has a DOM attribute\nawait expect(locator).toHaveClass() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-class)\nElement has specified CSS class property\nawait expect(locator).toHaveCount() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-count)\nList has exact number of children\nawait expect(locator).toHaveCSS() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-css)\nElement has CSS property\nawait expect(locator).toHaveId() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-id)\nElement has an ID\nawait expect(locator).toHaveJSProperty() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-js-property)\nElement has a JavaScript property\nawait expect(locator).toHaveRole() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-role)\nElement has a specific\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\nawait expect(locator).toHaveScreenshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-screenshot-1)\nElement has a screenshot\nawait expect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nElement matches text\nawait expect(locator).toHaveValue() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-value)\nInput has a value\nawait expect(locator).toHaveValues() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-values)\nSelect has options selected\nawait expect(locator).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-match-aria-snapshot)\nElement matches the Aria snapshot\nawait expect(page).toMatchAriaSnapshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-match-aria-snapshot)\nPage matches the Aria snapshot\nawait expect(page).toHaveScreenshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\nPage has a screenshot\nawait expect(page).toHaveTitle() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-title)\nPage has a title\nawait expect(page).toHaveURL() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-url)\nPage has a URL\nawait expect(response).toBeOK() (https://playwright.dev/docs/api/class-apiresponseassertions#api-response-assertions-to-be-ok)\nResponse has an OK status', "Playwright Test supports a timeout for the whole test run. This prevents excess resource usage when everything went wrong. There is no default global timeout, but you can set a reasonable one in the config, for example one hour. Global timeout produces the following error:\n\n```\n`Running 1000 tests using 10 workers514 skipped486 passedTimed out waiting 3600s for the entire test run`\n```\n\nYou can set global timeout in the config.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({globalTimeout:3_600_000,});`\n```\n\nAPI reference:\ntestConfig.globalTimeout (https://playwright.dev/docs/api/class-testconfig#test-config-global-timeout)\n.", 'Playwright performs a range of actionability checks on the elements before making actions to ensure these actions behave as expected. It auto-waits for all the relevant checks to pass and only then performs the requested action. If the required checks do not pass within the given\n`timeout`\n, action fails with the\n`TimeoutError`\n.\n\nFor example, for\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\n, Playwright will ensure that:\n\nlocator resolves to exactly one element\nelement is\nVisible (https://playwright.dev/docs/actionability#visible)\nelement is\nStable (https://playwright.dev/docs/actionability#stable)\n, as in not animating or completed animation\nelement\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\n, as in not obscured by other elements\nelement is\nEnabled (https://playwright.dev/docs/actionability#enabled)\n\nHere is the complete list of actionability checks performed for each action:\n\nAction\nVisible (https://playwright.dev/docs/actionability#visible)\nStable (https://playwright.dev/docs/actionability#stable)\nReceives Events (https://playwright.dev/docs/actionability#receives-events)\nEnabled (https://playwright.dev/docs/actionability#enabled)\nEditable (https://playwright.dev/docs/actionability#editable)\nlocator.check() (https://playwright.dev/docs/api/class-locator#locator-check)\nYes\nYes\nYes\nYes\n-\nlocator.click() (https://playwright.dev/docs/api/class-locator#locator-click)\nYes\nYes\nYes\nYes\n-\nlocator.dblclick() (https://playwright.dev/docs/api/class-locator#locator-dblclick)\nYes\nYes\nYes\nYes\n-\nlocator.setChecked() (https://playwright.dev/docs/api/class-locator#locator-set-checked)\nYes\nYes\nYes\nYes\n-\nlocator.tap() (https://playwright.dev/docs/api/class-locator#locator-tap)\nYes\nYes\nYes\nYes\n-\nlocator.uncheck() (https://playwright.dev/docs/api/class-locator#locator-uncheck)\nYes\nYes\nYes\nYes\n-\nlocator.hover() (https://playwright.dev/docs/api/class-locator#locator-hover)\nYes\nYes\nYes\n-\n-\nlocator.dragTo() (https://playwright.dev/docs/api/class-locator#locator-drag-to)\nYes\nYes\nYes\n-\n-\nlocator.screenshot() (https://playwright.dev/docs/api/class-locator#locator-screenshot)\nYes\nYes\n-\n-\n-\nlocator.fill() (https://playwright.dev/docs/api/class-locator#locator-fill)\nYes\n-\n-\nYes\nYes\nlocator.clear() (https://playwright.dev/docs/api/class-locator#locator-clear)\nYes\n-\n-\nYes\nYes\nlocator.selectOption() (https://playwright.dev/docs/api/class-locator#locator-select-option)\nYes\n-\n-\nYes\n-\nlocator.selectText() (https://playwright.dev/docs/api/class-locator#locator-select-text)\nYes\n-\n-\n-\n-\nlocator.scrollIntoViewIfNeeded() (https://playwright.dev/docs/api/class-locator#locator-scroll-into-view-if-needed)\n-\nYes\n-\n-\n-\nlocator.blur() (https://playwright.dev/docs/api/class-locator#locator-blur)\n-\n-\n-\n-\n-\nlocator.dispatchEvent() (https://playwright.dev/docs/api/class-locator#locator-dispatch-event)\n-\n-\n-\n-\n-\nlocator.focus() (https://playwright.dev/docs/api/class-locator#locator-focus)\n-\n-\n-\n-\n-\nlocator.press() (https://playwright.dev/docs/api/class-locator#locator-press)\n-\n-\n-\n-\n-\nlocator.pressSequentially() (https://playwright.dev/docs/api/class-locator#locator-press-sequentially)\n-\n-\n-\n-\n-\nlocator.setInputFiles() (https://playwright.dev/docs/api/class-locator#locator-set-input-files)\n-\n-\n-\n-\n-', 'Playwright supports\ntest retries\n. When enabled, failing tests will be retried multiple times until they pass, or until the maximum number of retries is reached. By default failing tests are not retried.\n\n```\n`# Give failing tests 3 retry attemptsnpx playwrighttest--retries=3`\n```\n\nYou can configure retries in the configuration file:\n\nplaywright.config.ts\n```\n`import{defineConfig}from\'@playwright/test\';exportdefaultdefineConfig({// Give failing tests 3 retry attemptsretries:3,});`\n```\n\nPlaywright Test will categorize tests as follows:\n\n"passed" - tests that passed on the first run;\n"flaky" - tests that failed on the first run, but passed when retried;\n"failed" - tests that failed on the first run and failed all retries.\n\n```\n`Running3tests using1worker✓ example.spec.ts:4:2 › first passes(438ms)x example.spec.ts:5:2 › second flaky(691ms)✓ example.spec.ts:5:2 › second flaky(522ms)✓ example.spec.ts:6:2 › third passes(932ms)1flakyexample.spec.ts:5:2 › second flaky2passed(4s)`\n```\n\nYou can detect retries at runtime with\ntestInfo.retry (https://playwright.dev/docs/api/class-testinfo#test-info-retry)\n, which is accessible to any test, hook or fixture. Here is an example that clears some server-side state before a retry.\n\n```\n`import{test,expect}from\'@playwright/test\';test(\'my test\',async({page},testInfo)=&gt;{if(testInfo.retry)awaitcleanSomeCachesOnTheServer();// ...});`\n```\n\nYou can specify retries for a specific group of tests or a single file with\ntest.describe.configure() (https://playwright.dev/docs/api/class-test#test-describe-configure)\n.\n\n```\n`import{test,expect}from\'@playwright/test\';test.describe(()=&gt;{// All tests in this describe group will get 2 retry attempts.test.describe.configure({retries:2});test(\'test 1\',async({page})=&gt;{// ...});test(\'test 2\',async({page})=&gt;{// ...});});`\n```']</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3956,16 +4044,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>The timeout that ran out is the **Expect timeout**, which has a default value of 5,000 ms. This is separate from the overall test timeout.
-Bumping the timeout is not necessarily the right response; you may be papering over an issue. Because the assertion is auto-retrying, it is waiting for the locator to satisfy the condition within that 5-second window. If it receives an empty string, it means the element was found but did not contain the expected text within that timeframe.
-To investigate why this is happening, you should use the **Trace Viewer**:
-*   **Check the Log:** Use the Trace Viewer to see the full log of the test. This will show you what Playwright was doing behind the scenes, such as scrolling, waiting for the element to be visible, enabled, or stable [3].
-*   **Inspect Actions:** Use the **Actions** tab to hover over actions and see the DOM snapshot change. You can use the **Before** and **After** tabs to visually inspect the state of the button at the time of the failure [6].
-If you determine that the element simply requires more time to reach the desired state, you can increase the timeout for that specific assertion using:
+          <t>The assertion `expect(page.locator('button')).toHaveText('my text')` failed because it reached its **expect timeout**, which is 5 seconds by default.
+### What ran out?
+The assertion timeout ran out. Auto-retrying assertions like `toHaveText()` have a dedicated timeout separate from the overall test timeout. Even though your test finishes in eight seconds when it passes, the assertion itself only waits for 5 seconds for the condition to be met. If the button's text is not present within that 5-second window, the assertion fails.
+### Is bumping the timeout the right response?
+The documentation does not explicitly state whether increasing the timeout is "papering over" an issue, but it provides the mechanism to adjust it if necessary. You can increase the timeout for a specific assertion or globally:
+*   **Override in a specific test:**
+    ```javascript
+    await expect(page.locator('button')).toHaveText('my text', { timeout: 10000 });
+    ```
+*   **Set in the config file:**
+    ```javascript
+    // playwright.config.ts
+    export default defineConfig({
+      expect: {
+        timeout: 10_000,
+      },
+    });
+    ```
+Because your test is flaky (failing one in four runs), you may also consider using **test retries** to handle intermittent failures. You can enable this in your configuration file:
 ```javascript
-await expect(page.locator('button')).toHaveText('my text', { timeout: 10000 });
-```
-Alternatively, you can set a global expect timeout in your configuration [5].</t>
+// playwright.config.ts
+export default defineConfig({
+  retries: 3,
+});
+```
+When retries are enabled, Playwright will retry failing tests until they pass or the maximum number of retries is reached.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3974,28 +4078,28 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.01015725</v>
+        <v>0.00164</v>
       </c>
       <c r="G54" t="n">
-        <v>36549</v>
+        <v>41995</v>
       </c>
       <c r="H54" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.48</v>
+        <v>0.63</v>
       </c>
       <c r="J54" t="n">
         <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>0.09375</v>
+        <v>0.1004566210045662</v>
       </c>
       <c r="L54" t="n">
-        <v>0.375</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="M54" t="n">
-        <v>0.8666666666377778</v>
+        <v>0.9166666666361111</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
@@ -4014,7 +4118,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Auto-retrying assertions like\nexpect(locator).toHaveText() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-text)\nhave a separate timeout, 5 seconds by default. Assertion timeout is unrelated to the test timeout. It produces the following error:\n\n```\n`example.spec.ts:3:1 \u203a basic test ===========================Error: expect(received).toHaveText(expected)Expected string: \my text\"Received string: \"\"Call log:- expect.toHaveText with timeout 5000ms- waiting for \"locator('button')\"`\n```",</t>
+          <t>['Evaluated scripts run in the browser environment, while your test runs in a testing environments. This means you cannot use variables from your test in the page and vice versa. Instead, you should pass them explicitly as an argument.\n\nThe following snippet is\nWRONG\nbecause it uses the variable directly:\n\n```\n`constdata=\'some data\';constresult=awaitpage.evaluate(()=&gt;{// WRONG: there is no "data" in the web page.window.myApp.use(data);});`\n```\n\nThe following snippet is\nCORRECT\nbecause it passes the value explicitly as an argument:\n\n```\n`constdata=\'some data\';// Pass |data| as a parameter.constresult=awaitpage.evaluate(data=&gt;{window.myApp.use(data);},data);`\n```', "Playwright evaluation methods like\npage.evaluate() (https://playwright.dev/docs/api/class-page#page-evaluate)\ntake a single optional argument. This argument can be a mix of\nSerializable (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/JSON/stringify#Description)\nvalues and\nJSHandle (https://playwright.dev/docs/api/class-jshandle)\ninstances. Handles are automatically converted to the value they represent.\n\n```\n`// A primitive value.awaitpage.evaluate(num=&gt;num,42);// An array.awaitpage.evaluate(array=&gt;array.length,[1,2,3]);// An object.awaitpage.evaluate(object=&gt;object.foo,{foo:'bar'});// A single handle.constbutton=awaitpage.evaluateHandle('window.button');awaitpage.evaluate(button=&gt;button.textContent,button);// Alternative notation using JSHandle.evaluate.awaitbutton.evaluate((button,from)=&gt;button.textContent.substring(from),5);// Object with multiple handles.constbutton1=awaitpage.evaluateHandle('window.button1');constbutton2=awaitpage.evaluateHandle('window.button2');awaitpage.evaluate(o=&gt;o.button1.textContent+o.button2.textContent,{button1,button2});// Object destructuring works. Note that property names must match// between the destructured object and the argument.// Also note the required parenthesis.awaitpage.evaluate(({button1,button2})=&gt;button1.textContent+button2.textContent,{button1,button2});// Array works as well. Arbitrary names can be used for destructuring.// Note the required parenthesis.awaitpage.evaluate(([b1,b2])=&gt;b1.textContent+b2.textContent,[button1,button2]);// Any mix of serializables and handles works.awaitpage.evaluate(x=&gt;x.button1.textContent+x.list[0].textContent+String(x.foo),{button1,list:[button2],foo:null});`\n```", "Playwright scripts run in your Playwright environment. Your page scripts run in the browser page environment. Those environments don't intersect, they are running in different virtual machines in different processes and even potentially on different computers.\n\nThe\npage.evaluate() (https://playwright.dev/docs/api/class-page#page-evaluate)\nAPI can run a JavaScript function in the context of the web page and bring results back to the Playwright environment. Browser globals like\n`window`\nand\n`document`\ncan be used in\n`evaluate`\n.\n\n```\n`consthref=awaitpage.evaluate(()=&gt;document.location.href);`\n```\n\nIf the result is a Promise or if the function is asynchronous evaluate will automatically wait until it's resolved:\n\n```\n`conststatus=awaitpage.evaluate(async()=&gt;{constresponse=awaitfetch(location.href);returnresponse.status;});`\n```"]</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4024,8 +4128,8 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>The error occurs because the script inside `page.evaluate` runs in the browser environment, while your variable `data` exists only in your test environment. These two environments cannot share variables directly.
-To fix this, you must pass the variable explicitly as an argument to `page.evaluate`.
+          <t>The error occurs because your test code and your page scripts run in different environments (different virtual machines, processes, or even different computers). Variables defined in your test environment are not accessible inside the browser environment where `page.evaluate()` executes.
+To fix this, you must pass the variable explicitly as an argument to `page.evaluate()`.
 **Correct approach:**
 ```javascript
 const data = 'some data';
@@ -4033,7 +4137,7 @@
   window.myApp.use(data);
 }, data);
 ```
-By passing `data` as the second argument to `page.evaluate`, it becomes available as the parameter within the callback function.</t>
+By passing `data` as the second argument to `page.evaluate`, it becomes available as a parameter to the function running inside the browser.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4042,10 +4146,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.00736275</v>
+        <v>0.00058925</v>
       </c>
       <c r="G55" t="n">
-        <v>28451</v>
+        <v>30473</v>
       </c>
       <c r="H55" t="n">
         <v>1</v>
@@ -4057,10 +4161,10 @@
         <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2738095238095238</v>
+        <v>0.1979166666666667</v>
       </c>
       <c r="L55" t="n">
-        <v>0.696969696969697</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="M55" t="n">
         <v>0.9999999999666667</v>
@@ -4080,7 +4184,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>See a full log of your test to better understand what Playwright is doing behind the scenes such as scrolling into view, waiting for element to be visible, enabled and stable and performing actions such as click, fill, press etc.,</t>
+          <t>['Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`', "example.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('slow test',async({page})=&gt;{test.slow();// Easy way to triple the default timeout// ...});test('very slow test',async({page})=&gt;{test.setTimeout(120_000);// ...});`\n```\n\nAPI reference:\ntest.setTimeout() (https://playwright.dev/docs/api/class-test#test-set-timeout)\nand\ntest.slow() (https://playwright.dev/docs/api/class-test#test-slow)\n.", "TestInfo | Playwright\n\n`TestInfo`\ncontains information about currently running test. It is available to test functions,\ntest.beforeEach() (https://playwright.dev/docs/api/class-test#test-before-each)\n,\ntest.afterEach() (https://playwright.dev/docs/api/class-test#test-after-each)\n,\ntest.beforeAll() (https://playwright.dev/docs/api/class-test#test-before-all)\nand\ntest.afterAll() (https://playwright.dev/docs/api/class-test#test-after-all)\nhooks, and test-scoped fixtures.\n`TestInfo`\nprovides utilities to control test execution: attach files, update test timeout, determine which test is currently running and whether it was retried, etc.\n\n```\n`import{test,expect}from'@playwright/test';test('basic test',async({page},testInfo)=&gt;{expect(testInfo.title).toBe('basic test');awaitpage.screenshot(testInfo.outputPath('screenshot.png'));});`\n```", "Added in: v1.10\n\ntestInfo.setTimeout\n\nChanges the timeout for the currently running test. Zero means no timeout. Learn more about\nvarious timeouts (https://playwright.dev/docs/test-timeouts)\n.\n\nTimeout is usually specified in the\nconfiguration file (https://playwright.dev/docs/test-configuration)\n, but it could be useful to change the timeout in certain scenarios:\n\n```\n`import{test,expect}from'@playwright/test';test.beforeEach(async({page},testInfo)=&gt;{// Extend timeout for all tests running this hook by 30 seconds.testInfo.setTimeout(testInfo.timeout+30000);});`\n```\n\nUsage\n\n```\n`testInfo.setTimeout(timeout);`\n```\n\nArguments\n\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n# (https://playwright.dev/docs/api/class-testinfo#test-info-set-timeout-option-timeout)\nTimeout in milliseconds.", 'Playwright Test enforces a timeout for each test, 30 seconds by default. Time spent by the test function, fixture setups, and\n`beforeEach`\nhooks is included in the test timeout.\n\nTimed out test produces the following error:\n\n```\n`example.spec.ts:3:1 › basic test ===========================Timeout of 30000ms exceeded.`\n```\n\nAdditional separate timeout, of the same value, is shared between fixture teardowns and\n`afterEach`\nhooks, after the test function has finished.\n\nThe same timeout value also applies to\n`beforeAll`\nand\n`afterAll`\nhooks, but they do not share time with any test.', "By default,\nfixture (https://playwright.dev/docs/test-fixtures)\nshares timeout with the test. However, for slow fixtures, especially\nworker-scoped (https://playwright.dev/docs/test-fixtures#worker-scoped-fixtures)\nones, it is convenient to have a separate timeout. This way you can keep the overall test timeout small, and give the slow fixture more time.\n\nexample.spec.ts\n```\n`import{testasbase,expect}from'@playwright/test';consttest=base.extend&lt;{slowFixture:string}&gt;({slowFixture:[async({},use)=&gt;{// ... perform a slow operation ...awaituse('hello');},{timeout:60_000}]});test('example test',async({slowFixture})=&gt;{// ...});`\n```\n\nAPI reference:\ntest.extend() (https://playwright.dev/docs/api/class-test#test-extend)\n.", 'Playwright supports tags and annotations that are displayed in the test report.\n\nYou can add your own tags and annotations at any moment, but Playwright comes with a few built-in ones:\n\ntest.skip() (https://playwright.dev/docs/api/class-test#test-skip)\nmarks the test as irrelevant. Playwright does not run such a test. Use this annotation when the test is not applicable in some configuration.\ntest.fail() (https://playwright.dev/docs/api/class-test#test-fail)\nmarks the test as failing. Playwright will run this test and ensure it does indeed fail. If the test does not fail, Playwright will complain.\ntest.fixme() (https://playwright.dev/docs/api/class-test#test-fixme)\nmarks the test as failing. Playwright will not run this test, as opposed to the\n`fail`\nannotation. Use\n`fixme`\nwhen running the test is slow or crashes.\ntest.slow() (https://playwright.dev/docs/api/class-test#test-slow)\nmarks the test as slow and triples the test timeout.\n\nAnnotations can be added to a single test or a group of tests.\n\nBuilt-in annotations can be conditional, in which case they apply when the condition is truthy, and may depend on test fixtures. There could be multiple annotations on the same test, possibly in different configurations.']</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4090,22 +4194,40 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>To increase the timeout for only the specific test that requires more time, you can use `test.setTimeout()` within that test.
-In your `example.spec.ts` file, add the following line inside the test block:
+          <t>To increase the timeout for only that specific test without affecting the others, you can use one of the following approaches:
+### 1. Use `test.setTimeout()` (Recommended)
+You can override the timeout directly within the test body. This is the most direct way to provide the specific amount of time needed for that test.
 ```typescript
 test('basic test', async ({ page }) =&gt; {
-  test.setTimeout(120000); // Sets the timeout to 120 seconds for this test only
-  // ... rest of your test code
+  test.setTimeout(120000); // Set to 120 seconds
+  // ...
 });
 ```
-Alternatively, if you only need to triple the default timeout, you can use `test.slow()`:
+### 2. Use `test.slow()`
+If you simply need to triple the default timeout (from 30 seconds to 90 seconds), you can use the built-in `test.slow()` annotation.
 ```typescript
 test('basic test', async ({ page }) =&gt; {
-  test.slow();
-  // ... rest of your test code
+  test.slow(); 
+  // ...
 });
 ```
-Both methods allow you to extend the duration for a single test without affecting the 30,000ms default timeout applied to the other 400 tests.</t>
+### 3. Use `testInfo.setTimeout()`
+If you are working within a hook or need to calculate the timeout dynamically, you can use the `testInfo` object, which is available to test functions and hooks.
+```typescript
+test('basic test', async ({ page }, testInfo) =&gt; {
+  testInfo.setTimeout(120000);
+  // ...
+});
+```
+**Note on Fixtures:** If the 30MB fixture is causing the timeout during its setup, you can alternatively define a custom timeout specifically for that fixture using `test.extend()`:
+```typescript
+const test = base.extend&lt;{ slowFixture: string }&gt;({
+  slowFixture: [async ({}, use) =&gt; {
+    // ... perform slow operation ...
+    await use('hello');
+  }, { timeout: 60000 }]
+});
+```</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4114,28 +4236,28 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.007936250000000001</v>
+        <v>0.00110975</v>
       </c>
       <c r="G56" t="n">
-        <v>30235</v>
+        <v>43092</v>
       </c>
       <c r="H56" t="n">
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>0.83</v>
+        <v>0.44</v>
       </c>
       <c r="J56" t="n">
         <v>5</v>
       </c>
       <c r="K56" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1</v>
       </c>
       <c r="L56" t="n">
-        <v>0.4324324324324325</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="M56" t="n">
-        <v>0.99999999995</v>
+        <v>0.9761904761742063</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
@@ -4154,7 +4276,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LocatorAssertions | Playwright\n\nThe\nLocatorAssertions (https://playwright.dev/docs/api/class-locatorassertions)\nclass provides assertion methods that can be used to make assertions about the\nLocator (https://playwright.dev/docs/api/class-locator)\nstate in the tests.\n\n```\n`import{test,expect}from'@playwright/test';test('status becomes submitted',async({page})=&gt;{// ...awaitpage.getByRole('button').click();awaitexpect(page.locator('.status')).toHaveText('Submitted');});`\n```,</t>
+          <t>["Locators support an option to only select elements that have or have not a descendant matching another locator. You can therefore filter by any other locator such as a\nlocator.getByRole() (https://playwright.dev/docs/api/class-locator#locator-get-by-role)\n,\nlocator.getByTestId() (https://playwright.dev/docs/api/class-locator#locator-get-by-test-id)\n,\nlocator.getByText() (https://playwright.dev/docs/api/class-locator#locator-get-by-text)\netc.\n\nhttp://localhost:3000\nProduct 1\nAdd to cart\nProduct 2\nAdd to cart\n```\n`&lt;ul&gt;&lt;li&gt;&lt;h3&gt;Product 1&lt;/h3&gt;&lt;button&gt;Add to cart&lt;/button&gt;&lt;/li&gt;&lt;li&gt;&lt;h3&gt;Product 2&lt;/h3&gt;&lt;button&gt;Add to cart&lt;/button&gt;&lt;/li&gt;&lt;/ul&gt;`\n```\n\n```\n`awaitpage.getByRole('listitem').filter({has:page.getByRole('heading',{name:'Product 2'})}).getByRole('button',{name:'Add to cart'}).click();`\n```\n\nWe can also assert the product card to make sure there is only one:\n\n```\n`awaitexpect(page.getByRole('listitem').filter({has:page.getByRole('heading',{name:'Product 2'})})).toHaveCount(1);`\n```\n\nThe filtering locator\nmust be relative\nto the original locator and is queried starting with the original locator match, not the document root. Therefore, the following will not work, because the filtering locator starts matching from the\n`&lt;ul&gt;`\nlist element that is outside of the\n`&lt;li&gt;`\nlist item matched by the original locator:\n\n```\n`// ✖ WRONGawaitexpect(page.getByRole('listitem').filter({has:page.getByRole('list').getByText('Product 2')})).toHaveCount(1);`\n```", 'Added in: v1.22\n\nlocator.filter\n\nThis method narrows existing locator according to the options, for example filters by text. It can be chained to filter multiple times.\n\nUsage\n\n```\n`constrowLocator=page.locator(\'tr\');// ...awaitrowLocator.filter({hasText:\'text in column 1\'}).filter({has:page.getByRole(\'button\',{name:\'column 2 button\'})}).screenshot();`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`has`\nLocator (https://playwright.dev/docs/api/class-locator)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-filter-option-has)\nNarrows down the results of the method to those which contain elements matching this relative locator. For example,\n`article`\nthat has\n`text=Playwright`\nmatches\n`&lt;article&gt;&lt;div&gt;Playwright&lt;/div&gt;&lt;/article&gt;`\n.\nInner locator\nmust be relative\nto the outer locator and is queried starting with the outer locator match, not the document root. For example, you can find\n`content`\nthat has\n`div`\nin\n`&lt;article&gt;&lt;content&gt;&lt;div&gt;Playwright&lt;/div&gt;&lt;/content&gt;&lt;/article&gt;`\n. However, looking for\n`content`\nthat has\n`article div`\nwill fail, because the inner locator must be relative and should not use any elements outside the\n`content`\n.\nNote that outer and inner locators must belong to the same frame. Inner locator must not contain\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\ns.\n`hasNot`\nLocator (https://playwright.dev/docs/api/class-locator)\n(optional)\nAdded in: v1.33\n# (https://playwright.dev/docs/api/class-locator#locator-filter-option-has-not)\nMatches elements that do not contain an element that matches an inner locator. Inner locator is queried against the outer one. For example,\n`article`\nthat does not have\n`div`\nmatches\n`&lt;article&gt;&lt;span&gt;Playwright&lt;/span&gt;&lt;/article&gt;`\n.\nNote that outer and inner locators must belong to the same frame. Inner locator must not contain\nFrameLocator (https://playwright.dev/docs/api/class-framelocator)\ns.\n`hasNotText`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n(optional)\nAdded in: v1.33\n# (https://playwright.dev/docs/api/class-locator#locator-filter-option-has-not-text)\nMatches elements that do not contain specified text somewhere inside, possibly in a child or a descendant element. When passed a\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n, matching is case-insensitive and searches for a substring.\n`hasText`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n(optional)\n# (https://playwright.dev/docs/api/class-locator#locator-filter-option-has-text)\nMatches elements containing specified text somewhere inside, possibly in a child or a descendant element. When passed a\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n, matching is case-insensitive and searches for a substring. For example,\n`"Playwright"`\nmatches\n`&lt;article&gt;&lt;div&gt;Playwright&lt;/div&gt;&lt;/article&gt;`\n.\n`visible`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.51\n# (https://playwright.dev/docs/api/class-locator#locator-filter-option-visible)\nOnly matches visible or invisible elements.\n\nReturns\n\nLocator (https://playwright.dev/docs/api/class-locator)\n# (https://playwright.dev/docs/api/class-locator#locator-filter-return)', 'When you have elements with various similarities, you can use the\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nmethod to select the right one. You can also chain multiple filters to narrow down the selection.\n\nFor example, consider the following DOM structure:\n\nhttp://localhost:3000\nJohn\nSay hello\nMary\nSay hello\nJohn\nSay goodbye\nMary\nSay goodbye\n```\n`&lt;ul&gt;&lt;li&gt;&lt;div&gt;John&lt;/div&gt;&lt;div&gt;&lt;button&gt;Say hello&lt;/button&gt;&lt;/div&gt;&lt;/li&gt;&lt;li&gt;&lt;div&gt;Mary&lt;/div&gt;&lt;div&gt;&lt;button&gt;Say hello&lt;/button&gt;&lt;/div&gt;&lt;/li&gt;&lt;li&gt;&lt;div&gt;John&lt;/div&gt;&lt;div&gt;&lt;button&gt;Say goodbye&lt;/button&gt;&lt;/div&gt;&lt;/li&gt;&lt;li&gt;&lt;div&gt;Mary&lt;/div&gt;&lt;div&gt;&lt;button&gt;Say goodbye&lt;/button&gt;&lt;/div&gt;&lt;/li&gt;&lt;/ul&gt;`\n```\n\nTo take a screenshot of the row with "Mary" and "Say goodbye":\n\n```\n`constrowLocator=page.getByRole(\'listitem\');awaitrowLocator.filter({hasText:\'Mary\'}).filter({has:page.getByRole(\'button\',{name:\'Say goodbye\'})}).screenshot({path:\'screenshot.png\'});`\n```\n\nYou should now have a "screenshot.png" file in your project\'s root directory.', 'You can chain methods that create a locator, like\npage.getByText() (https://playwright.dev/docs/api/class-page#page-get-by-text)\nor\nlocator.getByRole() (https://playwright.dev/docs/api/class-locator#locator-get-by-role)\n, to narrow down the search to a particular part of the page.\n\nIn this example we first create a locator called product by locating its role of\n`listitem`\n. We then filter by text. We can use the product locator again to get by role of button and click it and then use an assertion to make sure there is only one product with the text "Product 2".\n\n```\n`constproduct=page.getByRole(\'listitem\').filter({hasText:\'Product 2\'});awaitproduct.getByRole(\'button\',{name:\'Add to cart\'}).click();awaitexpect(product).toHaveCount(1);`\n```\n\nYou can also chain two locators together, for example to find a "Save" button inside a particular dialog:\n\n```\n`constsaveButton=page.getByRole(\'button\',{name:\'Save\'});// ...constdialog=page.getByTestId(\'settings-dialog\');awaitdialog.locator(saveButton).click();`\n```']</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4164,8 +4286,8 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>The code does not work because the filtering locator must be relative to the original locator and is queried starting from the original locator match, not the document root. 
-In your code, `page.getByRole('list').getByText('Product 2')` starts matching from the `&lt;ul&gt;` list element, which is outside of the `&lt;li&gt;` list item matched by `page.getByRole('listitem')`. As noted in the documentation, this specific approach is incorrect.</t>
+          <t>Your code does not work because the filtering locator must be relative to the original locator and is queried starting from the `listitem` match, not the document root.
+By including `page.getByRole('list')` inside your `has` filter, you are attempting to match a list element that is outside of the `listitem` you are currently filtering. The filtering locator must not use elements outside of the scope of the original locator.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4174,28 +4296,28 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.008291750000000001</v>
+        <v>0.00079875</v>
       </c>
       <c r="G57" t="n">
-        <v>32047</v>
+        <v>54823</v>
       </c>
       <c r="H57" t="n">
         <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="J57" t="n">
         <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3</v>
       </c>
       <c r="L57" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="M57" t="n">
-        <v>0.49999999995</v>
+        <v>0.99999999995</v>
       </c>
       <c r="N57" t="n">
         <v>1</v>
@@ -4212,7 +4334,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Timeouts | Playwright\n\nPlaywright Test has multiple configurable timeouts for various tasks.\n\nTimeout\nDefault\nDescription\nTest timeout\n30_000 ms\nTimeout for each test\nSet in config\n`{ timeout: 60_000 }`\nOverride in test\n`test.setTimeout(120_000)`\nExpect timeout\n5_000 ms\nTimeout for each assertion\nSet in config\n`{ expect: { timeout: 10_000 } }`\nOverride in test\n`expect(locator).toBeVisible({ timeout: 10_000 })`,</t>
+          <t>["When you run above for the first time, test runner will say:\n\n```\n`Error: A snapshot doesn't exist at example.spec.ts-snapshots/example-test-1-chromium-darwin.png, writing actual.`\n```\n\nThat's because there was no golden file yet. This method took a bunch of screenshots until two consecutive screenshots matched, and saved the last screenshot to file system. It is now ready to be added to the repository.\n\nThe name of the folder with the golden expectations starts with the name of your test file:\n\n```\n`drwxr-xr-x5user  group160Jun411:46.drwxr-xr-x6user  group192Jun411:45..-rw-r--r--1user  group231Jun411:16 example.spec.tsdrwxr-xr-x3user  group96Jun411:46 example.spec.ts-snapshots`\n```\n\nThe snapshot name\n`example-test-1-chromium-darwin.png`\nconsists of a few parts:\n\n`example-test-1.png`\n- an auto-generated name of the snapshot. Alternatively you can specify snapshot name as the first argument of the\n`toHaveScreenshot()`\nmethod:\n```\n`awaitexpect(page).toHaveScreenshot('landing.png');`\n```\n`chromium-darwin`\n- the browser name and the platform. Screenshots differ between browsers and platforms due to different rendering, fonts and more, so you will need different snapshots for them. If you use multiple projects in your\nconfiguration file (https://playwright.dev/docs/test-configuration)\n, project name will be used instead of\n`chromium`\n.\n\nThe snapshot name and path can be configured with\ntestConfig.snapshotPathTemplate (https://playwright.dev/docs/api/class-testconfig#test-config-snapshot-path-template)\nin the playwright config.\n\nNote that\n`toHaveScreenshot()`\nalso accepts an array of path segments to the snapshot file such as\n`expect().toHaveScreenshot(['relative', 'path', 'to', 'snapshot.png'])`\n.\nHowever, this path must stay within the snapshots directory for each test file (i.e.\n`a.spec.js-snapshots`\n), otherwise it will throw.", "Playwright Test includes the ability to produce and visually compare screenshots using\n`await expect(page).toHaveScreenshot()`\n. On first execution, Playwright test will generate reference screenshots. Subsequent runs will compare against the reference.\n\nexample.spec.ts\n```\n`import{test,expect}from'@playwright/test';test('example test',async({page})=&gt;{awaitpage.goto('https://playwright.dev');awaitexpect(page).toHaveScreenshot();});`\n```\n\nwarning\nBrowser rendering can vary based on the host OS, version, settings, hardware, power source (battery vs. power adapter), headless mode, and other factors. For consistent screenshots, run tests in the same environment where the baseline screenshots were generated.", 'Sometimes you need to update the reference screenshot, for example when the page has changed. Do this with the\n`--update-snapshots`\nflag.\n\n```\n`npx playwrighttest--update-snapshots`\n```', "Configuration for the expect assertion library.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({expect:{// Maximum time expect() should wait for the condition to be met.timeout:5000,toHaveScreenshot:{// An acceptable amount of pixels that could be different, unset by default.maxDiffPixels:10,},toMatchSnapshot:{// An acceptable ratio of pixels that are different to the// total amount of pixels, between 0 and 1.maxDiffPixelRatio:0.1,},},});`\n```\n\nOption\nDescription\ntestConfig.expect (https://playwright.dev/docs/api/class-testconfig#test-config-expect)\nWeb first assertions (https://playwright.dev/docs/test-assertions)\nlike\n`expect(locator).toHaveText()`\nhave a separate timeout of 5 seconds by default. This is the maximum time the\n`expect()`\nshould wait for the condition to be met. Learn more about\ntest and expect timeouts (https://playwright.dev/docs/test-timeouts)\nand how to set them for a single test.\nexpect(page).toHaveScreenshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\nConfiguration for the\n`expect(locator).toHaveScreenshot()`\nmethod.\nexpect(value).toMatchSnapshot() (https://playwright.dev/docs/api/class-snapshotassertions#snapshot-assertions-to-match-snapshot-1)\nConfiguration for the\n`expect(locator).toMatchSnapshot()`\nmethod.", 'Components Testing (preview)\nPlaywright Test can now test your\nReact (https://reactjs.org/)\nor\nVue.js (https://vuejs.org/)\ncomponents. You can use all the features of Playwright Test (such as parallelization, emulation &amp; debugging) while running components in real browsers.\nHere is what a typical component test looks like:\nApp.spec.tsx\n```\n`import{test,expect}from\'@playwright/experimental-ct-react\';importAppfrom\'./App\';// Let\'s test component in a dark scheme!test.use({colorScheme:\'dark\'});test(\'should render\',async({mount})=&gt;{constcomponent=awaitmount(&lt;App&gt;&lt;/App&gt;);// As with any Playwright test, assert locator text.awaitexpect(component).toContainText(\'React\');// Or do a screenshot 🚀awaitexpect(component).toHaveScreenshot();// Or use any Playwright methodawaitcomponent.click();});`\n```\nRead more in\nour documentation (https://playwright.dev/docs/test-components)\n.\nRole selectors that allow selecting elements by their\nARIA role (https://www.w3.org/TR/wai-aria-1.2/#roles)\n,\nARIA attributes (https://www.w3.org/TR/wai-aria-1.2/#aria-attributes)\nand\naccessible name (https://w3c.github.io/accname/#dfn-accessible-name)\n.\n```\n`// Click a button with accessible name "log in"awaitpage.locator(\'role=button[name="log in"]\').click();`\n```\nRead more in\nour documentation (https://playwright.dev/docs/locators#locate-by-role)\n.\nNew\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nAPI to filter an existing locator\n```\n`constbuttons=page.locator(\'role=button\');// ...constsubmitButton=buttons.filter({hasText:\'Submit\'});awaitsubmitButton.click();`\n```\nNew web-first assertions\nexpect(page).toHaveScreenshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\nand\nexpect(locator).toHaveScreenshot() (https://playwright.dev/docs/api/class-locatorassertions#locator-assertions-to-have-screenshot-1)\nthat wait for screenshot stabilization and enhances test reliability.\nThe new assertions has screenshot-specific defaults, such as:\ndisables animations\nuses CSS scale option\n```\n`awaitpage.goto(\'https://playwright.dev\');awaitexpect(page).toHaveScreenshot();`\n```\nThe new\nexpect(page).toHaveScreenshot() (https://playwright.dev/docs/api/class-pageassertions#page-assertions-to-have-screenshot-1)\nsaves screenshots at the same location as\nexpect(value).toMatchSnapshot() (https://playwright.dev/docs/api/class-snapshotassertions#snapshot-assertions-to-match-snapshot-1)\n.', 'Playwright tests can be executed in CI environments. We have created sample configurations for common CI providers.\n\n3 steps to get your tests running on CI:\n\nEnsure CI agent can run browsers\n: Use\nour Docker image (https://playwright.dev/docs/docker)\nin Linux agents or install your dependencies using the\nCLI (https://playwright.dev/docs/browsers#install-system-dependencies)\n.\nInstall Playwright\n:\n```\n`# Install NPM packagesnpmci# Install Playwright browsers and dependenciesnpx playwrightinstall--with-deps`\n```\nRun your tests\n:\n```\n`npx playwrighttest`\n```']</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4222,10 +4344,10 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Neither the test nor CI is "wrong." The error message indicates that this is the first time the test has run and no "golden" reference file exists yet.
-When `toHaveScreenshot()` is executed for the first time, Playwright generates the actual screenshot and saves it to the file system. The error message you see is the expected behavior for this initial run, as the test runner is informing you that it has written the "actual" file because no baseline snapshot was found to compare against.
-To resolve this, you must add the generated snapshot file to your repository so that subsequent runs have a reference to compare against.
-The reason the test passes locally but fails on CI is due to differences in the environment. Visual comparisons are sensitive to the host OS, browser, and other factors. Because the snapshot name includes the platform and browser (e.g., `chromium-darwin`), a snapshot generated on your local machine cannot be used as the baseline for CI if the CI environment uses a different platform or browser configuration. For consistent results, you must ensure that the baseline screenshots are generated in the same environment where the tests run on CI.</t>
+          <t>Neither the test nor CI is "wrong." The error message indicates that there is no golden reference file for the screenshot in your repository.
+When you run `await expect(page).toHaveScreenshot()` for the first time, Playwright generates a reference screenshot. Because this file does not yet exist in your repository, the test runner reports that it is "writing actual" and fails the test.
+To resolve this, you must commit the generated golden file to your repository.
+Additionally, note that browser rendering can vary based on factors like the host OS, hardware, and environment settings. Because of this, screenshots are platform-specific (e.g., `chromium-darwin`). If your local environment and CI environment differ, the screenshots generated in one may not match the other. For consistent results, it is recommended to run tests in the same environment where the baseline screenshots were generated.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4234,28 +4356,28 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.0100305</v>
+        <v>0.000923</v>
       </c>
       <c r="G58" t="n">
-        <v>36702</v>
+        <v>45755</v>
       </c>
       <c r="H58" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>0.61</v>
+        <v>0.29</v>
       </c>
       <c r="J58" t="n">
         <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1015228426395939</v>
+        <v>0.1126760563380282</v>
       </c>
       <c r="L58" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="M58" t="n">
-        <v>0.999999999975</v>
+        <v>0.99999999995</v>
       </c>
       <c r="N58" t="n">
         <v>1</v>
@@ -4274,7 +4396,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>In the Actions tab you can see what locator was used for every action and how long each one took to run. Hover over each action of your test and visually see the change in the DOM snapshot. Go back and forward in time and click an action to inspect and debug. Use the Before and After tabs to visually see what happened before and after the action.\n\nSelecting each action reveals:\n\nAction snapshots\nAction log\nSource code location,</t>
+          <t>['Video | Playwright\n\nWhen browser context is created with the\n`recordVideo`\noption, each page has a video object associated with it.\n\n```\n`console.log(awaitpage.video().path());`\n```', "Playwright Test can record videos for your tests, controlled by the\n`video`\noption in your Playwright config. By default videos are off.\n\n`'off'`\n- Do not record video.\n`'on'`\n- Record video for each test.\n`'retain-on-failure'`\n- Record video for each test, but remove all videos from successful test runs.\n`'on-first-retry'`\n- Record video only when retrying a test for the first time.\n\nVideo files will appear in the test output directory, typically\n`test-results`\n. See\ntestOptions.video (https://playwright.dev/docs/api/class-testoptions#test-options-video)\nfor advanced video configuration.\n\nVideos are saved upon\nbrowser context (https://playwright.dev/docs/browser-contexts)\nclosure at the end of a test. If you create a browser context manually, make sure to await\nbrowserContext.close() (https://playwright.dev/docs/api/class-browsercontext#browser-context-close)\n.\n\nTest\nLibrary\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:'on-first-retry',},});`\n```\n```\n`constcontext=awaitbrowser.newContext({recordVideo:{dir:'videos/'}});// Make sure to await close, so that videos are saved.awaitcontext.close();`\n```\n\nYou can also specify video size and annotation. The video size defaults to the viewport size scaled down to fit 800x800. The video of the viewport is placed in the top-left corner of the output video, scaled down to fit if necessary. You may need to set the viewport size to match your desired video size.\n\nWhen\n`show: { actions }`\nis specified, each action will be visually highlighted in the video with the element outline and action title subtitle. The optional\n`duration`\nproperty controls how long each annotation is displayed (defaults to\n`500`\nms).\n\nWhen\n`show: { test }`\nis specified, video will be annotated with the current test information with configurable\n`level`\n.\n\nplaywright.config.ts\n```\n`import{defineConfig}from'@playwright/test';exportdefaultdefineConfig({use:{video:{mode:'on-first-retry',size:{width:640,height:480},show:{actions:{duration:500,position:'top-right',fontSize:14,},test:{level:'step',position:'top-left',fontSize:12,}},},},});`\n```\n\nFor multi-page scenarios, you can access the video file associated with the page via the\npage.video() (https://playwright.dev/docs/api/class-page#page-video)\n.\n\n```\n`constpath=awaitpage.video().path();`\n```\n\nnote\nNote that the video is only available after the page or browser context is closed.", "BrowserContext | Playwright\n\nBrowserContexts provide a way to operate multiple independent browser sessions.\n\nIf a page opens another page, e.g. with a\n`window.open`\ncall, the popup will belong to the parent page's browser context.\n\nPlaywright allows creating isolated non-persistent browser contexts with\nbrowser.newContext() (https://playwright.dev/docs/api/class-browser#browser-new-context)\nmethod. Non-persistent browser contexts don't write any browsing data to disk.\n\n```\n`// Create a new incognito browser contextconstcontext=awaitbrowser.newContext();// Create a new page inside context.constpage=awaitcontext.newPage();awaitpage.goto('https://example.com');// Dispose context once it's no longer needed.awaitcontext.close();`\n```", 'Added before v1.9\n\nvideo.path\n\nReturns the file system path this video will be recorded to. The video is guaranteed to be written to the filesystem upon closing the browser context. This method throws when connected remotely.\n\nUsage\n\n```\n`awaitvideo.path();`\n```\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n&gt;\n# (https://playwright.dev/docs/api/class-video#video-path-return)', 'Added in: v1.11\n\nvideo.saveAs\n\nSaves the video to a user-specified path. It is safe to call this method while the video is still in progress, or after the page has closed. This method waits until the page is closed and the video is fully saved.\n\nUsage\n\n```\n`awaitvideo.saveAs(path);`\n```\n\nArguments\n\n`path`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-video#video-save-as-option-path)\nPath where the video should be saved.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-video#video-save-as-return)', 'Added before v1.9\n\nbrowserContext.close\n\nCloses the browser context. All the pages that belong to the browser context will be closed.\n\nnote\nThe default browser context cannot be closed.\n\nUsage\n\n```\n`awaitbrowserContext.close();awaitbrowserContext.close(options);`\n```\n\nArguments\n\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`reason`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\nAdded in: v1.40\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-close-option-reason)\nThe reason to be reported to the operations interrupted by the context closure.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-browsercontext#browser-context-close-return)', 'With Playwright you can record videos for your tests.']</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4284,7 +4406,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>The video files are not being created because you are not closing the browser context. Videos are saved upon browser context closure; you must call `await context.close()` to ensure the video is saved.</t>
+          <t>You are not closing the browser context. Videos are saved upon browser context closure at the end of a test. To ensure the video file is created and saved, you must call `await context.close();` after your test operations.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4293,28 +4415,28 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.007396750000000001</v>
+        <v>0.0006395</v>
       </c>
       <c r="G59" t="n">
-        <v>28902</v>
+        <v>47806</v>
       </c>
       <c r="H59" t="n">
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="L59" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="M59" t="n">
-        <v>0.49999999995</v>
+        <v>0.5333333333155555</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
@@ -4330,7 +4452,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Trace viewer | Playwright</t>
+          <t>['warning\nWe recommend the modern\ntext locator (https://playwright.dev/docs/locators#get-by-text)\ninstead.\n\nLegacy text locator matches elements that contain passed text.\n\n```\n`awaitpage.locator(\'text=Log in\').click();`\n```\n\nLegacy text locator has a few variations:\n\n`text=Log in`\n- default matching is case-insensitive, trims whitespace and searches for a substring. For example,\n`text=Log`\nmatches\n`&lt;button&gt;Log in&lt;/button&gt;`\n.\n```\n`awaitpage.locator(\'text=Log in\').click();`\n```\n`text="Log in"`\n- text body can be escaped with single or double quotes to search for a text node with exact content after trimming whitespace.\nFor example,\n`text="Log"`\ndoes not match\n`&lt;button&gt;Log in&lt;/button&gt;`\nbecause\n`&lt;button&gt;`\ncontains a single text node\n`"Log in"`\nthat is not equal to\n`"Log"`\n. However,\n`text="Log"`\nmatches\n`&lt;button&gt; Log &lt;span&gt;in&lt;/span&gt;&lt;/button&gt;`\n, because\n`&lt;button&gt;`\ncontains a text node\n`" Log "`\n. This exact mode implies case-sensitive matching, so\n`text="Download"`\nwill not match\n`&lt;button&gt;download&lt;/button&gt;`\n.\nQuoted body follows the usual escaping rules, e.g. use\n`\\"`\nto escape double quote in a double-quoted string:\n`text="foo\\"bar"`\n.\n```\n`awaitpage.locator(\'text="Log in"\').click();`\n```\n`/Log\\s*in/i`\n- body can be a\nJavaScript-like regex (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\nwrapped in\n`/`\nsymbols. For example,\n`text=/Log\\s*in/i`\nmatches\n`&lt;button&gt;Login&lt;/button&gt;`\nand\n`&lt;button&gt;log IN&lt;/button&gt;`\n.\n```\n`awaitpage.locator(\'text=/Log\\\\s*in/i\').click();`\n```\n\nnote\nString selectors starting and ending with a quote (either\n`"`\nor\n`\'`\n) are assumed to be a legacy text locators. For example,\n`"Log in"`\nis converted to\n`text="Log in"`\ninternally.\n\nnote\nMatching always normalizes whitespace. For example, it turns multiple spaces into one, turns line breaks into spaces and ignores leading and trailing whitespace.\n\nnote\nInput elements of the type\n`button`\nand\n`submit`\nare matched by their\n`value`\ninstead of text content. For example,\n`text=Log in`\nmatches\n`&lt;input type=button value="Log in"&gt;`\n.', "Locators can be filtered by text with the\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nmethod. It will search for a particular string somewhere inside the element, possibly in a descendant element, case-insensitively. You can also pass a regular expression.\n\n```\n`awaitpage.getByRole('listitem').filter({hasText:'Product 2'}).getByRole('button',{name:'Add to cart'}).click();`\n```\n\nUse a regular expression:\n\n```\n`awaitpage.getByRole('listitem').filter({hasText:/Product 2/}).getByRole('button',{name:'Add to cart'}).click();`\n```", 'Playwright include a number of CSS pseudo-classes to match elements by their text content.\n\n`article:has-text("Playwright")`\n- the\n`:has-text()`\nmatches any element containing specified text somewhere inside, possibly in a child or a descendant element. Matching is case-insensitive, trims whitespace and searches for a substring.\nFor example,\n`article:has-text("Playwright")`\nmatches\n`&lt;article&gt;&lt;div&gt;Playwright&lt;/div&gt;&lt;/article&gt;`\n.\nNote that\n`:has-text()`\nshould be used together with other CSS specifiers, otherwise it will match all the elements containing specified text, including the\n`&lt;body&gt;`\n.\n```\n`// Wrong, will match many elements including &lt;body&gt;awaitpage.locator(\':has-text("Playwright")\').click();// Correct, only matches the &lt;article&gt; elementawaitpage.locator(\'article:has-text("Playwright")\').click();`\n```\n`#nav-bar :text("Home")`\n- the\n`:text()`\npseudo-class matches the smallest element containing specified text. Matching is case-insensitive, trims whitespace and searches for a substring.\nFor example, this will find an element with text "Home" somewhere inside the\n`#nav-bar`\nelement:\n```\n`awaitpage.locator(\'#nav-bar :text("Home")\').click();`\n```\n`#nav-bar :text-is("Home")`\n- the\n`:text-is()`\npseudo-class matches the smallest element with exact text. Exact matching is case-sensitive, trims whitespace and searches for the full string.\nFor example,\n`:text-is("Log")`\ndoes not match\n`&lt;button&gt;Log in&lt;/button&gt;`\nbecause\n`&lt;button&gt;`\ncontains a single text node\n`"Log in"`\nthat is not equal to\n`"Log"`\n. However,\n`:text-is("Log")`\nmatches\n`&lt;button&gt; Log &lt;span&gt;in&lt;/span&gt;&lt;/button&gt;`\n, because\n`&lt;button&gt;`\ncontains a text node\n`" Log "`\n.\nSimilarly,\n`:text-is("Download")`\nwill not match\n`&lt;button&gt;download&lt;/button&gt;`\nbecause it is case-sensitive.\n\n`#nav-bar :text-matches("reg?ex", "i")`\n- the\n`:text-matches()`\npseudo-class matches the smallest element with text content matching the\nJavaScript-like regex (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n.\nFor example,\n`:text-matches("Log\\s*in", "i")`\nmatches\n`&lt;button&gt;Login&lt;/button&gt;`\nand\n`&lt;button&gt;log IN&lt;/button&gt;`\n.\n\nnote\nText matching always normalizes whitespace. For example, it turns multiple spaces into one, turns line breaks into spaces and ignores leading and trailing whitespace.\n\nnote\nInput elements of the type\n`button`\nand\n`submit`\nare matched by their\n`value`\ninstead of text content. For example,\n`:text("Log in")`\nmatches\n`&lt;input type=button value="Log in"&gt;`\n.', 'Use the\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nto locate a specific item in a list.\n\nFor example, consider the following DOM structure:\n\nhttp://localhost:3000\napple\nbanana\norange\n```\n`&lt;ul&gt;&lt;li&gt;apple&lt;/li&gt;&lt;li&gt;banana&lt;/li&gt;&lt;li&gt;orange&lt;/li&gt;&lt;/ul&gt;`\n```\n\nLocate an item by the role of "listitem" and then filter by the text of "orange" and then click it.\n\n```\n`awaitpage.getByRole(\'listitem\').filter({hasText:\'orange\'}).click();`\n```', "Use the\npage.getByText() (https://playwright.dev/docs/api/class-page#page-get-by-text)\nmethod to locate an element in a list by its text content and then click on it.\n\nFor example, consider the following DOM structure:\n\nhttp://localhost:3000\napple\nbanana\norange\n```\n`&lt;ul&gt;&lt;li&gt;apple&lt;/li&gt;&lt;li&gt;banana&lt;/li&gt;&lt;li&gt;orange&lt;/li&gt;&lt;/ul&gt;`\n```\n\nLocate an item by its text content and click it.\n\n```\n`awaitpage.getByText('orange').click();`\n```", "You can narrow down query to the n-th match using the\n`nth=`\nlocator passing a zero-based index.\n\n```\n`// Click first buttonawaitpage.locator('button').locator('nth=0').click();// Click last buttonawaitpage.locator('button').locator('nth=-1').click();`\n```", 'When you have elements with various similarities, you can use the\nlocator.filter() (https://playwright.dev/docs/api/class-locator#locator-filter)\nmethod to select the right one. You can also chain multiple filters to narrow down the selection.\n\nFor example, consider the following DOM structure:\n\nhttp://localhost:3000\nJohn\nSay hello\nMary\nSay hello\nJohn\nSay goodbye\nMary\nSay goodbye\n```\n`&lt;ul&gt;&lt;li&gt;&lt;div&gt;John&lt;/div&gt;&lt;div&gt;&lt;button&gt;Say hello&lt;/button&gt;&lt;/div&gt;&lt;/li&gt;&lt;li&gt;&lt;div&gt;Mary&lt;/div&gt;&lt;div&gt;&lt;button&gt;Say hello&lt;/button&gt;&lt;/div&gt;&lt;/li&gt;&lt;li&gt;&lt;div&gt;John&lt;/div&gt;&lt;div&gt;&lt;button&gt;Say goodbye&lt;/button&gt;&lt;/div&gt;&lt;/li&gt;&lt;li&gt;&lt;div&gt;Mary&lt;/div&gt;&lt;div&gt;&lt;button&gt;Say goodbye&lt;/button&gt;&lt;/div&gt;&lt;/li&gt;&lt;/ul&gt;`\n```\n\nTo take a screenshot of the row with "Mary" and "Say goodbye":\n\n```\n`constrowLocator=page.getByRole(\'listitem\');awaitrowLocator.filter({hasText:\'Mary\'}).filter({has:page.getByRole(\'button\',{name:\'Say goodbye\'})}).screenshot({path:\'screenshot.png\'});`\n```\n\nYou should now have a "screenshot.png" file in your project\'s root directory.']</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4340,16 +4462,13 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>The `:has-text("Playwright")` selector matches the `&lt;body&gt;` element because the text "Playwright" is contained within the body's descendant tree, and `:has-text` matches any element that contains the specified text.
-To narrow this to the specific element you want, the documentation recommends prioritizing **role locators** (`page.getByRole()`), as they reflect how users and assistive technology perceive the page. 
-You can refine your selection using the following approaches:
-*   **Use `page.getByRole()`:** Instead of searching by text, identify the element by its role (e.g., 'button', 'link', 'heading') and its accessible name.
-    *   Example: `await page.getByRole('button', { name: 'Playwright' }).click();`
-*   **Chain locators:** You can narrow the search by chaining locators to target a specific part of the page.
-    *   Example: `await page.getByTestId('card-container').getByText('Playwright').click();`
-*   **Filter:** You can use the `.filter()` method to narrow down a locator.
-    *   Example: `await page.locator('div').filter({ hasText: 'Playwright' }).click();`
-Additionally, you can use the **Pick locator** feature in UI Mode to hover over the element in the DOM snapshot, which will help you identify and test a more specific locator before adding it to your code.</t>
+          <t>The `:has-text()` pseudo-class matches any element containing the specified text somewhere inside it, including descendants. Because it is not used with other CSS specifiers, it matches all elements containing that text, which is why it resolves to many elements, including the `&lt;body&gt;`.
+To narrow this down to the specific element you want, you have several options:
+*   **Use a more specific CSS selector:** Combine `:has-text()` with another CSS specifier (e.g., `article:has-text("Playwright")`) to restrict the scope.
+*   **Use `:text()` or `:text-is()`:** These pseudo-classes match the smallest element containing the text, rather than any ancestor containing it. `:text()` performs a substring match, while `:text-is()` requires an exact match.
+*   **Use `locator.filter()`:** You can filter a locator by text using `locator.filter({hasText: 'Playwright'})`. This is useful for narrowing down a list of elements.
+*   **Use `page.getByText()`:** This method locates an element by its text content.
+*   **Use `nth=`:** If you have multiple matches and know the position, you can use `locator('nth=0')` to select the first match.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4358,31 +4477,31 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.01180775</v>
+        <v>0.00111775</v>
       </c>
       <c r="G60" t="n">
-        <v>42371</v>
+        <v>43794</v>
       </c>
       <c r="H60" t="n">
         <v>0.5</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="J60" t="n">
         <v>5</v>
       </c>
       <c r="K60" t="n">
-        <v>0.0918918918918919</v>
+        <v>0.1502890173410405</v>
       </c>
       <c r="L60" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>0.3095238095083334</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -4397,7 +4516,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>]</t>
+          <t>['Added before v1.9\n\npage.waitForLoadState\n\nReturns when the required load state has been reached.\n\nThis resolves when the page reaches a required load state,\n`load`\nby default. The navigation must have been committed when this method is called. If current document has already reached the required state, resolves immediately.\n\nnote\nMost of the time, this method is not needed because Playwright\nauto-waits before every action (https://playwright.dev/docs/actionability)\n.\n\nUsage\n\n```\n`awaitpage.getByRole(\'button\').click();// Click triggers navigation.awaitpage.waitForLoadState();// The promise resolves after \'load\' event.`\n```\n\n```\n`constpopupPromise=page.waitForEvent(\'popup\');awaitpage.getByRole(\'button\').click();// Click triggers a popup.constpopup=awaitpopupPromise;awaitpopup.waitForLoadState(\'domcontentloaded\');// Wait for the \'DOMContentLoaded\' event.console.log(awaitpopup.title());// Popup is ready to use.`\n```\n\nArguments\n\n`state`\n"load" | "domcontentloaded" | "networkidle"\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-load-state-option-state)\nOptional load state to wait for, defaults to\n`load`\n. If the state has been already reached while loading current document, the method resolves immediately. Can be one of:\n`\'load\'`\n- wait for the\n`load`\nevent to be fired.\n`\'domcontentloaded\'`\n- wait for the\n`DOMContentLoaded`\nevent to be fired.\n`\'networkidle\'`\n-\nDISCOURAGED\nwait until there are no network connections for at least\n`500`\nms. Don\'t use this method for testing, rely on web assertions to assess readiness instead.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-load-state-option-timeout)\nMaximum operation time in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`navigationTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultNavigationTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-navigation-timeout)\n,\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\n,\npage.setDefaultNavigationTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-navigation-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-page#page-wait-for-load-state-return)', 'Added before v1.9\n\npage.goto\n\nReturns the main resource response. In case of multiple redirects, the navigation will resolve with the first non-redirect response.\n\nThe method will throw an error if:\n\nthere\'s an SSL error (e.g. in case of self-signed certificates).\ntarget URL is invalid.\nthe\ntimeout (https://playwright.dev/docs/api/class-page#page-goto-option-timeout)\nis exceeded during navigation.\nthe remote server does not respond or is unreachable.\nthe main resource failed to load.\n\nThe method will not throw an error when any valid HTTP status code is returned by the remote server, including 404 "Not Found" and 500 "Internal Server Error".  The status code for such responses can be retrieved by calling\nresponse.status() (https://playwright.dev/docs/api/class-response#response-status)\n.\n\nnote\nThe method either throws an error or returns a main resource response. The only exceptions are navigation to\n`about:blank`\nor navigation to the same URL with a different hash, which would succeed and return\n`null`\n.\n\nnote\nHeadless mode doesn\'t support navigation to a PDF document. See the\nupstream issue (https://bugs.chromium.org/p/chromium/issues/detail?id=761295)\n.\n\nUsage\n\n```\n`awaitpage.goto(url);awaitpage.goto(url,options);`\n```\n\nArguments\n\n`url`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-page#page-goto-option-url)\nURL to navigate page to. The url should include scheme, e.g.\n`https://`\n. When a\nbaseURL (https://playwright.dev/docs/api/class-browser#browser-new-context-option-base-url)\nvia the context options was provided and the passed URL is a path, it gets merged via the\nnew URL() (https://developer.mozilla.org/en-US/docs/Web/API/URL/URL)\nconstructor.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`referer`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-goto-option-referer)\nReferer header value. If provided it will take preference over the referer header value set by\npage.setExtraHTTPHeaders() (https://playwright.dev/docs/api/class-page#page-set-extra-http-headers)\n.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-goto-option-timeout)\nMaximum operation time in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`navigationTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultNavigationTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-navigation-timeout)\n,\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\n,\npage.setDefaultNavigationTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-navigation-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n`waitUntil`\n"load" | "domcontentloaded" | "networkidle" | "commit"\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-goto-option-wait-until)\nWhen to consider operation succeeded, defaults to\n`load`\n. Events can be either:\n`\'domcontentloaded\'`\n- consider operation to be finished when the\n`DOMContentLoaded`\nevent is fired.\n`\'load\'`\n- consider operation to be finished when the\n`load`\nevent is fired.\n`\'networkidle\'`\n-\nDISCOURAGED\nconsider operation to be finished when there are no network connections for at least\n`500`\nms. Don\'t use this method for testing, rely on web assertions to assess readiness instead.\n`\'commit\'`\n- consider operation to be finished when network response is received and the document started loading.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nnull (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/null)\n|\nResponse (https://playwright.dev/docs/api/class-response)\n&gt;\n# (https://playwright.dev/docs/api/class-page#page-goto-return)', 'Added before v1.9\n\npage.waitForFunction\n\nReturns when the\npageFunction (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-expression)\nreturns a truthy value. It resolves to a JSHandle of the truthy value.\n\nUsage\n\nThe\npage.waitForFunction() (https://playwright.dev/docs/api/class-page#page-wait-for-function)\ncan be used to observe viewport size change:\n\n```\n`const{webkit}=require(\'playwright\');// Or \'chromium\' or \'firefox\'.(async()=&gt;{constbrowser=awaitwebkit.launch();constpage=awaitbrowser.newPage();constwatchDog=page.waitForFunction(()=&gt;window.innerWidth&lt;100);awaitpage.setViewportSize({width:50,height:50});awaitwatchDog;awaitbrowser.close();})();`\n```\n\nTo pass an argument to the predicate of\npage.waitForFunction() (https://playwright.dev/docs/api/class-page#page-wait-for-function)\nfunction:\n\n```\n`constselector=\'.foo\';awaitpage.waitForFunction(selector=&gt;!!document.querySelector(selector),selector);`\n```\n\nArguments\n\n`pageFunction`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n|\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-expression)\nFunction to be evaluated in the page context.\n`arg`\nEvaluationArgument (https://playwright.dev/docs/evaluating#evaluation-argument)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-arg)\nOptional argument to pass to\npageFunction (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-expression)\n.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`polling`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n| "raf"\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-polling)\nIf\npolling (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-polling)\nis\n`\'raf\'`\n, then\npageFunction (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-expression)\nis constantly executed in\n`requestAnimationFrame`\ncallback. If\npolling (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-polling)\nis a number, then it is treated as an interval in milliseconds at which the function would be executed. Defaults to\n`raf`\n.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-function-option-timeout)\nMaximum time to wait for in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`actionTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nJSHandle (https://playwright.dev/docs/api/class-jshandle)\n&gt;\n# (https://playwright.dev/docs/api/class-page#page-wait-for-function-return)', 'Added before v1.9\n\npage.waitForSelector\n\nDiscouraged\nUse web assertions that assert visibility or a locator-based\nlocator.waitFor() (https://playwright.dev/docs/api/class-locator#locator-wait-for)\ninstead. Read more about\nlocators (https://playwright.dev/docs/locators)\n.\n\nReturns when element specified by selector satisfies\nstate (https://playwright.dev/docs/api/class-page#page-wait-for-selector-option-state)\noption. Returns\n`null`\nif waiting for\n`hidden`\nor\n`detached`\n.\n\nnote\nPlaywright automatically waits for element to be ready before performing an action. Using\nLocator (https://playwright.dev/docs/api/class-locator)\nobjects and web-first assertions makes the code wait-for-selector-free.\n\nWait for the\nselector (https://playwright.dev/docs/api/class-page#page-wait-for-selector-option-selector)\nto satisfy\nstate (https://playwright.dev/docs/api/class-page#page-wait-for-selector-option-state)\noption (either appear/disappear from dom, or become visible/hidden). If at the moment of calling the method\nselector (https://playwright.dev/docs/api/class-page#page-wait-for-selector-option-selector)\nalready satisfies the condition, the method will return immediately. If the selector doesn\'t satisfy the condition for the\ntimeout (https://playwright.dev/docs/api/class-page#page-wait-for-selector-option-timeout)\nmilliseconds, the function will throw.\n\nUsage\n\nThis method works across navigations:\n\n```\n`const{chromium}=require(\'playwright\');// Or \'firefox\' or \'webkit\'.(async()=&gt;{constbrowser=awaitchromium.launch();constpage=awaitbrowser.newPage();for(constcurrentURLof[\'https://google.com\',\'https://bbc.com\']){awaitpage.goto(currentURL);constelement=awaitpage.waitForSelector(\'img\');console.log(\'Loaded image: \'+awaitelement.getAttribute(\'src\'));}awaitbrowser.close();})();`\n```\n\nArguments\n\n`selector`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-selector-option-selector)\nA selector to query for.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`state`\n"attached" | "detached" | "visible" | "hidden"\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-selector-option-state)\nDefaults to\n`\'visible\'`\n. Can be either:\n`\'attached\'`\n- wait for element to be present in DOM.\n`\'detached\'`\n- wait for element to not be present in DOM.\n`\'visible\'`\n- wait for element to have non-empty bounding box and no\n`visibility:hidden`\n. Note that element without any content or with\n`display:none`\nhas an empty bounding box and is not considered visible.\n`\'hidden\'`\n- wait for element to be either detached from DOM, or have an empty bounding box or\n`visibility:hidden`\n. This is opposite to the\n`\'visible\'`\noption.\n`strict`\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n(optional)\nAdded in: v1.14\n# (https://playwright.dev/docs/api/class-page#page-wait-for-selector-option-strict)\nWhen true, the call requires selector to resolve to a single element. If given selector resolves to more than one element, the call throws an exception.\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-selector-option-timeout)\nMaximum time in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`actionTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nnull (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/null)\n|\nElementHandle (https://playwright.dev/docs/api/class-elementhandle)\n&gt;\n# (https://playwright.dev/docs/api/class-page#page-wait-for-selector-return)', 'Added in: v1.11\n\npage.waitForURL\n\nWaits for the main frame to navigate to the given URL.\n\nUsage\n\n```\n`awaitpage.click(\'a.delayed-navigation\');// Clicking the link will indirectly cause a navigationawaitpage.waitForURL(\'**/target.html\');`\n```\n\nArguments\n\n`url`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n|\nURLPattern (https://developer.mozilla.org/en-US/docs/Web/API/URLPattern)\n|\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n(\nURL (https://nodejs.org/api/url.html)\n):\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-url-option-url)\nA glob pattern, regex pattern, URL pattern, or predicate receiving\nURL (https://nodejs.org/api/url.html)\nto match while waiting for the navigation. Note that if the parameter is a string without wildcard characters, the method will wait for navigation to URL that is exactly equal to the string.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-url-option-timeout)\nMaximum operation time in milliseconds. Defaults to\n`0`\n- no timeout. The default value can be changed via\n`navigationTimeout`\noption in the config, or by using the\nbrowserContext.setDefaultNavigationTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-navigation-timeout)\n,\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\n,\npage.setDefaultNavigationTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-navigation-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n`waitUntil`\n"load" | "domcontentloaded" | "networkidle" | "commit"\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-url-option-wait-until)\nWhen to consider operation succeeded, defaults to\n`load`\n. Events can be either:\n`\'domcontentloaded\'`\n- consider operation to be finished when the\n`DOMContentLoaded`\nevent is fired.\n`\'load\'`\n- consider operation to be finished when the\n`load`\nevent is fired.\n`\'networkidle\'`\n-\nDISCOURAGED\nconsider operation to be finished when there are no network connections for at least\n`500`\nms. Don\'t use this method for testing, rely on web assertions to assess readiness instead.\n`\'commit\'`\n- consider operation to be finished when network response is received and the document started loading.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nvoid (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/undefined)\n&gt;\n# (https://playwright.dev/docs/api/class-page#page-wait-for-url-return)', "Added before v1.9\n\npage.waitForRequest\n\nWaits for the matching request and returns it. See\nwaiting for event (https://playwright.dev/docs/events#waiting-for-event)\nfor more details about events.\n\nUsage\n\n```\n`// Start waiting for request before clicking. Note no await.constrequestPromise=page.waitForRequest('https://example.com/resource');awaitpage.getByText('trigger request').click();constrequest=awaitrequestPromise;// Alternative way with a predicate. Note no await.constrequestPromise=page.waitForRequest(request=&gt;request.url()==='https://example.com'&amp;&amp;request.method()==='GET',);awaitpage.getByText('trigger request').click();constrequest=awaitrequestPromise;`\n```\n\nArguments\n\n`urlOrPredicate`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n|\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n(\nRequest (https://playwright.dev/docs/api/class-request)\n):\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n|\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n&gt;\n# (https://playwright.dev/docs/api/class-page#page-wait-for-request-option-url-or-predicate)\nRequest URL string, regex or predicate receiving\nRequest (https://playwright.dev/docs/api/class-request)\nobject.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-request-option-timeout)\nMaximum wait time in milliseconds, defaults to 30 seconds, pass\n`0`\nto disable the timeout. The default value can be changed by using the\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethod.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nRequest (https://playwright.dev/docs/api/class-request)\n&gt;\n# (https://playwright.dev/docs/api/class-page#page-wait-for-request-return)", "Added before v1.9\n\npage.waitForResponse\n\nReturns the matched response. See\nwaiting for event (https://playwright.dev/docs/events#waiting-for-event)\nfor more details about events.\n\nUsage\n\n```\n`// Start waiting for response before clicking. Note no await.constresponsePromise=page.waitForResponse('https://example.com/resource');awaitpage.getByText('trigger response').click();constresponse=awaitresponsePromise;// Alternative way with a predicate. Note no await.constresponsePromise=page.waitForResponse(response=&gt;response.url()==='https://example.com'&amp;&amp;response.status()===200&amp;&amp;response.request().method()==='GET');awaitpage.getByText('trigger response').click();constresponse=awaitresponsePromise;`\n```\n\nArguments\n\n`urlOrPredicate`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n|\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n(\nResponse (https://playwright.dev/docs/api/class-response)\n):\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n|\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n&gt;\n# (https://playwright.dev/docs/api/class-page#page-wait-for-response-option-url-or-predicate)\nRequest URL string, regex or predicate receiving\nResponse (https://playwright.dev/docs/api/class-response)\nobject. When a\nbaseURL (https://playwright.dev/docs/api/class-browser#browser-new-context-option-base-url)\nvia the context options was provided and the passed URL is a path, it gets merged via the\nnew URL() (https://developer.mozilla.org/en-US/docs/Web/API/URL/URL)\nconstructor.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`timeout`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\n# (https://playwright.dev/docs/api/class-page#page-wait-for-response-option-timeout)\nMaximum wait time in milliseconds, defaults to 30 seconds, pass\n`0`\nto disable the timeout. The default value can be changed by using the\nbrowserContext.setDefaultTimeout() (https://playwright.dev/docs/api/class-browsercontext#browser-context-set-default-timeout)\nor\npage.setDefaultTimeout() (https://playwright.dev/docs/api/class-page#page-set-default-timeout)\nmethods.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nResponse (https://playwright.dev/docs/api/class-response)\n&gt;\n# (https://playwright.dev/docs/api/class-page#page-wait-for-response-return)"]</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4407,17 +4526,9 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>To wait for readiness in a way that avoids flakiness, you should use Playwright's auto-retrying assertions instead of `waitForLoadState`.
-Playwright includes async matchers that wait until the expected condition is met. For your specific case, you should use the `toBeVisible()` assertion on your locator:
-```javascript
-await page.goto('/dashboard');
-await expect(page.getByRole('heading', { name: 'Welcome' })).toBeVisible();
-```
-**Why this is recommended:**
-*   **Auto-retrying:** These assertions automatically retry until the condition is met, which removes flakiness.
-*   **Resilience:** Unlike `waitForLoadState`, which waits for network activity to cease, assertions focus on the actual state of the UI, making them better suited for single-page applications with ongoing polling or analytics.
-**Alternatives:**
-If you need to wait for a specific condition that is not covered by standard assertions, you can use `page.waitForFunction()`, which executes a function in the page context and returns when it evaluates to a truthy value. Additionally, if you need to wait for a specific network event, you can use `page.waitForResponse()`.</t>
+          <t>The use of `networkidle` is discouraged by the documentation, which explicitly advises against using it for testing and recommends relying on web assertions to assess readiness instead.
+To wait for readiness in your single-page app, you should use web-first assertions. Since you are already using `await expect(page.getByRole('heading', { name: 'Welcome' })).toBeVisible();`, you are correctly using a web assertion. Playwright automatically waits for elements to be ready before performing actions, and these assertions will poll until the condition is met or the timeout is reached.
+If you need to wait for specific conditions that are not covered by standard assertions, you can use `page.waitForFunction()` to observe state changes in the page context.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4426,28 +4537,28 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.01280775</v>
+        <v>0.00207075</v>
       </c>
       <c r="G61" t="n">
-        <v>48161</v>
+        <v>70142</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="J61" t="n">
         <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>0.08536585365853659</v>
+        <v>0.2155172413793103</v>
       </c>
       <c r="L61" t="n">
-        <v>0.3111111111111111</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8333333333055556</v>
+        <v>0.8874999999778125</v>
       </c>
       <c r="N61" t="n">
         <v>1</v>
@@ -4465,7 +4576,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>["Playwright's built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nallow your tests to natively route requests and perform mocking and interception.\n\nIf you're using Playwright's native\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n, and it appears network events are missing, disable Service Workers by setting\nserviceWorkers (https://playwright.dev/docs/api/class-browser#browser-new-context-option-service-workers)\nto\n`'block'`\n.\n\nIt might be that you are using a mock tool such as Mock Service Worker (MSW). While this tool works out of the box for mocking responses, it adds its own Service Worker that takes over the network requests, hence making them invisible to\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n. If you are interested in both network testing and mocking, consider using built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nfor\nresponse mocking (https://playwright.dev/docs/network#handle-requests)\n.", 'Mock APIs | Playwright', 'Network | Playwright', 'Route | Playwright\n\nWhenever a network route is set up with\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nor\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n, the\n`Route`\nobject allows to handle the route.\n\nLearn more about\nnetworking (https://playwright.dev/docs/network)\n.', 'Service Workers | Playwright', 'Components (experimental) | Playwright']</t>
+          <t>["Playwright's built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nallow your tests to natively route requests and perform mocking and interception.\n\nIf you're using Playwright's native\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n, and it appears network events are missing, disable Service Workers by setting\nserviceWorkers (https://playwright.dev/docs/api/class-browser#browser-new-context-option-service-workers)\nto\n`'block'`\n.\n\nIt might be that you are using a mock tool such as Mock Service Worker (MSW). While this tool works out of the box for mocking responses, it adds its own Service Worker that takes over the network requests, hence making them invisible to\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\n. If you are interested in both network testing and mocking, consider using built-in\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\nand\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nfor\nresponse mocking (https://playwright.dev/docs/network#handle-requests)\n.", "Added before v1.9\n\npage.route\n\nRouting provides the capability to modify network requests that are made by a page.\n\nOnce routing is enabled, every request matching the url pattern will stall unless it's continued, fulfilled or aborted.\n\nnote\nThe handler will only be called for the first url if the response is a redirect.\n\nnote\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nwill not intercept requests intercepted by Service Worker. See\nthis (https://github.com/microsoft/playwright/issues/1090)\nissue. We recommend disabling Service Workers when using request interception by setting\nserviceWorkers (https://playwright.dev/docs/api/class-browser#browser-new-context-option-service-workers)\nto\n`'block'`\n.\n\nnote\npage.route() (https://playwright.dev/docs/api/class-page#page-route)\nwill not intercept the first request of a popup page. Use\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\ninstead.\n\nUsage\n\nAn example of a naive handler that aborts all image requests:\n\n```\n`constpage=awaitbrowser.newPage();awaitpage.route('**/*.{png,jpg,jpeg}',route=&gt;route.abort());awaitpage.goto('https://example.com');awaitbrowser.close();`\n```\n\nor the same snippet using a regex pattern instead:\n\n```\n`constpage=awaitbrowser.newPage();awaitpage.route(/(\\.png$)|(\\.jpg$)/,route=&gt;route.abort());awaitpage.goto('https://example.com');awaitbrowser.close();`\n```\n\nIt is possible to examine the request to decide the route action. For example, mocking all requests that contain some post data, and leaving all other requests as is:\n\n```\n`awaitpage.route('/api/**',asyncroute=&gt;{if(route.request().postData().includes('my-string'))awaitroute.fulfill({body:'mocked-data'});elseawaitroute.continue();});`\n```\n\nIf a request matches multiple registered routes, the most recently registered route takes precedence.\n\nPage routes take precedence over browser context routes (set up with\nbrowserContext.route() (https://playwright.dev/docs/api/class-browsercontext#browser-context-route)\n) when request matches both handlers.\n\nTo remove a route with its handler you can use\npage.unroute() (https://playwright.dev/docs/api/class-page#page-unroute)\n.\n\nnote\nEnabling routing disables http cache.\n\nArguments\n\n`url`\nstring (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#String_type)\n|\nRegExp (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/RegExp)\n|\nURLPattern (https://developer.mozilla.org/en-US/docs/Web/API/URLPattern)\n|\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n(\nURL (https://nodejs.org/api/url.html)\n):\nboolean (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Boolean_type)\n# (https://playwright.dev/docs/api/class-page#page-route-option-url)\nA glob pattern, regex pattern, URL pattern, or predicate that receives a\nURL (https://nodejs.org/api/url.html)\nto match during routing. If\nbaseURL (https://playwright.dev/docs/api/class-browser#browser-new-context-option-base-url)\nis set in the context options and the provided URL is a string that does not start with\n`*`\n, it is resolved using the\nnew URL() (https://developer.mozilla.org/en-US/docs/Web/API/URL/URL)\nconstructor.\n`handler`\nfunction (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Function)\n(\nRoute (https://playwright.dev/docs/api/class-route)\n,\nRequest (https://playwright.dev/docs/api/class-request)\n):\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Promise)\n&lt;\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n&gt; |\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n# (https://playwright.dev/docs/api/class-page#page-route-option-handler)\nhandler function to route the request.\n`options`\nObject (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Object)\n(optional)\n`times`\nnumber (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Data_structures#Number_type)\n(optional)\nAdded in: v1.15\n# (https://playwright.dev/docs/api/class-page#page-route-option-times)\nHow often a route should be used. By default it will be used every time.\n\nReturns\n\nPromise (https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objec